--- a/Versão5/ABNT/Ontologia_NBR15965_2N.xlsx
+++ b/Versão5/ABNT/Ontologia_NBR15965_2N.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Construtor_Onto\ABNT\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AEE80F49-A154-4014-8AE3-498F3BF4CA3B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A9C3EC98-90B8-4049-94DD-D79BDCCF9392}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="24240" windowHeight="13290" activeTab="1" xr2:uid="{82C81399-C775-48F3-A336-58DE5F35A6D9}"/>
+    <workbookView xWindow="-103" yWindow="-103" windowWidth="22149" windowHeight="13200" activeTab="1" xr2:uid="{82C81399-C775-48F3-A336-58DE5F35A6D9}"/>
   </bookViews>
   <sheets>
     <sheet name="Projeto" sheetId="8" r:id="rId1"/>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4329" uniqueCount="567">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4329" uniqueCount="568">
   <si>
     <t>Indivíduo</t>
   </si>
@@ -1761,12 +1761,6 @@
     <t>NBR.Temáticas</t>
   </si>
   <si>
-    <t>[ OST_Materials ]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">[ IfcMaterial ] </t>
-  </si>
-  <si>
     <t>[ - ]</t>
   </si>
   <si>
@@ -1782,16 +1776,25 @@
     <t>[ OST_Rooms : OST_MEPSpaces : OST_MEPSystemZone ]</t>
   </si>
   <si>
-    <t>[ IfcSpace ]</t>
-  </si>
-  <si>
-    <t>[ IfcProperty ]</t>
-  </si>
-  <si>
     <t>[ OST_Sheets : OST_TitleBlocks : OST_Revisions : OST_RevisionNumberingSequences ]</t>
   </si>
   <si>
     <t>[ IfcAnnotation ]</t>
+  </si>
+  <si>
+    <t>[ OST_Materials : OST_MaterialTags ]</t>
+  </si>
+  <si>
+    <t>[ IfcMaterial : IfcText : IfcLabel : IfcMaterialRelationship ]</t>
+  </si>
+  <si>
+    <t>[ BuiltInParameter ]</t>
+  </si>
+  <si>
+    <t>[ IfcProperty : IfcIdentifier : IfcText ]</t>
+  </si>
+  <si>
+    <t>[ IfcSpace : IfcRelSpaceBoundary : IfcSpaceType : IfcSpaceTypeEnum ]</t>
   </si>
 </sst>
 </file>
@@ -2387,7 +2390,7 @@
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
     <cellStyle name="Normal 2" xfId="1" xr:uid="{A0D90F96-026A-4EEB-BDCF-93327D239D7A}"/>
   </cellStyles>
-  <dxfs count="61">
+  <dxfs count="62">
     <dxf>
       <font>
         <b val="0"/>
@@ -2427,6 +2430,13 @@
         <b val="0"/>
         <i/>
         <strike val="0"/>
+        <color theme="0" tint="-0.499984740745262"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i/>
         <color theme="0" tint="-0.499984740745262"/>
       </font>
     </dxf>
@@ -4242,33 +4252,33 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{A07C259E-03F8-41A3-821C-289758C0BF1B}" name="Tabla2" displayName="Tabla2" ref="A2:Y157" headerRowCount="0" totalsRowShown="0" headerRowDxfId="60" dataDxfId="58" headerRowBorderDxfId="59" tableBorderDxfId="57" totalsRowBorderDxfId="56">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{A07C259E-03F8-41A3-821C-289758C0BF1B}" name="Tabla2" displayName="Tabla2" ref="A2:Y157" headerRowCount="0" totalsRowShown="0" headerRowDxfId="61" dataDxfId="59" headerRowBorderDxfId="60" tableBorderDxfId="58" totalsRowBorderDxfId="57">
   <tableColumns count="25">
-    <tableColumn id="1" xr3:uid="{D841A366-4823-4EF9-B009-219AA94AF50A}" name="1" headerRowDxfId="55" dataDxfId="54"/>
-    <tableColumn id="2" xr3:uid="{41E717E1-E3DE-44C1-91C4-719DAB59A464}" name="Indivíduo" headerRowDxfId="53" dataDxfId="52"/>
-    <tableColumn id="3" xr3:uid="{38346B1D-47C6-4B44-A19C-766D16435669}" name="Classe" headerRowDxfId="51" dataDxfId="50"/>
-    <tableColumn id="5" xr3:uid="{27FF4C79-5131-4593-84DE-98F435DB6954}" name="Coluna2" headerRowDxfId="49" dataDxfId="48"/>
-    <tableColumn id="4" xr3:uid="{B4C1140F-50EB-4951-8734-6338EB3CF628}" name="Coluna1" headerRowDxfId="47" dataDxfId="46"/>
-    <tableColumn id="11" xr3:uid="{1EE4C35C-9E89-4C7C-8F68-2AC866434D95}" name="Coluna8" headerRowDxfId="45" dataDxfId="44"/>
-    <tableColumn id="10" xr3:uid="{0C28831F-E05A-4812-BB49-6E3DB059FDDA}" name="Coluna7" headerRowDxfId="43" dataDxfId="42"/>
-    <tableColumn id="9" xr3:uid="{C46F6396-5D54-4379-8FE7-47754ED408FB}" name="Coluna6" headerRowDxfId="41" dataDxfId="40"/>
-    <tableColumn id="14" xr3:uid="{7255F88A-C196-4C7D-BC78-487E43C6076E}" name="Coluna9" headerRowDxfId="39" dataDxfId="38"/>
-    <tableColumn id="15" xr3:uid="{CB39996D-E39C-41DF-9024-09188503F3A9}" name="Coluna10" headerRowDxfId="37" dataDxfId="36"/>
-    <tableColumn id="8" xr3:uid="{DC6BCDF7-14DD-4B0D-951F-937897AADF11}" name="Coluna5" headerRowDxfId="35" dataDxfId="34"/>
-    <tableColumn id="25" xr3:uid="{6E36A2EC-C3DA-4DF1-80AB-262ECBFDA8D3}" name="Coluna20" headerRowDxfId="33" dataDxfId="32"/>
-    <tableColumn id="24" xr3:uid="{7DA1B28C-8D87-49B1-8B12-94BDA4E3634B}" name="Coluna19" headerRowDxfId="31" dataDxfId="30"/>
-    <tableColumn id="12" xr3:uid="{72731FBF-D3F4-42FD-AF7E-09CD79716DE3}" name="Fato (11)" headerRowDxfId="29" dataDxfId="28"/>
-    <tableColumn id="13" xr3:uid="{40ED8FBD-39D6-4C0F-867B-9AA8C9C09316}" name="Valor8" headerRowDxfId="27" dataDxfId="26"/>
-    <tableColumn id="6" xr3:uid="{D7E37E62-C3F1-48D0-9ECE-1603C43E1947}" name="Coluna3" headerRowDxfId="25" dataDxfId="24"/>
-    <tableColumn id="7" xr3:uid="{8EAEA0F2-9F55-4FEE-86F2-D1912AEFC7F4}" name="Coluna4" headerRowDxfId="23" dataDxfId="22"/>
-    <tableColumn id="16" xr3:uid="{CB767617-3A28-42EC-8E47-CE6204F6D856}" name="Coluna11" headerRowDxfId="21" dataDxfId="20"/>
-    <tableColumn id="17" xr3:uid="{E29ADF84-36FF-41F7-9847-17BC340BAE5F}" name="Coluna12" headerRowDxfId="19" dataDxfId="18"/>
-    <tableColumn id="18" xr3:uid="{B5ADD4A7-EE28-45D9-B6FF-C285C2CD6E37}" name="Coluna13" headerRowDxfId="17" dataDxfId="16"/>
-    <tableColumn id="19" xr3:uid="{7FEDF53D-D312-4CF1-8EB3-4A56B77DEAA1}" name="Coluna14" headerRowDxfId="15" dataDxfId="14"/>
-    <tableColumn id="20" xr3:uid="{44C51568-5619-4D1B-B5B4-F2CF79CAB094}" name="Coluna15" headerRowDxfId="13" dataDxfId="12"/>
-    <tableColumn id="21" xr3:uid="{2A7C2A78-BAF9-429F-B898-EF931D80D830}" name="Coluna16" headerRowDxfId="11" dataDxfId="10"/>
-    <tableColumn id="22" xr3:uid="{3BB87186-A8C3-4EE2-9555-ACB7C40B9882}" name="Coluna17" headerRowDxfId="9" dataDxfId="8"/>
-    <tableColumn id="23" xr3:uid="{C574DFC8-E441-4BB1-A97D-83D5A9C08508}" name="Coluna18" headerRowDxfId="7" dataDxfId="6"/>
+    <tableColumn id="1" xr3:uid="{D841A366-4823-4EF9-B009-219AA94AF50A}" name="1" headerRowDxfId="56" dataDxfId="55"/>
+    <tableColumn id="2" xr3:uid="{41E717E1-E3DE-44C1-91C4-719DAB59A464}" name="Indivíduo" headerRowDxfId="54" dataDxfId="53"/>
+    <tableColumn id="3" xr3:uid="{38346B1D-47C6-4B44-A19C-766D16435669}" name="Classe" headerRowDxfId="52" dataDxfId="51"/>
+    <tableColumn id="5" xr3:uid="{27FF4C79-5131-4593-84DE-98F435DB6954}" name="Coluna2" headerRowDxfId="50" dataDxfId="49"/>
+    <tableColumn id="4" xr3:uid="{B4C1140F-50EB-4951-8734-6338EB3CF628}" name="Coluna1" headerRowDxfId="48" dataDxfId="47"/>
+    <tableColumn id="11" xr3:uid="{1EE4C35C-9E89-4C7C-8F68-2AC866434D95}" name="Coluna8" headerRowDxfId="46" dataDxfId="45"/>
+    <tableColumn id="10" xr3:uid="{0C28831F-E05A-4812-BB49-6E3DB059FDDA}" name="Coluna7" headerRowDxfId="44" dataDxfId="43"/>
+    <tableColumn id="9" xr3:uid="{C46F6396-5D54-4379-8FE7-47754ED408FB}" name="Coluna6" headerRowDxfId="42" dataDxfId="41"/>
+    <tableColumn id="14" xr3:uid="{7255F88A-C196-4C7D-BC78-487E43C6076E}" name="Coluna9" headerRowDxfId="40" dataDxfId="39"/>
+    <tableColumn id="15" xr3:uid="{CB39996D-E39C-41DF-9024-09188503F3A9}" name="Coluna10" headerRowDxfId="38" dataDxfId="37"/>
+    <tableColumn id="8" xr3:uid="{DC6BCDF7-14DD-4B0D-951F-937897AADF11}" name="Coluna5" headerRowDxfId="36" dataDxfId="35"/>
+    <tableColumn id="25" xr3:uid="{6E36A2EC-C3DA-4DF1-80AB-262ECBFDA8D3}" name="Coluna20" headerRowDxfId="34" dataDxfId="33"/>
+    <tableColumn id="24" xr3:uid="{7DA1B28C-8D87-49B1-8B12-94BDA4E3634B}" name="Coluna19" headerRowDxfId="32" dataDxfId="31"/>
+    <tableColumn id="12" xr3:uid="{72731FBF-D3F4-42FD-AF7E-09CD79716DE3}" name="Fato (11)" headerRowDxfId="30" dataDxfId="29"/>
+    <tableColumn id="13" xr3:uid="{40ED8FBD-39D6-4C0F-867B-9AA8C9C09316}" name="Valor8" headerRowDxfId="28" dataDxfId="27"/>
+    <tableColumn id="6" xr3:uid="{D7E37E62-C3F1-48D0-9ECE-1603C43E1947}" name="Coluna3" headerRowDxfId="26" dataDxfId="25"/>
+    <tableColumn id="7" xr3:uid="{8EAEA0F2-9F55-4FEE-86F2-D1912AEFC7F4}" name="Coluna4" headerRowDxfId="24" dataDxfId="23"/>
+    <tableColumn id="16" xr3:uid="{CB767617-3A28-42EC-8E47-CE6204F6D856}" name="Coluna11" headerRowDxfId="22" dataDxfId="21"/>
+    <tableColumn id="17" xr3:uid="{E29ADF84-36FF-41F7-9847-17BC340BAE5F}" name="Coluna12" headerRowDxfId="20" dataDxfId="19"/>
+    <tableColumn id="18" xr3:uid="{B5ADD4A7-EE28-45D9-B6FF-C285C2CD6E37}" name="Coluna13" headerRowDxfId="18" dataDxfId="17"/>
+    <tableColumn id="19" xr3:uid="{7FEDF53D-D312-4CF1-8EB3-4A56B77DEAA1}" name="Coluna14" headerRowDxfId="16" dataDxfId="15"/>
+    <tableColumn id="20" xr3:uid="{44C51568-5619-4D1B-B5B4-F2CF79CAB094}" name="Coluna15" headerRowDxfId="14" dataDxfId="13"/>
+    <tableColumn id="21" xr3:uid="{2A7C2A78-BAF9-429F-B898-EF931D80D830}" name="Coluna16" headerRowDxfId="12" dataDxfId="11"/>
+    <tableColumn id="22" xr3:uid="{3BB87186-A8C3-4EE2-9555-ACB7C40B9882}" name="Coluna17" headerRowDxfId="10" dataDxfId="9"/>
+    <tableColumn id="23" xr3:uid="{C574DFC8-E441-4BB1-A97D-83D5A9C08508}" name="Coluna18" headerRowDxfId="8" dataDxfId="7"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="0" showColumnStripes="0"/>
 </table>
@@ -4593,15 +4603,15 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{03763A90-6A45-4DA0-A35B-2601294A84FF}">
   <sheetPr codeName="Planilha1"/>
   <dimension ref="A1:C39"/>
-  <sheetFormatPr defaultColWidth="11" defaultRowHeight="9" customHeight="1" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="11" defaultRowHeight="9" customHeight="1" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="9.6640625" style="43" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="65.6640625" style="43" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="9.69921875" style="43" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="65.69921875" style="43" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="4.5" style="43" bestFit="1" customWidth="1"/>
     <col min="4" max="16384" width="11" style="43"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" ht="18.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:3" ht="19" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>4</v>
       </c>
@@ -4612,7 +4622,7 @@
         <v>403</v>
       </c>
     </row>
-    <row r="2" spans="1:3" ht="7.35" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:3" ht="7.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="3" t="s">
         <v>168</v>
       </c>
@@ -4623,7 +4633,7 @@
         <v>404</v>
       </c>
     </row>
-    <row r="3" spans="1:3" ht="7.35" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:3" ht="7.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="3" t="s">
         <v>169</v>
       </c>
@@ -4634,7 +4644,7 @@
         <v>404</v>
       </c>
     </row>
-    <row r="4" spans="1:3" ht="7.35" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:3" ht="7.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="4" t="s">
         <v>5</v>
       </c>
@@ -4645,7 +4655,7 @@
         <v>404</v>
       </c>
     </row>
-    <row r="5" spans="1:3" ht="7.35" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:3" ht="7.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="4" t="s">
         <v>6</v>
       </c>
@@ -4657,7 +4667,7 @@
         <v>404</v>
       </c>
     </row>
-    <row r="6" spans="1:3" ht="7.35" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:3" ht="7.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="4" t="s">
         <v>7</v>
       </c>
@@ -4669,7 +4679,7 @@
         <v>404</v>
       </c>
     </row>
-    <row r="7" spans="1:3" ht="7.35" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:3" ht="7.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="4" t="s">
         <v>8</v>
       </c>
@@ -4680,7 +4690,7 @@
         <v>404</v>
       </c>
     </row>
-    <row r="8" spans="1:3" ht="7.35" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:3" ht="7.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" s="39" t="s">
         <v>9</v>
       </c>
@@ -4691,7 +4701,7 @@
         <v>404</v>
       </c>
     </row>
-    <row r="9" spans="1:3" ht="7.35" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:3" ht="7.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="4" t="s">
         <v>170</v>
       </c>
@@ -4702,7 +4712,7 @@
         <v>404</v>
       </c>
     </row>
-    <row r="10" spans="1:3" ht="7.35" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:3" ht="7.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" s="4" t="s">
         <v>172</v>
       </c>
@@ -4713,7 +4723,7 @@
         <v>404</v>
       </c>
     </row>
-    <row r="11" spans="1:3" ht="7.35" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:3" ht="7.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A11" s="4" t="s">
         <v>173</v>
       </c>
@@ -4724,7 +4734,7 @@
         <v>404</v>
       </c>
     </row>
-    <row r="12" spans="1:3" ht="7.35" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:3" ht="7.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A12" s="4" t="s">
         <v>10</v>
       </c>
@@ -4735,7 +4745,7 @@
         <v>404</v>
       </c>
     </row>
-    <row r="13" spans="1:3" ht="7.35" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:3" ht="7.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A13" s="4" t="s">
         <v>174</v>
       </c>
@@ -4746,7 +4756,7 @@
         <v>404</v>
       </c>
     </row>
-    <row r="14" spans="1:3" ht="7.35" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:3" ht="7.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A14" s="4" t="s">
         <v>175</v>
       </c>
@@ -4757,7 +4767,7 @@
         <v>404</v>
       </c>
     </row>
-    <row r="15" spans="1:3" ht="7.35" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:3" ht="7.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A15" s="4" t="s">
         <v>176</v>
       </c>
@@ -4768,7 +4778,7 @@
         <v>404</v>
       </c>
     </row>
-    <row r="16" spans="1:3" ht="7.35" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:3" ht="7.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A16" s="4" t="s">
         <v>177</v>
       </c>
@@ -4779,7 +4789,7 @@
         <v>404</v>
       </c>
     </row>
-    <row r="17" spans="1:3" ht="7.35" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:3" ht="7.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A17" s="4" t="s">
         <v>12</v>
       </c>
@@ -4790,19 +4800,19 @@
         <v>404</v>
       </c>
     </row>
-    <row r="18" spans="1:3" ht="7.35" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:3" ht="7.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A18" s="4" t="s">
         <v>178</v>
       </c>
       <c r="B18" s="5">
         <f ca="1">NOW()</f>
-        <v>46244.497208564811</v>
+        <v>46249.323550694447</v>
       </c>
       <c r="C18" s="42" t="s">
         <v>404</v>
       </c>
     </row>
-    <row r="19" spans="1:3" ht="7.35" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:3" ht="7.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A19" s="4" t="s">
         <v>415</v>
       </c>
@@ -4813,7 +4823,7 @@
         <v>404</v>
       </c>
     </row>
-    <row r="20" spans="1:3" ht="7.35" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:3" ht="7.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A20" s="39" t="s">
         <v>411</v>
       </c>
@@ -4825,7 +4835,7 @@
         <v>405</v>
       </c>
     </row>
-    <row r="21" spans="1:3" ht="7.35" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:3" ht="7.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A21" s="39" t="s">
         <v>416</v>
       </c>
@@ -4837,7 +4847,7 @@
         <v>406</v>
       </c>
     </row>
-    <row r="22" spans="1:3" ht="7.35" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:3" ht="7.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A22" s="4" t="s">
         <v>167</v>
       </c>
@@ -4848,7 +4858,7 @@
         <v>404</v>
       </c>
     </row>
-    <row r="23" spans="1:3" ht="7.35" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:3" ht="7.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A23" s="4" t="s">
         <v>179</v>
       </c>
@@ -4859,7 +4869,7 @@
         <v>404</v>
       </c>
     </row>
-    <row r="24" spans="1:3" ht="7.35" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:3" ht="7.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A24" s="4" t="s">
         <v>184</v>
       </c>
@@ -4870,7 +4880,7 @@
         <v>404</v>
       </c>
     </row>
-    <row r="25" spans="1:3" ht="7.35" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:3" ht="7.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A25" s="4" t="s">
         <v>186</v>
       </c>
@@ -4881,7 +4891,7 @@
         <v>405</v>
       </c>
     </row>
-    <row r="26" spans="1:3" ht="7.35" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:3" ht="7.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A26" s="39" t="s">
         <v>400</v>
       </c>
@@ -4892,7 +4902,7 @@
         <v>406</v>
       </c>
     </row>
-    <row r="27" spans="1:3" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:3" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A27" s="39" t="s">
         <v>527</v>
       </c>
@@ -4903,7 +4913,7 @@
         <v>404</v>
       </c>
     </row>
-    <row r="28" spans="1:3" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:3" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A28" s="39" t="s">
         <v>529</v>
       </c>
@@ -4914,7 +4924,7 @@
         <v>404</v>
       </c>
     </row>
-    <row r="29" spans="1:3" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:3" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A29" s="39" t="s">
         <v>531</v>
       </c>
@@ -4925,7 +4935,7 @@
         <v>404</v>
       </c>
     </row>
-    <row r="30" spans="1:3" s="63" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="30" spans="1:3" s="63" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A30" s="39" t="s">
         <v>533</v>
       </c>
@@ -4936,7 +4946,7 @@
         <v>404</v>
       </c>
     </row>
-    <row r="31" spans="1:3" s="63" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="31" spans="1:3" s="63" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A31" s="39" t="s">
         <v>535</v>
       </c>
@@ -4947,7 +4957,7 @@
         <v>404</v>
       </c>
     </row>
-    <row r="32" spans="1:3" s="63" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="32" spans="1:3" s="63" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A32" s="39" t="s">
         <v>537</v>
       </c>
@@ -4958,7 +4968,7 @@
         <v>404</v>
       </c>
     </row>
-    <row r="33" spans="1:3" s="63" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="33" spans="1:3" s="63" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A33" s="39" t="s">
         <v>539</v>
       </c>
@@ -4969,7 +4979,7 @@
         <v>404</v>
       </c>
     </row>
-    <row r="34" spans="1:3" s="63" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="34" spans="1:3" s="63" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A34" s="39" t="s">
         <v>541</v>
       </c>
@@ -4980,7 +4990,7 @@
         <v>404</v>
       </c>
     </row>
-    <row r="35" spans="1:3" s="63" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="35" spans="1:3" s="63" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A35" s="39" t="s">
         <v>543</v>
       </c>
@@ -4991,7 +5001,7 @@
         <v>404</v>
       </c>
     </row>
-    <row r="36" spans="1:3" s="63" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="36" spans="1:3" s="63" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A36" s="39" t="s">
         <v>545</v>
       </c>
@@ -5002,7 +5012,7 @@
         <v>404</v>
       </c>
     </row>
-    <row r="37" spans="1:3" s="63" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="37" spans="1:3" s="63" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A37" s="39" t="s">
         <v>547</v>
       </c>
@@ -5013,7 +5023,7 @@
         <v>404</v>
       </c>
     </row>
-    <row r="38" spans="1:3" customFormat="1" ht="9.9499999999999993" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="38" spans="1:3" customFormat="1" ht="10" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A38" s="4" t="s">
         <v>549</v>
       </c>
@@ -5024,7 +5034,7 @@
         <v>404</v>
       </c>
     </row>
-    <row r="39" spans="1:3" s="67" customFormat="1" ht="9.6" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="39" spans="1:3" s="67" customFormat="1" ht="9.65" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A39" s="39" t="s">
         <v>551</v>
       </c>
@@ -5051,33 +5061,34 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{958751C2-A34E-4345-8D6A-082603A025F9}">
   <sheetPr codeName="Planilha2"/>
   <dimension ref="A1:AA23"/>
-  <sheetFormatPr defaultRowHeight="6.75" customHeight="1" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultRowHeight="6.75" customHeight="1" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="2.33203125" bestFit="1" customWidth="1"/>
-    <col min="2" max="3" width="6.83203125" style="34" customWidth="1"/>
-    <col min="4" max="4" width="8.6640625" style="34" customWidth="1"/>
-    <col min="5" max="5" width="7.6640625" style="34" customWidth="1"/>
-    <col min="6" max="6" width="14" style="34" bestFit="1" customWidth="1"/>
-    <col min="7" max="11" width="8.6640625" style="34" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="7" customWidth="1"/>
-    <col min="13" max="13" width="7.33203125" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="7" customWidth="1"/>
-    <col min="15" max="15" width="12" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="62" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="60.6640625" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="5.83203125" style="34" customWidth="1"/>
-    <col min="19" max="19" width="7" customWidth="1"/>
-    <col min="20" max="20" width="9.1640625" customWidth="1"/>
-    <col min="21" max="21" width="8" customWidth="1"/>
-    <col min="22" max="22" width="9.1640625" customWidth="1"/>
-    <col min="23" max="23" width="8.6640625" style="34" customWidth="1"/>
-    <col min="24" max="24" width="46.6640625" customWidth="1"/>
-    <col min="25" max="25" width="9.6640625" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="7.33203125" customWidth="1"/>
-    <col min="27" max="27" width="64.5" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="1.8984375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="5.5" style="34" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="6.09765625" style="34" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="7.8984375" style="34" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="5.796875" style="34" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="11.5" style="34" bestFit="1" customWidth="1"/>
+    <col min="7" max="11" width="8.3984375" style="34" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="6.5" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="7.8984375" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="6.5" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="11.5" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="62.296875" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="64.69921875" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="4.796875" style="34" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="6.09765625" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="7.8984375" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="5.796875" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="7.796875" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="7.5" style="34" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="45.69921875" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="36.09765625" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="6.69921875" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="57" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:27" ht="37.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:27" ht="37.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="22" t="s">
         <v>349</v>
       </c>
@@ -5160,7 +5171,7 @@
         <v>399</v>
       </c>
     </row>
-    <row r="2" spans="1:27" ht="9" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:27" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="49">
         <v>2</v>
       </c>
@@ -5239,10 +5250,10 @@
         <v>Key-ABNT-2</v>
       </c>
       <c r="X2" s="38" t="s">
-        <v>556</v>
+        <v>563</v>
       </c>
       <c r="Y2" s="38" t="s">
-        <v>557</v>
+        <v>564</v>
       </c>
       <c r="Z2" s="38" t="s">
         <v>420</v>
@@ -5251,7 +5262,7 @@
         <v>490</v>
       </c>
     </row>
-    <row r="3" spans="1:27" ht="9" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:27" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="49">
         <v>3</v>
       </c>
@@ -5330,10 +5341,10 @@
         <v>Key-ABNT-3</v>
       </c>
       <c r="X3" s="38" t="s">
-        <v>558</v>
+        <v>565</v>
       </c>
       <c r="Y3" s="38" t="s">
-        <v>564</v>
+        <v>566</v>
       </c>
       <c r="Z3" s="38" t="s">
         <v>421</v>
@@ -5342,7 +5353,7 @@
         <v>493</v>
       </c>
     </row>
-    <row r="4" spans="1:27" ht="9" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:27" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="49">
         <v>4</v>
       </c>
@@ -5421,10 +5432,10 @@
         <v>Key-ABNT-4</v>
       </c>
       <c r="X4" s="38" t="s">
-        <v>558</v>
+        <v>556</v>
       </c>
       <c r="Y4" s="38" t="s">
-        <v>559</v>
+        <v>557</v>
       </c>
       <c r="Z4" s="38" t="s">
         <v>422</v>
@@ -5433,7 +5444,7 @@
         <v>496</v>
       </c>
     </row>
-    <row r="5" spans="1:27" ht="9" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:27" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="49">
         <v>5</v>
       </c>
@@ -5512,10 +5523,10 @@
         <v>Key-ABNT-5</v>
       </c>
       <c r="X5" s="38" t="s">
-        <v>560</v>
+        <v>558</v>
       </c>
       <c r="Y5" s="38" t="s">
-        <v>561</v>
+        <v>559</v>
       </c>
       <c r="Z5" s="38" t="s">
         <v>423</v>
@@ -5524,7 +5535,7 @@
         <v>499</v>
       </c>
     </row>
-    <row r="6" spans="1:27" ht="9" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:27" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="49">
         <v>6</v>
       </c>
@@ -5603,10 +5614,10 @@
         <v>Key-ABNT-6</v>
       </c>
       <c r="X6" s="38" t="s">
-        <v>558</v>
+        <v>556</v>
       </c>
       <c r="Y6" s="38" t="s">
-        <v>559</v>
+        <v>557</v>
       </c>
       <c r="Z6" s="38" t="s">
         <v>424</v>
@@ -5615,7 +5626,7 @@
         <v>502</v>
       </c>
     </row>
-    <row r="7" spans="1:27" ht="9" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:27" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="49">
         <v>7</v>
       </c>
@@ -5694,10 +5705,10 @@
         <v>Key-ABNT-7</v>
       </c>
       <c r="X7" s="38" t="s">
-        <v>558</v>
+        <v>556</v>
       </c>
       <c r="Y7" s="38" t="s">
-        <v>558</v>
+        <v>556</v>
       </c>
       <c r="Z7" s="38" t="s">
         <v>425</v>
@@ -5706,7 +5717,7 @@
         <v>505</v>
       </c>
     </row>
-    <row r="8" spans="1:27" ht="9" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:27" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" s="49">
         <v>8</v>
       </c>
@@ -5785,10 +5796,10 @@
         <v>Key-ABNT-8</v>
       </c>
       <c r="X8" s="38" t="s">
-        <v>558</v>
+        <v>556</v>
       </c>
       <c r="Y8" s="38" t="s">
-        <v>558</v>
+        <v>556</v>
       </c>
       <c r="Z8" s="38" t="s">
         <v>342</v>
@@ -5797,7 +5808,7 @@
         <v>508</v>
       </c>
     </row>
-    <row r="9" spans="1:27" ht="9" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:27" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="49">
         <v>9</v>
       </c>
@@ -5876,10 +5887,10 @@
         <v>Key-ABNT-9</v>
       </c>
       <c r="X9" s="38" t="s">
-        <v>558</v>
+        <v>556</v>
       </c>
       <c r="Y9" s="38" t="s">
-        <v>558</v>
+        <v>556</v>
       </c>
       <c r="Z9" s="38" t="s">
         <v>426</v>
@@ -5888,7 +5899,7 @@
         <v>511</v>
       </c>
     </row>
-    <row r="10" spans="1:27" ht="9" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:27" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" s="49">
         <v>10</v>
       </c>
@@ -5967,10 +5978,10 @@
         <v>Key-ABNT-10</v>
       </c>
       <c r="X10" s="38" t="s">
-        <v>558</v>
+        <v>556</v>
       </c>
       <c r="Y10" s="38" t="s">
-        <v>558</v>
+        <v>556</v>
       </c>
       <c r="Z10" s="38" t="s">
         <v>427</v>
@@ -5979,7 +5990,7 @@
         <v>514</v>
       </c>
     </row>
-    <row r="11" spans="1:27" ht="9" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:27" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A11" s="49">
         <v>11</v>
       </c>
@@ -6058,10 +6069,10 @@
         <v>Key-ABNT-11</v>
       </c>
       <c r="X11" s="38" t="s">
-        <v>558</v>
+        <v>556</v>
       </c>
       <c r="Y11" s="38" t="s">
-        <v>558</v>
+        <v>556</v>
       </c>
       <c r="Z11" s="38" t="s">
         <v>428</v>
@@ -6070,7 +6081,7 @@
         <v>517</v>
       </c>
     </row>
-    <row r="12" spans="1:27" ht="9" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:27" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A12" s="49">
         <v>12</v>
       </c>
@@ -6149,10 +6160,10 @@
         <v>Key-ABNT-12</v>
       </c>
       <c r="X12" s="38" t="s">
-        <v>562</v>
+        <v>560</v>
       </c>
       <c r="Y12" s="38" t="s">
-        <v>563</v>
+        <v>567</v>
       </c>
       <c r="Z12" s="38" t="s">
         <v>429</v>
@@ -6161,7 +6172,7 @@
         <v>520</v>
       </c>
     </row>
-    <row r="13" spans="1:27" ht="9" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:27" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A13" s="49">
         <v>13</v>
       </c>
@@ -6240,10 +6251,10 @@
         <v>Key-ABNT-13</v>
       </c>
       <c r="X13" s="38" t="s">
-        <v>562</v>
+        <v>560</v>
       </c>
       <c r="Y13" s="38" t="s">
-        <v>563</v>
+        <v>567</v>
       </c>
       <c r="Z13" s="38" t="s">
         <v>430</v>
@@ -6252,7 +6263,7 @@
         <v>523</v>
       </c>
     </row>
-    <row r="14" spans="1:27" ht="9" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:27" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A14" s="49">
         <v>14</v>
       </c>
@@ -6331,10 +6342,10 @@
         <v>Key-ABNT-14</v>
       </c>
       <c r="X14" s="68" t="s">
-        <v>565</v>
+        <v>561</v>
       </c>
       <c r="Y14" s="69" t="s">
-        <v>566</v>
+        <v>562</v>
       </c>
       <c r="Z14" s="38" t="s">
         <v>431</v>
@@ -6343,7 +6354,7 @@
         <v>526</v>
       </c>
     </row>
-    <row r="15" spans="1:27" ht="9" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:27" ht="6.9" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A15" s="49">
         <v>15</v>
       </c>
@@ -6423,10 +6434,10 @@
         <v>Key-ABNT-15</v>
       </c>
       <c r="X15" s="38" t="s">
-        <v>558</v>
+        <v>556</v>
       </c>
       <c r="Y15" s="38" t="s">
-        <v>558</v>
+        <v>556</v>
       </c>
       <c r="Z15" s="53" t="s">
         <v>477</v>
@@ -6436,7 +6447,7 @@
         <v>Entrepreneurs</v>
       </c>
     </row>
-    <row r="16" spans="1:27" ht="9" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:27" ht="6.9" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A16" s="49">
         <v>16</v>
       </c>
@@ -6516,10 +6527,10 @@
         <v>Key-ABNT-16</v>
       </c>
       <c r="X16" s="38" t="s">
-        <v>558</v>
+        <v>556</v>
       </c>
       <c r="Y16" s="38" t="s">
-        <v>558</v>
+        <v>556</v>
       </c>
       <c r="Z16" s="53" t="s">
         <v>478</v>
@@ -6529,7 +6540,7 @@
         <v>Designers</v>
       </c>
     </row>
-    <row r="17" spans="1:27" ht="9" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:27" ht="6.9" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A17" s="49">
         <v>17</v>
       </c>
@@ -6609,10 +6620,10 @@
         <v>Key-ABNT-17</v>
       </c>
       <c r="X17" s="38" t="s">
-        <v>558</v>
+        <v>556</v>
       </c>
       <c r="Y17" s="38" t="s">
-        <v>558</v>
+        <v>556</v>
       </c>
       <c r="Z17" s="53" t="s">
         <v>479</v>
@@ -6622,7 +6633,7 @@
         <v>Managers</v>
       </c>
     </row>
-    <row r="18" spans="1:27" ht="9" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:27" ht="6.9" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A18" s="49">
         <v>18</v>
       </c>
@@ -6702,10 +6713,10 @@
         <v>Key-ABNT-18</v>
       </c>
       <c r="X18" s="38" t="s">
-        <v>558</v>
+        <v>556</v>
       </c>
       <c r="Y18" s="38" t="s">
-        <v>558</v>
+        <v>556</v>
       </c>
       <c r="Z18" s="53" t="s">
         <v>480</v>
@@ -6715,7 +6726,7 @@
         <v>Builders and Contractors</v>
       </c>
     </row>
-    <row r="19" spans="1:27" ht="9" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:27" ht="6.9" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A19" s="49">
         <v>19</v>
       </c>
@@ -6795,10 +6806,10 @@
         <v>Key-ABNT-19</v>
       </c>
       <c r="X19" s="38" t="s">
-        <v>558</v>
+        <v>556</v>
       </c>
       <c r="Y19" s="38" t="s">
-        <v>558</v>
+        <v>556</v>
       </c>
       <c r="Z19" s="53" t="s">
         <v>481</v>
@@ -6808,7 +6819,7 @@
         <v>Construction inspectors</v>
       </c>
     </row>
-    <row r="20" spans="1:27" ht="9" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:27" ht="6.9" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A20" s="49">
         <v>20</v>
       </c>
@@ -6888,10 +6899,10 @@
         <v>Key-ABNT-20</v>
       </c>
       <c r="X20" s="38" t="s">
-        <v>558</v>
+        <v>556</v>
       </c>
       <c r="Y20" s="38" t="s">
-        <v>558</v>
+        <v>556</v>
       </c>
       <c r="Z20" s="53" t="s">
         <v>482</v>
@@ -6901,7 +6912,7 @@
         <v>Supporters</v>
       </c>
     </row>
-    <row r="21" spans="1:27" ht="9" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:27" ht="6.9" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A21" s="49">
         <v>21</v>
       </c>
@@ -6981,10 +6992,10 @@
         <v>Key-ABNT-21</v>
       </c>
       <c r="X21" s="38" t="s">
-        <v>558</v>
+        <v>556</v>
       </c>
       <c r="Y21" s="38" t="s">
-        <v>558</v>
+        <v>556</v>
       </c>
       <c r="Z21" s="53" t="s">
         <v>483</v>
@@ -6994,7 +7005,7 @@
         <v>Marketers</v>
       </c>
     </row>
-    <row r="22" spans="1:27" ht="9" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:27" ht="6.9" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A22" s="49">
         <v>22</v>
       </c>
@@ -7074,10 +7085,10 @@
         <v>Key-ABNT-22</v>
       </c>
       <c r="X22" s="38" t="s">
-        <v>558</v>
+        <v>556</v>
       </c>
       <c r="Y22" s="38" t="s">
-        <v>558</v>
+        <v>556</v>
       </c>
       <c r="Z22" s="53" t="s">
         <v>484</v>
@@ -7087,7 +7098,7 @@
         <v>Outsourced</v>
       </c>
     </row>
-    <row r="23" spans="1:27" ht="9" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:27" ht="6.9" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A23" s="49">
         <v>23</v>
       </c>
@@ -7167,10 +7178,10 @@
         <v>Key-ABNT-23</v>
       </c>
       <c r="X23" s="38" t="s">
-        <v>558</v>
+        <v>556</v>
       </c>
       <c r="Y23" s="38" t="s">
-        <v>558</v>
+        <v>556</v>
       </c>
       <c r="Z23" s="53" t="s">
         <v>485</v>
@@ -7182,10 +7193,15 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="F2:F14">
-    <cfRule type="duplicateValues" dxfId="5" priority="2"/>
+    <cfRule type="duplicateValues" dxfId="6" priority="4"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="X2:Y2">
+    <cfRule type="cellIs" dxfId="5" priority="1" operator="equal">
+      <formula>"null"</formula>
+    </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AA1:AA23 A2:B23">
-    <cfRule type="cellIs" dxfId="4" priority="1" operator="equal">
+    <cfRule type="cellIs" dxfId="4" priority="3" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -7200,13 +7216,13 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B2B4A051-97A0-4486-9B30-1861C9F77522}">
   <sheetPr codeName="Planilha3"/>
   <dimension ref="A1:U2"/>
-  <sheetFormatPr defaultColWidth="5.33203125" defaultRowHeight="11.25" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="5.296875" defaultRowHeight="10.75" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="2" customWidth="1"/>
     <col min="2" max="21" width="5" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:21" ht="24.75" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:21" ht="23.15" x14ac:dyDescent="0.3">
       <c r="A1" s="27" t="s">
         <v>350</v>
       </c>
@@ -7271,7 +7287,7 @@
         <v>392</v>
       </c>
     </row>
-    <row r="2" spans="1:21" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:21" ht="8.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="27">
         <v>2</v>
       </c>
@@ -7353,13 +7369,13 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{78CA1C4B-37EB-4980-B878-E43323BA46B5}">
   <sheetPr codeName="Planilha4"/>
   <dimension ref="A1:C2"/>
-  <sheetFormatPr defaultRowHeight="11.25" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultRowHeight="10.75" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="3.33203125" bestFit="1" customWidth="1"/>
-    <col min="2" max="3" width="16.6640625" customWidth="1"/>
+    <col min="1" max="1" width="3.296875" bestFit="1" customWidth="1"/>
+    <col min="2" max="3" width="16.69921875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1" s="30">
         <v>1</v>
       </c>
@@ -7370,7 +7386,7 @@
         <v>395</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A2" s="21">
         <v>2</v>
       </c>
@@ -7395,30 +7411,30 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B79BA5E7-BFBD-4AC9-B36C-B9776AA17B75}">
   <sheetPr codeName="Planilha5"/>
   <dimension ref="A1:Y157"/>
-  <sheetFormatPr defaultColWidth="11.33203125" defaultRowHeight="6" customHeight="1" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="11.296875" defaultRowHeight="6" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="3.6640625" style="2" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="11.33203125" style="2" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="14.83203125" style="2" customWidth="1"/>
-    <col min="4" max="4" width="10.1640625" style="2" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="7.6640625" style="2" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="7.33203125" style="48" customWidth="1"/>
+    <col min="1" max="1" width="3.69921875" style="2" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="11.296875" style="2" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="14.796875" style="2" customWidth="1"/>
+    <col min="4" max="4" width="10.19921875" style="2" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="7.69921875" style="2" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="7.296875" style="48" customWidth="1"/>
     <col min="7" max="7" width="10" style="48" customWidth="1"/>
-    <col min="8" max="9" width="7.33203125" style="48" customWidth="1"/>
-    <col min="10" max="10" width="4.33203125" style="48" customWidth="1"/>
+    <col min="8" max="9" width="7.296875" style="48" customWidth="1"/>
+    <col min="10" max="10" width="4.296875" style="48" customWidth="1"/>
     <col min="11" max="11" width="14" style="48" bestFit="1" customWidth="1"/>
     <col min="12" max="12" width="7.5" style="48" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="29.1640625" style="48" customWidth="1"/>
+    <col min="13" max="13" width="29.19921875" style="48" customWidth="1"/>
     <col min="14" max="14" width="7" style="48" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="43.83203125" style="2" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="8.6640625" style="48" customWidth="1"/>
+    <col min="15" max="15" width="43.796875" style="2" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="8.69921875" style="48" customWidth="1"/>
     <col min="17" max="17" width="5" style="48" customWidth="1"/>
     <col min="18" max="18" width="5.5" style="48" customWidth="1"/>
     <col min="19" max="25" width="5" style="48" customWidth="1"/>
-    <col min="26" max="16384" width="11.33203125" style="2"/>
+    <col min="26" max="16384" width="11.296875" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:25" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:25" ht="18.649999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="7" t="s">
         <v>180</v>
       </c>
@@ -7491,7 +7507,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="9">
         <v>2</v>
       </c>
@@ -7568,7 +7584,7 @@
         <v>181</v>
       </c>
     </row>
-    <row r="3" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="9">
         <v>3</v>
       </c>
@@ -7645,7 +7661,7 @@
         <v>181</v>
       </c>
     </row>
-    <row r="4" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="9">
         <v>4</v>
       </c>
@@ -7722,7 +7738,7 @@
         <v>181</v>
       </c>
     </row>
-    <row r="5" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="9">
         <v>5</v>
       </c>
@@ -7799,7 +7815,7 @@
         <v>181</v>
       </c>
     </row>
-    <row r="6" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="9">
         <v>6</v>
       </c>
@@ -7876,7 +7892,7 @@
         <v>181</v>
       </c>
     </row>
-    <row r="7" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="9">
         <v>7</v>
       </c>
@@ -7953,7 +7969,7 @@
         <v>181</v>
       </c>
     </row>
-    <row r="8" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="9">
         <v>8</v>
       </c>
@@ -8030,7 +8046,7 @@
         <v>181</v>
       </c>
     </row>
-    <row r="9" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="9">
         <v>9</v>
       </c>
@@ -8107,7 +8123,7 @@
         <v>181</v>
       </c>
     </row>
-    <row r="10" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="9">
         <v>10</v>
       </c>
@@ -8184,7 +8200,7 @@
         <v>181</v>
       </c>
     </row>
-    <row r="11" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="9">
         <v>11</v>
       </c>
@@ -8261,7 +8277,7 @@
         <v>181</v>
       </c>
     </row>
-    <row r="12" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="9">
         <v>12</v>
       </c>
@@ -8338,7 +8354,7 @@
         <v>181</v>
       </c>
     </row>
-    <row r="13" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="9">
         <v>13</v>
       </c>
@@ -8415,7 +8431,7 @@
         <v>181</v>
       </c>
     </row>
-    <row r="14" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="9">
         <v>14</v>
       </c>
@@ -8492,7 +8508,7 @@
         <v>181</v>
       </c>
     </row>
-    <row r="15" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="9">
         <v>15</v>
       </c>
@@ -8569,7 +8585,7 @@
         <v>181</v>
       </c>
     </row>
-    <row r="16" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="9">
         <v>16</v>
       </c>
@@ -8646,7 +8662,7 @@
         <v>181</v>
       </c>
     </row>
-    <row r="17" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="9">
         <v>17</v>
       </c>
@@ -8723,7 +8739,7 @@
         <v>181</v>
       </c>
     </row>
-    <row r="18" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="9">
         <v>18</v>
       </c>
@@ -8800,7 +8816,7 @@
         <v>181</v>
       </c>
     </row>
-    <row r="19" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="9">
         <v>19</v>
       </c>
@@ -8877,7 +8893,7 @@
         <v>181</v>
       </c>
     </row>
-    <row r="20" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="9">
         <v>20</v>
       </c>
@@ -8954,7 +8970,7 @@
         <v>181</v>
       </c>
     </row>
-    <row r="21" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="9">
         <v>21</v>
       </c>
@@ -9031,7 +9047,7 @@
         <v>181</v>
       </c>
     </row>
-    <row r="22" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="9">
         <v>22</v>
       </c>
@@ -9108,7 +9124,7 @@
         <v>181</v>
       </c>
     </row>
-    <row r="23" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="9">
         <v>23</v>
       </c>
@@ -9185,7 +9201,7 @@
         <v>181</v>
       </c>
     </row>
-    <row r="24" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="9">
         <v>24</v>
       </c>
@@ -9262,7 +9278,7 @@
         <v>181</v>
       </c>
     </row>
-    <row r="25" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="9">
         <v>25</v>
       </c>
@@ -9339,7 +9355,7 @@
         <v>181</v>
       </c>
     </row>
-    <row r="26" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A26" s="9">
         <v>26</v>
       </c>
@@ -9416,7 +9432,7 @@
         <v>181</v>
       </c>
     </row>
-    <row r="27" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A27" s="9">
         <v>27</v>
       </c>
@@ -9493,7 +9509,7 @@
         <v>181</v>
       </c>
     </row>
-    <row r="28" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A28" s="9">
         <v>28</v>
       </c>
@@ -9570,7 +9586,7 @@
         <v>181</v>
       </c>
     </row>
-    <row r="29" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A29" s="9">
         <v>29</v>
       </c>
@@ -9647,7 +9663,7 @@
         <v>181</v>
       </c>
     </row>
-    <row r="30" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A30" s="9">
         <v>30</v>
       </c>
@@ -9724,7 +9740,7 @@
         <v>181</v>
       </c>
     </row>
-    <row r="31" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A31" s="9">
         <v>31</v>
       </c>
@@ -9801,7 +9817,7 @@
         <v>181</v>
       </c>
     </row>
-    <row r="32" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A32" s="9">
         <v>32</v>
       </c>
@@ -9878,7 +9894,7 @@
         <v>181</v>
       </c>
     </row>
-    <row r="33" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="33" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A33" s="9">
         <v>33</v>
       </c>
@@ -9955,7 +9971,7 @@
         <v>181</v>
       </c>
     </row>
-    <row r="34" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="34" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A34" s="9">
         <v>34</v>
       </c>
@@ -10032,7 +10048,7 @@
         <v>181</v>
       </c>
     </row>
-    <row r="35" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="35" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A35" s="9">
         <v>35</v>
       </c>
@@ -10109,7 +10125,7 @@
         <v>181</v>
       </c>
     </row>
-    <row r="36" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="36" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A36" s="9">
         <v>36</v>
       </c>
@@ -10186,7 +10202,7 @@
         <v>181</v>
       </c>
     </row>
-    <row r="37" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="37" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A37" s="9">
         <v>37</v>
       </c>
@@ -10263,7 +10279,7 @@
         <v>181</v>
       </c>
     </row>
-    <row r="38" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="38" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A38" s="9">
         <v>38</v>
       </c>
@@ -10340,7 +10356,7 @@
         <v>181</v>
       </c>
     </row>
-    <row r="39" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="39" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A39" s="9">
         <v>39</v>
       </c>
@@ -10417,7 +10433,7 @@
         <v>181</v>
       </c>
     </row>
-    <row r="40" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="40" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A40" s="9">
         <v>40</v>
       </c>
@@ -10494,7 +10510,7 @@
         <v>181</v>
       </c>
     </row>
-    <row r="41" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="41" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A41" s="9">
         <v>41</v>
       </c>
@@ -10571,7 +10587,7 @@
         <v>181</v>
       </c>
     </row>
-    <row r="42" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="42" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A42" s="9">
         <v>42</v>
       </c>
@@ -10648,7 +10664,7 @@
         <v>181</v>
       </c>
     </row>
-    <row r="43" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="43" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A43" s="9">
         <v>43</v>
       </c>
@@ -10725,7 +10741,7 @@
         <v>181</v>
       </c>
     </row>
-    <row r="44" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="44" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A44" s="9">
         <v>44</v>
       </c>
@@ -10802,7 +10818,7 @@
         <v>181</v>
       </c>
     </row>
-    <row r="45" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="45" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A45" s="9">
         <v>45</v>
       </c>
@@ -10879,7 +10895,7 @@
         <v>181</v>
       </c>
     </row>
-    <row r="46" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="46" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A46" s="9">
         <v>46</v>
       </c>
@@ -10956,7 +10972,7 @@
         <v>181</v>
       </c>
     </row>
-    <row r="47" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="47" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A47" s="9">
         <v>47</v>
       </c>
@@ -11033,7 +11049,7 @@
         <v>181</v>
       </c>
     </row>
-    <row r="48" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="48" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A48" s="9">
         <v>48</v>
       </c>
@@ -11110,7 +11126,7 @@
         <v>181</v>
       </c>
     </row>
-    <row r="49" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="49" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A49" s="9">
         <v>49</v>
       </c>
@@ -11187,7 +11203,7 @@
         <v>181</v>
       </c>
     </row>
-    <row r="50" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="50" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A50" s="9">
         <v>50</v>
       </c>
@@ -11264,7 +11280,7 @@
         <v>181</v>
       </c>
     </row>
-    <row r="51" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="51" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A51" s="9">
         <v>51</v>
       </c>
@@ -11341,7 +11357,7 @@
         <v>181</v>
       </c>
     </row>
-    <row r="52" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="52" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A52" s="9">
         <v>52</v>
       </c>
@@ -11418,7 +11434,7 @@
         <v>181</v>
       </c>
     </row>
-    <row r="53" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="53" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A53" s="9">
         <v>53</v>
       </c>
@@ -11495,7 +11511,7 @@
         <v>181</v>
       </c>
     </row>
-    <row r="54" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="54" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A54" s="9">
         <v>54</v>
       </c>
@@ -11572,7 +11588,7 @@
         <v>181</v>
       </c>
     </row>
-    <row r="55" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="55" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A55" s="9">
         <v>55</v>
       </c>
@@ -11649,7 +11665,7 @@
         <v>181</v>
       </c>
     </row>
-    <row r="56" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="56" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A56" s="9">
         <v>56</v>
       </c>
@@ -11726,7 +11742,7 @@
         <v>181</v>
       </c>
     </row>
-    <row r="57" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="57" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A57" s="9">
         <v>57</v>
       </c>
@@ -11803,7 +11819,7 @@
         <v>181</v>
       </c>
     </row>
-    <row r="58" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="58" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A58" s="9">
         <v>58</v>
       </c>
@@ -11880,7 +11896,7 @@
         <v>181</v>
       </c>
     </row>
-    <row r="59" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="59" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A59" s="9">
         <v>59</v>
       </c>
@@ -11957,7 +11973,7 @@
         <v>181</v>
       </c>
     </row>
-    <row r="60" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="60" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A60" s="9">
         <v>60</v>
       </c>
@@ -12034,7 +12050,7 @@
         <v>181</v>
       </c>
     </row>
-    <row r="61" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="61" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A61" s="9">
         <v>61</v>
       </c>
@@ -12111,7 +12127,7 @@
         <v>181</v>
       </c>
     </row>
-    <row r="62" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="62" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A62" s="9">
         <v>62</v>
       </c>
@@ -12188,7 +12204,7 @@
         <v>181</v>
       </c>
     </row>
-    <row r="63" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="63" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A63" s="9">
         <v>63</v>
       </c>
@@ -12265,7 +12281,7 @@
         <v>181</v>
       </c>
     </row>
-    <row r="64" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="64" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A64" s="9">
         <v>64</v>
       </c>
@@ -12342,7 +12358,7 @@
         <v>181</v>
       </c>
     </row>
-    <row r="65" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="65" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A65" s="9">
         <v>65</v>
       </c>
@@ -12419,7 +12435,7 @@
         <v>181</v>
       </c>
     </row>
-    <row r="66" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="66" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A66" s="9">
         <v>66</v>
       </c>
@@ -12496,7 +12512,7 @@
         <v>181</v>
       </c>
     </row>
-    <row r="67" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="67" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A67" s="9">
         <v>67</v>
       </c>
@@ -12573,7 +12589,7 @@
         <v>181</v>
       </c>
     </row>
-    <row r="68" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="68" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A68" s="9">
         <v>68</v>
       </c>
@@ -12650,7 +12666,7 @@
         <v>181</v>
       </c>
     </row>
-    <row r="69" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="69" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A69" s="9">
         <v>69</v>
       </c>
@@ -12727,7 +12743,7 @@
         <v>181</v>
       </c>
     </row>
-    <row r="70" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="70" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A70" s="9">
         <v>70</v>
       </c>
@@ -12804,7 +12820,7 @@
         <v>181</v>
       </c>
     </row>
-    <row r="71" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="71" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A71" s="9">
         <v>71</v>
       </c>
@@ -12881,7 +12897,7 @@
         <v>181</v>
       </c>
     </row>
-    <row r="72" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="72" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A72" s="9">
         <v>72</v>
       </c>
@@ -12958,7 +12974,7 @@
         <v>181</v>
       </c>
     </row>
-    <row r="73" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="73" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A73" s="9">
         <v>73</v>
       </c>
@@ -13035,7 +13051,7 @@
         <v>181</v>
       </c>
     </row>
-    <row r="74" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="74" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A74" s="9">
         <v>74</v>
       </c>
@@ -13112,7 +13128,7 @@
         <v>181</v>
       </c>
     </row>
-    <row r="75" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="75" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A75" s="9">
         <v>75</v>
       </c>
@@ -13189,7 +13205,7 @@
         <v>181</v>
       </c>
     </row>
-    <row r="76" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="76" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A76" s="9">
         <v>76</v>
       </c>
@@ -13266,7 +13282,7 @@
         <v>181</v>
       </c>
     </row>
-    <row r="77" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="77" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A77" s="9">
         <v>77</v>
       </c>
@@ -13343,7 +13359,7 @@
         <v>181</v>
       </c>
     </row>
-    <row r="78" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="78" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A78" s="9">
         <v>78</v>
       </c>
@@ -13420,7 +13436,7 @@
         <v>181</v>
       </c>
     </row>
-    <row r="79" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="79" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A79" s="9">
         <v>79</v>
       </c>
@@ -13497,7 +13513,7 @@
         <v>181</v>
       </c>
     </row>
-    <row r="80" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="80" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A80" s="9">
         <v>80</v>
       </c>
@@ -13574,7 +13590,7 @@
         <v>181</v>
       </c>
     </row>
-    <row r="81" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="81" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A81" s="9">
         <v>81</v>
       </c>
@@ -13651,7 +13667,7 @@
         <v>181</v>
       </c>
     </row>
-    <row r="82" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="82" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A82" s="9">
         <v>82</v>
       </c>
@@ -13728,7 +13744,7 @@
         <v>181</v>
       </c>
     </row>
-    <row r="83" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="83" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A83" s="9">
         <v>83</v>
       </c>
@@ -13805,7 +13821,7 @@
         <v>181</v>
       </c>
     </row>
-    <row r="84" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="84" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A84" s="9">
         <v>84</v>
       </c>
@@ -13882,7 +13898,7 @@
         <v>181</v>
       </c>
     </row>
-    <row r="85" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="85" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A85" s="9">
         <v>85</v>
       </c>
@@ -13959,7 +13975,7 @@
         <v>181</v>
       </c>
     </row>
-    <row r="86" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="86" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A86" s="9">
         <v>86</v>
       </c>
@@ -14036,7 +14052,7 @@
         <v>181</v>
       </c>
     </row>
-    <row r="87" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="87" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A87" s="9">
         <v>87</v>
       </c>
@@ -14113,7 +14129,7 @@
         <v>181</v>
       </c>
     </row>
-    <row r="88" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="88" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A88" s="9">
         <v>88</v>
       </c>
@@ -14190,7 +14206,7 @@
         <v>181</v>
       </c>
     </row>
-    <row r="89" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="89" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A89" s="9">
         <v>89</v>
       </c>
@@ -14267,7 +14283,7 @@
         <v>181</v>
       </c>
     </row>
-    <row r="90" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="90" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A90" s="9">
         <v>90</v>
       </c>
@@ -14344,7 +14360,7 @@
         <v>181</v>
       </c>
     </row>
-    <row r="91" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="91" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A91" s="9">
         <v>91</v>
       </c>
@@ -14421,7 +14437,7 @@
         <v>181</v>
       </c>
     </row>
-    <row r="92" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="92" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A92" s="9">
         <v>92</v>
       </c>
@@ -14498,7 +14514,7 @@
         <v>181</v>
       </c>
     </row>
-    <row r="93" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="93" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A93" s="9">
         <v>93</v>
       </c>
@@ -14575,7 +14591,7 @@
         <v>181</v>
       </c>
     </row>
-    <row r="94" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="94" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A94" s="9">
         <v>94</v>
       </c>
@@ -14652,7 +14668,7 @@
         <v>181</v>
       </c>
     </row>
-    <row r="95" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="95" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A95" s="9">
         <v>95</v>
       </c>
@@ -14729,7 +14745,7 @@
         <v>181</v>
       </c>
     </row>
-    <row r="96" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="96" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A96" s="9">
         <v>96</v>
       </c>
@@ -14806,7 +14822,7 @@
         <v>181</v>
       </c>
     </row>
-    <row r="97" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="97" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A97" s="9">
         <v>97</v>
       </c>
@@ -14883,7 +14899,7 @@
         <v>181</v>
       </c>
     </row>
-    <row r="98" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="98" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A98" s="9">
         <v>98</v>
       </c>
@@ -14960,7 +14976,7 @@
         <v>181</v>
       </c>
     </row>
-    <row r="99" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="99" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A99" s="9">
         <v>99</v>
       </c>
@@ -15037,7 +15053,7 @@
         <v>181</v>
       </c>
     </row>
-    <row r="100" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="100" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A100" s="9">
         <v>100</v>
       </c>
@@ -15114,7 +15130,7 @@
         <v>181</v>
       </c>
     </row>
-    <row r="101" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="101" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A101" s="9">
         <v>101</v>
       </c>
@@ -15191,7 +15207,7 @@
         <v>181</v>
       </c>
     </row>
-    <row r="102" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="102" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A102" s="9">
         <v>102</v>
       </c>
@@ -15268,7 +15284,7 @@
         <v>181</v>
       </c>
     </row>
-    <row r="103" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="103" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A103" s="9">
         <v>103</v>
       </c>
@@ -15345,7 +15361,7 @@
         <v>181</v>
       </c>
     </row>
-    <row r="104" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="104" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A104" s="9">
         <v>104</v>
       </c>
@@ -15422,7 +15438,7 @@
         <v>181</v>
       </c>
     </row>
-    <row r="105" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="105" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A105" s="9">
         <v>105</v>
       </c>
@@ -15499,7 +15515,7 @@
         <v>181</v>
       </c>
     </row>
-    <row r="106" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="106" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A106" s="9">
         <v>106</v>
       </c>
@@ -15576,7 +15592,7 @@
         <v>181</v>
       </c>
     </row>
-    <row r="107" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="107" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A107" s="9">
         <v>107</v>
       </c>
@@ -15653,7 +15669,7 @@
         <v>181</v>
       </c>
     </row>
-    <row r="108" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="108" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A108" s="9">
         <v>108</v>
       </c>
@@ -15730,7 +15746,7 @@
         <v>181</v>
       </c>
     </row>
-    <row r="109" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="109" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A109" s="9">
         <v>109</v>
       </c>
@@ -15807,7 +15823,7 @@
         <v>181</v>
       </c>
     </row>
-    <row r="110" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="110" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A110" s="9">
         <v>110</v>
       </c>
@@ -15884,7 +15900,7 @@
         <v>181</v>
       </c>
     </row>
-    <row r="111" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="111" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A111" s="9">
         <v>111</v>
       </c>
@@ -15961,7 +15977,7 @@
         <v>181</v>
       </c>
     </row>
-    <row r="112" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="112" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A112" s="9">
         <v>112</v>
       </c>
@@ -16038,7 +16054,7 @@
         <v>181</v>
       </c>
     </row>
-    <row r="113" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="113" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A113" s="9">
         <v>113</v>
       </c>
@@ -16115,7 +16131,7 @@
         <v>181</v>
       </c>
     </row>
-    <row r="114" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="114" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A114" s="9">
         <v>114</v>
       </c>
@@ -16192,7 +16208,7 @@
         <v>181</v>
       </c>
     </row>
-    <row r="115" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="115" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A115" s="9">
         <v>115</v>
       </c>
@@ -16269,7 +16285,7 @@
         <v>181</v>
       </c>
     </row>
-    <row r="116" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="116" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A116" s="9">
         <v>116</v>
       </c>
@@ -16346,7 +16362,7 @@
         <v>181</v>
       </c>
     </row>
-    <row r="117" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="117" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A117" s="9">
         <v>117</v>
       </c>
@@ -16423,7 +16439,7 @@
         <v>181</v>
       </c>
     </row>
-    <row r="118" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="118" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A118" s="9">
         <v>118</v>
       </c>
@@ -16500,7 +16516,7 @@
         <v>181</v>
       </c>
     </row>
-    <row r="119" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="119" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A119" s="9">
         <v>119</v>
       </c>
@@ -16577,7 +16593,7 @@
         <v>181</v>
       </c>
     </row>
-    <row r="120" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="120" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A120" s="9">
         <v>120</v>
       </c>
@@ -16654,7 +16670,7 @@
         <v>181</v>
       </c>
     </row>
-    <row r="121" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="121" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A121" s="9">
         <v>121</v>
       </c>
@@ -16731,7 +16747,7 @@
         <v>181</v>
       </c>
     </row>
-    <row r="122" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="122" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A122" s="9">
         <v>122</v>
       </c>
@@ -16808,7 +16824,7 @@
         <v>181</v>
       </c>
     </row>
-    <row r="123" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="123" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A123" s="9">
         <v>123</v>
       </c>
@@ -16885,7 +16901,7 @@
         <v>181</v>
       </c>
     </row>
-    <row r="124" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="124" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A124" s="9">
         <v>124</v>
       </c>
@@ -16962,7 +16978,7 @@
         <v>181</v>
       </c>
     </row>
-    <row r="125" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="125" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A125" s="9">
         <v>125</v>
       </c>
@@ -17039,7 +17055,7 @@
         <v>181</v>
       </c>
     </row>
-    <row r="126" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="126" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A126" s="9">
         <v>126</v>
       </c>
@@ -17116,7 +17132,7 @@
         <v>181</v>
       </c>
     </row>
-    <row r="127" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="127" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A127" s="9">
         <v>127</v>
       </c>
@@ -17193,7 +17209,7 @@
         <v>181</v>
       </c>
     </row>
-    <row r="128" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="128" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A128" s="9">
         <v>128</v>
       </c>
@@ -17270,7 +17286,7 @@
         <v>181</v>
       </c>
     </row>
-    <row r="129" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="129" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A129" s="9">
         <v>129</v>
       </c>
@@ -17347,7 +17363,7 @@
         <v>181</v>
       </c>
     </row>
-    <row r="130" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="130" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A130" s="9">
         <v>130</v>
       </c>
@@ -17424,7 +17440,7 @@
         <v>181</v>
       </c>
     </row>
-    <row r="131" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="131" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A131" s="9">
         <v>131</v>
       </c>
@@ -17501,7 +17517,7 @@
         <v>181</v>
       </c>
     </row>
-    <row r="132" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="132" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A132" s="9">
         <v>132</v>
       </c>
@@ -17578,7 +17594,7 @@
         <v>181</v>
       </c>
     </row>
-    <row r="133" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="133" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A133" s="9">
         <v>133</v>
       </c>
@@ -17655,7 +17671,7 @@
         <v>181</v>
       </c>
     </row>
-    <row r="134" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="134" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A134" s="9">
         <v>134</v>
       </c>
@@ -17732,7 +17748,7 @@
         <v>181</v>
       </c>
     </row>
-    <row r="135" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="135" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A135" s="9">
         <v>135</v>
       </c>
@@ -17809,7 +17825,7 @@
         <v>181</v>
       </c>
     </row>
-    <row r="136" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="136" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A136" s="9">
         <v>136</v>
       </c>
@@ -17886,7 +17902,7 @@
         <v>181</v>
       </c>
     </row>
-    <row r="137" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="137" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A137" s="9">
         <v>137</v>
       </c>
@@ -17963,7 +17979,7 @@
         <v>181</v>
       </c>
     </row>
-    <row r="138" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="138" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A138" s="9">
         <v>138</v>
       </c>
@@ -18040,7 +18056,7 @@
         <v>181</v>
       </c>
     </row>
-    <row r="139" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="139" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A139" s="9">
         <v>139</v>
       </c>
@@ -18117,7 +18133,7 @@
         <v>181</v>
       </c>
     </row>
-    <row r="140" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="140" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A140" s="9">
         <v>140</v>
       </c>
@@ -18194,7 +18210,7 @@
         <v>181</v>
       </c>
     </row>
-    <row r="141" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="141" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A141" s="9">
         <v>141</v>
       </c>
@@ -18271,7 +18287,7 @@
         <v>181</v>
       </c>
     </row>
-    <row r="142" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="142" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A142" s="9">
         <v>142</v>
       </c>
@@ -18348,7 +18364,7 @@
         <v>181</v>
       </c>
     </row>
-    <row r="143" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="143" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A143" s="9">
         <v>143</v>
       </c>
@@ -18425,7 +18441,7 @@
         <v>181</v>
       </c>
     </row>
-    <row r="144" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="144" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A144" s="9">
         <v>144</v>
       </c>
@@ -18502,7 +18518,7 @@
         <v>181</v>
       </c>
     </row>
-    <row r="145" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="145" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A145" s="9">
         <v>145</v>
       </c>
@@ -18579,7 +18595,7 @@
         <v>181</v>
       </c>
     </row>
-    <row r="146" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="146" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A146" s="9">
         <v>146</v>
       </c>
@@ -18656,7 +18672,7 @@
         <v>181</v>
       </c>
     </row>
-    <row r="147" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="147" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A147" s="9">
         <v>147</v>
       </c>
@@ -18733,7 +18749,7 @@
         <v>181</v>
       </c>
     </row>
-    <row r="148" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="148" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A148" s="9">
         <v>148</v>
       </c>
@@ -18810,7 +18826,7 @@
         <v>181</v>
       </c>
     </row>
-    <row r="149" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="149" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A149" s="9">
         <v>149</v>
       </c>
@@ -18887,7 +18903,7 @@
         <v>181</v>
       </c>
     </row>
-    <row r="150" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="150" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A150" s="9">
         <v>150</v>
       </c>
@@ -18964,7 +18980,7 @@
         <v>181</v>
       </c>
     </row>
-    <row r="151" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="151" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A151" s="9">
         <v>151</v>
       </c>
@@ -19041,7 +19057,7 @@
         <v>181</v>
       </c>
     </row>
-    <row r="152" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="152" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A152" s="9">
         <v>152</v>
       </c>
@@ -19118,7 +19134,7 @@
         <v>181</v>
       </c>
     </row>
-    <row r="153" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="153" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A153" s="9">
         <v>153</v>
       </c>
@@ -19195,7 +19211,7 @@
         <v>181</v>
       </c>
     </row>
-    <row r="154" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="154" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A154" s="9">
         <v>154</v>
       </c>
@@ -19272,7 +19288,7 @@
         <v>181</v>
       </c>
     </row>
-    <row r="155" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="155" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A155" s="9">
         <v>155</v>
       </c>
@@ -19349,7 +19365,7 @@
         <v>181</v>
       </c>
     </row>
-    <row r="156" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="156" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A156" s="9">
         <v>156</v>
       </c>
@@ -19426,7 +19442,7 @@
         <v>181</v>
       </c>
     </row>
-    <row r="157" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="157" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A157" s="9">
         <v>157</v>
       </c>

--- a/Versão5/ABNT/Ontologia_NBR15965_2N.xlsx
+++ b/Versão5/ABNT/Ontologia_NBR15965_2N.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Construtor_Onto\ABNT\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A9C3EC98-90B8-4049-94DD-D79BDCCF9392}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BF3BA571-3EC8-4A11-A37E-EC5DE9BDAEAE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-103" yWindow="-103" windowWidth="22149" windowHeight="13200" activeTab="1" xr2:uid="{82C81399-C775-48F3-A336-58DE5F35A6D9}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="24240" windowHeight="13290" activeTab="1" xr2:uid="{82C81399-C775-48F3-A336-58DE5F35A6D9}"/>
   </bookViews>
   <sheets>
     <sheet name="Projeto" sheetId="8" r:id="rId1"/>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4329" uniqueCount="568">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4393" uniqueCount="588">
   <si>
     <t>Indivíduo</t>
   </si>
@@ -1795,6 +1795,66 @@
   </si>
   <si>
     <t>[ IfcSpace : IfcRelSpaceBoundary : IfcSpaceType : IfcSpaceTypeEnum ]</t>
+  </si>
+  <si>
+    <t>Entrepreneurs</t>
+  </si>
+  <si>
+    <t>Designers</t>
+  </si>
+  <si>
+    <t>Managers</t>
+  </si>
+  <si>
+    <t>Builders and Contractors</t>
+  </si>
+  <si>
+    <t>Construction inspectors</t>
+  </si>
+  <si>
+    <t>Supporters</t>
+  </si>
+  <si>
+    <t>Marketers</t>
+  </si>
+  <si>
+    <t>Outsourced</t>
+  </si>
+  <si>
+    <t>Participating Companies and Groups</t>
+  </si>
+  <si>
+    <t>Emprendedores</t>
+  </si>
+  <si>
+    <t>Diseñadores</t>
+  </si>
+  <si>
+    <t>Entrenadores</t>
+  </si>
+  <si>
+    <t>Constructores y contratistas</t>
+  </si>
+  <si>
+    <t>Inspectores de construcción</t>
+  </si>
+  <si>
+    <t>Aficionados</t>
+  </si>
+  <si>
+    <t>Profesionales del marketing</t>
+  </si>
+  <si>
+    <t>Subcontratado</t>
+  </si>
+  <si>
+    <t>Empresas y Grupos Participantes</t>
+  </si>
+  <si>
+    <t>Parâmetros Rvt</t>
+  </si>
+  <si>
+    <t>Atributos Ifc</t>
   </si>
 </sst>
 </file>
@@ -2390,7 +2450,7 @@
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
     <cellStyle name="Normal 2" xfId="1" xr:uid="{A0D90F96-026A-4EEB-BDCF-93327D239D7A}"/>
   </cellStyles>
-  <dxfs count="62">
+  <dxfs count="63">
     <dxf>
       <font>
         <b val="0"/>
@@ -2423,6 +2483,14 @@
         <i/>
         <strike val="0"/>
         <color theme="0"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i/>
+        <strike val="0"/>
+        <color theme="0" tint="-0.499984740745262"/>
       </font>
     </dxf>
     <dxf>
@@ -4252,33 +4320,33 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{A07C259E-03F8-41A3-821C-289758C0BF1B}" name="Tabla2" displayName="Tabla2" ref="A2:Y157" headerRowCount="0" totalsRowShown="0" headerRowDxfId="61" dataDxfId="59" headerRowBorderDxfId="60" tableBorderDxfId="58" totalsRowBorderDxfId="57">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{A07C259E-03F8-41A3-821C-289758C0BF1B}" name="Tabla2" displayName="Tabla2" ref="A2:Y157" headerRowCount="0" totalsRowShown="0" headerRowDxfId="62" dataDxfId="60" headerRowBorderDxfId="61" tableBorderDxfId="59" totalsRowBorderDxfId="58">
   <tableColumns count="25">
-    <tableColumn id="1" xr3:uid="{D841A366-4823-4EF9-B009-219AA94AF50A}" name="1" headerRowDxfId="56" dataDxfId="55"/>
-    <tableColumn id="2" xr3:uid="{41E717E1-E3DE-44C1-91C4-719DAB59A464}" name="Indivíduo" headerRowDxfId="54" dataDxfId="53"/>
-    <tableColumn id="3" xr3:uid="{38346B1D-47C6-4B44-A19C-766D16435669}" name="Classe" headerRowDxfId="52" dataDxfId="51"/>
-    <tableColumn id="5" xr3:uid="{27FF4C79-5131-4593-84DE-98F435DB6954}" name="Coluna2" headerRowDxfId="50" dataDxfId="49"/>
-    <tableColumn id="4" xr3:uid="{B4C1140F-50EB-4951-8734-6338EB3CF628}" name="Coluna1" headerRowDxfId="48" dataDxfId="47"/>
-    <tableColumn id="11" xr3:uid="{1EE4C35C-9E89-4C7C-8F68-2AC866434D95}" name="Coluna8" headerRowDxfId="46" dataDxfId="45"/>
-    <tableColumn id="10" xr3:uid="{0C28831F-E05A-4812-BB49-6E3DB059FDDA}" name="Coluna7" headerRowDxfId="44" dataDxfId="43"/>
-    <tableColumn id="9" xr3:uid="{C46F6396-5D54-4379-8FE7-47754ED408FB}" name="Coluna6" headerRowDxfId="42" dataDxfId="41"/>
-    <tableColumn id="14" xr3:uid="{7255F88A-C196-4C7D-BC78-487E43C6076E}" name="Coluna9" headerRowDxfId="40" dataDxfId="39"/>
-    <tableColumn id="15" xr3:uid="{CB39996D-E39C-41DF-9024-09188503F3A9}" name="Coluna10" headerRowDxfId="38" dataDxfId="37"/>
-    <tableColumn id="8" xr3:uid="{DC6BCDF7-14DD-4B0D-951F-937897AADF11}" name="Coluna5" headerRowDxfId="36" dataDxfId="35"/>
-    <tableColumn id="25" xr3:uid="{6E36A2EC-C3DA-4DF1-80AB-262ECBFDA8D3}" name="Coluna20" headerRowDxfId="34" dataDxfId="33"/>
-    <tableColumn id="24" xr3:uid="{7DA1B28C-8D87-49B1-8B12-94BDA4E3634B}" name="Coluna19" headerRowDxfId="32" dataDxfId="31"/>
-    <tableColumn id="12" xr3:uid="{72731FBF-D3F4-42FD-AF7E-09CD79716DE3}" name="Fato (11)" headerRowDxfId="30" dataDxfId="29"/>
-    <tableColumn id="13" xr3:uid="{40ED8FBD-39D6-4C0F-867B-9AA8C9C09316}" name="Valor8" headerRowDxfId="28" dataDxfId="27"/>
-    <tableColumn id="6" xr3:uid="{D7E37E62-C3F1-48D0-9ECE-1603C43E1947}" name="Coluna3" headerRowDxfId="26" dataDxfId="25"/>
-    <tableColumn id="7" xr3:uid="{8EAEA0F2-9F55-4FEE-86F2-D1912AEFC7F4}" name="Coluna4" headerRowDxfId="24" dataDxfId="23"/>
-    <tableColumn id="16" xr3:uid="{CB767617-3A28-42EC-8E47-CE6204F6D856}" name="Coluna11" headerRowDxfId="22" dataDxfId="21"/>
-    <tableColumn id="17" xr3:uid="{E29ADF84-36FF-41F7-9847-17BC340BAE5F}" name="Coluna12" headerRowDxfId="20" dataDxfId="19"/>
-    <tableColumn id="18" xr3:uid="{B5ADD4A7-EE28-45D9-B6FF-C285C2CD6E37}" name="Coluna13" headerRowDxfId="18" dataDxfId="17"/>
-    <tableColumn id="19" xr3:uid="{7FEDF53D-D312-4CF1-8EB3-4A56B77DEAA1}" name="Coluna14" headerRowDxfId="16" dataDxfId="15"/>
-    <tableColumn id="20" xr3:uid="{44C51568-5619-4D1B-B5B4-F2CF79CAB094}" name="Coluna15" headerRowDxfId="14" dataDxfId="13"/>
-    <tableColumn id="21" xr3:uid="{2A7C2A78-BAF9-429F-B898-EF931D80D830}" name="Coluna16" headerRowDxfId="12" dataDxfId="11"/>
-    <tableColumn id="22" xr3:uid="{3BB87186-A8C3-4EE2-9555-ACB7C40B9882}" name="Coluna17" headerRowDxfId="10" dataDxfId="9"/>
-    <tableColumn id="23" xr3:uid="{C574DFC8-E441-4BB1-A97D-83D5A9C08508}" name="Coluna18" headerRowDxfId="8" dataDxfId="7"/>
+    <tableColumn id="1" xr3:uid="{D841A366-4823-4EF9-B009-219AA94AF50A}" name="1" headerRowDxfId="57" dataDxfId="56"/>
+    <tableColumn id="2" xr3:uid="{41E717E1-E3DE-44C1-91C4-719DAB59A464}" name="Indivíduo" headerRowDxfId="55" dataDxfId="54"/>
+    <tableColumn id="3" xr3:uid="{38346B1D-47C6-4B44-A19C-766D16435669}" name="Classe" headerRowDxfId="53" dataDxfId="52"/>
+    <tableColumn id="5" xr3:uid="{27FF4C79-5131-4593-84DE-98F435DB6954}" name="Coluna2" headerRowDxfId="51" dataDxfId="50"/>
+    <tableColumn id="4" xr3:uid="{B4C1140F-50EB-4951-8734-6338EB3CF628}" name="Coluna1" headerRowDxfId="49" dataDxfId="48"/>
+    <tableColumn id="11" xr3:uid="{1EE4C35C-9E89-4C7C-8F68-2AC866434D95}" name="Coluna8" headerRowDxfId="47" dataDxfId="46"/>
+    <tableColumn id="10" xr3:uid="{0C28831F-E05A-4812-BB49-6E3DB059FDDA}" name="Coluna7" headerRowDxfId="45" dataDxfId="44"/>
+    <tableColumn id="9" xr3:uid="{C46F6396-5D54-4379-8FE7-47754ED408FB}" name="Coluna6" headerRowDxfId="43" dataDxfId="42"/>
+    <tableColumn id="14" xr3:uid="{7255F88A-C196-4C7D-BC78-487E43C6076E}" name="Coluna9" headerRowDxfId="41" dataDxfId="40"/>
+    <tableColumn id="15" xr3:uid="{CB39996D-E39C-41DF-9024-09188503F3A9}" name="Coluna10" headerRowDxfId="39" dataDxfId="38"/>
+    <tableColumn id="8" xr3:uid="{DC6BCDF7-14DD-4B0D-951F-937897AADF11}" name="Coluna5" headerRowDxfId="37" dataDxfId="36"/>
+    <tableColumn id="25" xr3:uid="{6E36A2EC-C3DA-4DF1-80AB-262ECBFDA8D3}" name="Coluna20" headerRowDxfId="35" dataDxfId="34"/>
+    <tableColumn id="24" xr3:uid="{7DA1B28C-8D87-49B1-8B12-94BDA4E3634B}" name="Coluna19" headerRowDxfId="33" dataDxfId="32"/>
+    <tableColumn id="12" xr3:uid="{72731FBF-D3F4-42FD-AF7E-09CD79716DE3}" name="Fato (11)" headerRowDxfId="31" dataDxfId="30"/>
+    <tableColumn id="13" xr3:uid="{40ED8FBD-39D6-4C0F-867B-9AA8C9C09316}" name="Valor8" headerRowDxfId="29" dataDxfId="28"/>
+    <tableColumn id="6" xr3:uid="{D7E37E62-C3F1-48D0-9ECE-1603C43E1947}" name="Coluna3" headerRowDxfId="27" dataDxfId="26"/>
+    <tableColumn id="7" xr3:uid="{8EAEA0F2-9F55-4FEE-86F2-D1912AEFC7F4}" name="Coluna4" headerRowDxfId="25" dataDxfId="24"/>
+    <tableColumn id="16" xr3:uid="{CB767617-3A28-42EC-8E47-CE6204F6D856}" name="Coluna11" headerRowDxfId="23" dataDxfId="22"/>
+    <tableColumn id="17" xr3:uid="{E29ADF84-36FF-41F7-9847-17BC340BAE5F}" name="Coluna12" headerRowDxfId="21" dataDxfId="20"/>
+    <tableColumn id="18" xr3:uid="{B5ADD4A7-EE28-45D9-B6FF-C285C2CD6E37}" name="Coluna13" headerRowDxfId="19" dataDxfId="18"/>
+    <tableColumn id="19" xr3:uid="{7FEDF53D-D312-4CF1-8EB3-4A56B77DEAA1}" name="Coluna14" headerRowDxfId="17" dataDxfId="16"/>
+    <tableColumn id="20" xr3:uid="{44C51568-5619-4D1B-B5B4-F2CF79CAB094}" name="Coluna15" headerRowDxfId="15" dataDxfId="14"/>
+    <tableColumn id="21" xr3:uid="{2A7C2A78-BAF9-429F-B898-EF931D80D830}" name="Coluna16" headerRowDxfId="13" dataDxfId="12"/>
+    <tableColumn id="22" xr3:uid="{3BB87186-A8C3-4EE2-9555-ACB7C40B9882}" name="Coluna17" headerRowDxfId="11" dataDxfId="10"/>
+    <tableColumn id="23" xr3:uid="{C574DFC8-E441-4BB1-A97D-83D5A9C08508}" name="Coluna18" headerRowDxfId="9" dataDxfId="8"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="0" showColumnStripes="0"/>
 </table>
@@ -4603,15 +4671,15 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{03763A90-6A45-4DA0-A35B-2601294A84FF}">
   <sheetPr codeName="Planilha1"/>
   <dimension ref="A1:C39"/>
-  <sheetFormatPr defaultColWidth="11" defaultRowHeight="9" customHeight="1" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="11" defaultRowHeight="9" customHeight="1" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="9.69921875" style="43" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="65.69921875" style="43" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="9.6640625" style="43" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="65.6640625" style="43" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="4.5" style="43" bestFit="1" customWidth="1"/>
     <col min="4" max="16384" width="11" style="43"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" ht="19" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:3" ht="18.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>4</v>
       </c>
@@ -4622,7 +4690,7 @@
         <v>403</v>
       </c>
     </row>
-    <row r="2" spans="1:3" ht="7.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:3" ht="7.35" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="3" t="s">
         <v>168</v>
       </c>
@@ -4633,7 +4701,7 @@
         <v>404</v>
       </c>
     </row>
-    <row r="3" spans="1:3" ht="7.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:3" ht="7.35" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="3" t="s">
         <v>169</v>
       </c>
@@ -4644,7 +4712,7 @@
         <v>404</v>
       </c>
     </row>
-    <row r="4" spans="1:3" ht="7.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:3" ht="7.35" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="4" t="s">
         <v>5</v>
       </c>
@@ -4655,7 +4723,7 @@
         <v>404</v>
       </c>
     </row>
-    <row r="5" spans="1:3" ht="7.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:3" ht="7.35" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="4" t="s">
         <v>6</v>
       </c>
@@ -4667,7 +4735,7 @@
         <v>404</v>
       </c>
     </row>
-    <row r="6" spans="1:3" ht="7.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:3" ht="7.35" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A6" s="4" t="s">
         <v>7</v>
       </c>
@@ -4679,7 +4747,7 @@
         <v>404</v>
       </c>
     </row>
-    <row r="7" spans="1:3" ht="7.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:3" ht="7.35" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A7" s="4" t="s">
         <v>8</v>
       </c>
@@ -4690,7 +4758,7 @@
         <v>404</v>
       </c>
     </row>
-    <row r="8" spans="1:3" ht="7.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:3" ht="7.35" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" s="39" t="s">
         <v>9</v>
       </c>
@@ -4701,7 +4769,7 @@
         <v>404</v>
       </c>
     </row>
-    <row r="9" spans="1:3" ht="7.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:3" ht="7.35" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A9" s="4" t="s">
         <v>170</v>
       </c>
@@ -4712,7 +4780,7 @@
         <v>404</v>
       </c>
     </row>
-    <row r="10" spans="1:3" ht="7.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:3" ht="7.35" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A10" s="4" t="s">
         <v>172</v>
       </c>
@@ -4723,7 +4791,7 @@
         <v>404</v>
       </c>
     </row>
-    <row r="11" spans="1:3" ht="7.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:3" ht="7.35" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A11" s="4" t="s">
         <v>173</v>
       </c>
@@ -4734,7 +4802,7 @@
         <v>404</v>
       </c>
     </row>
-    <row r="12" spans="1:3" ht="7.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:3" ht="7.35" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A12" s="4" t="s">
         <v>10</v>
       </c>
@@ -4745,7 +4813,7 @@
         <v>404</v>
       </c>
     </row>
-    <row r="13" spans="1:3" ht="7.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:3" ht="7.35" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A13" s="4" t="s">
         <v>174</v>
       </c>
@@ -4756,7 +4824,7 @@
         <v>404</v>
       </c>
     </row>
-    <row r="14" spans="1:3" ht="7.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:3" ht="7.35" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A14" s="4" t="s">
         <v>175</v>
       </c>
@@ -4767,7 +4835,7 @@
         <v>404</v>
       </c>
     </row>
-    <row r="15" spans="1:3" ht="7.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:3" ht="7.35" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A15" s="4" t="s">
         <v>176</v>
       </c>
@@ -4778,7 +4846,7 @@
         <v>404</v>
       </c>
     </row>
-    <row r="16" spans="1:3" ht="7.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:3" ht="7.35" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A16" s="4" t="s">
         <v>177</v>
       </c>
@@ -4789,7 +4857,7 @@
         <v>404</v>
       </c>
     </row>
-    <row r="17" spans="1:3" ht="7.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:3" ht="7.35" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A17" s="4" t="s">
         <v>12</v>
       </c>
@@ -4800,19 +4868,19 @@
         <v>404</v>
       </c>
     </row>
-    <row r="18" spans="1:3" ht="7.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:3" ht="7.35" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A18" s="4" t="s">
         <v>178</v>
       </c>
       <c r="B18" s="5">
         <f ca="1">NOW()</f>
-        <v>46249.323550694447</v>
+        <v>46253.599096296297</v>
       </c>
       <c r="C18" s="42" t="s">
         <v>404</v>
       </c>
     </row>
-    <row r="19" spans="1:3" ht="7.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:3" ht="7.35" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A19" s="4" t="s">
         <v>415</v>
       </c>
@@ -4823,7 +4891,7 @@
         <v>404</v>
       </c>
     </row>
-    <row r="20" spans="1:3" ht="7.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:3" ht="7.35" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A20" s="39" t="s">
         <v>411</v>
       </c>
@@ -4835,7 +4903,7 @@
         <v>405</v>
       </c>
     </row>
-    <row r="21" spans="1:3" ht="7.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:3" ht="7.35" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A21" s="39" t="s">
         <v>416</v>
       </c>
@@ -4847,7 +4915,7 @@
         <v>406</v>
       </c>
     </row>
-    <row r="22" spans="1:3" ht="7.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:3" ht="7.35" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A22" s="4" t="s">
         <v>167</v>
       </c>
@@ -4858,7 +4926,7 @@
         <v>404</v>
       </c>
     </row>
-    <row r="23" spans="1:3" ht="7.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:3" ht="7.35" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A23" s="4" t="s">
         <v>179</v>
       </c>
@@ -4869,7 +4937,7 @@
         <v>404</v>
       </c>
     </row>
-    <row r="24" spans="1:3" ht="7.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:3" ht="7.35" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A24" s="4" t="s">
         <v>184</v>
       </c>
@@ -4880,7 +4948,7 @@
         <v>404</v>
       </c>
     </row>
-    <row r="25" spans="1:3" ht="7.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:3" ht="7.35" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A25" s="4" t="s">
         <v>186</v>
       </c>
@@ -4891,7 +4959,7 @@
         <v>405</v>
       </c>
     </row>
-    <row r="26" spans="1:3" ht="7.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:3" ht="7.35" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A26" s="39" t="s">
         <v>400</v>
       </c>
@@ -4902,7 +4970,7 @@
         <v>406</v>
       </c>
     </row>
-    <row r="27" spans="1:3" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:3" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A27" s="39" t="s">
         <v>527</v>
       </c>
@@ -4913,7 +4981,7 @@
         <v>404</v>
       </c>
     </row>
-    <row r="28" spans="1:3" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:3" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A28" s="39" t="s">
         <v>529</v>
       </c>
@@ -4924,7 +4992,7 @@
         <v>404</v>
       </c>
     </row>
-    <row r="29" spans="1:3" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:3" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A29" s="39" t="s">
         <v>531</v>
       </c>
@@ -4935,7 +5003,7 @@
         <v>404</v>
       </c>
     </row>
-    <row r="30" spans="1:3" s="63" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:3" s="63" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A30" s="39" t="s">
         <v>533</v>
       </c>
@@ -4946,7 +5014,7 @@
         <v>404</v>
       </c>
     </row>
-    <row r="31" spans="1:3" s="63" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:3" s="63" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A31" s="39" t="s">
         <v>535</v>
       </c>
@@ -4957,7 +5025,7 @@
         <v>404</v>
       </c>
     </row>
-    <row r="32" spans="1:3" s="63" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:3" s="63" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A32" s="39" t="s">
         <v>537</v>
       </c>
@@ -4968,7 +5036,7 @@
         <v>404</v>
       </c>
     </row>
-    <row r="33" spans="1:3" s="63" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="33" spans="1:3" s="63" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A33" s="39" t="s">
         <v>539</v>
       </c>
@@ -4979,7 +5047,7 @@
         <v>404</v>
       </c>
     </row>
-    <row r="34" spans="1:3" s="63" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="34" spans="1:3" s="63" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A34" s="39" t="s">
         <v>541</v>
       </c>
@@ -4990,7 +5058,7 @@
         <v>404</v>
       </c>
     </row>
-    <row r="35" spans="1:3" s="63" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="35" spans="1:3" s="63" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A35" s="39" t="s">
         <v>543</v>
       </c>
@@ -5001,7 +5069,7 @@
         <v>404</v>
       </c>
     </row>
-    <row r="36" spans="1:3" s="63" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="36" spans="1:3" s="63" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A36" s="39" t="s">
         <v>545</v>
       </c>
@@ -5012,7 +5080,7 @@
         <v>404</v>
       </c>
     </row>
-    <row r="37" spans="1:3" s="63" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="37" spans="1:3" s="63" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A37" s="39" t="s">
         <v>547</v>
       </c>
@@ -5023,7 +5091,7 @@
         <v>404</v>
       </c>
     </row>
-    <row r="38" spans="1:3" customFormat="1" ht="10" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:3" customFormat="1" ht="9.9499999999999993" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A38" s="4" t="s">
         <v>549</v>
       </c>
@@ -5034,7 +5102,7 @@
         <v>404</v>
       </c>
     </row>
-    <row r="39" spans="1:3" s="67" customFormat="1" ht="9.65" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="39" spans="1:3" s="67" customFormat="1" ht="9.6" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A39" s="39" t="s">
         <v>551</v>
       </c>
@@ -5060,35 +5128,37 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{958751C2-A34E-4345-8D6A-082603A025F9}">
   <sheetPr codeName="Planilha2"/>
-  <dimension ref="A1:AA23"/>
-  <sheetFormatPr defaultRowHeight="6.75" customHeight="1" x14ac:dyDescent="0.3"/>
+  <dimension ref="A1:AC23"/>
+  <sheetFormatPr defaultRowHeight="6.75" customHeight="1" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="1.8984375" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="5.5" style="34" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="6.09765625" style="34" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="7.8984375" style="34" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="5.796875" style="34" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="11.5" style="34" bestFit="1" customWidth="1"/>
-    <col min="7" max="11" width="8.3984375" style="34" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="6.5" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="7.8984375" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="6.5" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="11.5" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="62.296875" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="64.69921875" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="4.796875" style="34" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="6.09765625" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="7.8984375" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="5.796875" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="7.796875" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="7.5" style="34" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="45.69921875" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="36.09765625" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="6.69921875" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="57" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="2.83203125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="7.33203125" style="34" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="8.1640625" style="34" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="10.5" style="34" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="7.6640625" style="34" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.83203125" style="34" bestFit="1" customWidth="1"/>
+    <col min="7" max="11" width="11.83203125" style="34" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="8.1640625" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="10.5" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="8" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.83203125" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="78.1640625" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="80.5" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="71.6640625" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="5" style="34" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="8.1640625" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="10.5" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="7.6640625" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="10" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="9.83203125" style="34" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="43.83203125" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="9.83203125" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="44.83203125" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="8.83203125" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="8.6640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:27" ht="37.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:29" ht="37.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="22" t="s">
         <v>349</v>
       </c>
@@ -5140,38 +5210,44 @@
       <c r="Q1" s="24" t="s">
         <v>369</v>
       </c>
-      <c r="R1" s="24" t="s">
+      <c r="R1" s="37" t="s">
+        <v>399</v>
+      </c>
+      <c r="S1" s="24" t="s">
         <v>393</v>
       </c>
-      <c r="S1" s="24" t="s">
+      <c r="T1" s="24" t="s">
         <v>351</v>
       </c>
-      <c r="T1" s="24" t="s">
+      <c r="U1" s="24" t="s">
         <v>370</v>
       </c>
-      <c r="U1" s="24" t="s">
+      <c r="V1" s="24" t="s">
         <v>353</v>
       </c>
-      <c r="V1" s="24" t="s">
+      <c r="W1" s="24" t="s">
         <v>352</v>
       </c>
-      <c r="W1" s="59" t="s">
+      <c r="X1" s="59" t="s">
         <v>371</v>
       </c>
-      <c r="X1" s="24" t="s">
+      <c r="Y1" s="24" t="s">
         <v>397</v>
       </c>
-      <c r="Y1" s="24" t="s">
+      <c r="Z1" s="24" t="s">
+        <v>586</v>
+      </c>
+      <c r="AA1" s="24" t="s">
         <v>398</v>
       </c>
-      <c r="Z1" s="24" t="s">
+      <c r="AB1" s="24" t="s">
+        <v>587</v>
+      </c>
+      <c r="AC1" s="24" t="s">
         <v>372</v>
       </c>
-      <c r="AA1" s="37" t="s">
-        <v>399</v>
-      </c>
-    </row>
-    <row r="2" spans="1:27" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="2" spans="1:29" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="49">
         <v>2</v>
       </c>
@@ -5227,42 +5303,48 @@
       <c r="Q2" s="51" t="s">
         <v>489</v>
       </c>
-      <c r="R2" s="38" t="s">
-        <v>181</v>
-      </c>
-      <c r="S2" s="52" t="str">
-        <f t="shared" ref="S2:U14" si="2">SUBSTITUTE(C2, "_", " ")</f>
+      <c r="R2" s="53" t="s">
+        <v>490</v>
+      </c>
+      <c r="S2" s="38" t="s">
+        <v>181</v>
+      </c>
+      <c r="T2" s="52" t="str">
+        <f t="shared" ref="T2:V14" si="2">SUBSTITUTE(C2, "_", " ")</f>
         <v>Normativos</v>
       </c>
-      <c r="T2" s="52" t="str">
+      <c r="U2" s="52" t="str">
         <f t="shared" si="2"/>
         <v>ABNT</v>
       </c>
-      <c r="U2" s="51" t="str">
+      <c r="V2" s="51" t="str">
         <f t="shared" si="2"/>
         <v>NBR.Parte</v>
       </c>
-      <c r="V2" s="38" t="s">
+      <c r="W2" s="38" t="s">
         <v>419</v>
       </c>
-      <c r="W2" s="58" t="str">
-        <f t="shared" ref="W2:W14" si="3">CONCATENATE("Key-ABNT-",A2)</f>
+      <c r="X2" s="58" t="str">
+        <f t="shared" ref="X2:X14" si="3">CONCATENATE("Key-ABNT-",A2)</f>
         <v>Key-ABNT-2</v>
       </c>
-      <c r="X2" s="38" t="s">
+      <c r="Y2" s="38" t="s">
         <v>563</v>
       </c>
-      <c r="Y2" s="38" t="s">
+      <c r="Z2" s="38" t="s">
+        <v>556</v>
+      </c>
+      <c r="AA2" s="38" t="s">
         <v>564</v>
       </c>
-      <c r="Z2" s="38" t="s">
+      <c r="AB2" s="38" t="s">
+        <v>556</v>
+      </c>
+      <c r="AC2" s="38" t="s">
         <v>420</v>
       </c>
-      <c r="AA2" s="53" t="s">
-        <v>490</v>
-      </c>
-    </row>
-    <row r="3" spans="1:27" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="3" spans="1:29" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="49">
         <v>3</v>
       </c>
@@ -5318,42 +5400,48 @@
       <c r="Q3" s="51" t="s">
         <v>492</v>
       </c>
-      <c r="R3" s="38" t="s">
-        <v>181</v>
-      </c>
-      <c r="S3" s="52" t="str">
+      <c r="R3" s="53" t="s">
+        <v>493</v>
+      </c>
+      <c r="S3" s="38" t="s">
+        <v>181</v>
+      </c>
+      <c r="T3" s="52" t="str">
         <f t="shared" si="2"/>
         <v>Normativos</v>
       </c>
-      <c r="T3" s="52" t="str">
+      <c r="U3" s="52" t="str">
         <f t="shared" si="2"/>
         <v>ABNT</v>
       </c>
-      <c r="U3" s="51" t="str">
+      <c r="V3" s="51" t="str">
         <f t="shared" si="2"/>
         <v>NBR.Parte</v>
       </c>
-      <c r="V3" s="38" t="s">
+      <c r="W3" s="38" t="s">
         <v>419</v>
       </c>
-      <c r="W3" s="58" t="str">
+      <c r="X3" s="58" t="str">
         <f t="shared" si="3"/>
         <v>Key-ABNT-3</v>
       </c>
-      <c r="X3" s="38" t="s">
+      <c r="Y3" s="38" t="s">
         <v>565</v>
       </c>
-      <c r="Y3" s="38" t="s">
+      <c r="Z3" s="38" t="s">
+        <v>556</v>
+      </c>
+      <c r="AA3" s="38" t="s">
         <v>566</v>
       </c>
-      <c r="Z3" s="38" t="s">
+      <c r="AB3" s="38" t="s">
+        <v>556</v>
+      </c>
+      <c r="AC3" s="38" t="s">
         <v>421</v>
       </c>
-      <c r="AA3" s="53" t="s">
-        <v>493</v>
-      </c>
-    </row>
-    <row r="4" spans="1:27" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="4" spans="1:29" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="49">
         <v>4</v>
       </c>
@@ -5409,42 +5497,48 @@
       <c r="Q4" s="51" t="s">
         <v>495</v>
       </c>
-      <c r="R4" s="38" t="s">
-        <v>181</v>
-      </c>
-      <c r="S4" s="52" t="str">
+      <c r="R4" s="53" t="s">
+        <v>496</v>
+      </c>
+      <c r="S4" s="38" t="s">
+        <v>181</v>
+      </c>
+      <c r="T4" s="52" t="str">
         <f t="shared" si="2"/>
         <v>Normativos</v>
       </c>
-      <c r="T4" s="52" t="str">
+      <c r="U4" s="52" t="str">
         <f t="shared" si="2"/>
         <v>ABNT</v>
       </c>
-      <c r="U4" s="51" t="str">
+      <c r="V4" s="51" t="str">
         <f t="shared" si="2"/>
         <v>NBR.Parte</v>
       </c>
-      <c r="V4" s="38" t="s">
+      <c r="W4" s="38" t="s">
         <v>419</v>
       </c>
-      <c r="W4" s="58" t="str">
+      <c r="X4" s="58" t="str">
         <f t="shared" si="3"/>
         <v>Key-ABNT-4</v>
       </c>
-      <c r="X4" s="38" t="s">
+      <c r="Y4" s="38" t="s">
         <v>556</v>
       </c>
-      <c r="Y4" s="38" t="s">
+      <c r="Z4" s="38" t="s">
+        <v>556</v>
+      </c>
+      <c r="AA4" s="38" t="s">
         <v>557</v>
       </c>
-      <c r="Z4" s="38" t="s">
+      <c r="AB4" s="38" t="s">
+        <v>556</v>
+      </c>
+      <c r="AC4" s="38" t="s">
         <v>422</v>
       </c>
-      <c r="AA4" s="53" t="s">
-        <v>496</v>
-      </c>
-    </row>
-    <row r="5" spans="1:27" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="5" spans="1:29" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="49">
         <v>5</v>
       </c>
@@ -5500,42 +5594,48 @@
       <c r="Q5" s="51" t="s">
         <v>498</v>
       </c>
-      <c r="R5" s="38" t="s">
-        <v>181</v>
-      </c>
-      <c r="S5" s="52" t="str">
+      <c r="R5" s="53" t="s">
+        <v>499</v>
+      </c>
+      <c r="S5" s="38" t="s">
+        <v>181</v>
+      </c>
+      <c r="T5" s="52" t="str">
         <f t="shared" si="2"/>
         <v>Normativos</v>
       </c>
-      <c r="T5" s="52" t="str">
+      <c r="U5" s="52" t="str">
         <f t="shared" si="2"/>
         <v>ABNT</v>
       </c>
-      <c r="U5" s="51" t="str">
+      <c r="V5" s="51" t="str">
         <f t="shared" si="2"/>
         <v>NBR.Parte</v>
       </c>
-      <c r="V5" s="38" t="s">
+      <c r="W5" s="38" t="s">
         <v>419</v>
       </c>
-      <c r="W5" s="58" t="str">
+      <c r="X5" s="58" t="str">
         <f t="shared" si="3"/>
         <v>Key-ABNT-5</v>
       </c>
-      <c r="X5" s="38" t="s">
+      <c r="Y5" s="38" t="s">
         <v>558</v>
       </c>
-      <c r="Y5" s="38" t="s">
+      <c r="Z5" s="38" t="s">
+        <v>556</v>
+      </c>
+      <c r="AA5" s="38" t="s">
         <v>559</v>
       </c>
-      <c r="Z5" s="38" t="s">
+      <c r="AB5" s="38" t="s">
+        <v>556</v>
+      </c>
+      <c r="AC5" s="38" t="s">
         <v>423</v>
       </c>
-      <c r="AA5" s="53" t="s">
-        <v>499</v>
-      </c>
-    </row>
-    <row r="6" spans="1:27" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="6" spans="1:29" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A6" s="49">
         <v>6</v>
       </c>
@@ -5591,42 +5691,48 @@
       <c r="Q6" s="51" t="s">
         <v>501</v>
       </c>
-      <c r="R6" s="38" t="s">
-        <v>181</v>
-      </c>
-      <c r="S6" s="52" t="str">
+      <c r="R6" s="53" t="s">
+        <v>502</v>
+      </c>
+      <c r="S6" s="38" t="s">
+        <v>181</v>
+      </c>
+      <c r="T6" s="52" t="str">
         <f t="shared" si="2"/>
         <v>Normativos</v>
       </c>
-      <c r="T6" s="52" t="str">
+      <c r="U6" s="52" t="str">
         <f t="shared" si="2"/>
         <v>ABNT</v>
       </c>
-      <c r="U6" s="51" t="str">
+      <c r="V6" s="51" t="str">
         <f t="shared" si="2"/>
         <v>NBR.Parte</v>
       </c>
-      <c r="V6" s="38" t="s">
+      <c r="W6" s="38" t="s">
         <v>419</v>
       </c>
-      <c r="W6" s="58" t="str">
+      <c r="X6" s="58" t="str">
         <f t="shared" si="3"/>
         <v>Key-ABNT-6</v>
       </c>
-      <c r="X6" s="38" t="s">
+      <c r="Y6" s="38" t="s">
         <v>556</v>
       </c>
-      <c r="Y6" s="38" t="s">
+      <c r="Z6" s="38" t="s">
+        <v>556</v>
+      </c>
+      <c r="AA6" s="38" t="s">
         <v>557</v>
       </c>
-      <c r="Z6" s="38" t="s">
+      <c r="AB6" s="38" t="s">
+        <v>556</v>
+      </c>
+      <c r="AC6" s="38" t="s">
         <v>424</v>
       </c>
-      <c r="AA6" s="53" t="s">
-        <v>502</v>
-      </c>
-    </row>
-    <row r="7" spans="1:27" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="7" spans="1:29" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A7" s="49">
         <v>7</v>
       </c>
@@ -5682,42 +5788,48 @@
       <c r="Q7" s="51" t="s">
         <v>504</v>
       </c>
-      <c r="R7" s="38" t="s">
-        <v>181</v>
-      </c>
-      <c r="S7" s="52" t="str">
+      <c r="R7" s="53" t="s">
+        <v>505</v>
+      </c>
+      <c r="S7" s="38" t="s">
+        <v>181</v>
+      </c>
+      <c r="T7" s="52" t="str">
         <f t="shared" si="2"/>
         <v>Normativos</v>
       </c>
-      <c r="T7" s="52" t="str">
+      <c r="U7" s="52" t="str">
         <f t="shared" si="2"/>
         <v>ABNT</v>
       </c>
-      <c r="U7" s="51" t="str">
+      <c r="V7" s="51" t="str">
         <f t="shared" si="2"/>
         <v>NBR.Parte</v>
       </c>
-      <c r="V7" s="38" t="s">
+      <c r="W7" s="38" t="s">
         <v>419</v>
       </c>
-      <c r="W7" s="58" t="str">
+      <c r="X7" s="58" t="str">
         <f t="shared" si="3"/>
         <v>Key-ABNT-7</v>
       </c>
-      <c r="X7" s="38" t="s">
-        <v>556</v>
-      </c>
       <c r="Y7" s="38" t="s">
         <v>556</v>
       </c>
       <c r="Z7" s="38" t="s">
+        <v>556</v>
+      </c>
+      <c r="AA7" s="38" t="s">
+        <v>556</v>
+      </c>
+      <c r="AB7" s="38" t="s">
+        <v>556</v>
+      </c>
+      <c r="AC7" s="38" t="s">
         <v>425</v>
       </c>
-      <c r="AA7" s="53" t="s">
-        <v>505</v>
-      </c>
-    </row>
-    <row r="8" spans="1:27" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="8" spans="1:29" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" s="49">
         <v>8</v>
       </c>
@@ -5773,42 +5885,48 @@
       <c r="Q8" s="51" t="s">
         <v>507</v>
       </c>
-      <c r="R8" s="38" t="s">
-        <v>181</v>
-      </c>
-      <c r="S8" s="52" t="str">
+      <c r="R8" s="53" t="s">
+        <v>508</v>
+      </c>
+      <c r="S8" s="38" t="s">
+        <v>181</v>
+      </c>
+      <c r="T8" s="52" t="str">
         <f t="shared" si="2"/>
         <v>Normativos</v>
       </c>
-      <c r="T8" s="52" t="str">
+      <c r="U8" s="52" t="str">
         <f t="shared" si="2"/>
         <v>ABNT</v>
       </c>
-      <c r="U8" s="51" t="str">
+      <c r="V8" s="51" t="str">
         <f t="shared" si="2"/>
         <v>NBR.Parte</v>
       </c>
-      <c r="V8" s="38" t="s">
+      <c r="W8" s="38" t="s">
         <v>419</v>
       </c>
-      <c r="W8" s="58" t="str">
+      <c r="X8" s="58" t="str">
         <f t="shared" si="3"/>
         <v>Key-ABNT-8</v>
       </c>
-      <c r="X8" s="38" t="s">
-        <v>556</v>
-      </c>
       <c r="Y8" s="38" t="s">
         <v>556</v>
       </c>
       <c r="Z8" s="38" t="s">
+        <v>556</v>
+      </c>
+      <c r="AA8" s="38" t="s">
+        <v>556</v>
+      </c>
+      <c r="AB8" s="38" t="s">
+        <v>556</v>
+      </c>
+      <c r="AC8" s="38" t="s">
         <v>342</v>
       </c>
-      <c r="AA8" s="53" t="s">
-        <v>508</v>
-      </c>
-    </row>
-    <row r="9" spans="1:27" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="9" spans="1:29" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A9" s="49">
         <v>9</v>
       </c>
@@ -5864,42 +5982,48 @@
       <c r="Q9" s="51" t="s">
         <v>510</v>
       </c>
-      <c r="R9" s="38" t="s">
-        <v>181</v>
-      </c>
-      <c r="S9" s="52" t="str">
+      <c r="R9" s="53" t="s">
+        <v>511</v>
+      </c>
+      <c r="S9" s="38" t="s">
+        <v>181</v>
+      </c>
+      <c r="T9" s="52" t="str">
         <f t="shared" si="2"/>
         <v>Normativos</v>
       </c>
-      <c r="T9" s="52" t="str">
+      <c r="U9" s="52" t="str">
         <f t="shared" si="2"/>
         <v>ABNT</v>
       </c>
-      <c r="U9" s="51" t="str">
+      <c r="V9" s="51" t="str">
         <f t="shared" si="2"/>
         <v>NBR.Parte</v>
       </c>
-      <c r="V9" s="38" t="s">
+      <c r="W9" s="38" t="s">
         <v>419</v>
       </c>
-      <c r="W9" s="58" t="str">
+      <c r="X9" s="58" t="str">
         <f t="shared" si="3"/>
         <v>Key-ABNT-9</v>
       </c>
-      <c r="X9" s="38" t="s">
-        <v>556</v>
-      </c>
       <c r="Y9" s="38" t="s">
         <v>556</v>
       </c>
       <c r="Z9" s="38" t="s">
+        <v>556</v>
+      </c>
+      <c r="AA9" s="38" t="s">
+        <v>556</v>
+      </c>
+      <c r="AB9" s="38" t="s">
+        <v>556</v>
+      </c>
+      <c r="AC9" s="38" t="s">
         <v>426</v>
       </c>
-      <c r="AA9" s="53" t="s">
-        <v>511</v>
-      </c>
-    </row>
-    <row r="10" spans="1:27" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="10" spans="1:29" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A10" s="49">
         <v>10</v>
       </c>
@@ -5955,42 +6079,48 @@
       <c r="Q10" s="51" t="s">
         <v>513</v>
       </c>
-      <c r="R10" s="38" t="s">
-        <v>181</v>
-      </c>
-      <c r="S10" s="52" t="str">
+      <c r="R10" s="53" t="s">
+        <v>514</v>
+      </c>
+      <c r="S10" s="38" t="s">
+        <v>181</v>
+      </c>
+      <c r="T10" s="52" t="str">
         <f t="shared" si="2"/>
         <v>Normativos</v>
       </c>
-      <c r="T10" s="52" t="str">
+      <c r="U10" s="52" t="str">
         <f t="shared" si="2"/>
         <v>ABNT</v>
       </c>
-      <c r="U10" s="51" t="str">
+      <c r="V10" s="51" t="str">
         <f t="shared" si="2"/>
         <v>NBR.Parte</v>
       </c>
-      <c r="V10" s="38" t="s">
+      <c r="W10" s="38" t="s">
         <v>419</v>
       </c>
-      <c r="W10" s="58" t="str">
+      <c r="X10" s="58" t="str">
         <f t="shared" si="3"/>
         <v>Key-ABNT-10</v>
       </c>
-      <c r="X10" s="38" t="s">
-        <v>556</v>
-      </c>
       <c r="Y10" s="38" t="s">
         <v>556</v>
       </c>
       <c r="Z10" s="38" t="s">
+        <v>556</v>
+      </c>
+      <c r="AA10" s="38" t="s">
+        <v>556</v>
+      </c>
+      <c r="AB10" s="38" t="s">
+        <v>556</v>
+      </c>
+      <c r="AC10" s="38" t="s">
         <v>427</v>
       </c>
-      <c r="AA10" s="53" t="s">
-        <v>514</v>
-      </c>
-    </row>
-    <row r="11" spans="1:27" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="11" spans="1:29" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A11" s="49">
         <v>11</v>
       </c>
@@ -6046,42 +6176,48 @@
       <c r="Q11" s="51" t="s">
         <v>516</v>
       </c>
-      <c r="R11" s="38" t="s">
-        <v>181</v>
-      </c>
-      <c r="S11" s="52" t="str">
+      <c r="R11" s="53" t="s">
+        <v>517</v>
+      </c>
+      <c r="S11" s="38" t="s">
+        <v>181</v>
+      </c>
+      <c r="T11" s="52" t="str">
         <f t="shared" si="2"/>
         <v>Normativos</v>
       </c>
-      <c r="T11" s="52" t="str">
+      <c r="U11" s="52" t="str">
         <f t="shared" si="2"/>
         <v>ABNT</v>
       </c>
-      <c r="U11" s="51" t="str">
+      <c r="V11" s="51" t="str">
         <f t="shared" si="2"/>
         <v>NBR.Parte</v>
       </c>
-      <c r="V11" s="38" t="s">
+      <c r="W11" s="38" t="s">
         <v>419</v>
       </c>
-      <c r="W11" s="58" t="str">
+      <c r="X11" s="58" t="str">
         <f t="shared" si="3"/>
         <v>Key-ABNT-11</v>
       </c>
-      <c r="X11" s="38" t="s">
-        <v>556</v>
-      </c>
       <c r="Y11" s="38" t="s">
         <v>556</v>
       </c>
       <c r="Z11" s="38" t="s">
+        <v>556</v>
+      </c>
+      <c r="AA11" s="38" t="s">
+        <v>556</v>
+      </c>
+      <c r="AB11" s="38" t="s">
+        <v>556</v>
+      </c>
+      <c r="AC11" s="38" t="s">
         <v>428</v>
       </c>
-      <c r="AA11" s="53" t="s">
-        <v>517</v>
-      </c>
-    </row>
-    <row r="12" spans="1:27" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="12" spans="1:29" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A12" s="49">
         <v>12</v>
       </c>
@@ -6137,42 +6273,48 @@
       <c r="Q12" s="51" t="s">
         <v>519</v>
       </c>
-      <c r="R12" s="38" t="s">
-        <v>181</v>
-      </c>
-      <c r="S12" s="52" t="str">
+      <c r="R12" s="53" t="s">
+        <v>520</v>
+      </c>
+      <c r="S12" s="38" t="s">
+        <v>181</v>
+      </c>
+      <c r="T12" s="52" t="str">
         <f t="shared" si="2"/>
         <v>Normativos</v>
       </c>
-      <c r="T12" s="52" t="str">
+      <c r="U12" s="52" t="str">
         <f t="shared" si="2"/>
         <v>ABNT</v>
       </c>
-      <c r="U12" s="51" t="str">
+      <c r="V12" s="51" t="str">
         <f t="shared" si="2"/>
         <v>NBR.Parte</v>
       </c>
-      <c r="V12" s="38" t="s">
+      <c r="W12" s="38" t="s">
         <v>419</v>
       </c>
-      <c r="W12" s="58" t="str">
+      <c r="X12" s="58" t="str">
         <f t="shared" si="3"/>
         <v>Key-ABNT-12</v>
       </c>
-      <c r="X12" s="38" t="s">
+      <c r="Y12" s="38" t="s">
         <v>560</v>
       </c>
-      <c r="Y12" s="38" t="s">
+      <c r="Z12" s="38" t="s">
+        <v>556</v>
+      </c>
+      <c r="AA12" s="38" t="s">
         <v>567</v>
       </c>
-      <c r="Z12" s="38" t="s">
+      <c r="AB12" s="38" t="s">
+        <v>556</v>
+      </c>
+      <c r="AC12" s="38" t="s">
         <v>429</v>
       </c>
-      <c r="AA12" s="53" t="s">
-        <v>520</v>
-      </c>
-    </row>
-    <row r="13" spans="1:27" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="13" spans="1:29" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A13" s="49">
         <v>13</v>
       </c>
@@ -6228,42 +6370,48 @@
       <c r="Q13" s="51" t="s">
         <v>522</v>
       </c>
-      <c r="R13" s="38" t="s">
-        <v>181</v>
-      </c>
-      <c r="S13" s="52" t="str">
+      <c r="R13" s="53" t="s">
+        <v>523</v>
+      </c>
+      <c r="S13" s="38" t="s">
+        <v>181</v>
+      </c>
+      <c r="T13" s="52" t="str">
         <f t="shared" si="2"/>
         <v>Normativos</v>
       </c>
-      <c r="T13" s="52" t="str">
+      <c r="U13" s="52" t="str">
         <f t="shared" si="2"/>
         <v>ABNT</v>
       </c>
-      <c r="U13" s="51" t="str">
+      <c r="V13" s="51" t="str">
         <f t="shared" si="2"/>
         <v>NBR.Parte</v>
       </c>
-      <c r="V13" s="38" t="s">
+      <c r="W13" s="38" t="s">
         <v>419</v>
       </c>
-      <c r="W13" s="58" t="str">
+      <c r="X13" s="58" t="str">
         <f t="shared" si="3"/>
         <v>Key-ABNT-13</v>
       </c>
-      <c r="X13" s="38" t="s">
+      <c r="Y13" s="38" t="s">
         <v>560</v>
       </c>
-      <c r="Y13" s="38" t="s">
+      <c r="Z13" s="38" t="s">
+        <v>556</v>
+      </c>
+      <c r="AA13" s="38" t="s">
         <v>567</v>
       </c>
-      <c r="Z13" s="38" t="s">
+      <c r="AB13" s="38" t="s">
+        <v>556</v>
+      </c>
+      <c r="AC13" s="38" t="s">
         <v>430</v>
       </c>
-      <c r="AA13" s="53" t="s">
-        <v>523</v>
-      </c>
-    </row>
-    <row r="14" spans="1:27" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="14" spans="1:29" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A14" s="49">
         <v>14</v>
       </c>
@@ -6319,42 +6467,48 @@
       <c r="Q14" s="51" t="s">
         <v>525</v>
       </c>
-      <c r="R14" s="38" t="s">
-        <v>181</v>
-      </c>
-      <c r="S14" s="52" t="str">
+      <c r="R14" s="53" t="s">
+        <v>526</v>
+      </c>
+      <c r="S14" s="38" t="s">
+        <v>181</v>
+      </c>
+      <c r="T14" s="52" t="str">
         <f t="shared" si="2"/>
         <v>Normativos</v>
       </c>
-      <c r="T14" s="52" t="str">
+      <c r="U14" s="52" t="str">
         <f t="shared" si="2"/>
         <v>ABNT</v>
       </c>
-      <c r="U14" s="51" t="str">
+      <c r="V14" s="51" t="str">
         <f t="shared" si="2"/>
         <v>NBR.Parte</v>
       </c>
-      <c r="V14" s="38" t="s">
+      <c r="W14" s="38" t="s">
         <v>419</v>
       </c>
-      <c r="W14" s="58" t="str">
+      <c r="X14" s="58" t="str">
         <f t="shared" si="3"/>
         <v>Key-ABNT-14</v>
       </c>
-      <c r="X14" s="68" t="s">
+      <c r="Y14" s="68" t="s">
         <v>561</v>
       </c>
-      <c r="Y14" s="69" t="s">
+      <c r="Z14" s="38" t="s">
+        <v>556</v>
+      </c>
+      <c r="AA14" s="69" t="s">
         <v>562</v>
       </c>
-      <c r="Z14" s="38" t="s">
+      <c r="AB14" s="38" t="s">
+        <v>556</v>
+      </c>
+      <c r="AC14" s="38" t="s">
         <v>431</v>
       </c>
-      <c r="AA14" s="53" t="s">
-        <v>526</v>
-      </c>
-    </row>
-    <row r="15" spans="1:27" ht="6.9" customHeight="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="15" spans="1:29" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A15" s="49">
         <v>15</v>
       </c>
@@ -6407,47 +6561,51 @@
       <c r="P15" s="57" t="s">
         <v>468</v>
       </c>
-      <c r="Q15" s="51" t="str">
-        <f>_xlfn.TRANSLATE(P15,"pt","es")</f>
-        <v>Emprendedores</v>
-      </c>
-      <c r="R15" s="38" t="s">
-        <v>181</v>
-      </c>
-      <c r="S15" s="52" t="str">
-        <f t="shared" ref="S15:U17" si="6">SUBSTITUTE(C15, "_", " ")</f>
+      <c r="Q15" s="51" t="s">
+        <v>577</v>
+      </c>
+      <c r="R15" s="53" t="s">
+        <v>568</v>
+      </c>
+      <c r="S15" s="38" t="s">
+        <v>181</v>
+      </c>
+      <c r="T15" s="52" t="str">
+        <f t="shared" ref="T15:V17" si="6">SUBSTITUTE(C15, "_", " ")</f>
         <v>Normativos</v>
       </c>
-      <c r="T15" s="52" t="str">
+      <c r="U15" s="52" t="str">
         <f t="shared" si="6"/>
         <v>NBR.Temáticas</v>
       </c>
-      <c r="U15" s="51" t="str">
+      <c r="V15" s="51" t="str">
         <f t="shared" si="6"/>
         <v>NBR.N.RH</v>
       </c>
-      <c r="V15" s="38" t="s">
+      <c r="W15" s="38" t="s">
         <v>419</v>
       </c>
-      <c r="W15" s="58" t="str">
-        <f t="shared" ref="W15:W23" si="7">CONCATENATE("Key-ABNT-",A15)</f>
+      <c r="X15" s="58" t="str">
+        <f t="shared" ref="X15:X23" si="7">CONCATENATE("Key-ABNT-",A15)</f>
         <v>Key-ABNT-15</v>
-      </c>
-      <c r="X15" s="38" t="s">
-        <v>556</v>
       </c>
       <c r="Y15" s="38" t="s">
         <v>556</v>
       </c>
-      <c r="Z15" s="53" t="s">
+      <c r="Z15" s="38" t="s">
+        <v>556</v>
+      </c>
+      <c r="AA15" s="38" t="s">
+        <v>556</v>
+      </c>
+      <c r="AB15" s="38" t="s">
+        <v>556</v>
+      </c>
+      <c r="AC15" s="53" t="s">
         <v>477</v>
       </c>
-      <c r="AA15" s="53" t="str">
-        <f>_xlfn.TRANSLATE(P15,"pt","en")</f>
-        <v>Entrepreneurs</v>
-      </c>
-    </row>
-    <row r="16" spans="1:27" ht="6.9" customHeight="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="16" spans="1:29" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A16" s="49">
         <v>16</v>
       </c>
@@ -6500,47 +6658,51 @@
       <c r="P16" s="57" t="s">
         <v>469</v>
       </c>
-      <c r="Q16" s="51" t="str">
-        <f t="shared" ref="Q16:Q23" si="8">_xlfn.TRANSLATE(P16,"pt","es")</f>
-        <v>Diseñadores</v>
-      </c>
-      <c r="R16" s="38" t="s">
-        <v>181</v>
-      </c>
-      <c r="S16" s="52" t="str">
+      <c r="Q16" s="51" t="s">
+        <v>578</v>
+      </c>
+      <c r="R16" s="53" t="s">
+        <v>569</v>
+      </c>
+      <c r="S16" s="38" t="s">
+        <v>181</v>
+      </c>
+      <c r="T16" s="52" t="str">
         <f t="shared" si="6"/>
         <v>Normativos</v>
       </c>
-      <c r="T16" s="52" t="str">
+      <c r="U16" s="52" t="str">
         <f t="shared" si="6"/>
         <v>NBR.Temáticas</v>
       </c>
-      <c r="U16" s="51" t="str">
+      <c r="V16" s="51" t="str">
         <f t="shared" si="6"/>
         <v>NBR.N.RH</v>
       </c>
-      <c r="V16" s="38" t="s">
+      <c r="W16" s="38" t="s">
         <v>419</v>
       </c>
-      <c r="W16" s="58" t="str">
+      <c r="X16" s="58" t="str">
         <f t="shared" si="7"/>
         <v>Key-ABNT-16</v>
       </c>
-      <c r="X16" s="38" t="s">
-        <v>556</v>
-      </c>
       <c r="Y16" s="38" t="s">
         <v>556</v>
       </c>
-      <c r="Z16" s="53" t="s">
+      <c r="Z16" s="38" t="s">
+        <v>556</v>
+      </c>
+      <c r="AA16" s="38" t="s">
+        <v>556</v>
+      </c>
+      <c r="AB16" s="38" t="s">
+        <v>556</v>
+      </c>
+      <c r="AC16" s="53" t="s">
         <v>478</v>
       </c>
-      <c r="AA16" s="53" t="str">
-        <f t="shared" ref="AA16:AA23" si="9">_xlfn.TRANSLATE(P16,"pt","en")</f>
-        <v>Designers</v>
-      </c>
-    </row>
-    <row r="17" spans="1:27" ht="6.9" customHeight="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="17" spans="1:29" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A17" s="49">
         <v>17</v>
       </c>
@@ -6593,47 +6755,51 @@
       <c r="P17" s="57" t="s">
         <v>470</v>
       </c>
-      <c r="Q17" s="51" t="str">
-        <f t="shared" si="8"/>
-        <v>Entrenadores</v>
-      </c>
-      <c r="R17" s="38" t="s">
-        <v>181</v>
-      </c>
-      <c r="S17" s="52" t="str">
+      <c r="Q17" s="51" t="s">
+        <v>579</v>
+      </c>
+      <c r="R17" s="53" t="s">
+        <v>570</v>
+      </c>
+      <c r="S17" s="38" t="s">
+        <v>181</v>
+      </c>
+      <c r="T17" s="52" t="str">
         <f t="shared" si="6"/>
         <v>Normativos</v>
       </c>
-      <c r="T17" s="52" t="str">
+      <c r="U17" s="52" t="str">
         <f t="shared" si="6"/>
         <v>NBR.Temáticas</v>
       </c>
-      <c r="U17" s="51" t="str">
+      <c r="V17" s="51" t="str">
         <f t="shared" si="6"/>
         <v>NBR.N.RH</v>
       </c>
-      <c r="V17" s="38" t="s">
+      <c r="W17" s="38" t="s">
         <v>419</v>
       </c>
-      <c r="W17" s="58" t="str">
+      <c r="X17" s="58" t="str">
         <f t="shared" si="7"/>
         <v>Key-ABNT-17</v>
       </c>
-      <c r="X17" s="38" t="s">
-        <v>556</v>
-      </c>
       <c r="Y17" s="38" t="s">
         <v>556</v>
       </c>
-      <c r="Z17" s="53" t="s">
+      <c r="Z17" s="38" t="s">
+        <v>556</v>
+      </c>
+      <c r="AA17" s="38" t="s">
+        <v>556</v>
+      </c>
+      <c r="AB17" s="38" t="s">
+        <v>556</v>
+      </c>
+      <c r="AC17" s="53" t="s">
         <v>479</v>
       </c>
-      <c r="AA17" s="53" t="str">
-        <f t="shared" si="9"/>
-        <v>Managers</v>
-      </c>
-    </row>
-    <row r="18" spans="1:27" ht="6.9" customHeight="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="18" spans="1:29" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A18" s="49">
         <v>18</v>
       </c>
@@ -6686,47 +6852,51 @@
       <c r="P18" s="57" t="s">
         <v>471</v>
       </c>
-      <c r="Q18" s="51" t="str">
+      <c r="Q18" s="51" t="s">
+        <v>580</v>
+      </c>
+      <c r="R18" s="53" t="s">
+        <v>571</v>
+      </c>
+      <c r="S18" s="38" t="s">
+        <v>181</v>
+      </c>
+      <c r="T18" s="52" t="str">
+        <f t="shared" ref="T18:V23" si="8">SUBSTITUTE(C18, "_", " ")</f>
+        <v>Normativos</v>
+      </c>
+      <c r="U18" s="52" t="str">
         <f t="shared" si="8"/>
-        <v>Constructores y contratistas</v>
-      </c>
-      <c r="R18" s="38" t="s">
-        <v>181</v>
-      </c>
-      <c r="S18" s="52" t="str">
-        <f t="shared" ref="S18:U23" si="10">SUBSTITUTE(C18, "_", " ")</f>
-        <v>Normativos</v>
-      </c>
-      <c r="T18" s="52" t="str">
-        <f t="shared" si="10"/>
         <v>NBR.Temáticas</v>
       </c>
-      <c r="U18" s="51" t="str">
-        <f t="shared" si="10"/>
+      <c r="V18" s="51" t="str">
+        <f t="shared" si="8"/>
         <v>NBR.N.RH</v>
       </c>
-      <c r="V18" s="38" t="s">
+      <c r="W18" s="38" t="s">
         <v>419</v>
       </c>
-      <c r="W18" s="58" t="str">
+      <c r="X18" s="58" t="str">
         <f t="shared" si="7"/>
         <v>Key-ABNT-18</v>
       </c>
-      <c r="X18" s="38" t="s">
-        <v>556</v>
-      </c>
       <c r="Y18" s="38" t="s">
         <v>556</v>
       </c>
-      <c r="Z18" s="53" t="s">
+      <c r="Z18" s="38" t="s">
+        <v>556</v>
+      </c>
+      <c r="AA18" s="38" t="s">
+        <v>556</v>
+      </c>
+      <c r="AB18" s="38" t="s">
+        <v>556</v>
+      </c>
+      <c r="AC18" s="53" t="s">
         <v>480</v>
       </c>
-      <c r="AA18" s="53" t="str">
-        <f t="shared" si="9"/>
-        <v>Builders and Contractors</v>
-      </c>
-    </row>
-    <row r="19" spans="1:27" ht="6.9" customHeight="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="19" spans="1:29" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A19" s="49">
         <v>19</v>
       </c>
@@ -6779,47 +6949,51 @@
       <c r="P19" s="57" t="s">
         <v>472</v>
       </c>
-      <c r="Q19" s="51" t="str">
+      <c r="Q19" s="51" t="s">
+        <v>581</v>
+      </c>
+      <c r="R19" s="53" t="s">
+        <v>572</v>
+      </c>
+      <c r="S19" s="38" t="s">
+        <v>181</v>
+      </c>
+      <c r="T19" s="52" t="str">
         <f t="shared" si="8"/>
-        <v>Inspectores de construcción</v>
-      </c>
-      <c r="R19" s="38" t="s">
-        <v>181</v>
-      </c>
-      <c r="S19" s="52" t="str">
-        <f t="shared" si="10"/>
         <v>Normativos</v>
       </c>
-      <c r="T19" s="52" t="str">
-        <f t="shared" si="10"/>
+      <c r="U19" s="52" t="str">
+        <f t="shared" si="8"/>
         <v>NBR.Temáticas</v>
       </c>
-      <c r="U19" s="51" t="str">
-        <f t="shared" si="10"/>
+      <c r="V19" s="51" t="str">
+        <f t="shared" si="8"/>
         <v>NBR.N.RH</v>
       </c>
-      <c r="V19" s="38" t="s">
+      <c r="W19" s="38" t="s">
         <v>419</v>
       </c>
-      <c r="W19" s="58" t="str">
+      <c r="X19" s="58" t="str">
         <f t="shared" si="7"/>
         <v>Key-ABNT-19</v>
       </c>
-      <c r="X19" s="38" t="s">
-        <v>556</v>
-      </c>
       <c r="Y19" s="38" t="s">
         <v>556</v>
       </c>
-      <c r="Z19" s="53" t="s">
+      <c r="Z19" s="38" t="s">
+        <v>556</v>
+      </c>
+      <c r="AA19" s="38" t="s">
+        <v>556</v>
+      </c>
+      <c r="AB19" s="38" t="s">
+        <v>556</v>
+      </c>
+      <c r="AC19" s="53" t="s">
         <v>481</v>
       </c>
-      <c r="AA19" s="53" t="str">
-        <f t="shared" si="9"/>
-        <v>Construction inspectors</v>
-      </c>
-    </row>
-    <row r="20" spans="1:27" ht="6.9" customHeight="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="20" spans="1:29" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A20" s="49">
         <v>20</v>
       </c>
@@ -6872,47 +7046,51 @@
       <c r="P20" s="57" t="s">
         <v>473</v>
       </c>
-      <c r="Q20" s="51" t="str">
+      <c r="Q20" s="51" t="s">
+        <v>582</v>
+      </c>
+      <c r="R20" s="53" t="s">
+        <v>573</v>
+      </c>
+      <c r="S20" s="38" t="s">
+        <v>181</v>
+      </c>
+      <c r="T20" s="52" t="str">
         <f t="shared" si="8"/>
-        <v>Aficionados</v>
-      </c>
-      <c r="R20" s="38" t="s">
-        <v>181</v>
-      </c>
-      <c r="S20" s="52" t="str">
-        <f t="shared" si="10"/>
         <v>Normativos</v>
       </c>
-      <c r="T20" s="52" t="str">
-        <f t="shared" si="10"/>
+      <c r="U20" s="52" t="str">
+        <f t="shared" si="8"/>
         <v>NBR.Temáticas</v>
       </c>
-      <c r="U20" s="51" t="str">
-        <f t="shared" si="10"/>
+      <c r="V20" s="51" t="str">
+        <f t="shared" si="8"/>
         <v>NBR.N.RH</v>
       </c>
-      <c r="V20" s="38" t="s">
+      <c r="W20" s="38" t="s">
         <v>419</v>
       </c>
-      <c r="W20" s="58" t="str">
+      <c r="X20" s="58" t="str">
         <f t="shared" si="7"/>
         <v>Key-ABNT-20</v>
       </c>
-      <c r="X20" s="38" t="s">
-        <v>556</v>
-      </c>
       <c r="Y20" s="38" t="s">
         <v>556</v>
       </c>
-      <c r="Z20" s="53" t="s">
+      <c r="Z20" s="38" t="s">
+        <v>556</v>
+      </c>
+      <c r="AA20" s="38" t="s">
+        <v>556</v>
+      </c>
+      <c r="AB20" s="38" t="s">
+        <v>556</v>
+      </c>
+      <c r="AC20" s="53" t="s">
         <v>482</v>
       </c>
-      <c r="AA20" s="53" t="str">
-        <f t="shared" si="9"/>
-        <v>Supporters</v>
-      </c>
-    </row>
-    <row r="21" spans="1:27" ht="6.9" customHeight="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="21" spans="1:29" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A21" s="49">
         <v>21</v>
       </c>
@@ -6965,47 +7143,51 @@
       <c r="P21" s="57" t="s">
         <v>474</v>
       </c>
-      <c r="Q21" s="51" t="str">
+      <c r="Q21" s="51" t="s">
+        <v>583</v>
+      </c>
+      <c r="R21" s="53" t="s">
+        <v>574</v>
+      </c>
+      <c r="S21" s="38" t="s">
+        <v>181</v>
+      </c>
+      <c r="T21" s="52" t="str">
         <f t="shared" si="8"/>
-        <v>Profesionales del marketing</v>
-      </c>
-      <c r="R21" s="38" t="s">
-        <v>181</v>
-      </c>
-      <c r="S21" s="52" t="str">
-        <f t="shared" si="10"/>
         <v>Normativos</v>
       </c>
-      <c r="T21" s="52" t="str">
-        <f t="shared" si="10"/>
+      <c r="U21" s="52" t="str">
+        <f t="shared" si="8"/>
         <v>NBR.Temáticas</v>
       </c>
-      <c r="U21" s="51" t="str">
-        <f t="shared" si="10"/>
+      <c r="V21" s="51" t="str">
+        <f t="shared" si="8"/>
         <v>NBR.N.RH</v>
       </c>
-      <c r="V21" s="38" t="s">
+      <c r="W21" s="38" t="s">
         <v>419</v>
       </c>
-      <c r="W21" s="58" t="str">
+      <c r="X21" s="58" t="str">
         <f t="shared" si="7"/>
         <v>Key-ABNT-21</v>
       </c>
-      <c r="X21" s="38" t="s">
-        <v>556</v>
-      </c>
       <c r="Y21" s="38" t="s">
         <v>556</v>
       </c>
-      <c r="Z21" s="53" t="s">
+      <c r="Z21" s="38" t="s">
+        <v>556</v>
+      </c>
+      <c r="AA21" s="38" t="s">
+        <v>556</v>
+      </c>
+      <c r="AB21" s="38" t="s">
+        <v>556</v>
+      </c>
+      <c r="AC21" s="53" t="s">
         <v>483</v>
       </c>
-      <c r="AA21" s="53" t="str">
-        <f t="shared" si="9"/>
-        <v>Marketers</v>
-      </c>
-    </row>
-    <row r="22" spans="1:27" ht="6.9" customHeight="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="22" spans="1:29" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A22" s="49">
         <v>22</v>
       </c>
@@ -7058,47 +7240,51 @@
       <c r="P22" s="57" t="s">
         <v>475</v>
       </c>
-      <c r="Q22" s="51" t="str">
+      <c r="Q22" s="51" t="s">
+        <v>584</v>
+      </c>
+      <c r="R22" s="53" t="s">
+        <v>575</v>
+      </c>
+      <c r="S22" s="38" t="s">
+        <v>181</v>
+      </c>
+      <c r="T22" s="52" t="str">
         <f t="shared" si="8"/>
-        <v>Subcontratado</v>
-      </c>
-      <c r="R22" s="38" t="s">
-        <v>181</v>
-      </c>
-      <c r="S22" s="52" t="str">
-        <f t="shared" si="10"/>
         <v>Normativos</v>
       </c>
-      <c r="T22" s="52" t="str">
-        <f t="shared" si="10"/>
+      <c r="U22" s="52" t="str">
+        <f t="shared" si="8"/>
         <v>NBR.Temáticas</v>
       </c>
-      <c r="U22" s="51" t="str">
-        <f t="shared" si="10"/>
+      <c r="V22" s="51" t="str">
+        <f t="shared" si="8"/>
         <v>NBR.N.RH</v>
       </c>
-      <c r="V22" s="38" t="s">
+      <c r="W22" s="38" t="s">
         <v>419</v>
       </c>
-      <c r="W22" s="58" t="str">
+      <c r="X22" s="58" t="str">
         <f t="shared" si="7"/>
         <v>Key-ABNT-22</v>
       </c>
-      <c r="X22" s="38" t="s">
-        <v>556</v>
-      </c>
       <c r="Y22" s="38" t="s">
         <v>556</v>
       </c>
-      <c r="Z22" s="53" t="s">
+      <c r="Z22" s="38" t="s">
+        <v>556</v>
+      </c>
+      <c r="AA22" s="38" t="s">
+        <v>556</v>
+      </c>
+      <c r="AB22" s="38" t="s">
+        <v>556</v>
+      </c>
+      <c r="AC22" s="53" t="s">
         <v>484</v>
       </c>
-      <c r="AA22" s="53" t="str">
-        <f t="shared" si="9"/>
-        <v>Outsourced</v>
-      </c>
-    </row>
-    <row r="23" spans="1:27" ht="6.9" customHeight="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="23" spans="1:29" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A23" s="49">
         <v>23</v>
       </c>
@@ -7151,57 +7337,66 @@
       <c r="P23" s="57" t="s">
         <v>476</v>
       </c>
-      <c r="Q23" s="51" t="str">
+      <c r="Q23" s="51" t="s">
+        <v>585</v>
+      </c>
+      <c r="R23" s="53" t="s">
+        <v>576</v>
+      </c>
+      <c r="S23" s="38" t="s">
+        <v>181</v>
+      </c>
+      <c r="T23" s="52" t="str">
         <f t="shared" si="8"/>
-        <v>Empresas y Grupos Participantes</v>
-      </c>
-      <c r="R23" s="38" t="s">
-        <v>181</v>
-      </c>
-      <c r="S23" s="52" t="str">
-        <f t="shared" si="10"/>
         <v>Normativos</v>
       </c>
-      <c r="T23" s="52" t="str">
-        <f t="shared" si="10"/>
+      <c r="U23" s="52" t="str">
+        <f t="shared" si="8"/>
         <v>NBR.Temáticas</v>
       </c>
-      <c r="U23" s="51" t="str">
-        <f t="shared" si="10"/>
+      <c r="V23" s="51" t="str">
+        <f t="shared" si="8"/>
         <v>NBR.N.RH</v>
       </c>
-      <c r="V23" s="38" t="s">
+      <c r="W23" s="38" t="s">
         <v>419</v>
       </c>
-      <c r="W23" s="58" t="str">
+      <c r="X23" s="58" t="str">
         <f t="shared" si="7"/>
         <v>Key-ABNT-23</v>
       </c>
-      <c r="X23" s="38" t="s">
-        <v>556</v>
-      </c>
       <c r="Y23" s="38" t="s">
         <v>556</v>
       </c>
-      <c r="Z23" s="53" t="s">
+      <c r="Z23" s="38" t="s">
+        <v>556</v>
+      </c>
+      <c r="AA23" s="38" t="s">
+        <v>556</v>
+      </c>
+      <c r="AB23" s="38" t="s">
+        <v>556</v>
+      </c>
+      <c r="AC23" s="53" t="s">
         <v>485</v>
-      </c>
-      <c r="AA23" s="53" t="str">
-        <f t="shared" si="9"/>
-        <v>Participating Companies and Groups</v>
       </c>
     </row>
   </sheetData>
   <conditionalFormatting sqref="F2:F14">
-    <cfRule type="duplicateValues" dxfId="6" priority="4"/>
+    <cfRule type="duplicateValues" dxfId="7" priority="5"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="X2:Y2">
-    <cfRule type="cellIs" dxfId="5" priority="1" operator="equal">
+  <conditionalFormatting sqref="Y2 AA2">
+    <cfRule type="cellIs" dxfId="6" priority="2" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="AA1:AA23 A2:B23">
-    <cfRule type="cellIs" dxfId="4" priority="3" operator="equal">
+  <conditionalFormatting sqref="A2:B23">
+    <cfRule type="cellIs" dxfId="5" priority="4" operator="equal">
+      <formula>"null"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="R1:R23">
+    <cfRule type="cellIs" dxfId="4" priority="1" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -7216,13 +7411,13 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B2B4A051-97A0-4486-9B30-1861C9F77522}">
   <sheetPr codeName="Planilha3"/>
   <dimension ref="A1:U2"/>
-  <sheetFormatPr defaultColWidth="5.296875" defaultRowHeight="10.75" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="5.33203125" defaultRowHeight="11.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="2" customWidth="1"/>
     <col min="2" max="21" width="5" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:21" ht="23.15" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:21" ht="24.75" x14ac:dyDescent="0.2">
       <c r="A1" s="27" t="s">
         <v>350</v>
       </c>
@@ -7287,7 +7482,7 @@
         <v>392</v>
       </c>
     </row>
-    <row r="2" spans="1:21" ht="8.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:21" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="27">
         <v>2</v>
       </c>
@@ -7369,13 +7564,13 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{78CA1C4B-37EB-4980-B878-E43323BA46B5}">
   <sheetPr codeName="Planilha4"/>
   <dimension ref="A1:C2"/>
-  <sheetFormatPr defaultRowHeight="10.75" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="11.25" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="3.296875" bestFit="1" customWidth="1"/>
-    <col min="2" max="3" width="16.69921875" customWidth="1"/>
+    <col min="1" max="1" width="3.33203125" bestFit="1" customWidth="1"/>
+    <col min="2" max="3" width="16.6640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1" s="30">
         <v>1</v>
       </c>
@@ -7386,7 +7581,7 @@
         <v>395</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A2" s="21">
         <v>2</v>
       </c>
@@ -7411,30 +7606,30 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B79BA5E7-BFBD-4AC9-B36C-B9776AA17B75}">
   <sheetPr codeName="Planilha5"/>
   <dimension ref="A1:Y157"/>
-  <sheetFormatPr defaultColWidth="11.296875" defaultRowHeight="6" customHeight="1" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="11.33203125" defaultRowHeight="6" customHeight="1" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="3.69921875" style="2" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="11.296875" style="2" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="14.796875" style="2" customWidth="1"/>
-    <col min="4" max="4" width="10.19921875" style="2" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="7.69921875" style="2" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="7.296875" style="48" customWidth="1"/>
+    <col min="1" max="1" width="3.6640625" style="2" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="11.33203125" style="2" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="14.83203125" style="2" customWidth="1"/>
+    <col min="4" max="4" width="10.1640625" style="2" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="7.6640625" style="2" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="7.33203125" style="48" customWidth="1"/>
     <col min="7" max="7" width="10" style="48" customWidth="1"/>
-    <col min="8" max="9" width="7.296875" style="48" customWidth="1"/>
-    <col min="10" max="10" width="4.296875" style="48" customWidth="1"/>
+    <col min="8" max="9" width="7.33203125" style="48" customWidth="1"/>
+    <col min="10" max="10" width="4.33203125" style="48" customWidth="1"/>
     <col min="11" max="11" width="14" style="48" bestFit="1" customWidth="1"/>
     <col min="12" max="12" width="7.5" style="48" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="29.19921875" style="48" customWidth="1"/>
+    <col min="13" max="13" width="29.1640625" style="48" customWidth="1"/>
     <col min="14" max="14" width="7" style="48" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="43.796875" style="2" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="8.69921875" style="48" customWidth="1"/>
+    <col min="15" max="15" width="43.83203125" style="2" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="8.6640625" style="48" customWidth="1"/>
     <col min="17" max="17" width="5" style="48" customWidth="1"/>
     <col min="18" max="18" width="5.5" style="48" customWidth="1"/>
     <col min="19" max="25" width="5" style="48" customWidth="1"/>
-    <col min="26" max="16384" width="11.296875" style="2"/>
+    <col min="26" max="16384" width="11.33203125" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:25" ht="18.649999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:25" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="7" t="s">
         <v>180</v>
       </c>
@@ -7507,7 +7702,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="9">
         <v>2</v>
       </c>
@@ -7584,7 +7779,7 @@
         <v>181</v>
       </c>
     </row>
-    <row r="3" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="9">
         <v>3</v>
       </c>
@@ -7661,7 +7856,7 @@
         <v>181</v>
       </c>
     </row>
-    <row r="4" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="9">
         <v>4</v>
       </c>
@@ -7738,7 +7933,7 @@
         <v>181</v>
       </c>
     </row>
-    <row r="5" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="9">
         <v>5</v>
       </c>
@@ -7815,7 +8010,7 @@
         <v>181</v>
       </c>
     </row>
-    <row r="6" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A6" s="9">
         <v>6</v>
       </c>
@@ -7892,7 +8087,7 @@
         <v>181</v>
       </c>
     </row>
-    <row r="7" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A7" s="9">
         <v>7</v>
       </c>
@@ -7969,7 +8164,7 @@
         <v>181</v>
       </c>
     </row>
-    <row r="8" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" s="9">
         <v>8</v>
       </c>
@@ -8046,7 +8241,7 @@
         <v>181</v>
       </c>
     </row>
-    <row r="9" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A9" s="9">
         <v>9</v>
       </c>
@@ -8123,7 +8318,7 @@
         <v>181</v>
       </c>
     </row>
-    <row r="10" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A10" s="9">
         <v>10</v>
       </c>
@@ -8200,7 +8395,7 @@
         <v>181</v>
       </c>
     </row>
-    <row r="11" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A11" s="9">
         <v>11</v>
       </c>
@@ -8277,7 +8472,7 @@
         <v>181</v>
       </c>
     </row>
-    <row r="12" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A12" s="9">
         <v>12</v>
       </c>
@@ -8354,7 +8549,7 @@
         <v>181</v>
       </c>
     </row>
-    <row r="13" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A13" s="9">
         <v>13</v>
       </c>
@@ -8431,7 +8626,7 @@
         <v>181</v>
       </c>
     </row>
-    <row r="14" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A14" s="9">
         <v>14</v>
       </c>
@@ -8508,7 +8703,7 @@
         <v>181</v>
       </c>
     </row>
-    <row r="15" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A15" s="9">
         <v>15</v>
       </c>
@@ -8585,7 +8780,7 @@
         <v>181</v>
       </c>
     </row>
-    <row r="16" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A16" s="9">
         <v>16</v>
       </c>
@@ -8662,7 +8857,7 @@
         <v>181</v>
       </c>
     </row>
-    <row r="17" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A17" s="9">
         <v>17</v>
       </c>
@@ -8739,7 +8934,7 @@
         <v>181</v>
       </c>
     </row>
-    <row r="18" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A18" s="9">
         <v>18</v>
       </c>
@@ -8816,7 +9011,7 @@
         <v>181</v>
       </c>
     </row>
-    <row r="19" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A19" s="9">
         <v>19</v>
       </c>
@@ -8893,7 +9088,7 @@
         <v>181</v>
       </c>
     </row>
-    <row r="20" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A20" s="9">
         <v>20</v>
       </c>
@@ -8970,7 +9165,7 @@
         <v>181</v>
       </c>
     </row>
-    <row r="21" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A21" s="9">
         <v>21</v>
       </c>
@@ -9047,7 +9242,7 @@
         <v>181</v>
       </c>
     </row>
-    <row r="22" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A22" s="9">
         <v>22</v>
       </c>
@@ -9124,7 +9319,7 @@
         <v>181</v>
       </c>
     </row>
-    <row r="23" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A23" s="9">
         <v>23</v>
       </c>
@@ -9201,7 +9396,7 @@
         <v>181</v>
       </c>
     </row>
-    <row r="24" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A24" s="9">
         <v>24</v>
       </c>
@@ -9278,7 +9473,7 @@
         <v>181</v>
       </c>
     </row>
-    <row r="25" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A25" s="9">
         <v>25</v>
       </c>
@@ -9355,7 +9550,7 @@
         <v>181</v>
       </c>
     </row>
-    <row r="26" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A26" s="9">
         <v>26</v>
       </c>
@@ -9432,7 +9627,7 @@
         <v>181</v>
       </c>
     </row>
-    <row r="27" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A27" s="9">
         <v>27</v>
       </c>
@@ -9509,7 +9704,7 @@
         <v>181</v>
       </c>
     </row>
-    <row r="28" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A28" s="9">
         <v>28</v>
       </c>
@@ -9586,7 +9781,7 @@
         <v>181</v>
       </c>
     </row>
-    <row r="29" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A29" s="9">
         <v>29</v>
       </c>
@@ -9663,7 +9858,7 @@
         <v>181</v>
       </c>
     </row>
-    <row r="30" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A30" s="9">
         <v>30</v>
       </c>
@@ -9740,7 +9935,7 @@
         <v>181</v>
       </c>
     </row>
-    <row r="31" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A31" s="9">
         <v>31</v>
       </c>
@@ -9817,7 +10012,7 @@
         <v>181</v>
       </c>
     </row>
-    <row r="32" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A32" s="9">
         <v>32</v>
       </c>
@@ -9894,7 +10089,7 @@
         <v>181</v>
       </c>
     </row>
-    <row r="33" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A33" s="9">
         <v>33</v>
       </c>
@@ -9971,7 +10166,7 @@
         <v>181</v>
       </c>
     </row>
-    <row r="34" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A34" s="9">
         <v>34</v>
       </c>
@@ -10048,7 +10243,7 @@
         <v>181</v>
       </c>
     </row>
-    <row r="35" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A35" s="9">
         <v>35</v>
       </c>
@@ -10125,7 +10320,7 @@
         <v>181</v>
       </c>
     </row>
-    <row r="36" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A36" s="9">
         <v>36</v>
       </c>
@@ -10202,7 +10397,7 @@
         <v>181</v>
       </c>
     </row>
-    <row r="37" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A37" s="9">
         <v>37</v>
       </c>
@@ -10279,7 +10474,7 @@
         <v>181</v>
       </c>
     </row>
-    <row r="38" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A38" s="9">
         <v>38</v>
       </c>
@@ -10356,7 +10551,7 @@
         <v>181</v>
       </c>
     </row>
-    <row r="39" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A39" s="9">
         <v>39</v>
       </c>
@@ -10433,7 +10628,7 @@
         <v>181</v>
       </c>
     </row>
-    <row r="40" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A40" s="9">
         <v>40</v>
       </c>
@@ -10510,7 +10705,7 @@
         <v>181</v>
       </c>
     </row>
-    <row r="41" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A41" s="9">
         <v>41</v>
       </c>
@@ -10587,7 +10782,7 @@
         <v>181</v>
       </c>
     </row>
-    <row r="42" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A42" s="9">
         <v>42</v>
       </c>
@@ -10664,7 +10859,7 @@
         <v>181</v>
       </c>
     </row>
-    <row r="43" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A43" s="9">
         <v>43</v>
       </c>
@@ -10741,7 +10936,7 @@
         <v>181</v>
       </c>
     </row>
-    <row r="44" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A44" s="9">
         <v>44</v>
       </c>
@@ -10818,7 +11013,7 @@
         <v>181</v>
       </c>
     </row>
-    <row r="45" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A45" s="9">
         <v>45</v>
       </c>
@@ -10895,7 +11090,7 @@
         <v>181</v>
       </c>
     </row>
-    <row r="46" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A46" s="9">
         <v>46</v>
       </c>
@@ -10972,7 +11167,7 @@
         <v>181</v>
       </c>
     </row>
-    <row r="47" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A47" s="9">
         <v>47</v>
       </c>
@@ -11049,7 +11244,7 @@
         <v>181</v>
       </c>
     </row>
-    <row r="48" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A48" s="9">
         <v>48</v>
       </c>
@@ -11126,7 +11321,7 @@
         <v>181</v>
       </c>
     </row>
-    <row r="49" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A49" s="9">
         <v>49</v>
       </c>
@@ -11203,7 +11398,7 @@
         <v>181</v>
       </c>
     </row>
-    <row r="50" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A50" s="9">
         <v>50</v>
       </c>
@@ -11280,7 +11475,7 @@
         <v>181</v>
       </c>
     </row>
-    <row r="51" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A51" s="9">
         <v>51</v>
       </c>
@@ -11357,7 +11552,7 @@
         <v>181</v>
       </c>
     </row>
-    <row r="52" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A52" s="9">
         <v>52</v>
       </c>
@@ -11434,7 +11629,7 @@
         <v>181</v>
       </c>
     </row>
-    <row r="53" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A53" s="9">
         <v>53</v>
       </c>
@@ -11511,7 +11706,7 @@
         <v>181</v>
       </c>
     </row>
-    <row r="54" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A54" s="9">
         <v>54</v>
       </c>
@@ -11588,7 +11783,7 @@
         <v>181</v>
       </c>
     </row>
-    <row r="55" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A55" s="9">
         <v>55</v>
       </c>
@@ -11665,7 +11860,7 @@
         <v>181</v>
       </c>
     </row>
-    <row r="56" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A56" s="9">
         <v>56</v>
       </c>
@@ -11742,7 +11937,7 @@
         <v>181</v>
       </c>
     </row>
-    <row r="57" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A57" s="9">
         <v>57</v>
       </c>
@@ -11819,7 +12014,7 @@
         <v>181</v>
       </c>
     </row>
-    <row r="58" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A58" s="9">
         <v>58</v>
       </c>
@@ -11896,7 +12091,7 @@
         <v>181</v>
       </c>
     </row>
-    <row r="59" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A59" s="9">
         <v>59</v>
       </c>
@@ -11973,7 +12168,7 @@
         <v>181</v>
       </c>
     </row>
-    <row r="60" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A60" s="9">
         <v>60</v>
       </c>
@@ -12050,7 +12245,7 @@
         <v>181</v>
       </c>
     </row>
-    <row r="61" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A61" s="9">
         <v>61</v>
       </c>
@@ -12127,7 +12322,7 @@
         <v>181</v>
       </c>
     </row>
-    <row r="62" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A62" s="9">
         <v>62</v>
       </c>
@@ -12204,7 +12399,7 @@
         <v>181</v>
       </c>
     </row>
-    <row r="63" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A63" s="9">
         <v>63</v>
       </c>
@@ -12281,7 +12476,7 @@
         <v>181</v>
       </c>
     </row>
-    <row r="64" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A64" s="9">
         <v>64</v>
       </c>
@@ -12358,7 +12553,7 @@
         <v>181</v>
       </c>
     </row>
-    <row r="65" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A65" s="9">
         <v>65</v>
       </c>
@@ -12435,7 +12630,7 @@
         <v>181</v>
       </c>
     </row>
-    <row r="66" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A66" s="9">
         <v>66</v>
       </c>
@@ -12512,7 +12707,7 @@
         <v>181</v>
       </c>
     </row>
-    <row r="67" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A67" s="9">
         <v>67</v>
       </c>
@@ -12589,7 +12784,7 @@
         <v>181</v>
       </c>
     </row>
-    <row r="68" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A68" s="9">
         <v>68</v>
       </c>
@@ -12666,7 +12861,7 @@
         <v>181</v>
       </c>
     </row>
-    <row r="69" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A69" s="9">
         <v>69</v>
       </c>
@@ -12743,7 +12938,7 @@
         <v>181</v>
       </c>
     </row>
-    <row r="70" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A70" s="9">
         <v>70</v>
       </c>
@@ -12820,7 +13015,7 @@
         <v>181</v>
       </c>
     </row>
-    <row r="71" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A71" s="9">
         <v>71</v>
       </c>
@@ -12897,7 +13092,7 @@
         <v>181</v>
       </c>
     </row>
-    <row r="72" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A72" s="9">
         <v>72</v>
       </c>
@@ -12974,7 +13169,7 @@
         <v>181</v>
       </c>
     </row>
-    <row r="73" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A73" s="9">
         <v>73</v>
       </c>
@@ -13051,7 +13246,7 @@
         <v>181</v>
       </c>
     </row>
-    <row r="74" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A74" s="9">
         <v>74</v>
       </c>
@@ -13128,7 +13323,7 @@
         <v>181</v>
       </c>
     </row>
-    <row r="75" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A75" s="9">
         <v>75</v>
       </c>
@@ -13205,7 +13400,7 @@
         <v>181</v>
       </c>
     </row>
-    <row r="76" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A76" s="9">
         <v>76</v>
       </c>
@@ -13282,7 +13477,7 @@
         <v>181</v>
       </c>
     </row>
-    <row r="77" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A77" s="9">
         <v>77</v>
       </c>
@@ -13359,7 +13554,7 @@
         <v>181</v>
       </c>
     </row>
-    <row r="78" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A78" s="9">
         <v>78</v>
       </c>
@@ -13436,7 +13631,7 @@
         <v>181</v>
       </c>
     </row>
-    <row r="79" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A79" s="9">
         <v>79</v>
       </c>
@@ -13513,7 +13708,7 @@
         <v>181</v>
       </c>
     </row>
-    <row r="80" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A80" s="9">
         <v>80</v>
       </c>
@@ -13590,7 +13785,7 @@
         <v>181</v>
       </c>
     </row>
-    <row r="81" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A81" s="9">
         <v>81</v>
       </c>
@@ -13667,7 +13862,7 @@
         <v>181</v>
       </c>
     </row>
-    <row r="82" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A82" s="9">
         <v>82</v>
       </c>
@@ -13744,7 +13939,7 @@
         <v>181</v>
       </c>
     </row>
-    <row r="83" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A83" s="9">
         <v>83</v>
       </c>
@@ -13821,7 +14016,7 @@
         <v>181</v>
       </c>
     </row>
-    <row r="84" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A84" s="9">
         <v>84</v>
       </c>
@@ -13898,7 +14093,7 @@
         <v>181</v>
       </c>
     </row>
-    <row r="85" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A85" s="9">
         <v>85</v>
       </c>
@@ -13975,7 +14170,7 @@
         <v>181</v>
       </c>
     </row>
-    <row r="86" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A86" s="9">
         <v>86</v>
       </c>
@@ -14052,7 +14247,7 @@
         <v>181</v>
       </c>
     </row>
-    <row r="87" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A87" s="9">
         <v>87</v>
       </c>
@@ -14129,7 +14324,7 @@
         <v>181</v>
       </c>
     </row>
-    <row r="88" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A88" s="9">
         <v>88</v>
       </c>
@@ -14206,7 +14401,7 @@
         <v>181</v>
       </c>
     </row>
-    <row r="89" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A89" s="9">
         <v>89</v>
       </c>
@@ -14283,7 +14478,7 @@
         <v>181</v>
       </c>
     </row>
-    <row r="90" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A90" s="9">
         <v>90</v>
       </c>
@@ -14360,7 +14555,7 @@
         <v>181</v>
       </c>
     </row>
-    <row r="91" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A91" s="9">
         <v>91</v>
       </c>
@@ -14437,7 +14632,7 @@
         <v>181</v>
       </c>
     </row>
-    <row r="92" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A92" s="9">
         <v>92</v>
       </c>
@@ -14514,7 +14709,7 @@
         <v>181</v>
       </c>
     </row>
-    <row r="93" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A93" s="9">
         <v>93</v>
       </c>
@@ -14591,7 +14786,7 @@
         <v>181</v>
       </c>
     </row>
-    <row r="94" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A94" s="9">
         <v>94</v>
       </c>
@@ -14668,7 +14863,7 @@
         <v>181</v>
       </c>
     </row>
-    <row r="95" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A95" s="9">
         <v>95</v>
       </c>
@@ -14745,7 +14940,7 @@
         <v>181</v>
       </c>
     </row>
-    <row r="96" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A96" s="9">
         <v>96</v>
       </c>
@@ -14822,7 +15017,7 @@
         <v>181</v>
       </c>
     </row>
-    <row r="97" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A97" s="9">
         <v>97</v>
       </c>
@@ -14899,7 +15094,7 @@
         <v>181</v>
       </c>
     </row>
-    <row r="98" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A98" s="9">
         <v>98</v>
       </c>
@@ -14976,7 +15171,7 @@
         <v>181</v>
       </c>
     </row>
-    <row r="99" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A99" s="9">
         <v>99</v>
       </c>
@@ -15053,7 +15248,7 @@
         <v>181</v>
       </c>
     </row>
-    <row r="100" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A100" s="9">
         <v>100</v>
       </c>
@@ -15130,7 +15325,7 @@
         <v>181</v>
       </c>
     </row>
-    <row r="101" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A101" s="9">
         <v>101</v>
       </c>
@@ -15207,7 +15402,7 @@
         <v>181</v>
       </c>
     </row>
-    <row r="102" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A102" s="9">
         <v>102</v>
       </c>
@@ -15284,7 +15479,7 @@
         <v>181</v>
       </c>
     </row>
-    <row r="103" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A103" s="9">
         <v>103</v>
       </c>
@@ -15361,7 +15556,7 @@
         <v>181</v>
       </c>
     </row>
-    <row r="104" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A104" s="9">
         <v>104</v>
       </c>
@@ -15438,7 +15633,7 @@
         <v>181</v>
       </c>
     </row>
-    <row r="105" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="105" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A105" s="9">
         <v>105</v>
       </c>
@@ -15515,7 +15710,7 @@
         <v>181</v>
       </c>
     </row>
-    <row r="106" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="106" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A106" s="9">
         <v>106</v>
       </c>
@@ -15592,7 +15787,7 @@
         <v>181</v>
       </c>
     </row>
-    <row r="107" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="107" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A107" s="9">
         <v>107</v>
       </c>
@@ -15669,7 +15864,7 @@
         <v>181</v>
       </c>
     </row>
-    <row r="108" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="108" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A108" s="9">
         <v>108</v>
       </c>
@@ -15746,7 +15941,7 @@
         <v>181</v>
       </c>
     </row>
-    <row r="109" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="109" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A109" s="9">
         <v>109</v>
       </c>
@@ -15823,7 +16018,7 @@
         <v>181</v>
       </c>
     </row>
-    <row r="110" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="110" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A110" s="9">
         <v>110</v>
       </c>
@@ -15900,7 +16095,7 @@
         <v>181</v>
       </c>
     </row>
-    <row r="111" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="111" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A111" s="9">
         <v>111</v>
       </c>
@@ -15977,7 +16172,7 @@
         <v>181</v>
       </c>
     </row>
-    <row r="112" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="112" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A112" s="9">
         <v>112</v>
       </c>
@@ -16054,7 +16249,7 @@
         <v>181</v>
       </c>
     </row>
-    <row r="113" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="113" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A113" s="9">
         <v>113</v>
       </c>
@@ -16131,7 +16326,7 @@
         <v>181</v>
       </c>
     </row>
-    <row r="114" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="114" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A114" s="9">
         <v>114</v>
       </c>
@@ -16208,7 +16403,7 @@
         <v>181</v>
       </c>
     </row>
-    <row r="115" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="115" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A115" s="9">
         <v>115</v>
       </c>
@@ -16285,7 +16480,7 @@
         <v>181</v>
       </c>
     </row>
-    <row r="116" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="116" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A116" s="9">
         <v>116</v>
       </c>
@@ -16362,7 +16557,7 @@
         <v>181</v>
       </c>
     </row>
-    <row r="117" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="117" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A117" s="9">
         <v>117</v>
       </c>
@@ -16439,7 +16634,7 @@
         <v>181</v>
       </c>
     </row>
-    <row r="118" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="118" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A118" s="9">
         <v>118</v>
       </c>
@@ -16516,7 +16711,7 @@
         <v>181</v>
       </c>
     </row>
-    <row r="119" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="119" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A119" s="9">
         <v>119</v>
       </c>
@@ -16593,7 +16788,7 @@
         <v>181</v>
       </c>
     </row>
-    <row r="120" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="120" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A120" s="9">
         <v>120</v>
       </c>
@@ -16670,7 +16865,7 @@
         <v>181</v>
       </c>
     </row>
-    <row r="121" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="121" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A121" s="9">
         <v>121</v>
       </c>
@@ -16747,7 +16942,7 @@
         <v>181</v>
       </c>
     </row>
-    <row r="122" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="122" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A122" s="9">
         <v>122</v>
       </c>
@@ -16824,7 +17019,7 @@
         <v>181</v>
       </c>
     </row>
-    <row r="123" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="123" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A123" s="9">
         <v>123</v>
       </c>
@@ -16901,7 +17096,7 @@
         <v>181</v>
       </c>
     </row>
-    <row r="124" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="124" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A124" s="9">
         <v>124</v>
       </c>
@@ -16978,7 +17173,7 @@
         <v>181</v>
       </c>
     </row>
-    <row r="125" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="125" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A125" s="9">
         <v>125</v>
       </c>
@@ -17055,7 +17250,7 @@
         <v>181</v>
       </c>
     </row>
-    <row r="126" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="126" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A126" s="9">
         <v>126</v>
       </c>
@@ -17132,7 +17327,7 @@
         <v>181</v>
       </c>
     </row>
-    <row r="127" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="127" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A127" s="9">
         <v>127</v>
       </c>
@@ -17209,7 +17404,7 @@
         <v>181</v>
       </c>
     </row>
-    <row r="128" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="128" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A128" s="9">
         <v>128</v>
       </c>
@@ -17286,7 +17481,7 @@
         <v>181</v>
       </c>
     </row>
-    <row r="129" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="129" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A129" s="9">
         <v>129</v>
       </c>
@@ -17363,7 +17558,7 @@
         <v>181</v>
       </c>
     </row>
-    <row r="130" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="130" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A130" s="9">
         <v>130</v>
       </c>
@@ -17440,7 +17635,7 @@
         <v>181</v>
       </c>
     </row>
-    <row r="131" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="131" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A131" s="9">
         <v>131</v>
       </c>
@@ -17517,7 +17712,7 @@
         <v>181</v>
       </c>
     </row>
-    <row r="132" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="132" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A132" s="9">
         <v>132</v>
       </c>
@@ -17594,7 +17789,7 @@
         <v>181</v>
       </c>
     </row>
-    <row r="133" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="133" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A133" s="9">
         <v>133</v>
       </c>
@@ -17671,7 +17866,7 @@
         <v>181</v>
       </c>
     </row>
-    <row r="134" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="134" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A134" s="9">
         <v>134</v>
       </c>
@@ -17748,7 +17943,7 @@
         <v>181</v>
       </c>
     </row>
-    <row r="135" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="135" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A135" s="9">
         <v>135</v>
       </c>
@@ -17825,7 +18020,7 @@
         <v>181</v>
       </c>
     </row>
-    <row r="136" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="136" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A136" s="9">
         <v>136</v>
       </c>
@@ -17902,7 +18097,7 @@
         <v>181</v>
       </c>
     </row>
-    <row r="137" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="137" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A137" s="9">
         <v>137</v>
       </c>
@@ -17979,7 +18174,7 @@
         <v>181</v>
       </c>
     </row>
-    <row r="138" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="138" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A138" s="9">
         <v>138</v>
       </c>
@@ -18056,7 +18251,7 @@
         <v>181</v>
       </c>
     </row>
-    <row r="139" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="139" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A139" s="9">
         <v>139</v>
       </c>
@@ -18133,7 +18328,7 @@
         <v>181</v>
       </c>
     </row>
-    <row r="140" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="140" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A140" s="9">
         <v>140</v>
       </c>
@@ -18210,7 +18405,7 @@
         <v>181</v>
       </c>
     </row>
-    <row r="141" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="141" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A141" s="9">
         <v>141</v>
       </c>
@@ -18287,7 +18482,7 @@
         <v>181</v>
       </c>
     </row>
-    <row r="142" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="142" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A142" s="9">
         <v>142</v>
       </c>
@@ -18364,7 +18559,7 @@
         <v>181</v>
       </c>
     </row>
-    <row r="143" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="143" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A143" s="9">
         <v>143</v>
       </c>
@@ -18441,7 +18636,7 @@
         <v>181</v>
       </c>
     </row>
-    <row r="144" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="144" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A144" s="9">
         <v>144</v>
       </c>
@@ -18518,7 +18713,7 @@
         <v>181</v>
       </c>
     </row>
-    <row r="145" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="145" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A145" s="9">
         <v>145</v>
       </c>
@@ -18595,7 +18790,7 @@
         <v>181</v>
       </c>
     </row>
-    <row r="146" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="146" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A146" s="9">
         <v>146</v>
       </c>
@@ -18672,7 +18867,7 @@
         <v>181</v>
       </c>
     </row>
-    <row r="147" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="147" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A147" s="9">
         <v>147</v>
       </c>
@@ -18749,7 +18944,7 @@
         <v>181</v>
       </c>
     </row>
-    <row r="148" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="148" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A148" s="9">
         <v>148</v>
       </c>
@@ -18826,7 +19021,7 @@
         <v>181</v>
       </c>
     </row>
-    <row r="149" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="149" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A149" s="9">
         <v>149</v>
       </c>
@@ -18903,7 +19098,7 @@
         <v>181</v>
       </c>
     </row>
-    <row r="150" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="150" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A150" s="9">
         <v>150</v>
       </c>
@@ -18980,7 +19175,7 @@
         <v>181</v>
       </c>
     </row>
-    <row r="151" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="151" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A151" s="9">
         <v>151</v>
       </c>
@@ -19057,7 +19252,7 @@
         <v>181</v>
       </c>
     </row>
-    <row r="152" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="152" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A152" s="9">
         <v>152</v>
       </c>
@@ -19134,7 +19329,7 @@
         <v>181</v>
       </c>
     </row>
-    <row r="153" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="153" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A153" s="9">
         <v>153</v>
       </c>
@@ -19211,7 +19406,7 @@
         <v>181</v>
       </c>
     </row>
-    <row r="154" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="154" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A154" s="9">
         <v>154</v>
       </c>
@@ -19288,7 +19483,7 @@
         <v>181</v>
       </c>
     </row>
-    <row r="155" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="155" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A155" s="9">
         <v>155</v>
       </c>
@@ -19365,7 +19560,7 @@
         <v>181</v>
       </c>
     </row>
-    <row r="156" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="156" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A156" s="9">
         <v>156</v>
       </c>
@@ -19442,7 +19637,7 @@
         <v>181</v>
       </c>
     </row>
-    <row r="157" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="157" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A157" s="9">
         <v>157</v>
       </c>

--- a/Versão5/ABNT/Ontologia_NBR15965_2N.xlsx
+++ b/Versão5/ABNT/Ontologia_NBR15965_2N.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr codeName="EstaPastaDeTrabalho" defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Construtor_Onto\ABNT\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BF3BA571-3EC8-4A11-A37E-EC5DE9BDAEAE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9B0304A0-C0C4-4EF9-B14A-3E53F6EE9B65}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="24240" windowHeight="13290" activeTab="1" xr2:uid="{82C81399-C775-48F3-A336-58DE5F35A6D9}"/>
+    <workbookView xWindow="-103" yWindow="-103" windowWidth="22149" windowHeight="13200" activeTab="4" xr2:uid="{82C81399-C775-48F3-A336-58DE5F35A6D9}"/>
   </bookViews>
   <sheets>
     <sheet name="Projeto" sheetId="8" r:id="rId1"/>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4393" uniqueCount="588">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5829" uniqueCount="617">
   <si>
     <t>Indivíduo</t>
   </si>
@@ -1855,6 +1855,93 @@
   </si>
   <si>
     <t>Atributos Ifc</t>
+  </si>
+  <si>
+    <t>Projeto</t>
+  </si>
+  <si>
+    <t>De.API</t>
+  </si>
+  <si>
+    <t>Métodos</t>
+  </si>
+  <si>
+    <t>Macros</t>
+  </si>
+  <si>
+    <t>API.Revit</t>
+  </si>
+  <si>
+    <t>Aplicação Revit</t>
+  </si>
+  <si>
+    <t>Aplicativo Revit</t>
+  </si>
+  <si>
+    <t>Revit Aplication</t>
+  </si>
+  <si>
+    <t>API_Ambiente</t>
+  </si>
+  <si>
+    <t>"API"</t>
+  </si>
+  <si>
+    <t>"Elementos Ambientes"</t>
+  </si>
+  <si>
+    <t>"Individuo indicador de método API para selecionar ambientes do projeto"</t>
+  </si>
+  <si>
+    <t>API_Andar</t>
+  </si>
+  <si>
+    <t>"Elementos Andares"</t>
+  </si>
+  <si>
+    <t>"Individuo indicador de método API para selecionar andares do projeto"</t>
+  </si>
+  <si>
+    <t>API_Instância</t>
+  </si>
+  <si>
+    <t>"Elementos Instanciados"</t>
+  </si>
+  <si>
+    <t>"Individuo indicador de método API para selecionar instâncias do projeto"</t>
+  </si>
+  <si>
+    <t>API_Simbolo</t>
+  </si>
+  <si>
+    <t>"Elementos Tipificados"</t>
+  </si>
+  <si>
+    <t>"Individuo indicador de método API para selecionar elementos tipificados do projeto"</t>
+  </si>
+  <si>
+    <t>API_Material</t>
+  </si>
+  <si>
+    <t>"Elementos Materiais"</t>
+  </si>
+  <si>
+    <t>"Individuo indicador de método API para selecionar materiais do projeto"</t>
+  </si>
+  <si>
+    <t>é.rvt.ambiente</t>
+  </si>
+  <si>
+    <t>é.rvt.andar</t>
+  </si>
+  <si>
+    <t>é.rvt.elemento</t>
+  </si>
+  <si>
+    <t>é.rvt.tipo</t>
+  </si>
+  <si>
+    <t>é.rvt.material</t>
   </si>
 </sst>
 </file>
@@ -1970,7 +2057,7 @@
       <family val="2"/>
     </font>
   </fonts>
-  <fills count="33">
+  <fills count="36">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -2163,6 +2250,24 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.79998168889431442"/>
+        <bgColor rgb="FFFEF2CB"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="3" tint="0.749992370372631"/>
+        <bgColor rgb="FFFEF2CB"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.79998168889431442"/>
+        <bgColor rgb="FFFEF2CB"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="6">
     <border>
@@ -2243,7 +2348,7 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="70">
+  <cellXfs count="86">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
@@ -2444,13 +2549,61 @@
     <xf numFmtId="0" fontId="5" fillId="28" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="8" fillId="31" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="17" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="11" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="17" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="6" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="17" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="33" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="33" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="34" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="34" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="35" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="35" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="Hiperlink" xfId="2" builtinId="8"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
     <cellStyle name="Normal 2" xfId="1" xr:uid="{A0D90F96-026A-4EEB-BDCF-93327D239D7A}"/>
   </cellStyles>
-  <dxfs count="63">
+  <dxfs count="95">
     <dxf>
       <font>
         <b val="0"/>
@@ -2458,6 +2611,130 @@
         <strike val="0"/>
         <color theme="0" tint="-0.499984740745262"/>
       </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i/>
+        <strike val="0"/>
+        <color theme="0"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i/>
+        <strike val="0"/>
+        <color theme="0" tint="-0.499984740745262"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i/>
+        <strike val="0"/>
+        <color theme="0"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i/>
+        <strike val="0"/>
+        <color theme="0" tint="-0.499984740745262"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i/>
+        <strike val="0"/>
+        <color theme="0"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i/>
+        <strike val="0"/>
+        <color theme="0" tint="-0.499984740745262"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i/>
+        <strike val="0"/>
+        <color theme="0" tint="-0.499984740745262"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i/>
+        <strike val="0"/>
+        <color theme="0"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i/>
+        <strike val="0"/>
+        <color theme="0" tint="-0.499984740745262"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i/>
+        <strike val="0"/>
+        <color theme="0"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i/>
+        <strike val="0"/>
+        <color theme="0" tint="-0.499984740745262"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i/>
+        <strike val="0"/>
+        <color theme="0" tint="-0.499984740745262"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i/>
+        <strike val="0"/>
+        <color theme="0" tint="-0.499984740745262"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
     </dxf>
     <dxf>
       <font>
@@ -2489,7 +2766,6 @@
       <font>
         <b val="0"/>
         <i/>
-        <strike val="0"/>
         <color theme="0" tint="-0.499984740745262"/>
       </font>
     </dxf>
@@ -2503,10 +2779,13 @@
     </dxf>
     <dxf>
       <font>
-        <b val="0"/>
-        <i/>
-        <color theme="0" tint="-0.499984740745262"/>
+        <color rgb="FF9C0006"/>
       </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
     </dxf>
     <dxf>
       <font>
@@ -2517,6 +2796,398 @@
           <bgColor rgb="FFFFC7CE"/>
         </patternFill>
       </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i/>
+        <strike val="0"/>
+        <color theme="0" tint="-0.499984740745262"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <name val="Arial Nova Cond Light"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="left" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="6"/>
+        <color auto="1"/>
+        <name val="Arial Nova Cond Light"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor theme="0" tint="-0.249977111117893"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top/>
+        <bottom/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <name val="Arial Nova Cond Light"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="left" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="6"/>
+        <color auto="1"/>
+        <name val="Arial Nova Cond Light"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor theme="0" tint="-0.249977111117893"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top/>
+        <bottom/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <name val="Arial Nova Cond Light"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="left" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="6"/>
+        <color auto="1"/>
+        <name val="Arial Nova Cond Light"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor theme="0" tint="-0.249977111117893"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top/>
+        <bottom/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <name val="Arial Nova Cond Light"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="left" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="6"/>
+        <color auto="1"/>
+        <name val="Arial Nova Cond Light"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor theme="0" tint="-0.249977111117893"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top/>
+        <bottom/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <name val="Arial Nova Cond Light"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="left" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="6"/>
+        <color auto="1"/>
+        <name val="Arial Nova Cond Light"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor theme="0" tint="-0.249977111117893"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top/>
+        <bottom/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <name val="Arial Nova Cond Light"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="left" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="6"/>
+        <color auto="1"/>
+        <name val="Arial Nova Cond Light"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor theme="0" tint="-0.249977111117893"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top/>
+        <bottom/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <name val="Arial Nova Cond Light"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="left" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="6"/>
+        <color auto="1"/>
+        <name val="Arial Nova Cond Light"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor theme="0" tint="-0.249977111117893"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top/>
+        <bottom/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <name val="Arial Nova Cond Light"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="left" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="6"/>
+        <color auto="1"/>
+        <name val="Arial Nova Cond Light"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor theme="0" tint="-0.249977111117893"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top/>
+        <bottom/>
+      </border>
     </dxf>
     <dxf>
       <font>
@@ -4320,33 +4991,41 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{A07C259E-03F8-41A3-821C-289758C0BF1B}" name="Tabla2" displayName="Tabla2" ref="A2:Y157" headerRowCount="0" totalsRowShown="0" headerRowDxfId="62" dataDxfId="60" headerRowBorderDxfId="61" tableBorderDxfId="59" totalsRowBorderDxfId="58">
-  <tableColumns count="25">
-    <tableColumn id="1" xr3:uid="{D841A366-4823-4EF9-B009-219AA94AF50A}" name="1" headerRowDxfId="57" dataDxfId="56"/>
-    <tableColumn id="2" xr3:uid="{41E717E1-E3DE-44C1-91C4-719DAB59A464}" name="Indivíduo" headerRowDxfId="55" dataDxfId="54"/>
-    <tableColumn id="3" xr3:uid="{38346B1D-47C6-4B44-A19C-766D16435669}" name="Classe" headerRowDxfId="53" dataDxfId="52"/>
-    <tableColumn id="5" xr3:uid="{27FF4C79-5131-4593-84DE-98F435DB6954}" name="Coluna2" headerRowDxfId="51" dataDxfId="50"/>
-    <tableColumn id="4" xr3:uid="{B4C1140F-50EB-4951-8734-6338EB3CF628}" name="Coluna1" headerRowDxfId="49" dataDxfId="48"/>
-    <tableColumn id="11" xr3:uid="{1EE4C35C-9E89-4C7C-8F68-2AC866434D95}" name="Coluna8" headerRowDxfId="47" dataDxfId="46"/>
-    <tableColumn id="10" xr3:uid="{0C28831F-E05A-4812-BB49-6E3DB059FDDA}" name="Coluna7" headerRowDxfId="45" dataDxfId="44"/>
-    <tableColumn id="9" xr3:uid="{C46F6396-5D54-4379-8FE7-47754ED408FB}" name="Coluna6" headerRowDxfId="43" dataDxfId="42"/>
-    <tableColumn id="14" xr3:uid="{7255F88A-C196-4C7D-BC78-487E43C6076E}" name="Coluna9" headerRowDxfId="41" dataDxfId="40"/>
-    <tableColumn id="15" xr3:uid="{CB39996D-E39C-41DF-9024-09188503F3A9}" name="Coluna10" headerRowDxfId="39" dataDxfId="38"/>
-    <tableColumn id="8" xr3:uid="{DC6BCDF7-14DD-4B0D-951F-937897AADF11}" name="Coluna5" headerRowDxfId="37" dataDxfId="36"/>
-    <tableColumn id="25" xr3:uid="{6E36A2EC-C3DA-4DF1-80AB-262ECBFDA8D3}" name="Coluna20" headerRowDxfId="35" dataDxfId="34"/>
-    <tableColumn id="24" xr3:uid="{7DA1B28C-8D87-49B1-8B12-94BDA4E3634B}" name="Coluna19" headerRowDxfId="33" dataDxfId="32"/>
-    <tableColumn id="12" xr3:uid="{72731FBF-D3F4-42FD-AF7E-09CD79716DE3}" name="Fato (11)" headerRowDxfId="31" dataDxfId="30"/>
-    <tableColumn id="13" xr3:uid="{40ED8FBD-39D6-4C0F-867B-9AA8C9C09316}" name="Valor8" headerRowDxfId="29" dataDxfId="28"/>
-    <tableColumn id="6" xr3:uid="{D7E37E62-C3F1-48D0-9ECE-1603C43E1947}" name="Coluna3" headerRowDxfId="27" dataDxfId="26"/>
-    <tableColumn id="7" xr3:uid="{8EAEA0F2-9F55-4FEE-86F2-D1912AEFC7F4}" name="Coluna4" headerRowDxfId="25" dataDxfId="24"/>
-    <tableColumn id="16" xr3:uid="{CB767617-3A28-42EC-8E47-CE6204F6D856}" name="Coluna11" headerRowDxfId="23" dataDxfId="22"/>
-    <tableColumn id="17" xr3:uid="{E29ADF84-36FF-41F7-9847-17BC340BAE5F}" name="Coluna12" headerRowDxfId="21" dataDxfId="20"/>
-    <tableColumn id="18" xr3:uid="{B5ADD4A7-EE28-45D9-B6FF-C285C2CD6E37}" name="Coluna13" headerRowDxfId="19" dataDxfId="18"/>
-    <tableColumn id="19" xr3:uid="{7FEDF53D-D312-4CF1-8EB3-4A56B77DEAA1}" name="Coluna14" headerRowDxfId="17" dataDxfId="16"/>
-    <tableColumn id="20" xr3:uid="{44C51568-5619-4D1B-B5B4-F2CF79CAB094}" name="Coluna15" headerRowDxfId="15" dataDxfId="14"/>
-    <tableColumn id="21" xr3:uid="{2A7C2A78-BAF9-429F-B898-EF931D80D830}" name="Coluna16" headerRowDxfId="13" dataDxfId="12"/>
-    <tableColumn id="22" xr3:uid="{3BB87186-A8C3-4EE2-9555-ACB7C40B9882}" name="Coluna17" headerRowDxfId="11" dataDxfId="10"/>
-    <tableColumn id="23" xr3:uid="{C574DFC8-E441-4BB1-A97D-83D5A9C08508}" name="Coluna18" headerRowDxfId="9" dataDxfId="8"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{A07C259E-03F8-41A3-821C-289758C0BF1B}" name="Tabla2" displayName="Tabla2" ref="A2:AG162" headerRowCount="0" totalsRowShown="0" headerRowDxfId="94" dataDxfId="92" headerRowBorderDxfId="93" tableBorderDxfId="91" totalsRowBorderDxfId="90">
+  <tableColumns count="33">
+    <tableColumn id="1" xr3:uid="{D841A366-4823-4EF9-B009-219AA94AF50A}" name="1" headerRowDxfId="89" dataDxfId="88"/>
+    <tableColumn id="2" xr3:uid="{41E717E1-E3DE-44C1-91C4-719DAB59A464}" name="Indivíduo" headerRowDxfId="87" dataDxfId="86"/>
+    <tableColumn id="3" xr3:uid="{38346B1D-47C6-4B44-A19C-766D16435669}" name="Classe" headerRowDxfId="85" dataDxfId="84"/>
+    <tableColumn id="5" xr3:uid="{27FF4C79-5131-4593-84DE-98F435DB6954}" name="Coluna2" headerRowDxfId="83" dataDxfId="82"/>
+    <tableColumn id="4" xr3:uid="{B4C1140F-50EB-4951-8734-6338EB3CF628}" name="Coluna1" headerRowDxfId="81" dataDxfId="80"/>
+    <tableColumn id="11" xr3:uid="{1EE4C35C-9E89-4C7C-8F68-2AC866434D95}" name="Coluna8" headerRowDxfId="79" dataDxfId="78"/>
+    <tableColumn id="10" xr3:uid="{0C28831F-E05A-4812-BB49-6E3DB059FDDA}" name="Coluna7" headerRowDxfId="77" dataDxfId="76"/>
+    <tableColumn id="9" xr3:uid="{C46F6396-5D54-4379-8FE7-47754ED408FB}" name="Coluna6" headerRowDxfId="75" dataDxfId="74"/>
+    <tableColumn id="14" xr3:uid="{7255F88A-C196-4C7D-BC78-487E43C6076E}" name="Coluna9" headerRowDxfId="73" dataDxfId="72"/>
+    <tableColumn id="15" xr3:uid="{CB39996D-E39C-41DF-9024-09188503F3A9}" name="Coluna10" headerRowDxfId="71" dataDxfId="70"/>
+    <tableColumn id="8" xr3:uid="{DC6BCDF7-14DD-4B0D-951F-937897AADF11}" name="Coluna5" headerRowDxfId="69" dataDxfId="68"/>
+    <tableColumn id="25" xr3:uid="{6E36A2EC-C3DA-4DF1-80AB-262ECBFDA8D3}" name="Coluna20" headerRowDxfId="67" dataDxfId="66"/>
+    <tableColumn id="24" xr3:uid="{7DA1B28C-8D87-49B1-8B12-94BDA4E3634B}" name="Coluna19" headerRowDxfId="65" dataDxfId="64"/>
+    <tableColumn id="12" xr3:uid="{72731FBF-D3F4-42FD-AF7E-09CD79716DE3}" name="Fato (11)" headerRowDxfId="63" dataDxfId="62"/>
+    <tableColumn id="13" xr3:uid="{40ED8FBD-39D6-4C0F-867B-9AA8C9C09316}" name="Valor8" headerRowDxfId="61" dataDxfId="60"/>
+    <tableColumn id="6" xr3:uid="{D7E37E62-C3F1-48D0-9ECE-1603C43E1947}" name="Coluna3" headerRowDxfId="59" dataDxfId="58"/>
+    <tableColumn id="7" xr3:uid="{8EAEA0F2-9F55-4FEE-86F2-D1912AEFC7F4}" name="Coluna4" headerRowDxfId="57" dataDxfId="56"/>
+    <tableColumn id="16" xr3:uid="{CB767617-3A28-42EC-8E47-CE6204F6D856}" name="Coluna11" headerRowDxfId="55" dataDxfId="54"/>
+    <tableColumn id="17" xr3:uid="{E29ADF84-36FF-41F7-9847-17BC340BAE5F}" name="Coluna12" headerRowDxfId="53" dataDxfId="52"/>
+    <tableColumn id="18" xr3:uid="{B5ADD4A7-EE28-45D9-B6FF-C285C2CD6E37}" name="Coluna13" headerRowDxfId="51" dataDxfId="50"/>
+    <tableColumn id="19" xr3:uid="{7FEDF53D-D312-4CF1-8EB3-4A56B77DEAA1}" name="Coluna14" headerRowDxfId="49" dataDxfId="48"/>
+    <tableColumn id="20" xr3:uid="{44C51568-5619-4D1B-B5B4-F2CF79CAB094}" name="Coluna15" headerRowDxfId="47" dataDxfId="46"/>
+    <tableColumn id="21" xr3:uid="{2A7C2A78-BAF9-429F-B898-EF931D80D830}" name="Coluna16" headerRowDxfId="45" dataDxfId="44"/>
+    <tableColumn id="22" xr3:uid="{3BB87186-A8C3-4EE2-9555-ACB7C40B9882}" name="Coluna17" headerRowDxfId="43" dataDxfId="42"/>
+    <tableColumn id="23" xr3:uid="{C574DFC8-E441-4BB1-A97D-83D5A9C08508}" name="Coluna18" headerRowDxfId="41" dataDxfId="40"/>
+    <tableColumn id="26" xr3:uid="{28A75A21-9AEA-4450-8DD2-5FEB86E3D1BF}" name="Coluna21" headerRowDxfId="39" dataDxfId="38"/>
+    <tableColumn id="27" xr3:uid="{9A2D685F-22A0-4828-9E11-08F2267BE681}" name="Coluna22" headerRowDxfId="37" dataDxfId="36"/>
+    <tableColumn id="28" xr3:uid="{4A34D3E2-5187-4876-A257-7428FBB430CA}" name="Coluna23" headerRowDxfId="35" dataDxfId="34"/>
+    <tableColumn id="29" xr3:uid="{F0F265E4-3C4A-45DA-9BD0-B6223C3A5AF7}" name="Coluna24" headerRowDxfId="33" dataDxfId="32"/>
+    <tableColumn id="30" xr3:uid="{F4245AB0-585B-463B-BDE4-2C1B32093872}" name="Coluna25" headerRowDxfId="31" dataDxfId="30"/>
+    <tableColumn id="31" xr3:uid="{78D68B95-AF87-4681-A542-69147C523764}" name="Coluna26" headerRowDxfId="29" dataDxfId="28"/>
+    <tableColumn id="32" xr3:uid="{60FB0CF7-F304-410C-A14D-436E194DA0BF}" name="Coluna27" headerRowDxfId="27" dataDxfId="26"/>
+    <tableColumn id="33" xr3:uid="{29FD05D0-59E6-4A8E-892C-3A07058F43BE}" name="Coluna28" headerRowDxfId="25" dataDxfId="24"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="0" showColumnStripes="0"/>
 </table>
@@ -4671,15 +5350,15 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{03763A90-6A45-4DA0-A35B-2601294A84FF}">
   <sheetPr codeName="Planilha1"/>
   <dimension ref="A1:C39"/>
-  <sheetFormatPr defaultColWidth="11" defaultRowHeight="9" customHeight="1" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="11" defaultRowHeight="9" customHeight="1" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="9.6640625" style="43" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="65.6640625" style="43" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="9.69921875" style="43" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="65.69921875" style="43" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="4.5" style="43" bestFit="1" customWidth="1"/>
     <col min="4" max="16384" width="11" style="43"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" ht="18.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:3" ht="19" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>4</v>
       </c>
@@ -4690,7 +5369,7 @@
         <v>403</v>
       </c>
     </row>
-    <row r="2" spans="1:3" ht="7.35" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:3" ht="7.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="3" t="s">
         <v>168</v>
       </c>
@@ -4701,7 +5380,7 @@
         <v>404</v>
       </c>
     </row>
-    <row r="3" spans="1:3" ht="7.35" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:3" ht="7.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="3" t="s">
         <v>169</v>
       </c>
@@ -4712,7 +5391,7 @@
         <v>404</v>
       </c>
     </row>
-    <row r="4" spans="1:3" ht="7.35" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:3" ht="7.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="4" t="s">
         <v>5</v>
       </c>
@@ -4723,7 +5402,7 @@
         <v>404</v>
       </c>
     </row>
-    <row r="5" spans="1:3" ht="7.35" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:3" ht="7.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="4" t="s">
         <v>6</v>
       </c>
@@ -4735,7 +5414,7 @@
         <v>404</v>
       </c>
     </row>
-    <row r="6" spans="1:3" ht="7.35" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:3" ht="7.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="4" t="s">
         <v>7</v>
       </c>
@@ -4747,7 +5426,7 @@
         <v>404</v>
       </c>
     </row>
-    <row r="7" spans="1:3" ht="7.35" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:3" ht="7.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="4" t="s">
         <v>8</v>
       </c>
@@ -4758,7 +5437,7 @@
         <v>404</v>
       </c>
     </row>
-    <row r="8" spans="1:3" ht="7.35" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:3" ht="7.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" s="39" t="s">
         <v>9</v>
       </c>
@@ -4769,7 +5448,7 @@
         <v>404</v>
       </c>
     </row>
-    <row r="9" spans="1:3" ht="7.35" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:3" ht="7.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="4" t="s">
         <v>170</v>
       </c>
@@ -4780,7 +5459,7 @@
         <v>404</v>
       </c>
     </row>
-    <row r="10" spans="1:3" ht="7.35" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:3" ht="7.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" s="4" t="s">
         <v>172</v>
       </c>
@@ -4791,7 +5470,7 @@
         <v>404</v>
       </c>
     </row>
-    <row r="11" spans="1:3" ht="7.35" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:3" ht="7.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A11" s="4" t="s">
         <v>173</v>
       </c>
@@ -4802,7 +5481,7 @@
         <v>404</v>
       </c>
     </row>
-    <row r="12" spans="1:3" ht="7.35" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:3" ht="7.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A12" s="4" t="s">
         <v>10</v>
       </c>
@@ -4813,7 +5492,7 @@
         <v>404</v>
       </c>
     </row>
-    <row r="13" spans="1:3" ht="7.35" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:3" ht="7.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A13" s="4" t="s">
         <v>174</v>
       </c>
@@ -4824,7 +5503,7 @@
         <v>404</v>
       </c>
     </row>
-    <row r="14" spans="1:3" ht="7.35" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:3" ht="7.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A14" s="4" t="s">
         <v>175</v>
       </c>
@@ -4835,7 +5514,7 @@
         <v>404</v>
       </c>
     </row>
-    <row r="15" spans="1:3" ht="7.35" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:3" ht="7.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A15" s="4" t="s">
         <v>176</v>
       </c>
@@ -4846,7 +5525,7 @@
         <v>404</v>
       </c>
     </row>
-    <row r="16" spans="1:3" ht="7.35" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:3" ht="7.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A16" s="4" t="s">
         <v>177</v>
       </c>
@@ -4857,7 +5536,7 @@
         <v>404</v>
       </c>
     </row>
-    <row r="17" spans="1:3" ht="7.35" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:3" ht="7.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A17" s="4" t="s">
         <v>12</v>
       </c>
@@ -4868,19 +5547,19 @@
         <v>404</v>
       </c>
     </row>
-    <row r="18" spans="1:3" ht="7.35" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:3" ht="7.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A18" s="4" t="s">
         <v>178</v>
       </c>
       <c r="B18" s="5">
         <f ca="1">NOW()</f>
-        <v>46253.599096296297</v>
+        <v>46257.700794675926</v>
       </c>
       <c r="C18" s="42" t="s">
         <v>404</v>
       </c>
     </row>
-    <row r="19" spans="1:3" ht="7.35" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:3" ht="7.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A19" s="4" t="s">
         <v>415</v>
       </c>
@@ -4891,7 +5570,7 @@
         <v>404</v>
       </c>
     </row>
-    <row r="20" spans="1:3" ht="7.35" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:3" ht="7.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A20" s="39" t="s">
         <v>411</v>
       </c>
@@ -4903,7 +5582,7 @@
         <v>405</v>
       </c>
     </row>
-    <row r="21" spans="1:3" ht="7.35" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:3" ht="7.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A21" s="39" t="s">
         <v>416</v>
       </c>
@@ -4915,7 +5594,7 @@
         <v>406</v>
       </c>
     </row>
-    <row r="22" spans="1:3" ht="7.35" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:3" ht="7.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A22" s="4" t="s">
         <v>167</v>
       </c>
@@ -4926,7 +5605,7 @@
         <v>404</v>
       </c>
     </row>
-    <row r="23" spans="1:3" ht="7.35" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:3" ht="7.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A23" s="4" t="s">
         <v>179</v>
       </c>
@@ -4937,7 +5616,7 @@
         <v>404</v>
       </c>
     </row>
-    <row r="24" spans="1:3" ht="7.35" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:3" ht="7.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A24" s="4" t="s">
         <v>184</v>
       </c>
@@ -4948,7 +5627,7 @@
         <v>404</v>
       </c>
     </row>
-    <row r="25" spans="1:3" ht="7.35" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:3" ht="7.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A25" s="4" t="s">
         <v>186</v>
       </c>
@@ -4959,7 +5638,7 @@
         <v>405</v>
       </c>
     </row>
-    <row r="26" spans="1:3" ht="7.35" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:3" ht="7.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A26" s="39" t="s">
         <v>400</v>
       </c>
@@ -4970,7 +5649,7 @@
         <v>406</v>
       </c>
     </row>
-    <row r="27" spans="1:3" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:3" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A27" s="39" t="s">
         <v>527</v>
       </c>
@@ -4981,7 +5660,7 @@
         <v>404</v>
       </c>
     </row>
-    <row r="28" spans="1:3" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:3" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A28" s="39" t="s">
         <v>529</v>
       </c>
@@ -4992,7 +5671,7 @@
         <v>404</v>
       </c>
     </row>
-    <row r="29" spans="1:3" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:3" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A29" s="39" t="s">
         <v>531</v>
       </c>
@@ -5003,7 +5682,7 @@
         <v>404</v>
       </c>
     </row>
-    <row r="30" spans="1:3" s="63" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="30" spans="1:3" s="63" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A30" s="39" t="s">
         <v>533</v>
       </c>
@@ -5014,7 +5693,7 @@
         <v>404</v>
       </c>
     </row>
-    <row r="31" spans="1:3" s="63" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="31" spans="1:3" s="63" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A31" s="39" t="s">
         <v>535</v>
       </c>
@@ -5025,7 +5704,7 @@
         <v>404</v>
       </c>
     </row>
-    <row r="32" spans="1:3" s="63" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="32" spans="1:3" s="63" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A32" s="39" t="s">
         <v>537</v>
       </c>
@@ -5036,7 +5715,7 @@
         <v>404</v>
       </c>
     </row>
-    <row r="33" spans="1:3" s="63" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="33" spans="1:3" s="63" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A33" s="39" t="s">
         <v>539</v>
       </c>
@@ -5047,7 +5726,7 @@
         <v>404</v>
       </c>
     </row>
-    <row r="34" spans="1:3" s="63" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="34" spans="1:3" s="63" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A34" s="39" t="s">
         <v>541</v>
       </c>
@@ -5058,7 +5737,7 @@
         <v>404</v>
       </c>
     </row>
-    <row r="35" spans="1:3" s="63" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="35" spans="1:3" s="63" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A35" s="39" t="s">
         <v>543</v>
       </c>
@@ -5069,7 +5748,7 @@
         <v>404</v>
       </c>
     </row>
-    <row r="36" spans="1:3" s="63" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="36" spans="1:3" s="63" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A36" s="39" t="s">
         <v>545</v>
       </c>
@@ -5080,7 +5759,7 @@
         <v>404</v>
       </c>
     </row>
-    <row r="37" spans="1:3" s="63" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="37" spans="1:3" s="63" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A37" s="39" t="s">
         <v>547</v>
       </c>
@@ -5091,7 +5770,7 @@
         <v>404</v>
       </c>
     </row>
-    <row r="38" spans="1:3" customFormat="1" ht="9.9499999999999993" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="38" spans="1:3" customFormat="1" ht="10" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A38" s="4" t="s">
         <v>549</v>
       </c>
@@ -5102,7 +5781,7 @@
         <v>404</v>
       </c>
     </row>
-    <row r="39" spans="1:3" s="67" customFormat="1" ht="9.6" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="39" spans="1:3" s="67" customFormat="1" ht="9.65" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A39" s="39" t="s">
         <v>551</v>
       </c>
@@ -5128,37 +5807,37 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{958751C2-A34E-4345-8D6A-082603A025F9}">
   <sheetPr codeName="Planilha2"/>
-  <dimension ref="A1:AC23"/>
-  <sheetFormatPr defaultRowHeight="6.75" customHeight="1" x14ac:dyDescent="0.2"/>
+  <dimension ref="A1:AC24"/>
+  <sheetFormatPr defaultRowHeight="6.75" customHeight="1" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="2.83203125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="7.33203125" style="34" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="8.1640625" style="34" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="2.796875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="7.296875" style="34" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="8.19921875" style="34" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="10.5" style="34" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="7.6640625" style="34" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.83203125" style="34" bestFit="1" customWidth="1"/>
-    <col min="7" max="11" width="11.83203125" style="34" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="8.1640625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="7.69921875" style="34" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.796875" style="34" bestFit="1" customWidth="1"/>
+    <col min="7" max="11" width="11.796875" style="34" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="8.19921875" bestFit="1" customWidth="1"/>
     <col min="13" max="13" width="10.5" bestFit="1" customWidth="1"/>
     <col min="14" max="14" width="8" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.83203125" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="78.1640625" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.796875" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="78.19921875" bestFit="1" customWidth="1"/>
     <col min="17" max="17" width="80.5" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="71.6640625" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="71.69921875" bestFit="1" customWidth="1"/>
     <col min="19" max="19" width="5" style="34" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="8.1640625" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="8.19921875" bestFit="1" customWidth="1"/>
     <col min="21" max="21" width="10.5" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="7.6640625" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="7.69921875" bestFit="1" customWidth="1"/>
     <col min="23" max="23" width="10" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="9.83203125" style="34" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="43.83203125" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="9.83203125" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="44.83203125" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="8.83203125" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="8.6640625" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="9.796875" style="34" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="43.796875" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="9.796875" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="44.796875" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="8.796875" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="8.69921875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:29" ht="37.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:29" ht="37.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="22" t="s">
         <v>349</v>
       </c>
@@ -5247,7 +5926,7 @@
         <v>372</v>
       </c>
     </row>
-    <row r="2" spans="1:29" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:29" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="49">
         <v>2</v>
       </c>
@@ -5344,7 +6023,7 @@
         <v>420</v>
       </c>
     </row>
-    <row r="3" spans="1:29" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:29" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="49">
         <v>3</v>
       </c>
@@ -5441,7 +6120,7 @@
         <v>421</v>
       </c>
     </row>
-    <row r="4" spans="1:29" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:29" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="49">
         <v>4</v>
       </c>
@@ -5538,7 +6217,7 @@
         <v>422</v>
       </c>
     </row>
-    <row r="5" spans="1:29" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:29" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="49">
         <v>5</v>
       </c>
@@ -5635,7 +6314,7 @@
         <v>423</v>
       </c>
     </row>
-    <row r="6" spans="1:29" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:29" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="49">
         <v>6</v>
       </c>
@@ -5732,7 +6411,7 @@
         <v>424</v>
       </c>
     </row>
-    <row r="7" spans="1:29" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:29" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="49">
         <v>7</v>
       </c>
@@ -5829,7 +6508,7 @@
         <v>425</v>
       </c>
     </row>
-    <row r="8" spans="1:29" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:29" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" s="49">
         <v>8</v>
       </c>
@@ -5926,7 +6605,7 @@
         <v>342</v>
       </c>
     </row>
-    <row r="9" spans="1:29" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:29" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="49">
         <v>9</v>
       </c>
@@ -6023,7 +6702,7 @@
         <v>426</v>
       </c>
     </row>
-    <row r="10" spans="1:29" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:29" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" s="49">
         <v>10</v>
       </c>
@@ -6120,7 +6799,7 @@
         <v>427</v>
       </c>
     </row>
-    <row r="11" spans="1:29" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:29" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A11" s="49">
         <v>11</v>
       </c>
@@ -6217,7 +6896,7 @@
         <v>428</v>
       </c>
     </row>
-    <row r="12" spans="1:29" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:29" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A12" s="49">
         <v>12</v>
       </c>
@@ -6314,7 +6993,7 @@
         <v>429</v>
       </c>
     </row>
-    <row r="13" spans="1:29" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:29" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A13" s="49">
         <v>13</v>
       </c>
@@ -6411,7 +7090,7 @@
         <v>430</v>
       </c>
     </row>
-    <row r="14" spans="1:29" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:29" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A14" s="49">
         <v>14</v>
       </c>
@@ -6508,7 +7187,7 @@
         <v>431</v>
       </c>
     </row>
-    <row r="15" spans="1:29" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:29" ht="7" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A15" s="49">
         <v>15</v>
       </c>
@@ -6586,7 +7265,7 @@
         <v>419</v>
       </c>
       <c r="X15" s="58" t="str">
-        <f t="shared" ref="X15:X23" si="7">CONCATENATE("Key-ABNT-",A15)</f>
+        <f t="shared" ref="X15:X24" si="7">CONCATENATE("Key-ABNT-",A15)</f>
         <v>Key-ABNT-15</v>
       </c>
       <c r="Y15" s="38" t="s">
@@ -6605,7 +7284,7 @@
         <v>477</v>
       </c>
     </row>
-    <row r="16" spans="1:29" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:29" ht="7" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A16" s="49">
         <v>16</v>
       </c>
@@ -6702,7 +7381,7 @@
         <v>478</v>
       </c>
     </row>
-    <row r="17" spans="1:29" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:29" ht="7" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A17" s="49">
         <v>17</v>
       </c>
@@ -6799,7 +7478,7 @@
         <v>479</v>
       </c>
     </row>
-    <row r="18" spans="1:29" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:29" ht="7" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A18" s="49">
         <v>18</v>
       </c>
@@ -6896,7 +7575,7 @@
         <v>480</v>
       </c>
     </row>
-    <row r="19" spans="1:29" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:29" ht="7" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A19" s="49">
         <v>19</v>
       </c>
@@ -6993,7 +7672,7 @@
         <v>481</v>
       </c>
     </row>
-    <row r="20" spans="1:29" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:29" ht="7" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A20" s="49">
         <v>20</v>
       </c>
@@ -7090,7 +7769,7 @@
         <v>482</v>
       </c>
     </row>
-    <row r="21" spans="1:29" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:29" ht="7" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A21" s="49">
         <v>21</v>
       </c>
@@ -7187,7 +7866,7 @@
         <v>483</v>
       </c>
     </row>
-    <row r="22" spans="1:29" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:29" ht="7" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A22" s="49">
         <v>22</v>
       </c>
@@ -7284,7 +7963,7 @@
         <v>484</v>
       </c>
     </row>
-    <row r="23" spans="1:29" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:29" ht="7" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A23" s="49">
         <v>23</v>
       </c>
@@ -7381,22 +8060,122 @@
         <v>485</v>
       </c>
     </row>
+    <row r="24" spans="1:29" s="48" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A24" s="49">
+        <v>24</v>
+      </c>
+      <c r="B24" s="50" t="s">
+        <v>588</v>
+      </c>
+      <c r="C24" s="33" t="s">
+        <v>589</v>
+      </c>
+      <c r="D24" s="33" t="s">
+        <v>590</v>
+      </c>
+      <c r="E24" s="33" t="s">
+        <v>591</v>
+      </c>
+      <c r="F24" s="33" t="s">
+        <v>592</v>
+      </c>
+      <c r="G24" s="36" t="s">
+        <v>181</v>
+      </c>
+      <c r="H24" s="36" t="s">
+        <v>181</v>
+      </c>
+      <c r="I24" s="36" t="s">
+        <v>181</v>
+      </c>
+      <c r="J24" s="36" t="s">
+        <v>181</v>
+      </c>
+      <c r="K24" s="36" t="s">
+        <v>181</v>
+      </c>
+      <c r="L24" s="51" t="str">
+        <f t="shared" ref="L24:O24" si="9">SUBSTITUTE(CONCATENATE("", C24), ".", " ")</f>
+        <v>De API</v>
+      </c>
+      <c r="M24" s="51" t="str">
+        <f t="shared" si="9"/>
+        <v>Métodos</v>
+      </c>
+      <c r="N24" s="51" t="str">
+        <f t="shared" si="9"/>
+        <v>Macros</v>
+      </c>
+      <c r="O24" s="51" t="str">
+        <f t="shared" si="9"/>
+        <v>API Revit</v>
+      </c>
+      <c r="P24" s="38" t="s">
+        <v>593</v>
+      </c>
+      <c r="Q24" s="38" t="s">
+        <v>594</v>
+      </c>
+      <c r="R24" s="38" t="s">
+        <v>595</v>
+      </c>
+      <c r="S24" s="38" t="s">
+        <v>181</v>
+      </c>
+      <c r="T24" s="38" t="str">
+        <f t="shared" ref="T24:V24" si="10">SUBSTITUTE(C24, ".", " ")</f>
+        <v>De API</v>
+      </c>
+      <c r="U24" s="38" t="str">
+        <f t="shared" si="10"/>
+        <v>Métodos</v>
+      </c>
+      <c r="V24" s="52" t="str">
+        <f t="shared" si="10"/>
+        <v>Macros</v>
+      </c>
+      <c r="W24" s="38" t="s">
+        <v>419</v>
+      </c>
+      <c r="X24" s="58" t="str">
+        <f t="shared" si="7"/>
+        <v>Key-ABNT-24</v>
+      </c>
+      <c r="Y24" s="70" t="s">
+        <v>181</v>
+      </c>
+      <c r="Z24" s="70" t="s">
+        <v>181</v>
+      </c>
+      <c r="AA24" s="70" t="s">
+        <v>181</v>
+      </c>
+      <c r="AB24" s="70" t="s">
+        <v>181</v>
+      </c>
+      <c r="AC24" s="70" t="s">
+        <v>181</v>
+      </c>
+    </row>
   </sheetData>
-  <conditionalFormatting sqref="F2:F14">
-    <cfRule type="duplicateValues" dxfId="7" priority="5"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="Y2 AA2">
-    <cfRule type="cellIs" dxfId="6" priority="2" operator="equal">
+  <conditionalFormatting sqref="A2:B24">
+    <cfRule type="cellIs" dxfId="23" priority="2" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A2:B23">
-    <cfRule type="cellIs" dxfId="5" priority="4" operator="equal">
+  <conditionalFormatting sqref="F2:F14">
+    <cfRule type="duplicateValues" dxfId="22" priority="9"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F24">
+    <cfRule type="duplicateValues" dxfId="21" priority="3"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="R1:R24">
+    <cfRule type="cellIs" dxfId="20" priority="1" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="R1:R23">
-    <cfRule type="cellIs" dxfId="4" priority="1" operator="equal">
+  <conditionalFormatting sqref="Y2 AA2">
+    <cfRule type="cellIs" dxfId="19" priority="6" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -7411,13 +8190,13 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B2B4A051-97A0-4486-9B30-1861C9F77522}">
   <sheetPr codeName="Planilha3"/>
   <dimension ref="A1:U2"/>
-  <sheetFormatPr defaultColWidth="5.33203125" defaultRowHeight="11.25" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="5.296875" defaultRowHeight="10.75" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="2" customWidth="1"/>
     <col min="2" max="21" width="5" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:21" ht="24.75" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:21" ht="23.15" x14ac:dyDescent="0.3">
       <c r="A1" s="27" t="s">
         <v>350</v>
       </c>
@@ -7482,7 +8261,7 @@
         <v>392</v>
       </c>
     </row>
-    <row r="2" spans="1:21" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:21" ht="8.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="27">
         <v>2</v>
       </c>
@@ -7549,7 +8328,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:U2">
-    <cfRule type="cellIs" dxfId="3" priority="1" operator="equal">
+    <cfRule type="cellIs" dxfId="18" priority="1" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -7564,13 +8343,13 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{78CA1C4B-37EB-4980-B878-E43323BA46B5}">
   <sheetPr codeName="Planilha4"/>
   <dimension ref="A1:C2"/>
-  <sheetFormatPr defaultRowHeight="11.25" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultRowHeight="10.75" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="3.33203125" bestFit="1" customWidth="1"/>
-    <col min="2" max="3" width="16.6640625" customWidth="1"/>
+    <col min="1" max="1" width="3.296875" bestFit="1" customWidth="1"/>
+    <col min="2" max="3" width="16.69921875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1" s="30">
         <v>1</v>
       </c>
@@ -7581,7 +8360,7 @@
         <v>395</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A2" s="21">
         <v>2</v>
       </c>
@@ -7594,7 +8373,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:A2">
-    <cfRule type="cellIs" dxfId="2" priority="1" operator="equal">
+    <cfRule type="cellIs" dxfId="17" priority="1" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -7605,31 +8384,46 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B79BA5E7-BFBD-4AC9-B36C-B9776AA17B75}">
   <sheetPr codeName="Planilha5"/>
-  <dimension ref="A1:Y157"/>
-  <sheetFormatPr defaultColWidth="11.33203125" defaultRowHeight="6" customHeight="1" x14ac:dyDescent="0.2"/>
+  <dimension ref="A1:AG162"/>
+  <sheetFormatPr defaultColWidth="3.69921875" defaultRowHeight="6" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="3.6640625" style="2" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="11.33203125" style="2" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="14.83203125" style="2" customWidth="1"/>
-    <col min="4" max="4" width="10.1640625" style="2" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="7.6640625" style="2" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="7.33203125" style="48" customWidth="1"/>
-    <col min="7" max="7" width="10" style="48" customWidth="1"/>
-    <col min="8" max="9" width="7.33203125" style="48" customWidth="1"/>
-    <col min="10" max="10" width="4.33203125" style="48" customWidth="1"/>
-    <col min="11" max="11" width="14" style="48" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="7.5" style="48" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="29.1640625" style="48" customWidth="1"/>
-    <col min="14" max="14" width="7" style="48" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="43.83203125" style="2" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="8.6640625" style="48" customWidth="1"/>
-    <col min="17" max="17" width="5" style="48" customWidth="1"/>
-    <col min="18" max="18" width="5.5" style="48" customWidth="1"/>
-    <col min="19" max="25" width="5" style="48" customWidth="1"/>
-    <col min="26" max="16384" width="11.33203125" style="2"/>
+    <col min="1" max="1" width="2.5" style="2" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="8.19921875" style="2" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="11.3984375" style="2" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="8.09765625" style="2" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="5.8984375" style="2" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="3.796875" style="48" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="7.59765625" style="48" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="3.09765625" style="48" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="5.19921875" style="48" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="3.09765625" style="48" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="11.296875" style="48" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="4.796875" style="48" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="27.69921875" style="48" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="5.3984375" style="48" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="36.796875" style="2" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="7.5" style="48" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="3.69921875" style="48"/>
+    <col min="18" max="18" width="5.09765625" style="48" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="3.69921875" style="48"/>
+    <col min="20" max="20" width="3.09765625" style="48" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="3.69921875" style="48"/>
+    <col min="22" max="22" width="3.09765625" style="48" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="3.69921875" style="48"/>
+    <col min="24" max="24" width="7.5" style="48" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="7.796875" style="48" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="5.796875" style="2" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="6" style="2" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="7.59765625" style="2" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="7.5" style="2" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="4.8984375" style="2" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="7.19921875" style="2" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="6.8984375" style="2" bestFit="1" customWidth="1"/>
+    <col min="33" max="33" width="7.09765625" style="2" bestFit="1" customWidth="1"/>
+    <col min="34" max="16384" width="3.69921875" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:25" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:33" ht="18.649999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="7" t="s">
         <v>180</v>
       </c>
@@ -7695,14 +8489,38 @@
       <c r="W1" s="8" t="s">
         <v>3</v>
       </c>
-      <c r="X1" s="44" t="s">
+      <c r="X1" s="85" t="s">
         <v>2</v>
       </c>
-      <c r="Y1" s="8" t="s">
+      <c r="Y1" s="85" t="s">
         <v>3</v>
       </c>
+      <c r="Z1" s="85" t="s">
+        <v>2</v>
+      </c>
+      <c r="AA1" s="85" t="s">
+        <v>3</v>
+      </c>
+      <c r="AB1" s="85" t="s">
+        <v>2</v>
+      </c>
+      <c r="AC1" s="85" t="s">
+        <v>3</v>
+      </c>
+      <c r="AD1" s="85" t="s">
+        <v>2</v>
+      </c>
+      <c r="AE1" s="85" t="s">
+        <v>3</v>
+      </c>
+      <c r="AF1" s="85" t="s">
+        <v>2</v>
+      </c>
+      <c r="AG1" s="85" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="2" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:33" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="9">
         <v>2</v>
       </c>
@@ -7772,14 +8590,38 @@
       <c r="W2" s="46" t="s">
         <v>181</v>
       </c>
-      <c r="X2" s="45" t="s">
-        <v>181</v>
-      </c>
-      <c r="Y2" s="46" t="s">
+      <c r="X2" s="55" t="s">
+        <v>181</v>
+      </c>
+      <c r="Y2" s="56" t="s">
+        <v>181</v>
+      </c>
+      <c r="Z2" s="55" t="s">
+        <v>181</v>
+      </c>
+      <c r="AA2" s="56" t="s">
+        <v>181</v>
+      </c>
+      <c r="AB2" s="55" t="s">
+        <v>181</v>
+      </c>
+      <c r="AC2" s="56" t="s">
+        <v>181</v>
+      </c>
+      <c r="AD2" s="55" t="s">
+        <v>181</v>
+      </c>
+      <c r="AE2" s="56" t="s">
+        <v>181</v>
+      </c>
+      <c r="AF2" s="55" t="s">
+        <v>181</v>
+      </c>
+      <c r="AG2" s="56" t="s">
         <v>181</v>
       </c>
     </row>
-    <row r="3" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:33" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="9">
         <v>3</v>
       </c>
@@ -7849,14 +8691,38 @@
       <c r="W3" s="46" t="s">
         <v>181</v>
       </c>
-      <c r="X3" s="45" t="s">
-        <v>181</v>
-      </c>
-      <c r="Y3" s="46" t="s">
+      <c r="X3" s="55" t="s">
+        <v>181</v>
+      </c>
+      <c r="Y3" s="56" t="s">
+        <v>181</v>
+      </c>
+      <c r="Z3" s="55" t="s">
+        <v>181</v>
+      </c>
+      <c r="AA3" s="56" t="s">
+        <v>181</v>
+      </c>
+      <c r="AB3" s="55" t="s">
+        <v>181</v>
+      </c>
+      <c r="AC3" s="56" t="s">
+        <v>181</v>
+      </c>
+      <c r="AD3" s="55" t="s">
+        <v>181</v>
+      </c>
+      <c r="AE3" s="56" t="s">
+        <v>181</v>
+      </c>
+      <c r="AF3" s="55" t="s">
+        <v>181</v>
+      </c>
+      <c r="AG3" s="56" t="s">
         <v>181</v>
       </c>
     </row>
-    <row r="4" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:33" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="9">
         <v>4</v>
       </c>
@@ -7926,14 +8792,38 @@
       <c r="W4" s="46" t="s">
         <v>181</v>
       </c>
-      <c r="X4" s="45" t="s">
-        <v>181</v>
-      </c>
-      <c r="Y4" s="46" t="s">
-        <v>181</v>
+      <c r="X4" s="55" t="s">
+        <v>612</v>
+      </c>
+      <c r="Y4" s="56" t="s">
+        <v>596</v>
+      </c>
+      <c r="Z4" s="55" t="s">
+        <v>613</v>
+      </c>
+      <c r="AA4" s="56" t="s">
+        <v>600</v>
+      </c>
+      <c r="AB4" s="55" t="s">
+        <v>614</v>
+      </c>
+      <c r="AC4" s="56" t="s">
+        <v>603</v>
+      </c>
+      <c r="AD4" s="55" t="s">
+        <v>615</v>
+      </c>
+      <c r="AE4" s="56" t="s">
+        <v>606</v>
+      </c>
+      <c r="AF4" s="55" t="s">
+        <v>616</v>
+      </c>
+      <c r="AG4" s="56" t="s">
+        <v>609</v>
       </c>
     </row>
-    <row r="5" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:33" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="9">
         <v>5</v>
       </c>
@@ -8003,14 +8893,38 @@
       <c r="W5" s="46" t="s">
         <v>181</v>
       </c>
-      <c r="X5" s="45" t="s">
-        <v>181</v>
-      </c>
-      <c r="Y5" s="46" t="s">
-        <v>181</v>
+      <c r="X5" s="55" t="s">
+        <v>612</v>
+      </c>
+      <c r="Y5" s="56" t="s">
+        <v>596</v>
+      </c>
+      <c r="Z5" s="55" t="s">
+        <v>613</v>
+      </c>
+      <c r="AA5" s="56" t="s">
+        <v>600</v>
+      </c>
+      <c r="AB5" s="55" t="s">
+        <v>614</v>
+      </c>
+      <c r="AC5" s="56" t="s">
+        <v>603</v>
+      </c>
+      <c r="AD5" s="55" t="s">
+        <v>615</v>
+      </c>
+      <c r="AE5" s="56" t="s">
+        <v>606</v>
+      </c>
+      <c r="AF5" s="55" t="s">
+        <v>616</v>
+      </c>
+      <c r="AG5" s="56" t="s">
+        <v>609</v>
       </c>
     </row>
-    <row r="6" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:33" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="9">
         <v>6</v>
       </c>
@@ -8080,14 +8994,38 @@
       <c r="W6" s="46" t="s">
         <v>181</v>
       </c>
-      <c r="X6" s="45" t="s">
-        <v>181</v>
-      </c>
-      <c r="Y6" s="46" t="s">
-        <v>181</v>
+      <c r="X6" s="55" t="s">
+        <v>612</v>
+      </c>
+      <c r="Y6" s="56" t="s">
+        <v>596</v>
+      </c>
+      <c r="Z6" s="55" t="s">
+        <v>613</v>
+      </c>
+      <c r="AA6" s="56" t="s">
+        <v>600</v>
+      </c>
+      <c r="AB6" s="55" t="s">
+        <v>614</v>
+      </c>
+      <c r="AC6" s="56" t="s">
+        <v>603</v>
+      </c>
+      <c r="AD6" s="55" t="s">
+        <v>615</v>
+      </c>
+      <c r="AE6" s="56" t="s">
+        <v>606</v>
+      </c>
+      <c r="AF6" s="55" t="s">
+        <v>616</v>
+      </c>
+      <c r="AG6" s="56" t="s">
+        <v>609</v>
       </c>
     </row>
-    <row r="7" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:33" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="9">
         <v>7</v>
       </c>
@@ -8157,14 +9095,38 @@
       <c r="W7" s="46" t="s">
         <v>181</v>
       </c>
-      <c r="X7" s="45" t="s">
-        <v>181</v>
-      </c>
-      <c r="Y7" s="46" t="s">
-        <v>181</v>
+      <c r="X7" s="55" t="s">
+        <v>612</v>
+      </c>
+      <c r="Y7" s="56" t="s">
+        <v>596</v>
+      </c>
+      <c r="Z7" s="55" t="s">
+        <v>613</v>
+      </c>
+      <c r="AA7" s="56" t="s">
+        <v>600</v>
+      </c>
+      <c r="AB7" s="55" t="s">
+        <v>614</v>
+      </c>
+      <c r="AC7" s="56" t="s">
+        <v>603</v>
+      </c>
+      <c r="AD7" s="55" t="s">
+        <v>615</v>
+      </c>
+      <c r="AE7" s="56" t="s">
+        <v>606</v>
+      </c>
+      <c r="AF7" s="55" t="s">
+        <v>616</v>
+      </c>
+      <c r="AG7" s="56" t="s">
+        <v>609</v>
       </c>
     </row>
-    <row r="8" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:33" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="9">
         <v>8</v>
       </c>
@@ -8234,14 +9196,38 @@
       <c r="W8" s="46" t="s">
         <v>181</v>
       </c>
-      <c r="X8" s="45" t="s">
-        <v>181</v>
-      </c>
-      <c r="Y8" s="46" t="s">
-        <v>181</v>
+      <c r="X8" s="55" t="s">
+        <v>612</v>
+      </c>
+      <c r="Y8" s="56" t="s">
+        <v>596</v>
+      </c>
+      <c r="Z8" s="55" t="s">
+        <v>613</v>
+      </c>
+      <c r="AA8" s="56" t="s">
+        <v>600</v>
+      </c>
+      <c r="AB8" s="55" t="s">
+        <v>614</v>
+      </c>
+      <c r="AC8" s="56" t="s">
+        <v>603</v>
+      </c>
+      <c r="AD8" s="55" t="s">
+        <v>615</v>
+      </c>
+      <c r="AE8" s="56" t="s">
+        <v>606</v>
+      </c>
+      <c r="AF8" s="55" t="s">
+        <v>616</v>
+      </c>
+      <c r="AG8" s="56" t="s">
+        <v>609</v>
       </c>
     </row>
-    <row r="9" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:33" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="9">
         <v>9</v>
       </c>
@@ -8311,14 +9297,38 @@
       <c r="W9" s="46" t="s">
         <v>181</v>
       </c>
-      <c r="X9" s="45" t="s">
-        <v>181</v>
-      </c>
-      <c r="Y9" s="46" t="s">
-        <v>181</v>
+      <c r="X9" s="55" t="s">
+        <v>612</v>
+      </c>
+      <c r="Y9" s="56" t="s">
+        <v>596</v>
+      </c>
+      <c r="Z9" s="55" t="s">
+        <v>613</v>
+      </c>
+      <c r="AA9" s="56" t="s">
+        <v>600</v>
+      </c>
+      <c r="AB9" s="55" t="s">
+        <v>614</v>
+      </c>
+      <c r="AC9" s="56" t="s">
+        <v>603</v>
+      </c>
+      <c r="AD9" s="55" t="s">
+        <v>615</v>
+      </c>
+      <c r="AE9" s="56" t="s">
+        <v>606</v>
+      </c>
+      <c r="AF9" s="55" t="s">
+        <v>616</v>
+      </c>
+      <c r="AG9" s="56" t="s">
+        <v>609</v>
       </c>
     </row>
-    <row r="10" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:33" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="9">
         <v>10</v>
       </c>
@@ -8388,14 +9398,38 @@
       <c r="W10" s="46" t="s">
         <v>181</v>
       </c>
-      <c r="X10" s="45" t="s">
-        <v>181</v>
-      </c>
-      <c r="Y10" s="46" t="s">
-        <v>181</v>
+      <c r="X10" s="55" t="s">
+        <v>612</v>
+      </c>
+      <c r="Y10" s="56" t="s">
+        <v>596</v>
+      </c>
+      <c r="Z10" s="55" t="s">
+        <v>613</v>
+      </c>
+      <c r="AA10" s="56" t="s">
+        <v>600</v>
+      </c>
+      <c r="AB10" s="55" t="s">
+        <v>614</v>
+      </c>
+      <c r="AC10" s="56" t="s">
+        <v>603</v>
+      </c>
+      <c r="AD10" s="55" t="s">
+        <v>615</v>
+      </c>
+      <c r="AE10" s="56" t="s">
+        <v>606</v>
+      </c>
+      <c r="AF10" s="55" t="s">
+        <v>616</v>
+      </c>
+      <c r="AG10" s="56" t="s">
+        <v>609</v>
       </c>
     </row>
-    <row r="11" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:33" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="9">
         <v>11</v>
       </c>
@@ -8465,14 +9499,38 @@
       <c r="W11" s="46" t="s">
         <v>181</v>
       </c>
-      <c r="X11" s="45" t="s">
-        <v>181</v>
-      </c>
-      <c r="Y11" s="46" t="s">
-        <v>181</v>
+      <c r="X11" s="55" t="s">
+        <v>612</v>
+      </c>
+      <c r="Y11" s="56" t="s">
+        <v>596</v>
+      </c>
+      <c r="Z11" s="55" t="s">
+        <v>613</v>
+      </c>
+      <c r="AA11" s="56" t="s">
+        <v>600</v>
+      </c>
+      <c r="AB11" s="55" t="s">
+        <v>614</v>
+      </c>
+      <c r="AC11" s="56" t="s">
+        <v>603</v>
+      </c>
+      <c r="AD11" s="55" t="s">
+        <v>615</v>
+      </c>
+      <c r="AE11" s="56" t="s">
+        <v>606</v>
+      </c>
+      <c r="AF11" s="55" t="s">
+        <v>616</v>
+      </c>
+      <c r="AG11" s="56" t="s">
+        <v>609</v>
       </c>
     </row>
-    <row r="12" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:33" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="9">
         <v>12</v>
       </c>
@@ -8542,14 +9600,38 @@
       <c r="W12" s="46" t="s">
         <v>181</v>
       </c>
-      <c r="X12" s="45" t="s">
-        <v>181</v>
-      </c>
-      <c r="Y12" s="46" t="s">
-        <v>181</v>
+      <c r="X12" s="55" t="s">
+        <v>612</v>
+      </c>
+      <c r="Y12" s="56" t="s">
+        <v>596</v>
+      </c>
+      <c r="Z12" s="55" t="s">
+        <v>613</v>
+      </c>
+      <c r="AA12" s="56" t="s">
+        <v>600</v>
+      </c>
+      <c r="AB12" s="55" t="s">
+        <v>614</v>
+      </c>
+      <c r="AC12" s="56" t="s">
+        <v>603</v>
+      </c>
+      <c r="AD12" s="55" t="s">
+        <v>615</v>
+      </c>
+      <c r="AE12" s="56" t="s">
+        <v>606</v>
+      </c>
+      <c r="AF12" s="55" t="s">
+        <v>616</v>
+      </c>
+      <c r="AG12" s="56" t="s">
+        <v>609</v>
       </c>
     </row>
-    <row r="13" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:33" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="9">
         <v>13</v>
       </c>
@@ -8619,14 +9701,38 @@
       <c r="W13" s="46" t="s">
         <v>181</v>
       </c>
-      <c r="X13" s="45" t="s">
-        <v>181</v>
-      </c>
-      <c r="Y13" s="46" t="s">
-        <v>181</v>
+      <c r="X13" s="55" t="s">
+        <v>612</v>
+      </c>
+      <c r="Y13" s="56" t="s">
+        <v>596</v>
+      </c>
+      <c r="Z13" s="55" t="s">
+        <v>613</v>
+      </c>
+      <c r="AA13" s="56" t="s">
+        <v>600</v>
+      </c>
+      <c r="AB13" s="55" t="s">
+        <v>614</v>
+      </c>
+      <c r="AC13" s="56" t="s">
+        <v>603</v>
+      </c>
+      <c r="AD13" s="55" t="s">
+        <v>615</v>
+      </c>
+      <c r="AE13" s="56" t="s">
+        <v>606</v>
+      </c>
+      <c r="AF13" s="55" t="s">
+        <v>616</v>
+      </c>
+      <c r="AG13" s="56" t="s">
+        <v>609</v>
       </c>
     </row>
-    <row r="14" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:33" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="9">
         <v>14</v>
       </c>
@@ -8696,14 +9802,38 @@
       <c r="W14" s="46" t="s">
         <v>181</v>
       </c>
-      <c r="X14" s="45" t="s">
-        <v>181</v>
-      </c>
-      <c r="Y14" s="46" t="s">
-        <v>181</v>
+      <c r="X14" s="55" t="s">
+        <v>612</v>
+      </c>
+      <c r="Y14" s="56" t="s">
+        <v>596</v>
+      </c>
+      <c r="Z14" s="55" t="s">
+        <v>613</v>
+      </c>
+      <c r="AA14" s="56" t="s">
+        <v>600</v>
+      </c>
+      <c r="AB14" s="55" t="s">
+        <v>614</v>
+      </c>
+      <c r="AC14" s="56" t="s">
+        <v>603</v>
+      </c>
+      <c r="AD14" s="55" t="s">
+        <v>615</v>
+      </c>
+      <c r="AE14" s="56" t="s">
+        <v>606</v>
+      </c>
+      <c r="AF14" s="55" t="s">
+        <v>616</v>
+      </c>
+      <c r="AG14" s="56" t="s">
+        <v>609</v>
       </c>
     </row>
-    <row r="15" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:33" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="9">
         <v>15</v>
       </c>
@@ -8773,14 +9903,38 @@
       <c r="W15" s="46" t="s">
         <v>181</v>
       </c>
-      <c r="X15" s="45" t="s">
-        <v>181</v>
-      </c>
-      <c r="Y15" s="46" t="s">
-        <v>181</v>
+      <c r="X15" s="55" t="s">
+        <v>612</v>
+      </c>
+      <c r="Y15" s="56" t="s">
+        <v>596</v>
+      </c>
+      <c r="Z15" s="55" t="s">
+        <v>613</v>
+      </c>
+      <c r="AA15" s="56" t="s">
+        <v>600</v>
+      </c>
+      <c r="AB15" s="55" t="s">
+        <v>614</v>
+      </c>
+      <c r="AC15" s="56" t="s">
+        <v>603</v>
+      </c>
+      <c r="AD15" s="55" t="s">
+        <v>615</v>
+      </c>
+      <c r="AE15" s="56" t="s">
+        <v>606</v>
+      </c>
+      <c r="AF15" s="55" t="s">
+        <v>616</v>
+      </c>
+      <c r="AG15" s="56" t="s">
+        <v>609</v>
       </c>
     </row>
-    <row r="16" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:33" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="9">
         <v>16</v>
       </c>
@@ -8850,14 +10004,38 @@
       <c r="W16" s="46" t="s">
         <v>181</v>
       </c>
-      <c r="X16" s="45" t="s">
-        <v>181</v>
-      </c>
-      <c r="Y16" s="46" t="s">
-        <v>181</v>
+      <c r="X16" s="55" t="s">
+        <v>612</v>
+      </c>
+      <c r="Y16" s="56" t="s">
+        <v>596</v>
+      </c>
+      <c r="Z16" s="55" t="s">
+        <v>613</v>
+      </c>
+      <c r="AA16" s="56" t="s">
+        <v>600</v>
+      </c>
+      <c r="AB16" s="55" t="s">
+        <v>614</v>
+      </c>
+      <c r="AC16" s="56" t="s">
+        <v>603</v>
+      </c>
+      <c r="AD16" s="55" t="s">
+        <v>615</v>
+      </c>
+      <c r="AE16" s="56" t="s">
+        <v>606</v>
+      </c>
+      <c r="AF16" s="55" t="s">
+        <v>616</v>
+      </c>
+      <c r="AG16" s="56" t="s">
+        <v>609</v>
       </c>
     </row>
-    <row r="17" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:33" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="9">
         <v>17</v>
       </c>
@@ -8927,14 +10105,38 @@
       <c r="W17" s="46" t="s">
         <v>181</v>
       </c>
-      <c r="X17" s="45" t="s">
-        <v>181</v>
-      </c>
-      <c r="Y17" s="46" t="s">
-        <v>181</v>
+      <c r="X17" s="55" t="s">
+        <v>612</v>
+      </c>
+      <c r="Y17" s="56" t="s">
+        <v>596</v>
+      </c>
+      <c r="Z17" s="55" t="s">
+        <v>613</v>
+      </c>
+      <c r="AA17" s="56" t="s">
+        <v>600</v>
+      </c>
+      <c r="AB17" s="55" t="s">
+        <v>614</v>
+      </c>
+      <c r="AC17" s="56" t="s">
+        <v>603</v>
+      </c>
+      <c r="AD17" s="55" t="s">
+        <v>615</v>
+      </c>
+      <c r="AE17" s="56" t="s">
+        <v>606</v>
+      </c>
+      <c r="AF17" s="55" t="s">
+        <v>616</v>
+      </c>
+      <c r="AG17" s="56" t="s">
+        <v>609</v>
       </c>
     </row>
-    <row r="18" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:33" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="9">
         <v>18</v>
       </c>
@@ -9004,14 +10206,38 @@
       <c r="W18" s="46" t="s">
         <v>181</v>
       </c>
-      <c r="X18" s="45" t="s">
-        <v>181</v>
-      </c>
-      <c r="Y18" s="46" t="s">
-        <v>181</v>
+      <c r="X18" s="55" t="s">
+        <v>612</v>
+      </c>
+      <c r="Y18" s="56" t="s">
+        <v>596</v>
+      </c>
+      <c r="Z18" s="55" t="s">
+        <v>613</v>
+      </c>
+      <c r="AA18" s="56" t="s">
+        <v>600</v>
+      </c>
+      <c r="AB18" s="55" t="s">
+        <v>614</v>
+      </c>
+      <c r="AC18" s="56" t="s">
+        <v>603</v>
+      </c>
+      <c r="AD18" s="55" t="s">
+        <v>615</v>
+      </c>
+      <c r="AE18" s="56" t="s">
+        <v>606</v>
+      </c>
+      <c r="AF18" s="55" t="s">
+        <v>616</v>
+      </c>
+      <c r="AG18" s="56" t="s">
+        <v>609</v>
       </c>
     </row>
-    <row r="19" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:33" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="9">
         <v>19</v>
       </c>
@@ -9081,14 +10307,38 @@
       <c r="W19" s="46" t="s">
         <v>181</v>
       </c>
-      <c r="X19" s="45" t="s">
-        <v>181</v>
-      </c>
-      <c r="Y19" s="46" t="s">
-        <v>181</v>
+      <c r="X19" s="55" t="s">
+        <v>612</v>
+      </c>
+      <c r="Y19" s="56" t="s">
+        <v>596</v>
+      </c>
+      <c r="Z19" s="55" t="s">
+        <v>613</v>
+      </c>
+      <c r="AA19" s="56" t="s">
+        <v>600</v>
+      </c>
+      <c r="AB19" s="55" t="s">
+        <v>614</v>
+      </c>
+      <c r="AC19" s="56" t="s">
+        <v>603</v>
+      </c>
+      <c r="AD19" s="55" t="s">
+        <v>615</v>
+      </c>
+      <c r="AE19" s="56" t="s">
+        <v>606</v>
+      </c>
+      <c r="AF19" s="55" t="s">
+        <v>616</v>
+      </c>
+      <c r="AG19" s="56" t="s">
+        <v>609</v>
       </c>
     </row>
-    <row r="20" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:33" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="9">
         <v>20</v>
       </c>
@@ -9158,14 +10408,38 @@
       <c r="W20" s="46" t="s">
         <v>181</v>
       </c>
-      <c r="X20" s="45" t="s">
-        <v>181</v>
-      </c>
-      <c r="Y20" s="46" t="s">
-        <v>181</v>
+      <c r="X20" s="55" t="s">
+        <v>612</v>
+      </c>
+      <c r="Y20" s="56" t="s">
+        <v>596</v>
+      </c>
+      <c r="Z20" s="55" t="s">
+        <v>613</v>
+      </c>
+      <c r="AA20" s="56" t="s">
+        <v>600</v>
+      </c>
+      <c r="AB20" s="55" t="s">
+        <v>614</v>
+      </c>
+      <c r="AC20" s="56" t="s">
+        <v>603</v>
+      </c>
+      <c r="AD20" s="55" t="s">
+        <v>615</v>
+      </c>
+      <c r="AE20" s="56" t="s">
+        <v>606</v>
+      </c>
+      <c r="AF20" s="55" t="s">
+        <v>616</v>
+      </c>
+      <c r="AG20" s="56" t="s">
+        <v>609</v>
       </c>
     </row>
-    <row r="21" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:33" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="9">
         <v>21</v>
       </c>
@@ -9235,14 +10509,38 @@
       <c r="W21" s="46" t="s">
         <v>181</v>
       </c>
-      <c r="X21" s="45" t="s">
-        <v>181</v>
-      </c>
-      <c r="Y21" s="46" t="s">
-        <v>181</v>
+      <c r="X21" s="55" t="s">
+        <v>612</v>
+      </c>
+      <c r="Y21" s="56" t="s">
+        <v>596</v>
+      </c>
+      <c r="Z21" s="55" t="s">
+        <v>613</v>
+      </c>
+      <c r="AA21" s="56" t="s">
+        <v>600</v>
+      </c>
+      <c r="AB21" s="55" t="s">
+        <v>614</v>
+      </c>
+      <c r="AC21" s="56" t="s">
+        <v>603</v>
+      </c>
+      <c r="AD21" s="55" t="s">
+        <v>615</v>
+      </c>
+      <c r="AE21" s="56" t="s">
+        <v>606</v>
+      </c>
+      <c r="AF21" s="55" t="s">
+        <v>616</v>
+      </c>
+      <c r="AG21" s="56" t="s">
+        <v>609</v>
       </c>
     </row>
-    <row r="22" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:33" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="9">
         <v>22</v>
       </c>
@@ -9312,14 +10610,38 @@
       <c r="W22" s="46" t="s">
         <v>181</v>
       </c>
-      <c r="X22" s="45" t="s">
-        <v>181</v>
-      </c>
-      <c r="Y22" s="46" t="s">
-        <v>181</v>
+      <c r="X22" s="55" t="s">
+        <v>612</v>
+      </c>
+      <c r="Y22" s="56" t="s">
+        <v>596</v>
+      </c>
+      <c r="Z22" s="55" t="s">
+        <v>613</v>
+      </c>
+      <c r="AA22" s="56" t="s">
+        <v>600</v>
+      </c>
+      <c r="AB22" s="55" t="s">
+        <v>614</v>
+      </c>
+      <c r="AC22" s="56" t="s">
+        <v>603</v>
+      </c>
+      <c r="AD22" s="55" t="s">
+        <v>615</v>
+      </c>
+      <c r="AE22" s="56" t="s">
+        <v>606</v>
+      </c>
+      <c r="AF22" s="55" t="s">
+        <v>616</v>
+      </c>
+      <c r="AG22" s="56" t="s">
+        <v>609</v>
       </c>
     </row>
-    <row r="23" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:33" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="9">
         <v>23</v>
       </c>
@@ -9389,14 +10711,38 @@
       <c r="W23" s="46" t="s">
         <v>181</v>
       </c>
-      <c r="X23" s="45" t="s">
-        <v>181</v>
-      </c>
-      <c r="Y23" s="46" t="s">
-        <v>181</v>
+      <c r="X23" s="55" t="s">
+        <v>612</v>
+      </c>
+      <c r="Y23" s="56" t="s">
+        <v>596</v>
+      </c>
+      <c r="Z23" s="55" t="s">
+        <v>613</v>
+      </c>
+      <c r="AA23" s="56" t="s">
+        <v>600</v>
+      </c>
+      <c r="AB23" s="55" t="s">
+        <v>614</v>
+      </c>
+      <c r="AC23" s="56" t="s">
+        <v>603</v>
+      </c>
+      <c r="AD23" s="55" t="s">
+        <v>615</v>
+      </c>
+      <c r="AE23" s="56" t="s">
+        <v>606</v>
+      </c>
+      <c r="AF23" s="55" t="s">
+        <v>616</v>
+      </c>
+      <c r="AG23" s="56" t="s">
+        <v>609</v>
       </c>
     </row>
-    <row r="24" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:33" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="9">
         <v>24</v>
       </c>
@@ -9466,14 +10812,38 @@
       <c r="W24" s="46" t="s">
         <v>181</v>
       </c>
-      <c r="X24" s="45" t="s">
-        <v>181</v>
-      </c>
-      <c r="Y24" s="46" t="s">
-        <v>181</v>
+      <c r="X24" s="55" t="s">
+        <v>612</v>
+      </c>
+      <c r="Y24" s="56" t="s">
+        <v>596</v>
+      </c>
+      <c r="Z24" s="55" t="s">
+        <v>613</v>
+      </c>
+      <c r="AA24" s="56" t="s">
+        <v>600</v>
+      </c>
+      <c r="AB24" s="55" t="s">
+        <v>614</v>
+      </c>
+      <c r="AC24" s="56" t="s">
+        <v>603</v>
+      </c>
+      <c r="AD24" s="55" t="s">
+        <v>615</v>
+      </c>
+      <c r="AE24" s="56" t="s">
+        <v>606</v>
+      </c>
+      <c r="AF24" s="55" t="s">
+        <v>616</v>
+      </c>
+      <c r="AG24" s="56" t="s">
+        <v>609</v>
       </c>
     </row>
-    <row r="25" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:33" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="9">
         <v>25</v>
       </c>
@@ -9543,14 +10913,38 @@
       <c r="W25" s="46" t="s">
         <v>181</v>
       </c>
-      <c r="X25" s="45" t="s">
-        <v>181</v>
-      </c>
-      <c r="Y25" s="46" t="s">
-        <v>181</v>
+      <c r="X25" s="55" t="s">
+        <v>612</v>
+      </c>
+      <c r="Y25" s="56" t="s">
+        <v>596</v>
+      </c>
+      <c r="Z25" s="55" t="s">
+        <v>613</v>
+      </c>
+      <c r="AA25" s="56" t="s">
+        <v>600</v>
+      </c>
+      <c r="AB25" s="55" t="s">
+        <v>614</v>
+      </c>
+      <c r="AC25" s="56" t="s">
+        <v>603</v>
+      </c>
+      <c r="AD25" s="55" t="s">
+        <v>615</v>
+      </c>
+      <c r="AE25" s="56" t="s">
+        <v>606</v>
+      </c>
+      <c r="AF25" s="55" t="s">
+        <v>616</v>
+      </c>
+      <c r="AG25" s="56" t="s">
+        <v>609</v>
       </c>
     </row>
-    <row r="26" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:33" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A26" s="9">
         <v>26</v>
       </c>
@@ -9620,14 +11014,38 @@
       <c r="W26" s="46" t="s">
         <v>181</v>
       </c>
-      <c r="X26" s="45" t="s">
-        <v>181</v>
-      </c>
-      <c r="Y26" s="46" t="s">
-        <v>181</v>
+      <c r="X26" s="55" t="s">
+        <v>612</v>
+      </c>
+      <c r="Y26" s="56" t="s">
+        <v>596</v>
+      </c>
+      <c r="Z26" s="55" t="s">
+        <v>613</v>
+      </c>
+      <c r="AA26" s="56" t="s">
+        <v>600</v>
+      </c>
+      <c r="AB26" s="55" t="s">
+        <v>614</v>
+      </c>
+      <c r="AC26" s="56" t="s">
+        <v>603</v>
+      </c>
+      <c r="AD26" s="55" t="s">
+        <v>615</v>
+      </c>
+      <c r="AE26" s="56" t="s">
+        <v>606</v>
+      </c>
+      <c r="AF26" s="55" t="s">
+        <v>616</v>
+      </c>
+      <c r="AG26" s="56" t="s">
+        <v>609</v>
       </c>
     </row>
-    <row r="27" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:33" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A27" s="9">
         <v>27</v>
       </c>
@@ -9697,14 +11115,38 @@
       <c r="W27" s="46" t="s">
         <v>181</v>
       </c>
-      <c r="X27" s="45" t="s">
-        <v>181</v>
-      </c>
-      <c r="Y27" s="46" t="s">
-        <v>181</v>
+      <c r="X27" s="55" t="s">
+        <v>612</v>
+      </c>
+      <c r="Y27" s="56" t="s">
+        <v>596</v>
+      </c>
+      <c r="Z27" s="55" t="s">
+        <v>613</v>
+      </c>
+      <c r="AA27" s="56" t="s">
+        <v>600</v>
+      </c>
+      <c r="AB27" s="55" t="s">
+        <v>614</v>
+      </c>
+      <c r="AC27" s="56" t="s">
+        <v>603</v>
+      </c>
+      <c r="AD27" s="55" t="s">
+        <v>615</v>
+      </c>
+      <c r="AE27" s="56" t="s">
+        <v>606</v>
+      </c>
+      <c r="AF27" s="55" t="s">
+        <v>616</v>
+      </c>
+      <c r="AG27" s="56" t="s">
+        <v>609</v>
       </c>
     </row>
-    <row r="28" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:33" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A28" s="9">
         <v>28</v>
       </c>
@@ -9774,14 +11216,38 @@
       <c r="W28" s="46" t="s">
         <v>181</v>
       </c>
-      <c r="X28" s="45" t="s">
-        <v>181</v>
-      </c>
-      <c r="Y28" s="46" t="s">
-        <v>181</v>
+      <c r="X28" s="55" t="s">
+        <v>612</v>
+      </c>
+      <c r="Y28" s="56" t="s">
+        <v>596</v>
+      </c>
+      <c r="Z28" s="55" t="s">
+        <v>613</v>
+      </c>
+      <c r="AA28" s="56" t="s">
+        <v>600</v>
+      </c>
+      <c r="AB28" s="55" t="s">
+        <v>614</v>
+      </c>
+      <c r="AC28" s="56" t="s">
+        <v>603</v>
+      </c>
+      <c r="AD28" s="55" t="s">
+        <v>615</v>
+      </c>
+      <c r="AE28" s="56" t="s">
+        <v>606</v>
+      </c>
+      <c r="AF28" s="55" t="s">
+        <v>616</v>
+      </c>
+      <c r="AG28" s="56" t="s">
+        <v>609</v>
       </c>
     </row>
-    <row r="29" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:33" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A29" s="9">
         <v>29</v>
       </c>
@@ -9851,14 +11317,38 @@
       <c r="W29" s="46" t="s">
         <v>181</v>
       </c>
-      <c r="X29" s="45" t="s">
-        <v>181</v>
-      </c>
-      <c r="Y29" s="46" t="s">
-        <v>181</v>
+      <c r="X29" s="55" t="s">
+        <v>612</v>
+      </c>
+      <c r="Y29" s="56" t="s">
+        <v>596</v>
+      </c>
+      <c r="Z29" s="55" t="s">
+        <v>613</v>
+      </c>
+      <c r="AA29" s="56" t="s">
+        <v>600</v>
+      </c>
+      <c r="AB29" s="55" t="s">
+        <v>614</v>
+      </c>
+      <c r="AC29" s="56" t="s">
+        <v>603</v>
+      </c>
+      <c r="AD29" s="55" t="s">
+        <v>615</v>
+      </c>
+      <c r="AE29" s="56" t="s">
+        <v>606</v>
+      </c>
+      <c r="AF29" s="55" t="s">
+        <v>616</v>
+      </c>
+      <c r="AG29" s="56" t="s">
+        <v>609</v>
       </c>
     </row>
-    <row r="30" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:33" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A30" s="9">
         <v>30</v>
       </c>
@@ -9928,14 +11418,38 @@
       <c r="W30" s="46" t="s">
         <v>181</v>
       </c>
-      <c r="X30" s="45" t="s">
-        <v>181</v>
-      </c>
-      <c r="Y30" s="46" t="s">
-        <v>181</v>
+      <c r="X30" s="55" t="s">
+        <v>612</v>
+      </c>
+      <c r="Y30" s="56" t="s">
+        <v>596</v>
+      </c>
+      <c r="Z30" s="55" t="s">
+        <v>613</v>
+      </c>
+      <c r="AA30" s="56" t="s">
+        <v>600</v>
+      </c>
+      <c r="AB30" s="55" t="s">
+        <v>614</v>
+      </c>
+      <c r="AC30" s="56" t="s">
+        <v>603</v>
+      </c>
+      <c r="AD30" s="55" t="s">
+        <v>615</v>
+      </c>
+      <c r="AE30" s="56" t="s">
+        <v>606</v>
+      </c>
+      <c r="AF30" s="55" t="s">
+        <v>616</v>
+      </c>
+      <c r="AG30" s="56" t="s">
+        <v>609</v>
       </c>
     </row>
-    <row r="31" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:33" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A31" s="9">
         <v>31</v>
       </c>
@@ -10005,14 +11519,38 @@
       <c r="W31" s="46" t="s">
         <v>181</v>
       </c>
-      <c r="X31" s="45" t="s">
-        <v>181</v>
-      </c>
-      <c r="Y31" s="46" t="s">
-        <v>181</v>
+      <c r="X31" s="55" t="s">
+        <v>612</v>
+      </c>
+      <c r="Y31" s="56" t="s">
+        <v>596</v>
+      </c>
+      <c r="Z31" s="55" t="s">
+        <v>613</v>
+      </c>
+      <c r="AA31" s="56" t="s">
+        <v>600</v>
+      </c>
+      <c r="AB31" s="55" t="s">
+        <v>614</v>
+      </c>
+      <c r="AC31" s="56" t="s">
+        <v>603</v>
+      </c>
+      <c r="AD31" s="55" t="s">
+        <v>615</v>
+      </c>
+      <c r="AE31" s="56" t="s">
+        <v>606</v>
+      </c>
+      <c r="AF31" s="55" t="s">
+        <v>616</v>
+      </c>
+      <c r="AG31" s="56" t="s">
+        <v>609</v>
       </c>
     </row>
-    <row r="32" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:33" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A32" s="9">
         <v>32</v>
       </c>
@@ -10082,14 +11620,38 @@
       <c r="W32" s="46" t="s">
         <v>181</v>
       </c>
-      <c r="X32" s="45" t="s">
-        <v>181</v>
-      </c>
-      <c r="Y32" s="46" t="s">
-        <v>181</v>
+      <c r="X32" s="55" t="s">
+        <v>612</v>
+      </c>
+      <c r="Y32" s="56" t="s">
+        <v>596</v>
+      </c>
+      <c r="Z32" s="55" t="s">
+        <v>613</v>
+      </c>
+      <c r="AA32" s="56" t="s">
+        <v>600</v>
+      </c>
+      <c r="AB32" s="55" t="s">
+        <v>614</v>
+      </c>
+      <c r="AC32" s="56" t="s">
+        <v>603</v>
+      </c>
+      <c r="AD32" s="55" t="s">
+        <v>615</v>
+      </c>
+      <c r="AE32" s="56" t="s">
+        <v>606</v>
+      </c>
+      <c r="AF32" s="55" t="s">
+        <v>616</v>
+      </c>
+      <c r="AG32" s="56" t="s">
+        <v>609</v>
       </c>
     </row>
-    <row r="33" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="33" spans="1:33" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A33" s="9">
         <v>33</v>
       </c>
@@ -10159,14 +11721,38 @@
       <c r="W33" s="46" t="s">
         <v>181</v>
       </c>
-      <c r="X33" s="45" t="s">
-        <v>181</v>
-      </c>
-      <c r="Y33" s="46" t="s">
-        <v>181</v>
+      <c r="X33" s="55" t="s">
+        <v>612</v>
+      </c>
+      <c r="Y33" s="56" t="s">
+        <v>596</v>
+      </c>
+      <c r="Z33" s="55" t="s">
+        <v>613</v>
+      </c>
+      <c r="AA33" s="56" t="s">
+        <v>600</v>
+      </c>
+      <c r="AB33" s="55" t="s">
+        <v>614</v>
+      </c>
+      <c r="AC33" s="56" t="s">
+        <v>603</v>
+      </c>
+      <c r="AD33" s="55" t="s">
+        <v>615</v>
+      </c>
+      <c r="AE33" s="56" t="s">
+        <v>606</v>
+      </c>
+      <c r="AF33" s="55" t="s">
+        <v>616</v>
+      </c>
+      <c r="AG33" s="56" t="s">
+        <v>609</v>
       </c>
     </row>
-    <row r="34" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="34" spans="1:33" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A34" s="9">
         <v>34</v>
       </c>
@@ -10236,14 +11822,38 @@
       <c r="W34" s="46" t="s">
         <v>181</v>
       </c>
-      <c r="X34" s="45" t="s">
-        <v>181</v>
-      </c>
-      <c r="Y34" s="46" t="s">
-        <v>181</v>
+      <c r="X34" s="55" t="s">
+        <v>612</v>
+      </c>
+      <c r="Y34" s="56" t="s">
+        <v>596</v>
+      </c>
+      <c r="Z34" s="55" t="s">
+        <v>613</v>
+      </c>
+      <c r="AA34" s="56" t="s">
+        <v>600</v>
+      </c>
+      <c r="AB34" s="55" t="s">
+        <v>614</v>
+      </c>
+      <c r="AC34" s="56" t="s">
+        <v>603</v>
+      </c>
+      <c r="AD34" s="55" t="s">
+        <v>615</v>
+      </c>
+      <c r="AE34" s="56" t="s">
+        <v>606</v>
+      </c>
+      <c r="AF34" s="55" t="s">
+        <v>616</v>
+      </c>
+      <c r="AG34" s="56" t="s">
+        <v>609</v>
       </c>
     </row>
-    <row r="35" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="35" spans="1:33" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A35" s="9">
         <v>35</v>
       </c>
@@ -10313,14 +11923,38 @@
       <c r="W35" s="46" t="s">
         <v>181</v>
       </c>
-      <c r="X35" s="45" t="s">
-        <v>181</v>
-      </c>
-      <c r="Y35" s="46" t="s">
-        <v>181</v>
+      <c r="X35" s="55" t="s">
+        <v>612</v>
+      </c>
+      <c r="Y35" s="56" t="s">
+        <v>596</v>
+      </c>
+      <c r="Z35" s="55" t="s">
+        <v>613</v>
+      </c>
+      <c r="AA35" s="56" t="s">
+        <v>600</v>
+      </c>
+      <c r="AB35" s="55" t="s">
+        <v>614</v>
+      </c>
+      <c r="AC35" s="56" t="s">
+        <v>603</v>
+      </c>
+      <c r="AD35" s="55" t="s">
+        <v>615</v>
+      </c>
+      <c r="AE35" s="56" t="s">
+        <v>606</v>
+      </c>
+      <c r="AF35" s="55" t="s">
+        <v>616</v>
+      </c>
+      <c r="AG35" s="56" t="s">
+        <v>609</v>
       </c>
     </row>
-    <row r="36" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="36" spans="1:33" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A36" s="9">
         <v>36</v>
       </c>
@@ -10390,14 +12024,38 @@
       <c r="W36" s="46" t="s">
         <v>181</v>
       </c>
-      <c r="X36" s="45" t="s">
-        <v>181</v>
-      </c>
-      <c r="Y36" s="46" t="s">
-        <v>181</v>
+      <c r="X36" s="55" t="s">
+        <v>612</v>
+      </c>
+      <c r="Y36" s="56" t="s">
+        <v>596</v>
+      </c>
+      <c r="Z36" s="55" t="s">
+        <v>613</v>
+      </c>
+      <c r="AA36" s="56" t="s">
+        <v>600</v>
+      </c>
+      <c r="AB36" s="55" t="s">
+        <v>614</v>
+      </c>
+      <c r="AC36" s="56" t="s">
+        <v>603</v>
+      </c>
+      <c r="AD36" s="55" t="s">
+        <v>615</v>
+      </c>
+      <c r="AE36" s="56" t="s">
+        <v>606</v>
+      </c>
+      <c r="AF36" s="55" t="s">
+        <v>616</v>
+      </c>
+      <c r="AG36" s="56" t="s">
+        <v>609</v>
       </c>
     </row>
-    <row r="37" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="37" spans="1:33" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A37" s="9">
         <v>37</v>
       </c>
@@ -10467,14 +12125,38 @@
       <c r="W37" s="46" t="s">
         <v>181</v>
       </c>
-      <c r="X37" s="45" t="s">
-        <v>181</v>
-      </c>
-      <c r="Y37" s="46" t="s">
-        <v>181</v>
+      <c r="X37" s="55" t="s">
+        <v>612</v>
+      </c>
+      <c r="Y37" s="56" t="s">
+        <v>596</v>
+      </c>
+      <c r="Z37" s="55" t="s">
+        <v>613</v>
+      </c>
+      <c r="AA37" s="56" t="s">
+        <v>600</v>
+      </c>
+      <c r="AB37" s="55" t="s">
+        <v>614</v>
+      </c>
+      <c r="AC37" s="56" t="s">
+        <v>603</v>
+      </c>
+      <c r="AD37" s="55" t="s">
+        <v>615</v>
+      </c>
+      <c r="AE37" s="56" t="s">
+        <v>606</v>
+      </c>
+      <c r="AF37" s="55" t="s">
+        <v>616</v>
+      </c>
+      <c r="AG37" s="56" t="s">
+        <v>609</v>
       </c>
     </row>
-    <row r="38" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="38" spans="1:33" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A38" s="9">
         <v>38</v>
       </c>
@@ -10544,14 +12226,38 @@
       <c r="W38" s="46" t="s">
         <v>181</v>
       </c>
-      <c r="X38" s="45" t="s">
-        <v>181</v>
-      </c>
-      <c r="Y38" s="46" t="s">
-        <v>181</v>
+      <c r="X38" s="55" t="s">
+        <v>612</v>
+      </c>
+      <c r="Y38" s="56" t="s">
+        <v>596</v>
+      </c>
+      <c r="Z38" s="55" t="s">
+        <v>613</v>
+      </c>
+      <c r="AA38" s="56" t="s">
+        <v>600</v>
+      </c>
+      <c r="AB38" s="55" t="s">
+        <v>614</v>
+      </c>
+      <c r="AC38" s="56" t="s">
+        <v>603</v>
+      </c>
+      <c r="AD38" s="55" t="s">
+        <v>615</v>
+      </c>
+      <c r="AE38" s="56" t="s">
+        <v>606</v>
+      </c>
+      <c r="AF38" s="55" t="s">
+        <v>616</v>
+      </c>
+      <c r="AG38" s="56" t="s">
+        <v>609</v>
       </c>
     </row>
-    <row r="39" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="39" spans="1:33" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A39" s="9">
         <v>39</v>
       </c>
@@ -10621,14 +12327,38 @@
       <c r="W39" s="46" t="s">
         <v>181</v>
       </c>
-      <c r="X39" s="45" t="s">
-        <v>181</v>
-      </c>
-      <c r="Y39" s="46" t="s">
-        <v>181</v>
+      <c r="X39" s="55" t="s">
+        <v>612</v>
+      </c>
+      <c r="Y39" s="56" t="s">
+        <v>596</v>
+      </c>
+      <c r="Z39" s="55" t="s">
+        <v>613</v>
+      </c>
+      <c r="AA39" s="56" t="s">
+        <v>600</v>
+      </c>
+      <c r="AB39" s="55" t="s">
+        <v>614</v>
+      </c>
+      <c r="AC39" s="56" t="s">
+        <v>603</v>
+      </c>
+      <c r="AD39" s="55" t="s">
+        <v>615</v>
+      </c>
+      <c r="AE39" s="56" t="s">
+        <v>606</v>
+      </c>
+      <c r="AF39" s="55" t="s">
+        <v>616</v>
+      </c>
+      <c r="AG39" s="56" t="s">
+        <v>609</v>
       </c>
     </row>
-    <row r="40" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="40" spans="1:33" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A40" s="9">
         <v>40</v>
       </c>
@@ -10698,14 +12428,38 @@
       <c r="W40" s="46" t="s">
         <v>181</v>
       </c>
-      <c r="X40" s="45" t="s">
-        <v>181</v>
-      </c>
-      <c r="Y40" s="46" t="s">
-        <v>181</v>
+      <c r="X40" s="55" t="s">
+        <v>612</v>
+      </c>
+      <c r="Y40" s="56" t="s">
+        <v>596</v>
+      </c>
+      <c r="Z40" s="55" t="s">
+        <v>613</v>
+      </c>
+      <c r="AA40" s="56" t="s">
+        <v>600</v>
+      </c>
+      <c r="AB40" s="55" t="s">
+        <v>614</v>
+      </c>
+      <c r="AC40" s="56" t="s">
+        <v>603</v>
+      </c>
+      <c r="AD40" s="55" t="s">
+        <v>615</v>
+      </c>
+      <c r="AE40" s="56" t="s">
+        <v>606</v>
+      </c>
+      <c r="AF40" s="55" t="s">
+        <v>616</v>
+      </c>
+      <c r="AG40" s="56" t="s">
+        <v>609</v>
       </c>
     </row>
-    <row r="41" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="41" spans="1:33" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A41" s="9">
         <v>41</v>
       </c>
@@ -10775,14 +12529,38 @@
       <c r="W41" s="46" t="s">
         <v>181</v>
       </c>
-      <c r="X41" s="45" t="s">
-        <v>181</v>
-      </c>
-      <c r="Y41" s="46" t="s">
-        <v>181</v>
+      <c r="X41" s="55" t="s">
+        <v>612</v>
+      </c>
+      <c r="Y41" s="56" t="s">
+        <v>596</v>
+      </c>
+      <c r="Z41" s="55" t="s">
+        <v>613</v>
+      </c>
+      <c r="AA41" s="56" t="s">
+        <v>600</v>
+      </c>
+      <c r="AB41" s="55" t="s">
+        <v>614</v>
+      </c>
+      <c r="AC41" s="56" t="s">
+        <v>603</v>
+      </c>
+      <c r="AD41" s="55" t="s">
+        <v>615</v>
+      </c>
+      <c r="AE41" s="56" t="s">
+        <v>606</v>
+      </c>
+      <c r="AF41" s="55" t="s">
+        <v>616</v>
+      </c>
+      <c r="AG41" s="56" t="s">
+        <v>609</v>
       </c>
     </row>
-    <row r="42" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="42" spans="1:33" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A42" s="9">
         <v>42</v>
       </c>
@@ -10852,14 +12630,38 @@
       <c r="W42" s="46" t="s">
         <v>181</v>
       </c>
-      <c r="X42" s="45" t="s">
-        <v>181</v>
-      </c>
-      <c r="Y42" s="46" t="s">
-        <v>181</v>
+      <c r="X42" s="55" t="s">
+        <v>612</v>
+      </c>
+      <c r="Y42" s="56" t="s">
+        <v>596</v>
+      </c>
+      <c r="Z42" s="55" t="s">
+        <v>613</v>
+      </c>
+      <c r="AA42" s="56" t="s">
+        <v>600</v>
+      </c>
+      <c r="AB42" s="55" t="s">
+        <v>614</v>
+      </c>
+      <c r="AC42" s="56" t="s">
+        <v>603</v>
+      </c>
+      <c r="AD42" s="55" t="s">
+        <v>615</v>
+      </c>
+      <c r="AE42" s="56" t="s">
+        <v>606</v>
+      </c>
+      <c r="AF42" s="55" t="s">
+        <v>616</v>
+      </c>
+      <c r="AG42" s="56" t="s">
+        <v>609</v>
       </c>
     </row>
-    <row r="43" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="43" spans="1:33" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A43" s="9">
         <v>43</v>
       </c>
@@ -10929,14 +12731,38 @@
       <c r="W43" s="46" t="s">
         <v>181</v>
       </c>
-      <c r="X43" s="45" t="s">
-        <v>181</v>
-      </c>
-      <c r="Y43" s="46" t="s">
-        <v>181</v>
+      <c r="X43" s="55" t="s">
+        <v>612</v>
+      </c>
+      <c r="Y43" s="56" t="s">
+        <v>596</v>
+      </c>
+      <c r="Z43" s="55" t="s">
+        <v>613</v>
+      </c>
+      <c r="AA43" s="56" t="s">
+        <v>600</v>
+      </c>
+      <c r="AB43" s="55" t="s">
+        <v>614</v>
+      </c>
+      <c r="AC43" s="56" t="s">
+        <v>603</v>
+      </c>
+      <c r="AD43" s="55" t="s">
+        <v>615</v>
+      </c>
+      <c r="AE43" s="56" t="s">
+        <v>606</v>
+      </c>
+      <c r="AF43" s="55" t="s">
+        <v>616</v>
+      </c>
+      <c r="AG43" s="56" t="s">
+        <v>609</v>
       </c>
     </row>
-    <row r="44" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="44" spans="1:33" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A44" s="9">
         <v>44</v>
       </c>
@@ -11006,14 +12832,38 @@
       <c r="W44" s="46" t="s">
         <v>181</v>
       </c>
-      <c r="X44" s="45" t="s">
-        <v>181</v>
-      </c>
-      <c r="Y44" s="46" t="s">
-        <v>181</v>
+      <c r="X44" s="55" t="s">
+        <v>612</v>
+      </c>
+      <c r="Y44" s="56" t="s">
+        <v>596</v>
+      </c>
+      <c r="Z44" s="55" t="s">
+        <v>613</v>
+      </c>
+      <c r="AA44" s="56" t="s">
+        <v>600</v>
+      </c>
+      <c r="AB44" s="55" t="s">
+        <v>614</v>
+      </c>
+      <c r="AC44" s="56" t="s">
+        <v>603</v>
+      </c>
+      <c r="AD44" s="55" t="s">
+        <v>615</v>
+      </c>
+      <c r="AE44" s="56" t="s">
+        <v>606</v>
+      </c>
+      <c r="AF44" s="55" t="s">
+        <v>616</v>
+      </c>
+      <c r="AG44" s="56" t="s">
+        <v>609</v>
       </c>
     </row>
-    <row r="45" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="45" spans="1:33" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A45" s="9">
         <v>45</v>
       </c>
@@ -11083,14 +12933,38 @@
       <c r="W45" s="46" t="s">
         <v>181</v>
       </c>
-      <c r="X45" s="45" t="s">
-        <v>181</v>
-      </c>
-      <c r="Y45" s="46" t="s">
-        <v>181</v>
+      <c r="X45" s="55" t="s">
+        <v>612</v>
+      </c>
+      <c r="Y45" s="56" t="s">
+        <v>596</v>
+      </c>
+      <c r="Z45" s="55" t="s">
+        <v>613</v>
+      </c>
+      <c r="AA45" s="56" t="s">
+        <v>600</v>
+      </c>
+      <c r="AB45" s="55" t="s">
+        <v>614</v>
+      </c>
+      <c r="AC45" s="56" t="s">
+        <v>603</v>
+      </c>
+      <c r="AD45" s="55" t="s">
+        <v>615</v>
+      </c>
+      <c r="AE45" s="56" t="s">
+        <v>606</v>
+      </c>
+      <c r="AF45" s="55" t="s">
+        <v>616</v>
+      </c>
+      <c r="AG45" s="56" t="s">
+        <v>609</v>
       </c>
     </row>
-    <row r="46" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="46" spans="1:33" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A46" s="9">
         <v>46</v>
       </c>
@@ -11160,14 +13034,38 @@
       <c r="W46" s="46" t="s">
         <v>181</v>
       </c>
-      <c r="X46" s="45" t="s">
-        <v>181</v>
-      </c>
-      <c r="Y46" s="46" t="s">
-        <v>181</v>
+      <c r="X46" s="55" t="s">
+        <v>612</v>
+      </c>
+      <c r="Y46" s="56" t="s">
+        <v>596</v>
+      </c>
+      <c r="Z46" s="55" t="s">
+        <v>613</v>
+      </c>
+      <c r="AA46" s="56" t="s">
+        <v>600</v>
+      </c>
+      <c r="AB46" s="55" t="s">
+        <v>614</v>
+      </c>
+      <c r="AC46" s="56" t="s">
+        <v>603</v>
+      </c>
+      <c r="AD46" s="55" t="s">
+        <v>615</v>
+      </c>
+      <c r="AE46" s="56" t="s">
+        <v>606</v>
+      </c>
+      <c r="AF46" s="55" t="s">
+        <v>616</v>
+      </c>
+      <c r="AG46" s="56" t="s">
+        <v>609</v>
       </c>
     </row>
-    <row r="47" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="47" spans="1:33" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A47" s="9">
         <v>47</v>
       </c>
@@ -11237,14 +13135,38 @@
       <c r="W47" s="46" t="s">
         <v>181</v>
       </c>
-      <c r="X47" s="45" t="s">
-        <v>181</v>
-      </c>
-      <c r="Y47" s="46" t="s">
-        <v>181</v>
+      <c r="X47" s="55" t="s">
+        <v>612</v>
+      </c>
+      <c r="Y47" s="56" t="s">
+        <v>596</v>
+      </c>
+      <c r="Z47" s="55" t="s">
+        <v>613</v>
+      </c>
+      <c r="AA47" s="56" t="s">
+        <v>600</v>
+      </c>
+      <c r="AB47" s="55" t="s">
+        <v>614</v>
+      </c>
+      <c r="AC47" s="56" t="s">
+        <v>603</v>
+      </c>
+      <c r="AD47" s="55" t="s">
+        <v>615</v>
+      </c>
+      <c r="AE47" s="56" t="s">
+        <v>606</v>
+      </c>
+      <c r="AF47" s="55" t="s">
+        <v>616</v>
+      </c>
+      <c r="AG47" s="56" t="s">
+        <v>609</v>
       </c>
     </row>
-    <row r="48" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="48" spans="1:33" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A48" s="9">
         <v>48</v>
       </c>
@@ -11314,14 +13236,38 @@
       <c r="W48" s="46" t="s">
         <v>181</v>
       </c>
-      <c r="X48" s="45" t="s">
-        <v>181</v>
-      </c>
-      <c r="Y48" s="46" t="s">
-        <v>181</v>
+      <c r="X48" s="55" t="s">
+        <v>612</v>
+      </c>
+      <c r="Y48" s="56" t="s">
+        <v>596</v>
+      </c>
+      <c r="Z48" s="55" t="s">
+        <v>613</v>
+      </c>
+      <c r="AA48" s="56" t="s">
+        <v>600</v>
+      </c>
+      <c r="AB48" s="55" t="s">
+        <v>614</v>
+      </c>
+      <c r="AC48" s="56" t="s">
+        <v>603</v>
+      </c>
+      <c r="AD48" s="55" t="s">
+        <v>615</v>
+      </c>
+      <c r="AE48" s="56" t="s">
+        <v>606</v>
+      </c>
+      <c r="AF48" s="55" t="s">
+        <v>616</v>
+      </c>
+      <c r="AG48" s="56" t="s">
+        <v>609</v>
       </c>
     </row>
-    <row r="49" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="49" spans="1:33" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A49" s="9">
         <v>49</v>
       </c>
@@ -11391,14 +13337,38 @@
       <c r="W49" s="46" t="s">
         <v>181</v>
       </c>
-      <c r="X49" s="45" t="s">
-        <v>181</v>
-      </c>
-      <c r="Y49" s="46" t="s">
-        <v>181</v>
+      <c r="X49" s="55" t="s">
+        <v>612</v>
+      </c>
+      <c r="Y49" s="56" t="s">
+        <v>596</v>
+      </c>
+      <c r="Z49" s="55" t="s">
+        <v>613</v>
+      </c>
+      <c r="AA49" s="56" t="s">
+        <v>600</v>
+      </c>
+      <c r="AB49" s="55" t="s">
+        <v>614</v>
+      </c>
+      <c r="AC49" s="56" t="s">
+        <v>603</v>
+      </c>
+      <c r="AD49" s="55" t="s">
+        <v>615</v>
+      </c>
+      <c r="AE49" s="56" t="s">
+        <v>606</v>
+      </c>
+      <c r="AF49" s="55" t="s">
+        <v>616</v>
+      </c>
+      <c r="AG49" s="56" t="s">
+        <v>609</v>
       </c>
     </row>
-    <row r="50" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="50" spans="1:33" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A50" s="9">
         <v>50</v>
       </c>
@@ -11468,14 +13438,38 @@
       <c r="W50" s="46" t="s">
         <v>181</v>
       </c>
-      <c r="X50" s="45" t="s">
-        <v>181</v>
-      </c>
-      <c r="Y50" s="46" t="s">
-        <v>181</v>
+      <c r="X50" s="55" t="s">
+        <v>612</v>
+      </c>
+      <c r="Y50" s="56" t="s">
+        <v>596</v>
+      </c>
+      <c r="Z50" s="55" t="s">
+        <v>613</v>
+      </c>
+      <c r="AA50" s="56" t="s">
+        <v>600</v>
+      </c>
+      <c r="AB50" s="55" t="s">
+        <v>614</v>
+      </c>
+      <c r="AC50" s="56" t="s">
+        <v>603</v>
+      </c>
+      <c r="AD50" s="55" t="s">
+        <v>615</v>
+      </c>
+      <c r="AE50" s="56" t="s">
+        <v>606</v>
+      </c>
+      <c r="AF50" s="55" t="s">
+        <v>616</v>
+      </c>
+      <c r="AG50" s="56" t="s">
+        <v>609</v>
       </c>
     </row>
-    <row r="51" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="51" spans="1:33" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A51" s="9">
         <v>51</v>
       </c>
@@ -11545,14 +13539,38 @@
       <c r="W51" s="46" t="s">
         <v>181</v>
       </c>
-      <c r="X51" s="45" t="s">
-        <v>181</v>
-      </c>
-      <c r="Y51" s="46" t="s">
-        <v>181</v>
+      <c r="X51" s="55" t="s">
+        <v>612</v>
+      </c>
+      <c r="Y51" s="56" t="s">
+        <v>596</v>
+      </c>
+      <c r="Z51" s="55" t="s">
+        <v>613</v>
+      </c>
+      <c r="AA51" s="56" t="s">
+        <v>600</v>
+      </c>
+      <c r="AB51" s="55" t="s">
+        <v>614</v>
+      </c>
+      <c r="AC51" s="56" t="s">
+        <v>603</v>
+      </c>
+      <c r="AD51" s="55" t="s">
+        <v>615</v>
+      </c>
+      <c r="AE51" s="56" t="s">
+        <v>606</v>
+      </c>
+      <c r="AF51" s="55" t="s">
+        <v>616</v>
+      </c>
+      <c r="AG51" s="56" t="s">
+        <v>609</v>
       </c>
     </row>
-    <row r="52" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="52" spans="1:33" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A52" s="9">
         <v>52</v>
       </c>
@@ -11622,14 +13640,38 @@
       <c r="W52" s="46" t="s">
         <v>181</v>
       </c>
-      <c r="X52" s="45" t="s">
-        <v>181</v>
-      </c>
-      <c r="Y52" s="46" t="s">
-        <v>181</v>
+      <c r="X52" s="55" t="s">
+        <v>612</v>
+      </c>
+      <c r="Y52" s="56" t="s">
+        <v>596</v>
+      </c>
+      <c r="Z52" s="55" t="s">
+        <v>613</v>
+      </c>
+      <c r="AA52" s="56" t="s">
+        <v>600</v>
+      </c>
+      <c r="AB52" s="55" t="s">
+        <v>614</v>
+      </c>
+      <c r="AC52" s="56" t="s">
+        <v>603</v>
+      </c>
+      <c r="AD52" s="55" t="s">
+        <v>615</v>
+      </c>
+      <c r="AE52" s="56" t="s">
+        <v>606</v>
+      </c>
+      <c r="AF52" s="55" t="s">
+        <v>616</v>
+      </c>
+      <c r="AG52" s="56" t="s">
+        <v>609</v>
       </c>
     </row>
-    <row r="53" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="53" spans="1:33" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A53" s="9">
         <v>53</v>
       </c>
@@ -11699,14 +13741,38 @@
       <c r="W53" s="46" t="s">
         <v>181</v>
       </c>
-      <c r="X53" s="45" t="s">
-        <v>181</v>
-      </c>
-      <c r="Y53" s="46" t="s">
-        <v>181</v>
+      <c r="X53" s="55" t="s">
+        <v>612</v>
+      </c>
+      <c r="Y53" s="56" t="s">
+        <v>596</v>
+      </c>
+      <c r="Z53" s="55" t="s">
+        <v>613</v>
+      </c>
+      <c r="AA53" s="56" t="s">
+        <v>600</v>
+      </c>
+      <c r="AB53" s="55" t="s">
+        <v>614</v>
+      </c>
+      <c r="AC53" s="56" t="s">
+        <v>603</v>
+      </c>
+      <c r="AD53" s="55" t="s">
+        <v>615</v>
+      </c>
+      <c r="AE53" s="56" t="s">
+        <v>606</v>
+      </c>
+      <c r="AF53" s="55" t="s">
+        <v>616</v>
+      </c>
+      <c r="AG53" s="56" t="s">
+        <v>609</v>
       </c>
     </row>
-    <row r="54" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="54" spans="1:33" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A54" s="9">
         <v>54</v>
       </c>
@@ -11776,14 +13842,38 @@
       <c r="W54" s="46" t="s">
         <v>181</v>
       </c>
-      <c r="X54" s="45" t="s">
-        <v>181</v>
-      </c>
-      <c r="Y54" s="46" t="s">
-        <v>181</v>
+      <c r="X54" s="55" t="s">
+        <v>612</v>
+      </c>
+      <c r="Y54" s="56" t="s">
+        <v>596</v>
+      </c>
+      <c r="Z54" s="55" t="s">
+        <v>613</v>
+      </c>
+      <c r="AA54" s="56" t="s">
+        <v>600</v>
+      </c>
+      <c r="AB54" s="55" t="s">
+        <v>614</v>
+      </c>
+      <c r="AC54" s="56" t="s">
+        <v>603</v>
+      </c>
+      <c r="AD54" s="55" t="s">
+        <v>615</v>
+      </c>
+      <c r="AE54" s="56" t="s">
+        <v>606</v>
+      </c>
+      <c r="AF54" s="55" t="s">
+        <v>616</v>
+      </c>
+      <c r="AG54" s="56" t="s">
+        <v>609</v>
       </c>
     </row>
-    <row r="55" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="55" spans="1:33" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A55" s="9">
         <v>55</v>
       </c>
@@ -11853,14 +13943,38 @@
       <c r="W55" s="46" t="s">
         <v>181</v>
       </c>
-      <c r="X55" s="45" t="s">
-        <v>181</v>
-      </c>
-      <c r="Y55" s="46" t="s">
-        <v>181</v>
+      <c r="X55" s="55" t="s">
+        <v>612</v>
+      </c>
+      <c r="Y55" s="56" t="s">
+        <v>596</v>
+      </c>
+      <c r="Z55" s="55" t="s">
+        <v>613</v>
+      </c>
+      <c r="AA55" s="56" t="s">
+        <v>600</v>
+      </c>
+      <c r="AB55" s="55" t="s">
+        <v>614</v>
+      </c>
+      <c r="AC55" s="56" t="s">
+        <v>603</v>
+      </c>
+      <c r="AD55" s="55" t="s">
+        <v>615</v>
+      </c>
+      <c r="AE55" s="56" t="s">
+        <v>606</v>
+      </c>
+      <c r="AF55" s="55" t="s">
+        <v>616</v>
+      </c>
+      <c r="AG55" s="56" t="s">
+        <v>609</v>
       </c>
     </row>
-    <row r="56" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="56" spans="1:33" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A56" s="9">
         <v>56</v>
       </c>
@@ -11930,14 +14044,38 @@
       <c r="W56" s="46" t="s">
         <v>181</v>
       </c>
-      <c r="X56" s="45" t="s">
-        <v>181</v>
-      </c>
-      <c r="Y56" s="46" t="s">
-        <v>181</v>
+      <c r="X56" s="55" t="s">
+        <v>612</v>
+      </c>
+      <c r="Y56" s="56" t="s">
+        <v>596</v>
+      </c>
+      <c r="Z56" s="55" t="s">
+        <v>613</v>
+      </c>
+      <c r="AA56" s="56" t="s">
+        <v>600</v>
+      </c>
+      <c r="AB56" s="55" t="s">
+        <v>614</v>
+      </c>
+      <c r="AC56" s="56" t="s">
+        <v>603</v>
+      </c>
+      <c r="AD56" s="55" t="s">
+        <v>615</v>
+      </c>
+      <c r="AE56" s="56" t="s">
+        <v>606</v>
+      </c>
+      <c r="AF56" s="55" t="s">
+        <v>616</v>
+      </c>
+      <c r="AG56" s="56" t="s">
+        <v>609</v>
       </c>
     </row>
-    <row r="57" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="57" spans="1:33" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A57" s="9">
         <v>57</v>
       </c>
@@ -12007,14 +14145,38 @@
       <c r="W57" s="46" t="s">
         <v>181</v>
       </c>
-      <c r="X57" s="45" t="s">
-        <v>181</v>
-      </c>
-      <c r="Y57" s="46" t="s">
-        <v>181</v>
+      <c r="X57" s="55" t="s">
+        <v>612</v>
+      </c>
+      <c r="Y57" s="56" t="s">
+        <v>596</v>
+      </c>
+      <c r="Z57" s="55" t="s">
+        <v>613</v>
+      </c>
+      <c r="AA57" s="56" t="s">
+        <v>600</v>
+      </c>
+      <c r="AB57" s="55" t="s">
+        <v>614</v>
+      </c>
+      <c r="AC57" s="56" t="s">
+        <v>603</v>
+      </c>
+      <c r="AD57" s="55" t="s">
+        <v>615</v>
+      </c>
+      <c r="AE57" s="56" t="s">
+        <v>606</v>
+      </c>
+      <c r="AF57" s="55" t="s">
+        <v>616</v>
+      </c>
+      <c r="AG57" s="56" t="s">
+        <v>609</v>
       </c>
     </row>
-    <row r="58" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="58" spans="1:33" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A58" s="9">
         <v>58</v>
       </c>
@@ -12084,14 +14246,38 @@
       <c r="W58" s="46" t="s">
         <v>181</v>
       </c>
-      <c r="X58" s="45" t="s">
-        <v>181</v>
-      </c>
-      <c r="Y58" s="46" t="s">
-        <v>181</v>
+      <c r="X58" s="55" t="s">
+        <v>612</v>
+      </c>
+      <c r="Y58" s="56" t="s">
+        <v>596</v>
+      </c>
+      <c r="Z58" s="55" t="s">
+        <v>613</v>
+      </c>
+      <c r="AA58" s="56" t="s">
+        <v>600</v>
+      </c>
+      <c r="AB58" s="55" t="s">
+        <v>614</v>
+      </c>
+      <c r="AC58" s="56" t="s">
+        <v>603</v>
+      </c>
+      <c r="AD58" s="55" t="s">
+        <v>615</v>
+      </c>
+      <c r="AE58" s="56" t="s">
+        <v>606</v>
+      </c>
+      <c r="AF58" s="55" t="s">
+        <v>616</v>
+      </c>
+      <c r="AG58" s="56" t="s">
+        <v>609</v>
       </c>
     </row>
-    <row r="59" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="59" spans="1:33" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A59" s="9">
         <v>59</v>
       </c>
@@ -12161,14 +14347,38 @@
       <c r="W59" s="46" t="s">
         <v>181</v>
       </c>
-      <c r="X59" s="45" t="s">
-        <v>181</v>
-      </c>
-      <c r="Y59" s="46" t="s">
-        <v>181</v>
+      <c r="X59" s="55" t="s">
+        <v>612</v>
+      </c>
+      <c r="Y59" s="56" t="s">
+        <v>596</v>
+      </c>
+      <c r="Z59" s="55" t="s">
+        <v>613</v>
+      </c>
+      <c r="AA59" s="56" t="s">
+        <v>600</v>
+      </c>
+      <c r="AB59" s="55" t="s">
+        <v>614</v>
+      </c>
+      <c r="AC59" s="56" t="s">
+        <v>603</v>
+      </c>
+      <c r="AD59" s="55" t="s">
+        <v>615</v>
+      </c>
+      <c r="AE59" s="56" t="s">
+        <v>606</v>
+      </c>
+      <c r="AF59" s="55" t="s">
+        <v>616</v>
+      </c>
+      <c r="AG59" s="56" t="s">
+        <v>609</v>
       </c>
     </row>
-    <row r="60" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="60" spans="1:33" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A60" s="9">
         <v>60</v>
       </c>
@@ -12238,14 +14448,38 @@
       <c r="W60" s="46" t="s">
         <v>181</v>
       </c>
-      <c r="X60" s="45" t="s">
-        <v>181</v>
-      </c>
-      <c r="Y60" s="46" t="s">
-        <v>181</v>
+      <c r="X60" s="55" t="s">
+        <v>612</v>
+      </c>
+      <c r="Y60" s="56" t="s">
+        <v>596</v>
+      </c>
+      <c r="Z60" s="55" t="s">
+        <v>613</v>
+      </c>
+      <c r="AA60" s="56" t="s">
+        <v>600</v>
+      </c>
+      <c r="AB60" s="55" t="s">
+        <v>614</v>
+      </c>
+      <c r="AC60" s="56" t="s">
+        <v>603</v>
+      </c>
+      <c r="AD60" s="55" t="s">
+        <v>615</v>
+      </c>
+      <c r="AE60" s="56" t="s">
+        <v>606</v>
+      </c>
+      <c r="AF60" s="55" t="s">
+        <v>616</v>
+      </c>
+      <c r="AG60" s="56" t="s">
+        <v>609</v>
       </c>
     </row>
-    <row r="61" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="61" spans="1:33" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A61" s="9">
         <v>61</v>
       </c>
@@ -12315,14 +14549,38 @@
       <c r="W61" s="46" t="s">
         <v>181</v>
       </c>
-      <c r="X61" s="45" t="s">
-        <v>181</v>
-      </c>
-      <c r="Y61" s="46" t="s">
-        <v>181</v>
+      <c r="X61" s="55" t="s">
+        <v>612</v>
+      </c>
+      <c r="Y61" s="56" t="s">
+        <v>596</v>
+      </c>
+      <c r="Z61" s="55" t="s">
+        <v>613</v>
+      </c>
+      <c r="AA61" s="56" t="s">
+        <v>600</v>
+      </c>
+      <c r="AB61" s="55" t="s">
+        <v>614</v>
+      </c>
+      <c r="AC61" s="56" t="s">
+        <v>603</v>
+      </c>
+      <c r="AD61" s="55" t="s">
+        <v>615</v>
+      </c>
+      <c r="AE61" s="56" t="s">
+        <v>606</v>
+      </c>
+      <c r="AF61" s="55" t="s">
+        <v>616</v>
+      </c>
+      <c r="AG61" s="56" t="s">
+        <v>609</v>
       </c>
     </row>
-    <row r="62" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="62" spans="1:33" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A62" s="9">
         <v>62</v>
       </c>
@@ -12392,14 +14650,38 @@
       <c r="W62" s="46" t="s">
         <v>181</v>
       </c>
-      <c r="X62" s="45" t="s">
-        <v>181</v>
-      </c>
-      <c r="Y62" s="46" t="s">
-        <v>181</v>
+      <c r="X62" s="55" t="s">
+        <v>612</v>
+      </c>
+      <c r="Y62" s="56" t="s">
+        <v>596</v>
+      </c>
+      <c r="Z62" s="55" t="s">
+        <v>613</v>
+      </c>
+      <c r="AA62" s="56" t="s">
+        <v>600</v>
+      </c>
+      <c r="AB62" s="55" t="s">
+        <v>614</v>
+      </c>
+      <c r="AC62" s="56" t="s">
+        <v>603</v>
+      </c>
+      <c r="AD62" s="55" t="s">
+        <v>615</v>
+      </c>
+      <c r="AE62" s="56" t="s">
+        <v>606</v>
+      </c>
+      <c r="AF62" s="55" t="s">
+        <v>616</v>
+      </c>
+      <c r="AG62" s="56" t="s">
+        <v>609</v>
       </c>
     </row>
-    <row r="63" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="63" spans="1:33" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A63" s="9">
         <v>63</v>
       </c>
@@ -12469,14 +14751,38 @@
       <c r="W63" s="46" t="s">
         <v>181</v>
       </c>
-      <c r="X63" s="45" t="s">
-        <v>181</v>
-      </c>
-      <c r="Y63" s="46" t="s">
-        <v>181</v>
+      <c r="X63" s="55" t="s">
+        <v>612</v>
+      </c>
+      <c r="Y63" s="56" t="s">
+        <v>596</v>
+      </c>
+      <c r="Z63" s="55" t="s">
+        <v>613</v>
+      </c>
+      <c r="AA63" s="56" t="s">
+        <v>600</v>
+      </c>
+      <c r="AB63" s="55" t="s">
+        <v>614</v>
+      </c>
+      <c r="AC63" s="56" t="s">
+        <v>603</v>
+      </c>
+      <c r="AD63" s="55" t="s">
+        <v>615</v>
+      </c>
+      <c r="AE63" s="56" t="s">
+        <v>606</v>
+      </c>
+      <c r="AF63" s="55" t="s">
+        <v>616</v>
+      </c>
+      <c r="AG63" s="56" t="s">
+        <v>609</v>
       </c>
     </row>
-    <row r="64" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="64" spans="1:33" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A64" s="9">
         <v>64</v>
       </c>
@@ -12546,14 +14852,38 @@
       <c r="W64" s="46" t="s">
         <v>181</v>
       </c>
-      <c r="X64" s="45" t="s">
-        <v>181</v>
-      </c>
-      <c r="Y64" s="46" t="s">
-        <v>181</v>
+      <c r="X64" s="55" t="s">
+        <v>612</v>
+      </c>
+      <c r="Y64" s="56" t="s">
+        <v>596</v>
+      </c>
+      <c r="Z64" s="55" t="s">
+        <v>613</v>
+      </c>
+      <c r="AA64" s="56" t="s">
+        <v>600</v>
+      </c>
+      <c r="AB64" s="55" t="s">
+        <v>614</v>
+      </c>
+      <c r="AC64" s="56" t="s">
+        <v>603</v>
+      </c>
+      <c r="AD64" s="55" t="s">
+        <v>615</v>
+      </c>
+      <c r="AE64" s="56" t="s">
+        <v>606</v>
+      </c>
+      <c r="AF64" s="55" t="s">
+        <v>616</v>
+      </c>
+      <c r="AG64" s="56" t="s">
+        <v>609</v>
       </c>
     </row>
-    <row r="65" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="65" spans="1:33" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A65" s="9">
         <v>65</v>
       </c>
@@ -12623,14 +14953,38 @@
       <c r="W65" s="46" t="s">
         <v>181</v>
       </c>
-      <c r="X65" s="45" t="s">
-        <v>181</v>
-      </c>
-      <c r="Y65" s="46" t="s">
-        <v>181</v>
+      <c r="X65" s="55" t="s">
+        <v>612</v>
+      </c>
+      <c r="Y65" s="56" t="s">
+        <v>596</v>
+      </c>
+      <c r="Z65" s="55" t="s">
+        <v>613</v>
+      </c>
+      <c r="AA65" s="56" t="s">
+        <v>600</v>
+      </c>
+      <c r="AB65" s="55" t="s">
+        <v>614</v>
+      </c>
+      <c r="AC65" s="56" t="s">
+        <v>603</v>
+      </c>
+      <c r="AD65" s="55" t="s">
+        <v>615</v>
+      </c>
+      <c r="AE65" s="56" t="s">
+        <v>606</v>
+      </c>
+      <c r="AF65" s="55" t="s">
+        <v>616</v>
+      </c>
+      <c r="AG65" s="56" t="s">
+        <v>609</v>
       </c>
     </row>
-    <row r="66" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="66" spans="1:33" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A66" s="9">
         <v>66</v>
       </c>
@@ -12700,14 +15054,38 @@
       <c r="W66" s="46" t="s">
         <v>181</v>
       </c>
-      <c r="X66" s="45" t="s">
-        <v>181</v>
-      </c>
-      <c r="Y66" s="46" t="s">
-        <v>181</v>
+      <c r="X66" s="55" t="s">
+        <v>612</v>
+      </c>
+      <c r="Y66" s="56" t="s">
+        <v>596</v>
+      </c>
+      <c r="Z66" s="55" t="s">
+        <v>613</v>
+      </c>
+      <c r="AA66" s="56" t="s">
+        <v>600</v>
+      </c>
+      <c r="AB66" s="55" t="s">
+        <v>614</v>
+      </c>
+      <c r="AC66" s="56" t="s">
+        <v>603</v>
+      </c>
+      <c r="AD66" s="55" t="s">
+        <v>615</v>
+      </c>
+      <c r="AE66" s="56" t="s">
+        <v>606</v>
+      </c>
+      <c r="AF66" s="55" t="s">
+        <v>616</v>
+      </c>
+      <c r="AG66" s="56" t="s">
+        <v>609</v>
       </c>
     </row>
-    <row r="67" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="67" spans="1:33" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A67" s="9">
         <v>67</v>
       </c>
@@ -12777,14 +15155,38 @@
       <c r="W67" s="46" t="s">
         <v>181</v>
       </c>
-      <c r="X67" s="45" t="s">
-        <v>181</v>
-      </c>
-      <c r="Y67" s="46" t="s">
-        <v>181</v>
+      <c r="X67" s="55" t="s">
+        <v>612</v>
+      </c>
+      <c r="Y67" s="56" t="s">
+        <v>596</v>
+      </c>
+      <c r="Z67" s="55" t="s">
+        <v>613</v>
+      </c>
+      <c r="AA67" s="56" t="s">
+        <v>600</v>
+      </c>
+      <c r="AB67" s="55" t="s">
+        <v>614</v>
+      </c>
+      <c r="AC67" s="56" t="s">
+        <v>603</v>
+      </c>
+      <c r="AD67" s="55" t="s">
+        <v>615</v>
+      </c>
+      <c r="AE67" s="56" t="s">
+        <v>606</v>
+      </c>
+      <c r="AF67" s="55" t="s">
+        <v>616</v>
+      </c>
+      <c r="AG67" s="56" t="s">
+        <v>609</v>
       </c>
     </row>
-    <row r="68" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="68" spans="1:33" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A68" s="9">
         <v>68</v>
       </c>
@@ -12854,14 +15256,38 @@
       <c r="W68" s="46" t="s">
         <v>181</v>
       </c>
-      <c r="X68" s="45" t="s">
-        <v>181</v>
-      </c>
-      <c r="Y68" s="46" t="s">
-        <v>181</v>
+      <c r="X68" s="55" t="s">
+        <v>612</v>
+      </c>
+      <c r="Y68" s="56" t="s">
+        <v>596</v>
+      </c>
+      <c r="Z68" s="55" t="s">
+        <v>613</v>
+      </c>
+      <c r="AA68" s="56" t="s">
+        <v>600</v>
+      </c>
+      <c r="AB68" s="55" t="s">
+        <v>614</v>
+      </c>
+      <c r="AC68" s="56" t="s">
+        <v>603</v>
+      </c>
+      <c r="AD68" s="55" t="s">
+        <v>615</v>
+      </c>
+      <c r="AE68" s="56" t="s">
+        <v>606</v>
+      </c>
+      <c r="AF68" s="55" t="s">
+        <v>616</v>
+      </c>
+      <c r="AG68" s="56" t="s">
+        <v>609</v>
       </c>
     </row>
-    <row r="69" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="69" spans="1:33" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A69" s="9">
         <v>69</v>
       </c>
@@ -12931,14 +15357,38 @@
       <c r="W69" s="46" t="s">
         <v>181</v>
       </c>
-      <c r="X69" s="45" t="s">
-        <v>181</v>
-      </c>
-      <c r="Y69" s="46" t="s">
-        <v>181</v>
+      <c r="X69" s="55" t="s">
+        <v>612</v>
+      </c>
+      <c r="Y69" s="56" t="s">
+        <v>596</v>
+      </c>
+      <c r="Z69" s="55" t="s">
+        <v>613</v>
+      </c>
+      <c r="AA69" s="56" t="s">
+        <v>600</v>
+      </c>
+      <c r="AB69" s="55" t="s">
+        <v>614</v>
+      </c>
+      <c r="AC69" s="56" t="s">
+        <v>603</v>
+      </c>
+      <c r="AD69" s="55" t="s">
+        <v>615</v>
+      </c>
+      <c r="AE69" s="56" t="s">
+        <v>606</v>
+      </c>
+      <c r="AF69" s="55" t="s">
+        <v>616</v>
+      </c>
+      <c r="AG69" s="56" t="s">
+        <v>609</v>
       </c>
     </row>
-    <row r="70" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="70" spans="1:33" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A70" s="9">
         <v>70</v>
       </c>
@@ -13008,14 +15458,38 @@
       <c r="W70" s="46" t="s">
         <v>181</v>
       </c>
-      <c r="X70" s="45" t="s">
-        <v>181</v>
-      </c>
-      <c r="Y70" s="46" t="s">
-        <v>181</v>
+      <c r="X70" s="55" t="s">
+        <v>612</v>
+      </c>
+      <c r="Y70" s="56" t="s">
+        <v>596</v>
+      </c>
+      <c r="Z70" s="55" t="s">
+        <v>613</v>
+      </c>
+      <c r="AA70" s="56" t="s">
+        <v>600</v>
+      </c>
+      <c r="AB70" s="55" t="s">
+        <v>614</v>
+      </c>
+      <c r="AC70" s="56" t="s">
+        <v>603</v>
+      </c>
+      <c r="AD70" s="55" t="s">
+        <v>615</v>
+      </c>
+      <c r="AE70" s="56" t="s">
+        <v>606</v>
+      </c>
+      <c r="AF70" s="55" t="s">
+        <v>616</v>
+      </c>
+      <c r="AG70" s="56" t="s">
+        <v>609</v>
       </c>
     </row>
-    <row r="71" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="71" spans="1:33" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A71" s="9">
         <v>71</v>
       </c>
@@ -13085,14 +15559,38 @@
       <c r="W71" s="46" t="s">
         <v>181</v>
       </c>
-      <c r="X71" s="45" t="s">
-        <v>181</v>
-      </c>
-      <c r="Y71" s="46" t="s">
-        <v>181</v>
+      <c r="X71" s="55" t="s">
+        <v>612</v>
+      </c>
+      <c r="Y71" s="56" t="s">
+        <v>596</v>
+      </c>
+      <c r="Z71" s="55" t="s">
+        <v>613</v>
+      </c>
+      <c r="AA71" s="56" t="s">
+        <v>600</v>
+      </c>
+      <c r="AB71" s="55" t="s">
+        <v>614</v>
+      </c>
+      <c r="AC71" s="56" t="s">
+        <v>603</v>
+      </c>
+      <c r="AD71" s="55" t="s">
+        <v>615</v>
+      </c>
+      <c r="AE71" s="56" t="s">
+        <v>606</v>
+      </c>
+      <c r="AF71" s="55" t="s">
+        <v>616</v>
+      </c>
+      <c r="AG71" s="56" t="s">
+        <v>609</v>
       </c>
     </row>
-    <row r="72" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="72" spans="1:33" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A72" s="9">
         <v>72</v>
       </c>
@@ -13162,14 +15660,38 @@
       <c r="W72" s="46" t="s">
         <v>181</v>
       </c>
-      <c r="X72" s="45" t="s">
-        <v>181</v>
-      </c>
-      <c r="Y72" s="46" t="s">
-        <v>181</v>
+      <c r="X72" s="55" t="s">
+        <v>612</v>
+      </c>
+      <c r="Y72" s="56" t="s">
+        <v>596</v>
+      </c>
+      <c r="Z72" s="55" t="s">
+        <v>613</v>
+      </c>
+      <c r="AA72" s="56" t="s">
+        <v>600</v>
+      </c>
+      <c r="AB72" s="55" t="s">
+        <v>614</v>
+      </c>
+      <c r="AC72" s="56" t="s">
+        <v>603</v>
+      </c>
+      <c r="AD72" s="55" t="s">
+        <v>615</v>
+      </c>
+      <c r="AE72" s="56" t="s">
+        <v>606</v>
+      </c>
+      <c r="AF72" s="55" t="s">
+        <v>616</v>
+      </c>
+      <c r="AG72" s="56" t="s">
+        <v>609</v>
       </c>
     </row>
-    <row r="73" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="73" spans="1:33" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A73" s="9">
         <v>73</v>
       </c>
@@ -13239,14 +15761,38 @@
       <c r="W73" s="46" t="s">
         <v>181</v>
       </c>
-      <c r="X73" s="45" t="s">
-        <v>181</v>
-      </c>
-      <c r="Y73" s="46" t="s">
-        <v>181</v>
+      <c r="X73" s="55" t="s">
+        <v>612</v>
+      </c>
+      <c r="Y73" s="56" t="s">
+        <v>596</v>
+      </c>
+      <c r="Z73" s="55" t="s">
+        <v>613</v>
+      </c>
+      <c r="AA73" s="56" t="s">
+        <v>600</v>
+      </c>
+      <c r="AB73" s="55" t="s">
+        <v>614</v>
+      </c>
+      <c r="AC73" s="56" t="s">
+        <v>603</v>
+      </c>
+      <c r="AD73" s="55" t="s">
+        <v>615</v>
+      </c>
+      <c r="AE73" s="56" t="s">
+        <v>606</v>
+      </c>
+      <c r="AF73" s="55" t="s">
+        <v>616</v>
+      </c>
+      <c r="AG73" s="56" t="s">
+        <v>609</v>
       </c>
     </row>
-    <row r="74" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="74" spans="1:33" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A74" s="9">
         <v>74</v>
       </c>
@@ -13316,14 +15862,38 @@
       <c r="W74" s="46" t="s">
         <v>181</v>
       </c>
-      <c r="X74" s="45" t="s">
-        <v>181</v>
-      </c>
-      <c r="Y74" s="46" t="s">
-        <v>181</v>
+      <c r="X74" s="55" t="s">
+        <v>612</v>
+      </c>
+      <c r="Y74" s="56" t="s">
+        <v>596</v>
+      </c>
+      <c r="Z74" s="55" t="s">
+        <v>613</v>
+      </c>
+      <c r="AA74" s="56" t="s">
+        <v>600</v>
+      </c>
+      <c r="AB74" s="55" t="s">
+        <v>614</v>
+      </c>
+      <c r="AC74" s="56" t="s">
+        <v>603</v>
+      </c>
+      <c r="AD74" s="55" t="s">
+        <v>615</v>
+      </c>
+      <c r="AE74" s="56" t="s">
+        <v>606</v>
+      </c>
+      <c r="AF74" s="55" t="s">
+        <v>616</v>
+      </c>
+      <c r="AG74" s="56" t="s">
+        <v>609</v>
       </c>
     </row>
-    <row r="75" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="75" spans="1:33" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A75" s="9">
         <v>75</v>
       </c>
@@ -13393,14 +15963,38 @@
       <c r="W75" s="46" t="s">
         <v>181</v>
       </c>
-      <c r="X75" s="45" t="s">
-        <v>181</v>
-      </c>
-      <c r="Y75" s="46" t="s">
-        <v>181</v>
+      <c r="X75" s="55" t="s">
+        <v>612</v>
+      </c>
+      <c r="Y75" s="56" t="s">
+        <v>596</v>
+      </c>
+      <c r="Z75" s="55" t="s">
+        <v>613</v>
+      </c>
+      <c r="AA75" s="56" t="s">
+        <v>600</v>
+      </c>
+      <c r="AB75" s="55" t="s">
+        <v>614</v>
+      </c>
+      <c r="AC75" s="56" t="s">
+        <v>603</v>
+      </c>
+      <c r="AD75" s="55" t="s">
+        <v>615</v>
+      </c>
+      <c r="AE75" s="56" t="s">
+        <v>606</v>
+      </c>
+      <c r="AF75" s="55" t="s">
+        <v>616</v>
+      </c>
+      <c r="AG75" s="56" t="s">
+        <v>609</v>
       </c>
     </row>
-    <row r="76" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="76" spans="1:33" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A76" s="9">
         <v>76</v>
       </c>
@@ -13470,14 +16064,38 @@
       <c r="W76" s="46" t="s">
         <v>181</v>
       </c>
-      <c r="X76" s="45" t="s">
-        <v>181</v>
-      </c>
-      <c r="Y76" s="46" t="s">
-        <v>181</v>
+      <c r="X76" s="55" t="s">
+        <v>612</v>
+      </c>
+      <c r="Y76" s="56" t="s">
+        <v>596</v>
+      </c>
+      <c r="Z76" s="55" t="s">
+        <v>613</v>
+      </c>
+      <c r="AA76" s="56" t="s">
+        <v>600</v>
+      </c>
+      <c r="AB76" s="55" t="s">
+        <v>614</v>
+      </c>
+      <c r="AC76" s="56" t="s">
+        <v>603</v>
+      </c>
+      <c r="AD76" s="55" t="s">
+        <v>615</v>
+      </c>
+      <c r="AE76" s="56" t="s">
+        <v>606</v>
+      </c>
+      <c r="AF76" s="55" t="s">
+        <v>616</v>
+      </c>
+      <c r="AG76" s="56" t="s">
+        <v>609</v>
       </c>
     </row>
-    <row r="77" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="77" spans="1:33" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A77" s="9">
         <v>77</v>
       </c>
@@ -13547,14 +16165,38 @@
       <c r="W77" s="46" t="s">
         <v>181</v>
       </c>
-      <c r="X77" s="45" t="s">
-        <v>181</v>
-      </c>
-      <c r="Y77" s="46" t="s">
-        <v>181</v>
+      <c r="X77" s="55" t="s">
+        <v>612</v>
+      </c>
+      <c r="Y77" s="56" t="s">
+        <v>596</v>
+      </c>
+      <c r="Z77" s="55" t="s">
+        <v>613</v>
+      </c>
+      <c r="AA77" s="56" t="s">
+        <v>600</v>
+      </c>
+      <c r="AB77" s="55" t="s">
+        <v>614</v>
+      </c>
+      <c r="AC77" s="56" t="s">
+        <v>603</v>
+      </c>
+      <c r="AD77" s="55" t="s">
+        <v>615</v>
+      </c>
+      <c r="AE77" s="56" t="s">
+        <v>606</v>
+      </c>
+      <c r="AF77" s="55" t="s">
+        <v>616</v>
+      </c>
+      <c r="AG77" s="56" t="s">
+        <v>609</v>
       </c>
     </row>
-    <row r="78" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="78" spans="1:33" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A78" s="9">
         <v>78</v>
       </c>
@@ -13624,14 +16266,38 @@
       <c r="W78" s="46" t="s">
         <v>181</v>
       </c>
-      <c r="X78" s="45" t="s">
-        <v>181</v>
-      </c>
-      <c r="Y78" s="46" t="s">
-        <v>181</v>
+      <c r="X78" s="55" t="s">
+        <v>612</v>
+      </c>
+      <c r="Y78" s="56" t="s">
+        <v>596</v>
+      </c>
+      <c r="Z78" s="55" t="s">
+        <v>613</v>
+      </c>
+      <c r="AA78" s="56" t="s">
+        <v>600</v>
+      </c>
+      <c r="AB78" s="55" t="s">
+        <v>614</v>
+      </c>
+      <c r="AC78" s="56" t="s">
+        <v>603</v>
+      </c>
+      <c r="AD78" s="55" t="s">
+        <v>615</v>
+      </c>
+      <c r="AE78" s="56" t="s">
+        <v>606</v>
+      </c>
+      <c r="AF78" s="55" t="s">
+        <v>616</v>
+      </c>
+      <c r="AG78" s="56" t="s">
+        <v>609</v>
       </c>
     </row>
-    <row r="79" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="79" spans="1:33" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A79" s="9">
         <v>79</v>
       </c>
@@ -13701,14 +16367,38 @@
       <c r="W79" s="46" t="s">
         <v>181</v>
       </c>
-      <c r="X79" s="45" t="s">
-        <v>181</v>
-      </c>
-      <c r="Y79" s="46" t="s">
-        <v>181</v>
+      <c r="X79" s="55" t="s">
+        <v>612</v>
+      </c>
+      <c r="Y79" s="56" t="s">
+        <v>596</v>
+      </c>
+      <c r="Z79" s="55" t="s">
+        <v>613</v>
+      </c>
+      <c r="AA79" s="56" t="s">
+        <v>600</v>
+      </c>
+      <c r="AB79" s="55" t="s">
+        <v>614</v>
+      </c>
+      <c r="AC79" s="56" t="s">
+        <v>603</v>
+      </c>
+      <c r="AD79" s="55" t="s">
+        <v>615</v>
+      </c>
+      <c r="AE79" s="56" t="s">
+        <v>606</v>
+      </c>
+      <c r="AF79" s="55" t="s">
+        <v>616</v>
+      </c>
+      <c r="AG79" s="56" t="s">
+        <v>609</v>
       </c>
     </row>
-    <row r="80" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="80" spans="1:33" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A80" s="9">
         <v>80</v>
       </c>
@@ -13778,14 +16468,38 @@
       <c r="W80" s="46" t="s">
         <v>181</v>
       </c>
-      <c r="X80" s="45" t="s">
-        <v>181</v>
-      </c>
-      <c r="Y80" s="46" t="s">
-        <v>181</v>
+      <c r="X80" s="55" t="s">
+        <v>612</v>
+      </c>
+      <c r="Y80" s="56" t="s">
+        <v>596</v>
+      </c>
+      <c r="Z80" s="55" t="s">
+        <v>613</v>
+      </c>
+      <c r="AA80" s="56" t="s">
+        <v>600</v>
+      </c>
+      <c r="AB80" s="55" t="s">
+        <v>614</v>
+      </c>
+      <c r="AC80" s="56" t="s">
+        <v>603</v>
+      </c>
+      <c r="AD80" s="55" t="s">
+        <v>615</v>
+      </c>
+      <c r="AE80" s="56" t="s">
+        <v>606</v>
+      </c>
+      <c r="AF80" s="55" t="s">
+        <v>616</v>
+      </c>
+      <c r="AG80" s="56" t="s">
+        <v>609</v>
       </c>
     </row>
-    <row r="81" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="81" spans="1:33" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A81" s="9">
         <v>81</v>
       </c>
@@ -13855,14 +16569,38 @@
       <c r="W81" s="46" t="s">
         <v>181</v>
       </c>
-      <c r="X81" s="45" t="s">
-        <v>181</v>
-      </c>
-      <c r="Y81" s="46" t="s">
-        <v>181</v>
+      <c r="X81" s="55" t="s">
+        <v>612</v>
+      </c>
+      <c r="Y81" s="56" t="s">
+        <v>596</v>
+      </c>
+      <c r="Z81" s="55" t="s">
+        <v>613</v>
+      </c>
+      <c r="AA81" s="56" t="s">
+        <v>600</v>
+      </c>
+      <c r="AB81" s="55" t="s">
+        <v>614</v>
+      </c>
+      <c r="AC81" s="56" t="s">
+        <v>603</v>
+      </c>
+      <c r="AD81" s="55" t="s">
+        <v>615</v>
+      </c>
+      <c r="AE81" s="56" t="s">
+        <v>606</v>
+      </c>
+      <c r="AF81" s="55" t="s">
+        <v>616</v>
+      </c>
+      <c r="AG81" s="56" t="s">
+        <v>609</v>
       </c>
     </row>
-    <row r="82" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="82" spans="1:33" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A82" s="9">
         <v>82</v>
       </c>
@@ -13932,14 +16670,38 @@
       <c r="W82" s="46" t="s">
         <v>181</v>
       </c>
-      <c r="X82" s="45" t="s">
-        <v>181</v>
-      </c>
-      <c r="Y82" s="46" t="s">
-        <v>181</v>
+      <c r="X82" s="55" t="s">
+        <v>612</v>
+      </c>
+      <c r="Y82" s="56" t="s">
+        <v>596</v>
+      </c>
+      <c r="Z82" s="55" t="s">
+        <v>613</v>
+      </c>
+      <c r="AA82" s="56" t="s">
+        <v>600</v>
+      </c>
+      <c r="AB82" s="55" t="s">
+        <v>614</v>
+      </c>
+      <c r="AC82" s="56" t="s">
+        <v>603</v>
+      </c>
+      <c r="AD82" s="55" t="s">
+        <v>615</v>
+      </c>
+      <c r="AE82" s="56" t="s">
+        <v>606</v>
+      </c>
+      <c r="AF82" s="55" t="s">
+        <v>616</v>
+      </c>
+      <c r="AG82" s="56" t="s">
+        <v>609</v>
       </c>
     </row>
-    <row r="83" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="83" spans="1:33" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A83" s="9">
         <v>83</v>
       </c>
@@ -14009,14 +16771,38 @@
       <c r="W83" s="46" t="s">
         <v>181</v>
       </c>
-      <c r="X83" s="45" t="s">
-        <v>181</v>
-      </c>
-      <c r="Y83" s="46" t="s">
-        <v>181</v>
+      <c r="X83" s="55" t="s">
+        <v>612</v>
+      </c>
+      <c r="Y83" s="56" t="s">
+        <v>596</v>
+      </c>
+      <c r="Z83" s="55" t="s">
+        <v>613</v>
+      </c>
+      <c r="AA83" s="56" t="s">
+        <v>600</v>
+      </c>
+      <c r="AB83" s="55" t="s">
+        <v>614</v>
+      </c>
+      <c r="AC83" s="56" t="s">
+        <v>603</v>
+      </c>
+      <c r="AD83" s="55" t="s">
+        <v>615</v>
+      </c>
+      <c r="AE83" s="56" t="s">
+        <v>606</v>
+      </c>
+      <c r="AF83" s="55" t="s">
+        <v>616</v>
+      </c>
+      <c r="AG83" s="56" t="s">
+        <v>609</v>
       </c>
     </row>
-    <row r="84" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="84" spans="1:33" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A84" s="9">
         <v>84</v>
       </c>
@@ -14086,14 +16872,38 @@
       <c r="W84" s="46" t="s">
         <v>181</v>
       </c>
-      <c r="X84" s="45" t="s">
-        <v>181</v>
-      </c>
-      <c r="Y84" s="46" t="s">
-        <v>181</v>
+      <c r="X84" s="55" t="s">
+        <v>612</v>
+      </c>
+      <c r="Y84" s="56" t="s">
+        <v>596</v>
+      </c>
+      <c r="Z84" s="55" t="s">
+        <v>613</v>
+      </c>
+      <c r="AA84" s="56" t="s">
+        <v>600</v>
+      </c>
+      <c r="AB84" s="55" t="s">
+        <v>614</v>
+      </c>
+      <c r="AC84" s="56" t="s">
+        <v>603</v>
+      </c>
+      <c r="AD84" s="55" t="s">
+        <v>615</v>
+      </c>
+      <c r="AE84" s="56" t="s">
+        <v>606</v>
+      </c>
+      <c r="AF84" s="55" t="s">
+        <v>616</v>
+      </c>
+      <c r="AG84" s="56" t="s">
+        <v>609</v>
       </c>
     </row>
-    <row r="85" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="85" spans="1:33" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A85" s="9">
         <v>85</v>
       </c>
@@ -14163,14 +16973,38 @@
       <c r="W85" s="46" t="s">
         <v>181</v>
       </c>
-      <c r="X85" s="45" t="s">
-        <v>181</v>
-      </c>
-      <c r="Y85" s="46" t="s">
-        <v>181</v>
+      <c r="X85" s="55" t="s">
+        <v>612</v>
+      </c>
+      <c r="Y85" s="56" t="s">
+        <v>596</v>
+      </c>
+      <c r="Z85" s="55" t="s">
+        <v>613</v>
+      </c>
+      <c r="AA85" s="56" t="s">
+        <v>600</v>
+      </c>
+      <c r="AB85" s="55" t="s">
+        <v>614</v>
+      </c>
+      <c r="AC85" s="56" t="s">
+        <v>603</v>
+      </c>
+      <c r="AD85" s="55" t="s">
+        <v>615</v>
+      </c>
+      <c r="AE85" s="56" t="s">
+        <v>606</v>
+      </c>
+      <c r="AF85" s="55" t="s">
+        <v>616</v>
+      </c>
+      <c r="AG85" s="56" t="s">
+        <v>609</v>
       </c>
     </row>
-    <row r="86" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="86" spans="1:33" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A86" s="9">
         <v>86</v>
       </c>
@@ -14240,14 +17074,38 @@
       <c r="W86" s="46" t="s">
         <v>181</v>
       </c>
-      <c r="X86" s="45" t="s">
-        <v>181</v>
-      </c>
-      <c r="Y86" s="46" t="s">
-        <v>181</v>
+      <c r="X86" s="55" t="s">
+        <v>612</v>
+      </c>
+      <c r="Y86" s="56" t="s">
+        <v>596</v>
+      </c>
+      <c r="Z86" s="55" t="s">
+        <v>613</v>
+      </c>
+      <c r="AA86" s="56" t="s">
+        <v>600</v>
+      </c>
+      <c r="AB86" s="55" t="s">
+        <v>614</v>
+      </c>
+      <c r="AC86" s="56" t="s">
+        <v>603</v>
+      </c>
+      <c r="AD86" s="55" t="s">
+        <v>615</v>
+      </c>
+      <c r="AE86" s="56" t="s">
+        <v>606</v>
+      </c>
+      <c r="AF86" s="55" t="s">
+        <v>616</v>
+      </c>
+      <c r="AG86" s="56" t="s">
+        <v>609</v>
       </c>
     </row>
-    <row r="87" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="87" spans="1:33" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A87" s="9">
         <v>87</v>
       </c>
@@ -14317,14 +17175,38 @@
       <c r="W87" s="46" t="s">
         <v>181</v>
       </c>
-      <c r="X87" s="45" t="s">
-        <v>181</v>
-      </c>
-      <c r="Y87" s="46" t="s">
-        <v>181</v>
+      <c r="X87" s="55" t="s">
+        <v>612</v>
+      </c>
+      <c r="Y87" s="56" t="s">
+        <v>596</v>
+      </c>
+      <c r="Z87" s="55" t="s">
+        <v>613</v>
+      </c>
+      <c r="AA87" s="56" t="s">
+        <v>600</v>
+      </c>
+      <c r="AB87" s="55" t="s">
+        <v>614</v>
+      </c>
+      <c r="AC87" s="56" t="s">
+        <v>603</v>
+      </c>
+      <c r="AD87" s="55" t="s">
+        <v>615</v>
+      </c>
+      <c r="AE87" s="56" t="s">
+        <v>606</v>
+      </c>
+      <c r="AF87" s="55" t="s">
+        <v>616</v>
+      </c>
+      <c r="AG87" s="56" t="s">
+        <v>609</v>
       </c>
     </row>
-    <row r="88" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="88" spans="1:33" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A88" s="9">
         <v>88</v>
       </c>
@@ -14394,14 +17276,38 @@
       <c r="W88" s="46" t="s">
         <v>181</v>
       </c>
-      <c r="X88" s="45" t="s">
-        <v>181</v>
-      </c>
-      <c r="Y88" s="46" t="s">
-        <v>181</v>
+      <c r="X88" s="55" t="s">
+        <v>612</v>
+      </c>
+      <c r="Y88" s="56" t="s">
+        <v>596</v>
+      </c>
+      <c r="Z88" s="55" t="s">
+        <v>613</v>
+      </c>
+      <c r="AA88" s="56" t="s">
+        <v>600</v>
+      </c>
+      <c r="AB88" s="55" t="s">
+        <v>614</v>
+      </c>
+      <c r="AC88" s="56" t="s">
+        <v>603</v>
+      </c>
+      <c r="AD88" s="55" t="s">
+        <v>615</v>
+      </c>
+      <c r="AE88" s="56" t="s">
+        <v>606</v>
+      </c>
+      <c r="AF88" s="55" t="s">
+        <v>616</v>
+      </c>
+      <c r="AG88" s="56" t="s">
+        <v>609</v>
       </c>
     </row>
-    <row r="89" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="89" spans="1:33" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A89" s="9">
         <v>89</v>
       </c>
@@ -14471,14 +17377,38 @@
       <c r="W89" s="46" t="s">
         <v>181</v>
       </c>
-      <c r="X89" s="45" t="s">
-        <v>181</v>
-      </c>
-      <c r="Y89" s="46" t="s">
-        <v>181</v>
+      <c r="X89" s="55" t="s">
+        <v>612</v>
+      </c>
+      <c r="Y89" s="56" t="s">
+        <v>596</v>
+      </c>
+      <c r="Z89" s="55" t="s">
+        <v>613</v>
+      </c>
+      <c r="AA89" s="56" t="s">
+        <v>600</v>
+      </c>
+      <c r="AB89" s="55" t="s">
+        <v>614</v>
+      </c>
+      <c r="AC89" s="56" t="s">
+        <v>603</v>
+      </c>
+      <c r="AD89" s="55" t="s">
+        <v>615</v>
+      </c>
+      <c r="AE89" s="56" t="s">
+        <v>606</v>
+      </c>
+      <c r="AF89" s="55" t="s">
+        <v>616</v>
+      </c>
+      <c r="AG89" s="56" t="s">
+        <v>609</v>
       </c>
     </row>
-    <row r="90" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="90" spans="1:33" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A90" s="9">
         <v>90</v>
       </c>
@@ -14548,14 +17478,38 @@
       <c r="W90" s="46" t="s">
         <v>181</v>
       </c>
-      <c r="X90" s="45" t="s">
-        <v>181</v>
-      </c>
-      <c r="Y90" s="46" t="s">
-        <v>181</v>
+      <c r="X90" s="55" t="s">
+        <v>612</v>
+      </c>
+      <c r="Y90" s="56" t="s">
+        <v>596</v>
+      </c>
+      <c r="Z90" s="55" t="s">
+        <v>613</v>
+      </c>
+      <c r="AA90" s="56" t="s">
+        <v>600</v>
+      </c>
+      <c r="AB90" s="55" t="s">
+        <v>614</v>
+      </c>
+      <c r="AC90" s="56" t="s">
+        <v>603</v>
+      </c>
+      <c r="AD90" s="55" t="s">
+        <v>615</v>
+      </c>
+      <c r="AE90" s="56" t="s">
+        <v>606</v>
+      </c>
+      <c r="AF90" s="55" t="s">
+        <v>616</v>
+      </c>
+      <c r="AG90" s="56" t="s">
+        <v>609</v>
       </c>
     </row>
-    <row r="91" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="91" spans="1:33" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A91" s="9">
         <v>91</v>
       </c>
@@ -14625,14 +17579,38 @@
       <c r="W91" s="46" t="s">
         <v>181</v>
       </c>
-      <c r="X91" s="45" t="s">
-        <v>181</v>
-      </c>
-      <c r="Y91" s="46" t="s">
-        <v>181</v>
+      <c r="X91" s="55" t="s">
+        <v>612</v>
+      </c>
+      <c r="Y91" s="56" t="s">
+        <v>596</v>
+      </c>
+      <c r="Z91" s="55" t="s">
+        <v>613</v>
+      </c>
+      <c r="AA91" s="56" t="s">
+        <v>600</v>
+      </c>
+      <c r="AB91" s="55" t="s">
+        <v>614</v>
+      </c>
+      <c r="AC91" s="56" t="s">
+        <v>603</v>
+      </c>
+      <c r="AD91" s="55" t="s">
+        <v>615</v>
+      </c>
+      <c r="AE91" s="56" t="s">
+        <v>606</v>
+      </c>
+      <c r="AF91" s="55" t="s">
+        <v>616</v>
+      </c>
+      <c r="AG91" s="56" t="s">
+        <v>609</v>
       </c>
     </row>
-    <row r="92" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="92" spans="1:33" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A92" s="9">
         <v>92</v>
       </c>
@@ -14702,14 +17680,38 @@
       <c r="W92" s="46" t="s">
         <v>181</v>
       </c>
-      <c r="X92" s="45" t="s">
-        <v>181</v>
-      </c>
-      <c r="Y92" s="46" t="s">
-        <v>181</v>
+      <c r="X92" s="55" t="s">
+        <v>612</v>
+      </c>
+      <c r="Y92" s="56" t="s">
+        <v>596</v>
+      </c>
+      <c r="Z92" s="55" t="s">
+        <v>613</v>
+      </c>
+      <c r="AA92" s="56" t="s">
+        <v>600</v>
+      </c>
+      <c r="AB92" s="55" t="s">
+        <v>614</v>
+      </c>
+      <c r="AC92" s="56" t="s">
+        <v>603</v>
+      </c>
+      <c r="AD92" s="55" t="s">
+        <v>615</v>
+      </c>
+      <c r="AE92" s="56" t="s">
+        <v>606</v>
+      </c>
+      <c r="AF92" s="55" t="s">
+        <v>616</v>
+      </c>
+      <c r="AG92" s="56" t="s">
+        <v>609</v>
       </c>
     </row>
-    <row r="93" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="93" spans="1:33" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A93" s="9">
         <v>93</v>
       </c>
@@ -14779,14 +17781,38 @@
       <c r="W93" s="46" t="s">
         <v>181</v>
       </c>
-      <c r="X93" s="45" t="s">
-        <v>181</v>
-      </c>
-      <c r="Y93" s="46" t="s">
-        <v>181</v>
+      <c r="X93" s="55" t="s">
+        <v>612</v>
+      </c>
+      <c r="Y93" s="56" t="s">
+        <v>596</v>
+      </c>
+      <c r="Z93" s="55" t="s">
+        <v>613</v>
+      </c>
+      <c r="AA93" s="56" t="s">
+        <v>600</v>
+      </c>
+      <c r="AB93" s="55" t="s">
+        <v>614</v>
+      </c>
+      <c r="AC93" s="56" t="s">
+        <v>603</v>
+      </c>
+      <c r="AD93" s="55" t="s">
+        <v>615</v>
+      </c>
+      <c r="AE93" s="56" t="s">
+        <v>606</v>
+      </c>
+      <c r="AF93" s="55" t="s">
+        <v>616</v>
+      </c>
+      <c r="AG93" s="56" t="s">
+        <v>609</v>
       </c>
     </row>
-    <row r="94" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="94" spans="1:33" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A94" s="9">
         <v>94</v>
       </c>
@@ -14856,14 +17882,38 @@
       <c r="W94" s="46" t="s">
         <v>181</v>
       </c>
-      <c r="X94" s="45" t="s">
-        <v>181</v>
-      </c>
-      <c r="Y94" s="46" t="s">
-        <v>181</v>
+      <c r="X94" s="55" t="s">
+        <v>612</v>
+      </c>
+      <c r="Y94" s="56" t="s">
+        <v>596</v>
+      </c>
+      <c r="Z94" s="55" t="s">
+        <v>613</v>
+      </c>
+      <c r="AA94" s="56" t="s">
+        <v>600</v>
+      </c>
+      <c r="AB94" s="55" t="s">
+        <v>614</v>
+      </c>
+      <c r="AC94" s="56" t="s">
+        <v>603</v>
+      </c>
+      <c r="AD94" s="55" t="s">
+        <v>615</v>
+      </c>
+      <c r="AE94" s="56" t="s">
+        <v>606</v>
+      </c>
+      <c r="AF94" s="55" t="s">
+        <v>616</v>
+      </c>
+      <c r="AG94" s="56" t="s">
+        <v>609</v>
       </c>
     </row>
-    <row r="95" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="95" spans="1:33" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A95" s="9">
         <v>95</v>
       </c>
@@ -14933,14 +17983,38 @@
       <c r="W95" s="46" t="s">
         <v>181</v>
       </c>
-      <c r="X95" s="45" t="s">
-        <v>181</v>
-      </c>
-      <c r="Y95" s="46" t="s">
-        <v>181</v>
+      <c r="X95" s="55" t="s">
+        <v>612</v>
+      </c>
+      <c r="Y95" s="56" t="s">
+        <v>596</v>
+      </c>
+      <c r="Z95" s="55" t="s">
+        <v>613</v>
+      </c>
+      <c r="AA95" s="56" t="s">
+        <v>600</v>
+      </c>
+      <c r="AB95" s="55" t="s">
+        <v>614</v>
+      </c>
+      <c r="AC95" s="56" t="s">
+        <v>603</v>
+      </c>
+      <c r="AD95" s="55" t="s">
+        <v>615</v>
+      </c>
+      <c r="AE95" s="56" t="s">
+        <v>606</v>
+      </c>
+      <c r="AF95" s="55" t="s">
+        <v>616</v>
+      </c>
+      <c r="AG95" s="56" t="s">
+        <v>609</v>
       </c>
     </row>
-    <row r="96" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="96" spans="1:33" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A96" s="9">
         <v>96</v>
       </c>
@@ -15010,14 +18084,38 @@
       <c r="W96" s="46" t="s">
         <v>181</v>
       </c>
-      <c r="X96" s="45" t="s">
-        <v>181</v>
-      </c>
-      <c r="Y96" s="46" t="s">
-        <v>181</v>
+      <c r="X96" s="55" t="s">
+        <v>612</v>
+      </c>
+      <c r="Y96" s="56" t="s">
+        <v>596</v>
+      </c>
+      <c r="Z96" s="55" t="s">
+        <v>613</v>
+      </c>
+      <c r="AA96" s="56" t="s">
+        <v>600</v>
+      </c>
+      <c r="AB96" s="55" t="s">
+        <v>614</v>
+      </c>
+      <c r="AC96" s="56" t="s">
+        <v>603</v>
+      </c>
+      <c r="AD96" s="55" t="s">
+        <v>615</v>
+      </c>
+      <c r="AE96" s="56" t="s">
+        <v>606</v>
+      </c>
+      <c r="AF96" s="55" t="s">
+        <v>616</v>
+      </c>
+      <c r="AG96" s="56" t="s">
+        <v>609</v>
       </c>
     </row>
-    <row r="97" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="97" spans="1:33" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A97" s="9">
         <v>97</v>
       </c>
@@ -15087,14 +18185,38 @@
       <c r="W97" s="46" t="s">
         <v>181</v>
       </c>
-      <c r="X97" s="45" t="s">
-        <v>181</v>
-      </c>
-      <c r="Y97" s="46" t="s">
-        <v>181</v>
+      <c r="X97" s="55" t="s">
+        <v>612</v>
+      </c>
+      <c r="Y97" s="56" t="s">
+        <v>596</v>
+      </c>
+      <c r="Z97" s="55" t="s">
+        <v>613</v>
+      </c>
+      <c r="AA97" s="56" t="s">
+        <v>600</v>
+      </c>
+      <c r="AB97" s="55" t="s">
+        <v>614</v>
+      </c>
+      <c r="AC97" s="56" t="s">
+        <v>603</v>
+      </c>
+      <c r="AD97" s="55" t="s">
+        <v>615</v>
+      </c>
+      <c r="AE97" s="56" t="s">
+        <v>606</v>
+      </c>
+      <c r="AF97" s="55" t="s">
+        <v>616</v>
+      </c>
+      <c r="AG97" s="56" t="s">
+        <v>609</v>
       </c>
     </row>
-    <row r="98" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="98" spans="1:33" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A98" s="9">
         <v>98</v>
       </c>
@@ -15164,14 +18286,38 @@
       <c r="W98" s="46" t="s">
         <v>181</v>
       </c>
-      <c r="X98" s="45" t="s">
-        <v>181</v>
-      </c>
-      <c r="Y98" s="46" t="s">
-        <v>181</v>
+      <c r="X98" s="55" t="s">
+        <v>612</v>
+      </c>
+      <c r="Y98" s="56" t="s">
+        <v>596</v>
+      </c>
+      <c r="Z98" s="55" t="s">
+        <v>613</v>
+      </c>
+      <c r="AA98" s="56" t="s">
+        <v>600</v>
+      </c>
+      <c r="AB98" s="55" t="s">
+        <v>614</v>
+      </c>
+      <c r="AC98" s="56" t="s">
+        <v>603</v>
+      </c>
+      <c r="AD98" s="55" t="s">
+        <v>615</v>
+      </c>
+      <c r="AE98" s="56" t="s">
+        <v>606</v>
+      </c>
+      <c r="AF98" s="55" t="s">
+        <v>616</v>
+      </c>
+      <c r="AG98" s="56" t="s">
+        <v>609</v>
       </c>
     </row>
-    <row r="99" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="99" spans="1:33" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A99" s="9">
         <v>99</v>
       </c>
@@ -15241,14 +18387,38 @@
       <c r="W99" s="46" t="s">
         <v>181</v>
       </c>
-      <c r="X99" s="45" t="s">
-        <v>181</v>
-      </c>
-      <c r="Y99" s="46" t="s">
-        <v>181</v>
+      <c r="X99" s="55" t="s">
+        <v>612</v>
+      </c>
+      <c r="Y99" s="56" t="s">
+        <v>596</v>
+      </c>
+      <c r="Z99" s="55" t="s">
+        <v>613</v>
+      </c>
+      <c r="AA99" s="56" t="s">
+        <v>600</v>
+      </c>
+      <c r="AB99" s="55" t="s">
+        <v>614</v>
+      </c>
+      <c r="AC99" s="56" t="s">
+        <v>603</v>
+      </c>
+      <c r="AD99" s="55" t="s">
+        <v>615</v>
+      </c>
+      <c r="AE99" s="56" t="s">
+        <v>606</v>
+      </c>
+      <c r="AF99" s="55" t="s">
+        <v>616</v>
+      </c>
+      <c r="AG99" s="56" t="s">
+        <v>609</v>
       </c>
     </row>
-    <row r="100" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="100" spans="1:33" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A100" s="9">
         <v>100</v>
       </c>
@@ -15318,14 +18488,38 @@
       <c r="W100" s="46" t="s">
         <v>181</v>
       </c>
-      <c r="X100" s="45" t="s">
-        <v>181</v>
-      </c>
-      <c r="Y100" s="46" t="s">
-        <v>181</v>
+      <c r="X100" s="55" t="s">
+        <v>612</v>
+      </c>
+      <c r="Y100" s="56" t="s">
+        <v>596</v>
+      </c>
+      <c r="Z100" s="55" t="s">
+        <v>613</v>
+      </c>
+      <c r="AA100" s="56" t="s">
+        <v>600</v>
+      </c>
+      <c r="AB100" s="55" t="s">
+        <v>614</v>
+      </c>
+      <c r="AC100" s="56" t="s">
+        <v>603</v>
+      </c>
+      <c r="AD100" s="55" t="s">
+        <v>615</v>
+      </c>
+      <c r="AE100" s="56" t="s">
+        <v>606</v>
+      </c>
+      <c r="AF100" s="55" t="s">
+        <v>616</v>
+      </c>
+      <c r="AG100" s="56" t="s">
+        <v>609</v>
       </c>
     </row>
-    <row r="101" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="101" spans="1:33" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A101" s="9">
         <v>101</v>
       </c>
@@ -15395,14 +18589,38 @@
       <c r="W101" s="46" t="s">
         <v>181</v>
       </c>
-      <c r="X101" s="45" t="s">
-        <v>181</v>
-      </c>
-      <c r="Y101" s="46" t="s">
-        <v>181</v>
+      <c r="X101" s="55" t="s">
+        <v>612</v>
+      </c>
+      <c r="Y101" s="56" t="s">
+        <v>596</v>
+      </c>
+      <c r="Z101" s="55" t="s">
+        <v>613</v>
+      </c>
+      <c r="AA101" s="56" t="s">
+        <v>600</v>
+      </c>
+      <c r="AB101" s="55" t="s">
+        <v>614</v>
+      </c>
+      <c r="AC101" s="56" t="s">
+        <v>603</v>
+      </c>
+      <c r="AD101" s="55" t="s">
+        <v>615</v>
+      </c>
+      <c r="AE101" s="56" t="s">
+        <v>606</v>
+      </c>
+      <c r="AF101" s="55" t="s">
+        <v>616</v>
+      </c>
+      <c r="AG101" s="56" t="s">
+        <v>609</v>
       </c>
     </row>
-    <row r="102" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="102" spans="1:33" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A102" s="9">
         <v>102</v>
       </c>
@@ -15472,14 +18690,38 @@
       <c r="W102" s="46" t="s">
         <v>181</v>
       </c>
-      <c r="X102" s="45" t="s">
-        <v>181</v>
-      </c>
-      <c r="Y102" s="46" t="s">
-        <v>181</v>
+      <c r="X102" s="55" t="s">
+        <v>612</v>
+      </c>
+      <c r="Y102" s="56" t="s">
+        <v>596</v>
+      </c>
+      <c r="Z102" s="55" t="s">
+        <v>613</v>
+      </c>
+      <c r="AA102" s="56" t="s">
+        <v>600</v>
+      </c>
+      <c r="AB102" s="55" t="s">
+        <v>614</v>
+      </c>
+      <c r="AC102" s="56" t="s">
+        <v>603</v>
+      </c>
+      <c r="AD102" s="55" t="s">
+        <v>615</v>
+      </c>
+      <c r="AE102" s="56" t="s">
+        <v>606</v>
+      </c>
+      <c r="AF102" s="55" t="s">
+        <v>616</v>
+      </c>
+      <c r="AG102" s="56" t="s">
+        <v>609</v>
       </c>
     </row>
-    <row r="103" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="103" spans="1:33" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A103" s="9">
         <v>103</v>
       </c>
@@ -15549,14 +18791,38 @@
       <c r="W103" s="46" t="s">
         <v>181</v>
       </c>
-      <c r="X103" s="45" t="s">
-        <v>181</v>
-      </c>
-      <c r="Y103" s="46" t="s">
-        <v>181</v>
+      <c r="X103" s="55" t="s">
+        <v>612</v>
+      </c>
+      <c r="Y103" s="56" t="s">
+        <v>596</v>
+      </c>
+      <c r="Z103" s="55" t="s">
+        <v>613</v>
+      </c>
+      <c r="AA103" s="56" t="s">
+        <v>600</v>
+      </c>
+      <c r="AB103" s="55" t="s">
+        <v>614</v>
+      </c>
+      <c r="AC103" s="56" t="s">
+        <v>603</v>
+      </c>
+      <c r="AD103" s="55" t="s">
+        <v>615</v>
+      </c>
+      <c r="AE103" s="56" t="s">
+        <v>606</v>
+      </c>
+      <c r="AF103" s="55" t="s">
+        <v>616</v>
+      </c>
+      <c r="AG103" s="56" t="s">
+        <v>609</v>
       </c>
     </row>
-    <row r="104" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="104" spans="1:33" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A104" s="9">
         <v>104</v>
       </c>
@@ -15626,14 +18892,38 @@
       <c r="W104" s="46" t="s">
         <v>181</v>
       </c>
-      <c r="X104" s="45" t="s">
-        <v>181</v>
-      </c>
-      <c r="Y104" s="46" t="s">
-        <v>181</v>
+      <c r="X104" s="55" t="s">
+        <v>612</v>
+      </c>
+      <c r="Y104" s="56" t="s">
+        <v>596</v>
+      </c>
+      <c r="Z104" s="55" t="s">
+        <v>613</v>
+      </c>
+      <c r="AA104" s="56" t="s">
+        <v>600</v>
+      </c>
+      <c r="AB104" s="55" t="s">
+        <v>614</v>
+      </c>
+      <c r="AC104" s="56" t="s">
+        <v>603</v>
+      </c>
+      <c r="AD104" s="55" t="s">
+        <v>615</v>
+      </c>
+      <c r="AE104" s="56" t="s">
+        <v>606</v>
+      </c>
+      <c r="AF104" s="55" t="s">
+        <v>616</v>
+      </c>
+      <c r="AG104" s="56" t="s">
+        <v>609</v>
       </c>
     </row>
-    <row r="105" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="105" spans="1:33" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A105" s="9">
         <v>105</v>
       </c>
@@ -15703,14 +18993,38 @@
       <c r="W105" s="46" t="s">
         <v>181</v>
       </c>
-      <c r="X105" s="45" t="s">
-        <v>181</v>
-      </c>
-      <c r="Y105" s="46" t="s">
-        <v>181</v>
+      <c r="X105" s="55" t="s">
+        <v>612</v>
+      </c>
+      <c r="Y105" s="56" t="s">
+        <v>596</v>
+      </c>
+      <c r="Z105" s="55" t="s">
+        <v>613</v>
+      </c>
+      <c r="AA105" s="56" t="s">
+        <v>600</v>
+      </c>
+      <c r="AB105" s="55" t="s">
+        <v>614</v>
+      </c>
+      <c r="AC105" s="56" t="s">
+        <v>603</v>
+      </c>
+      <c r="AD105" s="55" t="s">
+        <v>615</v>
+      </c>
+      <c r="AE105" s="56" t="s">
+        <v>606</v>
+      </c>
+      <c r="AF105" s="55" t="s">
+        <v>616</v>
+      </c>
+      <c r="AG105" s="56" t="s">
+        <v>609</v>
       </c>
     </row>
-    <row r="106" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="106" spans="1:33" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A106" s="9">
         <v>106</v>
       </c>
@@ -15780,14 +19094,38 @@
       <c r="W106" s="46" t="s">
         <v>181</v>
       </c>
-      <c r="X106" s="45" t="s">
-        <v>181</v>
-      </c>
-      <c r="Y106" s="46" t="s">
-        <v>181</v>
+      <c r="X106" s="55" t="s">
+        <v>612</v>
+      </c>
+      <c r="Y106" s="56" t="s">
+        <v>596</v>
+      </c>
+      <c r="Z106" s="55" t="s">
+        <v>613</v>
+      </c>
+      <c r="AA106" s="56" t="s">
+        <v>600</v>
+      </c>
+      <c r="AB106" s="55" t="s">
+        <v>614</v>
+      </c>
+      <c r="AC106" s="56" t="s">
+        <v>603</v>
+      </c>
+      <c r="AD106" s="55" t="s">
+        <v>615</v>
+      </c>
+      <c r="AE106" s="56" t="s">
+        <v>606</v>
+      </c>
+      <c r="AF106" s="55" t="s">
+        <v>616</v>
+      </c>
+      <c r="AG106" s="56" t="s">
+        <v>609</v>
       </c>
     </row>
-    <row r="107" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="107" spans="1:33" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A107" s="9">
         <v>107</v>
       </c>
@@ -15857,14 +19195,38 @@
       <c r="W107" s="46" t="s">
         <v>181</v>
       </c>
-      <c r="X107" s="45" t="s">
-        <v>181</v>
-      </c>
-      <c r="Y107" s="46" t="s">
-        <v>181</v>
+      <c r="X107" s="55" t="s">
+        <v>612</v>
+      </c>
+      <c r="Y107" s="56" t="s">
+        <v>596</v>
+      </c>
+      <c r="Z107" s="55" t="s">
+        <v>613</v>
+      </c>
+      <c r="AA107" s="56" t="s">
+        <v>600</v>
+      </c>
+      <c r="AB107" s="55" t="s">
+        <v>614</v>
+      </c>
+      <c r="AC107" s="56" t="s">
+        <v>603</v>
+      </c>
+      <c r="AD107" s="55" t="s">
+        <v>615</v>
+      </c>
+      <c r="AE107" s="56" t="s">
+        <v>606</v>
+      </c>
+      <c r="AF107" s="55" t="s">
+        <v>616</v>
+      </c>
+      <c r="AG107" s="56" t="s">
+        <v>609</v>
       </c>
     </row>
-    <row r="108" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="108" spans="1:33" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A108" s="9">
         <v>108</v>
       </c>
@@ -15934,14 +19296,38 @@
       <c r="W108" s="46" t="s">
         <v>181</v>
       </c>
-      <c r="X108" s="45" t="s">
-        <v>181</v>
-      </c>
-      <c r="Y108" s="46" t="s">
-        <v>181</v>
+      <c r="X108" s="55" t="s">
+        <v>612</v>
+      </c>
+      <c r="Y108" s="56" t="s">
+        <v>596</v>
+      </c>
+      <c r="Z108" s="55" t="s">
+        <v>613</v>
+      </c>
+      <c r="AA108" s="56" t="s">
+        <v>600</v>
+      </c>
+      <c r="AB108" s="55" t="s">
+        <v>614</v>
+      </c>
+      <c r="AC108" s="56" t="s">
+        <v>603</v>
+      </c>
+      <c r="AD108" s="55" t="s">
+        <v>615</v>
+      </c>
+      <c r="AE108" s="56" t="s">
+        <v>606</v>
+      </c>
+      <c r="AF108" s="55" t="s">
+        <v>616</v>
+      </c>
+      <c r="AG108" s="56" t="s">
+        <v>609</v>
       </c>
     </row>
-    <row r="109" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="109" spans="1:33" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A109" s="9">
         <v>109</v>
       </c>
@@ -16011,14 +19397,38 @@
       <c r="W109" s="46" t="s">
         <v>181</v>
       </c>
-      <c r="X109" s="45" t="s">
-        <v>181</v>
-      </c>
-      <c r="Y109" s="46" t="s">
-        <v>181</v>
+      <c r="X109" s="55" t="s">
+        <v>612</v>
+      </c>
+      <c r="Y109" s="56" t="s">
+        <v>596</v>
+      </c>
+      <c r="Z109" s="55" t="s">
+        <v>613</v>
+      </c>
+      <c r="AA109" s="56" t="s">
+        <v>600</v>
+      </c>
+      <c r="AB109" s="55" t="s">
+        <v>614</v>
+      </c>
+      <c r="AC109" s="56" t="s">
+        <v>603</v>
+      </c>
+      <c r="AD109" s="55" t="s">
+        <v>615</v>
+      </c>
+      <c r="AE109" s="56" t="s">
+        <v>606</v>
+      </c>
+      <c r="AF109" s="55" t="s">
+        <v>616</v>
+      </c>
+      <c r="AG109" s="56" t="s">
+        <v>609</v>
       </c>
     </row>
-    <row r="110" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="110" spans="1:33" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A110" s="9">
         <v>110</v>
       </c>
@@ -16088,14 +19498,38 @@
       <c r="W110" s="46" t="s">
         <v>181</v>
       </c>
-      <c r="X110" s="45" t="s">
-        <v>181</v>
-      </c>
-      <c r="Y110" s="46" t="s">
-        <v>181</v>
+      <c r="X110" s="55" t="s">
+        <v>612</v>
+      </c>
+      <c r="Y110" s="56" t="s">
+        <v>596</v>
+      </c>
+      <c r="Z110" s="55" t="s">
+        <v>613</v>
+      </c>
+      <c r="AA110" s="56" t="s">
+        <v>600</v>
+      </c>
+      <c r="AB110" s="55" t="s">
+        <v>614</v>
+      </c>
+      <c r="AC110" s="56" t="s">
+        <v>603</v>
+      </c>
+      <c r="AD110" s="55" t="s">
+        <v>615</v>
+      </c>
+      <c r="AE110" s="56" t="s">
+        <v>606</v>
+      </c>
+      <c r="AF110" s="55" t="s">
+        <v>616</v>
+      </c>
+      <c r="AG110" s="56" t="s">
+        <v>609</v>
       </c>
     </row>
-    <row r="111" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="111" spans="1:33" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A111" s="9">
         <v>111</v>
       </c>
@@ -16165,14 +19599,38 @@
       <c r="W111" s="46" t="s">
         <v>181</v>
       </c>
-      <c r="X111" s="45" t="s">
-        <v>181</v>
-      </c>
-      <c r="Y111" s="46" t="s">
-        <v>181</v>
+      <c r="X111" s="55" t="s">
+        <v>612</v>
+      </c>
+      <c r="Y111" s="56" t="s">
+        <v>596</v>
+      </c>
+      <c r="Z111" s="55" t="s">
+        <v>613</v>
+      </c>
+      <c r="AA111" s="56" t="s">
+        <v>600</v>
+      </c>
+      <c r="AB111" s="55" t="s">
+        <v>614</v>
+      </c>
+      <c r="AC111" s="56" t="s">
+        <v>603</v>
+      </c>
+      <c r="AD111" s="55" t="s">
+        <v>615</v>
+      </c>
+      <c r="AE111" s="56" t="s">
+        <v>606</v>
+      </c>
+      <c r="AF111" s="55" t="s">
+        <v>616</v>
+      </c>
+      <c r="AG111" s="56" t="s">
+        <v>609</v>
       </c>
     </row>
-    <row r="112" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="112" spans="1:33" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A112" s="9">
         <v>112</v>
       </c>
@@ -16242,14 +19700,38 @@
       <c r="W112" s="46" t="s">
         <v>181</v>
       </c>
-      <c r="X112" s="45" t="s">
-        <v>181</v>
-      </c>
-      <c r="Y112" s="46" t="s">
-        <v>181</v>
+      <c r="X112" s="55" t="s">
+        <v>612</v>
+      </c>
+      <c r="Y112" s="56" t="s">
+        <v>596</v>
+      </c>
+      <c r="Z112" s="55" t="s">
+        <v>613</v>
+      </c>
+      <c r="AA112" s="56" t="s">
+        <v>600</v>
+      </c>
+      <c r="AB112" s="55" t="s">
+        <v>614</v>
+      </c>
+      <c r="AC112" s="56" t="s">
+        <v>603</v>
+      </c>
+      <c r="AD112" s="55" t="s">
+        <v>615</v>
+      </c>
+      <c r="AE112" s="56" t="s">
+        <v>606</v>
+      </c>
+      <c r="AF112" s="55" t="s">
+        <v>616</v>
+      </c>
+      <c r="AG112" s="56" t="s">
+        <v>609</v>
       </c>
     </row>
-    <row r="113" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="113" spans="1:33" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A113" s="9">
         <v>113</v>
       </c>
@@ -16319,14 +19801,38 @@
       <c r="W113" s="46" t="s">
         <v>181</v>
       </c>
-      <c r="X113" s="45" t="s">
-        <v>181</v>
-      </c>
-      <c r="Y113" s="46" t="s">
-        <v>181</v>
+      <c r="X113" s="55" t="s">
+        <v>612</v>
+      </c>
+      <c r="Y113" s="56" t="s">
+        <v>596</v>
+      </c>
+      <c r="Z113" s="55" t="s">
+        <v>613</v>
+      </c>
+      <c r="AA113" s="56" t="s">
+        <v>600</v>
+      </c>
+      <c r="AB113" s="55" t="s">
+        <v>614</v>
+      </c>
+      <c r="AC113" s="56" t="s">
+        <v>603</v>
+      </c>
+      <c r="AD113" s="55" t="s">
+        <v>615</v>
+      </c>
+      <c r="AE113" s="56" t="s">
+        <v>606</v>
+      </c>
+      <c r="AF113" s="55" t="s">
+        <v>616</v>
+      </c>
+      <c r="AG113" s="56" t="s">
+        <v>609</v>
       </c>
     </row>
-    <row r="114" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="114" spans="1:33" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A114" s="9">
         <v>114</v>
       </c>
@@ -16396,14 +19902,38 @@
       <c r="W114" s="46" t="s">
         <v>181</v>
       </c>
-      <c r="X114" s="45" t="s">
-        <v>181</v>
-      </c>
-      <c r="Y114" s="46" t="s">
-        <v>181</v>
+      <c r="X114" s="55" t="s">
+        <v>612</v>
+      </c>
+      <c r="Y114" s="56" t="s">
+        <v>596</v>
+      </c>
+      <c r="Z114" s="55" t="s">
+        <v>613</v>
+      </c>
+      <c r="AA114" s="56" t="s">
+        <v>600</v>
+      </c>
+      <c r="AB114" s="55" t="s">
+        <v>614</v>
+      </c>
+      <c r="AC114" s="56" t="s">
+        <v>603</v>
+      </c>
+      <c r="AD114" s="55" t="s">
+        <v>615</v>
+      </c>
+      <c r="AE114" s="56" t="s">
+        <v>606</v>
+      </c>
+      <c r="AF114" s="55" t="s">
+        <v>616</v>
+      </c>
+      <c r="AG114" s="56" t="s">
+        <v>609</v>
       </c>
     </row>
-    <row r="115" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="115" spans="1:33" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A115" s="9">
         <v>115</v>
       </c>
@@ -16473,14 +20003,38 @@
       <c r="W115" s="46" t="s">
         <v>181</v>
       </c>
-      <c r="X115" s="45" t="s">
-        <v>181</v>
-      </c>
-      <c r="Y115" s="46" t="s">
-        <v>181</v>
+      <c r="X115" s="55" t="s">
+        <v>612</v>
+      </c>
+      <c r="Y115" s="56" t="s">
+        <v>596</v>
+      </c>
+      <c r="Z115" s="55" t="s">
+        <v>613</v>
+      </c>
+      <c r="AA115" s="56" t="s">
+        <v>600</v>
+      </c>
+      <c r="AB115" s="55" t="s">
+        <v>614</v>
+      </c>
+      <c r="AC115" s="56" t="s">
+        <v>603</v>
+      </c>
+      <c r="AD115" s="55" t="s">
+        <v>615</v>
+      </c>
+      <c r="AE115" s="56" t="s">
+        <v>606</v>
+      </c>
+      <c r="AF115" s="55" t="s">
+        <v>616</v>
+      </c>
+      <c r="AG115" s="56" t="s">
+        <v>609</v>
       </c>
     </row>
-    <row r="116" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="116" spans="1:33" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A116" s="9">
         <v>116</v>
       </c>
@@ -16550,14 +20104,38 @@
       <c r="W116" s="46" t="s">
         <v>181</v>
       </c>
-      <c r="X116" s="45" t="s">
-        <v>181</v>
-      </c>
-      <c r="Y116" s="46" t="s">
-        <v>181</v>
+      <c r="X116" s="55" t="s">
+        <v>612</v>
+      </c>
+      <c r="Y116" s="56" t="s">
+        <v>596</v>
+      </c>
+      <c r="Z116" s="55" t="s">
+        <v>613</v>
+      </c>
+      <c r="AA116" s="56" t="s">
+        <v>600</v>
+      </c>
+      <c r="AB116" s="55" t="s">
+        <v>614</v>
+      </c>
+      <c r="AC116" s="56" t="s">
+        <v>603</v>
+      </c>
+      <c r="AD116" s="55" t="s">
+        <v>615</v>
+      </c>
+      <c r="AE116" s="56" t="s">
+        <v>606</v>
+      </c>
+      <c r="AF116" s="55" t="s">
+        <v>616</v>
+      </c>
+      <c r="AG116" s="56" t="s">
+        <v>609</v>
       </c>
     </row>
-    <row r="117" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="117" spans="1:33" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A117" s="9">
         <v>117</v>
       </c>
@@ -16627,14 +20205,38 @@
       <c r="W117" s="46" t="s">
         <v>181</v>
       </c>
-      <c r="X117" s="45" t="s">
-        <v>181</v>
-      </c>
-      <c r="Y117" s="46" t="s">
-        <v>181</v>
+      <c r="X117" s="55" t="s">
+        <v>612</v>
+      </c>
+      <c r="Y117" s="56" t="s">
+        <v>596</v>
+      </c>
+      <c r="Z117" s="55" t="s">
+        <v>613</v>
+      </c>
+      <c r="AA117" s="56" t="s">
+        <v>600</v>
+      </c>
+      <c r="AB117" s="55" t="s">
+        <v>614</v>
+      </c>
+      <c r="AC117" s="56" t="s">
+        <v>603</v>
+      </c>
+      <c r="AD117" s="55" t="s">
+        <v>615</v>
+      </c>
+      <c r="AE117" s="56" t="s">
+        <v>606</v>
+      </c>
+      <c r="AF117" s="55" t="s">
+        <v>616</v>
+      </c>
+      <c r="AG117" s="56" t="s">
+        <v>609</v>
       </c>
     </row>
-    <row r="118" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="118" spans="1:33" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A118" s="9">
         <v>118</v>
       </c>
@@ -16704,14 +20306,38 @@
       <c r="W118" s="46" t="s">
         <v>181</v>
       </c>
-      <c r="X118" s="45" t="s">
-        <v>181</v>
-      </c>
-      <c r="Y118" s="46" t="s">
-        <v>181</v>
+      <c r="X118" s="55" t="s">
+        <v>612</v>
+      </c>
+      <c r="Y118" s="56" t="s">
+        <v>596</v>
+      </c>
+      <c r="Z118" s="55" t="s">
+        <v>613</v>
+      </c>
+      <c r="AA118" s="56" t="s">
+        <v>600</v>
+      </c>
+      <c r="AB118" s="55" t="s">
+        <v>614</v>
+      </c>
+      <c r="AC118" s="56" t="s">
+        <v>603</v>
+      </c>
+      <c r="AD118" s="55" t="s">
+        <v>615</v>
+      </c>
+      <c r="AE118" s="56" t="s">
+        <v>606</v>
+      </c>
+      <c r="AF118" s="55" t="s">
+        <v>616</v>
+      </c>
+      <c r="AG118" s="56" t="s">
+        <v>609</v>
       </c>
     </row>
-    <row r="119" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="119" spans="1:33" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A119" s="9">
         <v>119</v>
       </c>
@@ -16781,14 +20407,38 @@
       <c r="W119" s="46" t="s">
         <v>181</v>
       </c>
-      <c r="X119" s="45" t="s">
-        <v>181</v>
-      </c>
-      <c r="Y119" s="46" t="s">
-        <v>181</v>
+      <c r="X119" s="55" t="s">
+        <v>612</v>
+      </c>
+      <c r="Y119" s="56" t="s">
+        <v>596</v>
+      </c>
+      <c r="Z119" s="55" t="s">
+        <v>613</v>
+      </c>
+      <c r="AA119" s="56" t="s">
+        <v>600</v>
+      </c>
+      <c r="AB119" s="55" t="s">
+        <v>614</v>
+      </c>
+      <c r="AC119" s="56" t="s">
+        <v>603</v>
+      </c>
+      <c r="AD119" s="55" t="s">
+        <v>615</v>
+      </c>
+      <c r="AE119" s="56" t="s">
+        <v>606</v>
+      </c>
+      <c r="AF119" s="55" t="s">
+        <v>616</v>
+      </c>
+      <c r="AG119" s="56" t="s">
+        <v>609</v>
       </c>
     </row>
-    <row r="120" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="120" spans="1:33" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A120" s="9">
         <v>120</v>
       </c>
@@ -16858,14 +20508,38 @@
       <c r="W120" s="46" t="s">
         <v>181</v>
       </c>
-      <c r="X120" s="45" t="s">
-        <v>181</v>
-      </c>
-      <c r="Y120" s="46" t="s">
-        <v>181</v>
+      <c r="X120" s="55" t="s">
+        <v>612</v>
+      </c>
+      <c r="Y120" s="56" t="s">
+        <v>596</v>
+      </c>
+      <c r="Z120" s="55" t="s">
+        <v>613</v>
+      </c>
+      <c r="AA120" s="56" t="s">
+        <v>600</v>
+      </c>
+      <c r="AB120" s="55" t="s">
+        <v>614</v>
+      </c>
+      <c r="AC120" s="56" t="s">
+        <v>603</v>
+      </c>
+      <c r="AD120" s="55" t="s">
+        <v>615</v>
+      </c>
+      <c r="AE120" s="56" t="s">
+        <v>606</v>
+      </c>
+      <c r="AF120" s="55" t="s">
+        <v>616</v>
+      </c>
+      <c r="AG120" s="56" t="s">
+        <v>609</v>
       </c>
     </row>
-    <row r="121" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="121" spans="1:33" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A121" s="9">
         <v>121</v>
       </c>
@@ -16935,14 +20609,38 @@
       <c r="W121" s="46" t="s">
         <v>181</v>
       </c>
-      <c r="X121" s="45" t="s">
-        <v>181</v>
-      </c>
-      <c r="Y121" s="46" t="s">
-        <v>181</v>
+      <c r="X121" s="55" t="s">
+        <v>612</v>
+      </c>
+      <c r="Y121" s="56" t="s">
+        <v>596</v>
+      </c>
+      <c r="Z121" s="55" t="s">
+        <v>613</v>
+      </c>
+      <c r="AA121" s="56" t="s">
+        <v>600</v>
+      </c>
+      <c r="AB121" s="55" t="s">
+        <v>614</v>
+      </c>
+      <c r="AC121" s="56" t="s">
+        <v>603</v>
+      </c>
+      <c r="AD121" s="55" t="s">
+        <v>615</v>
+      </c>
+      <c r="AE121" s="56" t="s">
+        <v>606</v>
+      </c>
+      <c r="AF121" s="55" t="s">
+        <v>616</v>
+      </c>
+      <c r="AG121" s="56" t="s">
+        <v>609</v>
       </c>
     </row>
-    <row r="122" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="122" spans="1:33" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A122" s="9">
         <v>122</v>
       </c>
@@ -17012,14 +20710,38 @@
       <c r="W122" s="46" t="s">
         <v>181</v>
       </c>
-      <c r="X122" s="45" t="s">
-        <v>181</v>
-      </c>
-      <c r="Y122" s="46" t="s">
-        <v>181</v>
+      <c r="X122" s="55" t="s">
+        <v>612</v>
+      </c>
+      <c r="Y122" s="56" t="s">
+        <v>596</v>
+      </c>
+      <c r="Z122" s="55" t="s">
+        <v>613</v>
+      </c>
+      <c r="AA122" s="56" t="s">
+        <v>600</v>
+      </c>
+      <c r="AB122" s="55" t="s">
+        <v>614</v>
+      </c>
+      <c r="AC122" s="56" t="s">
+        <v>603</v>
+      </c>
+      <c r="AD122" s="55" t="s">
+        <v>615</v>
+      </c>
+      <c r="AE122" s="56" t="s">
+        <v>606</v>
+      </c>
+      <c r="AF122" s="55" t="s">
+        <v>616</v>
+      </c>
+      <c r="AG122" s="56" t="s">
+        <v>609</v>
       </c>
     </row>
-    <row r="123" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="123" spans="1:33" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A123" s="9">
         <v>123</v>
       </c>
@@ -17089,14 +20811,38 @@
       <c r="W123" s="46" t="s">
         <v>181</v>
       </c>
-      <c r="X123" s="45" t="s">
-        <v>181</v>
-      </c>
-      <c r="Y123" s="46" t="s">
-        <v>181</v>
+      <c r="X123" s="55" t="s">
+        <v>612</v>
+      </c>
+      <c r="Y123" s="56" t="s">
+        <v>596</v>
+      </c>
+      <c r="Z123" s="55" t="s">
+        <v>613</v>
+      </c>
+      <c r="AA123" s="56" t="s">
+        <v>600</v>
+      </c>
+      <c r="AB123" s="55" t="s">
+        <v>614</v>
+      </c>
+      <c r="AC123" s="56" t="s">
+        <v>603</v>
+      </c>
+      <c r="AD123" s="55" t="s">
+        <v>615</v>
+      </c>
+      <c r="AE123" s="56" t="s">
+        <v>606</v>
+      </c>
+      <c r="AF123" s="55" t="s">
+        <v>616</v>
+      </c>
+      <c r="AG123" s="56" t="s">
+        <v>609</v>
       </c>
     </row>
-    <row r="124" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="124" spans="1:33" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A124" s="9">
         <v>124</v>
       </c>
@@ -17166,14 +20912,38 @@
       <c r="W124" s="46" t="s">
         <v>181</v>
       </c>
-      <c r="X124" s="45" t="s">
-        <v>181</v>
-      </c>
-      <c r="Y124" s="46" t="s">
-        <v>181</v>
+      <c r="X124" s="55" t="s">
+        <v>612</v>
+      </c>
+      <c r="Y124" s="56" t="s">
+        <v>596</v>
+      </c>
+      <c r="Z124" s="55" t="s">
+        <v>613</v>
+      </c>
+      <c r="AA124" s="56" t="s">
+        <v>600</v>
+      </c>
+      <c r="AB124" s="55" t="s">
+        <v>614</v>
+      </c>
+      <c r="AC124" s="56" t="s">
+        <v>603</v>
+      </c>
+      <c r="AD124" s="55" t="s">
+        <v>615</v>
+      </c>
+      <c r="AE124" s="56" t="s">
+        <v>606</v>
+      </c>
+      <c r="AF124" s="55" t="s">
+        <v>616</v>
+      </c>
+      <c r="AG124" s="56" t="s">
+        <v>609</v>
       </c>
     </row>
-    <row r="125" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="125" spans="1:33" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A125" s="9">
         <v>125</v>
       </c>
@@ -17243,14 +21013,38 @@
       <c r="W125" s="46" t="s">
         <v>181</v>
       </c>
-      <c r="X125" s="45" t="s">
-        <v>181</v>
-      </c>
-      <c r="Y125" s="46" t="s">
-        <v>181</v>
+      <c r="X125" s="55" t="s">
+        <v>612</v>
+      </c>
+      <c r="Y125" s="56" t="s">
+        <v>596</v>
+      </c>
+      <c r="Z125" s="55" t="s">
+        <v>613</v>
+      </c>
+      <c r="AA125" s="56" t="s">
+        <v>600</v>
+      </c>
+      <c r="AB125" s="55" t="s">
+        <v>614</v>
+      </c>
+      <c r="AC125" s="56" t="s">
+        <v>603</v>
+      </c>
+      <c r="AD125" s="55" t="s">
+        <v>615</v>
+      </c>
+      <c r="AE125" s="56" t="s">
+        <v>606</v>
+      </c>
+      <c r="AF125" s="55" t="s">
+        <v>616</v>
+      </c>
+      <c r="AG125" s="56" t="s">
+        <v>609</v>
       </c>
     </row>
-    <row r="126" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="126" spans="1:33" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A126" s="9">
         <v>126</v>
       </c>
@@ -17320,14 +21114,38 @@
       <c r="W126" s="46" t="s">
         <v>181</v>
       </c>
-      <c r="X126" s="45" t="s">
-        <v>181</v>
-      </c>
-      <c r="Y126" s="46" t="s">
-        <v>181</v>
+      <c r="X126" s="55" t="s">
+        <v>612</v>
+      </c>
+      <c r="Y126" s="56" t="s">
+        <v>596</v>
+      </c>
+      <c r="Z126" s="55" t="s">
+        <v>613</v>
+      </c>
+      <c r="AA126" s="56" t="s">
+        <v>600</v>
+      </c>
+      <c r="AB126" s="55" t="s">
+        <v>614</v>
+      </c>
+      <c r="AC126" s="56" t="s">
+        <v>603</v>
+      </c>
+      <c r="AD126" s="55" t="s">
+        <v>615</v>
+      </c>
+      <c r="AE126" s="56" t="s">
+        <v>606</v>
+      </c>
+      <c r="AF126" s="55" t="s">
+        <v>616</v>
+      </c>
+      <c r="AG126" s="56" t="s">
+        <v>609</v>
       </c>
     </row>
-    <row r="127" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="127" spans="1:33" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A127" s="9">
         <v>127</v>
       </c>
@@ -17397,14 +21215,38 @@
       <c r="W127" s="46" t="s">
         <v>181</v>
       </c>
-      <c r="X127" s="45" t="s">
-        <v>181</v>
-      </c>
-      <c r="Y127" s="46" t="s">
-        <v>181</v>
+      <c r="X127" s="55" t="s">
+        <v>612</v>
+      </c>
+      <c r="Y127" s="56" t="s">
+        <v>596</v>
+      </c>
+      <c r="Z127" s="55" t="s">
+        <v>613</v>
+      </c>
+      <c r="AA127" s="56" t="s">
+        <v>600</v>
+      </c>
+      <c r="AB127" s="55" t="s">
+        <v>614</v>
+      </c>
+      <c r="AC127" s="56" t="s">
+        <v>603</v>
+      </c>
+      <c r="AD127" s="55" t="s">
+        <v>615</v>
+      </c>
+      <c r="AE127" s="56" t="s">
+        <v>606</v>
+      </c>
+      <c r="AF127" s="55" t="s">
+        <v>616</v>
+      </c>
+      <c r="AG127" s="56" t="s">
+        <v>609</v>
       </c>
     </row>
-    <row r="128" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="128" spans="1:33" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A128" s="9">
         <v>128</v>
       </c>
@@ -17474,14 +21316,38 @@
       <c r="W128" s="46" t="s">
         <v>181</v>
       </c>
-      <c r="X128" s="45" t="s">
-        <v>181</v>
-      </c>
-      <c r="Y128" s="46" t="s">
-        <v>181</v>
+      <c r="X128" s="55" t="s">
+        <v>612</v>
+      </c>
+      <c r="Y128" s="56" t="s">
+        <v>596</v>
+      </c>
+      <c r="Z128" s="55" t="s">
+        <v>613</v>
+      </c>
+      <c r="AA128" s="56" t="s">
+        <v>600</v>
+      </c>
+      <c r="AB128" s="55" t="s">
+        <v>614</v>
+      </c>
+      <c r="AC128" s="56" t="s">
+        <v>603</v>
+      </c>
+      <c r="AD128" s="55" t="s">
+        <v>615</v>
+      </c>
+      <c r="AE128" s="56" t="s">
+        <v>606</v>
+      </c>
+      <c r="AF128" s="55" t="s">
+        <v>616</v>
+      </c>
+      <c r="AG128" s="56" t="s">
+        <v>609</v>
       </c>
     </row>
-    <row r="129" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="129" spans="1:33" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A129" s="9">
         <v>129</v>
       </c>
@@ -17551,14 +21417,38 @@
       <c r="W129" s="46" t="s">
         <v>181</v>
       </c>
-      <c r="X129" s="45" t="s">
-        <v>181</v>
-      </c>
-      <c r="Y129" s="46" t="s">
-        <v>181</v>
+      <c r="X129" s="55" t="s">
+        <v>612</v>
+      </c>
+      <c r="Y129" s="56" t="s">
+        <v>596</v>
+      </c>
+      <c r="Z129" s="55" t="s">
+        <v>613</v>
+      </c>
+      <c r="AA129" s="56" t="s">
+        <v>600</v>
+      </c>
+      <c r="AB129" s="55" t="s">
+        <v>614</v>
+      </c>
+      <c r="AC129" s="56" t="s">
+        <v>603</v>
+      </c>
+      <c r="AD129" s="55" t="s">
+        <v>615</v>
+      </c>
+      <c r="AE129" s="56" t="s">
+        <v>606</v>
+      </c>
+      <c r="AF129" s="55" t="s">
+        <v>616</v>
+      </c>
+      <c r="AG129" s="56" t="s">
+        <v>609</v>
       </c>
     </row>
-    <row r="130" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="130" spans="1:33" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A130" s="9">
         <v>130</v>
       </c>
@@ -17628,14 +21518,38 @@
       <c r="W130" s="46" t="s">
         <v>181</v>
       </c>
-      <c r="X130" s="45" t="s">
-        <v>181</v>
-      </c>
-      <c r="Y130" s="46" t="s">
-        <v>181</v>
+      <c r="X130" s="55" t="s">
+        <v>612</v>
+      </c>
+      <c r="Y130" s="56" t="s">
+        <v>596</v>
+      </c>
+      <c r="Z130" s="55" t="s">
+        <v>613</v>
+      </c>
+      <c r="AA130" s="56" t="s">
+        <v>600</v>
+      </c>
+      <c r="AB130" s="55" t="s">
+        <v>614</v>
+      </c>
+      <c r="AC130" s="56" t="s">
+        <v>603</v>
+      </c>
+      <c r="AD130" s="55" t="s">
+        <v>615</v>
+      </c>
+      <c r="AE130" s="56" t="s">
+        <v>606</v>
+      </c>
+      <c r="AF130" s="55" t="s">
+        <v>616</v>
+      </c>
+      <c r="AG130" s="56" t="s">
+        <v>609</v>
       </c>
     </row>
-    <row r="131" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="131" spans="1:33" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A131" s="9">
         <v>131</v>
       </c>
@@ -17705,14 +21619,38 @@
       <c r="W131" s="46" t="s">
         <v>181</v>
       </c>
-      <c r="X131" s="45" t="s">
-        <v>181</v>
-      </c>
-      <c r="Y131" s="46" t="s">
-        <v>181</v>
+      <c r="X131" s="55" t="s">
+        <v>612</v>
+      </c>
+      <c r="Y131" s="56" t="s">
+        <v>596</v>
+      </c>
+      <c r="Z131" s="55" t="s">
+        <v>613</v>
+      </c>
+      <c r="AA131" s="56" t="s">
+        <v>600</v>
+      </c>
+      <c r="AB131" s="55" t="s">
+        <v>614</v>
+      </c>
+      <c r="AC131" s="56" t="s">
+        <v>603</v>
+      </c>
+      <c r="AD131" s="55" t="s">
+        <v>615</v>
+      </c>
+      <c r="AE131" s="56" t="s">
+        <v>606</v>
+      </c>
+      <c r="AF131" s="55" t="s">
+        <v>616</v>
+      </c>
+      <c r="AG131" s="56" t="s">
+        <v>609</v>
       </c>
     </row>
-    <row r="132" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="132" spans="1:33" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A132" s="9">
         <v>132</v>
       </c>
@@ -17782,14 +21720,38 @@
       <c r="W132" s="46" t="s">
         <v>181</v>
       </c>
-      <c r="X132" s="45" t="s">
-        <v>181</v>
-      </c>
-      <c r="Y132" s="46" t="s">
-        <v>181</v>
+      <c r="X132" s="55" t="s">
+        <v>612</v>
+      </c>
+      <c r="Y132" s="56" t="s">
+        <v>596</v>
+      </c>
+      <c r="Z132" s="55" t="s">
+        <v>613</v>
+      </c>
+      <c r="AA132" s="56" t="s">
+        <v>600</v>
+      </c>
+      <c r="AB132" s="55" t="s">
+        <v>614</v>
+      </c>
+      <c r="AC132" s="56" t="s">
+        <v>603</v>
+      </c>
+      <c r="AD132" s="55" t="s">
+        <v>615</v>
+      </c>
+      <c r="AE132" s="56" t="s">
+        <v>606</v>
+      </c>
+      <c r="AF132" s="55" t="s">
+        <v>616</v>
+      </c>
+      <c r="AG132" s="56" t="s">
+        <v>609</v>
       </c>
     </row>
-    <row r="133" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="133" spans="1:33" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A133" s="9">
         <v>133</v>
       </c>
@@ -17859,14 +21821,38 @@
       <c r="W133" s="46" t="s">
         <v>181</v>
       </c>
-      <c r="X133" s="45" t="s">
-        <v>181</v>
-      </c>
-      <c r="Y133" s="46" t="s">
-        <v>181</v>
+      <c r="X133" s="55" t="s">
+        <v>612</v>
+      </c>
+      <c r="Y133" s="56" t="s">
+        <v>596</v>
+      </c>
+      <c r="Z133" s="55" t="s">
+        <v>613</v>
+      </c>
+      <c r="AA133" s="56" t="s">
+        <v>600</v>
+      </c>
+      <c r="AB133" s="55" t="s">
+        <v>614</v>
+      </c>
+      <c r="AC133" s="56" t="s">
+        <v>603</v>
+      </c>
+      <c r="AD133" s="55" t="s">
+        <v>615</v>
+      </c>
+      <c r="AE133" s="56" t="s">
+        <v>606</v>
+      </c>
+      <c r="AF133" s="55" t="s">
+        <v>616</v>
+      </c>
+      <c r="AG133" s="56" t="s">
+        <v>609</v>
       </c>
     </row>
-    <row r="134" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="134" spans="1:33" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A134" s="9">
         <v>134</v>
       </c>
@@ -17936,14 +21922,38 @@
       <c r="W134" s="46" t="s">
         <v>181</v>
       </c>
-      <c r="X134" s="45" t="s">
-        <v>181</v>
-      </c>
-      <c r="Y134" s="46" t="s">
-        <v>181</v>
+      <c r="X134" s="55" t="s">
+        <v>612</v>
+      </c>
+      <c r="Y134" s="56" t="s">
+        <v>596</v>
+      </c>
+      <c r="Z134" s="55" t="s">
+        <v>613</v>
+      </c>
+      <c r="AA134" s="56" t="s">
+        <v>600</v>
+      </c>
+      <c r="AB134" s="55" t="s">
+        <v>614</v>
+      </c>
+      <c r="AC134" s="56" t="s">
+        <v>603</v>
+      </c>
+      <c r="AD134" s="55" t="s">
+        <v>615</v>
+      </c>
+      <c r="AE134" s="56" t="s">
+        <v>606</v>
+      </c>
+      <c r="AF134" s="55" t="s">
+        <v>616</v>
+      </c>
+      <c r="AG134" s="56" t="s">
+        <v>609</v>
       </c>
     </row>
-    <row r="135" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="135" spans="1:33" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A135" s="9">
         <v>135</v>
       </c>
@@ -18013,14 +22023,38 @@
       <c r="W135" s="46" t="s">
         <v>181</v>
       </c>
-      <c r="X135" s="45" t="s">
-        <v>181</v>
-      </c>
-      <c r="Y135" s="46" t="s">
-        <v>181</v>
+      <c r="X135" s="55" t="s">
+        <v>612</v>
+      </c>
+      <c r="Y135" s="56" t="s">
+        <v>596</v>
+      </c>
+      <c r="Z135" s="55" t="s">
+        <v>613</v>
+      </c>
+      <c r="AA135" s="56" t="s">
+        <v>600</v>
+      </c>
+      <c r="AB135" s="55" t="s">
+        <v>614</v>
+      </c>
+      <c r="AC135" s="56" t="s">
+        <v>603</v>
+      </c>
+      <c r="AD135" s="55" t="s">
+        <v>615</v>
+      </c>
+      <c r="AE135" s="56" t="s">
+        <v>606</v>
+      </c>
+      <c r="AF135" s="55" t="s">
+        <v>616</v>
+      </c>
+      <c r="AG135" s="56" t="s">
+        <v>609</v>
       </c>
     </row>
-    <row r="136" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="136" spans="1:33" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A136" s="9">
         <v>136</v>
       </c>
@@ -18090,14 +22124,38 @@
       <c r="W136" s="46" t="s">
         <v>181</v>
       </c>
-      <c r="X136" s="45" t="s">
-        <v>181</v>
-      </c>
-      <c r="Y136" s="46" t="s">
-        <v>181</v>
+      <c r="X136" s="55" t="s">
+        <v>612</v>
+      </c>
+      <c r="Y136" s="56" t="s">
+        <v>596</v>
+      </c>
+      <c r="Z136" s="55" t="s">
+        <v>613</v>
+      </c>
+      <c r="AA136" s="56" t="s">
+        <v>600</v>
+      </c>
+      <c r="AB136" s="55" t="s">
+        <v>614</v>
+      </c>
+      <c r="AC136" s="56" t="s">
+        <v>603</v>
+      </c>
+      <c r="AD136" s="55" t="s">
+        <v>615</v>
+      </c>
+      <c r="AE136" s="56" t="s">
+        <v>606</v>
+      </c>
+      <c r="AF136" s="55" t="s">
+        <v>616</v>
+      </c>
+      <c r="AG136" s="56" t="s">
+        <v>609</v>
       </c>
     </row>
-    <row r="137" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="137" spans="1:33" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A137" s="9">
         <v>137</v>
       </c>
@@ -18167,14 +22225,38 @@
       <c r="W137" s="46" t="s">
         <v>181</v>
       </c>
-      <c r="X137" s="45" t="s">
-        <v>181</v>
-      </c>
-      <c r="Y137" s="46" t="s">
-        <v>181</v>
+      <c r="X137" s="55" t="s">
+        <v>612</v>
+      </c>
+      <c r="Y137" s="56" t="s">
+        <v>596</v>
+      </c>
+      <c r="Z137" s="55" t="s">
+        <v>613</v>
+      </c>
+      <c r="AA137" s="56" t="s">
+        <v>600</v>
+      </c>
+      <c r="AB137" s="55" t="s">
+        <v>614</v>
+      </c>
+      <c r="AC137" s="56" t="s">
+        <v>603</v>
+      </c>
+      <c r="AD137" s="55" t="s">
+        <v>615</v>
+      </c>
+      <c r="AE137" s="56" t="s">
+        <v>606</v>
+      </c>
+      <c r="AF137" s="55" t="s">
+        <v>616</v>
+      </c>
+      <c r="AG137" s="56" t="s">
+        <v>609</v>
       </c>
     </row>
-    <row r="138" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="138" spans="1:33" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A138" s="9">
         <v>138</v>
       </c>
@@ -18244,14 +22326,38 @@
       <c r="W138" s="46" t="s">
         <v>181</v>
       </c>
-      <c r="X138" s="45" t="s">
-        <v>181</v>
-      </c>
-      <c r="Y138" s="46" t="s">
-        <v>181</v>
+      <c r="X138" s="55" t="s">
+        <v>612</v>
+      </c>
+      <c r="Y138" s="56" t="s">
+        <v>596</v>
+      </c>
+      <c r="Z138" s="55" t="s">
+        <v>613</v>
+      </c>
+      <c r="AA138" s="56" t="s">
+        <v>600</v>
+      </c>
+      <c r="AB138" s="55" t="s">
+        <v>614</v>
+      </c>
+      <c r="AC138" s="56" t="s">
+        <v>603</v>
+      </c>
+      <c r="AD138" s="55" t="s">
+        <v>615</v>
+      </c>
+      <c r="AE138" s="56" t="s">
+        <v>606</v>
+      </c>
+      <c r="AF138" s="55" t="s">
+        <v>616</v>
+      </c>
+      <c r="AG138" s="56" t="s">
+        <v>609</v>
       </c>
     </row>
-    <row r="139" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="139" spans="1:33" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A139" s="9">
         <v>139</v>
       </c>
@@ -18321,14 +22427,38 @@
       <c r="W139" s="46" t="s">
         <v>181</v>
       </c>
-      <c r="X139" s="45" t="s">
-        <v>181</v>
-      </c>
-      <c r="Y139" s="46" t="s">
-        <v>181</v>
+      <c r="X139" s="55" t="s">
+        <v>612</v>
+      </c>
+      <c r="Y139" s="56" t="s">
+        <v>596</v>
+      </c>
+      <c r="Z139" s="55" t="s">
+        <v>613</v>
+      </c>
+      <c r="AA139" s="56" t="s">
+        <v>600</v>
+      </c>
+      <c r="AB139" s="55" t="s">
+        <v>614</v>
+      </c>
+      <c r="AC139" s="56" t="s">
+        <v>603</v>
+      </c>
+      <c r="AD139" s="55" t="s">
+        <v>615</v>
+      </c>
+      <c r="AE139" s="56" t="s">
+        <v>606</v>
+      </c>
+      <c r="AF139" s="55" t="s">
+        <v>616</v>
+      </c>
+      <c r="AG139" s="56" t="s">
+        <v>609</v>
       </c>
     </row>
-    <row r="140" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="140" spans="1:33" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A140" s="9">
         <v>140</v>
       </c>
@@ -18398,14 +22528,38 @@
       <c r="W140" s="46" t="s">
         <v>181</v>
       </c>
-      <c r="X140" s="45" t="s">
-        <v>181</v>
-      </c>
-      <c r="Y140" s="46" t="s">
-        <v>181</v>
+      <c r="X140" s="55" t="s">
+        <v>612</v>
+      </c>
+      <c r="Y140" s="56" t="s">
+        <v>596</v>
+      </c>
+      <c r="Z140" s="55" t="s">
+        <v>613</v>
+      </c>
+      <c r="AA140" s="56" t="s">
+        <v>600</v>
+      </c>
+      <c r="AB140" s="55" t="s">
+        <v>614</v>
+      </c>
+      <c r="AC140" s="56" t="s">
+        <v>603</v>
+      </c>
+      <c r="AD140" s="55" t="s">
+        <v>615</v>
+      </c>
+      <c r="AE140" s="56" t="s">
+        <v>606</v>
+      </c>
+      <c r="AF140" s="55" t="s">
+        <v>616</v>
+      </c>
+      <c r="AG140" s="56" t="s">
+        <v>609</v>
       </c>
     </row>
-    <row r="141" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="141" spans="1:33" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A141" s="9">
         <v>141</v>
       </c>
@@ -18475,14 +22629,38 @@
       <c r="W141" s="46" t="s">
         <v>181</v>
       </c>
-      <c r="X141" s="45" t="s">
-        <v>181</v>
-      </c>
-      <c r="Y141" s="46" t="s">
-        <v>181</v>
+      <c r="X141" s="55" t="s">
+        <v>612</v>
+      </c>
+      <c r="Y141" s="56" t="s">
+        <v>596</v>
+      </c>
+      <c r="Z141" s="55" t="s">
+        <v>613</v>
+      </c>
+      <c r="AA141" s="56" t="s">
+        <v>600</v>
+      </c>
+      <c r="AB141" s="55" t="s">
+        <v>614</v>
+      </c>
+      <c r="AC141" s="56" t="s">
+        <v>603</v>
+      </c>
+      <c r="AD141" s="55" t="s">
+        <v>615</v>
+      </c>
+      <c r="AE141" s="56" t="s">
+        <v>606</v>
+      </c>
+      <c r="AF141" s="55" t="s">
+        <v>616</v>
+      </c>
+      <c r="AG141" s="56" t="s">
+        <v>609</v>
       </c>
     </row>
-    <row r="142" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="142" spans="1:33" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A142" s="9">
         <v>142</v>
       </c>
@@ -18552,14 +22730,38 @@
       <c r="W142" s="46" t="s">
         <v>181</v>
       </c>
-      <c r="X142" s="45" t="s">
-        <v>181</v>
-      </c>
-      <c r="Y142" s="46" t="s">
-        <v>181</v>
+      <c r="X142" s="55" t="s">
+        <v>612</v>
+      </c>
+      <c r="Y142" s="56" t="s">
+        <v>596</v>
+      </c>
+      <c r="Z142" s="55" t="s">
+        <v>613</v>
+      </c>
+      <c r="AA142" s="56" t="s">
+        <v>600</v>
+      </c>
+      <c r="AB142" s="55" t="s">
+        <v>614</v>
+      </c>
+      <c r="AC142" s="56" t="s">
+        <v>603</v>
+      </c>
+      <c r="AD142" s="55" t="s">
+        <v>615</v>
+      </c>
+      <c r="AE142" s="56" t="s">
+        <v>606</v>
+      </c>
+      <c r="AF142" s="55" t="s">
+        <v>616</v>
+      </c>
+      <c r="AG142" s="56" t="s">
+        <v>609</v>
       </c>
     </row>
-    <row r="143" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="143" spans="1:33" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A143" s="9">
         <v>143</v>
       </c>
@@ -18629,14 +22831,38 @@
       <c r="W143" s="46" t="s">
         <v>181</v>
       </c>
-      <c r="X143" s="45" t="s">
-        <v>181</v>
-      </c>
-      <c r="Y143" s="46" t="s">
-        <v>181</v>
+      <c r="X143" s="55" t="s">
+        <v>612</v>
+      </c>
+      <c r="Y143" s="56" t="s">
+        <v>596</v>
+      </c>
+      <c r="Z143" s="55" t="s">
+        <v>613</v>
+      </c>
+      <c r="AA143" s="56" t="s">
+        <v>600</v>
+      </c>
+      <c r="AB143" s="55" t="s">
+        <v>614</v>
+      </c>
+      <c r="AC143" s="56" t="s">
+        <v>603</v>
+      </c>
+      <c r="AD143" s="55" t="s">
+        <v>615</v>
+      </c>
+      <c r="AE143" s="56" t="s">
+        <v>606</v>
+      </c>
+      <c r="AF143" s="55" t="s">
+        <v>616</v>
+      </c>
+      <c r="AG143" s="56" t="s">
+        <v>609</v>
       </c>
     </row>
-    <row r="144" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="144" spans="1:33" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A144" s="9">
         <v>144</v>
       </c>
@@ -18706,14 +22932,38 @@
       <c r="W144" s="46" t="s">
         <v>181</v>
       </c>
-      <c r="X144" s="45" t="s">
-        <v>181</v>
-      </c>
-      <c r="Y144" s="46" t="s">
-        <v>181</v>
+      <c r="X144" s="55" t="s">
+        <v>612</v>
+      </c>
+      <c r="Y144" s="56" t="s">
+        <v>596</v>
+      </c>
+      <c r="Z144" s="55" t="s">
+        <v>613</v>
+      </c>
+      <c r="AA144" s="56" t="s">
+        <v>600</v>
+      </c>
+      <c r="AB144" s="55" t="s">
+        <v>614</v>
+      </c>
+      <c r="AC144" s="56" t="s">
+        <v>603</v>
+      </c>
+      <c r="AD144" s="55" t="s">
+        <v>615</v>
+      </c>
+      <c r="AE144" s="56" t="s">
+        <v>606</v>
+      </c>
+      <c r="AF144" s="55" t="s">
+        <v>616</v>
+      </c>
+      <c r="AG144" s="56" t="s">
+        <v>609</v>
       </c>
     </row>
-    <row r="145" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="145" spans="1:33" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A145" s="9">
         <v>145</v>
       </c>
@@ -18783,14 +23033,38 @@
       <c r="W145" s="46" t="s">
         <v>181</v>
       </c>
-      <c r="X145" s="45" t="s">
-        <v>181</v>
-      </c>
-      <c r="Y145" s="46" t="s">
-        <v>181</v>
+      <c r="X145" s="55" t="s">
+        <v>612</v>
+      </c>
+      <c r="Y145" s="56" t="s">
+        <v>596</v>
+      </c>
+      <c r="Z145" s="55" t="s">
+        <v>613</v>
+      </c>
+      <c r="AA145" s="56" t="s">
+        <v>600</v>
+      </c>
+      <c r="AB145" s="55" t="s">
+        <v>614</v>
+      </c>
+      <c r="AC145" s="56" t="s">
+        <v>603</v>
+      </c>
+      <c r="AD145" s="55" t="s">
+        <v>615</v>
+      </c>
+      <c r="AE145" s="56" t="s">
+        <v>606</v>
+      </c>
+      <c r="AF145" s="55" t="s">
+        <v>616</v>
+      </c>
+      <c r="AG145" s="56" t="s">
+        <v>609</v>
       </c>
     </row>
-    <row r="146" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="146" spans="1:33" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A146" s="9">
         <v>146</v>
       </c>
@@ -18860,14 +23134,38 @@
       <c r="W146" s="46" t="s">
         <v>181</v>
       </c>
-      <c r="X146" s="45" t="s">
-        <v>181</v>
-      </c>
-      <c r="Y146" s="46" t="s">
-        <v>181</v>
+      <c r="X146" s="55" t="s">
+        <v>612</v>
+      </c>
+      <c r="Y146" s="56" t="s">
+        <v>596</v>
+      </c>
+      <c r="Z146" s="55" t="s">
+        <v>613</v>
+      </c>
+      <c r="AA146" s="56" t="s">
+        <v>600</v>
+      </c>
+      <c r="AB146" s="55" t="s">
+        <v>614</v>
+      </c>
+      <c r="AC146" s="56" t="s">
+        <v>603</v>
+      </c>
+      <c r="AD146" s="55" t="s">
+        <v>615</v>
+      </c>
+      <c r="AE146" s="56" t="s">
+        <v>606</v>
+      </c>
+      <c r="AF146" s="55" t="s">
+        <v>616</v>
+      </c>
+      <c r="AG146" s="56" t="s">
+        <v>609</v>
       </c>
     </row>
-    <row r="147" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="147" spans="1:33" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A147" s="9">
         <v>147</v>
       </c>
@@ -18937,14 +23235,38 @@
       <c r="W147" s="46" t="s">
         <v>181</v>
       </c>
-      <c r="X147" s="45" t="s">
-        <v>181</v>
-      </c>
-      <c r="Y147" s="46" t="s">
-        <v>181</v>
+      <c r="X147" s="55" t="s">
+        <v>612</v>
+      </c>
+      <c r="Y147" s="56" t="s">
+        <v>596</v>
+      </c>
+      <c r="Z147" s="55" t="s">
+        <v>613</v>
+      </c>
+      <c r="AA147" s="56" t="s">
+        <v>600</v>
+      </c>
+      <c r="AB147" s="55" t="s">
+        <v>614</v>
+      </c>
+      <c r="AC147" s="56" t="s">
+        <v>603</v>
+      </c>
+      <c r="AD147" s="55" t="s">
+        <v>615</v>
+      </c>
+      <c r="AE147" s="56" t="s">
+        <v>606</v>
+      </c>
+      <c r="AF147" s="55" t="s">
+        <v>616</v>
+      </c>
+      <c r="AG147" s="56" t="s">
+        <v>609</v>
       </c>
     </row>
-    <row r="148" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="148" spans="1:33" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A148" s="9">
         <v>148</v>
       </c>
@@ -19014,14 +23336,38 @@
       <c r="W148" s="46" t="s">
         <v>181</v>
       </c>
-      <c r="X148" s="45" t="s">
-        <v>181</v>
-      </c>
-      <c r="Y148" s="46" t="s">
-        <v>181</v>
+      <c r="X148" s="55" t="s">
+        <v>612</v>
+      </c>
+      <c r="Y148" s="56" t="s">
+        <v>596</v>
+      </c>
+      <c r="Z148" s="55" t="s">
+        <v>613</v>
+      </c>
+      <c r="AA148" s="56" t="s">
+        <v>600</v>
+      </c>
+      <c r="AB148" s="55" t="s">
+        <v>614</v>
+      </c>
+      <c r="AC148" s="56" t="s">
+        <v>603</v>
+      </c>
+      <c r="AD148" s="55" t="s">
+        <v>615</v>
+      </c>
+      <c r="AE148" s="56" t="s">
+        <v>606</v>
+      </c>
+      <c r="AF148" s="55" t="s">
+        <v>616</v>
+      </c>
+      <c r="AG148" s="56" t="s">
+        <v>609</v>
       </c>
     </row>
-    <row r="149" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="149" spans="1:33" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A149" s="9">
         <v>149</v>
       </c>
@@ -19091,14 +23437,38 @@
       <c r="W149" s="46" t="s">
         <v>181</v>
       </c>
-      <c r="X149" s="45" t="s">
-        <v>181</v>
-      </c>
-      <c r="Y149" s="46" t="s">
-        <v>181</v>
+      <c r="X149" s="55" t="s">
+        <v>612</v>
+      </c>
+      <c r="Y149" s="56" t="s">
+        <v>596</v>
+      </c>
+      <c r="Z149" s="55" t="s">
+        <v>613</v>
+      </c>
+      <c r="AA149" s="56" t="s">
+        <v>600</v>
+      </c>
+      <c r="AB149" s="55" t="s">
+        <v>614</v>
+      </c>
+      <c r="AC149" s="56" t="s">
+        <v>603</v>
+      </c>
+      <c r="AD149" s="55" t="s">
+        <v>615</v>
+      </c>
+      <c r="AE149" s="56" t="s">
+        <v>606</v>
+      </c>
+      <c r="AF149" s="55" t="s">
+        <v>616</v>
+      </c>
+      <c r="AG149" s="56" t="s">
+        <v>609</v>
       </c>
     </row>
-    <row r="150" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="150" spans="1:33" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A150" s="9">
         <v>150</v>
       </c>
@@ -19168,14 +23538,38 @@
       <c r="W150" s="46" t="s">
         <v>181</v>
       </c>
-      <c r="X150" s="45" t="s">
-        <v>181</v>
-      </c>
-      <c r="Y150" s="46" t="s">
-        <v>181</v>
+      <c r="X150" s="55" t="s">
+        <v>612</v>
+      </c>
+      <c r="Y150" s="56" t="s">
+        <v>596</v>
+      </c>
+      <c r="Z150" s="55" t="s">
+        <v>613</v>
+      </c>
+      <c r="AA150" s="56" t="s">
+        <v>600</v>
+      </c>
+      <c r="AB150" s="55" t="s">
+        <v>614</v>
+      </c>
+      <c r="AC150" s="56" t="s">
+        <v>603</v>
+      </c>
+      <c r="AD150" s="55" t="s">
+        <v>615</v>
+      </c>
+      <c r="AE150" s="56" t="s">
+        <v>606</v>
+      </c>
+      <c r="AF150" s="55" t="s">
+        <v>616</v>
+      </c>
+      <c r="AG150" s="56" t="s">
+        <v>609</v>
       </c>
     </row>
-    <row r="151" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="151" spans="1:33" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A151" s="9">
         <v>151</v>
       </c>
@@ -19245,14 +23639,38 @@
       <c r="W151" s="46" t="s">
         <v>181</v>
       </c>
-      <c r="X151" s="45" t="s">
-        <v>181</v>
-      </c>
-      <c r="Y151" s="46" t="s">
-        <v>181</v>
+      <c r="X151" s="55" t="s">
+        <v>612</v>
+      </c>
+      <c r="Y151" s="56" t="s">
+        <v>596</v>
+      </c>
+      <c r="Z151" s="55" t="s">
+        <v>613</v>
+      </c>
+      <c r="AA151" s="56" t="s">
+        <v>600</v>
+      </c>
+      <c r="AB151" s="55" t="s">
+        <v>614</v>
+      </c>
+      <c r="AC151" s="56" t="s">
+        <v>603</v>
+      </c>
+      <c r="AD151" s="55" t="s">
+        <v>615</v>
+      </c>
+      <c r="AE151" s="56" t="s">
+        <v>606</v>
+      </c>
+      <c r="AF151" s="55" t="s">
+        <v>616</v>
+      </c>
+      <c r="AG151" s="56" t="s">
+        <v>609</v>
       </c>
     </row>
-    <row r="152" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="152" spans="1:33" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A152" s="9">
         <v>152</v>
       </c>
@@ -19322,14 +23740,38 @@
       <c r="W152" s="46" t="s">
         <v>181</v>
       </c>
-      <c r="X152" s="45" t="s">
-        <v>181</v>
-      </c>
-      <c r="Y152" s="46" t="s">
-        <v>181</v>
+      <c r="X152" s="55" t="s">
+        <v>612</v>
+      </c>
+      <c r="Y152" s="56" t="s">
+        <v>596</v>
+      </c>
+      <c r="Z152" s="55" t="s">
+        <v>613</v>
+      </c>
+      <c r="AA152" s="56" t="s">
+        <v>600</v>
+      </c>
+      <c r="AB152" s="55" t="s">
+        <v>614</v>
+      </c>
+      <c r="AC152" s="56" t="s">
+        <v>603</v>
+      </c>
+      <c r="AD152" s="55" t="s">
+        <v>615</v>
+      </c>
+      <c r="AE152" s="56" t="s">
+        <v>606</v>
+      </c>
+      <c r="AF152" s="55" t="s">
+        <v>616</v>
+      </c>
+      <c r="AG152" s="56" t="s">
+        <v>609</v>
       </c>
     </row>
-    <row r="153" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="153" spans="1:33" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A153" s="9">
         <v>153</v>
       </c>
@@ -19399,14 +23841,38 @@
       <c r="W153" s="46" t="s">
         <v>181</v>
       </c>
-      <c r="X153" s="45" t="s">
-        <v>181</v>
-      </c>
-      <c r="Y153" s="46" t="s">
-        <v>181</v>
+      <c r="X153" s="55" t="s">
+        <v>612</v>
+      </c>
+      <c r="Y153" s="56" t="s">
+        <v>596</v>
+      </c>
+      <c r="Z153" s="55" t="s">
+        <v>613</v>
+      </c>
+      <c r="AA153" s="56" t="s">
+        <v>600</v>
+      </c>
+      <c r="AB153" s="55" t="s">
+        <v>614</v>
+      </c>
+      <c r="AC153" s="56" t="s">
+        <v>603</v>
+      </c>
+      <c r="AD153" s="55" t="s">
+        <v>615</v>
+      </c>
+      <c r="AE153" s="56" t="s">
+        <v>606</v>
+      </c>
+      <c r="AF153" s="55" t="s">
+        <v>616</v>
+      </c>
+      <c r="AG153" s="56" t="s">
+        <v>609</v>
       </c>
     </row>
-    <row r="154" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="154" spans="1:33" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A154" s="9">
         <v>154</v>
       </c>
@@ -19476,14 +23942,38 @@
       <c r="W154" s="46" t="s">
         <v>181</v>
       </c>
-      <c r="X154" s="45" t="s">
-        <v>181</v>
-      </c>
-      <c r="Y154" s="46" t="s">
-        <v>181</v>
+      <c r="X154" s="55" t="s">
+        <v>612</v>
+      </c>
+      <c r="Y154" s="56" t="s">
+        <v>596</v>
+      </c>
+      <c r="Z154" s="55" t="s">
+        <v>613</v>
+      </c>
+      <c r="AA154" s="56" t="s">
+        <v>600</v>
+      </c>
+      <c r="AB154" s="55" t="s">
+        <v>614</v>
+      </c>
+      <c r="AC154" s="56" t="s">
+        <v>603</v>
+      </c>
+      <c r="AD154" s="55" t="s">
+        <v>615</v>
+      </c>
+      <c r="AE154" s="56" t="s">
+        <v>606</v>
+      </c>
+      <c r="AF154" s="55" t="s">
+        <v>616</v>
+      </c>
+      <c r="AG154" s="56" t="s">
+        <v>609</v>
       </c>
     </row>
-    <row r="155" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="155" spans="1:33" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A155" s="9">
         <v>155</v>
       </c>
@@ -19553,14 +24043,38 @@
       <c r="W155" s="46" t="s">
         <v>181</v>
       </c>
-      <c r="X155" s="45" t="s">
-        <v>181</v>
-      </c>
-      <c r="Y155" s="46" t="s">
-        <v>181</v>
+      <c r="X155" s="55" t="s">
+        <v>612</v>
+      </c>
+      <c r="Y155" s="56" t="s">
+        <v>596</v>
+      </c>
+      <c r="Z155" s="55" t="s">
+        <v>613</v>
+      </c>
+      <c r="AA155" s="56" t="s">
+        <v>600</v>
+      </c>
+      <c r="AB155" s="55" t="s">
+        <v>614</v>
+      </c>
+      <c r="AC155" s="56" t="s">
+        <v>603</v>
+      </c>
+      <c r="AD155" s="55" t="s">
+        <v>615</v>
+      </c>
+      <c r="AE155" s="56" t="s">
+        <v>606</v>
+      </c>
+      <c r="AF155" s="55" t="s">
+        <v>616</v>
+      </c>
+      <c r="AG155" s="56" t="s">
+        <v>609</v>
       </c>
     </row>
-    <row r="156" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="156" spans="1:33" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A156" s="9">
         <v>156</v>
       </c>
@@ -19630,14 +24144,38 @@
       <c r="W156" s="46" t="s">
         <v>181</v>
       </c>
-      <c r="X156" s="45" t="s">
-        <v>181</v>
-      </c>
-      <c r="Y156" s="46" t="s">
-        <v>181</v>
+      <c r="X156" s="55" t="s">
+        <v>612</v>
+      </c>
+      <c r="Y156" s="56" t="s">
+        <v>596</v>
+      </c>
+      <c r="Z156" s="55" t="s">
+        <v>613</v>
+      </c>
+      <c r="AA156" s="56" t="s">
+        <v>600</v>
+      </c>
+      <c r="AB156" s="55" t="s">
+        <v>614</v>
+      </c>
+      <c r="AC156" s="56" t="s">
+        <v>603</v>
+      </c>
+      <c r="AD156" s="55" t="s">
+        <v>615</v>
+      </c>
+      <c r="AE156" s="56" t="s">
+        <v>606</v>
+      </c>
+      <c r="AF156" s="55" t="s">
+        <v>616</v>
+      </c>
+      <c r="AG156" s="56" t="s">
+        <v>609</v>
       </c>
     </row>
-    <row r="157" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="157" spans="1:33" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A157" s="9">
         <v>157</v>
       </c>
@@ -19707,20 +24245,618 @@
       <c r="W157" s="46" t="s">
         <v>181</v>
       </c>
-      <c r="X157" s="45" t="s">
-        <v>181</v>
-      </c>
-      <c r="Y157" s="46" t="s">
-        <v>181</v>
+      <c r="X157" s="55" t="s">
+        <v>612</v>
+      </c>
+      <c r="Y157" s="56" t="s">
+        <v>596</v>
+      </c>
+      <c r="Z157" s="55" t="s">
+        <v>613</v>
+      </c>
+      <c r="AA157" s="56" t="s">
+        <v>600</v>
+      </c>
+      <c r="AB157" s="55" t="s">
+        <v>614</v>
+      </c>
+      <c r="AC157" s="56" t="s">
+        <v>603</v>
+      </c>
+      <c r="AD157" s="55" t="s">
+        <v>615</v>
+      </c>
+      <c r="AE157" s="56" t="s">
+        <v>606</v>
+      </c>
+      <c r="AF157" s="55" t="s">
+        <v>616</v>
+      </c>
+      <c r="AG157" s="56" t="s">
+        <v>609</v>
+      </c>
+    </row>
+    <row r="158" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A158" s="9">
+        <v>158</v>
+      </c>
+      <c r="B158" s="15" t="s">
+        <v>596</v>
+      </c>
+      <c r="C158" s="14" t="s">
+        <v>592</v>
+      </c>
+      <c r="D158" s="81" t="s">
+        <v>181</v>
+      </c>
+      <c r="E158" s="83" t="s">
+        <v>181</v>
+      </c>
+      <c r="F158" s="47" t="s">
+        <v>181</v>
+      </c>
+      <c r="G158" s="79" t="s">
+        <v>181</v>
+      </c>
+      <c r="H158" s="47" t="s">
+        <v>181</v>
+      </c>
+      <c r="I158" s="46" t="s">
+        <v>181</v>
+      </c>
+      <c r="J158" s="71" t="s">
+        <v>340</v>
+      </c>
+      <c r="K158" s="79" t="s">
+        <v>597</v>
+      </c>
+      <c r="L158" s="71" t="s">
+        <v>412</v>
+      </c>
+      <c r="M158" s="46" t="s">
+        <v>598</v>
+      </c>
+      <c r="N158" s="47" t="s">
+        <v>1</v>
+      </c>
+      <c r="O158" s="72" t="s">
+        <v>599</v>
+      </c>
+      <c r="P158" s="45" t="s">
+        <v>181</v>
+      </c>
+      <c r="Q158" s="46" t="s">
+        <v>181</v>
+      </c>
+      <c r="R158" s="45" t="s">
+        <v>181</v>
+      </c>
+      <c r="S158" s="46" t="s">
+        <v>181</v>
+      </c>
+      <c r="T158" s="45" t="s">
+        <v>181</v>
+      </c>
+      <c r="U158" s="46" t="s">
+        <v>181</v>
+      </c>
+      <c r="V158" s="45" t="s">
+        <v>181</v>
+      </c>
+      <c r="W158" s="46" t="s">
+        <v>181</v>
+      </c>
+      <c r="X158" s="55" t="s">
+        <v>612</v>
+      </c>
+      <c r="Y158" s="56" t="s">
+        <v>596</v>
+      </c>
+      <c r="Z158" s="55" t="s">
+        <v>613</v>
+      </c>
+      <c r="AA158" s="56" t="s">
+        <v>600</v>
+      </c>
+      <c r="AB158" s="55" t="s">
+        <v>614</v>
+      </c>
+      <c r="AC158" s="56" t="s">
+        <v>603</v>
+      </c>
+      <c r="AD158" s="55" t="s">
+        <v>615</v>
+      </c>
+      <c r="AE158" s="56" t="s">
+        <v>606</v>
+      </c>
+      <c r="AF158" s="55" t="s">
+        <v>616</v>
+      </c>
+      <c r="AG158" s="56" t="s">
+        <v>609</v>
+      </c>
+    </row>
+    <row r="159" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A159" s="9">
+        <v>159</v>
+      </c>
+      <c r="B159" s="15" t="s">
+        <v>600</v>
+      </c>
+      <c r="C159" s="14" t="s">
+        <v>592</v>
+      </c>
+      <c r="D159" s="81" t="s">
+        <v>181</v>
+      </c>
+      <c r="E159" s="83" t="s">
+        <v>181</v>
+      </c>
+      <c r="F159" s="47" t="s">
+        <v>181</v>
+      </c>
+      <c r="G159" s="79" t="s">
+        <v>181</v>
+      </c>
+      <c r="H159" s="47" t="s">
+        <v>181</v>
+      </c>
+      <c r="I159" s="46" t="s">
+        <v>181</v>
+      </c>
+      <c r="J159" s="71" t="s">
+        <v>340</v>
+      </c>
+      <c r="K159" s="79" t="s">
+        <v>597</v>
+      </c>
+      <c r="L159" s="71" t="s">
+        <v>412</v>
+      </c>
+      <c r="M159" s="46" t="s">
+        <v>601</v>
+      </c>
+      <c r="N159" s="47" t="s">
+        <v>1</v>
+      </c>
+      <c r="O159" s="72" t="s">
+        <v>602</v>
+      </c>
+      <c r="P159" s="45" t="s">
+        <v>181</v>
+      </c>
+      <c r="Q159" s="46" t="s">
+        <v>181</v>
+      </c>
+      <c r="R159" s="45" t="s">
+        <v>181</v>
+      </c>
+      <c r="S159" s="46" t="s">
+        <v>181</v>
+      </c>
+      <c r="T159" s="45" t="s">
+        <v>181</v>
+      </c>
+      <c r="U159" s="46" t="s">
+        <v>181</v>
+      </c>
+      <c r="V159" s="45" t="s">
+        <v>181</v>
+      </c>
+      <c r="W159" s="46" t="s">
+        <v>181</v>
+      </c>
+      <c r="X159" s="55" t="s">
+        <v>612</v>
+      </c>
+      <c r="Y159" s="56" t="s">
+        <v>596</v>
+      </c>
+      <c r="Z159" s="55" t="s">
+        <v>613</v>
+      </c>
+      <c r="AA159" s="56" t="s">
+        <v>600</v>
+      </c>
+      <c r="AB159" s="55" t="s">
+        <v>614</v>
+      </c>
+      <c r="AC159" s="56" t="s">
+        <v>603</v>
+      </c>
+      <c r="AD159" s="55" t="s">
+        <v>615</v>
+      </c>
+      <c r="AE159" s="56" t="s">
+        <v>606</v>
+      </c>
+      <c r="AF159" s="55" t="s">
+        <v>616</v>
+      </c>
+      <c r="AG159" s="56" t="s">
+        <v>609</v>
+      </c>
+    </row>
+    <row r="160" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A160" s="9">
+        <v>160</v>
+      </c>
+      <c r="B160" s="15" t="s">
+        <v>603</v>
+      </c>
+      <c r="C160" s="14" t="s">
+        <v>592</v>
+      </c>
+      <c r="D160" s="81" t="s">
+        <v>181</v>
+      </c>
+      <c r="E160" s="83" t="s">
+        <v>181</v>
+      </c>
+      <c r="F160" s="47" t="s">
+        <v>181</v>
+      </c>
+      <c r="G160" s="79" t="s">
+        <v>181</v>
+      </c>
+      <c r="H160" s="47" t="s">
+        <v>181</v>
+      </c>
+      <c r="I160" s="46" t="s">
+        <v>181</v>
+      </c>
+      <c r="J160" s="71" t="s">
+        <v>340</v>
+      </c>
+      <c r="K160" s="79" t="s">
+        <v>597</v>
+      </c>
+      <c r="L160" s="71" t="s">
+        <v>412</v>
+      </c>
+      <c r="M160" s="46" t="s">
+        <v>604</v>
+      </c>
+      <c r="N160" s="47" t="s">
+        <v>1</v>
+      </c>
+      <c r="O160" s="72" t="s">
+        <v>605</v>
+      </c>
+      <c r="P160" s="45" t="s">
+        <v>181</v>
+      </c>
+      <c r="Q160" s="46" t="s">
+        <v>181</v>
+      </c>
+      <c r="R160" s="45" t="s">
+        <v>181</v>
+      </c>
+      <c r="S160" s="46" t="s">
+        <v>181</v>
+      </c>
+      <c r="T160" s="45" t="s">
+        <v>181</v>
+      </c>
+      <c r="U160" s="46" t="s">
+        <v>181</v>
+      </c>
+      <c r="V160" s="45" t="s">
+        <v>181</v>
+      </c>
+      <c r="W160" s="46" t="s">
+        <v>181</v>
+      </c>
+      <c r="X160" s="55" t="s">
+        <v>612</v>
+      </c>
+      <c r="Y160" s="56" t="s">
+        <v>596</v>
+      </c>
+      <c r="Z160" s="55" t="s">
+        <v>613</v>
+      </c>
+      <c r="AA160" s="56" t="s">
+        <v>600</v>
+      </c>
+      <c r="AB160" s="55" t="s">
+        <v>614</v>
+      </c>
+      <c r="AC160" s="56" t="s">
+        <v>603</v>
+      </c>
+      <c r="AD160" s="55" t="s">
+        <v>615</v>
+      </c>
+      <c r="AE160" s="56" t="s">
+        <v>606</v>
+      </c>
+      <c r="AF160" s="55" t="s">
+        <v>616</v>
+      </c>
+      <c r="AG160" s="56" t="s">
+        <v>609</v>
+      </c>
+    </row>
+    <row r="161" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A161" s="9">
+        <v>161</v>
+      </c>
+      <c r="B161" s="15" t="s">
+        <v>606</v>
+      </c>
+      <c r="C161" s="14" t="s">
+        <v>592</v>
+      </c>
+      <c r="D161" s="81" t="s">
+        <v>181</v>
+      </c>
+      <c r="E161" s="83" t="s">
+        <v>181</v>
+      </c>
+      <c r="F161" s="47" t="s">
+        <v>181</v>
+      </c>
+      <c r="G161" s="79" t="s">
+        <v>181</v>
+      </c>
+      <c r="H161" s="47" t="s">
+        <v>181</v>
+      </c>
+      <c r="I161" s="46" t="s">
+        <v>181</v>
+      </c>
+      <c r="J161" s="71" t="s">
+        <v>340</v>
+      </c>
+      <c r="K161" s="79" t="s">
+        <v>597</v>
+      </c>
+      <c r="L161" s="71" t="s">
+        <v>412</v>
+      </c>
+      <c r="M161" s="46" t="s">
+        <v>607</v>
+      </c>
+      <c r="N161" s="47" t="s">
+        <v>1</v>
+      </c>
+      <c r="O161" s="72" t="s">
+        <v>608</v>
+      </c>
+      <c r="P161" s="45" t="s">
+        <v>181</v>
+      </c>
+      <c r="Q161" s="46" t="s">
+        <v>181</v>
+      </c>
+      <c r="R161" s="45" t="s">
+        <v>181</v>
+      </c>
+      <c r="S161" s="46" t="s">
+        <v>181</v>
+      </c>
+      <c r="T161" s="45" t="s">
+        <v>181</v>
+      </c>
+      <c r="U161" s="46" t="s">
+        <v>181</v>
+      </c>
+      <c r="V161" s="45" t="s">
+        <v>181</v>
+      </c>
+      <c r="W161" s="46" t="s">
+        <v>181</v>
+      </c>
+      <c r="X161" s="55" t="s">
+        <v>612</v>
+      </c>
+      <c r="Y161" s="56" t="s">
+        <v>596</v>
+      </c>
+      <c r="Z161" s="55" t="s">
+        <v>613</v>
+      </c>
+      <c r="AA161" s="56" t="s">
+        <v>600</v>
+      </c>
+      <c r="AB161" s="55" t="s">
+        <v>614</v>
+      </c>
+      <c r="AC161" s="56" t="s">
+        <v>603</v>
+      </c>
+      <c r="AD161" s="55" t="s">
+        <v>615</v>
+      </c>
+      <c r="AE161" s="56" t="s">
+        <v>606</v>
+      </c>
+      <c r="AF161" s="55" t="s">
+        <v>616</v>
+      </c>
+      <c r="AG161" s="56" t="s">
+        <v>609</v>
+      </c>
+    </row>
+    <row r="162" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A162" s="9">
+        <v>162</v>
+      </c>
+      <c r="B162" s="19" t="s">
+        <v>609</v>
+      </c>
+      <c r="C162" s="73" t="s">
+        <v>592</v>
+      </c>
+      <c r="D162" s="82" t="s">
+        <v>181</v>
+      </c>
+      <c r="E162" s="84" t="s">
+        <v>181</v>
+      </c>
+      <c r="F162" s="76" t="s">
+        <v>181</v>
+      </c>
+      <c r="G162" s="80" t="s">
+        <v>181</v>
+      </c>
+      <c r="H162" s="76" t="s">
+        <v>181</v>
+      </c>
+      <c r="I162" s="74" t="s">
+        <v>181</v>
+      </c>
+      <c r="J162" s="75" t="s">
+        <v>340</v>
+      </c>
+      <c r="K162" s="80" t="s">
+        <v>597</v>
+      </c>
+      <c r="L162" s="75" t="s">
+        <v>412</v>
+      </c>
+      <c r="M162" s="74" t="s">
+        <v>610</v>
+      </c>
+      <c r="N162" s="76" t="s">
+        <v>1</v>
+      </c>
+      <c r="O162" s="77" t="s">
+        <v>611</v>
+      </c>
+      <c r="P162" s="78" t="s">
+        <v>181</v>
+      </c>
+      <c r="Q162" s="74" t="s">
+        <v>181</v>
+      </c>
+      <c r="R162" s="78" t="s">
+        <v>181</v>
+      </c>
+      <c r="S162" s="74" t="s">
+        <v>181</v>
+      </c>
+      <c r="T162" s="78" t="s">
+        <v>181</v>
+      </c>
+      <c r="U162" s="74" t="s">
+        <v>181</v>
+      </c>
+      <c r="V162" s="78" t="s">
+        <v>181</v>
+      </c>
+      <c r="W162" s="74" t="s">
+        <v>181</v>
+      </c>
+      <c r="X162" s="55" t="s">
+        <v>612</v>
+      </c>
+      <c r="Y162" s="56" t="s">
+        <v>596</v>
+      </c>
+      <c r="Z162" s="55" t="s">
+        <v>613</v>
+      </c>
+      <c r="AA162" s="56" t="s">
+        <v>600</v>
+      </c>
+      <c r="AB162" s="55" t="s">
+        <v>614</v>
+      </c>
+      <c r="AC162" s="56" t="s">
+        <v>603</v>
+      </c>
+      <c r="AD162" s="55" t="s">
+        <v>615</v>
+      </c>
+      <c r="AE162" s="56" t="s">
+        <v>606</v>
+      </c>
+      <c r="AF162" s="55" t="s">
+        <v>616</v>
+      </c>
+      <c r="AG162" s="56" t="s">
+        <v>609</v>
       </c>
     </row>
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>
-  <conditionalFormatting sqref="B1:B1048576">
-    <cfRule type="duplicateValues" dxfId="1" priority="1"/>
+  <conditionalFormatting sqref="B1:B157 B163:B1048576">
+    <cfRule type="duplicateValues" dxfId="16" priority="16"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="T1:Y1048576">
-    <cfRule type="cellIs" dxfId="0" priority="2" operator="equal">
+  <conditionalFormatting sqref="B158:B162">
+    <cfRule type="duplicateValues" dxfId="15" priority="14"/>
+    <cfRule type="duplicateValues" dxfId="14" priority="15"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="P158:W162">
+    <cfRule type="cellIs" dxfId="13" priority="13" operator="equal">
+      <formula>"null"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="T1:W157 T163:Y1048576">
+    <cfRule type="cellIs" dxfId="12" priority="17" operator="equal">
+      <formula>"null"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="X1:AG1">
+    <cfRule type="cellIs" dxfId="11" priority="7" operator="equal">
+      <formula>"null"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="X1">
+    <cfRule type="cellIs" dxfId="10" priority="12" operator="equal">
+      <formula>"null"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="X2:Y162">
+    <cfRule type="cellIs" dxfId="9" priority="5" operator="equal">
+      <formula>"null"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="Z1">
+    <cfRule type="cellIs" dxfId="8" priority="11" operator="equal">
+      <formula>"null"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="Z2:AA3">
+    <cfRule type="cellIs" dxfId="7" priority="4" operator="equal">
+      <formula>"null"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="Z4:AG162">
+    <cfRule type="cellIs" dxfId="6" priority="6" operator="equal">
+      <formula>"null"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="AB1">
+    <cfRule type="cellIs" dxfId="5" priority="10" operator="equal">
+      <formula>"null"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="AB2:AC3">
+    <cfRule type="cellIs" dxfId="4" priority="3" operator="equal">
+      <formula>"null"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="AD1">
+    <cfRule type="cellIs" dxfId="3" priority="9" operator="equal">
+      <formula>"null"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="AD2:AE3">
+    <cfRule type="cellIs" dxfId="2" priority="2" operator="equal">
+      <formula>"null"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="AF1">
+    <cfRule type="cellIs" dxfId="1" priority="8" operator="equal">
+      <formula>"null"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="AF2:AG3">
+    <cfRule type="cellIs" dxfId="0" priority="1" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>

--- a/Versão5/ABNT/Ontologia_NBR15965_2N.xlsx
+++ b/Versão5/ABNT/Ontologia_NBR15965_2N.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Construtor_Onto\ABNT\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9B0304A0-C0C4-4EF9-B14A-3E53F6EE9B65}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B06B3EC3-6907-4363-AEC0-B080DD23B4CC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-103" yWindow="-103" windowWidth="22149" windowHeight="13200" activeTab="4" xr2:uid="{82C81399-C775-48F3-A336-58DE5F35A6D9}"/>
   </bookViews>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5829" uniqueCount="617">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5824" uniqueCount="618">
   <si>
     <t>Indivíduo</t>
   </si>
@@ -1929,19 +1929,22 @@
     <t>"Individuo indicador de método API para selecionar materiais do projeto"</t>
   </si>
   <si>
-    <t>é.rvt.ambiente</t>
-  </si>
-  <si>
-    <t>é.rvt.andar</t>
-  </si>
-  <si>
-    <t>é.rvt.elemento</t>
-  </si>
-  <si>
-    <t>é.rvt.tipo</t>
-  </si>
-  <si>
-    <t>é.rvt.material</t>
+    <t>é.selecionado.por</t>
+  </si>
+  <si>
+    <t>"[ FilteredElementCollector(doc).OfClass(typeof(SpatialElement)).Cast&lt;SpatialElement&gt;().OrderBy(e =&gt; e.Name).ToList() ]"</t>
+  </si>
+  <si>
+    <t>"[ FilteredElementCollector(doc).OfClass(typeof(Level)).Cast&lt;Level&gt;().OrderBy(e =&gt; e.Name).ToList() ]"</t>
+  </si>
+  <si>
+    <t>"[ EleBuscado : FilteredElementCollector(doc).OfClass(typeof(FamilyInstance)).Cast&lt;FamilyInstance&gt;().FirstOrDefault( e =&gt; e.Symbol.Name == 'InsBuscada') ]"</t>
+  </si>
+  <si>
+    <t>"[ TipBuscado : FilteredElementCollector(doc).OfClass(typeof(FamilySymbol )).Cast&lt;FamilySymbol&gt;( ).FirstOrDefault( e =&gt; e.Name        == 'TipBuscado') ]"</t>
+  </si>
+  <si>
+    <t>"[ MtlBuscado : FilteredElementCollector(doc).OfClass(typeof(Material)).Cast&lt;Material&gt;( ).FirstOrDefault( e =&gt; e.Name  == 'MtlBuscado') ]"</t>
   </si>
 </sst>
 </file>
@@ -2057,7 +2060,7 @@
       <family val="2"/>
     </font>
   </fonts>
-  <fills count="36">
+  <fills count="38">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -2268,6 +2271,18 @@
         <bgColor rgb="FFFEF2CB"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.59999389629810485"/>
+        <bgColor rgb="FF000000"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.79998168889431442"/>
+        <bgColor rgb="FF000000"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="6">
     <border>
@@ -2348,7 +2363,7 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="86">
+  <cellXfs count="88">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
@@ -2597,13 +2612,35 @@
     <xf numFmtId="0" fontId="7" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="8" fillId="36" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="37" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="Hiperlink" xfId="2" builtinId="8"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
     <cellStyle name="Normal 2" xfId="1" xr:uid="{A0D90F96-026A-4EEB-BDCF-93327D239D7A}"/>
   </cellStyles>
-  <dxfs count="95">
+  <dxfs count="102">
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i/>
+        <strike val="0"/>
+        <color theme="0" tint="-0.499984740745262"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i/>
+        <strike val="0"/>
+        <color theme="0" tint="-0.499984740745262"/>
+      </font>
+    </dxf>
     <dxf>
       <font>
         <b val="0"/>
@@ -2633,7 +2670,39 @@
         <b val="0"/>
         <i/>
         <strike val="0"/>
+        <color theme="0" tint="-0.499984740745262"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i/>
+        <strike val="0"/>
+        <color theme="0" tint="-0.499984740745262"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i/>
+        <strike val="0"/>
         <color theme="0"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i/>
+        <strike val="0"/>
+        <color theme="0" tint="-0.499984740745262"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i/>
+        <strike val="0"/>
+        <color theme="0" tint="-0.499984740745262"/>
       </font>
     </dxf>
     <dxf>
@@ -2674,6 +2743,14 @@
         <i/>
         <strike val="0"/>
         <color theme="0"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i/>
+        <strike val="0"/>
+        <color theme="0" tint="-0.499984740745262"/>
       </font>
     </dxf>
     <dxf>
@@ -2860,11 +2937,34 @@
         <shadow val="0"/>
         <u val="none"/>
         <vertAlign val="baseline"/>
+        <sz val="6"/>
         <name val="Arial Nova Cond Light"/>
         <family val="2"/>
         <scheme val="none"/>
       </font>
-      <alignment horizontal="left" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor theme="3" tint="0.749992370372631"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
     </dxf>
     <dxf>
       <font>
@@ -2956,11 +3056,34 @@
         <shadow val="0"/>
         <u val="none"/>
         <vertAlign val="baseline"/>
+        <sz val="6"/>
         <name val="Arial Nova Cond Light"/>
         <family val="2"/>
         <scheme val="none"/>
       </font>
-      <alignment horizontal="left" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor theme="3" tint="0.749992370372631"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
     </dxf>
     <dxf>
       <font>
@@ -3052,11 +3175,34 @@
         <shadow val="0"/>
         <u val="none"/>
         <vertAlign val="baseline"/>
+        <sz val="6"/>
         <name val="Arial Nova Cond Light"/>
         <family val="2"/>
         <scheme val="none"/>
       </font>
-      <alignment horizontal="left" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor theme="3" tint="0.749992370372631"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
     </dxf>
     <dxf>
       <font>
@@ -3148,11 +3294,34 @@
         <shadow val="0"/>
         <u val="none"/>
         <vertAlign val="baseline"/>
+        <sz val="6"/>
         <name val="Arial Nova Cond Light"/>
         <family val="2"/>
         <scheme val="none"/>
       </font>
-      <alignment horizontal="left" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor theme="3" tint="0.749992370372631"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
     </dxf>
     <dxf>
       <font>
@@ -4991,41 +5160,41 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{A07C259E-03F8-41A3-821C-289758C0BF1B}" name="Tabla2" displayName="Tabla2" ref="A2:AG162" headerRowCount="0" totalsRowShown="0" headerRowDxfId="94" dataDxfId="92" headerRowBorderDxfId="93" tableBorderDxfId="91" totalsRowBorderDxfId="90">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{A07C259E-03F8-41A3-821C-289758C0BF1B}" name="Tabla2" displayName="Tabla2" ref="A2:AG162" headerRowCount="0" totalsRowShown="0" headerRowDxfId="101" dataDxfId="99" headerRowBorderDxfId="100" tableBorderDxfId="98" totalsRowBorderDxfId="97">
   <tableColumns count="33">
-    <tableColumn id="1" xr3:uid="{D841A366-4823-4EF9-B009-219AA94AF50A}" name="1" headerRowDxfId="89" dataDxfId="88"/>
-    <tableColumn id="2" xr3:uid="{41E717E1-E3DE-44C1-91C4-719DAB59A464}" name="Indivíduo" headerRowDxfId="87" dataDxfId="86"/>
-    <tableColumn id="3" xr3:uid="{38346B1D-47C6-4B44-A19C-766D16435669}" name="Classe" headerRowDxfId="85" dataDxfId="84"/>
-    <tableColumn id="5" xr3:uid="{27FF4C79-5131-4593-84DE-98F435DB6954}" name="Coluna2" headerRowDxfId="83" dataDxfId="82"/>
-    <tableColumn id="4" xr3:uid="{B4C1140F-50EB-4951-8734-6338EB3CF628}" name="Coluna1" headerRowDxfId="81" dataDxfId="80"/>
-    <tableColumn id="11" xr3:uid="{1EE4C35C-9E89-4C7C-8F68-2AC866434D95}" name="Coluna8" headerRowDxfId="79" dataDxfId="78"/>
-    <tableColumn id="10" xr3:uid="{0C28831F-E05A-4812-BB49-6E3DB059FDDA}" name="Coluna7" headerRowDxfId="77" dataDxfId="76"/>
-    <tableColumn id="9" xr3:uid="{C46F6396-5D54-4379-8FE7-47754ED408FB}" name="Coluna6" headerRowDxfId="75" dataDxfId="74"/>
-    <tableColumn id="14" xr3:uid="{7255F88A-C196-4C7D-BC78-487E43C6076E}" name="Coluna9" headerRowDxfId="73" dataDxfId="72"/>
-    <tableColumn id="15" xr3:uid="{CB39996D-E39C-41DF-9024-09188503F3A9}" name="Coluna10" headerRowDxfId="71" dataDxfId="70"/>
-    <tableColumn id="8" xr3:uid="{DC6BCDF7-14DD-4B0D-951F-937897AADF11}" name="Coluna5" headerRowDxfId="69" dataDxfId="68"/>
-    <tableColumn id="25" xr3:uid="{6E36A2EC-C3DA-4DF1-80AB-262ECBFDA8D3}" name="Coluna20" headerRowDxfId="67" dataDxfId="66"/>
-    <tableColumn id="24" xr3:uid="{7DA1B28C-8D87-49B1-8B12-94BDA4E3634B}" name="Coluna19" headerRowDxfId="65" dataDxfId="64"/>
-    <tableColumn id="12" xr3:uid="{72731FBF-D3F4-42FD-AF7E-09CD79716DE3}" name="Fato (11)" headerRowDxfId="63" dataDxfId="62"/>
-    <tableColumn id="13" xr3:uid="{40ED8FBD-39D6-4C0F-867B-9AA8C9C09316}" name="Valor8" headerRowDxfId="61" dataDxfId="60"/>
-    <tableColumn id="6" xr3:uid="{D7E37E62-C3F1-48D0-9ECE-1603C43E1947}" name="Coluna3" headerRowDxfId="59" dataDxfId="58"/>
-    <tableColumn id="7" xr3:uid="{8EAEA0F2-9F55-4FEE-86F2-D1912AEFC7F4}" name="Coluna4" headerRowDxfId="57" dataDxfId="56"/>
-    <tableColumn id="16" xr3:uid="{CB767617-3A28-42EC-8E47-CE6204F6D856}" name="Coluna11" headerRowDxfId="55" dataDxfId="54"/>
-    <tableColumn id="17" xr3:uid="{E29ADF84-36FF-41F7-9847-17BC340BAE5F}" name="Coluna12" headerRowDxfId="53" dataDxfId="52"/>
-    <tableColumn id="18" xr3:uid="{B5ADD4A7-EE28-45D9-B6FF-C285C2CD6E37}" name="Coluna13" headerRowDxfId="51" dataDxfId="50"/>
-    <tableColumn id="19" xr3:uid="{7FEDF53D-D312-4CF1-8EB3-4A56B77DEAA1}" name="Coluna14" headerRowDxfId="49" dataDxfId="48"/>
-    <tableColumn id="20" xr3:uid="{44C51568-5619-4D1B-B5B4-F2CF79CAB094}" name="Coluna15" headerRowDxfId="47" dataDxfId="46"/>
-    <tableColumn id="21" xr3:uid="{2A7C2A78-BAF9-429F-B898-EF931D80D830}" name="Coluna16" headerRowDxfId="45" dataDxfId="44"/>
-    <tableColumn id="22" xr3:uid="{3BB87186-A8C3-4EE2-9555-ACB7C40B9882}" name="Coluna17" headerRowDxfId="43" dataDxfId="42"/>
-    <tableColumn id="23" xr3:uid="{C574DFC8-E441-4BB1-A97D-83D5A9C08508}" name="Coluna18" headerRowDxfId="41" dataDxfId="40"/>
-    <tableColumn id="26" xr3:uid="{28A75A21-9AEA-4450-8DD2-5FEB86E3D1BF}" name="Coluna21" headerRowDxfId="39" dataDxfId="38"/>
-    <tableColumn id="27" xr3:uid="{9A2D685F-22A0-4828-9E11-08F2267BE681}" name="Coluna22" headerRowDxfId="37" dataDxfId="36"/>
-    <tableColumn id="28" xr3:uid="{4A34D3E2-5187-4876-A257-7428FBB430CA}" name="Coluna23" headerRowDxfId="35" dataDxfId="34"/>
-    <tableColumn id="29" xr3:uid="{F0F265E4-3C4A-45DA-9BD0-B6223C3A5AF7}" name="Coluna24" headerRowDxfId="33" dataDxfId="32"/>
-    <tableColumn id="30" xr3:uid="{F4245AB0-585B-463B-BDE4-2C1B32093872}" name="Coluna25" headerRowDxfId="31" dataDxfId="30"/>
-    <tableColumn id="31" xr3:uid="{78D68B95-AF87-4681-A542-69147C523764}" name="Coluna26" headerRowDxfId="29" dataDxfId="28"/>
-    <tableColumn id="32" xr3:uid="{60FB0CF7-F304-410C-A14D-436E194DA0BF}" name="Coluna27" headerRowDxfId="27" dataDxfId="26"/>
-    <tableColumn id="33" xr3:uid="{29FD05D0-59E6-4A8E-892C-3A07058F43BE}" name="Coluna28" headerRowDxfId="25" dataDxfId="24"/>
+    <tableColumn id="1" xr3:uid="{D841A366-4823-4EF9-B009-219AA94AF50A}" name="1" headerRowDxfId="96" dataDxfId="95"/>
+    <tableColumn id="2" xr3:uid="{41E717E1-E3DE-44C1-91C4-719DAB59A464}" name="Indivíduo" headerRowDxfId="94" dataDxfId="93"/>
+    <tableColumn id="3" xr3:uid="{38346B1D-47C6-4B44-A19C-766D16435669}" name="Classe" headerRowDxfId="92" dataDxfId="91"/>
+    <tableColumn id="5" xr3:uid="{27FF4C79-5131-4593-84DE-98F435DB6954}" name="Coluna2" headerRowDxfId="90" dataDxfId="89"/>
+    <tableColumn id="4" xr3:uid="{B4C1140F-50EB-4951-8734-6338EB3CF628}" name="Coluna1" headerRowDxfId="88" dataDxfId="87"/>
+    <tableColumn id="11" xr3:uid="{1EE4C35C-9E89-4C7C-8F68-2AC866434D95}" name="Coluna8" headerRowDxfId="86" dataDxfId="85"/>
+    <tableColumn id="10" xr3:uid="{0C28831F-E05A-4812-BB49-6E3DB059FDDA}" name="Coluna7" headerRowDxfId="84" dataDxfId="83"/>
+    <tableColumn id="9" xr3:uid="{C46F6396-5D54-4379-8FE7-47754ED408FB}" name="Coluna6" headerRowDxfId="82" dataDxfId="81"/>
+    <tableColumn id="14" xr3:uid="{7255F88A-C196-4C7D-BC78-487E43C6076E}" name="Coluna9" headerRowDxfId="80" dataDxfId="79"/>
+    <tableColumn id="15" xr3:uid="{CB39996D-E39C-41DF-9024-09188503F3A9}" name="Coluna10" headerRowDxfId="78" dataDxfId="77"/>
+    <tableColumn id="8" xr3:uid="{DC6BCDF7-14DD-4B0D-951F-937897AADF11}" name="Coluna5" headerRowDxfId="76" dataDxfId="75"/>
+    <tableColumn id="25" xr3:uid="{6E36A2EC-C3DA-4DF1-80AB-262ECBFDA8D3}" name="Coluna20" headerRowDxfId="74" dataDxfId="73"/>
+    <tableColumn id="24" xr3:uid="{7DA1B28C-8D87-49B1-8B12-94BDA4E3634B}" name="Coluna19" headerRowDxfId="72" dataDxfId="71"/>
+    <tableColumn id="12" xr3:uid="{72731FBF-D3F4-42FD-AF7E-09CD79716DE3}" name="Fato (11)" headerRowDxfId="70" dataDxfId="69"/>
+    <tableColumn id="13" xr3:uid="{40ED8FBD-39D6-4C0F-867B-9AA8C9C09316}" name="Valor8" headerRowDxfId="68" dataDxfId="67"/>
+    <tableColumn id="6" xr3:uid="{D7E37E62-C3F1-48D0-9ECE-1603C43E1947}" name="Coluna3" headerRowDxfId="66" dataDxfId="65"/>
+    <tableColumn id="7" xr3:uid="{8EAEA0F2-9F55-4FEE-86F2-D1912AEFC7F4}" name="Coluna4" headerRowDxfId="64" dataDxfId="63"/>
+    <tableColumn id="16" xr3:uid="{CB767617-3A28-42EC-8E47-CE6204F6D856}" name="Coluna11" headerRowDxfId="62" dataDxfId="61"/>
+    <tableColumn id="17" xr3:uid="{E29ADF84-36FF-41F7-9847-17BC340BAE5F}" name="Coluna12" headerRowDxfId="60" dataDxfId="59"/>
+    <tableColumn id="18" xr3:uid="{B5ADD4A7-EE28-45D9-B6FF-C285C2CD6E37}" name="Coluna13" headerRowDxfId="58" dataDxfId="57"/>
+    <tableColumn id="19" xr3:uid="{7FEDF53D-D312-4CF1-8EB3-4A56B77DEAA1}" name="Coluna14" headerRowDxfId="56" dataDxfId="55"/>
+    <tableColumn id="20" xr3:uid="{44C51568-5619-4D1B-B5B4-F2CF79CAB094}" name="Coluna15" headerRowDxfId="54" dataDxfId="53"/>
+    <tableColumn id="21" xr3:uid="{2A7C2A78-BAF9-429F-B898-EF931D80D830}" name="Coluna16" headerRowDxfId="52" dataDxfId="51"/>
+    <tableColumn id="22" xr3:uid="{3BB87186-A8C3-4EE2-9555-ACB7C40B9882}" name="Coluna17" headerRowDxfId="50" dataDxfId="49"/>
+    <tableColumn id="23" xr3:uid="{C574DFC8-E441-4BB1-A97D-83D5A9C08508}" name="Coluna18" headerRowDxfId="48" dataDxfId="47"/>
+    <tableColumn id="26" xr3:uid="{28A75A21-9AEA-4450-8DD2-5FEB86E3D1BF}" name="Coluna21" headerRowDxfId="46" dataDxfId="45"/>
+    <tableColumn id="27" xr3:uid="{9A2D685F-22A0-4828-9E11-08F2267BE681}" name="Coluna22" headerRowDxfId="44" dataDxfId="43"/>
+    <tableColumn id="28" xr3:uid="{4A34D3E2-5187-4876-A257-7428FBB430CA}" name="Coluna23" headerRowDxfId="42" dataDxfId="41"/>
+    <tableColumn id="29" xr3:uid="{F0F265E4-3C4A-45DA-9BD0-B6223C3A5AF7}" name="Coluna24" headerRowDxfId="40" dataDxfId="39"/>
+    <tableColumn id="30" xr3:uid="{F4245AB0-585B-463B-BDE4-2C1B32093872}" name="Coluna25" headerRowDxfId="38" dataDxfId="37"/>
+    <tableColumn id="31" xr3:uid="{78D68B95-AF87-4681-A542-69147C523764}" name="Coluna26" headerRowDxfId="36" dataDxfId="35"/>
+    <tableColumn id="32" xr3:uid="{60FB0CF7-F304-410C-A14D-436E194DA0BF}" name="Coluna27" headerRowDxfId="34" dataDxfId="33"/>
+    <tableColumn id="33" xr3:uid="{29FD05D0-59E6-4A8E-892C-3A07058F43BE}" name="Coluna28" headerRowDxfId="32" dataDxfId="31"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="0" showColumnStripes="0"/>
 </table>
@@ -5553,7 +5722,7 @@
       </c>
       <c r="B18" s="5">
         <f ca="1">NOW()</f>
-        <v>46257.700794675926</v>
+        <v>46257.756787500002</v>
       </c>
       <c r="C18" s="42" t="s">
         <v>404</v>
@@ -8159,23 +8328,23 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A2:B24">
-    <cfRule type="cellIs" dxfId="23" priority="2" operator="equal">
+    <cfRule type="cellIs" dxfId="30" priority="2" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F2:F14">
-    <cfRule type="duplicateValues" dxfId="22" priority="9"/>
+    <cfRule type="duplicateValues" dxfId="29" priority="9"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F24">
-    <cfRule type="duplicateValues" dxfId="21" priority="3"/>
+    <cfRule type="duplicateValues" dxfId="28" priority="3"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="R1:R24">
-    <cfRule type="cellIs" dxfId="20" priority="1" operator="equal">
+    <cfRule type="cellIs" dxfId="27" priority="1" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="Y2 AA2">
-    <cfRule type="cellIs" dxfId="19" priority="6" operator="equal">
+    <cfRule type="cellIs" dxfId="26" priority="6" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -8328,7 +8497,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:U2">
-    <cfRule type="cellIs" dxfId="18" priority="1" operator="equal">
+    <cfRule type="cellIs" dxfId="25" priority="1" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -8373,7 +8542,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:A2">
-    <cfRule type="cellIs" dxfId="17" priority="1" operator="equal">
+    <cfRule type="cellIs" dxfId="24" priority="1" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -8385,7 +8554,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B79BA5E7-BFBD-4AC9-B36C-B9776AA17B75}">
   <sheetPr codeName="Planilha5"/>
   <dimension ref="A1:AG162"/>
-  <sheetFormatPr defaultColWidth="3.69921875" defaultRowHeight="6" customHeight="1" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="9.3984375" defaultRowHeight="6" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="2.5" style="2" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="8.19921875" style="2" bestFit="1" customWidth="1"/>
@@ -8403,24 +8572,24 @@
     <col min="14" max="14" width="5.3984375" style="48" bestFit="1" customWidth="1"/>
     <col min="15" max="15" width="36.796875" style="2" bestFit="1" customWidth="1"/>
     <col min="16" max="16" width="7.5" style="48" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="3.69921875" style="48"/>
+    <col min="17" max="17" width="80.59765625" style="48" bestFit="1" customWidth="1"/>
     <col min="18" max="18" width="5.09765625" style="48" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="3.69921875" style="48"/>
+    <col min="19" max="19" width="3.69921875" style="48" bestFit="1" customWidth="1"/>
     <col min="20" max="20" width="3.09765625" style="48" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="3.69921875" style="48"/>
+    <col min="21" max="21" width="3.69921875" style="48" bestFit="1" customWidth="1"/>
     <col min="22" max="22" width="3.09765625" style="48" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="3.69921875" style="48"/>
-    <col min="24" max="24" width="7.5" style="48" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="3.69921875" style="48" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="9.296875" style="48" bestFit="1" customWidth="1"/>
     <col min="25" max="25" width="7.796875" style="48" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="5.796875" style="2" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="9.296875" style="48" bestFit="1" customWidth="1"/>
     <col min="27" max="27" width="6" style="2" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="7.59765625" style="2" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="9.296875" style="48" bestFit="1" customWidth="1"/>
     <col min="29" max="29" width="7.5" style="2" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="4.8984375" style="2" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="9.296875" style="48" bestFit="1" customWidth="1"/>
     <col min="31" max="31" width="7.19921875" style="2" bestFit="1" customWidth="1"/>
-    <col min="32" max="32" width="6.8984375" style="2" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="9.296875" style="48" bestFit="1" customWidth="1"/>
     <col min="33" max="33" width="7.09765625" style="2" bestFit="1" customWidth="1"/>
-    <col min="34" max="16384" width="3.69921875" style="2"/>
+    <col min="34" max="16384" width="9.3984375" style="2"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:33" ht="18.649999999999999" customHeight="1" x14ac:dyDescent="0.25">
@@ -8799,25 +8968,25 @@
         <v>596</v>
       </c>
       <c r="Z4" s="55" t="s">
-        <v>613</v>
+        <v>612</v>
       </c>
       <c r="AA4" s="56" t="s">
         <v>600</v>
       </c>
       <c r="AB4" s="55" t="s">
-        <v>614</v>
+        <v>612</v>
       </c>
       <c r="AC4" s="56" t="s">
         <v>603</v>
       </c>
       <c r="AD4" s="55" t="s">
-        <v>615</v>
+        <v>612</v>
       </c>
       <c r="AE4" s="56" t="s">
         <v>606</v>
       </c>
       <c r="AF4" s="55" t="s">
-        <v>616</v>
+        <v>612</v>
       </c>
       <c r="AG4" s="56" t="s">
         <v>609</v>
@@ -8900,25 +9069,25 @@
         <v>596</v>
       </c>
       <c r="Z5" s="55" t="s">
-        <v>613</v>
+        <v>612</v>
       </c>
       <c r="AA5" s="56" t="s">
         <v>600</v>
       </c>
       <c r="AB5" s="55" t="s">
-        <v>614</v>
+        <v>612</v>
       </c>
       <c r="AC5" s="56" t="s">
         <v>603</v>
       </c>
       <c r="AD5" s="55" t="s">
-        <v>615</v>
+        <v>612</v>
       </c>
       <c r="AE5" s="56" t="s">
         <v>606</v>
       </c>
       <c r="AF5" s="55" t="s">
-        <v>616</v>
+        <v>612</v>
       </c>
       <c r="AG5" s="56" t="s">
         <v>609</v>
@@ -9001,25 +9170,25 @@
         <v>596</v>
       </c>
       <c r="Z6" s="55" t="s">
-        <v>613</v>
+        <v>612</v>
       </c>
       <c r="AA6" s="56" t="s">
         <v>600</v>
       </c>
       <c r="AB6" s="55" t="s">
-        <v>614</v>
+        <v>612</v>
       </c>
       <c r="AC6" s="56" t="s">
         <v>603</v>
       </c>
       <c r="AD6" s="55" t="s">
-        <v>615</v>
+        <v>612</v>
       </c>
       <c r="AE6" s="56" t="s">
         <v>606</v>
       </c>
       <c r="AF6" s="55" t="s">
-        <v>616</v>
+        <v>612</v>
       </c>
       <c r="AG6" s="56" t="s">
         <v>609</v>
@@ -9102,25 +9271,25 @@
         <v>596</v>
       </c>
       <c r="Z7" s="55" t="s">
-        <v>613</v>
+        <v>612</v>
       </c>
       <c r="AA7" s="56" t="s">
         <v>600</v>
       </c>
       <c r="AB7" s="55" t="s">
-        <v>614</v>
+        <v>612</v>
       </c>
       <c r="AC7" s="56" t="s">
         <v>603</v>
       </c>
       <c r="AD7" s="55" t="s">
-        <v>615</v>
+        <v>612</v>
       </c>
       <c r="AE7" s="56" t="s">
         <v>606</v>
       </c>
       <c r="AF7" s="55" t="s">
-        <v>616</v>
+        <v>612</v>
       </c>
       <c r="AG7" s="56" t="s">
         <v>609</v>
@@ -9203,25 +9372,25 @@
         <v>596</v>
       </c>
       <c r="Z8" s="55" t="s">
-        <v>613</v>
+        <v>612</v>
       </c>
       <c r="AA8" s="56" t="s">
         <v>600</v>
       </c>
       <c r="AB8" s="55" t="s">
-        <v>614</v>
+        <v>612</v>
       </c>
       <c r="AC8" s="56" t="s">
         <v>603</v>
       </c>
       <c r="AD8" s="55" t="s">
-        <v>615</v>
+        <v>612</v>
       </c>
       <c r="AE8" s="56" t="s">
         <v>606</v>
       </c>
       <c r="AF8" s="55" t="s">
-        <v>616</v>
+        <v>612</v>
       </c>
       <c r="AG8" s="56" t="s">
         <v>609</v>
@@ -9304,25 +9473,25 @@
         <v>596</v>
       </c>
       <c r="Z9" s="55" t="s">
-        <v>613</v>
+        <v>612</v>
       </c>
       <c r="AA9" s="56" t="s">
         <v>600</v>
       </c>
       <c r="AB9" s="55" t="s">
-        <v>614</v>
+        <v>612</v>
       </c>
       <c r="AC9" s="56" t="s">
         <v>603</v>
       </c>
       <c r="AD9" s="55" t="s">
-        <v>615</v>
+        <v>612</v>
       </c>
       <c r="AE9" s="56" t="s">
         <v>606</v>
       </c>
       <c r="AF9" s="55" t="s">
-        <v>616</v>
+        <v>612</v>
       </c>
       <c r="AG9" s="56" t="s">
         <v>609</v>
@@ -9405,25 +9574,25 @@
         <v>596</v>
       </c>
       <c r="Z10" s="55" t="s">
-        <v>613</v>
+        <v>612</v>
       </c>
       <c r="AA10" s="56" t="s">
         <v>600</v>
       </c>
       <c r="AB10" s="55" t="s">
-        <v>614</v>
+        <v>612</v>
       </c>
       <c r="AC10" s="56" t="s">
         <v>603</v>
       </c>
       <c r="AD10" s="55" t="s">
-        <v>615</v>
+        <v>612</v>
       </c>
       <c r="AE10" s="56" t="s">
         <v>606</v>
       </c>
       <c r="AF10" s="55" t="s">
-        <v>616</v>
+        <v>612</v>
       </c>
       <c r="AG10" s="56" t="s">
         <v>609</v>
@@ -9506,25 +9675,25 @@
         <v>596</v>
       </c>
       <c r="Z11" s="55" t="s">
-        <v>613</v>
+        <v>612</v>
       </c>
       <c r="AA11" s="56" t="s">
         <v>600</v>
       </c>
       <c r="AB11" s="55" t="s">
-        <v>614</v>
+        <v>612</v>
       </c>
       <c r="AC11" s="56" t="s">
         <v>603</v>
       </c>
       <c r="AD11" s="55" t="s">
-        <v>615</v>
+        <v>612</v>
       </c>
       <c r="AE11" s="56" t="s">
         <v>606</v>
       </c>
       <c r="AF11" s="55" t="s">
-        <v>616</v>
+        <v>612</v>
       </c>
       <c r="AG11" s="56" t="s">
         <v>609</v>
@@ -9607,25 +9776,25 @@
         <v>596</v>
       </c>
       <c r="Z12" s="55" t="s">
-        <v>613</v>
+        <v>612</v>
       </c>
       <c r="AA12" s="56" t="s">
         <v>600</v>
       </c>
       <c r="AB12" s="55" t="s">
-        <v>614</v>
+        <v>612</v>
       </c>
       <c r="AC12" s="56" t="s">
         <v>603</v>
       </c>
       <c r="AD12" s="55" t="s">
-        <v>615</v>
+        <v>612</v>
       </c>
       <c r="AE12" s="56" t="s">
         <v>606</v>
       </c>
       <c r="AF12" s="55" t="s">
-        <v>616</v>
+        <v>612</v>
       </c>
       <c r="AG12" s="56" t="s">
         <v>609</v>
@@ -9708,25 +9877,25 @@
         <v>596</v>
       </c>
       <c r="Z13" s="55" t="s">
-        <v>613</v>
+        <v>612</v>
       </c>
       <c r="AA13" s="56" t="s">
         <v>600</v>
       </c>
       <c r="AB13" s="55" t="s">
-        <v>614</v>
+        <v>612</v>
       </c>
       <c r="AC13" s="56" t="s">
         <v>603</v>
       </c>
       <c r="AD13" s="55" t="s">
-        <v>615</v>
+        <v>612</v>
       </c>
       <c r="AE13" s="56" t="s">
         <v>606</v>
       </c>
       <c r="AF13" s="55" t="s">
-        <v>616</v>
+        <v>612</v>
       </c>
       <c r="AG13" s="56" t="s">
         <v>609</v>
@@ -9809,25 +9978,25 @@
         <v>596</v>
       </c>
       <c r="Z14" s="55" t="s">
-        <v>613</v>
+        <v>612</v>
       </c>
       <c r="AA14" s="56" t="s">
         <v>600</v>
       </c>
       <c r="AB14" s="55" t="s">
-        <v>614</v>
+        <v>612</v>
       </c>
       <c r="AC14" s="56" t="s">
         <v>603</v>
       </c>
       <c r="AD14" s="55" t="s">
-        <v>615</v>
+        <v>612</v>
       </c>
       <c r="AE14" s="56" t="s">
         <v>606</v>
       </c>
       <c r="AF14" s="55" t="s">
-        <v>616</v>
+        <v>612</v>
       </c>
       <c r="AG14" s="56" t="s">
         <v>609</v>
@@ -9910,25 +10079,25 @@
         <v>596</v>
       </c>
       <c r="Z15" s="55" t="s">
-        <v>613</v>
+        <v>612</v>
       </c>
       <c r="AA15" s="56" t="s">
         <v>600</v>
       </c>
       <c r="AB15" s="55" t="s">
-        <v>614</v>
+        <v>612</v>
       </c>
       <c r="AC15" s="56" t="s">
         <v>603</v>
       </c>
       <c r="AD15" s="55" t="s">
-        <v>615</v>
+        <v>612</v>
       </c>
       <c r="AE15" s="56" t="s">
         <v>606</v>
       </c>
       <c r="AF15" s="55" t="s">
-        <v>616</v>
+        <v>612</v>
       </c>
       <c r="AG15" s="56" t="s">
         <v>609</v>
@@ -10011,25 +10180,25 @@
         <v>596</v>
       </c>
       <c r="Z16" s="55" t="s">
-        <v>613</v>
+        <v>612</v>
       </c>
       <c r="AA16" s="56" t="s">
         <v>600</v>
       </c>
       <c r="AB16" s="55" t="s">
-        <v>614</v>
+        <v>612</v>
       </c>
       <c r="AC16" s="56" t="s">
         <v>603</v>
       </c>
       <c r="AD16" s="55" t="s">
-        <v>615</v>
+        <v>612</v>
       </c>
       <c r="AE16" s="56" t="s">
         <v>606</v>
       </c>
       <c r="AF16" s="55" t="s">
-        <v>616</v>
+        <v>612</v>
       </c>
       <c r="AG16" s="56" t="s">
         <v>609</v>
@@ -10112,25 +10281,25 @@
         <v>596</v>
       </c>
       <c r="Z17" s="55" t="s">
-        <v>613</v>
+        <v>612</v>
       </c>
       <c r="AA17" s="56" t="s">
         <v>600</v>
       </c>
       <c r="AB17" s="55" t="s">
-        <v>614</v>
+        <v>612</v>
       </c>
       <c r="AC17" s="56" t="s">
         <v>603</v>
       </c>
       <c r="AD17" s="55" t="s">
-        <v>615</v>
+        <v>612</v>
       </c>
       <c r="AE17" s="56" t="s">
         <v>606</v>
       </c>
       <c r="AF17" s="55" t="s">
-        <v>616</v>
+        <v>612</v>
       </c>
       <c r="AG17" s="56" t="s">
         <v>609</v>
@@ -10213,25 +10382,25 @@
         <v>596</v>
       </c>
       <c r="Z18" s="55" t="s">
-        <v>613</v>
+        <v>612</v>
       </c>
       <c r="AA18" s="56" t="s">
         <v>600</v>
       </c>
       <c r="AB18" s="55" t="s">
-        <v>614</v>
+        <v>612</v>
       </c>
       <c r="AC18" s="56" t="s">
         <v>603</v>
       </c>
       <c r="AD18" s="55" t="s">
-        <v>615</v>
+        <v>612</v>
       </c>
       <c r="AE18" s="56" t="s">
         <v>606</v>
       </c>
       <c r="AF18" s="55" t="s">
-        <v>616</v>
+        <v>612</v>
       </c>
       <c r="AG18" s="56" t="s">
         <v>609</v>
@@ -10314,25 +10483,25 @@
         <v>596</v>
       </c>
       <c r="Z19" s="55" t="s">
-        <v>613</v>
+        <v>612</v>
       </c>
       <c r="AA19" s="56" t="s">
         <v>600</v>
       </c>
       <c r="AB19" s="55" t="s">
-        <v>614</v>
+        <v>612</v>
       </c>
       <c r="AC19" s="56" t="s">
         <v>603</v>
       </c>
       <c r="AD19" s="55" t="s">
-        <v>615</v>
+        <v>612</v>
       </c>
       <c r="AE19" s="56" t="s">
         <v>606</v>
       </c>
       <c r="AF19" s="55" t="s">
-        <v>616</v>
+        <v>612</v>
       </c>
       <c r="AG19" s="56" t="s">
         <v>609</v>
@@ -10415,25 +10584,25 @@
         <v>596</v>
       </c>
       <c r="Z20" s="55" t="s">
-        <v>613</v>
+        <v>612</v>
       </c>
       <c r="AA20" s="56" t="s">
         <v>600</v>
       </c>
       <c r="AB20" s="55" t="s">
-        <v>614</v>
+        <v>612</v>
       </c>
       <c r="AC20" s="56" t="s">
         <v>603</v>
       </c>
       <c r="AD20" s="55" t="s">
-        <v>615</v>
+        <v>612</v>
       </c>
       <c r="AE20" s="56" t="s">
         <v>606</v>
       </c>
       <c r="AF20" s="55" t="s">
-        <v>616</v>
+        <v>612</v>
       </c>
       <c r="AG20" s="56" t="s">
         <v>609</v>
@@ -10516,25 +10685,25 @@
         <v>596</v>
       </c>
       <c r="Z21" s="55" t="s">
-        <v>613</v>
+        <v>612</v>
       </c>
       <c r="AA21" s="56" t="s">
         <v>600</v>
       </c>
       <c r="AB21" s="55" t="s">
-        <v>614</v>
+        <v>612</v>
       </c>
       <c r="AC21" s="56" t="s">
         <v>603</v>
       </c>
       <c r="AD21" s="55" t="s">
-        <v>615</v>
+        <v>612</v>
       </c>
       <c r="AE21" s="56" t="s">
         <v>606</v>
       </c>
       <c r="AF21" s="55" t="s">
-        <v>616</v>
+        <v>612</v>
       </c>
       <c r="AG21" s="56" t="s">
         <v>609</v>
@@ -10617,25 +10786,25 @@
         <v>596</v>
       </c>
       <c r="Z22" s="55" t="s">
-        <v>613</v>
+        <v>612</v>
       </c>
       <c r="AA22" s="56" t="s">
         <v>600</v>
       </c>
       <c r="AB22" s="55" t="s">
-        <v>614</v>
+        <v>612</v>
       </c>
       <c r="AC22" s="56" t="s">
         <v>603</v>
       </c>
       <c r="AD22" s="55" t="s">
-        <v>615</v>
+        <v>612</v>
       </c>
       <c r="AE22" s="56" t="s">
         <v>606</v>
       </c>
       <c r="AF22" s="55" t="s">
-        <v>616</v>
+        <v>612</v>
       </c>
       <c r="AG22" s="56" t="s">
         <v>609</v>
@@ -10718,25 +10887,25 @@
         <v>596</v>
       </c>
       <c r="Z23" s="55" t="s">
-        <v>613</v>
+        <v>612</v>
       </c>
       <c r="AA23" s="56" t="s">
         <v>600</v>
       </c>
       <c r="AB23" s="55" t="s">
-        <v>614</v>
+        <v>612</v>
       </c>
       <c r="AC23" s="56" t="s">
         <v>603</v>
       </c>
       <c r="AD23" s="55" t="s">
-        <v>615</v>
+        <v>612</v>
       </c>
       <c r="AE23" s="56" t="s">
         <v>606</v>
       </c>
       <c r="AF23" s="55" t="s">
-        <v>616</v>
+        <v>612</v>
       </c>
       <c r="AG23" s="56" t="s">
         <v>609</v>
@@ -10819,25 +10988,25 @@
         <v>596</v>
       </c>
       <c r="Z24" s="55" t="s">
-        <v>613</v>
+        <v>612</v>
       </c>
       <c r="AA24" s="56" t="s">
         <v>600</v>
       </c>
       <c r="AB24" s="55" t="s">
-        <v>614</v>
+        <v>612</v>
       </c>
       <c r="AC24" s="56" t="s">
         <v>603</v>
       </c>
       <c r="AD24" s="55" t="s">
-        <v>615</v>
+        <v>612</v>
       </c>
       <c r="AE24" s="56" t="s">
         <v>606</v>
       </c>
       <c r="AF24" s="55" t="s">
-        <v>616</v>
+        <v>612</v>
       </c>
       <c r="AG24" s="56" t="s">
         <v>609</v>
@@ -10920,25 +11089,25 @@
         <v>596</v>
       </c>
       <c r="Z25" s="55" t="s">
-        <v>613</v>
+        <v>612</v>
       </c>
       <c r="AA25" s="56" t="s">
         <v>600</v>
       </c>
       <c r="AB25" s="55" t="s">
-        <v>614</v>
+        <v>612</v>
       </c>
       <c r="AC25" s="56" t="s">
         <v>603</v>
       </c>
       <c r="AD25" s="55" t="s">
-        <v>615</v>
+        <v>612</v>
       </c>
       <c r="AE25" s="56" t="s">
         <v>606</v>
       </c>
       <c r="AF25" s="55" t="s">
-        <v>616</v>
+        <v>612</v>
       </c>
       <c r="AG25" s="56" t="s">
         <v>609</v>
@@ -11021,25 +11190,25 @@
         <v>596</v>
       </c>
       <c r="Z26" s="55" t="s">
-        <v>613</v>
+        <v>612</v>
       </c>
       <c r="AA26" s="56" t="s">
         <v>600</v>
       </c>
       <c r="AB26" s="55" t="s">
-        <v>614</v>
+        <v>612</v>
       </c>
       <c r="AC26" s="56" t="s">
         <v>603</v>
       </c>
       <c r="AD26" s="55" t="s">
-        <v>615</v>
+        <v>612</v>
       </c>
       <c r="AE26" s="56" t="s">
         <v>606</v>
       </c>
       <c r="AF26" s="55" t="s">
-        <v>616</v>
+        <v>612</v>
       </c>
       <c r="AG26" s="56" t="s">
         <v>609</v>
@@ -11122,25 +11291,25 @@
         <v>596</v>
       </c>
       <c r="Z27" s="55" t="s">
-        <v>613</v>
+        <v>612</v>
       </c>
       <c r="AA27" s="56" t="s">
         <v>600</v>
       </c>
       <c r="AB27" s="55" t="s">
-        <v>614</v>
+        <v>612</v>
       </c>
       <c r="AC27" s="56" t="s">
         <v>603</v>
       </c>
       <c r="AD27" s="55" t="s">
-        <v>615</v>
+        <v>612</v>
       </c>
       <c r="AE27" s="56" t="s">
         <v>606</v>
       </c>
       <c r="AF27" s="55" t="s">
-        <v>616</v>
+        <v>612</v>
       </c>
       <c r="AG27" s="56" t="s">
         <v>609</v>
@@ -11223,25 +11392,25 @@
         <v>596</v>
       </c>
       <c r="Z28" s="55" t="s">
-        <v>613</v>
+        <v>612</v>
       </c>
       <c r="AA28" s="56" t="s">
         <v>600</v>
       </c>
       <c r="AB28" s="55" t="s">
-        <v>614</v>
+        <v>612</v>
       </c>
       <c r="AC28" s="56" t="s">
         <v>603</v>
       </c>
       <c r="AD28" s="55" t="s">
-        <v>615</v>
+        <v>612</v>
       </c>
       <c r="AE28" s="56" t="s">
         <v>606</v>
       </c>
       <c r="AF28" s="55" t="s">
-        <v>616</v>
+        <v>612</v>
       </c>
       <c r="AG28" s="56" t="s">
         <v>609</v>
@@ -11324,25 +11493,25 @@
         <v>596</v>
       </c>
       <c r="Z29" s="55" t="s">
-        <v>613</v>
+        <v>612</v>
       </c>
       <c r="AA29" s="56" t="s">
         <v>600</v>
       </c>
       <c r="AB29" s="55" t="s">
-        <v>614</v>
+        <v>612</v>
       </c>
       <c r="AC29" s="56" t="s">
         <v>603</v>
       </c>
       <c r="AD29" s="55" t="s">
-        <v>615</v>
+        <v>612</v>
       </c>
       <c r="AE29" s="56" t="s">
         <v>606</v>
       </c>
       <c r="AF29" s="55" t="s">
-        <v>616</v>
+        <v>612</v>
       </c>
       <c r="AG29" s="56" t="s">
         <v>609</v>
@@ -11425,25 +11594,25 @@
         <v>596</v>
       </c>
       <c r="Z30" s="55" t="s">
-        <v>613</v>
+        <v>612</v>
       </c>
       <c r="AA30" s="56" t="s">
         <v>600</v>
       </c>
       <c r="AB30" s="55" t="s">
-        <v>614</v>
+        <v>612</v>
       </c>
       <c r="AC30" s="56" t="s">
         <v>603</v>
       </c>
       <c r="AD30" s="55" t="s">
-        <v>615</v>
+        <v>612</v>
       </c>
       <c r="AE30" s="56" t="s">
         <v>606</v>
       </c>
       <c r="AF30" s="55" t="s">
-        <v>616</v>
+        <v>612</v>
       </c>
       <c r="AG30" s="56" t="s">
         <v>609</v>
@@ -11526,25 +11695,25 @@
         <v>596</v>
       </c>
       <c r="Z31" s="55" t="s">
-        <v>613</v>
+        <v>612</v>
       </c>
       <c r="AA31" s="56" t="s">
         <v>600</v>
       </c>
       <c r="AB31" s="55" t="s">
-        <v>614</v>
+        <v>612</v>
       </c>
       <c r="AC31" s="56" t="s">
         <v>603</v>
       </c>
       <c r="AD31" s="55" t="s">
-        <v>615</v>
+        <v>612</v>
       </c>
       <c r="AE31" s="56" t="s">
         <v>606</v>
       </c>
       <c r="AF31" s="55" t="s">
-        <v>616</v>
+        <v>612</v>
       </c>
       <c r="AG31" s="56" t="s">
         <v>609</v>
@@ -11627,25 +11796,25 @@
         <v>596</v>
       </c>
       <c r="Z32" s="55" t="s">
-        <v>613</v>
+        <v>612</v>
       </c>
       <c r="AA32" s="56" t="s">
         <v>600</v>
       </c>
       <c r="AB32" s="55" t="s">
-        <v>614</v>
+        <v>612</v>
       </c>
       <c r="AC32" s="56" t="s">
         <v>603</v>
       </c>
       <c r="AD32" s="55" t="s">
-        <v>615</v>
+        <v>612</v>
       </c>
       <c r="AE32" s="56" t="s">
         <v>606</v>
       </c>
       <c r="AF32" s="55" t="s">
-        <v>616</v>
+        <v>612</v>
       </c>
       <c r="AG32" s="56" t="s">
         <v>609</v>
@@ -11728,25 +11897,25 @@
         <v>596</v>
       </c>
       <c r="Z33" s="55" t="s">
-        <v>613</v>
+        <v>612</v>
       </c>
       <c r="AA33" s="56" t="s">
         <v>600</v>
       </c>
       <c r="AB33" s="55" t="s">
-        <v>614</v>
+        <v>612</v>
       </c>
       <c r="AC33" s="56" t="s">
         <v>603</v>
       </c>
       <c r="AD33" s="55" t="s">
-        <v>615</v>
+        <v>612</v>
       </c>
       <c r="AE33" s="56" t="s">
         <v>606</v>
       </c>
       <c r="AF33" s="55" t="s">
-        <v>616</v>
+        <v>612</v>
       </c>
       <c r="AG33" s="56" t="s">
         <v>609</v>
@@ -11829,25 +11998,25 @@
         <v>596</v>
       </c>
       <c r="Z34" s="55" t="s">
-        <v>613</v>
+        <v>612</v>
       </c>
       <c r="AA34" s="56" t="s">
         <v>600</v>
       </c>
       <c r="AB34" s="55" t="s">
-        <v>614</v>
+        <v>612</v>
       </c>
       <c r="AC34" s="56" t="s">
         <v>603</v>
       </c>
       <c r="AD34" s="55" t="s">
-        <v>615</v>
+        <v>612</v>
       </c>
       <c r="AE34" s="56" t="s">
         <v>606</v>
       </c>
       <c r="AF34" s="55" t="s">
-        <v>616</v>
+        <v>612</v>
       </c>
       <c r="AG34" s="56" t="s">
         <v>609</v>
@@ -11930,25 +12099,25 @@
         <v>596</v>
       </c>
       <c r="Z35" s="55" t="s">
-        <v>613</v>
+        <v>612</v>
       </c>
       <c r="AA35" s="56" t="s">
         <v>600</v>
       </c>
       <c r="AB35" s="55" t="s">
-        <v>614</v>
+        <v>612</v>
       </c>
       <c r="AC35" s="56" t="s">
         <v>603</v>
       </c>
       <c r="AD35" s="55" t="s">
-        <v>615</v>
+        <v>612</v>
       </c>
       <c r="AE35" s="56" t="s">
         <v>606</v>
       </c>
       <c r="AF35" s="55" t="s">
-        <v>616</v>
+        <v>612</v>
       </c>
       <c r="AG35" s="56" t="s">
         <v>609</v>
@@ -12031,25 +12200,25 @@
         <v>596</v>
       </c>
       <c r="Z36" s="55" t="s">
-        <v>613</v>
+        <v>612</v>
       </c>
       <c r="AA36" s="56" t="s">
         <v>600</v>
       </c>
       <c r="AB36" s="55" t="s">
-        <v>614</v>
+        <v>612</v>
       </c>
       <c r="AC36" s="56" t="s">
         <v>603</v>
       </c>
       <c r="AD36" s="55" t="s">
-        <v>615</v>
+        <v>612</v>
       </c>
       <c r="AE36" s="56" t="s">
         <v>606</v>
       </c>
       <c r="AF36" s="55" t="s">
-        <v>616</v>
+        <v>612</v>
       </c>
       <c r="AG36" s="56" t="s">
         <v>609</v>
@@ -12132,25 +12301,25 @@
         <v>596</v>
       </c>
       <c r="Z37" s="55" t="s">
-        <v>613</v>
+        <v>612</v>
       </c>
       <c r="AA37" s="56" t="s">
         <v>600</v>
       </c>
       <c r="AB37" s="55" t="s">
-        <v>614</v>
+        <v>612</v>
       </c>
       <c r="AC37" s="56" t="s">
         <v>603</v>
       </c>
       <c r="AD37" s="55" t="s">
-        <v>615</v>
+        <v>612</v>
       </c>
       <c r="AE37" s="56" t="s">
         <v>606</v>
       </c>
       <c r="AF37" s="55" t="s">
-        <v>616</v>
+        <v>612</v>
       </c>
       <c r="AG37" s="56" t="s">
         <v>609</v>
@@ -12233,25 +12402,25 @@
         <v>596</v>
       </c>
       <c r="Z38" s="55" t="s">
-        <v>613</v>
+        <v>612</v>
       </c>
       <c r="AA38" s="56" t="s">
         <v>600</v>
       </c>
       <c r="AB38" s="55" t="s">
-        <v>614</v>
+        <v>612</v>
       </c>
       <c r="AC38" s="56" t="s">
         <v>603</v>
       </c>
       <c r="AD38" s="55" t="s">
-        <v>615</v>
+        <v>612</v>
       </c>
       <c r="AE38" s="56" t="s">
         <v>606</v>
       </c>
       <c r="AF38" s="55" t="s">
-        <v>616</v>
+        <v>612</v>
       </c>
       <c r="AG38" s="56" t="s">
         <v>609</v>
@@ -12334,25 +12503,25 @@
         <v>596</v>
       </c>
       <c r="Z39" s="55" t="s">
-        <v>613</v>
+        <v>612</v>
       </c>
       <c r="AA39" s="56" t="s">
         <v>600</v>
       </c>
       <c r="AB39" s="55" t="s">
-        <v>614</v>
+        <v>612</v>
       </c>
       <c r="AC39" s="56" t="s">
         <v>603</v>
       </c>
       <c r="AD39" s="55" t="s">
-        <v>615</v>
+        <v>612</v>
       </c>
       <c r="AE39" s="56" t="s">
         <v>606</v>
       </c>
       <c r="AF39" s="55" t="s">
-        <v>616</v>
+        <v>612</v>
       </c>
       <c r="AG39" s="56" t="s">
         <v>609</v>
@@ -12435,25 +12604,25 @@
         <v>596</v>
       </c>
       <c r="Z40" s="55" t="s">
-        <v>613</v>
+        <v>612</v>
       </c>
       <c r="AA40" s="56" t="s">
         <v>600</v>
       </c>
       <c r="AB40" s="55" t="s">
-        <v>614</v>
+        <v>612</v>
       </c>
       <c r="AC40" s="56" t="s">
         <v>603</v>
       </c>
       <c r="AD40" s="55" t="s">
-        <v>615</v>
+        <v>612</v>
       </c>
       <c r="AE40" s="56" t="s">
         <v>606</v>
       </c>
       <c r="AF40" s="55" t="s">
-        <v>616</v>
+        <v>612</v>
       </c>
       <c r="AG40" s="56" t="s">
         <v>609</v>
@@ -12536,25 +12705,25 @@
         <v>596</v>
       </c>
       <c r="Z41" s="55" t="s">
-        <v>613</v>
+        <v>612</v>
       </c>
       <c r="AA41" s="56" t="s">
         <v>600</v>
       </c>
       <c r="AB41" s="55" t="s">
-        <v>614</v>
+        <v>612</v>
       </c>
       <c r="AC41" s="56" t="s">
         <v>603</v>
       </c>
       <c r="AD41" s="55" t="s">
-        <v>615</v>
+        <v>612</v>
       </c>
       <c r="AE41" s="56" t="s">
         <v>606</v>
       </c>
       <c r="AF41" s="55" t="s">
-        <v>616</v>
+        <v>612</v>
       </c>
       <c r="AG41" s="56" t="s">
         <v>609</v>
@@ -12637,25 +12806,25 @@
         <v>596</v>
       </c>
       <c r="Z42" s="55" t="s">
-        <v>613</v>
+        <v>612</v>
       </c>
       <c r="AA42" s="56" t="s">
         <v>600</v>
       </c>
       <c r="AB42" s="55" t="s">
-        <v>614</v>
+        <v>612</v>
       </c>
       <c r="AC42" s="56" t="s">
         <v>603</v>
       </c>
       <c r="AD42" s="55" t="s">
-        <v>615</v>
+        <v>612</v>
       </c>
       <c r="AE42" s="56" t="s">
         <v>606</v>
       </c>
       <c r="AF42" s="55" t="s">
-        <v>616</v>
+        <v>612</v>
       </c>
       <c r="AG42" s="56" t="s">
         <v>609</v>
@@ -12738,25 +12907,25 @@
         <v>596</v>
       </c>
       <c r="Z43" s="55" t="s">
-        <v>613</v>
+        <v>612</v>
       </c>
       <c r="AA43" s="56" t="s">
         <v>600</v>
       </c>
       <c r="AB43" s="55" t="s">
-        <v>614</v>
+        <v>612</v>
       </c>
       <c r="AC43" s="56" t="s">
         <v>603</v>
       </c>
       <c r="AD43" s="55" t="s">
-        <v>615</v>
+        <v>612</v>
       </c>
       <c r="AE43" s="56" t="s">
         <v>606</v>
       </c>
       <c r="AF43" s="55" t="s">
-        <v>616</v>
+        <v>612</v>
       </c>
       <c r="AG43" s="56" t="s">
         <v>609</v>
@@ -12839,25 +13008,25 @@
         <v>596</v>
       </c>
       <c r="Z44" s="55" t="s">
-        <v>613</v>
+        <v>612</v>
       </c>
       <c r="AA44" s="56" t="s">
         <v>600</v>
       </c>
       <c r="AB44" s="55" t="s">
-        <v>614</v>
+        <v>612</v>
       </c>
       <c r="AC44" s="56" t="s">
         <v>603</v>
       </c>
       <c r="AD44" s="55" t="s">
-        <v>615</v>
+        <v>612</v>
       </c>
       <c r="AE44" s="56" t="s">
         <v>606</v>
       </c>
       <c r="AF44" s="55" t="s">
-        <v>616</v>
+        <v>612</v>
       </c>
       <c r="AG44" s="56" t="s">
         <v>609</v>
@@ -12940,25 +13109,25 @@
         <v>596</v>
       </c>
       <c r="Z45" s="55" t="s">
-        <v>613</v>
+        <v>612</v>
       </c>
       <c r="AA45" s="56" t="s">
         <v>600</v>
       </c>
       <c r="AB45" s="55" t="s">
-        <v>614</v>
+        <v>612</v>
       </c>
       <c r="AC45" s="56" t="s">
         <v>603</v>
       </c>
       <c r="AD45" s="55" t="s">
-        <v>615</v>
+        <v>612</v>
       </c>
       <c r="AE45" s="56" t="s">
         <v>606</v>
       </c>
       <c r="AF45" s="55" t="s">
-        <v>616</v>
+        <v>612</v>
       </c>
       <c r="AG45" s="56" t="s">
         <v>609</v>
@@ -13041,25 +13210,25 @@
         <v>596</v>
       </c>
       <c r="Z46" s="55" t="s">
-        <v>613</v>
+        <v>612</v>
       </c>
       <c r="AA46" s="56" t="s">
         <v>600</v>
       </c>
       <c r="AB46" s="55" t="s">
-        <v>614</v>
+        <v>612</v>
       </c>
       <c r="AC46" s="56" t="s">
         <v>603</v>
       </c>
       <c r="AD46" s="55" t="s">
-        <v>615</v>
+        <v>612</v>
       </c>
       <c r="AE46" s="56" t="s">
         <v>606</v>
       </c>
       <c r="AF46" s="55" t="s">
-        <v>616</v>
+        <v>612</v>
       </c>
       <c r="AG46" s="56" t="s">
         <v>609</v>
@@ -13142,25 +13311,25 @@
         <v>596</v>
       </c>
       <c r="Z47" s="55" t="s">
-        <v>613</v>
+        <v>612</v>
       </c>
       <c r="AA47" s="56" t="s">
         <v>600</v>
       </c>
       <c r="AB47" s="55" t="s">
-        <v>614</v>
+        <v>612</v>
       </c>
       <c r="AC47" s="56" t="s">
         <v>603</v>
       </c>
       <c r="AD47" s="55" t="s">
-        <v>615</v>
+        <v>612</v>
       </c>
       <c r="AE47" s="56" t="s">
         <v>606</v>
       </c>
       <c r="AF47" s="55" t="s">
-        <v>616</v>
+        <v>612</v>
       </c>
       <c r="AG47" s="56" t="s">
         <v>609</v>
@@ -13243,25 +13412,25 @@
         <v>596</v>
       </c>
       <c r="Z48" s="55" t="s">
-        <v>613</v>
+        <v>612</v>
       </c>
       <c r="AA48" s="56" t="s">
         <v>600</v>
       </c>
       <c r="AB48" s="55" t="s">
-        <v>614</v>
+        <v>612</v>
       </c>
       <c r="AC48" s="56" t="s">
         <v>603</v>
       </c>
       <c r="AD48" s="55" t="s">
-        <v>615</v>
+        <v>612</v>
       </c>
       <c r="AE48" s="56" t="s">
         <v>606</v>
       </c>
       <c r="AF48" s="55" t="s">
-        <v>616</v>
+        <v>612</v>
       </c>
       <c r="AG48" s="56" t="s">
         <v>609</v>
@@ -13344,25 +13513,25 @@
         <v>596</v>
       </c>
       <c r="Z49" s="55" t="s">
-        <v>613</v>
+        <v>612</v>
       </c>
       <c r="AA49" s="56" t="s">
         <v>600</v>
       </c>
       <c r="AB49" s="55" t="s">
-        <v>614</v>
+        <v>612</v>
       </c>
       <c r="AC49" s="56" t="s">
         <v>603</v>
       </c>
       <c r="AD49" s="55" t="s">
-        <v>615</v>
+        <v>612</v>
       </c>
       <c r="AE49" s="56" t="s">
         <v>606</v>
       </c>
       <c r="AF49" s="55" t="s">
-        <v>616</v>
+        <v>612</v>
       </c>
       <c r="AG49" s="56" t="s">
         <v>609</v>
@@ -13445,25 +13614,25 @@
         <v>596</v>
       </c>
       <c r="Z50" s="55" t="s">
-        <v>613</v>
+        <v>612</v>
       </c>
       <c r="AA50" s="56" t="s">
         <v>600</v>
       </c>
       <c r="AB50" s="55" t="s">
-        <v>614</v>
+        <v>612</v>
       </c>
       <c r="AC50" s="56" t="s">
         <v>603</v>
       </c>
       <c r="AD50" s="55" t="s">
-        <v>615</v>
+        <v>612</v>
       </c>
       <c r="AE50" s="56" t="s">
         <v>606</v>
       </c>
       <c r="AF50" s="55" t="s">
-        <v>616</v>
+        <v>612</v>
       </c>
       <c r="AG50" s="56" t="s">
         <v>609</v>
@@ -13546,25 +13715,25 @@
         <v>596</v>
       </c>
       <c r="Z51" s="55" t="s">
-        <v>613</v>
+        <v>612</v>
       </c>
       <c r="AA51" s="56" t="s">
         <v>600</v>
       </c>
       <c r="AB51" s="55" t="s">
-        <v>614</v>
+        <v>612</v>
       </c>
       <c r="AC51" s="56" t="s">
         <v>603</v>
       </c>
       <c r="AD51" s="55" t="s">
-        <v>615</v>
+        <v>612</v>
       </c>
       <c r="AE51" s="56" t="s">
         <v>606</v>
       </c>
       <c r="AF51" s="55" t="s">
-        <v>616</v>
+        <v>612</v>
       </c>
       <c r="AG51" s="56" t="s">
         <v>609</v>
@@ -13647,25 +13816,25 @@
         <v>596</v>
       </c>
       <c r="Z52" s="55" t="s">
-        <v>613</v>
+        <v>612</v>
       </c>
       <c r="AA52" s="56" t="s">
         <v>600</v>
       </c>
       <c r="AB52" s="55" t="s">
-        <v>614</v>
+        <v>612</v>
       </c>
       <c r="AC52" s="56" t="s">
         <v>603</v>
       </c>
       <c r="AD52" s="55" t="s">
-        <v>615</v>
+        <v>612</v>
       </c>
       <c r="AE52" s="56" t="s">
         <v>606</v>
       </c>
       <c r="AF52" s="55" t="s">
-        <v>616</v>
+        <v>612</v>
       </c>
       <c r="AG52" s="56" t="s">
         <v>609</v>
@@ -13748,25 +13917,25 @@
         <v>596</v>
       </c>
       <c r="Z53" s="55" t="s">
-        <v>613</v>
+        <v>612</v>
       </c>
       <c r="AA53" s="56" t="s">
         <v>600</v>
       </c>
       <c r="AB53" s="55" t="s">
-        <v>614</v>
+        <v>612</v>
       </c>
       <c r="AC53" s="56" t="s">
         <v>603</v>
       </c>
       <c r="AD53" s="55" t="s">
-        <v>615</v>
+        <v>612</v>
       </c>
       <c r="AE53" s="56" t="s">
         <v>606</v>
       </c>
       <c r="AF53" s="55" t="s">
-        <v>616</v>
+        <v>612</v>
       </c>
       <c r="AG53" s="56" t="s">
         <v>609</v>
@@ -13849,25 +14018,25 @@
         <v>596</v>
       </c>
       <c r="Z54" s="55" t="s">
-        <v>613</v>
+        <v>612</v>
       </c>
       <c r="AA54" s="56" t="s">
         <v>600</v>
       </c>
       <c r="AB54" s="55" t="s">
-        <v>614</v>
+        <v>612</v>
       </c>
       <c r="AC54" s="56" t="s">
         <v>603</v>
       </c>
       <c r="AD54" s="55" t="s">
-        <v>615</v>
+        <v>612</v>
       </c>
       <c r="AE54" s="56" t="s">
         <v>606</v>
       </c>
       <c r="AF54" s="55" t="s">
-        <v>616</v>
+        <v>612</v>
       </c>
       <c r="AG54" s="56" t="s">
         <v>609</v>
@@ -13950,25 +14119,25 @@
         <v>596</v>
       </c>
       <c r="Z55" s="55" t="s">
-        <v>613</v>
+        <v>612</v>
       </c>
       <c r="AA55" s="56" t="s">
         <v>600</v>
       </c>
       <c r="AB55" s="55" t="s">
-        <v>614</v>
+        <v>612</v>
       </c>
       <c r="AC55" s="56" t="s">
         <v>603</v>
       </c>
       <c r="AD55" s="55" t="s">
-        <v>615</v>
+        <v>612</v>
       </c>
       <c r="AE55" s="56" t="s">
         <v>606</v>
       </c>
       <c r="AF55" s="55" t="s">
-        <v>616</v>
+        <v>612</v>
       </c>
       <c r="AG55" s="56" t="s">
         <v>609</v>
@@ -14051,25 +14220,25 @@
         <v>596</v>
       </c>
       <c r="Z56" s="55" t="s">
-        <v>613</v>
+        <v>612</v>
       </c>
       <c r="AA56" s="56" t="s">
         <v>600</v>
       </c>
       <c r="AB56" s="55" t="s">
-        <v>614</v>
+        <v>612</v>
       </c>
       <c r="AC56" s="56" t="s">
         <v>603</v>
       </c>
       <c r="AD56" s="55" t="s">
-        <v>615</v>
+        <v>612</v>
       </c>
       <c r="AE56" s="56" t="s">
         <v>606</v>
       </c>
       <c r="AF56" s="55" t="s">
-        <v>616</v>
+        <v>612</v>
       </c>
       <c r="AG56" s="56" t="s">
         <v>609</v>
@@ -14152,25 +14321,25 @@
         <v>596</v>
       </c>
       <c r="Z57" s="55" t="s">
-        <v>613</v>
+        <v>612</v>
       </c>
       <c r="AA57" s="56" t="s">
         <v>600</v>
       </c>
       <c r="AB57" s="55" t="s">
-        <v>614</v>
+        <v>612</v>
       </c>
       <c r="AC57" s="56" t="s">
         <v>603</v>
       </c>
       <c r="AD57" s="55" t="s">
-        <v>615</v>
+        <v>612</v>
       </c>
       <c r="AE57" s="56" t="s">
         <v>606</v>
       </c>
       <c r="AF57" s="55" t="s">
-        <v>616</v>
+        <v>612</v>
       </c>
       <c r="AG57" s="56" t="s">
         <v>609</v>
@@ -14253,25 +14422,25 @@
         <v>596</v>
       </c>
       <c r="Z58" s="55" t="s">
-        <v>613</v>
+        <v>612</v>
       </c>
       <c r="AA58" s="56" t="s">
         <v>600</v>
       </c>
       <c r="AB58" s="55" t="s">
-        <v>614</v>
+        <v>612</v>
       </c>
       <c r="AC58" s="56" t="s">
         <v>603</v>
       </c>
       <c r="AD58" s="55" t="s">
-        <v>615</v>
+        <v>612</v>
       </c>
       <c r="AE58" s="56" t="s">
         <v>606</v>
       </c>
       <c r="AF58" s="55" t="s">
-        <v>616</v>
+        <v>612</v>
       </c>
       <c r="AG58" s="56" t="s">
         <v>609</v>
@@ -14354,25 +14523,25 @@
         <v>596</v>
       </c>
       <c r="Z59" s="55" t="s">
-        <v>613</v>
+        <v>612</v>
       </c>
       <c r="AA59" s="56" t="s">
         <v>600</v>
       </c>
       <c r="AB59" s="55" t="s">
-        <v>614</v>
+        <v>612</v>
       </c>
       <c r="AC59" s="56" t="s">
         <v>603</v>
       </c>
       <c r="AD59" s="55" t="s">
-        <v>615</v>
+        <v>612</v>
       </c>
       <c r="AE59" s="56" t="s">
         <v>606</v>
       </c>
       <c r="AF59" s="55" t="s">
-        <v>616</v>
+        <v>612</v>
       </c>
       <c r="AG59" s="56" t="s">
         <v>609</v>
@@ -14455,25 +14624,25 @@
         <v>596</v>
       </c>
       <c r="Z60" s="55" t="s">
-        <v>613</v>
+        <v>612</v>
       </c>
       <c r="AA60" s="56" t="s">
         <v>600</v>
       </c>
       <c r="AB60" s="55" t="s">
-        <v>614</v>
+        <v>612</v>
       </c>
       <c r="AC60" s="56" t="s">
         <v>603</v>
       </c>
       <c r="AD60" s="55" t="s">
-        <v>615</v>
+        <v>612</v>
       </c>
       <c r="AE60" s="56" t="s">
         <v>606</v>
       </c>
       <c r="AF60" s="55" t="s">
-        <v>616</v>
+        <v>612</v>
       </c>
       <c r="AG60" s="56" t="s">
         <v>609</v>
@@ -14556,25 +14725,25 @@
         <v>596</v>
       </c>
       <c r="Z61" s="55" t="s">
-        <v>613</v>
+        <v>612</v>
       </c>
       <c r="AA61" s="56" t="s">
         <v>600</v>
       </c>
       <c r="AB61" s="55" t="s">
-        <v>614</v>
+        <v>612</v>
       </c>
       <c r="AC61" s="56" t="s">
         <v>603</v>
       </c>
       <c r="AD61" s="55" t="s">
-        <v>615</v>
+        <v>612</v>
       </c>
       <c r="AE61" s="56" t="s">
         <v>606</v>
       </c>
       <c r="AF61" s="55" t="s">
-        <v>616</v>
+        <v>612</v>
       </c>
       <c r="AG61" s="56" t="s">
         <v>609</v>
@@ -14657,25 +14826,25 @@
         <v>596</v>
       </c>
       <c r="Z62" s="55" t="s">
-        <v>613</v>
+        <v>612</v>
       </c>
       <c r="AA62" s="56" t="s">
         <v>600</v>
       </c>
       <c r="AB62" s="55" t="s">
-        <v>614</v>
+        <v>612</v>
       </c>
       <c r="AC62" s="56" t="s">
         <v>603</v>
       </c>
       <c r="AD62" s="55" t="s">
-        <v>615</v>
+        <v>612</v>
       </c>
       <c r="AE62" s="56" t="s">
         <v>606</v>
       </c>
       <c r="AF62" s="55" t="s">
-        <v>616</v>
+        <v>612</v>
       </c>
       <c r="AG62" s="56" t="s">
         <v>609</v>
@@ -14758,25 +14927,25 @@
         <v>596</v>
       </c>
       <c r="Z63" s="55" t="s">
-        <v>613</v>
+        <v>612</v>
       </c>
       <c r="AA63" s="56" t="s">
         <v>600</v>
       </c>
       <c r="AB63" s="55" t="s">
-        <v>614</v>
+        <v>612</v>
       </c>
       <c r="AC63" s="56" t="s">
         <v>603</v>
       </c>
       <c r="AD63" s="55" t="s">
-        <v>615</v>
+        <v>612</v>
       </c>
       <c r="AE63" s="56" t="s">
         <v>606</v>
       </c>
       <c r="AF63" s="55" t="s">
-        <v>616</v>
+        <v>612</v>
       </c>
       <c r="AG63" s="56" t="s">
         <v>609</v>
@@ -14859,25 +15028,25 @@
         <v>596</v>
       </c>
       <c r="Z64" s="55" t="s">
-        <v>613</v>
+        <v>612</v>
       </c>
       <c r="AA64" s="56" t="s">
         <v>600</v>
       </c>
       <c r="AB64" s="55" t="s">
-        <v>614</v>
+        <v>612</v>
       </c>
       <c r="AC64" s="56" t="s">
         <v>603</v>
       </c>
       <c r="AD64" s="55" t="s">
-        <v>615</v>
+        <v>612</v>
       </c>
       <c r="AE64" s="56" t="s">
         <v>606</v>
       </c>
       <c r="AF64" s="55" t="s">
-        <v>616</v>
+        <v>612</v>
       </c>
       <c r="AG64" s="56" t="s">
         <v>609</v>
@@ -14960,25 +15129,25 @@
         <v>596</v>
       </c>
       <c r="Z65" s="55" t="s">
-        <v>613</v>
+        <v>612</v>
       </c>
       <c r="AA65" s="56" t="s">
         <v>600</v>
       </c>
       <c r="AB65" s="55" t="s">
-        <v>614</v>
+        <v>612</v>
       </c>
       <c r="AC65" s="56" t="s">
         <v>603</v>
       </c>
       <c r="AD65" s="55" t="s">
-        <v>615</v>
+        <v>612</v>
       </c>
       <c r="AE65" s="56" t="s">
         <v>606</v>
       </c>
       <c r="AF65" s="55" t="s">
-        <v>616</v>
+        <v>612</v>
       </c>
       <c r="AG65" s="56" t="s">
         <v>609</v>
@@ -15061,25 +15230,25 @@
         <v>596</v>
       </c>
       <c r="Z66" s="55" t="s">
-        <v>613</v>
+        <v>612</v>
       </c>
       <c r="AA66" s="56" t="s">
         <v>600</v>
       </c>
       <c r="AB66" s="55" t="s">
-        <v>614</v>
+        <v>612</v>
       </c>
       <c r="AC66" s="56" t="s">
         <v>603</v>
       </c>
       <c r="AD66" s="55" t="s">
-        <v>615</v>
+        <v>612</v>
       </c>
       <c r="AE66" s="56" t="s">
         <v>606</v>
       </c>
       <c r="AF66" s="55" t="s">
-        <v>616</v>
+        <v>612</v>
       </c>
       <c r="AG66" s="56" t="s">
         <v>609</v>
@@ -15162,25 +15331,25 @@
         <v>596</v>
       </c>
       <c r="Z67" s="55" t="s">
-        <v>613</v>
+        <v>612</v>
       </c>
       <c r="AA67" s="56" t="s">
         <v>600</v>
       </c>
       <c r="AB67" s="55" t="s">
-        <v>614</v>
+        <v>612</v>
       </c>
       <c r="AC67" s="56" t="s">
         <v>603</v>
       </c>
       <c r="AD67" s="55" t="s">
-        <v>615</v>
+        <v>612</v>
       </c>
       <c r="AE67" s="56" t="s">
         <v>606</v>
       </c>
       <c r="AF67" s="55" t="s">
-        <v>616</v>
+        <v>612</v>
       </c>
       <c r="AG67" s="56" t="s">
         <v>609</v>
@@ -15263,25 +15432,25 @@
         <v>596</v>
       </c>
       <c r="Z68" s="55" t="s">
-        <v>613</v>
+        <v>612</v>
       </c>
       <c r="AA68" s="56" t="s">
         <v>600</v>
       </c>
       <c r="AB68" s="55" t="s">
-        <v>614</v>
+        <v>612</v>
       </c>
       <c r="AC68" s="56" t="s">
         <v>603</v>
       </c>
       <c r="AD68" s="55" t="s">
-        <v>615</v>
+        <v>612</v>
       </c>
       <c r="AE68" s="56" t="s">
         <v>606</v>
       </c>
       <c r="AF68" s="55" t="s">
-        <v>616</v>
+        <v>612</v>
       </c>
       <c r="AG68" s="56" t="s">
         <v>609</v>
@@ -15364,25 +15533,25 @@
         <v>596</v>
       </c>
       <c r="Z69" s="55" t="s">
-        <v>613</v>
+        <v>612</v>
       </c>
       <c r="AA69" s="56" t="s">
         <v>600</v>
       </c>
       <c r="AB69" s="55" t="s">
-        <v>614</v>
+        <v>612</v>
       </c>
       <c r="AC69" s="56" t="s">
         <v>603</v>
       </c>
       <c r="AD69" s="55" t="s">
-        <v>615</v>
+        <v>612</v>
       </c>
       <c r="AE69" s="56" t="s">
         <v>606</v>
       </c>
       <c r="AF69" s="55" t="s">
-        <v>616</v>
+        <v>612</v>
       </c>
       <c r="AG69" s="56" t="s">
         <v>609</v>
@@ -15465,25 +15634,25 @@
         <v>596</v>
       </c>
       <c r="Z70" s="55" t="s">
-        <v>613</v>
+        <v>612</v>
       </c>
       <c r="AA70" s="56" t="s">
         <v>600</v>
       </c>
       <c r="AB70" s="55" t="s">
-        <v>614</v>
+        <v>612</v>
       </c>
       <c r="AC70" s="56" t="s">
         <v>603</v>
       </c>
       <c r="AD70" s="55" t="s">
-        <v>615</v>
+        <v>612</v>
       </c>
       <c r="AE70" s="56" t="s">
         <v>606</v>
       </c>
       <c r="AF70" s="55" t="s">
-        <v>616</v>
+        <v>612</v>
       </c>
       <c r="AG70" s="56" t="s">
         <v>609</v>
@@ -15566,25 +15735,25 @@
         <v>596</v>
       </c>
       <c r="Z71" s="55" t="s">
-        <v>613</v>
+        <v>612</v>
       </c>
       <c r="AA71" s="56" t="s">
         <v>600</v>
       </c>
       <c r="AB71" s="55" t="s">
-        <v>614</v>
+        <v>612</v>
       </c>
       <c r="AC71" s="56" t="s">
         <v>603</v>
       </c>
       <c r="AD71" s="55" t="s">
-        <v>615</v>
+        <v>612</v>
       </c>
       <c r="AE71" s="56" t="s">
         <v>606</v>
       </c>
       <c r="AF71" s="55" t="s">
-        <v>616</v>
+        <v>612</v>
       </c>
       <c r="AG71" s="56" t="s">
         <v>609</v>
@@ -15667,25 +15836,25 @@
         <v>596</v>
       </c>
       <c r="Z72" s="55" t="s">
-        <v>613</v>
+        <v>612</v>
       </c>
       <c r="AA72" s="56" t="s">
         <v>600</v>
       </c>
       <c r="AB72" s="55" t="s">
-        <v>614</v>
+        <v>612</v>
       </c>
       <c r="AC72" s="56" t="s">
         <v>603</v>
       </c>
       <c r="AD72" s="55" t="s">
-        <v>615</v>
+        <v>612</v>
       </c>
       <c r="AE72" s="56" t="s">
         <v>606</v>
       </c>
       <c r="AF72" s="55" t="s">
-        <v>616</v>
+        <v>612</v>
       </c>
       <c r="AG72" s="56" t="s">
         <v>609</v>
@@ -15768,25 +15937,25 @@
         <v>596</v>
       </c>
       <c r="Z73" s="55" t="s">
-        <v>613</v>
+        <v>612</v>
       </c>
       <c r="AA73" s="56" t="s">
         <v>600</v>
       </c>
       <c r="AB73" s="55" t="s">
-        <v>614</v>
+        <v>612</v>
       </c>
       <c r="AC73" s="56" t="s">
         <v>603</v>
       </c>
       <c r="AD73" s="55" t="s">
-        <v>615</v>
+        <v>612</v>
       </c>
       <c r="AE73" s="56" t="s">
         <v>606</v>
       </c>
       <c r="AF73" s="55" t="s">
-        <v>616</v>
+        <v>612</v>
       </c>
       <c r="AG73" s="56" t="s">
         <v>609</v>
@@ -15869,25 +16038,25 @@
         <v>596</v>
       </c>
       <c r="Z74" s="55" t="s">
-        <v>613</v>
+        <v>612</v>
       </c>
       <c r="AA74" s="56" t="s">
         <v>600</v>
       </c>
       <c r="AB74" s="55" t="s">
-        <v>614</v>
+        <v>612</v>
       </c>
       <c r="AC74" s="56" t="s">
         <v>603</v>
       </c>
       <c r="AD74" s="55" t="s">
-        <v>615</v>
+        <v>612</v>
       </c>
       <c r="AE74" s="56" t="s">
         <v>606</v>
       </c>
       <c r="AF74" s="55" t="s">
-        <v>616</v>
+        <v>612</v>
       </c>
       <c r="AG74" s="56" t="s">
         <v>609</v>
@@ -15970,25 +16139,25 @@
         <v>596</v>
       </c>
       <c r="Z75" s="55" t="s">
-        <v>613</v>
+        <v>612</v>
       </c>
       <c r="AA75" s="56" t="s">
         <v>600</v>
       </c>
       <c r="AB75" s="55" t="s">
-        <v>614</v>
+        <v>612</v>
       </c>
       <c r="AC75" s="56" t="s">
         <v>603</v>
       </c>
       <c r="AD75" s="55" t="s">
-        <v>615</v>
+        <v>612</v>
       </c>
       <c r="AE75" s="56" t="s">
         <v>606</v>
       </c>
       <c r="AF75" s="55" t="s">
-        <v>616</v>
+        <v>612</v>
       </c>
       <c r="AG75" s="56" t="s">
         <v>609</v>
@@ -16071,25 +16240,25 @@
         <v>596</v>
       </c>
       <c r="Z76" s="55" t="s">
-        <v>613</v>
+        <v>612</v>
       </c>
       <c r="AA76" s="56" t="s">
         <v>600</v>
       </c>
       <c r="AB76" s="55" t="s">
-        <v>614</v>
+        <v>612</v>
       </c>
       <c r="AC76" s="56" t="s">
         <v>603</v>
       </c>
       <c r="AD76" s="55" t="s">
-        <v>615</v>
+        <v>612</v>
       </c>
       <c r="AE76" s="56" t="s">
         <v>606</v>
       </c>
       <c r="AF76" s="55" t="s">
-        <v>616</v>
+        <v>612</v>
       </c>
       <c r="AG76" s="56" t="s">
         <v>609</v>
@@ -16172,25 +16341,25 @@
         <v>596</v>
       </c>
       <c r="Z77" s="55" t="s">
-        <v>613</v>
+        <v>612</v>
       </c>
       <c r="AA77" s="56" t="s">
         <v>600</v>
       </c>
       <c r="AB77" s="55" t="s">
-        <v>614</v>
+        <v>612</v>
       </c>
       <c r="AC77" s="56" t="s">
         <v>603</v>
       </c>
       <c r="AD77" s="55" t="s">
-        <v>615</v>
+        <v>612</v>
       </c>
       <c r="AE77" s="56" t="s">
         <v>606</v>
       </c>
       <c r="AF77" s="55" t="s">
-        <v>616</v>
+        <v>612</v>
       </c>
       <c r="AG77" s="56" t="s">
         <v>609</v>
@@ -16273,25 +16442,25 @@
         <v>596</v>
       </c>
       <c r="Z78" s="55" t="s">
-        <v>613</v>
+        <v>612</v>
       </c>
       <c r="AA78" s="56" t="s">
         <v>600</v>
       </c>
       <c r="AB78" s="55" t="s">
-        <v>614</v>
+        <v>612</v>
       </c>
       <c r="AC78" s="56" t="s">
         <v>603</v>
       </c>
       <c r="AD78" s="55" t="s">
-        <v>615</v>
+        <v>612</v>
       </c>
       <c r="AE78" s="56" t="s">
         <v>606</v>
       </c>
       <c r="AF78" s="55" t="s">
-        <v>616</v>
+        <v>612</v>
       </c>
       <c r="AG78" s="56" t="s">
         <v>609</v>
@@ -16374,25 +16543,25 @@
         <v>596</v>
       </c>
       <c r="Z79" s="55" t="s">
-        <v>613</v>
+        <v>612</v>
       </c>
       <c r="AA79" s="56" t="s">
         <v>600</v>
       </c>
       <c r="AB79" s="55" t="s">
-        <v>614</v>
+        <v>612</v>
       </c>
       <c r="AC79" s="56" t="s">
         <v>603</v>
       </c>
       <c r="AD79" s="55" t="s">
-        <v>615</v>
+        <v>612</v>
       </c>
       <c r="AE79" s="56" t="s">
         <v>606</v>
       </c>
       <c r="AF79" s="55" t="s">
-        <v>616</v>
+        <v>612</v>
       </c>
       <c r="AG79" s="56" t="s">
         <v>609</v>
@@ -16475,25 +16644,25 @@
         <v>596</v>
       </c>
       <c r="Z80" s="55" t="s">
-        <v>613</v>
+        <v>612</v>
       </c>
       <c r="AA80" s="56" t="s">
         <v>600</v>
       </c>
       <c r="AB80" s="55" t="s">
-        <v>614</v>
+        <v>612</v>
       </c>
       <c r="AC80" s="56" t="s">
         <v>603</v>
       </c>
       <c r="AD80" s="55" t="s">
-        <v>615</v>
+        <v>612</v>
       </c>
       <c r="AE80" s="56" t="s">
         <v>606</v>
       </c>
       <c r="AF80" s="55" t="s">
-        <v>616</v>
+        <v>612</v>
       </c>
       <c r="AG80" s="56" t="s">
         <v>609</v>
@@ -16576,25 +16745,25 @@
         <v>596</v>
       </c>
       <c r="Z81" s="55" t="s">
-        <v>613</v>
+        <v>612</v>
       </c>
       <c r="AA81" s="56" t="s">
         <v>600</v>
       </c>
       <c r="AB81" s="55" t="s">
-        <v>614</v>
+        <v>612</v>
       </c>
       <c r="AC81" s="56" t="s">
         <v>603</v>
       </c>
       <c r="AD81" s="55" t="s">
-        <v>615</v>
+        <v>612</v>
       </c>
       <c r="AE81" s="56" t="s">
         <v>606</v>
       </c>
       <c r="AF81" s="55" t="s">
-        <v>616</v>
+        <v>612</v>
       </c>
       <c r="AG81" s="56" t="s">
         <v>609</v>
@@ -16677,25 +16846,25 @@
         <v>596</v>
       </c>
       <c r="Z82" s="55" t="s">
-        <v>613</v>
+        <v>612</v>
       </c>
       <c r="AA82" s="56" t="s">
         <v>600</v>
       </c>
       <c r="AB82" s="55" t="s">
-        <v>614</v>
+        <v>612</v>
       </c>
       <c r="AC82" s="56" t="s">
         <v>603</v>
       </c>
       <c r="AD82" s="55" t="s">
-        <v>615</v>
+        <v>612</v>
       </c>
       <c r="AE82" s="56" t="s">
         <v>606</v>
       </c>
       <c r="AF82" s="55" t="s">
-        <v>616</v>
+        <v>612</v>
       </c>
       <c r="AG82" s="56" t="s">
         <v>609</v>
@@ -16778,25 +16947,25 @@
         <v>596</v>
       </c>
       <c r="Z83" s="55" t="s">
-        <v>613</v>
+        <v>612</v>
       </c>
       <c r="AA83" s="56" t="s">
         <v>600</v>
       </c>
       <c r="AB83" s="55" t="s">
-        <v>614</v>
+        <v>612</v>
       </c>
       <c r="AC83" s="56" t="s">
         <v>603</v>
       </c>
       <c r="AD83" s="55" t="s">
-        <v>615</v>
+        <v>612</v>
       </c>
       <c r="AE83" s="56" t="s">
         <v>606</v>
       </c>
       <c r="AF83" s="55" t="s">
-        <v>616</v>
+        <v>612</v>
       </c>
       <c r="AG83" s="56" t="s">
         <v>609</v>
@@ -16879,25 +17048,25 @@
         <v>596</v>
       </c>
       <c r="Z84" s="55" t="s">
-        <v>613</v>
+        <v>612</v>
       </c>
       <c r="AA84" s="56" t="s">
         <v>600</v>
       </c>
       <c r="AB84" s="55" t="s">
-        <v>614</v>
+        <v>612</v>
       </c>
       <c r="AC84" s="56" t="s">
         <v>603</v>
       </c>
       <c r="AD84" s="55" t="s">
-        <v>615</v>
+        <v>612</v>
       </c>
       <c r="AE84" s="56" t="s">
         <v>606</v>
       </c>
       <c r="AF84" s="55" t="s">
-        <v>616</v>
+        <v>612</v>
       </c>
       <c r="AG84" s="56" t="s">
         <v>609</v>
@@ -16980,25 +17149,25 @@
         <v>596</v>
       </c>
       <c r="Z85" s="55" t="s">
-        <v>613</v>
+        <v>612</v>
       </c>
       <c r="AA85" s="56" t="s">
         <v>600</v>
       </c>
       <c r="AB85" s="55" t="s">
-        <v>614</v>
+        <v>612</v>
       </c>
       <c r="AC85" s="56" t="s">
         <v>603</v>
       </c>
       <c r="AD85" s="55" t="s">
-        <v>615</v>
+        <v>612</v>
       </c>
       <c r="AE85" s="56" t="s">
         <v>606</v>
       </c>
       <c r="AF85" s="55" t="s">
-        <v>616</v>
+        <v>612</v>
       </c>
       <c r="AG85" s="56" t="s">
         <v>609</v>
@@ -17081,25 +17250,25 @@
         <v>596</v>
       </c>
       <c r="Z86" s="55" t="s">
-        <v>613</v>
+        <v>612</v>
       </c>
       <c r="AA86" s="56" t="s">
         <v>600</v>
       </c>
       <c r="AB86" s="55" t="s">
-        <v>614</v>
+        <v>612</v>
       </c>
       <c r="AC86" s="56" t="s">
         <v>603</v>
       </c>
       <c r="AD86" s="55" t="s">
-        <v>615</v>
+        <v>612</v>
       </c>
       <c r="AE86" s="56" t="s">
         <v>606</v>
       </c>
       <c r="AF86" s="55" t="s">
-        <v>616</v>
+        <v>612</v>
       </c>
       <c r="AG86" s="56" t="s">
         <v>609</v>
@@ -17182,25 +17351,25 @@
         <v>596</v>
       </c>
       <c r="Z87" s="55" t="s">
-        <v>613</v>
+        <v>612</v>
       </c>
       <c r="AA87" s="56" t="s">
         <v>600</v>
       </c>
       <c r="AB87" s="55" t="s">
-        <v>614</v>
+        <v>612</v>
       </c>
       <c r="AC87" s="56" t="s">
         <v>603</v>
       </c>
       <c r="AD87" s="55" t="s">
-        <v>615</v>
+        <v>612</v>
       </c>
       <c r="AE87" s="56" t="s">
         <v>606</v>
       </c>
       <c r="AF87" s="55" t="s">
-        <v>616</v>
+        <v>612</v>
       </c>
       <c r="AG87" s="56" t="s">
         <v>609</v>
@@ -17283,25 +17452,25 @@
         <v>596</v>
       </c>
       <c r="Z88" s="55" t="s">
-        <v>613</v>
+        <v>612</v>
       </c>
       <c r="AA88" s="56" t="s">
         <v>600</v>
       </c>
       <c r="AB88" s="55" t="s">
-        <v>614</v>
+        <v>612</v>
       </c>
       <c r="AC88" s="56" t="s">
         <v>603</v>
       </c>
       <c r="AD88" s="55" t="s">
-        <v>615</v>
+        <v>612</v>
       </c>
       <c r="AE88" s="56" t="s">
         <v>606</v>
       </c>
       <c r="AF88" s="55" t="s">
-        <v>616</v>
+        <v>612</v>
       </c>
       <c r="AG88" s="56" t="s">
         <v>609</v>
@@ -17384,25 +17553,25 @@
         <v>596</v>
       </c>
       <c r="Z89" s="55" t="s">
-        <v>613</v>
+        <v>612</v>
       </c>
       <c r="AA89" s="56" t="s">
         <v>600</v>
       </c>
       <c r="AB89" s="55" t="s">
-        <v>614</v>
+        <v>612</v>
       </c>
       <c r="AC89" s="56" t="s">
         <v>603</v>
       </c>
       <c r="AD89" s="55" t="s">
-        <v>615</v>
+        <v>612</v>
       </c>
       <c r="AE89" s="56" t="s">
         <v>606</v>
       </c>
       <c r="AF89" s="55" t="s">
-        <v>616</v>
+        <v>612</v>
       </c>
       <c r="AG89" s="56" t="s">
         <v>609</v>
@@ -17485,25 +17654,25 @@
         <v>596</v>
       </c>
       <c r="Z90" s="55" t="s">
-        <v>613</v>
+        <v>612</v>
       </c>
       <c r="AA90" s="56" t="s">
         <v>600</v>
       </c>
       <c r="AB90" s="55" t="s">
-        <v>614</v>
+        <v>612</v>
       </c>
       <c r="AC90" s="56" t="s">
         <v>603</v>
       </c>
       <c r="AD90" s="55" t="s">
-        <v>615</v>
+        <v>612</v>
       </c>
       <c r="AE90" s="56" t="s">
         <v>606</v>
       </c>
       <c r="AF90" s="55" t="s">
-        <v>616</v>
+        <v>612</v>
       </c>
       <c r="AG90" s="56" t="s">
         <v>609</v>
@@ -17586,25 +17755,25 @@
         <v>596</v>
       </c>
       <c r="Z91" s="55" t="s">
-        <v>613</v>
+        <v>612</v>
       </c>
       <c r="AA91" s="56" t="s">
         <v>600</v>
       </c>
       <c r="AB91" s="55" t="s">
-        <v>614</v>
+        <v>612</v>
       </c>
       <c r="AC91" s="56" t="s">
         <v>603</v>
       </c>
       <c r="AD91" s="55" t="s">
-        <v>615</v>
+        <v>612</v>
       </c>
       <c r="AE91" s="56" t="s">
         <v>606</v>
       </c>
       <c r="AF91" s="55" t="s">
-        <v>616</v>
+        <v>612</v>
       </c>
       <c r="AG91" s="56" t="s">
         <v>609</v>
@@ -17687,25 +17856,25 @@
         <v>596</v>
       </c>
       <c r="Z92" s="55" t="s">
-        <v>613</v>
+        <v>612</v>
       </c>
       <c r="AA92" s="56" t="s">
         <v>600</v>
       </c>
       <c r="AB92" s="55" t="s">
-        <v>614</v>
+        <v>612</v>
       </c>
       <c r="AC92" s="56" t="s">
         <v>603</v>
       </c>
       <c r="AD92" s="55" t="s">
-        <v>615</v>
+        <v>612</v>
       </c>
       <c r="AE92" s="56" t="s">
         <v>606</v>
       </c>
       <c r="AF92" s="55" t="s">
-        <v>616</v>
+        <v>612</v>
       </c>
       <c r="AG92" s="56" t="s">
         <v>609</v>
@@ -17788,25 +17957,25 @@
         <v>596</v>
       </c>
       <c r="Z93" s="55" t="s">
-        <v>613</v>
+        <v>612</v>
       </c>
       <c r="AA93" s="56" t="s">
         <v>600</v>
       </c>
       <c r="AB93" s="55" t="s">
-        <v>614</v>
+        <v>612</v>
       </c>
       <c r="AC93" s="56" t="s">
         <v>603</v>
       </c>
       <c r="AD93" s="55" t="s">
-        <v>615</v>
+        <v>612</v>
       </c>
       <c r="AE93" s="56" t="s">
         <v>606</v>
       </c>
       <c r="AF93" s="55" t="s">
-        <v>616</v>
+        <v>612</v>
       </c>
       <c r="AG93" s="56" t="s">
         <v>609</v>
@@ -17889,25 +18058,25 @@
         <v>596</v>
       </c>
       <c r="Z94" s="55" t="s">
-        <v>613</v>
+        <v>612</v>
       </c>
       <c r="AA94" s="56" t="s">
         <v>600</v>
       </c>
       <c r="AB94" s="55" t="s">
-        <v>614</v>
+        <v>612</v>
       </c>
       <c r="AC94" s="56" t="s">
         <v>603</v>
       </c>
       <c r="AD94" s="55" t="s">
-        <v>615</v>
+        <v>612</v>
       </c>
       <c r="AE94" s="56" t="s">
         <v>606</v>
       </c>
       <c r="AF94" s="55" t="s">
-        <v>616</v>
+        <v>612</v>
       </c>
       <c r="AG94" s="56" t="s">
         <v>609</v>
@@ -17990,25 +18159,25 @@
         <v>596</v>
       </c>
       <c r="Z95" s="55" t="s">
-        <v>613</v>
+        <v>612</v>
       </c>
       <c r="AA95" s="56" t="s">
         <v>600</v>
       </c>
       <c r="AB95" s="55" t="s">
-        <v>614</v>
+        <v>612</v>
       </c>
       <c r="AC95" s="56" t="s">
         <v>603</v>
       </c>
       <c r="AD95" s="55" t="s">
-        <v>615</v>
+        <v>612</v>
       </c>
       <c r="AE95" s="56" t="s">
         <v>606</v>
       </c>
       <c r="AF95" s="55" t="s">
-        <v>616</v>
+        <v>612</v>
       </c>
       <c r="AG95" s="56" t="s">
         <v>609</v>
@@ -18091,25 +18260,25 @@
         <v>596</v>
       </c>
       <c r="Z96" s="55" t="s">
-        <v>613</v>
+        <v>612</v>
       </c>
       <c r="AA96" s="56" t="s">
         <v>600</v>
       </c>
       <c r="AB96" s="55" t="s">
-        <v>614</v>
+        <v>612</v>
       </c>
       <c r="AC96" s="56" t="s">
         <v>603</v>
       </c>
       <c r="AD96" s="55" t="s">
-        <v>615</v>
+        <v>612</v>
       </c>
       <c r="AE96" s="56" t="s">
         <v>606</v>
       </c>
       <c r="AF96" s="55" t="s">
-        <v>616</v>
+        <v>612</v>
       </c>
       <c r="AG96" s="56" t="s">
         <v>609</v>
@@ -18192,25 +18361,25 @@
         <v>596</v>
       </c>
       <c r="Z97" s="55" t="s">
-        <v>613</v>
+        <v>612</v>
       </c>
       <c r="AA97" s="56" t="s">
         <v>600</v>
       </c>
       <c r="AB97" s="55" t="s">
-        <v>614</v>
+        <v>612</v>
       </c>
       <c r="AC97" s="56" t="s">
         <v>603</v>
       </c>
       <c r="AD97" s="55" t="s">
-        <v>615</v>
+        <v>612</v>
       </c>
       <c r="AE97" s="56" t="s">
         <v>606</v>
       </c>
       <c r="AF97" s="55" t="s">
-        <v>616</v>
+        <v>612</v>
       </c>
       <c r="AG97" s="56" t="s">
         <v>609</v>
@@ -18293,25 +18462,25 @@
         <v>596</v>
       </c>
       <c r="Z98" s="55" t="s">
-        <v>613</v>
+        <v>612</v>
       </c>
       <c r="AA98" s="56" t="s">
         <v>600</v>
       </c>
       <c r="AB98" s="55" t="s">
-        <v>614</v>
+        <v>612</v>
       </c>
       <c r="AC98" s="56" t="s">
         <v>603</v>
       </c>
       <c r="AD98" s="55" t="s">
-        <v>615</v>
+        <v>612</v>
       </c>
       <c r="AE98" s="56" t="s">
         <v>606</v>
       </c>
       <c r="AF98" s="55" t="s">
-        <v>616</v>
+        <v>612</v>
       </c>
       <c r="AG98" s="56" t="s">
         <v>609</v>
@@ -18394,25 +18563,25 @@
         <v>596</v>
       </c>
       <c r="Z99" s="55" t="s">
-        <v>613</v>
+        <v>612</v>
       </c>
       <c r="AA99" s="56" t="s">
         <v>600</v>
       </c>
       <c r="AB99" s="55" t="s">
-        <v>614</v>
+        <v>612</v>
       </c>
       <c r="AC99" s="56" t="s">
         <v>603</v>
       </c>
       <c r="AD99" s="55" t="s">
-        <v>615</v>
+        <v>612</v>
       </c>
       <c r="AE99" s="56" t="s">
         <v>606</v>
       </c>
       <c r="AF99" s="55" t="s">
-        <v>616</v>
+        <v>612</v>
       </c>
       <c r="AG99" s="56" t="s">
         <v>609</v>
@@ -18495,25 +18664,25 @@
         <v>596</v>
       </c>
       <c r="Z100" s="55" t="s">
-        <v>613</v>
+        <v>612</v>
       </c>
       <c r="AA100" s="56" t="s">
         <v>600</v>
       </c>
       <c r="AB100" s="55" t="s">
-        <v>614</v>
+        <v>612</v>
       </c>
       <c r="AC100" s="56" t="s">
         <v>603</v>
       </c>
       <c r="AD100" s="55" t="s">
-        <v>615</v>
+        <v>612</v>
       </c>
       <c r="AE100" s="56" t="s">
         <v>606</v>
       </c>
       <c r="AF100" s="55" t="s">
-        <v>616</v>
+        <v>612</v>
       </c>
       <c r="AG100" s="56" t="s">
         <v>609</v>
@@ -18596,25 +18765,25 @@
         <v>596</v>
       </c>
       <c r="Z101" s="55" t="s">
-        <v>613</v>
+        <v>612</v>
       </c>
       <c r="AA101" s="56" t="s">
         <v>600</v>
       </c>
       <c r="AB101" s="55" t="s">
-        <v>614</v>
+        <v>612</v>
       </c>
       <c r="AC101" s="56" t="s">
         <v>603</v>
       </c>
       <c r="AD101" s="55" t="s">
-        <v>615</v>
+        <v>612</v>
       </c>
       <c r="AE101" s="56" t="s">
         <v>606</v>
       </c>
       <c r="AF101" s="55" t="s">
-        <v>616</v>
+        <v>612</v>
       </c>
       <c r="AG101" s="56" t="s">
         <v>609</v>
@@ -18697,25 +18866,25 @@
         <v>596</v>
       </c>
       <c r="Z102" s="55" t="s">
-        <v>613</v>
+        <v>612</v>
       </c>
       <c r="AA102" s="56" t="s">
         <v>600</v>
       </c>
       <c r="AB102" s="55" t="s">
-        <v>614</v>
+        <v>612</v>
       </c>
       <c r="AC102" s="56" t="s">
         <v>603</v>
       </c>
       <c r="AD102" s="55" t="s">
-        <v>615</v>
+        <v>612</v>
       </c>
       <c r="AE102" s="56" t="s">
         <v>606</v>
       </c>
       <c r="AF102" s="55" t="s">
-        <v>616</v>
+        <v>612</v>
       </c>
       <c r="AG102" s="56" t="s">
         <v>609</v>
@@ -18798,25 +18967,25 @@
         <v>596</v>
       </c>
       <c r="Z103" s="55" t="s">
-        <v>613</v>
+        <v>612</v>
       </c>
       <c r="AA103" s="56" t="s">
         <v>600</v>
       </c>
       <c r="AB103" s="55" t="s">
-        <v>614</v>
+        <v>612</v>
       </c>
       <c r="AC103" s="56" t="s">
         <v>603</v>
       </c>
       <c r="AD103" s="55" t="s">
-        <v>615</v>
+        <v>612</v>
       </c>
       <c r="AE103" s="56" t="s">
         <v>606</v>
       </c>
       <c r="AF103" s="55" t="s">
-        <v>616</v>
+        <v>612</v>
       </c>
       <c r="AG103" s="56" t="s">
         <v>609</v>
@@ -18899,25 +19068,25 @@
         <v>596</v>
       </c>
       <c r="Z104" s="55" t="s">
-        <v>613</v>
+        <v>612</v>
       </c>
       <c r="AA104" s="56" t="s">
         <v>600</v>
       </c>
       <c r="AB104" s="55" t="s">
-        <v>614</v>
+        <v>612</v>
       </c>
       <c r="AC104" s="56" t="s">
         <v>603</v>
       </c>
       <c r="AD104" s="55" t="s">
-        <v>615</v>
+        <v>612</v>
       </c>
       <c r="AE104" s="56" t="s">
         <v>606</v>
       </c>
       <c r="AF104" s="55" t="s">
-        <v>616</v>
+        <v>612</v>
       </c>
       <c r="AG104" s="56" t="s">
         <v>609</v>
@@ -19000,25 +19169,25 @@
         <v>596</v>
       </c>
       <c r="Z105" s="55" t="s">
-        <v>613</v>
+        <v>612</v>
       </c>
       <c r="AA105" s="56" t="s">
         <v>600</v>
       </c>
       <c r="AB105" s="55" t="s">
-        <v>614</v>
+        <v>612</v>
       </c>
       <c r="AC105" s="56" t="s">
         <v>603</v>
       </c>
       <c r="AD105" s="55" t="s">
-        <v>615</v>
+        <v>612</v>
       </c>
       <c r="AE105" s="56" t="s">
         <v>606</v>
       </c>
       <c r="AF105" s="55" t="s">
-        <v>616</v>
+        <v>612</v>
       </c>
       <c r="AG105" s="56" t="s">
         <v>609</v>
@@ -19101,25 +19270,25 @@
         <v>596</v>
       </c>
       <c r="Z106" s="55" t="s">
-        <v>613</v>
+        <v>612</v>
       </c>
       <c r="AA106" s="56" t="s">
         <v>600</v>
       </c>
       <c r="AB106" s="55" t="s">
-        <v>614</v>
+        <v>612</v>
       </c>
       <c r="AC106" s="56" t="s">
         <v>603</v>
       </c>
       <c r="AD106" s="55" t="s">
-        <v>615</v>
+        <v>612</v>
       </c>
       <c r="AE106" s="56" t="s">
         <v>606</v>
       </c>
       <c r="AF106" s="55" t="s">
-        <v>616</v>
+        <v>612</v>
       </c>
       <c r="AG106" s="56" t="s">
         <v>609</v>
@@ -19202,25 +19371,25 @@
         <v>596</v>
       </c>
       <c r="Z107" s="55" t="s">
-        <v>613</v>
+        <v>612</v>
       </c>
       <c r="AA107" s="56" t="s">
         <v>600</v>
       </c>
       <c r="AB107" s="55" t="s">
-        <v>614</v>
+        <v>612</v>
       </c>
       <c r="AC107" s="56" t="s">
         <v>603</v>
       </c>
       <c r="AD107" s="55" t="s">
-        <v>615</v>
+        <v>612</v>
       </c>
       <c r="AE107" s="56" t="s">
         <v>606</v>
       </c>
       <c r="AF107" s="55" t="s">
-        <v>616</v>
+        <v>612</v>
       </c>
       <c r="AG107" s="56" t="s">
         <v>609</v>
@@ -19303,25 +19472,25 @@
         <v>596</v>
       </c>
       <c r="Z108" s="55" t="s">
-        <v>613</v>
+        <v>612</v>
       </c>
       <c r="AA108" s="56" t="s">
         <v>600</v>
       </c>
       <c r="AB108" s="55" t="s">
-        <v>614</v>
+        <v>612</v>
       </c>
       <c r="AC108" s="56" t="s">
         <v>603</v>
       </c>
       <c r="AD108" s="55" t="s">
-        <v>615</v>
+        <v>612</v>
       </c>
       <c r="AE108" s="56" t="s">
         <v>606</v>
       </c>
       <c r="AF108" s="55" t="s">
-        <v>616</v>
+        <v>612</v>
       </c>
       <c r="AG108" s="56" t="s">
         <v>609</v>
@@ -19404,25 +19573,25 @@
         <v>596</v>
       </c>
       <c r="Z109" s="55" t="s">
-        <v>613</v>
+        <v>612</v>
       </c>
       <c r="AA109" s="56" t="s">
         <v>600</v>
       </c>
       <c r="AB109" s="55" t="s">
-        <v>614</v>
+        <v>612</v>
       </c>
       <c r="AC109" s="56" t="s">
         <v>603</v>
       </c>
       <c r="AD109" s="55" t="s">
-        <v>615</v>
+        <v>612</v>
       </c>
       <c r="AE109" s="56" t="s">
         <v>606</v>
       </c>
       <c r="AF109" s="55" t="s">
-        <v>616</v>
+        <v>612</v>
       </c>
       <c r="AG109" s="56" t="s">
         <v>609</v>
@@ -19505,25 +19674,25 @@
         <v>596</v>
       </c>
       <c r="Z110" s="55" t="s">
-        <v>613</v>
+        <v>612</v>
       </c>
       <c r="AA110" s="56" t="s">
         <v>600</v>
       </c>
       <c r="AB110" s="55" t="s">
-        <v>614</v>
+        <v>612</v>
       </c>
       <c r="AC110" s="56" t="s">
         <v>603</v>
       </c>
       <c r="AD110" s="55" t="s">
-        <v>615</v>
+        <v>612</v>
       </c>
       <c r="AE110" s="56" t="s">
         <v>606</v>
       </c>
       <c r="AF110" s="55" t="s">
-        <v>616</v>
+        <v>612</v>
       </c>
       <c r="AG110" s="56" t="s">
         <v>609</v>
@@ -19606,25 +19775,25 @@
         <v>596</v>
       </c>
       <c r="Z111" s="55" t="s">
-        <v>613</v>
+        <v>612</v>
       </c>
       <c r="AA111" s="56" t="s">
         <v>600</v>
       </c>
       <c r="AB111" s="55" t="s">
-        <v>614</v>
+        <v>612</v>
       </c>
       <c r="AC111" s="56" t="s">
         <v>603</v>
       </c>
       <c r="AD111" s="55" t="s">
-        <v>615</v>
+        <v>612</v>
       </c>
       <c r="AE111" s="56" t="s">
         <v>606</v>
       </c>
       <c r="AF111" s="55" t="s">
-        <v>616</v>
+        <v>612</v>
       </c>
       <c r="AG111" s="56" t="s">
         <v>609</v>
@@ -19707,25 +19876,25 @@
         <v>596</v>
       </c>
       <c r="Z112" s="55" t="s">
-        <v>613</v>
+        <v>612</v>
       </c>
       <c r="AA112" s="56" t="s">
         <v>600</v>
       </c>
       <c r="AB112" s="55" t="s">
-        <v>614</v>
+        <v>612</v>
       </c>
       <c r="AC112" s="56" t="s">
         <v>603</v>
       </c>
       <c r="AD112" s="55" t="s">
-        <v>615</v>
+        <v>612</v>
       </c>
       <c r="AE112" s="56" t="s">
         <v>606</v>
       </c>
       <c r="AF112" s="55" t="s">
-        <v>616</v>
+        <v>612</v>
       </c>
       <c r="AG112" s="56" t="s">
         <v>609</v>
@@ -19808,25 +19977,25 @@
         <v>596</v>
       </c>
       <c r="Z113" s="55" t="s">
-        <v>613</v>
+        <v>612</v>
       </c>
       <c r="AA113" s="56" t="s">
         <v>600</v>
       </c>
       <c r="AB113" s="55" t="s">
-        <v>614</v>
+        <v>612</v>
       </c>
       <c r="AC113" s="56" t="s">
         <v>603</v>
       </c>
       <c r="AD113" s="55" t="s">
-        <v>615</v>
+        <v>612</v>
       </c>
       <c r="AE113" s="56" t="s">
         <v>606</v>
       </c>
       <c r="AF113" s="55" t="s">
-        <v>616</v>
+        <v>612</v>
       </c>
       <c r="AG113" s="56" t="s">
         <v>609</v>
@@ -19909,25 +20078,25 @@
         <v>596</v>
       </c>
       <c r="Z114" s="55" t="s">
-        <v>613</v>
+        <v>612</v>
       </c>
       <c r="AA114" s="56" t="s">
         <v>600</v>
       </c>
       <c r="AB114" s="55" t="s">
-        <v>614</v>
+        <v>612</v>
       </c>
       <c r="AC114" s="56" t="s">
         <v>603</v>
       </c>
       <c r="AD114" s="55" t="s">
-        <v>615</v>
+        <v>612</v>
       </c>
       <c r="AE114" s="56" t="s">
         <v>606</v>
       </c>
       <c r="AF114" s="55" t="s">
-        <v>616</v>
+        <v>612</v>
       </c>
       <c r="AG114" s="56" t="s">
         <v>609</v>
@@ -20010,25 +20179,25 @@
         <v>596</v>
       </c>
       <c r="Z115" s="55" t="s">
-        <v>613</v>
+        <v>612</v>
       </c>
       <c r="AA115" s="56" t="s">
         <v>600</v>
       </c>
       <c r="AB115" s="55" t="s">
-        <v>614</v>
+        <v>612</v>
       </c>
       <c r="AC115" s="56" t="s">
         <v>603</v>
       </c>
       <c r="AD115" s="55" t="s">
-        <v>615</v>
+        <v>612</v>
       </c>
       <c r="AE115" s="56" t="s">
         <v>606</v>
       </c>
       <c r="AF115" s="55" t="s">
-        <v>616</v>
+        <v>612</v>
       </c>
       <c r="AG115" s="56" t="s">
         <v>609</v>
@@ -20111,25 +20280,25 @@
         <v>596</v>
       </c>
       <c r="Z116" s="55" t="s">
-        <v>613</v>
+        <v>612</v>
       </c>
       <c r="AA116" s="56" t="s">
         <v>600</v>
       </c>
       <c r="AB116" s="55" t="s">
-        <v>614</v>
+        <v>612</v>
       </c>
       <c r="AC116" s="56" t="s">
         <v>603</v>
       </c>
       <c r="AD116" s="55" t="s">
-        <v>615</v>
+        <v>612</v>
       </c>
       <c r="AE116" s="56" t="s">
         <v>606</v>
       </c>
       <c r="AF116" s="55" t="s">
-        <v>616</v>
+        <v>612</v>
       </c>
       <c r="AG116" s="56" t="s">
         <v>609</v>
@@ -20212,25 +20381,25 @@
         <v>596</v>
       </c>
       <c r="Z117" s="55" t="s">
-        <v>613</v>
+        <v>612</v>
       </c>
       <c r="AA117" s="56" t="s">
         <v>600</v>
       </c>
       <c r="AB117" s="55" t="s">
-        <v>614</v>
+        <v>612</v>
       </c>
       <c r="AC117" s="56" t="s">
         <v>603</v>
       </c>
       <c r="AD117" s="55" t="s">
-        <v>615</v>
+        <v>612</v>
       </c>
       <c r="AE117" s="56" t="s">
         <v>606</v>
       </c>
       <c r="AF117" s="55" t="s">
-        <v>616</v>
+        <v>612</v>
       </c>
       <c r="AG117" s="56" t="s">
         <v>609</v>
@@ -20313,25 +20482,25 @@
         <v>596</v>
       </c>
       <c r="Z118" s="55" t="s">
-        <v>613</v>
+        <v>612</v>
       </c>
       <c r="AA118" s="56" t="s">
         <v>600</v>
       </c>
       <c r="AB118" s="55" t="s">
-        <v>614</v>
+        <v>612</v>
       </c>
       <c r="AC118" s="56" t="s">
         <v>603</v>
       </c>
       <c r="AD118" s="55" t="s">
-        <v>615</v>
+        <v>612</v>
       </c>
       <c r="AE118" s="56" t="s">
         <v>606</v>
       </c>
       <c r="AF118" s="55" t="s">
-        <v>616</v>
+        <v>612</v>
       </c>
       <c r="AG118" s="56" t="s">
         <v>609</v>
@@ -20414,25 +20583,25 @@
         <v>596</v>
       </c>
       <c r="Z119" s="55" t="s">
-        <v>613</v>
+        <v>612</v>
       </c>
       <c r="AA119" s="56" t="s">
         <v>600</v>
       </c>
       <c r="AB119" s="55" t="s">
-        <v>614</v>
+        <v>612</v>
       </c>
       <c r="AC119" s="56" t="s">
         <v>603</v>
       </c>
       <c r="AD119" s="55" t="s">
-        <v>615</v>
+        <v>612</v>
       </c>
       <c r="AE119" s="56" t="s">
         <v>606</v>
       </c>
       <c r="AF119" s="55" t="s">
-        <v>616</v>
+        <v>612</v>
       </c>
       <c r="AG119" s="56" t="s">
         <v>609</v>
@@ -20515,25 +20684,25 @@
         <v>596</v>
       </c>
       <c r="Z120" s="55" t="s">
-        <v>613</v>
+        <v>612</v>
       </c>
       <c r="AA120" s="56" t="s">
         <v>600</v>
       </c>
       <c r="AB120" s="55" t="s">
-        <v>614</v>
+        <v>612</v>
       </c>
       <c r="AC120" s="56" t="s">
         <v>603</v>
       </c>
       <c r="AD120" s="55" t="s">
-        <v>615</v>
+        <v>612</v>
       </c>
       <c r="AE120" s="56" t="s">
         <v>606</v>
       </c>
       <c r="AF120" s="55" t="s">
-        <v>616</v>
+        <v>612</v>
       </c>
       <c r="AG120" s="56" t="s">
         <v>609</v>
@@ -20616,25 +20785,25 @@
         <v>596</v>
       </c>
       <c r="Z121" s="55" t="s">
-        <v>613</v>
+        <v>612</v>
       </c>
       <c r="AA121" s="56" t="s">
         <v>600</v>
       </c>
       <c r="AB121" s="55" t="s">
-        <v>614</v>
+        <v>612</v>
       </c>
       <c r="AC121" s="56" t="s">
         <v>603</v>
       </c>
       <c r="AD121" s="55" t="s">
-        <v>615</v>
+        <v>612</v>
       </c>
       <c r="AE121" s="56" t="s">
         <v>606</v>
       </c>
       <c r="AF121" s="55" t="s">
-        <v>616</v>
+        <v>612</v>
       </c>
       <c r="AG121" s="56" t="s">
         <v>609</v>
@@ -20717,25 +20886,25 @@
         <v>596</v>
       </c>
       <c r="Z122" s="55" t="s">
-        <v>613</v>
+        <v>612</v>
       </c>
       <c r="AA122" s="56" t="s">
         <v>600</v>
       </c>
       <c r="AB122" s="55" t="s">
-        <v>614</v>
+        <v>612</v>
       </c>
       <c r="AC122" s="56" t="s">
         <v>603</v>
       </c>
       <c r="AD122" s="55" t="s">
-        <v>615</v>
+        <v>612</v>
       </c>
       <c r="AE122" s="56" t="s">
         <v>606</v>
       </c>
       <c r="AF122" s="55" t="s">
-        <v>616</v>
+        <v>612</v>
       </c>
       <c r="AG122" s="56" t="s">
         <v>609</v>
@@ -20818,25 +20987,25 @@
         <v>596</v>
       </c>
       <c r="Z123" s="55" t="s">
-        <v>613</v>
+        <v>612</v>
       </c>
       <c r="AA123" s="56" t="s">
         <v>600</v>
       </c>
       <c r="AB123" s="55" t="s">
-        <v>614</v>
+        <v>612</v>
       </c>
       <c r="AC123" s="56" t="s">
         <v>603</v>
       </c>
       <c r="AD123" s="55" t="s">
-        <v>615</v>
+        <v>612</v>
       </c>
       <c r="AE123" s="56" t="s">
         <v>606</v>
       </c>
       <c r="AF123" s="55" t="s">
-        <v>616</v>
+        <v>612</v>
       </c>
       <c r="AG123" s="56" t="s">
         <v>609</v>
@@ -20919,25 +21088,25 @@
         <v>596</v>
       </c>
       <c r="Z124" s="55" t="s">
-        <v>613</v>
+        <v>612</v>
       </c>
       <c r="AA124" s="56" t="s">
         <v>600</v>
       </c>
       <c r="AB124" s="55" t="s">
-        <v>614</v>
+        <v>612</v>
       </c>
       <c r="AC124" s="56" t="s">
         <v>603</v>
       </c>
       <c r="AD124" s="55" t="s">
-        <v>615</v>
+        <v>612</v>
       </c>
       <c r="AE124" s="56" t="s">
         <v>606</v>
       </c>
       <c r="AF124" s="55" t="s">
-        <v>616</v>
+        <v>612</v>
       </c>
       <c r="AG124" s="56" t="s">
         <v>609</v>
@@ -21020,25 +21189,25 @@
         <v>596</v>
       </c>
       <c r="Z125" s="55" t="s">
-        <v>613</v>
+        <v>612</v>
       </c>
       <c r="AA125" s="56" t="s">
         <v>600</v>
       </c>
       <c r="AB125" s="55" t="s">
-        <v>614</v>
+        <v>612</v>
       </c>
       <c r="AC125" s="56" t="s">
         <v>603</v>
       </c>
       <c r="AD125" s="55" t="s">
-        <v>615</v>
+        <v>612</v>
       </c>
       <c r="AE125" s="56" t="s">
         <v>606</v>
       </c>
       <c r="AF125" s="55" t="s">
-        <v>616</v>
+        <v>612</v>
       </c>
       <c r="AG125" s="56" t="s">
         <v>609</v>
@@ -21121,25 +21290,25 @@
         <v>596</v>
       </c>
       <c r="Z126" s="55" t="s">
-        <v>613</v>
+        <v>612</v>
       </c>
       <c r="AA126" s="56" t="s">
         <v>600</v>
       </c>
       <c r="AB126" s="55" t="s">
-        <v>614</v>
+        <v>612</v>
       </c>
       <c r="AC126" s="56" t="s">
         <v>603</v>
       </c>
       <c r="AD126" s="55" t="s">
-        <v>615</v>
+        <v>612</v>
       </c>
       <c r="AE126" s="56" t="s">
         <v>606</v>
       </c>
       <c r="AF126" s="55" t="s">
-        <v>616</v>
+        <v>612</v>
       </c>
       <c r="AG126" s="56" t="s">
         <v>609</v>
@@ -21222,25 +21391,25 @@
         <v>596</v>
       </c>
       <c r="Z127" s="55" t="s">
-        <v>613</v>
+        <v>612</v>
       </c>
       <c r="AA127" s="56" t="s">
         <v>600</v>
       </c>
       <c r="AB127" s="55" t="s">
-        <v>614</v>
+        <v>612</v>
       </c>
       <c r="AC127" s="56" t="s">
         <v>603</v>
       </c>
       <c r="AD127" s="55" t="s">
-        <v>615</v>
+        <v>612</v>
       </c>
       <c r="AE127" s="56" t="s">
         <v>606</v>
       </c>
       <c r="AF127" s="55" t="s">
-        <v>616</v>
+        <v>612</v>
       </c>
       <c r="AG127" s="56" t="s">
         <v>609</v>
@@ -21323,25 +21492,25 @@
         <v>596</v>
       </c>
       <c r="Z128" s="55" t="s">
-        <v>613</v>
+        <v>612</v>
       </c>
       <c r="AA128" s="56" t="s">
         <v>600</v>
       </c>
       <c r="AB128" s="55" t="s">
-        <v>614</v>
+        <v>612</v>
       </c>
       <c r="AC128" s="56" t="s">
         <v>603</v>
       </c>
       <c r="AD128" s="55" t="s">
-        <v>615</v>
+        <v>612</v>
       </c>
       <c r="AE128" s="56" t="s">
         <v>606</v>
       </c>
       <c r="AF128" s="55" t="s">
-        <v>616</v>
+        <v>612</v>
       </c>
       <c r="AG128" s="56" t="s">
         <v>609</v>
@@ -21424,25 +21593,25 @@
         <v>596</v>
       </c>
       <c r="Z129" s="55" t="s">
-        <v>613</v>
+        <v>612</v>
       </c>
       <c r="AA129" s="56" t="s">
         <v>600</v>
       </c>
       <c r="AB129" s="55" t="s">
-        <v>614</v>
+        <v>612</v>
       </c>
       <c r="AC129" s="56" t="s">
         <v>603</v>
       </c>
       <c r="AD129" s="55" t="s">
-        <v>615</v>
+        <v>612</v>
       </c>
       <c r="AE129" s="56" t="s">
         <v>606</v>
       </c>
       <c r="AF129" s="55" t="s">
-        <v>616</v>
+        <v>612</v>
       </c>
       <c r="AG129" s="56" t="s">
         <v>609</v>
@@ -21525,25 +21694,25 @@
         <v>596</v>
       </c>
       <c r="Z130" s="55" t="s">
-        <v>613</v>
+        <v>612</v>
       </c>
       <c r="AA130" s="56" t="s">
         <v>600</v>
       </c>
       <c r="AB130" s="55" t="s">
-        <v>614</v>
+        <v>612</v>
       </c>
       <c r="AC130" s="56" t="s">
         <v>603</v>
       </c>
       <c r="AD130" s="55" t="s">
-        <v>615</v>
+        <v>612</v>
       </c>
       <c r="AE130" s="56" t="s">
         <v>606</v>
       </c>
       <c r="AF130" s="55" t="s">
-        <v>616</v>
+        <v>612</v>
       </c>
       <c r="AG130" s="56" t="s">
         <v>609</v>
@@ -21626,25 +21795,25 @@
         <v>596</v>
       </c>
       <c r="Z131" s="55" t="s">
-        <v>613</v>
+        <v>612</v>
       </c>
       <c r="AA131" s="56" t="s">
         <v>600</v>
       </c>
       <c r="AB131" s="55" t="s">
-        <v>614</v>
+        <v>612</v>
       </c>
       <c r="AC131" s="56" t="s">
         <v>603</v>
       </c>
       <c r="AD131" s="55" t="s">
-        <v>615</v>
+        <v>612</v>
       </c>
       <c r="AE131" s="56" t="s">
         <v>606</v>
       </c>
       <c r="AF131" s="55" t="s">
-        <v>616</v>
+        <v>612</v>
       </c>
       <c r="AG131" s="56" t="s">
         <v>609</v>
@@ -21727,25 +21896,25 @@
         <v>596</v>
       </c>
       <c r="Z132" s="55" t="s">
-        <v>613</v>
+        <v>612</v>
       </c>
       <c r="AA132" s="56" t="s">
         <v>600</v>
       </c>
       <c r="AB132" s="55" t="s">
-        <v>614</v>
+        <v>612</v>
       </c>
       <c r="AC132" s="56" t="s">
         <v>603</v>
       </c>
       <c r="AD132" s="55" t="s">
-        <v>615</v>
+        <v>612</v>
       </c>
       <c r="AE132" s="56" t="s">
         <v>606</v>
       </c>
       <c r="AF132" s="55" t="s">
-        <v>616</v>
+        <v>612</v>
       </c>
       <c r="AG132" s="56" t="s">
         <v>609</v>
@@ -21828,25 +21997,25 @@
         <v>596</v>
       </c>
       <c r="Z133" s="55" t="s">
-        <v>613</v>
+        <v>612</v>
       </c>
       <c r="AA133" s="56" t="s">
         <v>600</v>
       </c>
       <c r="AB133" s="55" t="s">
-        <v>614</v>
+        <v>612</v>
       </c>
       <c r="AC133" s="56" t="s">
         <v>603</v>
       </c>
       <c r="AD133" s="55" t="s">
-        <v>615</v>
+        <v>612</v>
       </c>
       <c r="AE133" s="56" t="s">
         <v>606</v>
       </c>
       <c r="AF133" s="55" t="s">
-        <v>616</v>
+        <v>612</v>
       </c>
       <c r="AG133" s="56" t="s">
         <v>609</v>
@@ -21929,25 +22098,25 @@
         <v>596</v>
       </c>
       <c r="Z134" s="55" t="s">
-        <v>613</v>
+        <v>612</v>
       </c>
       <c r="AA134" s="56" t="s">
         <v>600</v>
       </c>
       <c r="AB134" s="55" t="s">
-        <v>614</v>
+        <v>612</v>
       </c>
       <c r="AC134" s="56" t="s">
         <v>603</v>
       </c>
       <c r="AD134" s="55" t="s">
-        <v>615</v>
+        <v>612</v>
       </c>
       <c r="AE134" s="56" t="s">
         <v>606</v>
       </c>
       <c r="AF134" s="55" t="s">
-        <v>616</v>
+        <v>612</v>
       </c>
       <c r="AG134" s="56" t="s">
         <v>609</v>
@@ -22030,25 +22199,25 @@
         <v>596</v>
       </c>
       <c r="Z135" s="55" t="s">
-        <v>613</v>
+        <v>612</v>
       </c>
       <c r="AA135" s="56" t="s">
         <v>600</v>
       </c>
       <c r="AB135" s="55" t="s">
-        <v>614</v>
+        <v>612</v>
       </c>
       <c r="AC135" s="56" t="s">
         <v>603</v>
       </c>
       <c r="AD135" s="55" t="s">
-        <v>615</v>
+        <v>612</v>
       </c>
       <c r="AE135" s="56" t="s">
         <v>606</v>
       </c>
       <c r="AF135" s="55" t="s">
-        <v>616</v>
+        <v>612</v>
       </c>
       <c r="AG135" s="56" t="s">
         <v>609</v>
@@ -22131,25 +22300,25 @@
         <v>596</v>
       </c>
       <c r="Z136" s="55" t="s">
-        <v>613</v>
+        <v>612</v>
       </c>
       <c r="AA136" s="56" t="s">
         <v>600</v>
       </c>
       <c r="AB136" s="55" t="s">
-        <v>614</v>
+        <v>612</v>
       </c>
       <c r="AC136" s="56" t="s">
         <v>603</v>
       </c>
       <c r="AD136" s="55" t="s">
-        <v>615</v>
+        <v>612</v>
       </c>
       <c r="AE136" s="56" t="s">
         <v>606</v>
       </c>
       <c r="AF136" s="55" t="s">
-        <v>616</v>
+        <v>612</v>
       </c>
       <c r="AG136" s="56" t="s">
         <v>609</v>
@@ -22232,25 +22401,25 @@
         <v>596</v>
       </c>
       <c r="Z137" s="55" t="s">
-        <v>613</v>
+        <v>612</v>
       </c>
       <c r="AA137" s="56" t="s">
         <v>600</v>
       </c>
       <c r="AB137" s="55" t="s">
-        <v>614</v>
+        <v>612</v>
       </c>
       <c r="AC137" s="56" t="s">
         <v>603</v>
       </c>
       <c r="AD137" s="55" t="s">
-        <v>615</v>
+        <v>612</v>
       </c>
       <c r="AE137" s="56" t="s">
         <v>606</v>
       </c>
       <c r="AF137" s="55" t="s">
-        <v>616</v>
+        <v>612</v>
       </c>
       <c r="AG137" s="56" t="s">
         <v>609</v>
@@ -22333,25 +22502,25 @@
         <v>596</v>
       </c>
       <c r="Z138" s="55" t="s">
-        <v>613</v>
+        <v>612</v>
       </c>
       <c r="AA138" s="56" t="s">
         <v>600</v>
       </c>
       <c r="AB138" s="55" t="s">
-        <v>614</v>
+        <v>612</v>
       </c>
       <c r="AC138" s="56" t="s">
         <v>603</v>
       </c>
       <c r="AD138" s="55" t="s">
-        <v>615</v>
+        <v>612</v>
       </c>
       <c r="AE138" s="56" t="s">
         <v>606</v>
       </c>
       <c r="AF138" s="55" t="s">
-        <v>616</v>
+        <v>612</v>
       </c>
       <c r="AG138" s="56" t="s">
         <v>609</v>
@@ -22434,25 +22603,25 @@
         <v>596</v>
       </c>
       <c r="Z139" s="55" t="s">
-        <v>613</v>
+        <v>612</v>
       </c>
       <c r="AA139" s="56" t="s">
         <v>600</v>
       </c>
       <c r="AB139" s="55" t="s">
-        <v>614</v>
+        <v>612</v>
       </c>
       <c r="AC139" s="56" t="s">
         <v>603</v>
       </c>
       <c r="AD139" s="55" t="s">
-        <v>615</v>
+        <v>612</v>
       </c>
       <c r="AE139" s="56" t="s">
         <v>606</v>
       </c>
       <c r="AF139" s="55" t="s">
-        <v>616</v>
+        <v>612</v>
       </c>
       <c r="AG139" s="56" t="s">
         <v>609</v>
@@ -22535,25 +22704,25 @@
         <v>596</v>
       </c>
       <c r="Z140" s="55" t="s">
-        <v>613</v>
+        <v>612</v>
       </c>
       <c r="AA140" s="56" t="s">
         <v>600</v>
       </c>
       <c r="AB140" s="55" t="s">
-        <v>614</v>
+        <v>612</v>
       </c>
       <c r="AC140" s="56" t="s">
         <v>603</v>
       </c>
       <c r="AD140" s="55" t="s">
-        <v>615</v>
+        <v>612</v>
       </c>
       <c r="AE140" s="56" t="s">
         <v>606</v>
       </c>
       <c r="AF140" s="55" t="s">
-        <v>616</v>
+        <v>612</v>
       </c>
       <c r="AG140" s="56" t="s">
         <v>609</v>
@@ -22636,25 +22805,25 @@
         <v>596</v>
       </c>
       <c r="Z141" s="55" t="s">
-        <v>613</v>
+        <v>612</v>
       </c>
       <c r="AA141" s="56" t="s">
         <v>600</v>
       </c>
       <c r="AB141" s="55" t="s">
-        <v>614</v>
+        <v>612</v>
       </c>
       <c r="AC141" s="56" t="s">
         <v>603</v>
       </c>
       <c r="AD141" s="55" t="s">
-        <v>615</v>
+        <v>612</v>
       </c>
       <c r="AE141" s="56" t="s">
         <v>606</v>
       </c>
       <c r="AF141" s="55" t="s">
-        <v>616</v>
+        <v>612</v>
       </c>
       <c r="AG141" s="56" t="s">
         <v>609</v>
@@ -22737,25 +22906,25 @@
         <v>596</v>
       </c>
       <c r="Z142" s="55" t="s">
-        <v>613</v>
+        <v>612</v>
       </c>
       <c r="AA142" s="56" t="s">
         <v>600</v>
       </c>
       <c r="AB142" s="55" t="s">
-        <v>614</v>
+        <v>612</v>
       </c>
       <c r="AC142" s="56" t="s">
         <v>603</v>
       </c>
       <c r="AD142" s="55" t="s">
-        <v>615</v>
+        <v>612</v>
       </c>
       <c r="AE142" s="56" t="s">
         <v>606</v>
       </c>
       <c r="AF142" s="55" t="s">
-        <v>616</v>
+        <v>612</v>
       </c>
       <c r="AG142" s="56" t="s">
         <v>609</v>
@@ -22838,25 +23007,25 @@
         <v>596</v>
       </c>
       <c r="Z143" s="55" t="s">
-        <v>613</v>
+        <v>612</v>
       </c>
       <c r="AA143" s="56" t="s">
         <v>600</v>
       </c>
       <c r="AB143" s="55" t="s">
-        <v>614</v>
+        <v>612</v>
       </c>
       <c r="AC143" s="56" t="s">
         <v>603</v>
       </c>
       <c r="AD143" s="55" t="s">
-        <v>615</v>
+        <v>612</v>
       </c>
       <c r="AE143" s="56" t="s">
         <v>606</v>
       </c>
       <c r="AF143" s="55" t="s">
-        <v>616</v>
+        <v>612</v>
       </c>
       <c r="AG143" s="56" t="s">
         <v>609</v>
@@ -22939,25 +23108,25 @@
         <v>596</v>
       </c>
       <c r="Z144" s="55" t="s">
-        <v>613</v>
+        <v>612</v>
       </c>
       <c r="AA144" s="56" t="s">
         <v>600</v>
       </c>
       <c r="AB144" s="55" t="s">
-        <v>614</v>
+        <v>612</v>
       </c>
       <c r="AC144" s="56" t="s">
         <v>603</v>
       </c>
       <c r="AD144" s="55" t="s">
-        <v>615</v>
+        <v>612</v>
       </c>
       <c r="AE144" s="56" t="s">
         <v>606</v>
       </c>
       <c r="AF144" s="55" t="s">
-        <v>616</v>
+        <v>612</v>
       </c>
       <c r="AG144" s="56" t="s">
         <v>609</v>
@@ -23040,25 +23209,25 @@
         <v>596</v>
       </c>
       <c r="Z145" s="55" t="s">
-        <v>613</v>
+        <v>612</v>
       </c>
       <c r="AA145" s="56" t="s">
         <v>600</v>
       </c>
       <c r="AB145" s="55" t="s">
-        <v>614</v>
+        <v>612</v>
       </c>
       <c r="AC145" s="56" t="s">
         <v>603</v>
       </c>
       <c r="AD145" s="55" t="s">
-        <v>615</v>
+        <v>612</v>
       </c>
       <c r="AE145" s="56" t="s">
         <v>606</v>
       </c>
       <c r="AF145" s="55" t="s">
-        <v>616</v>
+        <v>612</v>
       </c>
       <c r="AG145" s="56" t="s">
         <v>609</v>
@@ -23141,25 +23310,25 @@
         <v>596</v>
       </c>
       <c r="Z146" s="55" t="s">
-        <v>613</v>
+        <v>612</v>
       </c>
       <c r="AA146" s="56" t="s">
         <v>600</v>
       </c>
       <c r="AB146" s="55" t="s">
-        <v>614</v>
+        <v>612</v>
       </c>
       <c r="AC146" s="56" t="s">
         <v>603</v>
       </c>
       <c r="AD146" s="55" t="s">
-        <v>615</v>
+        <v>612</v>
       </c>
       <c r="AE146" s="56" t="s">
         <v>606</v>
       </c>
       <c r="AF146" s="55" t="s">
-        <v>616</v>
+        <v>612</v>
       </c>
       <c r="AG146" s="56" t="s">
         <v>609</v>
@@ -23242,25 +23411,25 @@
         <v>596</v>
       </c>
       <c r="Z147" s="55" t="s">
-        <v>613</v>
+        <v>612</v>
       </c>
       <c r="AA147" s="56" t="s">
         <v>600</v>
       </c>
       <c r="AB147" s="55" t="s">
-        <v>614</v>
+        <v>612</v>
       </c>
       <c r="AC147" s="56" t="s">
         <v>603</v>
       </c>
       <c r="AD147" s="55" t="s">
-        <v>615</v>
+        <v>612</v>
       </c>
       <c r="AE147" s="56" t="s">
         <v>606</v>
       </c>
       <c r="AF147" s="55" t="s">
-        <v>616</v>
+        <v>612</v>
       </c>
       <c r="AG147" s="56" t="s">
         <v>609</v>
@@ -23343,25 +23512,25 @@
         <v>596</v>
       </c>
       <c r="Z148" s="55" t="s">
-        <v>613</v>
+        <v>612</v>
       </c>
       <c r="AA148" s="56" t="s">
         <v>600</v>
       </c>
       <c r="AB148" s="55" t="s">
-        <v>614</v>
+        <v>612</v>
       </c>
       <c r="AC148" s="56" t="s">
         <v>603</v>
       </c>
       <c r="AD148" s="55" t="s">
-        <v>615</v>
+        <v>612</v>
       </c>
       <c r="AE148" s="56" t="s">
         <v>606</v>
       </c>
       <c r="AF148" s="55" t="s">
-        <v>616</v>
+        <v>612</v>
       </c>
       <c r="AG148" s="56" t="s">
         <v>609</v>
@@ -23444,25 +23613,25 @@
         <v>596</v>
       </c>
       <c r="Z149" s="55" t="s">
-        <v>613</v>
+        <v>612</v>
       </c>
       <c r="AA149" s="56" t="s">
         <v>600</v>
       </c>
       <c r="AB149" s="55" t="s">
-        <v>614</v>
+        <v>612</v>
       </c>
       <c r="AC149" s="56" t="s">
         <v>603</v>
       </c>
       <c r="AD149" s="55" t="s">
-        <v>615</v>
+        <v>612</v>
       </c>
       <c r="AE149" s="56" t="s">
         <v>606</v>
       </c>
       <c r="AF149" s="55" t="s">
-        <v>616</v>
+        <v>612</v>
       </c>
       <c r="AG149" s="56" t="s">
         <v>609</v>
@@ -23545,25 +23714,25 @@
         <v>596</v>
       </c>
       <c r="Z150" s="55" t="s">
-        <v>613</v>
+        <v>612</v>
       </c>
       <c r="AA150" s="56" t="s">
         <v>600</v>
       </c>
       <c r="AB150" s="55" t="s">
-        <v>614</v>
+        <v>612</v>
       </c>
       <c r="AC150" s="56" t="s">
         <v>603</v>
       </c>
       <c r="AD150" s="55" t="s">
-        <v>615</v>
+        <v>612</v>
       </c>
       <c r="AE150" s="56" t="s">
         <v>606</v>
       </c>
       <c r="AF150" s="55" t="s">
-        <v>616</v>
+        <v>612</v>
       </c>
       <c r="AG150" s="56" t="s">
         <v>609</v>
@@ -23646,25 +23815,25 @@
         <v>596</v>
       </c>
       <c r="Z151" s="55" t="s">
-        <v>613</v>
+        <v>612</v>
       </c>
       <c r="AA151" s="56" t="s">
         <v>600</v>
       </c>
       <c r="AB151" s="55" t="s">
-        <v>614</v>
+        <v>612</v>
       </c>
       <c r="AC151" s="56" t="s">
         <v>603</v>
       </c>
       <c r="AD151" s="55" t="s">
-        <v>615</v>
+        <v>612</v>
       </c>
       <c r="AE151" s="56" t="s">
         <v>606</v>
       </c>
       <c r="AF151" s="55" t="s">
-        <v>616</v>
+        <v>612</v>
       </c>
       <c r="AG151" s="56" t="s">
         <v>609</v>
@@ -23747,25 +23916,25 @@
         <v>596</v>
       </c>
       <c r="Z152" s="55" t="s">
-        <v>613</v>
+        <v>612</v>
       </c>
       <c r="AA152" s="56" t="s">
         <v>600</v>
       </c>
       <c r="AB152" s="55" t="s">
-        <v>614</v>
+        <v>612</v>
       </c>
       <c r="AC152" s="56" t="s">
         <v>603</v>
       </c>
       <c r="AD152" s="55" t="s">
-        <v>615</v>
+        <v>612</v>
       </c>
       <c r="AE152" s="56" t="s">
         <v>606</v>
       </c>
       <c r="AF152" s="55" t="s">
-        <v>616</v>
+        <v>612</v>
       </c>
       <c r="AG152" s="56" t="s">
         <v>609</v>
@@ -23848,25 +24017,25 @@
         <v>596</v>
       </c>
       <c r="Z153" s="55" t="s">
-        <v>613</v>
+        <v>612</v>
       </c>
       <c r="AA153" s="56" t="s">
         <v>600</v>
       </c>
       <c r="AB153" s="55" t="s">
-        <v>614</v>
+        <v>612</v>
       </c>
       <c r="AC153" s="56" t="s">
         <v>603</v>
       </c>
       <c r="AD153" s="55" t="s">
-        <v>615</v>
+        <v>612</v>
       </c>
       <c r="AE153" s="56" t="s">
         <v>606</v>
       </c>
       <c r="AF153" s="55" t="s">
-        <v>616</v>
+        <v>612</v>
       </c>
       <c r="AG153" s="56" t="s">
         <v>609</v>
@@ -23949,25 +24118,25 @@
         <v>596</v>
       </c>
       <c r="Z154" s="55" t="s">
-        <v>613</v>
+        <v>612</v>
       </c>
       <c r="AA154" s="56" t="s">
         <v>600</v>
       </c>
       <c r="AB154" s="55" t="s">
-        <v>614</v>
+        <v>612</v>
       </c>
       <c r="AC154" s="56" t="s">
         <v>603</v>
       </c>
       <c r="AD154" s="55" t="s">
-        <v>615</v>
+        <v>612</v>
       </c>
       <c r="AE154" s="56" t="s">
         <v>606</v>
       </c>
       <c r="AF154" s="55" t="s">
-        <v>616</v>
+        <v>612</v>
       </c>
       <c r="AG154" s="56" t="s">
         <v>609</v>
@@ -24050,25 +24219,25 @@
         <v>596</v>
       </c>
       <c r="Z155" s="55" t="s">
-        <v>613</v>
+        <v>612</v>
       </c>
       <c r="AA155" s="56" t="s">
         <v>600</v>
       </c>
       <c r="AB155" s="55" t="s">
-        <v>614</v>
+        <v>612</v>
       </c>
       <c r="AC155" s="56" t="s">
         <v>603</v>
       </c>
       <c r="AD155" s="55" t="s">
-        <v>615</v>
+        <v>612</v>
       </c>
       <c r="AE155" s="56" t="s">
         <v>606</v>
       </c>
       <c r="AF155" s="55" t="s">
-        <v>616</v>
+        <v>612</v>
       </c>
       <c r="AG155" s="56" t="s">
         <v>609</v>
@@ -24151,25 +24320,25 @@
         <v>596</v>
       </c>
       <c r="Z156" s="55" t="s">
-        <v>613</v>
+        <v>612</v>
       </c>
       <c r="AA156" s="56" t="s">
         <v>600</v>
       </c>
       <c r="AB156" s="55" t="s">
-        <v>614</v>
+        <v>612</v>
       </c>
       <c r="AC156" s="56" t="s">
         <v>603</v>
       </c>
       <c r="AD156" s="55" t="s">
-        <v>615</v>
+        <v>612</v>
       </c>
       <c r="AE156" s="56" t="s">
         <v>606</v>
       </c>
       <c r="AF156" s="55" t="s">
-        <v>616</v>
+        <v>612</v>
       </c>
       <c r="AG156" s="56" t="s">
         <v>609</v>
@@ -24252,25 +24421,25 @@
         <v>596</v>
       </c>
       <c r="Z157" s="55" t="s">
-        <v>613</v>
+        <v>612</v>
       </c>
       <c r="AA157" s="56" t="s">
         <v>600</v>
       </c>
       <c r="AB157" s="55" t="s">
-        <v>614</v>
+        <v>612</v>
       </c>
       <c r="AC157" s="56" t="s">
         <v>603</v>
       </c>
       <c r="AD157" s="55" t="s">
-        <v>615</v>
+        <v>612</v>
       </c>
       <c r="AE157" s="56" t="s">
         <v>606</v>
       </c>
       <c r="AF157" s="55" t="s">
-        <v>616</v>
+        <v>612</v>
       </c>
       <c r="AG157" s="56" t="s">
         <v>609</v>
@@ -24322,11 +24491,12 @@
       <c r="O158" s="72" t="s">
         <v>599</v>
       </c>
-      <c r="P158" s="45" t="s">
-        <v>181</v>
-      </c>
-      <c r="Q158" s="46" t="s">
-        <v>181</v>
+      <c r="P158" s="86" t="str">
+        <f t="shared" ref="P158:P162" si="0">IF(Q158="null", "null", "método.revit")</f>
+        <v>método.revit</v>
+      </c>
+      <c r="Q158" s="87" t="s">
+        <v>613</v>
       </c>
       <c r="R158" s="45" t="s">
         <v>181</v>
@@ -24353,25 +24523,25 @@
         <v>596</v>
       </c>
       <c r="Z158" s="55" t="s">
-        <v>613</v>
+        <v>612</v>
       </c>
       <c r="AA158" s="56" t="s">
         <v>600</v>
       </c>
       <c r="AB158" s="55" t="s">
-        <v>614</v>
+        <v>612</v>
       </c>
       <c r="AC158" s="56" t="s">
         <v>603</v>
       </c>
       <c r="AD158" s="55" t="s">
-        <v>615</v>
+        <v>612</v>
       </c>
       <c r="AE158" s="56" t="s">
         <v>606</v>
       </c>
       <c r="AF158" s="55" t="s">
-        <v>616</v>
+        <v>612</v>
       </c>
       <c r="AG158" s="56" t="s">
         <v>609</v>
@@ -24423,11 +24593,12 @@
       <c r="O159" s="72" t="s">
         <v>602</v>
       </c>
-      <c r="P159" s="45" t="s">
-        <v>181</v>
-      </c>
-      <c r="Q159" s="46" t="s">
-        <v>181</v>
+      <c r="P159" s="86" t="str">
+        <f t="shared" si="0"/>
+        <v>método.revit</v>
+      </c>
+      <c r="Q159" s="87" t="s">
+        <v>614</v>
       </c>
       <c r="R159" s="45" t="s">
         <v>181</v>
@@ -24454,25 +24625,25 @@
         <v>596</v>
       </c>
       <c r="Z159" s="55" t="s">
-        <v>613</v>
+        <v>612</v>
       </c>
       <c r="AA159" s="56" t="s">
         <v>600</v>
       </c>
       <c r="AB159" s="55" t="s">
-        <v>614</v>
+        <v>612</v>
       </c>
       <c r="AC159" s="56" t="s">
         <v>603</v>
       </c>
       <c r="AD159" s="55" t="s">
-        <v>615</v>
+        <v>612</v>
       </c>
       <c r="AE159" s="56" t="s">
         <v>606</v>
       </c>
       <c r="AF159" s="55" t="s">
-        <v>616</v>
+        <v>612</v>
       </c>
       <c r="AG159" s="56" t="s">
         <v>609</v>
@@ -24524,11 +24695,12 @@
       <c r="O160" s="72" t="s">
         <v>605</v>
       </c>
-      <c r="P160" s="45" t="s">
-        <v>181</v>
-      </c>
-      <c r="Q160" s="46" t="s">
-        <v>181</v>
+      <c r="P160" s="86" t="str">
+        <f t="shared" si="0"/>
+        <v>método.revit</v>
+      </c>
+      <c r="Q160" s="87" t="s">
+        <v>615</v>
       </c>
       <c r="R160" s="45" t="s">
         <v>181</v>
@@ -24555,25 +24727,25 @@
         <v>596</v>
       </c>
       <c r="Z160" s="55" t="s">
-        <v>613</v>
+        <v>612</v>
       </c>
       <c r="AA160" s="56" t="s">
         <v>600</v>
       </c>
       <c r="AB160" s="55" t="s">
-        <v>614</v>
+        <v>612</v>
       </c>
       <c r="AC160" s="56" t="s">
         <v>603</v>
       </c>
       <c r="AD160" s="55" t="s">
-        <v>615</v>
+        <v>612</v>
       </c>
       <c r="AE160" s="56" t="s">
         <v>606</v>
       </c>
       <c r="AF160" s="55" t="s">
-        <v>616</v>
+        <v>612</v>
       </c>
       <c r="AG160" s="56" t="s">
         <v>609</v>
@@ -24625,11 +24797,12 @@
       <c r="O161" s="72" t="s">
         <v>608</v>
       </c>
-      <c r="P161" s="45" t="s">
-        <v>181</v>
-      </c>
-      <c r="Q161" s="46" t="s">
-        <v>181</v>
+      <c r="P161" s="86" t="str">
+        <f t="shared" si="0"/>
+        <v>método.revit</v>
+      </c>
+      <c r="Q161" s="87" t="s">
+        <v>616</v>
       </c>
       <c r="R161" s="45" t="s">
         <v>181</v>
@@ -24656,25 +24829,25 @@
         <v>596</v>
       </c>
       <c r="Z161" s="55" t="s">
-        <v>613</v>
+        <v>612</v>
       </c>
       <c r="AA161" s="56" t="s">
         <v>600</v>
       </c>
       <c r="AB161" s="55" t="s">
-        <v>614</v>
+        <v>612</v>
       </c>
       <c r="AC161" s="56" t="s">
         <v>603</v>
       </c>
       <c r="AD161" s="55" t="s">
-        <v>615</v>
+        <v>612</v>
       </c>
       <c r="AE161" s="56" t="s">
         <v>606</v>
       </c>
       <c r="AF161" s="55" t="s">
-        <v>616</v>
+        <v>612</v>
       </c>
       <c r="AG161" s="56" t="s">
         <v>609</v>
@@ -24726,11 +24899,12 @@
       <c r="O162" s="77" t="s">
         <v>611</v>
       </c>
-      <c r="P162" s="78" t="s">
-        <v>181</v>
-      </c>
-      <c r="Q162" s="74" t="s">
-        <v>181</v>
+      <c r="P162" s="86" t="str">
+        <f t="shared" si="0"/>
+        <v>método.revit</v>
+      </c>
+      <c r="Q162" s="87" t="s">
+        <v>617</v>
       </c>
       <c r="R162" s="78" t="s">
         <v>181</v>
@@ -24757,25 +24931,25 @@
         <v>596</v>
       </c>
       <c r="Z162" s="55" t="s">
-        <v>613</v>
+        <v>612</v>
       </c>
       <c r="AA162" s="56" t="s">
         <v>600</v>
       </c>
       <c r="AB162" s="55" t="s">
-        <v>614</v>
+        <v>612</v>
       </c>
       <c r="AC162" s="56" t="s">
         <v>603</v>
       </c>
       <c r="AD162" s="55" t="s">
-        <v>615</v>
+        <v>612</v>
       </c>
       <c r="AE162" s="56" t="s">
         <v>606</v>
       </c>
       <c r="AF162" s="55" t="s">
-        <v>616</v>
+        <v>612</v>
       </c>
       <c r="AG162" s="56" t="s">
         <v>609</v>
@@ -24784,79 +24958,114 @@
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>
   <conditionalFormatting sqref="B1:B157 B163:B1048576">
-    <cfRule type="duplicateValues" dxfId="16" priority="16"/>
+    <cfRule type="duplicateValues" dxfId="23" priority="28"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B158:B162">
-    <cfRule type="duplicateValues" dxfId="15" priority="14"/>
-    <cfRule type="duplicateValues" dxfId="14" priority="15"/>
+    <cfRule type="duplicateValues" dxfId="22" priority="26"/>
+    <cfRule type="duplicateValues" dxfId="21" priority="27"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="P158:W162">
-    <cfRule type="cellIs" dxfId="13" priority="13" operator="equal">
+  <conditionalFormatting sqref="R158:W162">
+    <cfRule type="cellIs" dxfId="20" priority="25" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="T1:W157 T163:Y1048576">
-    <cfRule type="cellIs" dxfId="12" priority="17" operator="equal">
+  <conditionalFormatting sqref="T1:W157">
+    <cfRule type="cellIs" dxfId="19" priority="29" operator="equal">
+      <formula>"null"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="T163:Z1048576">
+    <cfRule type="cellIs" dxfId="18" priority="12" operator="equal">
+      <formula>"null"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="X1">
+    <cfRule type="cellIs" dxfId="17" priority="24" operator="equal">
+      <formula>"null"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="X2:Y162">
+    <cfRule type="cellIs" dxfId="16" priority="17" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="X1:AG1">
-    <cfRule type="cellIs" dxfId="11" priority="7" operator="equal">
-      <formula>"null"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="X1">
-    <cfRule type="cellIs" dxfId="10" priority="12" operator="equal">
-      <formula>"null"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="X2:Y162">
-    <cfRule type="cellIs" dxfId="9" priority="5" operator="equal">
+    <cfRule type="cellIs" dxfId="15" priority="19" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="Z1">
-    <cfRule type="cellIs" dxfId="8" priority="11" operator="equal">
+    <cfRule type="cellIs" dxfId="14" priority="11" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="Z2:AA3">
-    <cfRule type="cellIs" dxfId="7" priority="4" operator="equal">
+  <conditionalFormatting sqref="Z2:Z162">
+    <cfRule type="cellIs" dxfId="13" priority="10" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="Z4:AG162">
-    <cfRule type="cellIs" dxfId="6" priority="6" operator="equal">
+  <conditionalFormatting sqref="AA2:AA162">
+    <cfRule type="cellIs" dxfId="12" priority="16" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AB1">
-    <cfRule type="cellIs" dxfId="5" priority="10" operator="equal">
+    <cfRule type="cellIs" dxfId="11" priority="8" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="AB2:AC3">
-    <cfRule type="cellIs" dxfId="4" priority="3" operator="equal">
+  <conditionalFormatting sqref="AB2:AB162">
+    <cfRule type="cellIs" dxfId="10" priority="7" operator="equal">
+      <formula>"null"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="AB163:AB1048576">
+    <cfRule type="cellIs" dxfId="9" priority="9" operator="equal">
+      <formula>"null"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="AC2:AC162">
+    <cfRule type="cellIs" dxfId="8" priority="15" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AD1">
-    <cfRule type="cellIs" dxfId="3" priority="9" operator="equal">
+    <cfRule type="cellIs" dxfId="7" priority="5" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="AD2:AE3">
-    <cfRule type="cellIs" dxfId="2" priority="2" operator="equal">
+  <conditionalFormatting sqref="AD2:AD162">
+    <cfRule type="cellIs" dxfId="6" priority="4" operator="equal">
+      <formula>"null"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="AD163:AD1048576">
+    <cfRule type="cellIs" dxfId="5" priority="6" operator="equal">
+      <formula>"null"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="AE2:AE162">
+    <cfRule type="cellIs" dxfId="4" priority="14" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AF1">
-    <cfRule type="cellIs" dxfId="1" priority="8" operator="equal">
+    <cfRule type="cellIs" dxfId="3" priority="2" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="AF2:AG3">
-    <cfRule type="cellIs" dxfId="0" priority="1" operator="equal">
+  <conditionalFormatting sqref="AF2:AF162">
+    <cfRule type="cellIs" dxfId="2" priority="1" operator="equal">
+      <formula>"null"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="AF163:AF1048576">
+    <cfRule type="cellIs" dxfId="1" priority="3" operator="equal">
+      <formula>"null"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="AG2:AG162">
+    <cfRule type="cellIs" dxfId="0" priority="13" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>

--- a/Versão5/ABNT/Ontologia_NBR15965_2N.xlsx
+++ b/Versão5/ABNT/Ontologia_NBR15965_2N.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
   <workbookPr codeName="EstaPastaDeTrabalho" defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Construtor_Onto\ABNT\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B06B3EC3-6907-4363-AEC0-B080DD23B4CC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EE74558F-F6AB-49F6-81A1-23DA570A4B6F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-103" yWindow="-103" windowWidth="22149" windowHeight="13200" activeTab="4" xr2:uid="{82C81399-C775-48F3-A336-58DE5F35A6D9}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="24240" windowHeight="13290" activeTab="4" xr2:uid="{82C81399-C775-48F3-A336-58DE5F35A6D9}"/>
   </bookViews>
   <sheets>
     <sheet name="Projeto" sheetId="8" r:id="rId1"/>
@@ -1932,19 +1932,19 @@
     <t>é.selecionado.por</t>
   </si>
   <si>
-    <t>"[ FilteredElementCollector(doc).OfClass(typeof(SpatialElement)).Cast&lt;SpatialElement&gt;().OrderBy(e =&gt; e.Name).ToList() ]"</t>
-  </si>
-  <si>
-    <t>"[ FilteredElementCollector(doc).OfClass(typeof(Level)).Cast&lt;Level&gt;().OrderBy(e =&gt; e.Name).ToList() ]"</t>
-  </si>
-  <si>
-    <t>"[ EleBuscado : FilteredElementCollector(doc).OfClass(typeof(FamilyInstance)).Cast&lt;FamilyInstance&gt;().FirstOrDefault( e =&gt; e.Symbol.Name == 'InsBuscada') ]"</t>
-  </si>
-  <si>
-    <t>"[ TipBuscado : FilteredElementCollector(doc).OfClass(typeof(FamilySymbol )).Cast&lt;FamilySymbol&gt;( ).FirstOrDefault( e =&gt; e.Name        == 'TipBuscado') ]"</t>
-  </si>
-  <si>
-    <t>"[ MtlBuscado : FilteredElementCollector(doc).OfClass(typeof(Material)).Cast&lt;Material&gt;( ).FirstOrDefault( e =&gt; e.Name  == 'MtlBuscado') ]"</t>
+    <t>"[ Ambientes ]"</t>
+  </si>
+  <si>
+    <t>"[ Pavimentos ]"</t>
+  </si>
+  <si>
+    <t>"[ Elementos ]"</t>
+  </si>
+  <si>
+    <t>"[ Tipos ]"</t>
+  </si>
+  <si>
+    <t>"[ Materiais ]"</t>
   </si>
 </sst>
 </file>
@@ -5519,15 +5519,15 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{03763A90-6A45-4DA0-A35B-2601294A84FF}">
   <sheetPr codeName="Planilha1"/>
   <dimension ref="A1:C39"/>
-  <sheetFormatPr defaultColWidth="11" defaultRowHeight="9" customHeight="1" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="11" defaultRowHeight="9" customHeight="1" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="9.69921875" style="43" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="65.69921875" style="43" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="9.6640625" style="43" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="65.6640625" style="43" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="4.5" style="43" bestFit="1" customWidth="1"/>
     <col min="4" max="16384" width="11" style="43"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" ht="19" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:3" ht="18.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>4</v>
       </c>
@@ -5538,7 +5538,7 @@
         <v>403</v>
       </c>
     </row>
-    <row r="2" spans="1:3" ht="7.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:3" ht="7.35" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="3" t="s">
         <v>168</v>
       </c>
@@ -5549,7 +5549,7 @@
         <v>404</v>
       </c>
     </row>
-    <row r="3" spans="1:3" ht="7.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:3" ht="7.35" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="3" t="s">
         <v>169</v>
       </c>
@@ -5560,7 +5560,7 @@
         <v>404</v>
       </c>
     </row>
-    <row r="4" spans="1:3" ht="7.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:3" ht="7.35" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="4" t="s">
         <v>5</v>
       </c>
@@ -5571,7 +5571,7 @@
         <v>404</v>
       </c>
     </row>
-    <row r="5" spans="1:3" ht="7.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:3" ht="7.35" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="4" t="s">
         <v>6</v>
       </c>
@@ -5583,7 +5583,7 @@
         <v>404</v>
       </c>
     </row>
-    <row r="6" spans="1:3" ht="7.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:3" ht="7.35" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A6" s="4" t="s">
         <v>7</v>
       </c>
@@ -5595,7 +5595,7 @@
         <v>404</v>
       </c>
     </row>
-    <row r="7" spans="1:3" ht="7.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:3" ht="7.35" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A7" s="4" t="s">
         <v>8</v>
       </c>
@@ -5606,7 +5606,7 @@
         <v>404</v>
       </c>
     </row>
-    <row r="8" spans="1:3" ht="7.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:3" ht="7.35" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" s="39" t="s">
         <v>9</v>
       </c>
@@ -5617,7 +5617,7 @@
         <v>404</v>
       </c>
     </row>
-    <row r="9" spans="1:3" ht="7.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:3" ht="7.35" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A9" s="4" t="s">
         <v>170</v>
       </c>
@@ -5628,7 +5628,7 @@
         <v>404</v>
       </c>
     </row>
-    <row r="10" spans="1:3" ht="7.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:3" ht="7.35" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A10" s="4" t="s">
         <v>172</v>
       </c>
@@ -5639,7 +5639,7 @@
         <v>404</v>
       </c>
     </row>
-    <row r="11" spans="1:3" ht="7.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:3" ht="7.35" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A11" s="4" t="s">
         <v>173</v>
       </c>
@@ -5650,7 +5650,7 @@
         <v>404</v>
       </c>
     </row>
-    <row r="12" spans="1:3" ht="7.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:3" ht="7.35" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A12" s="4" t="s">
         <v>10</v>
       </c>
@@ -5661,7 +5661,7 @@
         <v>404</v>
       </c>
     </row>
-    <row r="13" spans="1:3" ht="7.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:3" ht="7.35" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A13" s="4" t="s">
         <v>174</v>
       </c>
@@ -5672,7 +5672,7 @@
         <v>404</v>
       </c>
     </row>
-    <row r="14" spans="1:3" ht="7.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:3" ht="7.35" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A14" s="4" t="s">
         <v>175</v>
       </c>
@@ -5683,7 +5683,7 @@
         <v>404</v>
       </c>
     </row>
-    <row r="15" spans="1:3" ht="7.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:3" ht="7.35" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A15" s="4" t="s">
         <v>176</v>
       </c>
@@ -5694,7 +5694,7 @@
         <v>404</v>
       </c>
     </row>
-    <row r="16" spans="1:3" ht="7.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:3" ht="7.35" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A16" s="4" t="s">
         <v>177</v>
       </c>
@@ -5705,7 +5705,7 @@
         <v>404</v>
       </c>
     </row>
-    <row r="17" spans="1:3" ht="7.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:3" ht="7.35" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A17" s="4" t="s">
         <v>12</v>
       </c>
@@ -5716,19 +5716,19 @@
         <v>404</v>
       </c>
     </row>
-    <row r="18" spans="1:3" ht="7.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:3" ht="7.35" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A18" s="4" t="s">
         <v>178</v>
       </c>
       <c r="B18" s="5">
         <f ca="1">NOW()</f>
-        <v>46257.756787500002</v>
+        <v>46258.545176041669</v>
       </c>
       <c r="C18" s="42" t="s">
         <v>404</v>
       </c>
     </row>
-    <row r="19" spans="1:3" ht="7.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:3" ht="7.35" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A19" s="4" t="s">
         <v>415</v>
       </c>
@@ -5739,7 +5739,7 @@
         <v>404</v>
       </c>
     </row>
-    <row r="20" spans="1:3" ht="7.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:3" ht="7.35" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A20" s="39" t="s">
         <v>411</v>
       </c>
@@ -5751,7 +5751,7 @@
         <v>405</v>
       </c>
     </row>
-    <row r="21" spans="1:3" ht="7.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:3" ht="7.35" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A21" s="39" t="s">
         <v>416</v>
       </c>
@@ -5763,7 +5763,7 @@
         <v>406</v>
       </c>
     </row>
-    <row r="22" spans="1:3" ht="7.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:3" ht="7.35" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A22" s="4" t="s">
         <v>167</v>
       </c>
@@ -5774,7 +5774,7 @@
         <v>404</v>
       </c>
     </row>
-    <row r="23" spans="1:3" ht="7.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:3" ht="7.35" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A23" s="4" t="s">
         <v>179</v>
       </c>
@@ -5785,7 +5785,7 @@
         <v>404</v>
       </c>
     </row>
-    <row r="24" spans="1:3" ht="7.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:3" ht="7.35" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A24" s="4" t="s">
         <v>184</v>
       </c>
@@ -5796,7 +5796,7 @@
         <v>404</v>
       </c>
     </row>
-    <row r="25" spans="1:3" ht="7.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:3" ht="7.35" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A25" s="4" t="s">
         <v>186</v>
       </c>
@@ -5807,7 +5807,7 @@
         <v>405</v>
       </c>
     </row>
-    <row r="26" spans="1:3" ht="7.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:3" ht="7.35" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A26" s="39" t="s">
         <v>400</v>
       </c>
@@ -5818,7 +5818,7 @@
         <v>406</v>
       </c>
     </row>
-    <row r="27" spans="1:3" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:3" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A27" s="39" t="s">
         <v>527</v>
       </c>
@@ -5829,7 +5829,7 @@
         <v>404</v>
       </c>
     </row>
-    <row r="28" spans="1:3" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:3" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A28" s="39" t="s">
         <v>529</v>
       </c>
@@ -5840,7 +5840,7 @@
         <v>404</v>
       </c>
     </row>
-    <row r="29" spans="1:3" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:3" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A29" s="39" t="s">
         <v>531</v>
       </c>
@@ -5851,7 +5851,7 @@
         <v>404</v>
       </c>
     </row>
-    <row r="30" spans="1:3" s="63" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:3" s="63" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A30" s="39" t="s">
         <v>533</v>
       </c>
@@ -5862,7 +5862,7 @@
         <v>404</v>
       </c>
     </row>
-    <row r="31" spans="1:3" s="63" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:3" s="63" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A31" s="39" t="s">
         <v>535</v>
       </c>
@@ -5873,7 +5873,7 @@
         <v>404</v>
       </c>
     </row>
-    <row r="32" spans="1:3" s="63" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:3" s="63" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A32" s="39" t="s">
         <v>537</v>
       </c>
@@ -5884,7 +5884,7 @@
         <v>404</v>
       </c>
     </row>
-    <row r="33" spans="1:3" s="63" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="33" spans="1:3" s="63" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A33" s="39" t="s">
         <v>539</v>
       </c>
@@ -5895,7 +5895,7 @@
         <v>404</v>
       </c>
     </row>
-    <row r="34" spans="1:3" s="63" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="34" spans="1:3" s="63" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A34" s="39" t="s">
         <v>541</v>
       </c>
@@ -5906,7 +5906,7 @@
         <v>404</v>
       </c>
     </row>
-    <row r="35" spans="1:3" s="63" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="35" spans="1:3" s="63" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A35" s="39" t="s">
         <v>543</v>
       </c>
@@ -5917,7 +5917,7 @@
         <v>404</v>
       </c>
     </row>
-    <row r="36" spans="1:3" s="63" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="36" spans="1:3" s="63" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A36" s="39" t="s">
         <v>545</v>
       </c>
@@ -5928,7 +5928,7 @@
         <v>404</v>
       </c>
     </row>
-    <row r="37" spans="1:3" s="63" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="37" spans="1:3" s="63" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A37" s="39" t="s">
         <v>547</v>
       </c>
@@ -5939,7 +5939,7 @@
         <v>404</v>
       </c>
     </row>
-    <row r="38" spans="1:3" customFormat="1" ht="10" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:3" customFormat="1" ht="9.9499999999999993" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A38" s="4" t="s">
         <v>549</v>
       </c>
@@ -5950,7 +5950,7 @@
         <v>404</v>
       </c>
     </row>
-    <row r="39" spans="1:3" s="67" customFormat="1" ht="9.65" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="39" spans="1:3" s="67" customFormat="1" ht="9.6" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A39" s="39" t="s">
         <v>551</v>
       </c>
@@ -5977,36 +5977,36 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{958751C2-A34E-4345-8D6A-082603A025F9}">
   <sheetPr codeName="Planilha2"/>
   <dimension ref="A1:AC24"/>
-  <sheetFormatPr defaultRowHeight="6.75" customHeight="1" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="6.75" customHeight="1" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="2.796875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="7.296875" style="34" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="8.19921875" style="34" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="2.83203125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="7.33203125" style="34" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="8.1640625" style="34" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="10.5" style="34" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="7.69921875" style="34" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.796875" style="34" bestFit="1" customWidth="1"/>
-    <col min="7" max="11" width="11.796875" style="34" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="8.19921875" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="7.6640625" style="34" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.83203125" style="34" bestFit="1" customWidth="1"/>
+    <col min="7" max="11" width="11.83203125" style="34" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="8.1640625" bestFit="1" customWidth="1"/>
     <col min="13" max="13" width="10.5" bestFit="1" customWidth="1"/>
     <col min="14" max="14" width="8" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.796875" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="78.19921875" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.83203125" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="78.1640625" bestFit="1" customWidth="1"/>
     <col min="17" max="17" width="80.5" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="71.69921875" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="71.6640625" bestFit="1" customWidth="1"/>
     <col min="19" max="19" width="5" style="34" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="8.19921875" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="8.1640625" bestFit="1" customWidth="1"/>
     <col min="21" max="21" width="10.5" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="7.69921875" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="7.6640625" bestFit="1" customWidth="1"/>
     <col min="23" max="23" width="10" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="9.796875" style="34" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="43.796875" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="9.796875" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="44.796875" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="8.796875" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="8.69921875" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="9.83203125" style="34" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="43.83203125" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="9.83203125" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="44.83203125" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="8.83203125" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="8.6640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:29" ht="37.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:29" ht="37.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="22" t="s">
         <v>349</v>
       </c>
@@ -6095,7 +6095,7 @@
         <v>372</v>
       </c>
     </row>
-    <row r="2" spans="1:29" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:29" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="49">
         <v>2</v>
       </c>
@@ -6192,7 +6192,7 @@
         <v>420</v>
       </c>
     </row>
-    <row r="3" spans="1:29" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:29" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="49">
         <v>3</v>
       </c>
@@ -6289,7 +6289,7 @@
         <v>421</v>
       </c>
     </row>
-    <row r="4" spans="1:29" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:29" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="49">
         <v>4</v>
       </c>
@@ -6386,7 +6386,7 @@
         <v>422</v>
       </c>
     </row>
-    <row r="5" spans="1:29" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:29" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="49">
         <v>5</v>
       </c>
@@ -6483,7 +6483,7 @@
         <v>423</v>
       </c>
     </row>
-    <row r="6" spans="1:29" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:29" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A6" s="49">
         <v>6</v>
       </c>
@@ -6580,7 +6580,7 @@
         <v>424</v>
       </c>
     </row>
-    <row r="7" spans="1:29" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:29" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A7" s="49">
         <v>7</v>
       </c>
@@ -6677,7 +6677,7 @@
         <v>425</v>
       </c>
     </row>
-    <row r="8" spans="1:29" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:29" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" s="49">
         <v>8</v>
       </c>
@@ -6774,7 +6774,7 @@
         <v>342</v>
       </c>
     </row>
-    <row r="9" spans="1:29" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:29" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A9" s="49">
         <v>9</v>
       </c>
@@ -6871,7 +6871,7 @@
         <v>426</v>
       </c>
     </row>
-    <row r="10" spans="1:29" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:29" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A10" s="49">
         <v>10</v>
       </c>
@@ -6968,7 +6968,7 @@
         <v>427</v>
       </c>
     </row>
-    <row r="11" spans="1:29" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:29" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A11" s="49">
         <v>11</v>
       </c>
@@ -7065,7 +7065,7 @@
         <v>428</v>
       </c>
     </row>
-    <row r="12" spans="1:29" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:29" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A12" s="49">
         <v>12</v>
       </c>
@@ -7162,7 +7162,7 @@
         <v>429</v>
       </c>
     </row>
-    <row r="13" spans="1:29" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:29" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A13" s="49">
         <v>13</v>
       </c>
@@ -7259,7 +7259,7 @@
         <v>430</v>
       </c>
     </row>
-    <row r="14" spans="1:29" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:29" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A14" s="49">
         <v>14</v>
       </c>
@@ -7356,7 +7356,7 @@
         <v>431</v>
       </c>
     </row>
-    <row r="15" spans="1:29" ht="7" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:29" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A15" s="49">
         <v>15</v>
       </c>
@@ -7453,7 +7453,7 @@
         <v>477</v>
       </c>
     </row>
-    <row r="16" spans="1:29" ht="7" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:29" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A16" s="49">
         <v>16</v>
       </c>
@@ -7550,7 +7550,7 @@
         <v>478</v>
       </c>
     </row>
-    <row r="17" spans="1:29" ht="7" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:29" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A17" s="49">
         <v>17</v>
       </c>
@@ -7647,7 +7647,7 @@
         <v>479</v>
       </c>
     </row>
-    <row r="18" spans="1:29" ht="7" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:29" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A18" s="49">
         <v>18</v>
       </c>
@@ -7744,7 +7744,7 @@
         <v>480</v>
       </c>
     </row>
-    <row r="19" spans="1:29" ht="7" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:29" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A19" s="49">
         <v>19</v>
       </c>
@@ -7841,7 +7841,7 @@
         <v>481</v>
       </c>
     </row>
-    <row r="20" spans="1:29" ht="7" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:29" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A20" s="49">
         <v>20</v>
       </c>
@@ -7938,7 +7938,7 @@
         <v>482</v>
       </c>
     </row>
-    <row r="21" spans="1:29" ht="7" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:29" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A21" s="49">
         <v>21</v>
       </c>
@@ -8035,7 +8035,7 @@
         <v>483</v>
       </c>
     </row>
-    <row r="22" spans="1:29" ht="7" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:29" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A22" s="49">
         <v>22</v>
       </c>
@@ -8132,7 +8132,7 @@
         <v>484</v>
       </c>
     </row>
-    <row r="23" spans="1:29" ht="7" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:29" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A23" s="49">
         <v>23</v>
       </c>
@@ -8229,7 +8229,7 @@
         <v>485</v>
       </c>
     </row>
-    <row r="24" spans="1:29" s="48" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:29" s="48" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A24" s="49">
         <v>24</v>
       </c>
@@ -8359,13 +8359,13 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B2B4A051-97A0-4486-9B30-1861C9F77522}">
   <sheetPr codeName="Planilha3"/>
   <dimension ref="A1:U2"/>
-  <sheetFormatPr defaultColWidth="5.296875" defaultRowHeight="10.75" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="5.33203125" defaultRowHeight="11.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="2" customWidth="1"/>
     <col min="2" max="21" width="5" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:21" ht="23.15" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:21" ht="24.75" x14ac:dyDescent="0.2">
       <c r="A1" s="27" t="s">
         <v>350</v>
       </c>
@@ -8430,7 +8430,7 @@
         <v>392</v>
       </c>
     </row>
-    <row r="2" spans="1:21" ht="8.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:21" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="27">
         <v>2</v>
       </c>
@@ -8512,13 +8512,13 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{78CA1C4B-37EB-4980-B878-E43323BA46B5}">
   <sheetPr codeName="Planilha4"/>
   <dimension ref="A1:C2"/>
-  <sheetFormatPr defaultRowHeight="10.75" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="11.25" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="3.296875" bestFit="1" customWidth="1"/>
-    <col min="2" max="3" width="16.69921875" customWidth="1"/>
+    <col min="1" max="1" width="3.33203125" bestFit="1" customWidth="1"/>
+    <col min="2" max="3" width="16.6640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1" s="30">
         <v>1</v>
       </c>
@@ -8529,7 +8529,7 @@
         <v>395</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A2" s="21">
         <v>2</v>
       </c>
@@ -8554,45 +8554,45 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B79BA5E7-BFBD-4AC9-B36C-B9776AA17B75}">
   <sheetPr codeName="Planilha5"/>
   <dimension ref="A1:AG162"/>
-  <sheetFormatPr defaultColWidth="9.3984375" defaultRowHeight="6" customHeight="1" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="9.33203125" defaultRowHeight="6" customHeight="1" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="2.5" style="2" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="8.19921875" style="2" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="11.3984375" style="2" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="8.09765625" style="2" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="5.8984375" style="2" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="3.796875" style="48" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="7.59765625" style="48" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="3.09765625" style="48" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="5.19921875" style="48" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="3.09765625" style="48" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="11.296875" style="48" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="4.796875" style="48" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="27.69921875" style="48" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="5.3984375" style="48" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="36.796875" style="2" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="7.5" style="48" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="80.59765625" style="48" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="5.09765625" style="48" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="3.69921875" style="48" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="3.09765625" style="48" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="3.69921875" style="48" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="3.09765625" style="48" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="3.69921875" style="48" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="9.296875" style="48" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="7.796875" style="48" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="9.296875" style="48" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="6" style="2" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="9.296875" style="48" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="7.5" style="2" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="9.296875" style="48" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="7.19921875" style="2" bestFit="1" customWidth="1"/>
-    <col min="32" max="32" width="9.296875" style="48" bestFit="1" customWidth="1"/>
-    <col min="33" max="33" width="7.09765625" style="2" bestFit="1" customWidth="1"/>
-    <col min="34" max="16384" width="9.3984375" style="2"/>
+    <col min="1" max="1" width="3.6640625" style="2" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="11" style="2" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="14.83203125" style="2" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="10.1640625" style="2" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="7.6640625" style="2" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="4.83203125" style="48" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="9.6640625" style="48" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="5" style="48" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="6.83203125" style="48" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="5" style="48" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14" style="48" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="6.1640625" style="48" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="33.83203125" style="48" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="7" style="48" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="43.83203125" style="2" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="9.83203125" style="48" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="11" style="48" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="6.6640625" style="48" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="5.6640625" style="48" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="4.5" style="48" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="5.6640625" style="48" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="4.5" style="48" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="5.6640625" style="48" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="11.83203125" style="48" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="9.83203125" style="48" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="11.83203125" style="48" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="7.83203125" style="2" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="11.83203125" style="48" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="9.33203125" style="2" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="11.83203125" style="48" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="9.1640625" style="2" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="11.83203125" style="48" bestFit="1" customWidth="1"/>
+    <col min="33" max="33" width="9.1640625" style="2" bestFit="1" customWidth="1"/>
+    <col min="34" max="16384" width="9.33203125" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:33" ht="18.649999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:33" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="7" t="s">
         <v>180</v>
       </c>
@@ -8689,7 +8689,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:33" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:33" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="9">
         <v>2</v>
       </c>
@@ -8790,7 +8790,7 @@
         <v>181</v>
       </c>
     </row>
-    <row r="3" spans="1:33" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:33" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="9">
         <v>3</v>
       </c>
@@ -8891,7 +8891,7 @@
         <v>181</v>
       </c>
     </row>
-    <row r="4" spans="1:33" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:33" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="9">
         <v>4</v>
       </c>
@@ -8992,7 +8992,7 @@
         <v>609</v>
       </c>
     </row>
-    <row r="5" spans="1:33" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:33" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="9">
         <v>5</v>
       </c>
@@ -9093,7 +9093,7 @@
         <v>609</v>
       </c>
     </row>
-    <row r="6" spans="1:33" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:33" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A6" s="9">
         <v>6</v>
       </c>
@@ -9194,7 +9194,7 @@
         <v>609</v>
       </c>
     </row>
-    <row r="7" spans="1:33" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:33" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A7" s="9">
         <v>7</v>
       </c>
@@ -9295,7 +9295,7 @@
         <v>609</v>
       </c>
     </row>
-    <row r="8" spans="1:33" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:33" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" s="9">
         <v>8</v>
       </c>
@@ -9396,7 +9396,7 @@
         <v>609</v>
       </c>
     </row>
-    <row r="9" spans="1:33" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:33" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A9" s="9">
         <v>9</v>
       </c>
@@ -9497,7 +9497,7 @@
         <v>609</v>
       </c>
     </row>
-    <row r="10" spans="1:33" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:33" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A10" s="9">
         <v>10</v>
       </c>
@@ -9598,7 +9598,7 @@
         <v>609</v>
       </c>
     </row>
-    <row r="11" spans="1:33" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:33" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A11" s="9">
         <v>11</v>
       </c>
@@ -9699,7 +9699,7 @@
         <v>609</v>
       </c>
     </row>
-    <row r="12" spans="1:33" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:33" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A12" s="9">
         <v>12</v>
       </c>
@@ -9800,7 +9800,7 @@
         <v>609</v>
       </c>
     </row>
-    <row r="13" spans="1:33" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:33" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A13" s="9">
         <v>13</v>
       </c>
@@ -9901,7 +9901,7 @@
         <v>609</v>
       </c>
     </row>
-    <row r="14" spans="1:33" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:33" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A14" s="9">
         <v>14</v>
       </c>
@@ -10002,7 +10002,7 @@
         <v>609</v>
       </c>
     </row>
-    <row r="15" spans="1:33" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:33" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A15" s="9">
         <v>15</v>
       </c>
@@ -10103,7 +10103,7 @@
         <v>609</v>
       </c>
     </row>
-    <row r="16" spans="1:33" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:33" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A16" s="9">
         <v>16</v>
       </c>
@@ -10204,7 +10204,7 @@
         <v>609</v>
       </c>
     </row>
-    <row r="17" spans="1:33" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:33" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A17" s="9">
         <v>17</v>
       </c>
@@ -10305,7 +10305,7 @@
         <v>609</v>
       </c>
     </row>
-    <row r="18" spans="1:33" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:33" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A18" s="9">
         <v>18</v>
       </c>
@@ -10406,7 +10406,7 @@
         <v>609</v>
       </c>
     </row>
-    <row r="19" spans="1:33" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:33" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A19" s="9">
         <v>19</v>
       </c>
@@ -10507,7 +10507,7 @@
         <v>609</v>
       </c>
     </row>
-    <row r="20" spans="1:33" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:33" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A20" s="9">
         <v>20</v>
       </c>
@@ -10608,7 +10608,7 @@
         <v>609</v>
       </c>
     </row>
-    <row r="21" spans="1:33" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:33" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A21" s="9">
         <v>21</v>
       </c>
@@ -10709,7 +10709,7 @@
         <v>609</v>
       </c>
     </row>
-    <row r="22" spans="1:33" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:33" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A22" s="9">
         <v>22</v>
       </c>
@@ -10810,7 +10810,7 @@
         <v>609</v>
       </c>
     </row>
-    <row r="23" spans="1:33" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:33" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A23" s="9">
         <v>23</v>
       </c>
@@ -10911,7 +10911,7 @@
         <v>609</v>
       </c>
     </row>
-    <row r="24" spans="1:33" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:33" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A24" s="9">
         <v>24</v>
       </c>
@@ -11012,7 +11012,7 @@
         <v>609</v>
       </c>
     </row>
-    <row r="25" spans="1:33" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:33" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A25" s="9">
         <v>25</v>
       </c>
@@ -11113,7 +11113,7 @@
         <v>609</v>
       </c>
     </row>
-    <row r="26" spans="1:33" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:33" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A26" s="9">
         <v>26</v>
       </c>
@@ -11214,7 +11214,7 @@
         <v>609</v>
       </c>
     </row>
-    <row r="27" spans="1:33" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:33" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A27" s="9">
         <v>27</v>
       </c>
@@ -11315,7 +11315,7 @@
         <v>609</v>
       </c>
     </row>
-    <row r="28" spans="1:33" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:33" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A28" s="9">
         <v>28</v>
       </c>
@@ -11416,7 +11416,7 @@
         <v>609</v>
       </c>
     </row>
-    <row r="29" spans="1:33" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:33" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A29" s="9">
         <v>29</v>
       </c>
@@ -11517,7 +11517,7 @@
         <v>609</v>
       </c>
     </row>
-    <row r="30" spans="1:33" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:33" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A30" s="9">
         <v>30</v>
       </c>
@@ -11618,7 +11618,7 @@
         <v>609</v>
       </c>
     </row>
-    <row r="31" spans="1:33" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:33" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A31" s="9">
         <v>31</v>
       </c>
@@ -11719,7 +11719,7 @@
         <v>609</v>
       </c>
     </row>
-    <row r="32" spans="1:33" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:33" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A32" s="9">
         <v>32</v>
       </c>
@@ -11820,7 +11820,7 @@
         <v>609</v>
       </c>
     </row>
-    <row r="33" spans="1:33" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:33" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A33" s="9">
         <v>33</v>
       </c>
@@ -11921,7 +11921,7 @@
         <v>609</v>
       </c>
     </row>
-    <row r="34" spans="1:33" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:33" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A34" s="9">
         <v>34</v>
       </c>
@@ -12022,7 +12022,7 @@
         <v>609</v>
       </c>
     </row>
-    <row r="35" spans="1:33" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:33" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A35" s="9">
         <v>35</v>
       </c>
@@ -12123,7 +12123,7 @@
         <v>609</v>
       </c>
     </row>
-    <row r="36" spans="1:33" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:33" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A36" s="9">
         <v>36</v>
       </c>
@@ -12224,7 +12224,7 @@
         <v>609</v>
       </c>
     </row>
-    <row r="37" spans="1:33" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:33" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A37" s="9">
         <v>37</v>
       </c>
@@ -12325,7 +12325,7 @@
         <v>609</v>
       </c>
     </row>
-    <row r="38" spans="1:33" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:33" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A38" s="9">
         <v>38</v>
       </c>
@@ -12426,7 +12426,7 @@
         <v>609</v>
       </c>
     </row>
-    <row r="39" spans="1:33" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:33" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A39" s="9">
         <v>39</v>
       </c>
@@ -12527,7 +12527,7 @@
         <v>609</v>
       </c>
     </row>
-    <row r="40" spans="1:33" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:33" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A40" s="9">
         <v>40</v>
       </c>
@@ -12628,7 +12628,7 @@
         <v>609</v>
       </c>
     </row>
-    <row r="41" spans="1:33" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:33" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A41" s="9">
         <v>41</v>
       </c>
@@ -12729,7 +12729,7 @@
         <v>609</v>
       </c>
     </row>
-    <row r="42" spans="1:33" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:33" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A42" s="9">
         <v>42</v>
       </c>
@@ -12830,7 +12830,7 @@
         <v>609</v>
       </c>
     </row>
-    <row r="43" spans="1:33" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:33" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A43" s="9">
         <v>43</v>
       </c>
@@ -12931,7 +12931,7 @@
         <v>609</v>
       </c>
     </row>
-    <row r="44" spans="1:33" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:33" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A44" s="9">
         <v>44</v>
       </c>
@@ -13032,7 +13032,7 @@
         <v>609</v>
       </c>
     </row>
-    <row r="45" spans="1:33" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:33" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A45" s="9">
         <v>45</v>
       </c>
@@ -13133,7 +13133,7 @@
         <v>609</v>
       </c>
     </row>
-    <row r="46" spans="1:33" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:33" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A46" s="9">
         <v>46</v>
       </c>
@@ -13234,7 +13234,7 @@
         <v>609</v>
       </c>
     </row>
-    <row r="47" spans="1:33" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:33" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A47" s="9">
         <v>47</v>
       </c>
@@ -13335,7 +13335,7 @@
         <v>609</v>
       </c>
     </row>
-    <row r="48" spans="1:33" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:33" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A48" s="9">
         <v>48</v>
       </c>
@@ -13436,7 +13436,7 @@
         <v>609</v>
       </c>
     </row>
-    <row r="49" spans="1:33" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:33" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A49" s="9">
         <v>49</v>
       </c>
@@ -13537,7 +13537,7 @@
         <v>609</v>
       </c>
     </row>
-    <row r="50" spans="1:33" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:33" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A50" s="9">
         <v>50</v>
       </c>
@@ -13638,7 +13638,7 @@
         <v>609</v>
       </c>
     </row>
-    <row r="51" spans="1:33" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:33" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A51" s="9">
         <v>51</v>
       </c>
@@ -13739,7 +13739,7 @@
         <v>609</v>
       </c>
     </row>
-    <row r="52" spans="1:33" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:33" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A52" s="9">
         <v>52</v>
       </c>
@@ -13840,7 +13840,7 @@
         <v>609</v>
       </c>
     </row>
-    <row r="53" spans="1:33" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:33" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A53" s="9">
         <v>53</v>
       </c>
@@ -13941,7 +13941,7 @@
         <v>609</v>
       </c>
     </row>
-    <row r="54" spans="1:33" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:33" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A54" s="9">
         <v>54</v>
       </c>
@@ -14042,7 +14042,7 @@
         <v>609</v>
       </c>
     </row>
-    <row r="55" spans="1:33" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:33" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A55" s="9">
         <v>55</v>
       </c>
@@ -14143,7 +14143,7 @@
         <v>609</v>
       </c>
     </row>
-    <row r="56" spans="1:33" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:33" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A56" s="9">
         <v>56</v>
       </c>
@@ -14244,7 +14244,7 @@
         <v>609</v>
       </c>
     </row>
-    <row r="57" spans="1:33" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:33" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A57" s="9">
         <v>57</v>
       </c>
@@ -14345,7 +14345,7 @@
         <v>609</v>
       </c>
     </row>
-    <row r="58" spans="1:33" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:33" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A58" s="9">
         <v>58</v>
       </c>
@@ -14446,7 +14446,7 @@
         <v>609</v>
       </c>
     </row>
-    <row r="59" spans="1:33" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:33" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A59" s="9">
         <v>59</v>
       </c>
@@ -14547,7 +14547,7 @@
         <v>609</v>
       </c>
     </row>
-    <row r="60" spans="1:33" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:33" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A60" s="9">
         <v>60</v>
       </c>
@@ -14648,7 +14648,7 @@
         <v>609</v>
       </c>
     </row>
-    <row r="61" spans="1:33" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:33" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A61" s="9">
         <v>61</v>
       </c>
@@ -14749,7 +14749,7 @@
         <v>609</v>
       </c>
     </row>
-    <row r="62" spans="1:33" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:33" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A62" s="9">
         <v>62</v>
       </c>
@@ -14850,7 +14850,7 @@
         <v>609</v>
       </c>
     </row>
-    <row r="63" spans="1:33" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:33" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A63" s="9">
         <v>63</v>
       </c>
@@ -14951,7 +14951,7 @@
         <v>609</v>
       </c>
     </row>
-    <row r="64" spans="1:33" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:33" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A64" s="9">
         <v>64</v>
       </c>
@@ -15052,7 +15052,7 @@
         <v>609</v>
       </c>
     </row>
-    <row r="65" spans="1:33" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:33" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A65" s="9">
         <v>65</v>
       </c>
@@ -15153,7 +15153,7 @@
         <v>609</v>
       </c>
     </row>
-    <row r="66" spans="1:33" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:33" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A66" s="9">
         <v>66</v>
       </c>
@@ -15254,7 +15254,7 @@
         <v>609</v>
       </c>
     </row>
-    <row r="67" spans="1:33" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:33" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A67" s="9">
         <v>67</v>
       </c>
@@ -15355,7 +15355,7 @@
         <v>609</v>
       </c>
     </row>
-    <row r="68" spans="1:33" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:33" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A68" s="9">
         <v>68</v>
       </c>
@@ -15456,7 +15456,7 @@
         <v>609</v>
       </c>
     </row>
-    <row r="69" spans="1:33" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:33" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A69" s="9">
         <v>69</v>
       </c>
@@ -15557,7 +15557,7 @@
         <v>609</v>
       </c>
     </row>
-    <row r="70" spans="1:33" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:33" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A70" s="9">
         <v>70</v>
       </c>
@@ -15658,7 +15658,7 @@
         <v>609</v>
       </c>
     </row>
-    <row r="71" spans="1:33" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:33" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A71" s="9">
         <v>71</v>
       </c>
@@ -15759,7 +15759,7 @@
         <v>609</v>
       </c>
     </row>
-    <row r="72" spans="1:33" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:33" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A72" s="9">
         <v>72</v>
       </c>
@@ -15860,7 +15860,7 @@
         <v>609</v>
       </c>
     </row>
-    <row r="73" spans="1:33" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:33" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A73" s="9">
         <v>73</v>
       </c>
@@ -15961,7 +15961,7 @@
         <v>609</v>
       </c>
     </row>
-    <row r="74" spans="1:33" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:33" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A74" s="9">
         <v>74</v>
       </c>
@@ -16062,7 +16062,7 @@
         <v>609</v>
       </c>
     </row>
-    <row r="75" spans="1:33" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:33" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A75" s="9">
         <v>75</v>
       </c>
@@ -16163,7 +16163,7 @@
         <v>609</v>
       </c>
     </row>
-    <row r="76" spans="1:33" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:33" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A76" s="9">
         <v>76</v>
       </c>
@@ -16264,7 +16264,7 @@
         <v>609</v>
       </c>
     </row>
-    <row r="77" spans="1:33" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:33" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A77" s="9">
         <v>77</v>
       </c>
@@ -16365,7 +16365,7 @@
         <v>609</v>
       </c>
     </row>
-    <row r="78" spans="1:33" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:33" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A78" s="9">
         <v>78</v>
       </c>
@@ -16466,7 +16466,7 @@
         <v>609</v>
       </c>
     </row>
-    <row r="79" spans="1:33" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:33" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A79" s="9">
         <v>79</v>
       </c>
@@ -16567,7 +16567,7 @@
         <v>609</v>
       </c>
     </row>
-    <row r="80" spans="1:33" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:33" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A80" s="9">
         <v>80</v>
       </c>
@@ -16668,7 +16668,7 @@
         <v>609</v>
       </c>
     </row>
-    <row r="81" spans="1:33" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:33" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A81" s="9">
         <v>81</v>
       </c>
@@ -16769,7 +16769,7 @@
         <v>609</v>
       </c>
     </row>
-    <row r="82" spans="1:33" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:33" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A82" s="9">
         <v>82</v>
       </c>
@@ -16870,7 +16870,7 @@
         <v>609</v>
       </c>
     </row>
-    <row r="83" spans="1:33" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:33" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A83" s="9">
         <v>83</v>
       </c>
@@ -16971,7 +16971,7 @@
         <v>609</v>
       </c>
     </row>
-    <row r="84" spans="1:33" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:33" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A84" s="9">
         <v>84</v>
       </c>
@@ -17072,7 +17072,7 @@
         <v>609</v>
       </c>
     </row>
-    <row r="85" spans="1:33" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:33" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A85" s="9">
         <v>85</v>
       </c>
@@ -17173,7 +17173,7 @@
         <v>609</v>
       </c>
     </row>
-    <row r="86" spans="1:33" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:33" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A86" s="9">
         <v>86</v>
       </c>
@@ -17274,7 +17274,7 @@
         <v>609</v>
       </c>
     </row>
-    <row r="87" spans="1:33" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:33" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A87" s="9">
         <v>87</v>
       </c>
@@ -17375,7 +17375,7 @@
         <v>609</v>
       </c>
     </row>
-    <row r="88" spans="1:33" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:33" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A88" s="9">
         <v>88</v>
       </c>
@@ -17476,7 +17476,7 @@
         <v>609</v>
       </c>
     </row>
-    <row r="89" spans="1:33" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:33" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A89" s="9">
         <v>89</v>
       </c>
@@ -17577,7 +17577,7 @@
         <v>609</v>
       </c>
     </row>
-    <row r="90" spans="1:33" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:33" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A90" s="9">
         <v>90</v>
       </c>
@@ -17678,7 +17678,7 @@
         <v>609</v>
       </c>
     </row>
-    <row r="91" spans="1:33" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:33" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A91" s="9">
         <v>91</v>
       </c>
@@ -17779,7 +17779,7 @@
         <v>609</v>
       </c>
     </row>
-    <row r="92" spans="1:33" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:33" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A92" s="9">
         <v>92</v>
       </c>
@@ -17880,7 +17880,7 @@
         <v>609</v>
       </c>
     </row>
-    <row r="93" spans="1:33" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:33" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A93" s="9">
         <v>93</v>
       </c>
@@ -17981,7 +17981,7 @@
         <v>609</v>
       </c>
     </row>
-    <row r="94" spans="1:33" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:33" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A94" s="9">
         <v>94</v>
       </c>
@@ -18082,7 +18082,7 @@
         <v>609</v>
       </c>
     </row>
-    <row r="95" spans="1:33" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:33" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A95" s="9">
         <v>95</v>
       </c>
@@ -18183,7 +18183,7 @@
         <v>609</v>
       </c>
     </row>
-    <row r="96" spans="1:33" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:33" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A96" s="9">
         <v>96</v>
       </c>
@@ -18284,7 +18284,7 @@
         <v>609</v>
       </c>
     </row>
-    <row r="97" spans="1:33" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:33" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A97" s="9">
         <v>97</v>
       </c>
@@ -18385,7 +18385,7 @@
         <v>609</v>
       </c>
     </row>
-    <row r="98" spans="1:33" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:33" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A98" s="9">
         <v>98</v>
       </c>
@@ -18486,7 +18486,7 @@
         <v>609</v>
       </c>
     </row>
-    <row r="99" spans="1:33" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:33" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A99" s="9">
         <v>99</v>
       </c>
@@ -18587,7 +18587,7 @@
         <v>609</v>
       </c>
     </row>
-    <row r="100" spans="1:33" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:33" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A100" s="9">
         <v>100</v>
       </c>
@@ -18688,7 +18688,7 @@
         <v>609</v>
       </c>
     </row>
-    <row r="101" spans="1:33" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:33" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A101" s="9">
         <v>101</v>
       </c>
@@ -18789,7 +18789,7 @@
         <v>609</v>
       </c>
     </row>
-    <row r="102" spans="1:33" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:33" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A102" s="9">
         <v>102</v>
       </c>
@@ -18890,7 +18890,7 @@
         <v>609</v>
       </c>
     </row>
-    <row r="103" spans="1:33" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:33" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A103" s="9">
         <v>103</v>
       </c>
@@ -18991,7 +18991,7 @@
         <v>609</v>
       </c>
     </row>
-    <row r="104" spans="1:33" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:33" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A104" s="9">
         <v>104</v>
       </c>
@@ -19092,7 +19092,7 @@
         <v>609</v>
       </c>
     </row>
-    <row r="105" spans="1:33" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="105" spans="1:33" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A105" s="9">
         <v>105</v>
       </c>
@@ -19193,7 +19193,7 @@
         <v>609</v>
       </c>
     </row>
-    <row r="106" spans="1:33" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="106" spans="1:33" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A106" s="9">
         <v>106</v>
       </c>
@@ -19294,7 +19294,7 @@
         <v>609</v>
       </c>
     </row>
-    <row r="107" spans="1:33" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="107" spans="1:33" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A107" s="9">
         <v>107</v>
       </c>
@@ -19395,7 +19395,7 @@
         <v>609</v>
       </c>
     </row>
-    <row r="108" spans="1:33" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="108" spans="1:33" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A108" s="9">
         <v>108</v>
       </c>
@@ -19496,7 +19496,7 @@
         <v>609</v>
       </c>
     </row>
-    <row r="109" spans="1:33" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="109" spans="1:33" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A109" s="9">
         <v>109</v>
       </c>
@@ -19597,7 +19597,7 @@
         <v>609</v>
       </c>
     </row>
-    <row r="110" spans="1:33" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="110" spans="1:33" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A110" s="9">
         <v>110</v>
       </c>
@@ -19698,7 +19698,7 @@
         <v>609</v>
       </c>
     </row>
-    <row r="111" spans="1:33" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="111" spans="1:33" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A111" s="9">
         <v>111</v>
       </c>
@@ -19799,7 +19799,7 @@
         <v>609</v>
       </c>
     </row>
-    <row r="112" spans="1:33" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="112" spans="1:33" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A112" s="9">
         <v>112</v>
       </c>
@@ -19900,7 +19900,7 @@
         <v>609</v>
       </c>
     </row>
-    <row r="113" spans="1:33" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="113" spans="1:33" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A113" s="9">
         <v>113</v>
       </c>
@@ -20001,7 +20001,7 @@
         <v>609</v>
       </c>
     </row>
-    <row r="114" spans="1:33" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="114" spans="1:33" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A114" s="9">
         <v>114</v>
       </c>
@@ -20102,7 +20102,7 @@
         <v>609</v>
       </c>
     </row>
-    <row r="115" spans="1:33" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="115" spans="1:33" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A115" s="9">
         <v>115</v>
       </c>
@@ -20203,7 +20203,7 @@
         <v>609</v>
       </c>
     </row>
-    <row r="116" spans="1:33" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="116" spans="1:33" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A116" s="9">
         <v>116</v>
       </c>
@@ -20304,7 +20304,7 @@
         <v>609</v>
       </c>
     </row>
-    <row r="117" spans="1:33" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="117" spans="1:33" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A117" s="9">
         <v>117</v>
       </c>
@@ -20405,7 +20405,7 @@
         <v>609</v>
       </c>
     </row>
-    <row r="118" spans="1:33" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="118" spans="1:33" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A118" s="9">
         <v>118</v>
       </c>
@@ -20506,7 +20506,7 @@
         <v>609</v>
       </c>
     </row>
-    <row r="119" spans="1:33" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="119" spans="1:33" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A119" s="9">
         <v>119</v>
       </c>
@@ -20607,7 +20607,7 @@
         <v>609</v>
       </c>
     </row>
-    <row r="120" spans="1:33" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="120" spans="1:33" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A120" s="9">
         <v>120</v>
       </c>
@@ -20708,7 +20708,7 @@
         <v>609</v>
       </c>
     </row>
-    <row r="121" spans="1:33" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="121" spans="1:33" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A121" s="9">
         <v>121</v>
       </c>
@@ -20809,7 +20809,7 @@
         <v>609</v>
       </c>
     </row>
-    <row r="122" spans="1:33" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="122" spans="1:33" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A122" s="9">
         <v>122</v>
       </c>
@@ -20910,7 +20910,7 @@
         <v>609</v>
       </c>
     </row>
-    <row r="123" spans="1:33" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="123" spans="1:33" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A123" s="9">
         <v>123</v>
       </c>
@@ -21011,7 +21011,7 @@
         <v>609</v>
       </c>
     </row>
-    <row r="124" spans="1:33" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="124" spans="1:33" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A124" s="9">
         <v>124</v>
       </c>
@@ -21112,7 +21112,7 @@
         <v>609</v>
       </c>
     </row>
-    <row r="125" spans="1:33" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="125" spans="1:33" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A125" s="9">
         <v>125</v>
       </c>
@@ -21213,7 +21213,7 @@
         <v>609</v>
       </c>
     </row>
-    <row r="126" spans="1:33" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="126" spans="1:33" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A126" s="9">
         <v>126</v>
       </c>
@@ -21314,7 +21314,7 @@
         <v>609</v>
       </c>
     </row>
-    <row r="127" spans="1:33" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="127" spans="1:33" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A127" s="9">
         <v>127</v>
       </c>
@@ -21415,7 +21415,7 @@
         <v>609</v>
       </c>
     </row>
-    <row r="128" spans="1:33" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="128" spans="1:33" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A128" s="9">
         <v>128</v>
       </c>
@@ -21516,7 +21516,7 @@
         <v>609</v>
       </c>
     </row>
-    <row r="129" spans="1:33" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="129" spans="1:33" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A129" s="9">
         <v>129</v>
       </c>
@@ -21617,7 +21617,7 @@
         <v>609</v>
       </c>
     </row>
-    <row r="130" spans="1:33" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="130" spans="1:33" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A130" s="9">
         <v>130</v>
       </c>
@@ -21718,7 +21718,7 @@
         <v>609</v>
       </c>
     </row>
-    <row r="131" spans="1:33" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="131" spans="1:33" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A131" s="9">
         <v>131</v>
       </c>
@@ -21819,7 +21819,7 @@
         <v>609</v>
       </c>
     </row>
-    <row r="132" spans="1:33" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="132" spans="1:33" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A132" s="9">
         <v>132</v>
       </c>
@@ -21920,7 +21920,7 @@
         <v>609</v>
       </c>
     </row>
-    <row r="133" spans="1:33" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="133" spans="1:33" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A133" s="9">
         <v>133</v>
       </c>
@@ -22021,7 +22021,7 @@
         <v>609</v>
       </c>
     </row>
-    <row r="134" spans="1:33" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="134" spans="1:33" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A134" s="9">
         <v>134</v>
       </c>
@@ -22122,7 +22122,7 @@
         <v>609</v>
       </c>
     </row>
-    <row r="135" spans="1:33" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="135" spans="1:33" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A135" s="9">
         <v>135</v>
       </c>
@@ -22223,7 +22223,7 @@
         <v>609</v>
       </c>
     </row>
-    <row r="136" spans="1:33" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="136" spans="1:33" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A136" s="9">
         <v>136</v>
       </c>
@@ -22324,7 +22324,7 @@
         <v>609</v>
       </c>
     </row>
-    <row r="137" spans="1:33" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="137" spans="1:33" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A137" s="9">
         <v>137</v>
       </c>
@@ -22425,7 +22425,7 @@
         <v>609</v>
       </c>
     </row>
-    <row r="138" spans="1:33" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="138" spans="1:33" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A138" s="9">
         <v>138</v>
       </c>
@@ -22526,7 +22526,7 @@
         <v>609</v>
       </c>
     </row>
-    <row r="139" spans="1:33" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="139" spans="1:33" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A139" s="9">
         <v>139</v>
       </c>
@@ -22627,7 +22627,7 @@
         <v>609</v>
       </c>
     </row>
-    <row r="140" spans="1:33" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="140" spans="1:33" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A140" s="9">
         <v>140</v>
       </c>
@@ -22728,7 +22728,7 @@
         <v>609</v>
       </c>
     </row>
-    <row r="141" spans="1:33" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="141" spans="1:33" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A141" s="9">
         <v>141</v>
       </c>
@@ -22829,7 +22829,7 @@
         <v>609</v>
       </c>
     </row>
-    <row r="142" spans="1:33" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="142" spans="1:33" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A142" s="9">
         <v>142</v>
       </c>
@@ -22930,7 +22930,7 @@
         <v>609</v>
       </c>
     </row>
-    <row r="143" spans="1:33" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="143" spans="1:33" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A143" s="9">
         <v>143</v>
       </c>
@@ -23031,7 +23031,7 @@
         <v>609</v>
       </c>
     </row>
-    <row r="144" spans="1:33" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="144" spans="1:33" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A144" s="9">
         <v>144</v>
       </c>
@@ -23132,7 +23132,7 @@
         <v>609</v>
       </c>
     </row>
-    <row r="145" spans="1:33" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="145" spans="1:33" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A145" s="9">
         <v>145</v>
       </c>
@@ -23233,7 +23233,7 @@
         <v>609</v>
       </c>
     </row>
-    <row r="146" spans="1:33" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="146" spans="1:33" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A146" s="9">
         <v>146</v>
       </c>
@@ -23334,7 +23334,7 @@
         <v>609</v>
       </c>
     </row>
-    <row r="147" spans="1:33" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="147" spans="1:33" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A147" s="9">
         <v>147</v>
       </c>
@@ -23435,7 +23435,7 @@
         <v>609</v>
       </c>
     </row>
-    <row r="148" spans="1:33" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="148" spans="1:33" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A148" s="9">
         <v>148</v>
       </c>
@@ -23536,7 +23536,7 @@
         <v>609</v>
       </c>
     </row>
-    <row r="149" spans="1:33" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="149" spans="1:33" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A149" s="9">
         <v>149</v>
       </c>
@@ -23637,7 +23637,7 @@
         <v>609</v>
       </c>
     </row>
-    <row r="150" spans="1:33" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="150" spans="1:33" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A150" s="9">
         <v>150</v>
       </c>
@@ -23738,7 +23738,7 @@
         <v>609</v>
       </c>
     </row>
-    <row r="151" spans="1:33" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="151" spans="1:33" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A151" s="9">
         <v>151</v>
       </c>
@@ -23839,7 +23839,7 @@
         <v>609</v>
       </c>
     </row>
-    <row r="152" spans="1:33" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="152" spans="1:33" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A152" s="9">
         <v>152</v>
       </c>
@@ -23940,7 +23940,7 @@
         <v>609</v>
       </c>
     </row>
-    <row r="153" spans="1:33" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="153" spans="1:33" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A153" s="9">
         <v>153</v>
       </c>
@@ -24041,7 +24041,7 @@
         <v>609</v>
       </c>
     </row>
-    <row r="154" spans="1:33" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="154" spans="1:33" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A154" s="9">
         <v>154</v>
       </c>
@@ -24142,7 +24142,7 @@
         <v>609</v>
       </c>
     </row>
-    <row r="155" spans="1:33" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="155" spans="1:33" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A155" s="9">
         <v>155</v>
       </c>
@@ -24243,7 +24243,7 @@
         <v>609</v>
       </c>
     </row>
-    <row r="156" spans="1:33" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="156" spans="1:33" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A156" s="9">
         <v>156</v>
       </c>
@@ -24344,7 +24344,7 @@
         <v>609</v>
       </c>
     </row>
-    <row r="157" spans="1:33" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="157" spans="1:33" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A157" s="9">
         <v>157</v>
       </c>
@@ -24445,7 +24445,7 @@
         <v>609</v>
       </c>
     </row>
-    <row r="158" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="158" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A158" s="9">
         <v>158</v>
       </c>
@@ -24547,7 +24547,7 @@
         <v>609</v>
       </c>
     </row>
-    <row r="159" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="159" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A159" s="9">
         <v>159</v>
       </c>
@@ -24649,7 +24649,7 @@
         <v>609</v>
       </c>
     </row>
-    <row r="160" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="160" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A160" s="9">
         <v>160</v>
       </c>
@@ -24751,7 +24751,7 @@
         <v>609</v>
       </c>
     </row>
-    <row r="161" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="161" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A161" s="9">
         <v>161</v>
       </c>
@@ -24853,7 +24853,7 @@
         <v>609</v>
       </c>
     </row>
-    <row r="162" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="162" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A162" s="9">
         <v>162</v>
       </c>

--- a/Versão5/ABNT/Ontologia_NBR15965_2N.xlsx
+++ b/Versão5/ABNT/Ontologia_NBR15965_2N.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr codeName="EstaPastaDeTrabalho" defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Construtor_Onto\ABNT\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EE74558F-F6AB-49F6-81A1-23DA570A4B6F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4219B41B-888B-49FE-B823-9BFDDB2016C9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="24240" windowHeight="13290" activeTab="4" xr2:uid="{82C81399-C775-48F3-A336-58DE5F35A6D9}"/>
+    <workbookView xWindow="-103" yWindow="-103" windowWidth="22149" windowHeight="13200" activeTab="1" xr2:uid="{82C81399-C775-48F3-A336-58DE5F35A6D9}"/>
   </bookViews>
   <sheets>
     <sheet name="Projeto" sheetId="8" r:id="rId1"/>
@@ -5519,15 +5519,15 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{03763A90-6A45-4DA0-A35B-2601294A84FF}">
   <sheetPr codeName="Planilha1"/>
   <dimension ref="A1:C39"/>
-  <sheetFormatPr defaultColWidth="11" defaultRowHeight="9" customHeight="1" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="11" defaultRowHeight="9" customHeight="1" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="9.6640625" style="43" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="65.6640625" style="43" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="9.69921875" style="43" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="65.69921875" style="43" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="4.5" style="43" bestFit="1" customWidth="1"/>
     <col min="4" max="16384" width="11" style="43"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" ht="18.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:3" ht="19" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>4</v>
       </c>
@@ -5538,7 +5538,7 @@
         <v>403</v>
       </c>
     </row>
-    <row r="2" spans="1:3" ht="7.35" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:3" ht="7.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="3" t="s">
         <v>168</v>
       </c>
@@ -5549,7 +5549,7 @@
         <v>404</v>
       </c>
     </row>
-    <row r="3" spans="1:3" ht="7.35" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:3" ht="7.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="3" t="s">
         <v>169</v>
       </c>
@@ -5560,7 +5560,7 @@
         <v>404</v>
       </c>
     </row>
-    <row r="4" spans="1:3" ht="7.35" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:3" ht="7.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="4" t="s">
         <v>5</v>
       </c>
@@ -5571,7 +5571,7 @@
         <v>404</v>
       </c>
     </row>
-    <row r="5" spans="1:3" ht="7.35" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:3" ht="7.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="4" t="s">
         <v>6</v>
       </c>
@@ -5583,7 +5583,7 @@
         <v>404</v>
       </c>
     </row>
-    <row r="6" spans="1:3" ht="7.35" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:3" ht="7.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="4" t="s">
         <v>7</v>
       </c>
@@ -5595,7 +5595,7 @@
         <v>404</v>
       </c>
     </row>
-    <row r="7" spans="1:3" ht="7.35" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:3" ht="7.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="4" t="s">
         <v>8</v>
       </c>
@@ -5606,7 +5606,7 @@
         <v>404</v>
       </c>
     </row>
-    <row r="8" spans="1:3" ht="7.35" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:3" ht="7.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" s="39" t="s">
         <v>9</v>
       </c>
@@ -5617,7 +5617,7 @@
         <v>404</v>
       </c>
     </row>
-    <row r="9" spans="1:3" ht="7.35" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:3" ht="7.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="4" t="s">
         <v>170</v>
       </c>
@@ -5628,7 +5628,7 @@
         <v>404</v>
       </c>
     </row>
-    <row r="10" spans="1:3" ht="7.35" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:3" ht="7.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" s="4" t="s">
         <v>172</v>
       </c>
@@ -5639,7 +5639,7 @@
         <v>404</v>
       </c>
     </row>
-    <row r="11" spans="1:3" ht="7.35" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:3" ht="7.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A11" s="4" t="s">
         <v>173</v>
       </c>
@@ -5650,7 +5650,7 @@
         <v>404</v>
       </c>
     </row>
-    <row r="12" spans="1:3" ht="7.35" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:3" ht="7.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A12" s="4" t="s">
         <v>10</v>
       </c>
@@ -5661,7 +5661,7 @@
         <v>404</v>
       </c>
     </row>
-    <row r="13" spans="1:3" ht="7.35" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:3" ht="7.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A13" s="4" t="s">
         <v>174</v>
       </c>
@@ -5672,7 +5672,7 @@
         <v>404</v>
       </c>
     </row>
-    <row r="14" spans="1:3" ht="7.35" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:3" ht="7.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A14" s="4" t="s">
         <v>175</v>
       </c>
@@ -5683,7 +5683,7 @@
         <v>404</v>
       </c>
     </row>
-    <row r="15" spans="1:3" ht="7.35" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:3" ht="7.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A15" s="4" t="s">
         <v>176</v>
       </c>
@@ -5694,7 +5694,7 @@
         <v>404</v>
       </c>
     </row>
-    <row r="16" spans="1:3" ht="7.35" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:3" ht="7.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A16" s="4" t="s">
         <v>177</v>
       </c>
@@ -5705,7 +5705,7 @@
         <v>404</v>
       </c>
     </row>
-    <row r="17" spans="1:3" ht="7.35" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:3" ht="7.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A17" s="4" t="s">
         <v>12</v>
       </c>
@@ -5716,19 +5716,19 @@
         <v>404</v>
       </c>
     </row>
-    <row r="18" spans="1:3" ht="7.35" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:3" ht="7.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A18" s="4" t="s">
         <v>178</v>
       </c>
       <c r="B18" s="5">
         <f ca="1">NOW()</f>
-        <v>46258.545176041669</v>
+        <v>46264.561653472221</v>
       </c>
       <c r="C18" s="42" t="s">
         <v>404</v>
       </c>
     </row>
-    <row r="19" spans="1:3" ht="7.35" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:3" ht="7.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A19" s="4" t="s">
         <v>415</v>
       </c>
@@ -5739,7 +5739,7 @@
         <v>404</v>
       </c>
     </row>
-    <row r="20" spans="1:3" ht="7.35" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:3" ht="7.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A20" s="39" t="s">
         <v>411</v>
       </c>
@@ -5751,7 +5751,7 @@
         <v>405</v>
       </c>
     </row>
-    <row r="21" spans="1:3" ht="7.35" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:3" ht="7.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A21" s="39" t="s">
         <v>416</v>
       </c>
@@ -5763,7 +5763,7 @@
         <v>406</v>
       </c>
     </row>
-    <row r="22" spans="1:3" ht="7.35" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:3" ht="7.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A22" s="4" t="s">
         <v>167</v>
       </c>
@@ -5774,7 +5774,7 @@
         <v>404</v>
       </c>
     </row>
-    <row r="23" spans="1:3" ht="7.35" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:3" ht="7.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A23" s="4" t="s">
         <v>179</v>
       </c>
@@ -5785,7 +5785,7 @@
         <v>404</v>
       </c>
     </row>
-    <row r="24" spans="1:3" ht="7.35" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:3" ht="7.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A24" s="4" t="s">
         <v>184</v>
       </c>
@@ -5796,7 +5796,7 @@
         <v>404</v>
       </c>
     </row>
-    <row r="25" spans="1:3" ht="7.35" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:3" ht="7.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A25" s="4" t="s">
         <v>186</v>
       </c>
@@ -5807,7 +5807,7 @@
         <v>405</v>
       </c>
     </row>
-    <row r="26" spans="1:3" ht="7.35" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:3" ht="7.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A26" s="39" t="s">
         <v>400</v>
       </c>
@@ -5818,7 +5818,7 @@
         <v>406</v>
       </c>
     </row>
-    <row r="27" spans="1:3" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:3" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A27" s="39" t="s">
         <v>527</v>
       </c>
@@ -5829,7 +5829,7 @@
         <v>404</v>
       </c>
     </row>
-    <row r="28" spans="1:3" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:3" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A28" s="39" t="s">
         <v>529</v>
       </c>
@@ -5840,7 +5840,7 @@
         <v>404</v>
       </c>
     </row>
-    <row r="29" spans="1:3" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:3" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A29" s="39" t="s">
         <v>531</v>
       </c>
@@ -5851,7 +5851,7 @@
         <v>404</v>
       </c>
     </row>
-    <row r="30" spans="1:3" s="63" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="30" spans="1:3" s="63" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A30" s="39" t="s">
         <v>533</v>
       </c>
@@ -5862,7 +5862,7 @@
         <v>404</v>
       </c>
     </row>
-    <row r="31" spans="1:3" s="63" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="31" spans="1:3" s="63" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A31" s="39" t="s">
         <v>535</v>
       </c>
@@ -5873,7 +5873,7 @@
         <v>404</v>
       </c>
     </row>
-    <row r="32" spans="1:3" s="63" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="32" spans="1:3" s="63" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A32" s="39" t="s">
         <v>537</v>
       </c>
@@ -5884,7 +5884,7 @@
         <v>404</v>
       </c>
     </row>
-    <row r="33" spans="1:3" s="63" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="33" spans="1:3" s="63" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A33" s="39" t="s">
         <v>539</v>
       </c>
@@ -5895,7 +5895,7 @@
         <v>404</v>
       </c>
     </row>
-    <row r="34" spans="1:3" s="63" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="34" spans="1:3" s="63" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A34" s="39" t="s">
         <v>541</v>
       </c>
@@ -5906,7 +5906,7 @@
         <v>404</v>
       </c>
     </row>
-    <row r="35" spans="1:3" s="63" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="35" spans="1:3" s="63" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A35" s="39" t="s">
         <v>543</v>
       </c>
@@ -5917,7 +5917,7 @@
         <v>404</v>
       </c>
     </row>
-    <row r="36" spans="1:3" s="63" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="36" spans="1:3" s="63" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A36" s="39" t="s">
         <v>545</v>
       </c>
@@ -5928,7 +5928,7 @@
         <v>404</v>
       </c>
     </row>
-    <row r="37" spans="1:3" s="63" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="37" spans="1:3" s="63" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A37" s="39" t="s">
         <v>547</v>
       </c>
@@ -5939,7 +5939,7 @@
         <v>404</v>
       </c>
     </row>
-    <row r="38" spans="1:3" customFormat="1" ht="9.9499999999999993" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="38" spans="1:3" customFormat="1" ht="10" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A38" s="4" t="s">
         <v>549</v>
       </c>
@@ -5950,7 +5950,7 @@
         <v>404</v>
       </c>
     </row>
-    <row r="39" spans="1:3" s="67" customFormat="1" ht="9.6" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="39" spans="1:3" s="67" customFormat="1" ht="9.65" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A39" s="39" t="s">
         <v>551</v>
       </c>
@@ -5977,36 +5977,36 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{958751C2-A34E-4345-8D6A-082603A025F9}">
   <sheetPr codeName="Planilha2"/>
   <dimension ref="A1:AC24"/>
-  <sheetFormatPr defaultRowHeight="6.75" customHeight="1" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultRowHeight="6.75" customHeight="1" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="2.83203125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="7.33203125" style="34" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="8.1640625" style="34" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="2.796875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="7.296875" style="34" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="8.19921875" style="34" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="10.5" style="34" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="7.6640625" style="34" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.83203125" style="34" bestFit="1" customWidth="1"/>
-    <col min="7" max="11" width="11.83203125" style="34" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="8.1640625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="7.69921875" style="34" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.796875" style="34" bestFit="1" customWidth="1"/>
+    <col min="7" max="11" width="11.796875" style="34" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="8.19921875" bestFit="1" customWidth="1"/>
     <col min="13" max="13" width="10.5" bestFit="1" customWidth="1"/>
     <col min="14" max="14" width="8" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.83203125" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="78.1640625" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.796875" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="78.19921875" bestFit="1" customWidth="1"/>
     <col min="17" max="17" width="80.5" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="71.6640625" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="71.69921875" bestFit="1" customWidth="1"/>
     <col min="19" max="19" width="5" style="34" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="8.1640625" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="8.19921875" bestFit="1" customWidth="1"/>
     <col min="21" max="21" width="10.5" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="7.6640625" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="7.69921875" bestFit="1" customWidth="1"/>
     <col min="23" max="23" width="10" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="9.83203125" style="34" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="43.83203125" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="9.83203125" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="44.83203125" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="8.83203125" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="8.6640625" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="9.796875" style="34" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="43.796875" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="9.796875" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="44.796875" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="8.796875" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="8.69921875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:29" ht="37.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:29" ht="37.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="22" t="s">
         <v>349</v>
       </c>
@@ -6095,7 +6095,7 @@
         <v>372</v>
       </c>
     </row>
-    <row r="2" spans="1:29" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:29" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="49">
         <v>2</v>
       </c>
@@ -6192,7 +6192,7 @@
         <v>420</v>
       </c>
     </row>
-    <row r="3" spans="1:29" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:29" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="49">
         <v>3</v>
       </c>
@@ -6289,7 +6289,7 @@
         <v>421</v>
       </c>
     </row>
-    <row r="4" spans="1:29" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:29" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="49">
         <v>4</v>
       </c>
@@ -6386,7 +6386,7 @@
         <v>422</v>
       </c>
     </row>
-    <row r="5" spans="1:29" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:29" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="49">
         <v>5</v>
       </c>
@@ -6483,7 +6483,7 @@
         <v>423</v>
       </c>
     </row>
-    <row r="6" spans="1:29" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:29" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="49">
         <v>6</v>
       </c>
@@ -6580,7 +6580,7 @@
         <v>424</v>
       </c>
     </row>
-    <row r="7" spans="1:29" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:29" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="49">
         <v>7</v>
       </c>
@@ -6677,7 +6677,7 @@
         <v>425</v>
       </c>
     </row>
-    <row r="8" spans="1:29" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:29" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" s="49">
         <v>8</v>
       </c>
@@ -6774,7 +6774,7 @@
         <v>342</v>
       </c>
     </row>
-    <row r="9" spans="1:29" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:29" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="49">
         <v>9</v>
       </c>
@@ -6871,7 +6871,7 @@
         <v>426</v>
       </c>
     </row>
-    <row r="10" spans="1:29" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:29" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" s="49">
         <v>10</v>
       </c>
@@ -6968,7 +6968,7 @@
         <v>427</v>
       </c>
     </row>
-    <row r="11" spans="1:29" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:29" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A11" s="49">
         <v>11</v>
       </c>
@@ -7065,7 +7065,7 @@
         <v>428</v>
       </c>
     </row>
-    <row r="12" spans="1:29" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:29" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A12" s="49">
         <v>12</v>
       </c>
@@ -7162,7 +7162,7 @@
         <v>429</v>
       </c>
     </row>
-    <row r="13" spans="1:29" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:29" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A13" s="49">
         <v>13</v>
       </c>
@@ -7259,7 +7259,7 @@
         <v>430</v>
       </c>
     </row>
-    <row r="14" spans="1:29" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:29" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A14" s="49">
         <v>14</v>
       </c>
@@ -7356,7 +7356,7 @@
         <v>431</v>
       </c>
     </row>
-    <row r="15" spans="1:29" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:29" ht="7" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A15" s="49">
         <v>15</v>
       </c>
@@ -7453,7 +7453,7 @@
         <v>477</v>
       </c>
     </row>
-    <row r="16" spans="1:29" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:29" ht="7" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A16" s="49">
         <v>16</v>
       </c>
@@ -7550,7 +7550,7 @@
         <v>478</v>
       </c>
     </row>
-    <row r="17" spans="1:29" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:29" ht="7" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A17" s="49">
         <v>17</v>
       </c>
@@ -7647,7 +7647,7 @@
         <v>479</v>
       </c>
     </row>
-    <row r="18" spans="1:29" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:29" ht="7" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A18" s="49">
         <v>18</v>
       </c>
@@ -7744,7 +7744,7 @@
         <v>480</v>
       </c>
     </row>
-    <row r="19" spans="1:29" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:29" ht="7" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A19" s="49">
         <v>19</v>
       </c>
@@ -7841,7 +7841,7 @@
         <v>481</v>
       </c>
     </row>
-    <row r="20" spans="1:29" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:29" ht="7" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A20" s="49">
         <v>20</v>
       </c>
@@ -7938,7 +7938,7 @@
         <v>482</v>
       </c>
     </row>
-    <row r="21" spans="1:29" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:29" ht="7" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A21" s="49">
         <v>21</v>
       </c>
@@ -8035,7 +8035,7 @@
         <v>483</v>
       </c>
     </row>
-    <row r="22" spans="1:29" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:29" ht="7" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A22" s="49">
         <v>22</v>
       </c>
@@ -8132,7 +8132,7 @@
         <v>484</v>
       </c>
     </row>
-    <row r="23" spans="1:29" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:29" ht="7" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A23" s="49">
         <v>23</v>
       </c>
@@ -8229,7 +8229,7 @@
         <v>485</v>
       </c>
     </row>
-    <row r="24" spans="1:29" s="48" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:29" s="48" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="49">
         <v>24</v>
       </c>
@@ -8240,10 +8240,10 @@
         <v>589</v>
       </c>
       <c r="D24" s="33" t="s">
+        <v>591</v>
+      </c>
+      <c r="E24" s="33" t="s">
         <v>590</v>
-      </c>
-      <c r="E24" s="33" t="s">
-        <v>591</v>
       </c>
       <c r="F24" s="33" t="s">
         <v>592</v>
@@ -8269,11 +8269,11 @@
       </c>
       <c r="M24" s="51" t="str">
         <f t="shared" si="9"/>
-        <v>Métodos</v>
+        <v>Macros</v>
       </c>
       <c r="N24" s="51" t="str">
         <f t="shared" si="9"/>
-        <v>Macros</v>
+        <v>Métodos</v>
       </c>
       <c r="O24" s="51" t="str">
         <f t="shared" si="9"/>
@@ -8297,11 +8297,11 @@
       </c>
       <c r="U24" s="38" t="str">
         <f t="shared" si="10"/>
-        <v>Métodos</v>
+        <v>Macros</v>
       </c>
       <c r="V24" s="52" t="str">
         <f t="shared" si="10"/>
-        <v>Macros</v>
+        <v>Métodos</v>
       </c>
       <c r="W24" s="38" t="s">
         <v>419</v>
@@ -8359,13 +8359,13 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B2B4A051-97A0-4486-9B30-1861C9F77522}">
   <sheetPr codeName="Planilha3"/>
   <dimension ref="A1:U2"/>
-  <sheetFormatPr defaultColWidth="5.33203125" defaultRowHeight="11.25" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="5.296875" defaultRowHeight="10.75" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="2" customWidth="1"/>
     <col min="2" max="21" width="5" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:21" ht="24.75" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:21" ht="23.15" x14ac:dyDescent="0.3">
       <c r="A1" s="27" t="s">
         <v>350</v>
       </c>
@@ -8430,7 +8430,7 @@
         <v>392</v>
       </c>
     </row>
-    <row r="2" spans="1:21" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:21" ht="8.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="27">
         <v>2</v>
       </c>
@@ -8512,13 +8512,13 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{78CA1C4B-37EB-4980-B878-E43323BA46B5}">
   <sheetPr codeName="Planilha4"/>
   <dimension ref="A1:C2"/>
-  <sheetFormatPr defaultRowHeight="11.25" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultRowHeight="10.75" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="3.33203125" bestFit="1" customWidth="1"/>
-    <col min="2" max="3" width="16.6640625" customWidth="1"/>
+    <col min="1" max="1" width="3.296875" bestFit="1" customWidth="1"/>
+    <col min="2" max="3" width="16.69921875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1" s="30">
         <v>1</v>
       </c>
@@ -8529,7 +8529,7 @@
         <v>395</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A2" s="21">
         <v>2</v>
       </c>
@@ -8554,45 +8554,45 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B79BA5E7-BFBD-4AC9-B36C-B9776AA17B75}">
   <sheetPr codeName="Planilha5"/>
   <dimension ref="A1:AG162"/>
-  <sheetFormatPr defaultColWidth="9.33203125" defaultRowHeight="6" customHeight="1" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="9.296875" defaultRowHeight="6" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="3.6640625" style="2" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="3.69921875" style="2" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="11" style="2" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="14.83203125" style="2" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="10.1640625" style="2" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="7.6640625" style="2" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="4.83203125" style="48" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="9.6640625" style="48" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="14.796875" style="2" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="10.19921875" style="2" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="7.69921875" style="2" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="4.796875" style="48" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="9.69921875" style="48" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="5" style="48" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="6.83203125" style="48" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="6.796875" style="48" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="5" style="48" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="14" style="48" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="6.1640625" style="48" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="33.83203125" style="48" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="6.19921875" style="48" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="33.796875" style="48" bestFit="1" customWidth="1"/>
     <col min="14" max="14" width="7" style="48" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="43.83203125" style="2" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="9.83203125" style="48" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="43.796875" style="2" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="9.796875" style="48" bestFit="1" customWidth="1"/>
     <col min="17" max="17" width="11" style="48" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="6.6640625" style="48" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="5.6640625" style="48" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="6.69921875" style="48" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="5.69921875" style="48" bestFit="1" customWidth="1"/>
     <col min="20" max="20" width="4.5" style="48" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="5.6640625" style="48" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="5.69921875" style="48" bestFit="1" customWidth="1"/>
     <col min="22" max="22" width="4.5" style="48" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="5.6640625" style="48" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="11.83203125" style="48" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="9.83203125" style="48" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="11.83203125" style="48" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="7.83203125" style="2" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="11.83203125" style="48" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="9.33203125" style="2" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="11.83203125" style="48" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="9.1640625" style="2" bestFit="1" customWidth="1"/>
-    <col min="32" max="32" width="11.83203125" style="48" bestFit="1" customWidth="1"/>
-    <col min="33" max="33" width="9.1640625" style="2" bestFit="1" customWidth="1"/>
-    <col min="34" max="16384" width="9.33203125" style="2"/>
+    <col min="23" max="23" width="5.69921875" style="48" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="11.796875" style="48" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="9.796875" style="48" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="11.796875" style="48" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="7.796875" style="2" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="11.796875" style="48" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="9.296875" style="2" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="11.796875" style="48" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="9.19921875" style="2" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="11.796875" style="48" bestFit="1" customWidth="1"/>
+    <col min="33" max="33" width="9.19921875" style="2" bestFit="1" customWidth="1"/>
+    <col min="34" max="16384" width="9.296875" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:33" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:33" ht="18.649999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="7" t="s">
         <v>180</v>
       </c>
@@ -8689,7 +8689,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:33" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:33" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="9">
         <v>2</v>
       </c>
@@ -8790,7 +8790,7 @@
         <v>181</v>
       </c>
     </row>
-    <row r="3" spans="1:33" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:33" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="9">
         <v>3</v>
       </c>
@@ -8891,7 +8891,7 @@
         <v>181</v>
       </c>
     </row>
-    <row r="4" spans="1:33" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:33" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="9">
         <v>4</v>
       </c>
@@ -8992,7 +8992,7 @@
         <v>609</v>
       </c>
     </row>
-    <row r="5" spans="1:33" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:33" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="9">
         <v>5</v>
       </c>
@@ -9093,7 +9093,7 @@
         <v>609</v>
       </c>
     </row>
-    <row r="6" spans="1:33" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:33" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="9">
         <v>6</v>
       </c>
@@ -9194,7 +9194,7 @@
         <v>609</v>
       </c>
     </row>
-    <row r="7" spans="1:33" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:33" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="9">
         <v>7</v>
       </c>
@@ -9295,7 +9295,7 @@
         <v>609</v>
       </c>
     </row>
-    <row r="8" spans="1:33" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:33" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="9">
         <v>8</v>
       </c>
@@ -9396,7 +9396,7 @@
         <v>609</v>
       </c>
     </row>
-    <row r="9" spans="1:33" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:33" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="9">
         <v>9</v>
       </c>
@@ -9497,7 +9497,7 @@
         <v>609</v>
       </c>
     </row>
-    <row r="10" spans="1:33" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:33" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="9">
         <v>10</v>
       </c>
@@ -9598,7 +9598,7 @@
         <v>609</v>
       </c>
     </row>
-    <row r="11" spans="1:33" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:33" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="9">
         <v>11</v>
       </c>
@@ -9699,7 +9699,7 @@
         <v>609</v>
       </c>
     </row>
-    <row r="12" spans="1:33" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:33" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="9">
         <v>12</v>
       </c>
@@ -9800,7 +9800,7 @@
         <v>609</v>
       </c>
     </row>
-    <row r="13" spans="1:33" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:33" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="9">
         <v>13</v>
       </c>
@@ -9901,7 +9901,7 @@
         <v>609</v>
       </c>
     </row>
-    <row r="14" spans="1:33" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:33" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="9">
         <v>14</v>
       </c>
@@ -10002,7 +10002,7 @@
         <v>609</v>
       </c>
     </row>
-    <row r="15" spans="1:33" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:33" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="9">
         <v>15</v>
       </c>
@@ -10103,7 +10103,7 @@
         <v>609</v>
       </c>
     </row>
-    <row r="16" spans="1:33" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:33" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="9">
         <v>16</v>
       </c>
@@ -10204,7 +10204,7 @@
         <v>609</v>
       </c>
     </row>
-    <row r="17" spans="1:33" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:33" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="9">
         <v>17</v>
       </c>
@@ -10305,7 +10305,7 @@
         <v>609</v>
       </c>
     </row>
-    <row r="18" spans="1:33" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:33" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="9">
         <v>18</v>
       </c>
@@ -10406,7 +10406,7 @@
         <v>609</v>
       </c>
     </row>
-    <row r="19" spans="1:33" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:33" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="9">
         <v>19</v>
       </c>
@@ -10507,7 +10507,7 @@
         <v>609</v>
       </c>
     </row>
-    <row r="20" spans="1:33" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:33" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="9">
         <v>20</v>
       </c>
@@ -10608,7 +10608,7 @@
         <v>609</v>
       </c>
     </row>
-    <row r="21" spans="1:33" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:33" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="9">
         <v>21</v>
       </c>
@@ -10709,7 +10709,7 @@
         <v>609</v>
       </c>
     </row>
-    <row r="22" spans="1:33" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:33" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="9">
         <v>22</v>
       </c>
@@ -10810,7 +10810,7 @@
         <v>609</v>
       </c>
     </row>
-    <row r="23" spans="1:33" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:33" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="9">
         <v>23</v>
       </c>
@@ -10911,7 +10911,7 @@
         <v>609</v>
       </c>
     </row>
-    <row r="24" spans="1:33" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:33" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="9">
         <v>24</v>
       </c>
@@ -11012,7 +11012,7 @@
         <v>609</v>
       </c>
     </row>
-    <row r="25" spans="1:33" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:33" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="9">
         <v>25</v>
       </c>
@@ -11113,7 +11113,7 @@
         <v>609</v>
       </c>
     </row>
-    <row r="26" spans="1:33" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:33" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A26" s="9">
         <v>26</v>
       </c>
@@ -11214,7 +11214,7 @@
         <v>609</v>
       </c>
     </row>
-    <row r="27" spans="1:33" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:33" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A27" s="9">
         <v>27</v>
       </c>
@@ -11315,7 +11315,7 @@
         <v>609</v>
       </c>
     </row>
-    <row r="28" spans="1:33" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:33" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A28" s="9">
         <v>28</v>
       </c>
@@ -11416,7 +11416,7 @@
         <v>609</v>
       </c>
     </row>
-    <row r="29" spans="1:33" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:33" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A29" s="9">
         <v>29</v>
       </c>
@@ -11517,7 +11517,7 @@
         <v>609</v>
       </c>
     </row>
-    <row r="30" spans="1:33" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:33" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A30" s="9">
         <v>30</v>
       </c>
@@ -11618,7 +11618,7 @@
         <v>609</v>
       </c>
     </row>
-    <row r="31" spans="1:33" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:33" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A31" s="9">
         <v>31</v>
       </c>
@@ -11719,7 +11719,7 @@
         <v>609</v>
       </c>
     </row>
-    <row r="32" spans="1:33" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:33" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A32" s="9">
         <v>32</v>
       </c>
@@ -11820,7 +11820,7 @@
         <v>609</v>
       </c>
     </row>
-    <row r="33" spans="1:33" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="33" spans="1:33" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A33" s="9">
         <v>33</v>
       </c>
@@ -11921,7 +11921,7 @@
         <v>609</v>
       </c>
     </row>
-    <row r="34" spans="1:33" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="34" spans="1:33" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A34" s="9">
         <v>34</v>
       </c>
@@ -12022,7 +12022,7 @@
         <v>609</v>
       </c>
     </row>
-    <row r="35" spans="1:33" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="35" spans="1:33" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A35" s="9">
         <v>35</v>
       </c>
@@ -12123,7 +12123,7 @@
         <v>609</v>
       </c>
     </row>
-    <row r="36" spans="1:33" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="36" spans="1:33" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A36" s="9">
         <v>36</v>
       </c>
@@ -12224,7 +12224,7 @@
         <v>609</v>
       </c>
     </row>
-    <row r="37" spans="1:33" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="37" spans="1:33" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A37" s="9">
         <v>37</v>
       </c>
@@ -12325,7 +12325,7 @@
         <v>609</v>
       </c>
     </row>
-    <row r="38" spans="1:33" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="38" spans="1:33" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A38" s="9">
         <v>38</v>
       </c>
@@ -12426,7 +12426,7 @@
         <v>609</v>
       </c>
     </row>
-    <row r="39" spans="1:33" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="39" spans="1:33" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A39" s="9">
         <v>39</v>
       </c>
@@ -12527,7 +12527,7 @@
         <v>609</v>
       </c>
     </row>
-    <row r="40" spans="1:33" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="40" spans="1:33" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A40" s="9">
         <v>40</v>
       </c>
@@ -12628,7 +12628,7 @@
         <v>609</v>
       </c>
     </row>
-    <row r="41" spans="1:33" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="41" spans="1:33" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A41" s="9">
         <v>41</v>
       </c>
@@ -12729,7 +12729,7 @@
         <v>609</v>
       </c>
     </row>
-    <row r="42" spans="1:33" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="42" spans="1:33" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A42" s="9">
         <v>42</v>
       </c>
@@ -12830,7 +12830,7 @@
         <v>609</v>
       </c>
     </row>
-    <row r="43" spans="1:33" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="43" spans="1:33" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A43" s="9">
         <v>43</v>
       </c>
@@ -12931,7 +12931,7 @@
         <v>609</v>
       </c>
     </row>
-    <row r="44" spans="1:33" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="44" spans="1:33" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A44" s="9">
         <v>44</v>
       </c>
@@ -13032,7 +13032,7 @@
         <v>609</v>
       </c>
     </row>
-    <row r="45" spans="1:33" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="45" spans="1:33" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A45" s="9">
         <v>45</v>
       </c>
@@ -13133,7 +13133,7 @@
         <v>609</v>
       </c>
     </row>
-    <row r="46" spans="1:33" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="46" spans="1:33" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A46" s="9">
         <v>46</v>
       </c>
@@ -13234,7 +13234,7 @@
         <v>609</v>
       </c>
     </row>
-    <row r="47" spans="1:33" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="47" spans="1:33" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A47" s="9">
         <v>47</v>
       </c>
@@ -13335,7 +13335,7 @@
         <v>609</v>
       </c>
     </row>
-    <row r="48" spans="1:33" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="48" spans="1:33" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A48" s="9">
         <v>48</v>
       </c>
@@ -13436,7 +13436,7 @@
         <v>609</v>
       </c>
     </row>
-    <row r="49" spans="1:33" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="49" spans="1:33" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A49" s="9">
         <v>49</v>
       </c>
@@ -13537,7 +13537,7 @@
         <v>609</v>
       </c>
     </row>
-    <row r="50" spans="1:33" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="50" spans="1:33" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A50" s="9">
         <v>50</v>
       </c>
@@ -13638,7 +13638,7 @@
         <v>609</v>
       </c>
     </row>
-    <row r="51" spans="1:33" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="51" spans="1:33" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A51" s="9">
         <v>51</v>
       </c>
@@ -13739,7 +13739,7 @@
         <v>609</v>
       </c>
     </row>
-    <row r="52" spans="1:33" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="52" spans="1:33" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A52" s="9">
         <v>52</v>
       </c>
@@ -13840,7 +13840,7 @@
         <v>609</v>
       </c>
     </row>
-    <row r="53" spans="1:33" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="53" spans="1:33" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A53" s="9">
         <v>53</v>
       </c>
@@ -13941,7 +13941,7 @@
         <v>609</v>
       </c>
     </row>
-    <row r="54" spans="1:33" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="54" spans="1:33" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A54" s="9">
         <v>54</v>
       </c>
@@ -14042,7 +14042,7 @@
         <v>609</v>
       </c>
     </row>
-    <row r="55" spans="1:33" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="55" spans="1:33" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A55" s="9">
         <v>55</v>
       </c>
@@ -14143,7 +14143,7 @@
         <v>609</v>
       </c>
     </row>
-    <row r="56" spans="1:33" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="56" spans="1:33" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A56" s="9">
         <v>56</v>
       </c>
@@ -14244,7 +14244,7 @@
         <v>609</v>
       </c>
     </row>
-    <row r="57" spans="1:33" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="57" spans="1:33" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A57" s="9">
         <v>57</v>
       </c>
@@ -14345,7 +14345,7 @@
         <v>609</v>
       </c>
     </row>
-    <row r="58" spans="1:33" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="58" spans="1:33" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A58" s="9">
         <v>58</v>
       </c>
@@ -14446,7 +14446,7 @@
         <v>609</v>
       </c>
     </row>
-    <row r="59" spans="1:33" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="59" spans="1:33" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A59" s="9">
         <v>59</v>
       </c>
@@ -14547,7 +14547,7 @@
         <v>609</v>
       </c>
     </row>
-    <row r="60" spans="1:33" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="60" spans="1:33" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A60" s="9">
         <v>60</v>
       </c>
@@ -14648,7 +14648,7 @@
         <v>609</v>
       </c>
     </row>
-    <row r="61" spans="1:33" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="61" spans="1:33" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A61" s="9">
         <v>61</v>
       </c>
@@ -14749,7 +14749,7 @@
         <v>609</v>
       </c>
     </row>
-    <row r="62" spans="1:33" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="62" spans="1:33" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A62" s="9">
         <v>62</v>
       </c>
@@ -14850,7 +14850,7 @@
         <v>609</v>
       </c>
     </row>
-    <row r="63" spans="1:33" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="63" spans="1:33" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A63" s="9">
         <v>63</v>
       </c>
@@ -14951,7 +14951,7 @@
         <v>609</v>
       </c>
     </row>
-    <row r="64" spans="1:33" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="64" spans="1:33" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A64" s="9">
         <v>64</v>
       </c>
@@ -15052,7 +15052,7 @@
         <v>609</v>
       </c>
     </row>
-    <row r="65" spans="1:33" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="65" spans="1:33" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A65" s="9">
         <v>65</v>
       </c>
@@ -15153,7 +15153,7 @@
         <v>609</v>
       </c>
     </row>
-    <row r="66" spans="1:33" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="66" spans="1:33" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A66" s="9">
         <v>66</v>
       </c>
@@ -15254,7 +15254,7 @@
         <v>609</v>
       </c>
     </row>
-    <row r="67" spans="1:33" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="67" spans="1:33" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A67" s="9">
         <v>67</v>
       </c>
@@ -15355,7 +15355,7 @@
         <v>609</v>
       </c>
     </row>
-    <row r="68" spans="1:33" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="68" spans="1:33" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A68" s="9">
         <v>68</v>
       </c>
@@ -15456,7 +15456,7 @@
         <v>609</v>
       </c>
     </row>
-    <row r="69" spans="1:33" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="69" spans="1:33" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A69" s="9">
         <v>69</v>
       </c>
@@ -15557,7 +15557,7 @@
         <v>609</v>
       </c>
     </row>
-    <row r="70" spans="1:33" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="70" spans="1:33" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A70" s="9">
         <v>70</v>
       </c>
@@ -15658,7 +15658,7 @@
         <v>609</v>
       </c>
     </row>
-    <row r="71" spans="1:33" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="71" spans="1:33" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A71" s="9">
         <v>71</v>
       </c>
@@ -15759,7 +15759,7 @@
         <v>609</v>
       </c>
     </row>
-    <row r="72" spans="1:33" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="72" spans="1:33" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A72" s="9">
         <v>72</v>
       </c>
@@ -15860,7 +15860,7 @@
         <v>609</v>
       </c>
     </row>
-    <row r="73" spans="1:33" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="73" spans="1:33" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A73" s="9">
         <v>73</v>
       </c>
@@ -15961,7 +15961,7 @@
         <v>609</v>
       </c>
     </row>
-    <row r="74" spans="1:33" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="74" spans="1:33" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A74" s="9">
         <v>74</v>
       </c>
@@ -16062,7 +16062,7 @@
         <v>609</v>
       </c>
     </row>
-    <row r="75" spans="1:33" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="75" spans="1:33" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A75" s="9">
         <v>75</v>
       </c>
@@ -16163,7 +16163,7 @@
         <v>609</v>
       </c>
     </row>
-    <row r="76" spans="1:33" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="76" spans="1:33" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A76" s="9">
         <v>76</v>
       </c>
@@ -16264,7 +16264,7 @@
         <v>609</v>
       </c>
     </row>
-    <row r="77" spans="1:33" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="77" spans="1:33" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A77" s="9">
         <v>77</v>
       </c>
@@ -16365,7 +16365,7 @@
         <v>609</v>
       </c>
     </row>
-    <row r="78" spans="1:33" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="78" spans="1:33" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A78" s="9">
         <v>78</v>
       </c>
@@ -16466,7 +16466,7 @@
         <v>609</v>
       </c>
     </row>
-    <row r="79" spans="1:33" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="79" spans="1:33" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A79" s="9">
         <v>79</v>
       </c>
@@ -16567,7 +16567,7 @@
         <v>609</v>
       </c>
     </row>
-    <row r="80" spans="1:33" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="80" spans="1:33" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A80" s="9">
         <v>80</v>
       </c>
@@ -16668,7 +16668,7 @@
         <v>609</v>
       </c>
     </row>
-    <row r="81" spans="1:33" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="81" spans="1:33" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A81" s="9">
         <v>81</v>
       </c>
@@ -16769,7 +16769,7 @@
         <v>609</v>
       </c>
     </row>
-    <row r="82" spans="1:33" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="82" spans="1:33" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A82" s="9">
         <v>82</v>
       </c>
@@ -16870,7 +16870,7 @@
         <v>609</v>
       </c>
     </row>
-    <row r="83" spans="1:33" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="83" spans="1:33" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A83" s="9">
         <v>83</v>
       </c>
@@ -16971,7 +16971,7 @@
         <v>609</v>
       </c>
     </row>
-    <row r="84" spans="1:33" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="84" spans="1:33" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A84" s="9">
         <v>84</v>
       </c>
@@ -17072,7 +17072,7 @@
         <v>609</v>
       </c>
     </row>
-    <row r="85" spans="1:33" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="85" spans="1:33" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A85" s="9">
         <v>85</v>
       </c>
@@ -17173,7 +17173,7 @@
         <v>609</v>
       </c>
     </row>
-    <row r="86" spans="1:33" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="86" spans="1:33" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A86" s="9">
         <v>86</v>
       </c>
@@ -17274,7 +17274,7 @@
         <v>609</v>
       </c>
     </row>
-    <row r="87" spans="1:33" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="87" spans="1:33" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A87" s="9">
         <v>87</v>
       </c>
@@ -17375,7 +17375,7 @@
         <v>609</v>
       </c>
     </row>
-    <row r="88" spans="1:33" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="88" spans="1:33" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A88" s="9">
         <v>88</v>
       </c>
@@ -17476,7 +17476,7 @@
         <v>609</v>
       </c>
     </row>
-    <row r="89" spans="1:33" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="89" spans="1:33" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A89" s="9">
         <v>89</v>
       </c>
@@ -17577,7 +17577,7 @@
         <v>609</v>
       </c>
     </row>
-    <row r="90" spans="1:33" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="90" spans="1:33" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A90" s="9">
         <v>90</v>
       </c>
@@ -17678,7 +17678,7 @@
         <v>609</v>
       </c>
     </row>
-    <row r="91" spans="1:33" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="91" spans="1:33" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A91" s="9">
         <v>91</v>
       </c>
@@ -17779,7 +17779,7 @@
         <v>609</v>
       </c>
     </row>
-    <row r="92" spans="1:33" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="92" spans="1:33" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A92" s="9">
         <v>92</v>
       </c>
@@ -17880,7 +17880,7 @@
         <v>609</v>
       </c>
     </row>
-    <row r="93" spans="1:33" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="93" spans="1:33" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A93" s="9">
         <v>93</v>
       </c>
@@ -17981,7 +17981,7 @@
         <v>609</v>
       </c>
     </row>
-    <row r="94" spans="1:33" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="94" spans="1:33" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A94" s="9">
         <v>94</v>
       </c>
@@ -18082,7 +18082,7 @@
         <v>609</v>
       </c>
     </row>
-    <row r="95" spans="1:33" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="95" spans="1:33" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A95" s="9">
         <v>95</v>
       </c>
@@ -18183,7 +18183,7 @@
         <v>609</v>
       </c>
     </row>
-    <row r="96" spans="1:33" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="96" spans="1:33" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A96" s="9">
         <v>96</v>
       </c>
@@ -18284,7 +18284,7 @@
         <v>609</v>
       </c>
     </row>
-    <row r="97" spans="1:33" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="97" spans="1:33" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A97" s="9">
         <v>97</v>
       </c>
@@ -18385,7 +18385,7 @@
         <v>609</v>
       </c>
     </row>
-    <row r="98" spans="1:33" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="98" spans="1:33" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A98" s="9">
         <v>98</v>
       </c>
@@ -18486,7 +18486,7 @@
         <v>609</v>
       </c>
     </row>
-    <row r="99" spans="1:33" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="99" spans="1:33" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A99" s="9">
         <v>99</v>
       </c>
@@ -18587,7 +18587,7 @@
         <v>609</v>
       </c>
     </row>
-    <row r="100" spans="1:33" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="100" spans="1:33" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A100" s="9">
         <v>100</v>
       </c>
@@ -18688,7 +18688,7 @@
         <v>609</v>
       </c>
     </row>
-    <row r="101" spans="1:33" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="101" spans="1:33" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A101" s="9">
         <v>101</v>
       </c>
@@ -18789,7 +18789,7 @@
         <v>609</v>
       </c>
     </row>
-    <row r="102" spans="1:33" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="102" spans="1:33" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A102" s="9">
         <v>102</v>
       </c>
@@ -18890,7 +18890,7 @@
         <v>609</v>
       </c>
     </row>
-    <row r="103" spans="1:33" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="103" spans="1:33" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A103" s="9">
         <v>103</v>
       </c>
@@ -18991,7 +18991,7 @@
         <v>609</v>
       </c>
     </row>
-    <row r="104" spans="1:33" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="104" spans="1:33" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A104" s="9">
         <v>104</v>
       </c>
@@ -19092,7 +19092,7 @@
         <v>609</v>
       </c>
     </row>
-    <row r="105" spans="1:33" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="105" spans="1:33" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A105" s="9">
         <v>105</v>
       </c>
@@ -19193,7 +19193,7 @@
         <v>609</v>
       </c>
     </row>
-    <row r="106" spans="1:33" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="106" spans="1:33" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A106" s="9">
         <v>106</v>
       </c>
@@ -19294,7 +19294,7 @@
         <v>609</v>
       </c>
     </row>
-    <row r="107" spans="1:33" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="107" spans="1:33" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A107" s="9">
         <v>107</v>
       </c>
@@ -19395,7 +19395,7 @@
         <v>609</v>
       </c>
     </row>
-    <row r="108" spans="1:33" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="108" spans="1:33" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A108" s="9">
         <v>108</v>
       </c>
@@ -19496,7 +19496,7 @@
         <v>609</v>
       </c>
     </row>
-    <row r="109" spans="1:33" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="109" spans="1:33" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A109" s="9">
         <v>109</v>
       </c>
@@ -19597,7 +19597,7 @@
         <v>609</v>
       </c>
     </row>
-    <row r="110" spans="1:33" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="110" spans="1:33" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A110" s="9">
         <v>110</v>
       </c>
@@ -19698,7 +19698,7 @@
         <v>609</v>
       </c>
     </row>
-    <row r="111" spans="1:33" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="111" spans="1:33" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A111" s="9">
         <v>111</v>
       </c>
@@ -19799,7 +19799,7 @@
         <v>609</v>
       </c>
     </row>
-    <row r="112" spans="1:33" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="112" spans="1:33" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A112" s="9">
         <v>112</v>
       </c>
@@ -19900,7 +19900,7 @@
         <v>609</v>
       </c>
     </row>
-    <row r="113" spans="1:33" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="113" spans="1:33" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A113" s="9">
         <v>113</v>
       </c>
@@ -20001,7 +20001,7 @@
         <v>609</v>
       </c>
     </row>
-    <row r="114" spans="1:33" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="114" spans="1:33" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A114" s="9">
         <v>114</v>
       </c>
@@ -20102,7 +20102,7 @@
         <v>609</v>
       </c>
     </row>
-    <row r="115" spans="1:33" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="115" spans="1:33" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A115" s="9">
         <v>115</v>
       </c>
@@ -20203,7 +20203,7 @@
         <v>609</v>
       </c>
     </row>
-    <row r="116" spans="1:33" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="116" spans="1:33" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A116" s="9">
         <v>116</v>
       </c>
@@ -20304,7 +20304,7 @@
         <v>609</v>
       </c>
     </row>
-    <row r="117" spans="1:33" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="117" spans="1:33" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A117" s="9">
         <v>117</v>
       </c>
@@ -20405,7 +20405,7 @@
         <v>609</v>
       </c>
     </row>
-    <row r="118" spans="1:33" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="118" spans="1:33" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A118" s="9">
         <v>118</v>
       </c>
@@ -20506,7 +20506,7 @@
         <v>609</v>
       </c>
     </row>
-    <row r="119" spans="1:33" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="119" spans="1:33" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A119" s="9">
         <v>119</v>
       </c>
@@ -20607,7 +20607,7 @@
         <v>609</v>
       </c>
     </row>
-    <row r="120" spans="1:33" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="120" spans="1:33" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A120" s="9">
         <v>120</v>
       </c>
@@ -20708,7 +20708,7 @@
         <v>609</v>
       </c>
     </row>
-    <row r="121" spans="1:33" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="121" spans="1:33" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A121" s="9">
         <v>121</v>
       </c>
@@ -20809,7 +20809,7 @@
         <v>609</v>
       </c>
     </row>
-    <row r="122" spans="1:33" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="122" spans="1:33" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A122" s="9">
         <v>122</v>
       </c>
@@ -20910,7 +20910,7 @@
         <v>609</v>
       </c>
     </row>
-    <row r="123" spans="1:33" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="123" spans="1:33" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A123" s="9">
         <v>123</v>
       </c>
@@ -21011,7 +21011,7 @@
         <v>609</v>
       </c>
     </row>
-    <row r="124" spans="1:33" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="124" spans="1:33" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A124" s="9">
         <v>124</v>
       </c>
@@ -21112,7 +21112,7 @@
         <v>609</v>
       </c>
     </row>
-    <row r="125" spans="1:33" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="125" spans="1:33" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A125" s="9">
         <v>125</v>
       </c>
@@ -21213,7 +21213,7 @@
         <v>609</v>
       </c>
     </row>
-    <row r="126" spans="1:33" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="126" spans="1:33" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A126" s="9">
         <v>126</v>
       </c>
@@ -21314,7 +21314,7 @@
         <v>609</v>
       </c>
     </row>
-    <row r="127" spans="1:33" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="127" spans="1:33" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A127" s="9">
         <v>127</v>
       </c>
@@ -21415,7 +21415,7 @@
         <v>609</v>
       </c>
     </row>
-    <row r="128" spans="1:33" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="128" spans="1:33" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A128" s="9">
         <v>128</v>
       </c>
@@ -21516,7 +21516,7 @@
         <v>609</v>
       </c>
     </row>
-    <row r="129" spans="1:33" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="129" spans="1:33" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A129" s="9">
         <v>129</v>
       </c>
@@ -21617,7 +21617,7 @@
         <v>609</v>
       </c>
     </row>
-    <row r="130" spans="1:33" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="130" spans="1:33" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A130" s="9">
         <v>130</v>
       </c>
@@ -21718,7 +21718,7 @@
         <v>609</v>
       </c>
     </row>
-    <row r="131" spans="1:33" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="131" spans="1:33" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A131" s="9">
         <v>131</v>
       </c>
@@ -21819,7 +21819,7 @@
         <v>609</v>
       </c>
     </row>
-    <row r="132" spans="1:33" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="132" spans="1:33" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A132" s="9">
         <v>132</v>
       </c>
@@ -21920,7 +21920,7 @@
         <v>609</v>
       </c>
     </row>
-    <row r="133" spans="1:33" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="133" spans="1:33" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A133" s="9">
         <v>133</v>
       </c>
@@ -22021,7 +22021,7 @@
         <v>609</v>
       </c>
     </row>
-    <row r="134" spans="1:33" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="134" spans="1:33" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A134" s="9">
         <v>134</v>
       </c>
@@ -22122,7 +22122,7 @@
         <v>609</v>
       </c>
     </row>
-    <row r="135" spans="1:33" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="135" spans="1:33" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A135" s="9">
         <v>135</v>
       </c>
@@ -22223,7 +22223,7 @@
         <v>609</v>
       </c>
     </row>
-    <row r="136" spans="1:33" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="136" spans="1:33" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A136" s="9">
         <v>136</v>
       </c>
@@ -22324,7 +22324,7 @@
         <v>609</v>
       </c>
     </row>
-    <row r="137" spans="1:33" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="137" spans="1:33" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A137" s="9">
         <v>137</v>
       </c>
@@ -22425,7 +22425,7 @@
         <v>609</v>
       </c>
     </row>
-    <row r="138" spans="1:33" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="138" spans="1:33" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A138" s="9">
         <v>138</v>
       </c>
@@ -22526,7 +22526,7 @@
         <v>609</v>
       </c>
     </row>
-    <row r="139" spans="1:33" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="139" spans="1:33" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A139" s="9">
         <v>139</v>
       </c>
@@ -22627,7 +22627,7 @@
         <v>609</v>
       </c>
     </row>
-    <row r="140" spans="1:33" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="140" spans="1:33" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A140" s="9">
         <v>140</v>
       </c>
@@ -22728,7 +22728,7 @@
         <v>609</v>
       </c>
     </row>
-    <row r="141" spans="1:33" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="141" spans="1:33" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A141" s="9">
         <v>141</v>
       </c>
@@ -22829,7 +22829,7 @@
         <v>609</v>
       </c>
     </row>
-    <row r="142" spans="1:33" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="142" spans="1:33" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A142" s="9">
         <v>142</v>
       </c>
@@ -22930,7 +22930,7 @@
         <v>609</v>
       </c>
     </row>
-    <row r="143" spans="1:33" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="143" spans="1:33" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A143" s="9">
         <v>143</v>
       </c>
@@ -23031,7 +23031,7 @@
         <v>609</v>
       </c>
     </row>
-    <row r="144" spans="1:33" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="144" spans="1:33" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A144" s="9">
         <v>144</v>
       </c>
@@ -23132,7 +23132,7 @@
         <v>609</v>
       </c>
     </row>
-    <row r="145" spans="1:33" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="145" spans="1:33" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A145" s="9">
         <v>145</v>
       </c>
@@ -23233,7 +23233,7 @@
         <v>609</v>
       </c>
     </row>
-    <row r="146" spans="1:33" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="146" spans="1:33" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A146" s="9">
         <v>146</v>
       </c>
@@ -23334,7 +23334,7 @@
         <v>609</v>
       </c>
     </row>
-    <row r="147" spans="1:33" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="147" spans="1:33" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A147" s="9">
         <v>147</v>
       </c>
@@ -23435,7 +23435,7 @@
         <v>609</v>
       </c>
     </row>
-    <row r="148" spans="1:33" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="148" spans="1:33" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A148" s="9">
         <v>148</v>
       </c>
@@ -23536,7 +23536,7 @@
         <v>609</v>
       </c>
     </row>
-    <row r="149" spans="1:33" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="149" spans="1:33" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A149" s="9">
         <v>149</v>
       </c>
@@ -23637,7 +23637,7 @@
         <v>609</v>
       </c>
     </row>
-    <row r="150" spans="1:33" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="150" spans="1:33" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A150" s="9">
         <v>150</v>
       </c>
@@ -23738,7 +23738,7 @@
         <v>609</v>
       </c>
     </row>
-    <row r="151" spans="1:33" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="151" spans="1:33" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A151" s="9">
         <v>151</v>
       </c>
@@ -23839,7 +23839,7 @@
         <v>609</v>
       </c>
     </row>
-    <row r="152" spans="1:33" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="152" spans="1:33" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A152" s="9">
         <v>152</v>
       </c>
@@ -23940,7 +23940,7 @@
         <v>609</v>
       </c>
     </row>
-    <row r="153" spans="1:33" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="153" spans="1:33" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A153" s="9">
         <v>153</v>
       </c>
@@ -24041,7 +24041,7 @@
         <v>609</v>
       </c>
     </row>
-    <row r="154" spans="1:33" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="154" spans="1:33" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A154" s="9">
         <v>154</v>
       </c>
@@ -24142,7 +24142,7 @@
         <v>609</v>
       </c>
     </row>
-    <row r="155" spans="1:33" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="155" spans="1:33" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A155" s="9">
         <v>155</v>
       </c>
@@ -24243,7 +24243,7 @@
         <v>609</v>
       </c>
     </row>
-    <row r="156" spans="1:33" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="156" spans="1:33" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A156" s="9">
         <v>156</v>
       </c>
@@ -24344,7 +24344,7 @@
         <v>609</v>
       </c>
     </row>
-    <row r="157" spans="1:33" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="157" spans="1:33" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A157" s="9">
         <v>157</v>
       </c>
@@ -24445,7 +24445,7 @@
         <v>609</v>
       </c>
     </row>
-    <row r="158" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="158" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A158" s="9">
         <v>158</v>
       </c>
@@ -24547,7 +24547,7 @@
         <v>609</v>
       </c>
     </row>
-    <row r="159" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="159" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A159" s="9">
         <v>159</v>
       </c>
@@ -24649,7 +24649,7 @@
         <v>609</v>
       </c>
     </row>
-    <row r="160" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="160" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A160" s="9">
         <v>160</v>
       </c>
@@ -24751,7 +24751,7 @@
         <v>609</v>
       </c>
     </row>
-    <row r="161" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="161" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A161" s="9">
         <v>161</v>
       </c>
@@ -24853,7 +24853,7 @@
         <v>609</v>
       </c>
     </row>
-    <row r="162" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="162" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A162" s="9">
         <v>162</v>
       </c>

--- a/Versão5/ABNT/Ontologia_NBR15965_2N.xlsx
+++ b/Versão5/ABNT/Ontologia_NBR15965_2N.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Construtor_Onto\ABNT\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B2DE84F5-825B-421C-94BE-D311B2C06D93}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2A5A8758-1460-4955-9254-BB1D85C4DB76}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="24240" windowHeight="13290" activeTab="1" xr2:uid="{82C81399-C775-48F3-A336-58DE5F35A6D9}"/>
   </bookViews>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5904" uniqueCount="634">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5932" uniqueCount="635">
   <si>
     <t>Indivíduo</t>
   </si>
@@ -1993,6 +1993,9 @@
   </si>
   <si>
     <t>Defines a Code written in visual programming systems</t>
+  </si>
+  <si>
+    <t>KML</t>
   </si>
 </sst>
 </file>
@@ -2669,233 +2672,7 @@
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
     <cellStyle name="Normal 2" xfId="1" xr:uid="{A0D90F96-026A-4EEB-BDCF-93327D239D7A}"/>
   </cellStyles>
-  <dxfs count="129">
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i/>
-        <strike val="0"/>
-        <color theme="0" tint="-0.499984740745262"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i/>
-        <strike val="0"/>
-        <color theme="0" tint="-0.499984740745262"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i/>
-        <strike val="0"/>
-        <color theme="0" tint="-0.499984740745262"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i/>
-        <strike val="0"/>
-        <color theme="0"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i/>
-        <strike val="0"/>
-        <color theme="0" tint="-0.499984740745262"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i/>
-        <strike val="0"/>
-        <color theme="0" tint="-0.499984740745262"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i/>
-        <strike val="0"/>
-        <color theme="0" tint="-0.499984740745262"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i/>
-        <strike val="0"/>
-        <color theme="0"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i/>
-        <strike val="0"/>
-        <color theme="0" tint="-0.499984740745262"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i/>
-        <strike val="0"/>
-        <color theme="0" tint="-0.499984740745262"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i/>
-        <strike val="0"/>
-        <color theme="0" tint="-0.499984740745262"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i/>
-        <strike val="0"/>
-        <color theme="0"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i/>
-        <strike val="0"/>
-        <color theme="0" tint="-0.499984740745262"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i/>
-        <strike val="0"/>
-        <color theme="0" tint="-0.499984740745262"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i/>
-        <strike val="0"/>
-        <color theme="0"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i/>
-        <strike val="0"/>
-        <color theme="0" tint="-0.499984740745262"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i/>
-        <strike val="0"/>
-        <color theme="0" tint="-0.499984740745262"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i/>
-        <strike val="0"/>
-        <color theme="0"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i/>
-        <strike val="0"/>
-        <color theme="0" tint="-0.499984740745262"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i/>
-        <strike val="0"/>
-        <color theme="0" tint="-0.499984740745262"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i/>
-        <strike val="0"/>
-        <color theme="0" tint="-0.499984740745262"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i/>
-        <strike val="0"/>
-        <color theme="0" tint="-0.499984740745262"/>
-      </font>
-    </dxf>
+  <dxfs count="103">
     <dxf>
       <font>
         <b val="0"/>
@@ -3154,6 +2931,14 @@
           <bgColor rgb="FFFFC7CE"/>
         </patternFill>
       </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i/>
+        <strike val="0"/>
+        <color theme="0" tint="-0.499984740745262"/>
+      </font>
     </dxf>
     <dxf>
       <font>
@@ -5433,41 +5218,41 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{A07C259E-03F8-41A3-821C-289758C0BF1B}" name="Tabla2" displayName="Tabla2" ref="A2:AG162" headerRowCount="0" totalsRowShown="0" headerRowDxfId="128" dataDxfId="126" headerRowBorderDxfId="127" tableBorderDxfId="125" totalsRowBorderDxfId="124">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{A07C259E-03F8-41A3-821C-289758C0BF1B}" name="Tabla2" displayName="Tabla2" ref="A2:AG162" headerRowCount="0" totalsRowShown="0" headerRowDxfId="102" dataDxfId="100" headerRowBorderDxfId="101" tableBorderDxfId="99" totalsRowBorderDxfId="98">
   <tableColumns count="33">
-    <tableColumn id="1" xr3:uid="{D841A366-4823-4EF9-B009-219AA94AF50A}" name="1" headerRowDxfId="123" dataDxfId="122"/>
-    <tableColumn id="2" xr3:uid="{41E717E1-E3DE-44C1-91C4-719DAB59A464}" name="Indivíduo" headerRowDxfId="121" dataDxfId="120"/>
-    <tableColumn id="3" xr3:uid="{38346B1D-47C6-4B44-A19C-766D16435669}" name="Classe" headerRowDxfId="119" dataDxfId="118"/>
-    <tableColumn id="5" xr3:uid="{27FF4C79-5131-4593-84DE-98F435DB6954}" name="Coluna2" headerRowDxfId="117" dataDxfId="116"/>
-    <tableColumn id="4" xr3:uid="{B4C1140F-50EB-4951-8734-6338EB3CF628}" name="Coluna1" headerRowDxfId="115" dataDxfId="114"/>
-    <tableColumn id="11" xr3:uid="{1EE4C35C-9E89-4C7C-8F68-2AC866434D95}" name="Coluna8" headerRowDxfId="113" dataDxfId="112"/>
-    <tableColumn id="10" xr3:uid="{0C28831F-E05A-4812-BB49-6E3DB059FDDA}" name="Coluna7" headerRowDxfId="111" dataDxfId="110"/>
-    <tableColumn id="9" xr3:uid="{C46F6396-5D54-4379-8FE7-47754ED408FB}" name="Coluna6" headerRowDxfId="109" dataDxfId="108"/>
-    <tableColumn id="14" xr3:uid="{7255F88A-C196-4C7D-BC78-487E43C6076E}" name="Coluna9" headerRowDxfId="107" dataDxfId="106"/>
-    <tableColumn id="15" xr3:uid="{CB39996D-E39C-41DF-9024-09188503F3A9}" name="Coluna10" headerRowDxfId="105" dataDxfId="104"/>
-    <tableColumn id="8" xr3:uid="{DC6BCDF7-14DD-4B0D-951F-937897AADF11}" name="Coluna5" headerRowDxfId="103" dataDxfId="102"/>
-    <tableColumn id="25" xr3:uid="{6E36A2EC-C3DA-4DF1-80AB-262ECBFDA8D3}" name="Coluna20" headerRowDxfId="101" dataDxfId="100"/>
-    <tableColumn id="24" xr3:uid="{7DA1B28C-8D87-49B1-8B12-94BDA4E3634B}" name="Coluna19" headerRowDxfId="99" dataDxfId="98"/>
-    <tableColumn id="12" xr3:uid="{72731FBF-D3F4-42FD-AF7E-09CD79716DE3}" name="Fato (11)" headerRowDxfId="97" dataDxfId="96"/>
-    <tableColumn id="13" xr3:uid="{40ED8FBD-39D6-4C0F-867B-9AA8C9C09316}" name="Valor8" headerRowDxfId="95" dataDxfId="94"/>
-    <tableColumn id="6" xr3:uid="{D7E37E62-C3F1-48D0-9ECE-1603C43E1947}" name="Coluna3" headerRowDxfId="93" dataDxfId="92"/>
-    <tableColumn id="7" xr3:uid="{8EAEA0F2-9F55-4FEE-86F2-D1912AEFC7F4}" name="Coluna4" headerRowDxfId="91" dataDxfId="90"/>
-    <tableColumn id="16" xr3:uid="{CB767617-3A28-42EC-8E47-CE6204F6D856}" name="Coluna11" headerRowDxfId="89" dataDxfId="88"/>
-    <tableColumn id="17" xr3:uid="{E29ADF84-36FF-41F7-9847-17BC340BAE5F}" name="Coluna12" headerRowDxfId="87" dataDxfId="86"/>
-    <tableColumn id="18" xr3:uid="{B5ADD4A7-EE28-45D9-B6FF-C285C2CD6E37}" name="Coluna13" headerRowDxfId="85" dataDxfId="84"/>
-    <tableColumn id="19" xr3:uid="{7FEDF53D-D312-4CF1-8EB3-4A56B77DEAA1}" name="Coluna14" headerRowDxfId="83" dataDxfId="82"/>
-    <tableColumn id="20" xr3:uid="{44C51568-5619-4D1B-B5B4-F2CF79CAB094}" name="Coluna15" headerRowDxfId="81" dataDxfId="80"/>
-    <tableColumn id="21" xr3:uid="{2A7C2A78-BAF9-429F-B898-EF931D80D830}" name="Coluna16" headerRowDxfId="79" dataDxfId="78"/>
-    <tableColumn id="22" xr3:uid="{3BB87186-A8C3-4EE2-9555-ACB7C40B9882}" name="Coluna17" headerRowDxfId="77" dataDxfId="76"/>
-    <tableColumn id="23" xr3:uid="{C574DFC8-E441-4BB1-A97D-83D5A9C08508}" name="Coluna18" headerRowDxfId="75" dataDxfId="74"/>
-    <tableColumn id="26" xr3:uid="{28A75A21-9AEA-4450-8DD2-5FEB86E3D1BF}" name="Coluna21" headerRowDxfId="73" dataDxfId="72"/>
-    <tableColumn id="27" xr3:uid="{9A2D685F-22A0-4828-9E11-08F2267BE681}" name="Coluna22" headerRowDxfId="71" dataDxfId="70"/>
-    <tableColumn id="28" xr3:uid="{4A34D3E2-5187-4876-A257-7428FBB430CA}" name="Coluna23" headerRowDxfId="69" dataDxfId="68"/>
-    <tableColumn id="29" xr3:uid="{F0F265E4-3C4A-45DA-9BD0-B6223C3A5AF7}" name="Coluna24" headerRowDxfId="67" dataDxfId="66"/>
-    <tableColumn id="30" xr3:uid="{F4245AB0-585B-463B-BDE4-2C1B32093872}" name="Coluna25" headerRowDxfId="65" dataDxfId="64"/>
-    <tableColumn id="31" xr3:uid="{78D68B95-AF87-4681-A542-69147C523764}" name="Coluna26" headerRowDxfId="63" dataDxfId="62"/>
-    <tableColumn id="32" xr3:uid="{60FB0CF7-F304-410C-A14D-436E194DA0BF}" name="Coluna27" headerRowDxfId="61" dataDxfId="60"/>
-    <tableColumn id="33" xr3:uid="{29FD05D0-59E6-4A8E-892C-3A07058F43BE}" name="Coluna28" headerRowDxfId="59" dataDxfId="58"/>
+    <tableColumn id="1" xr3:uid="{D841A366-4823-4EF9-B009-219AA94AF50A}" name="1" headerRowDxfId="97" dataDxfId="96"/>
+    <tableColumn id="2" xr3:uid="{41E717E1-E3DE-44C1-91C4-719DAB59A464}" name="Indivíduo" headerRowDxfId="95" dataDxfId="94"/>
+    <tableColumn id="3" xr3:uid="{38346B1D-47C6-4B44-A19C-766D16435669}" name="Classe" headerRowDxfId="93" dataDxfId="92"/>
+    <tableColumn id="5" xr3:uid="{27FF4C79-5131-4593-84DE-98F435DB6954}" name="Coluna2" headerRowDxfId="91" dataDxfId="90"/>
+    <tableColumn id="4" xr3:uid="{B4C1140F-50EB-4951-8734-6338EB3CF628}" name="Coluna1" headerRowDxfId="89" dataDxfId="88"/>
+    <tableColumn id="11" xr3:uid="{1EE4C35C-9E89-4C7C-8F68-2AC866434D95}" name="Coluna8" headerRowDxfId="87" dataDxfId="86"/>
+    <tableColumn id="10" xr3:uid="{0C28831F-E05A-4812-BB49-6E3DB059FDDA}" name="Coluna7" headerRowDxfId="85" dataDxfId="84"/>
+    <tableColumn id="9" xr3:uid="{C46F6396-5D54-4379-8FE7-47754ED408FB}" name="Coluna6" headerRowDxfId="83" dataDxfId="82"/>
+    <tableColumn id="14" xr3:uid="{7255F88A-C196-4C7D-BC78-487E43C6076E}" name="Coluna9" headerRowDxfId="81" dataDxfId="80"/>
+    <tableColumn id="15" xr3:uid="{CB39996D-E39C-41DF-9024-09188503F3A9}" name="Coluna10" headerRowDxfId="79" dataDxfId="78"/>
+    <tableColumn id="8" xr3:uid="{DC6BCDF7-14DD-4B0D-951F-937897AADF11}" name="Coluna5" headerRowDxfId="77" dataDxfId="76"/>
+    <tableColumn id="25" xr3:uid="{6E36A2EC-C3DA-4DF1-80AB-262ECBFDA8D3}" name="Coluna20" headerRowDxfId="75" dataDxfId="74"/>
+    <tableColumn id="24" xr3:uid="{7DA1B28C-8D87-49B1-8B12-94BDA4E3634B}" name="Coluna19" headerRowDxfId="73" dataDxfId="72"/>
+    <tableColumn id="12" xr3:uid="{72731FBF-D3F4-42FD-AF7E-09CD79716DE3}" name="Fato (11)" headerRowDxfId="71" dataDxfId="70"/>
+    <tableColumn id="13" xr3:uid="{40ED8FBD-39D6-4C0F-867B-9AA8C9C09316}" name="Valor8" headerRowDxfId="69" dataDxfId="68"/>
+    <tableColumn id="6" xr3:uid="{D7E37E62-C3F1-48D0-9ECE-1603C43E1947}" name="Coluna3" headerRowDxfId="67" dataDxfId="66"/>
+    <tableColumn id="7" xr3:uid="{8EAEA0F2-9F55-4FEE-86F2-D1912AEFC7F4}" name="Coluna4" headerRowDxfId="65" dataDxfId="64"/>
+    <tableColumn id="16" xr3:uid="{CB767617-3A28-42EC-8E47-CE6204F6D856}" name="Coluna11" headerRowDxfId="63" dataDxfId="62"/>
+    <tableColumn id="17" xr3:uid="{E29ADF84-36FF-41F7-9847-17BC340BAE5F}" name="Coluna12" headerRowDxfId="61" dataDxfId="60"/>
+    <tableColumn id="18" xr3:uid="{B5ADD4A7-EE28-45D9-B6FF-C285C2CD6E37}" name="Coluna13" headerRowDxfId="59" dataDxfId="58"/>
+    <tableColumn id="19" xr3:uid="{7FEDF53D-D312-4CF1-8EB3-4A56B77DEAA1}" name="Coluna14" headerRowDxfId="57" dataDxfId="56"/>
+    <tableColumn id="20" xr3:uid="{44C51568-5619-4D1B-B5B4-F2CF79CAB094}" name="Coluna15" headerRowDxfId="55" dataDxfId="54"/>
+    <tableColumn id="21" xr3:uid="{2A7C2A78-BAF9-429F-B898-EF931D80D830}" name="Coluna16" headerRowDxfId="53" dataDxfId="52"/>
+    <tableColumn id="22" xr3:uid="{3BB87186-A8C3-4EE2-9555-ACB7C40B9882}" name="Coluna17" headerRowDxfId="51" dataDxfId="50"/>
+    <tableColumn id="23" xr3:uid="{C574DFC8-E441-4BB1-A97D-83D5A9C08508}" name="Coluna18" headerRowDxfId="49" dataDxfId="48"/>
+    <tableColumn id="26" xr3:uid="{28A75A21-9AEA-4450-8DD2-5FEB86E3D1BF}" name="Coluna21" headerRowDxfId="47" dataDxfId="46"/>
+    <tableColumn id="27" xr3:uid="{9A2D685F-22A0-4828-9E11-08F2267BE681}" name="Coluna22" headerRowDxfId="45" dataDxfId="44"/>
+    <tableColumn id="28" xr3:uid="{4A34D3E2-5187-4876-A257-7428FBB430CA}" name="Coluna23" headerRowDxfId="43" dataDxfId="42"/>
+    <tableColumn id="29" xr3:uid="{F0F265E4-3C4A-45DA-9BD0-B6223C3A5AF7}" name="Coluna24" headerRowDxfId="41" dataDxfId="40"/>
+    <tableColumn id="30" xr3:uid="{F4245AB0-585B-463B-BDE4-2C1B32093872}" name="Coluna25" headerRowDxfId="39" dataDxfId="38"/>
+    <tableColumn id="31" xr3:uid="{78D68B95-AF87-4681-A542-69147C523764}" name="Coluna26" headerRowDxfId="37" dataDxfId="36"/>
+    <tableColumn id="32" xr3:uid="{60FB0CF7-F304-410C-A14D-436E194DA0BF}" name="Coluna27" headerRowDxfId="35" dataDxfId="34"/>
+    <tableColumn id="33" xr3:uid="{29FD05D0-59E6-4A8E-892C-3A07058F43BE}" name="Coluna28" headerRowDxfId="33" dataDxfId="32"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="0" showColumnStripes="0"/>
 </table>
@@ -5995,7 +5780,7 @@
       </c>
       <c r="B18" s="5">
         <f ca="1">NOW()</f>
-        <v>46268.463744560184</v>
+        <v>46268.686271990744</v>
       </c>
       <c r="C18" s="42" t="s">
         <v>404</v>
@@ -6249,7 +6034,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{958751C2-A34E-4345-8D6A-082603A025F9}">
   <sheetPr codeName="Planilha2"/>
-  <dimension ref="A1:AC28"/>
+  <dimension ref="A1:AD28"/>
   <sheetFormatPr defaultRowHeight="7.5" customHeight="1" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="2.83203125" bestFit="1" customWidth="1"/>
@@ -6277,9 +6062,10 @@
     <col min="27" max="27" width="44.83203125" bestFit="1" customWidth="1"/>
     <col min="28" max="28" width="8.83203125" bestFit="1" customWidth="1"/>
     <col min="29" max="29" width="8.6640625" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="8.83203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:29" ht="37.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:30" ht="37.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="22" t="s">
         <v>349</v>
       </c>
@@ -6367,8 +6153,11 @@
       <c r="AC1" s="24" t="s">
         <v>372</v>
       </c>
+      <c r="AD1" s="24" t="s">
+        <v>634</v>
+      </c>
     </row>
-    <row r="2" spans="1:29" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:30" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="49">
         <v>2</v>
       </c>
@@ -6464,8 +6253,11 @@
       <c r="AC2" s="38" t="s">
         <v>420</v>
       </c>
+      <c r="AD2" s="70" t="s">
+        <v>181</v>
+      </c>
     </row>
-    <row r="3" spans="1:29" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:30" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="49">
         <v>3</v>
       </c>
@@ -6561,8 +6353,11 @@
       <c r="AC3" s="38" t="s">
         <v>421</v>
       </c>
+      <c r="AD3" s="70" t="s">
+        <v>181</v>
+      </c>
     </row>
-    <row r="4" spans="1:29" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:30" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="49">
         <v>4</v>
       </c>
@@ -6658,8 +6453,11 @@
       <c r="AC4" s="38" t="s">
         <v>422</v>
       </c>
+      <c r="AD4" s="70" t="s">
+        <v>181</v>
+      </c>
     </row>
-    <row r="5" spans="1:29" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:30" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="49">
         <v>5</v>
       </c>
@@ -6755,8 +6553,11 @@
       <c r="AC5" s="38" t="s">
         <v>423</v>
       </c>
+      <c r="AD5" s="70" t="s">
+        <v>181</v>
+      </c>
     </row>
-    <row r="6" spans="1:29" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:30" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A6" s="49">
         <v>6</v>
       </c>
@@ -6852,8 +6653,11 @@
       <c r="AC6" s="38" t="s">
         <v>424</v>
       </c>
+      <c r="AD6" s="70" t="s">
+        <v>181</v>
+      </c>
     </row>
-    <row r="7" spans="1:29" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:30" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A7" s="49">
         <v>7</v>
       </c>
@@ -6949,8 +6753,11 @@
       <c r="AC7" s="38" t="s">
         <v>425</v>
       </c>
+      <c r="AD7" s="70" t="s">
+        <v>181</v>
+      </c>
     </row>
-    <row r="8" spans="1:29" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:30" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" s="49">
         <v>8</v>
       </c>
@@ -7046,8 +6853,11 @@
       <c r="AC8" s="38" t="s">
         <v>342</v>
       </c>
+      <c r="AD8" s="70" t="s">
+        <v>181</v>
+      </c>
     </row>
-    <row r="9" spans="1:29" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:30" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A9" s="49">
         <v>9</v>
       </c>
@@ -7143,8 +6953,11 @@
       <c r="AC9" s="38" t="s">
         <v>426</v>
       </c>
+      <c r="AD9" s="70" t="s">
+        <v>181</v>
+      </c>
     </row>
-    <row r="10" spans="1:29" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:30" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A10" s="49">
         <v>10</v>
       </c>
@@ -7240,8 +7053,11 @@
       <c r="AC10" s="38" t="s">
         <v>427</v>
       </c>
+      <c r="AD10" s="70" t="s">
+        <v>181</v>
+      </c>
     </row>
-    <row r="11" spans="1:29" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:30" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A11" s="49">
         <v>11</v>
       </c>
@@ -7337,8 +7153,11 @@
       <c r="AC11" s="38" t="s">
         <v>428</v>
       </c>
+      <c r="AD11" s="70" t="s">
+        <v>181</v>
+      </c>
     </row>
-    <row r="12" spans="1:29" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:30" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A12" s="49">
         <v>12</v>
       </c>
@@ -7434,8 +7253,11 @@
       <c r="AC12" s="38" t="s">
         <v>429</v>
       </c>
+      <c r="AD12" s="70" t="s">
+        <v>181</v>
+      </c>
     </row>
-    <row r="13" spans="1:29" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:30" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A13" s="49">
         <v>13</v>
       </c>
@@ -7531,8 +7353,11 @@
       <c r="AC13" s="38" t="s">
         <v>430</v>
       </c>
+      <c r="AD13" s="70" t="s">
+        <v>181</v>
+      </c>
     </row>
-    <row r="14" spans="1:29" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:30" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A14" s="49">
         <v>14</v>
       </c>
@@ -7628,8 +7453,11 @@
       <c r="AC14" s="38" t="s">
         <v>431</v>
       </c>
+      <c r="AD14" s="70" t="s">
+        <v>181</v>
+      </c>
     </row>
-    <row r="15" spans="1:29" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:30" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A15" s="49">
         <v>15</v>
       </c>
@@ -7725,8 +7553,11 @@
       <c r="AC15" s="53" t="s">
         <v>477</v>
       </c>
+      <c r="AD15" s="70" t="s">
+        <v>181</v>
+      </c>
     </row>
-    <row r="16" spans="1:29" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:30" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A16" s="49">
         <v>16</v>
       </c>
@@ -7822,8 +7653,11 @@
       <c r="AC16" s="53" t="s">
         <v>478</v>
       </c>
+      <c r="AD16" s="70" t="s">
+        <v>181</v>
+      </c>
     </row>
-    <row r="17" spans="1:29" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:30" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A17" s="49">
         <v>17</v>
       </c>
@@ -7919,8 +7753,11 @@
       <c r="AC17" s="53" t="s">
         <v>479</v>
       </c>
+      <c r="AD17" s="70" t="s">
+        <v>181</v>
+      </c>
     </row>
-    <row r="18" spans="1:29" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:30" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A18" s="49">
         <v>18</v>
       </c>
@@ -8016,8 +7853,11 @@
       <c r="AC18" s="53" t="s">
         <v>480</v>
       </c>
+      <c r="AD18" s="70" t="s">
+        <v>181</v>
+      </c>
     </row>
-    <row r="19" spans="1:29" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:30" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A19" s="49">
         <v>19</v>
       </c>
@@ -8113,8 +7953,11 @@
       <c r="AC19" s="53" t="s">
         <v>481</v>
       </c>
+      <c r="AD19" s="70" t="s">
+        <v>181</v>
+      </c>
     </row>
-    <row r="20" spans="1:29" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:30" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A20" s="49">
         <v>20</v>
       </c>
@@ -8210,8 +8053,11 @@
       <c r="AC20" s="53" t="s">
         <v>482</v>
       </c>
+      <c r="AD20" s="70" t="s">
+        <v>181</v>
+      </c>
     </row>
-    <row r="21" spans="1:29" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:30" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A21" s="49">
         <v>21</v>
       </c>
@@ -8307,8 +8153,11 @@
       <c r="AC21" s="53" t="s">
         <v>483</v>
       </c>
+      <c r="AD21" s="70" t="s">
+        <v>181</v>
+      </c>
     </row>
-    <row r="22" spans="1:29" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:30" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A22" s="49">
         <v>22</v>
       </c>
@@ -8404,8 +8253,11 @@
       <c r="AC22" s="53" t="s">
         <v>484</v>
       </c>
+      <c r="AD22" s="70" t="s">
+        <v>181</v>
+      </c>
     </row>
-    <row r="23" spans="1:29" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:30" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A23" s="49">
         <v>23</v>
       </c>
@@ -8501,8 +8353,11 @@
       <c r="AC23" s="53" t="s">
         <v>485</v>
       </c>
+      <c r="AD23" s="70" t="s">
+        <v>181</v>
+      </c>
     </row>
-    <row r="24" spans="1:29" s="48" customFormat="1" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:30" s="48" customFormat="1" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A24" s="49">
         <v>24</v>
       </c>
@@ -8598,8 +8453,11 @@
       <c r="AC24" s="70" t="s">
         <v>181</v>
       </c>
+      <c r="AD24" s="70" t="s">
+        <v>181</v>
+      </c>
     </row>
-    <row r="25" spans="1:29" s="48" customFormat="1" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:30" s="48" customFormat="1" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A25" s="49">
         <v>25</v>
       </c>
@@ -8695,8 +8553,11 @@
       <c r="AC25" s="70" t="s">
         <v>181</v>
       </c>
+      <c r="AD25" s="70" t="s">
+        <v>181</v>
+      </c>
     </row>
-    <row r="26" spans="1:29" s="48" customFormat="1" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:30" s="48" customFormat="1" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A26" s="49">
         <v>26</v>
       </c>
@@ -8792,8 +8653,11 @@
       <c r="AC26" s="70" t="s">
         <v>181</v>
       </c>
+      <c r="AD26" s="70" t="s">
+        <v>181</v>
+      </c>
     </row>
-    <row r="27" spans="1:29" s="48" customFormat="1" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:30" s="48" customFormat="1" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A27" s="49">
         <v>27</v>
       </c>
@@ -8889,8 +8753,11 @@
       <c r="AC27" s="70" t="s">
         <v>181</v>
       </c>
+      <c r="AD27" s="70" t="s">
+        <v>181</v>
+      </c>
     </row>
-    <row r="28" spans="1:29" s="48" customFormat="1" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:30" s="48" customFormat="1" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A28" s="49">
         <v>28</v>
       </c>
@@ -8986,29 +8853,32 @@
       <c r="AC28" s="70" t="s">
         <v>181</v>
       </c>
+      <c r="AD28" s="70" t="s">
+        <v>181</v>
+      </c>
     </row>
   </sheetData>
   <conditionalFormatting sqref="A2:B28">
-    <cfRule type="cellIs" dxfId="26" priority="1" operator="equal">
+    <cfRule type="cellIs" dxfId="31" priority="1" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E28:F28">
-    <cfRule type="duplicateValues" dxfId="57" priority="2"/>
+    <cfRule type="duplicateValues" dxfId="30" priority="2"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F2:F14">
-    <cfRule type="duplicateValues" dxfId="56" priority="16"/>
+    <cfRule type="duplicateValues" dxfId="29" priority="16"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F24:F27">
-    <cfRule type="duplicateValues" dxfId="55" priority="7"/>
+    <cfRule type="duplicateValues" dxfId="28" priority="7"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="R1:R23">
-    <cfRule type="cellIs" dxfId="54" priority="8" operator="equal">
+    <cfRule type="cellIs" dxfId="27" priority="8" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="Y2 AA2">
-    <cfRule type="cellIs" dxfId="53" priority="13" operator="equal">
+    <cfRule type="cellIs" dxfId="26" priority="13" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -9161,7 +9031,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:U2">
-    <cfRule type="cellIs" dxfId="52" priority="1" operator="equal">
+    <cfRule type="cellIs" dxfId="25" priority="1" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -9206,7 +9076,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:A2">
-    <cfRule type="cellIs" dxfId="51" priority="1" operator="equal">
+    <cfRule type="cellIs" dxfId="24" priority="1" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -25622,114 +25492,114 @@
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>
   <conditionalFormatting sqref="B1:B157 B163:B1048576">
-    <cfRule type="duplicateValues" dxfId="50" priority="29"/>
+    <cfRule type="duplicateValues" dxfId="23" priority="29"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B158:B162">
-    <cfRule type="duplicateValues" dxfId="49" priority="27"/>
-    <cfRule type="duplicateValues" dxfId="48" priority="28"/>
+    <cfRule type="duplicateValues" dxfId="22" priority="27"/>
+    <cfRule type="duplicateValues" dxfId="21" priority="28"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="R158:W162">
-    <cfRule type="cellIs" dxfId="47" priority="26" operator="equal">
+    <cfRule type="cellIs" dxfId="20" priority="26" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="T1:W157">
-    <cfRule type="cellIs" dxfId="46" priority="30" operator="equal">
+    <cfRule type="cellIs" dxfId="19" priority="30" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="T163:Z1048576">
-    <cfRule type="cellIs" dxfId="45" priority="13" operator="equal">
+    <cfRule type="cellIs" dxfId="18" priority="13" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="X1">
-    <cfRule type="cellIs" dxfId="44" priority="25" operator="equal">
+    <cfRule type="cellIs" dxfId="17" priority="25" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="X2:Y162">
-    <cfRule type="cellIs" dxfId="43" priority="18" operator="equal">
+    <cfRule type="cellIs" dxfId="16" priority="18" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="X1:AG1">
-    <cfRule type="cellIs" dxfId="42" priority="20" operator="equal">
+    <cfRule type="cellIs" dxfId="15" priority="20" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="Z1">
-    <cfRule type="cellIs" dxfId="41" priority="12" operator="equal">
+    <cfRule type="cellIs" dxfId="14" priority="12" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="Z2:Z162">
-    <cfRule type="cellIs" dxfId="40" priority="11" operator="equal">
+    <cfRule type="cellIs" dxfId="13" priority="11" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AA2:AA162">
-    <cfRule type="cellIs" dxfId="39" priority="17" operator="equal">
+    <cfRule type="cellIs" dxfId="12" priority="17" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AB1">
-    <cfRule type="cellIs" dxfId="38" priority="9" operator="equal">
+    <cfRule type="cellIs" dxfId="11" priority="9" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AB2:AB162">
-    <cfRule type="cellIs" dxfId="37" priority="8" operator="equal">
+    <cfRule type="cellIs" dxfId="10" priority="8" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AB163:AB1048576">
-    <cfRule type="cellIs" dxfId="36" priority="10" operator="equal">
+    <cfRule type="cellIs" dxfId="9" priority="10" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AC2:AC162">
-    <cfRule type="cellIs" dxfId="35" priority="16" operator="equal">
+    <cfRule type="cellIs" dxfId="8" priority="16" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AD1">
-    <cfRule type="cellIs" dxfId="34" priority="6" operator="equal">
+    <cfRule type="cellIs" dxfId="7" priority="6" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AD2:AD162">
-    <cfRule type="cellIs" dxfId="33" priority="5" operator="equal">
+    <cfRule type="cellIs" dxfId="6" priority="5" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AD163:AD1048576">
-    <cfRule type="cellIs" dxfId="32" priority="7" operator="equal">
+    <cfRule type="cellIs" dxfId="5" priority="7" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AE2:AE162">
-    <cfRule type="cellIs" dxfId="31" priority="15" operator="equal">
+    <cfRule type="cellIs" dxfId="4" priority="15" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AF1">
-    <cfRule type="cellIs" dxfId="30" priority="3" operator="equal">
+    <cfRule type="cellIs" dxfId="3" priority="3" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AF2:AF162">
-    <cfRule type="cellIs" dxfId="29" priority="2" operator="equal">
+    <cfRule type="cellIs" dxfId="2" priority="2" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AF163:AF1048576">
-    <cfRule type="cellIs" dxfId="28" priority="4" operator="equal">
+    <cfRule type="cellIs" dxfId="1" priority="4" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AG2:AG162">
-    <cfRule type="cellIs" dxfId="27" priority="14" operator="equal">
+    <cfRule type="cellIs" dxfId="0" priority="14" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>

--- a/Versão5/ABNT/Ontologia_NBR15965_2N.xlsx
+++ b/Versão5/ABNT/Ontologia_NBR15965_2N.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Construtor_Onto\ABNT\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2A5A8758-1460-4955-9254-BB1D85C4DB76}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{890768E2-146D-44AC-A209-440582D1E8AA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="24240" windowHeight="13290" activeTab="1" xr2:uid="{82C81399-C775-48F3-A336-58DE5F35A6D9}"/>
   </bookViews>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5932" uniqueCount="635">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5967" uniqueCount="646">
   <si>
     <t>Indivíduo</t>
   </si>
@@ -1854,18 +1854,6 @@
     <t>Atributos Ifc</t>
   </si>
   <si>
-    <t>Projeto</t>
-  </si>
-  <si>
-    <t>De.API</t>
-  </si>
-  <si>
-    <t>Métodos</t>
-  </si>
-  <si>
-    <t>Macros</t>
-  </si>
-  <si>
     <t>API_Ambiente</t>
   </si>
   <si>
@@ -1980,9 +1968,6 @@
     <t>Define a Function to filter objects in an application</t>
   </si>
   <si>
-    <t>Códigos.Visuais</t>
-  </si>
-  <si>
     <t>Bloco.de.Código</t>
   </si>
   <si>
@@ -1996,6 +1981,54 @@
   </si>
   <si>
     <t>KML</t>
+  </si>
+  <si>
+    <t>API</t>
+  </si>
+  <si>
+    <t>API.Plataforma</t>
+  </si>
+  <si>
+    <t>API.Macros</t>
+  </si>
+  <si>
+    <t>API.Método</t>
+  </si>
+  <si>
+    <t>API.Macros.Visuais</t>
+  </si>
+  <si>
+    <t>API.Método.Visual</t>
+  </si>
+  <si>
+    <t>API Método</t>
+  </si>
+  <si>
+    <t>Função Auxiliar</t>
+  </si>
+  <si>
+    <t>API Plataforma</t>
+  </si>
+  <si>
+    <t>API Macros</t>
+  </si>
+  <si>
+    <t>Função Global</t>
+  </si>
+  <si>
+    <t>Função Local</t>
+  </si>
+  <si>
+    <t>Função Filtro</t>
+  </si>
+  <si>
+    <t>API Método Visual</t>
+  </si>
+  <si>
+    <t>Bloco de Código</t>
+  </si>
+  <si>
+    <t>API Macros Visuais</t>
   </si>
 </sst>
 </file>
@@ -2414,7 +2447,7 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="87">
+  <cellXfs count="90">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
@@ -2666,13 +2699,86 @@
     <xf numFmtId="0" fontId="8" fillId="37" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="25" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="Hiperlink" xfId="2" builtinId="8"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
     <cellStyle name="Normal 2" xfId="1" xr:uid="{A0D90F96-026A-4EEB-BDCF-93327D239D7A}"/>
   </cellStyles>
-  <dxfs count="103">
+  <dxfs count="109">
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i/>
+        <strike val="0"/>
+        <color theme="0" tint="-0.499984740745262"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i/>
+        <strike val="0"/>
+        <color theme="0" tint="-0.499984740745262"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i/>
+        <strike val="0"/>
+        <color theme="0" tint="-0.499984740745262"/>
+      </font>
+    </dxf>
     <dxf>
       <font>
         <b val="0"/>
@@ -2931,14 +3037,6 @@
           <bgColor rgb="FFFFC7CE"/>
         </patternFill>
       </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i/>
-        <strike val="0"/>
-        <color theme="0" tint="-0.499984740745262"/>
-      </font>
     </dxf>
     <dxf>
       <font>
@@ -5218,41 +5316,41 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{A07C259E-03F8-41A3-821C-289758C0BF1B}" name="Tabla2" displayName="Tabla2" ref="A2:AG162" headerRowCount="0" totalsRowShown="0" headerRowDxfId="102" dataDxfId="100" headerRowBorderDxfId="101" tableBorderDxfId="99" totalsRowBorderDxfId="98">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{A07C259E-03F8-41A3-821C-289758C0BF1B}" name="Tabla2" displayName="Tabla2" ref="A2:AG162" headerRowCount="0" totalsRowShown="0" headerRowDxfId="108" dataDxfId="106" headerRowBorderDxfId="107" tableBorderDxfId="105" totalsRowBorderDxfId="104">
   <tableColumns count="33">
-    <tableColumn id="1" xr3:uid="{D841A366-4823-4EF9-B009-219AA94AF50A}" name="1" headerRowDxfId="97" dataDxfId="96"/>
-    <tableColumn id="2" xr3:uid="{41E717E1-E3DE-44C1-91C4-719DAB59A464}" name="Indivíduo" headerRowDxfId="95" dataDxfId="94"/>
-    <tableColumn id="3" xr3:uid="{38346B1D-47C6-4B44-A19C-766D16435669}" name="Classe" headerRowDxfId="93" dataDxfId="92"/>
-    <tableColumn id="5" xr3:uid="{27FF4C79-5131-4593-84DE-98F435DB6954}" name="Coluna2" headerRowDxfId="91" dataDxfId="90"/>
-    <tableColumn id="4" xr3:uid="{B4C1140F-50EB-4951-8734-6338EB3CF628}" name="Coluna1" headerRowDxfId="89" dataDxfId="88"/>
-    <tableColumn id="11" xr3:uid="{1EE4C35C-9E89-4C7C-8F68-2AC866434D95}" name="Coluna8" headerRowDxfId="87" dataDxfId="86"/>
-    <tableColumn id="10" xr3:uid="{0C28831F-E05A-4812-BB49-6E3DB059FDDA}" name="Coluna7" headerRowDxfId="85" dataDxfId="84"/>
-    <tableColumn id="9" xr3:uid="{C46F6396-5D54-4379-8FE7-47754ED408FB}" name="Coluna6" headerRowDxfId="83" dataDxfId="82"/>
-    <tableColumn id="14" xr3:uid="{7255F88A-C196-4C7D-BC78-487E43C6076E}" name="Coluna9" headerRowDxfId="81" dataDxfId="80"/>
-    <tableColumn id="15" xr3:uid="{CB39996D-E39C-41DF-9024-09188503F3A9}" name="Coluna10" headerRowDxfId="79" dataDxfId="78"/>
-    <tableColumn id="8" xr3:uid="{DC6BCDF7-14DD-4B0D-951F-937897AADF11}" name="Coluna5" headerRowDxfId="77" dataDxfId="76"/>
-    <tableColumn id="25" xr3:uid="{6E36A2EC-C3DA-4DF1-80AB-262ECBFDA8D3}" name="Coluna20" headerRowDxfId="75" dataDxfId="74"/>
-    <tableColumn id="24" xr3:uid="{7DA1B28C-8D87-49B1-8B12-94BDA4E3634B}" name="Coluna19" headerRowDxfId="73" dataDxfId="72"/>
-    <tableColumn id="12" xr3:uid="{72731FBF-D3F4-42FD-AF7E-09CD79716DE3}" name="Fato (11)" headerRowDxfId="71" dataDxfId="70"/>
-    <tableColumn id="13" xr3:uid="{40ED8FBD-39D6-4C0F-867B-9AA8C9C09316}" name="Valor8" headerRowDxfId="69" dataDxfId="68"/>
-    <tableColumn id="6" xr3:uid="{D7E37E62-C3F1-48D0-9ECE-1603C43E1947}" name="Coluna3" headerRowDxfId="67" dataDxfId="66"/>
-    <tableColumn id="7" xr3:uid="{8EAEA0F2-9F55-4FEE-86F2-D1912AEFC7F4}" name="Coluna4" headerRowDxfId="65" dataDxfId="64"/>
-    <tableColumn id="16" xr3:uid="{CB767617-3A28-42EC-8E47-CE6204F6D856}" name="Coluna11" headerRowDxfId="63" dataDxfId="62"/>
-    <tableColumn id="17" xr3:uid="{E29ADF84-36FF-41F7-9847-17BC340BAE5F}" name="Coluna12" headerRowDxfId="61" dataDxfId="60"/>
-    <tableColumn id="18" xr3:uid="{B5ADD4A7-EE28-45D9-B6FF-C285C2CD6E37}" name="Coluna13" headerRowDxfId="59" dataDxfId="58"/>
-    <tableColumn id="19" xr3:uid="{7FEDF53D-D312-4CF1-8EB3-4A56B77DEAA1}" name="Coluna14" headerRowDxfId="57" dataDxfId="56"/>
-    <tableColumn id="20" xr3:uid="{44C51568-5619-4D1B-B5B4-F2CF79CAB094}" name="Coluna15" headerRowDxfId="55" dataDxfId="54"/>
-    <tableColumn id="21" xr3:uid="{2A7C2A78-BAF9-429F-B898-EF931D80D830}" name="Coluna16" headerRowDxfId="53" dataDxfId="52"/>
-    <tableColumn id="22" xr3:uid="{3BB87186-A8C3-4EE2-9555-ACB7C40B9882}" name="Coluna17" headerRowDxfId="51" dataDxfId="50"/>
-    <tableColumn id="23" xr3:uid="{C574DFC8-E441-4BB1-A97D-83D5A9C08508}" name="Coluna18" headerRowDxfId="49" dataDxfId="48"/>
-    <tableColumn id="26" xr3:uid="{28A75A21-9AEA-4450-8DD2-5FEB86E3D1BF}" name="Coluna21" headerRowDxfId="47" dataDxfId="46"/>
-    <tableColumn id="27" xr3:uid="{9A2D685F-22A0-4828-9E11-08F2267BE681}" name="Coluna22" headerRowDxfId="45" dataDxfId="44"/>
-    <tableColumn id="28" xr3:uid="{4A34D3E2-5187-4876-A257-7428FBB430CA}" name="Coluna23" headerRowDxfId="43" dataDxfId="42"/>
-    <tableColumn id="29" xr3:uid="{F0F265E4-3C4A-45DA-9BD0-B6223C3A5AF7}" name="Coluna24" headerRowDxfId="41" dataDxfId="40"/>
-    <tableColumn id="30" xr3:uid="{F4245AB0-585B-463B-BDE4-2C1B32093872}" name="Coluna25" headerRowDxfId="39" dataDxfId="38"/>
-    <tableColumn id="31" xr3:uid="{78D68B95-AF87-4681-A542-69147C523764}" name="Coluna26" headerRowDxfId="37" dataDxfId="36"/>
-    <tableColumn id="32" xr3:uid="{60FB0CF7-F304-410C-A14D-436E194DA0BF}" name="Coluna27" headerRowDxfId="35" dataDxfId="34"/>
-    <tableColumn id="33" xr3:uid="{29FD05D0-59E6-4A8E-892C-3A07058F43BE}" name="Coluna28" headerRowDxfId="33" dataDxfId="32"/>
+    <tableColumn id="1" xr3:uid="{D841A366-4823-4EF9-B009-219AA94AF50A}" name="1" headerRowDxfId="103" dataDxfId="102"/>
+    <tableColumn id="2" xr3:uid="{41E717E1-E3DE-44C1-91C4-719DAB59A464}" name="Indivíduo" headerRowDxfId="101" dataDxfId="100"/>
+    <tableColumn id="3" xr3:uid="{38346B1D-47C6-4B44-A19C-766D16435669}" name="Classe" headerRowDxfId="99" dataDxfId="98"/>
+    <tableColumn id="5" xr3:uid="{27FF4C79-5131-4593-84DE-98F435DB6954}" name="Coluna2" headerRowDxfId="97" dataDxfId="96"/>
+    <tableColumn id="4" xr3:uid="{B4C1140F-50EB-4951-8734-6338EB3CF628}" name="Coluna1" headerRowDxfId="95" dataDxfId="94"/>
+    <tableColumn id="11" xr3:uid="{1EE4C35C-9E89-4C7C-8F68-2AC866434D95}" name="Coluna8" headerRowDxfId="93" dataDxfId="92"/>
+    <tableColumn id="10" xr3:uid="{0C28831F-E05A-4812-BB49-6E3DB059FDDA}" name="Coluna7" headerRowDxfId="91" dataDxfId="90"/>
+    <tableColumn id="9" xr3:uid="{C46F6396-5D54-4379-8FE7-47754ED408FB}" name="Coluna6" headerRowDxfId="89" dataDxfId="88"/>
+    <tableColumn id="14" xr3:uid="{7255F88A-C196-4C7D-BC78-487E43C6076E}" name="Coluna9" headerRowDxfId="87" dataDxfId="86"/>
+    <tableColumn id="15" xr3:uid="{CB39996D-E39C-41DF-9024-09188503F3A9}" name="Coluna10" headerRowDxfId="85" dataDxfId="84"/>
+    <tableColumn id="8" xr3:uid="{DC6BCDF7-14DD-4B0D-951F-937897AADF11}" name="Coluna5" headerRowDxfId="83" dataDxfId="82"/>
+    <tableColumn id="25" xr3:uid="{6E36A2EC-C3DA-4DF1-80AB-262ECBFDA8D3}" name="Coluna20" headerRowDxfId="81" dataDxfId="80"/>
+    <tableColumn id="24" xr3:uid="{7DA1B28C-8D87-49B1-8B12-94BDA4E3634B}" name="Coluna19" headerRowDxfId="79" dataDxfId="78"/>
+    <tableColumn id="12" xr3:uid="{72731FBF-D3F4-42FD-AF7E-09CD79716DE3}" name="Fato (11)" headerRowDxfId="77" dataDxfId="76"/>
+    <tableColumn id="13" xr3:uid="{40ED8FBD-39D6-4C0F-867B-9AA8C9C09316}" name="Valor8" headerRowDxfId="75" dataDxfId="74"/>
+    <tableColumn id="6" xr3:uid="{D7E37E62-C3F1-48D0-9ECE-1603C43E1947}" name="Coluna3" headerRowDxfId="73" dataDxfId="72"/>
+    <tableColumn id="7" xr3:uid="{8EAEA0F2-9F55-4FEE-86F2-D1912AEFC7F4}" name="Coluna4" headerRowDxfId="71" dataDxfId="70"/>
+    <tableColumn id="16" xr3:uid="{CB767617-3A28-42EC-8E47-CE6204F6D856}" name="Coluna11" headerRowDxfId="69" dataDxfId="68"/>
+    <tableColumn id="17" xr3:uid="{E29ADF84-36FF-41F7-9847-17BC340BAE5F}" name="Coluna12" headerRowDxfId="67" dataDxfId="66"/>
+    <tableColumn id="18" xr3:uid="{B5ADD4A7-EE28-45D9-B6FF-C285C2CD6E37}" name="Coluna13" headerRowDxfId="65" dataDxfId="64"/>
+    <tableColumn id="19" xr3:uid="{7FEDF53D-D312-4CF1-8EB3-4A56B77DEAA1}" name="Coluna14" headerRowDxfId="63" dataDxfId="62"/>
+    <tableColumn id="20" xr3:uid="{44C51568-5619-4D1B-B5B4-F2CF79CAB094}" name="Coluna15" headerRowDxfId="61" dataDxfId="60"/>
+    <tableColumn id="21" xr3:uid="{2A7C2A78-BAF9-429F-B898-EF931D80D830}" name="Coluna16" headerRowDxfId="59" dataDxfId="58"/>
+    <tableColumn id="22" xr3:uid="{3BB87186-A8C3-4EE2-9555-ACB7C40B9882}" name="Coluna17" headerRowDxfId="57" dataDxfId="56"/>
+    <tableColumn id="23" xr3:uid="{C574DFC8-E441-4BB1-A97D-83D5A9C08508}" name="Coluna18" headerRowDxfId="55" dataDxfId="54"/>
+    <tableColumn id="26" xr3:uid="{28A75A21-9AEA-4450-8DD2-5FEB86E3D1BF}" name="Coluna21" headerRowDxfId="53" dataDxfId="52"/>
+    <tableColumn id="27" xr3:uid="{9A2D685F-22A0-4828-9E11-08F2267BE681}" name="Coluna22" headerRowDxfId="51" dataDxfId="50"/>
+    <tableColumn id="28" xr3:uid="{4A34D3E2-5187-4876-A257-7428FBB430CA}" name="Coluna23" headerRowDxfId="49" dataDxfId="48"/>
+    <tableColumn id="29" xr3:uid="{F0F265E4-3C4A-45DA-9BD0-B6223C3A5AF7}" name="Coluna24" headerRowDxfId="47" dataDxfId="46"/>
+    <tableColumn id="30" xr3:uid="{F4245AB0-585B-463B-BDE4-2C1B32093872}" name="Coluna25" headerRowDxfId="45" dataDxfId="44"/>
+    <tableColumn id="31" xr3:uid="{78D68B95-AF87-4681-A542-69147C523764}" name="Coluna26" headerRowDxfId="43" dataDxfId="42"/>
+    <tableColumn id="32" xr3:uid="{60FB0CF7-F304-410C-A14D-436E194DA0BF}" name="Coluna27" headerRowDxfId="41" dataDxfId="40"/>
+    <tableColumn id="33" xr3:uid="{29FD05D0-59E6-4A8E-892C-3A07058F43BE}" name="Coluna28" headerRowDxfId="39" dataDxfId="38"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="0" showColumnStripes="0"/>
 </table>
@@ -5780,7 +5878,7 @@
       </c>
       <c r="B18" s="5">
         <f ca="1">NOW()</f>
-        <v>46268.686271990744</v>
+        <v>46273.464248379627</v>
       </c>
       <c r="C18" s="42" t="s">
         <v>404</v>
@@ -6051,7 +6149,7 @@
     <col min="16" max="16" width="78.1640625" bestFit="1" customWidth="1"/>
     <col min="17" max="17" width="80.5" bestFit="1" customWidth="1"/>
     <col min="18" max="18" width="71.6640625" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="5" style="34" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="5" style="89" bestFit="1" customWidth="1"/>
     <col min="20" max="20" width="8.1640625" bestFit="1" customWidth="1"/>
     <col min="21" max="21" width="10.5" bestFit="1" customWidth="1"/>
     <col min="22" max="22" width="11.1640625" bestFit="1" customWidth="1"/>
@@ -6120,7 +6218,7 @@
       <c r="R1" s="37" t="s">
         <v>399</v>
       </c>
-      <c r="S1" s="24" t="s">
+      <c r="S1" s="25" t="s">
         <v>393</v>
       </c>
       <c r="T1" s="24" t="s">
@@ -6154,7 +6252,7 @@
         <v>372</v>
       </c>
       <c r="AD1" s="24" t="s">
-        <v>634</v>
+        <v>629</v>
       </c>
     </row>
     <row r="2" spans="1:30" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
@@ -6216,7 +6314,7 @@
       <c r="R2" s="53" t="s">
         <v>490</v>
       </c>
-      <c r="S2" s="38" t="s">
+      <c r="S2" s="87" t="s">
         <v>181</v>
       </c>
       <c r="T2" s="52" t="str">
@@ -6316,7 +6414,7 @@
       <c r="R3" s="53" t="s">
         <v>493</v>
       </c>
-      <c r="S3" s="38" t="s">
+      <c r="S3" s="87" t="s">
         <v>181</v>
       </c>
       <c r="T3" s="52" t="str">
@@ -6416,7 +6514,7 @@
       <c r="R4" s="53" t="s">
         <v>496</v>
       </c>
-      <c r="S4" s="38" t="s">
+      <c r="S4" s="87" t="s">
         <v>181</v>
       </c>
       <c r="T4" s="52" t="str">
@@ -6516,7 +6614,7 @@
       <c r="R5" s="53" t="s">
         <v>499</v>
       </c>
-      <c r="S5" s="38" t="s">
+      <c r="S5" s="87" t="s">
         <v>181</v>
       </c>
       <c r="T5" s="52" t="str">
@@ -6616,7 +6714,7 @@
       <c r="R6" s="53" t="s">
         <v>502</v>
       </c>
-      <c r="S6" s="38" t="s">
+      <c r="S6" s="87" t="s">
         <v>181</v>
       </c>
       <c r="T6" s="52" t="str">
@@ -6716,7 +6814,7 @@
       <c r="R7" s="53" t="s">
         <v>505</v>
       </c>
-      <c r="S7" s="38" t="s">
+      <c r="S7" s="87" t="s">
         <v>181</v>
       </c>
       <c r="T7" s="52" t="str">
@@ -6816,7 +6914,7 @@
       <c r="R8" s="53" t="s">
         <v>508</v>
       </c>
-      <c r="S8" s="38" t="s">
+      <c r="S8" s="87" t="s">
         <v>181</v>
       </c>
       <c r="T8" s="52" t="str">
@@ -6916,7 +7014,7 @@
       <c r="R9" s="53" t="s">
         <v>511</v>
       </c>
-      <c r="S9" s="38" t="s">
+      <c r="S9" s="87" t="s">
         <v>181</v>
       </c>
       <c r="T9" s="52" t="str">
@@ -7016,7 +7114,7 @@
       <c r="R10" s="53" t="s">
         <v>514</v>
       </c>
-      <c r="S10" s="38" t="s">
+      <c r="S10" s="87" t="s">
         <v>181</v>
       </c>
       <c r="T10" s="52" t="str">
@@ -7116,7 +7214,7 @@
       <c r="R11" s="53" t="s">
         <v>517</v>
       </c>
-      <c r="S11" s="38" t="s">
+      <c r="S11" s="87" t="s">
         <v>181</v>
       </c>
       <c r="T11" s="52" t="str">
@@ -7216,7 +7314,7 @@
       <c r="R12" s="53" t="s">
         <v>520</v>
       </c>
-      <c r="S12" s="38" t="s">
+      <c r="S12" s="87" t="s">
         <v>181</v>
       </c>
       <c r="T12" s="52" t="str">
@@ -7316,7 +7414,7 @@
       <c r="R13" s="53" t="s">
         <v>523</v>
       </c>
-      <c r="S13" s="38" t="s">
+      <c r="S13" s="87" t="s">
         <v>181</v>
       </c>
       <c r="T13" s="52" t="str">
@@ -7416,7 +7514,7 @@
       <c r="R14" s="53" t="s">
         <v>526</v>
       </c>
-      <c r="S14" s="38" t="s">
+      <c r="S14" s="87" t="s">
         <v>181</v>
       </c>
       <c r="T14" s="52" t="str">
@@ -7492,7 +7590,7 @@
         <v>181</v>
       </c>
       <c r="L15" s="51" t="str">
-        <f t="shared" ref="L15:N23" si="4">CONCATENATE("", C15)</f>
+        <f t="shared" ref="L15:N28" si="4">CONCATENATE("", C15)</f>
         <v>Normativos</v>
       </c>
       <c r="M15" s="51" t="str">
@@ -7516,7 +7614,7 @@
       <c r="R15" s="53" t="s">
         <v>567</v>
       </c>
-      <c r="S15" s="38" t="s">
+      <c r="S15" s="87" t="s">
         <v>181</v>
       </c>
       <c r="T15" s="52" t="str">
@@ -7616,7 +7714,7 @@
       <c r="R16" s="53" t="s">
         <v>568</v>
       </c>
-      <c r="S16" s="38" t="s">
+      <c r="S16" s="87" t="s">
         <v>181</v>
       </c>
       <c r="T16" s="52" t="str">
@@ -7716,7 +7814,7 @@
       <c r="R17" s="53" t="s">
         <v>569</v>
       </c>
-      <c r="S17" s="38" t="s">
+      <c r="S17" s="87" t="s">
         <v>181</v>
       </c>
       <c r="T17" s="52" t="str">
@@ -7816,7 +7914,7 @@
       <c r="R18" s="53" t="s">
         <v>570</v>
       </c>
-      <c r="S18" s="38" t="s">
+      <c r="S18" s="87" t="s">
         <v>181</v>
       </c>
       <c r="T18" s="52" t="str">
@@ -7916,7 +8014,7 @@
       <c r="R19" s="53" t="s">
         <v>571</v>
       </c>
-      <c r="S19" s="38" t="s">
+      <c r="S19" s="87" t="s">
         <v>181</v>
       </c>
       <c r="T19" s="52" t="str">
@@ -8016,7 +8114,7 @@
       <c r="R20" s="53" t="s">
         <v>572</v>
       </c>
-      <c r="S20" s="38" t="s">
+      <c r="S20" s="87" t="s">
         <v>181</v>
       </c>
       <c r="T20" s="52" t="str">
@@ -8116,7 +8214,7 @@
       <c r="R21" s="53" t="s">
         <v>573</v>
       </c>
-      <c r="S21" s="38" t="s">
+      <c r="S21" s="87" t="s">
         <v>181</v>
       </c>
       <c r="T21" s="52" t="str">
@@ -8216,7 +8314,7 @@
       <c r="R22" s="53" t="s">
         <v>574</v>
       </c>
-      <c r="S22" s="38" t="s">
+      <c r="S22" s="87" t="s">
         <v>181</v>
       </c>
       <c r="T22" s="52" t="str">
@@ -8316,7 +8414,7 @@
       <c r="R23" s="53" t="s">
         <v>575</v>
       </c>
-      <c r="S23" s="38" t="s">
+      <c r="S23" s="87" t="s">
         <v>181</v>
       </c>
       <c r="T23" s="52" t="str">
@@ -8357,24 +8455,24 @@
         <v>181</v>
       </c>
     </row>
-    <row r="24" spans="1:30" s="48" customFormat="1" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:30" s="88" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A24" s="49">
         <v>24</v>
       </c>
       <c r="B24" s="50" t="s">
-        <v>587</v>
+        <v>630</v>
       </c>
       <c r="C24" s="33" t="s">
-        <v>588</v>
+        <v>631</v>
       </c>
       <c r="D24" s="33" t="s">
-        <v>590</v>
+        <v>632</v>
       </c>
       <c r="E24" s="33" t="s">
-        <v>589</v>
+        <v>633</v>
       </c>
       <c r="F24" s="33" t="s">
-        <v>613</v>
+        <v>609</v>
       </c>
       <c r="G24" s="36" t="s">
         <v>181</v>
@@ -8391,45 +8489,38 @@
       <c r="K24" s="36" t="s">
         <v>181</v>
       </c>
-      <c r="L24" s="51" t="str">
-        <f t="shared" ref="L24:O28" si="9">SUBSTITUTE(CONCATENATE("", C24), ".", " ")</f>
-        <v>De API</v>
-      </c>
-      <c r="M24" s="51" t="str">
-        <f t="shared" si="9"/>
-        <v>Macros</v>
-      </c>
-      <c r="N24" s="51" t="str">
-        <f t="shared" si="9"/>
-        <v>Métodos</v>
-      </c>
-      <c r="O24" s="51" t="str">
-        <f t="shared" si="9"/>
-        <v>Função Auxiliar</v>
+      <c r="L24" s="51" t="s">
+        <v>631</v>
+      </c>
+      <c r="M24" s="51" t="s">
+        <v>632</v>
+      </c>
+      <c r="N24" s="51" t="s">
+        <v>636</v>
+      </c>
+      <c r="O24" s="51" t="s">
+        <v>637</v>
       </c>
       <c r="P24" s="38" t="s">
-        <v>614</v>
+        <v>610</v>
       </c>
       <c r="Q24" s="38" t="s">
-        <v>615</v>
+        <v>611</v>
       </c>
       <c r="R24" s="38" t="s">
-        <v>616</v>
-      </c>
-      <c r="S24" s="38" t="s">
-        <v>181</v>
-      </c>
-      <c r="T24" s="38" t="str">
-        <f t="shared" ref="T24:V28" si="10">SUBSTITUTE(C24, ".", " ")</f>
-        <v>De API</v>
-      </c>
-      <c r="U24" s="38" t="str">
-        <f t="shared" si="10"/>
-        <v>Macros</v>
-      </c>
-      <c r="V24" s="52" t="str">
-        <f t="shared" si="10"/>
-        <v>Métodos</v>
+        <v>612</v>
+      </c>
+      <c r="S24" s="87" t="s">
+        <v>181</v>
+      </c>
+      <c r="T24" s="38" t="s">
+        <v>638</v>
+      </c>
+      <c r="U24" s="38" t="s">
+        <v>639</v>
+      </c>
+      <c r="V24" s="52" t="s">
+        <v>636</v>
       </c>
       <c r="W24" s="38" t="s">
         <v>419</v>
@@ -8457,24 +8548,24 @@
         <v>181</v>
       </c>
     </row>
-    <row r="25" spans="1:30" s="48" customFormat="1" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:30" s="88" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A25" s="49">
         <v>25</v>
       </c>
       <c r="B25" s="50" t="s">
-        <v>587</v>
+        <v>630</v>
       </c>
       <c r="C25" s="33" t="s">
-        <v>588</v>
+        <v>631</v>
       </c>
       <c r="D25" s="33" t="s">
-        <v>590</v>
+        <v>632</v>
       </c>
       <c r="E25" s="33" t="s">
-        <v>589</v>
+        <v>633</v>
       </c>
       <c r="F25" s="33" t="s">
-        <v>617</v>
+        <v>613</v>
       </c>
       <c r="G25" s="36" t="s">
         <v>181</v>
@@ -8491,45 +8582,38 @@
       <c r="K25" s="36" t="s">
         <v>181</v>
       </c>
-      <c r="L25" s="51" t="str">
-        <f t="shared" si="9"/>
-        <v>De API</v>
-      </c>
-      <c r="M25" s="51" t="str">
-        <f t="shared" si="9"/>
-        <v>Macros</v>
-      </c>
-      <c r="N25" s="51" t="str">
-        <f t="shared" si="9"/>
-        <v>Métodos</v>
-      </c>
-      <c r="O25" s="51" t="str">
-        <f t="shared" si="9"/>
-        <v>Função Global</v>
+      <c r="L25" s="51" t="s">
+        <v>631</v>
+      </c>
+      <c r="M25" s="51" t="s">
+        <v>632</v>
+      </c>
+      <c r="N25" s="51" t="s">
+        <v>636</v>
+      </c>
+      <c r="O25" s="51" t="s">
+        <v>640</v>
       </c>
       <c r="P25" s="38" t="s">
-        <v>618</v>
+        <v>614</v>
       </c>
       <c r="Q25" s="38" t="s">
-        <v>619</v>
+        <v>615</v>
       </c>
       <c r="R25" s="38" t="s">
-        <v>620</v>
-      </c>
-      <c r="S25" s="38" t="s">
-        <v>181</v>
-      </c>
-      <c r="T25" s="38" t="str">
-        <f t="shared" si="10"/>
-        <v>De API</v>
-      </c>
-      <c r="U25" s="38" t="str">
-        <f t="shared" si="10"/>
-        <v>Macros</v>
-      </c>
-      <c r="V25" s="52" t="str">
-        <f t="shared" si="10"/>
-        <v>Métodos</v>
+        <v>616</v>
+      </c>
+      <c r="S25" s="87" t="s">
+        <v>181</v>
+      </c>
+      <c r="T25" s="38" t="s">
+        <v>638</v>
+      </c>
+      <c r="U25" s="38" t="s">
+        <v>639</v>
+      </c>
+      <c r="V25" s="52" t="s">
+        <v>636</v>
       </c>
       <c r="W25" s="38" t="s">
         <v>419</v>
@@ -8557,24 +8641,24 @@
         <v>181</v>
       </c>
     </row>
-    <row r="26" spans="1:30" s="48" customFormat="1" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:30" s="88" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A26" s="49">
         <v>26</v>
       </c>
       <c r="B26" s="50" t="s">
-        <v>587</v>
+        <v>630</v>
       </c>
       <c r="C26" s="33" t="s">
-        <v>588</v>
+        <v>631</v>
       </c>
       <c r="D26" s="33" t="s">
-        <v>590</v>
+        <v>632</v>
       </c>
       <c r="E26" s="33" t="s">
-        <v>589</v>
+        <v>633</v>
       </c>
       <c r="F26" s="33" t="s">
-        <v>621</v>
+        <v>617</v>
       </c>
       <c r="G26" s="36" t="s">
         <v>181</v>
@@ -8591,45 +8675,38 @@
       <c r="K26" s="36" t="s">
         <v>181</v>
       </c>
-      <c r="L26" s="51" t="str">
-        <f t="shared" si="9"/>
-        <v>De API</v>
-      </c>
-      <c r="M26" s="51" t="str">
-        <f t="shared" si="9"/>
-        <v>Macros</v>
-      </c>
-      <c r="N26" s="51" t="str">
-        <f t="shared" si="9"/>
-        <v>Métodos</v>
-      </c>
-      <c r="O26" s="51" t="str">
-        <f t="shared" si="9"/>
-        <v>Função Local</v>
+      <c r="L26" s="51" t="s">
+        <v>631</v>
+      </c>
+      <c r="M26" s="51" t="s">
+        <v>632</v>
+      </c>
+      <c r="N26" s="51" t="s">
+        <v>636</v>
+      </c>
+      <c r="O26" s="51" t="s">
+        <v>641</v>
       </c>
       <c r="P26" s="38" t="s">
-        <v>622</v>
+        <v>618</v>
       </c>
       <c r="Q26" s="38" t="s">
-        <v>623</v>
+        <v>619</v>
       </c>
       <c r="R26" s="38" t="s">
-        <v>624</v>
-      </c>
-      <c r="S26" s="38" t="s">
-        <v>181</v>
-      </c>
-      <c r="T26" s="38" t="str">
-        <f t="shared" si="10"/>
-        <v>De API</v>
-      </c>
-      <c r="U26" s="38" t="str">
-        <f t="shared" si="10"/>
-        <v>Macros</v>
-      </c>
-      <c r="V26" s="52" t="str">
-        <f t="shared" si="10"/>
-        <v>Métodos</v>
+        <v>620</v>
+      </c>
+      <c r="S26" s="87" t="s">
+        <v>181</v>
+      </c>
+      <c r="T26" s="38" t="s">
+        <v>638</v>
+      </c>
+      <c r="U26" s="38" t="s">
+        <v>639</v>
+      </c>
+      <c r="V26" s="52" t="s">
+        <v>636</v>
       </c>
       <c r="W26" s="38" t="s">
         <v>419</v>
@@ -8657,24 +8734,24 @@
         <v>181</v>
       </c>
     </row>
-    <row r="27" spans="1:30" s="48" customFormat="1" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:30" s="88" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A27" s="49">
         <v>27</v>
       </c>
       <c r="B27" s="50" t="s">
-        <v>587</v>
+        <v>630</v>
       </c>
       <c r="C27" s="33" t="s">
-        <v>588</v>
+        <v>631</v>
       </c>
       <c r="D27" s="33" t="s">
-        <v>590</v>
+        <v>632</v>
       </c>
       <c r="E27" s="33" t="s">
-        <v>589</v>
+        <v>633</v>
       </c>
       <c r="F27" s="33" t="s">
-        <v>625</v>
+        <v>621</v>
       </c>
       <c r="G27" s="36" t="s">
         <v>181</v>
@@ -8691,45 +8768,38 @@
       <c r="K27" s="36" t="s">
         <v>181</v>
       </c>
-      <c r="L27" s="51" t="str">
-        <f t="shared" si="9"/>
-        <v>De API</v>
-      </c>
-      <c r="M27" s="51" t="str">
-        <f t="shared" si="9"/>
-        <v>Macros</v>
-      </c>
-      <c r="N27" s="51" t="str">
-        <f t="shared" si="9"/>
-        <v>Métodos</v>
-      </c>
-      <c r="O27" s="51" t="str">
-        <f t="shared" si="9"/>
-        <v>Função Filtro</v>
+      <c r="L27" s="51" t="s">
+        <v>631</v>
+      </c>
+      <c r="M27" s="51" t="s">
+        <v>632</v>
+      </c>
+      <c r="N27" s="51" t="s">
+        <v>636</v>
+      </c>
+      <c r="O27" s="51" t="s">
+        <v>642</v>
       </c>
       <c r="P27" s="38" t="s">
-        <v>626</v>
+        <v>622</v>
       </c>
       <c r="Q27" s="38" t="s">
-        <v>627</v>
+        <v>623</v>
       </c>
       <c r="R27" s="38" t="s">
-        <v>628</v>
-      </c>
-      <c r="S27" s="38" t="s">
-        <v>181</v>
-      </c>
-      <c r="T27" s="38" t="str">
-        <f t="shared" si="10"/>
-        <v>De API</v>
-      </c>
-      <c r="U27" s="38" t="str">
-        <f t="shared" si="10"/>
-        <v>Macros</v>
-      </c>
-      <c r="V27" s="52" t="str">
-        <f t="shared" si="10"/>
-        <v>Métodos</v>
+        <v>624</v>
+      </c>
+      <c r="S27" s="87" t="s">
+        <v>181</v>
+      </c>
+      <c r="T27" s="38" t="s">
+        <v>638</v>
+      </c>
+      <c r="U27" s="38" t="s">
+        <v>639</v>
+      </c>
+      <c r="V27" s="52" t="s">
+        <v>636</v>
       </c>
       <c r="W27" s="38" t="s">
         <v>419</v>
@@ -8757,24 +8827,24 @@
         <v>181</v>
       </c>
     </row>
-    <row r="28" spans="1:30" s="48" customFormat="1" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:30" s="88" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A28" s="49">
         <v>28</v>
       </c>
       <c r="B28" s="50" t="s">
-        <v>587</v>
+        <v>630</v>
       </c>
       <c r="C28" s="33" t="s">
-        <v>588</v>
+        <v>631</v>
       </c>
       <c r="D28" s="33" t="s">
-        <v>590</v>
+        <v>634</v>
       </c>
       <c r="E28" s="33" t="s">
-        <v>629</v>
+        <v>635</v>
       </c>
       <c r="F28" s="33" t="s">
-        <v>630</v>
+        <v>625</v>
       </c>
       <c r="G28" s="36" t="s">
         <v>181</v>
@@ -8791,45 +8861,38 @@
       <c r="K28" s="36" t="s">
         <v>181</v>
       </c>
-      <c r="L28" s="51" t="str">
-        <f t="shared" si="9"/>
-        <v>De API</v>
-      </c>
-      <c r="M28" s="51" t="str">
-        <f t="shared" si="9"/>
-        <v>Macros</v>
-      </c>
-      <c r="N28" s="51" t="str">
-        <f t="shared" si="9"/>
-        <v>Códigos Visuais</v>
-      </c>
-      <c r="O28" s="51" t="str">
-        <f t="shared" si="9"/>
-        <v>Bloco de Código</v>
+      <c r="L28" s="51" t="s">
+        <v>631</v>
+      </c>
+      <c r="M28" s="51" t="s">
+        <v>634</v>
+      </c>
+      <c r="N28" s="51" t="s">
+        <v>643</v>
+      </c>
+      <c r="O28" s="51" t="s">
+        <v>644</v>
       </c>
       <c r="P28" s="38" t="s">
-        <v>631</v>
+        <v>626</v>
       </c>
       <c r="Q28" s="38" t="s">
-        <v>632</v>
+        <v>627</v>
       </c>
       <c r="R28" s="38" t="s">
-        <v>633</v>
-      </c>
-      <c r="S28" s="38" t="s">
-        <v>181</v>
-      </c>
-      <c r="T28" s="38" t="str">
-        <f t="shared" si="10"/>
-        <v>De API</v>
-      </c>
-      <c r="U28" s="38" t="str">
-        <f t="shared" si="10"/>
-        <v>Macros</v>
-      </c>
-      <c r="V28" s="52" t="str">
-        <f t="shared" si="10"/>
-        <v>Códigos Visuais</v>
+        <v>628</v>
+      </c>
+      <c r="S28" s="87" t="s">
+        <v>181</v>
+      </c>
+      <c r="T28" s="38" t="s">
+        <v>638</v>
+      </c>
+      <c r="U28" s="38" t="s">
+        <v>645</v>
+      </c>
+      <c r="V28" s="52" t="s">
+        <v>643</v>
       </c>
       <c r="W28" s="38" t="s">
         <v>419</v>
@@ -8858,29 +8921,29 @@
       </c>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="A2:B28">
-    <cfRule type="cellIs" dxfId="31" priority="1" operator="equal">
+  <conditionalFormatting sqref="A2:B23 A24:A28">
+    <cfRule type="cellIs" dxfId="0" priority="7" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="E28:F28">
-    <cfRule type="duplicateValues" dxfId="30" priority="2"/>
-  </conditionalFormatting>
   <conditionalFormatting sqref="F2:F14">
-    <cfRule type="duplicateValues" dxfId="29" priority="16"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="F24:F27">
-    <cfRule type="duplicateValues" dxfId="28" priority="7"/>
+    <cfRule type="duplicateValues" dxfId="36" priority="22"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="R1:R23">
-    <cfRule type="cellIs" dxfId="27" priority="8" operator="equal">
+    <cfRule type="cellIs" dxfId="34" priority="14" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="Y2 AA2">
-    <cfRule type="cellIs" dxfId="26" priority="13" operator="equal">
+    <cfRule type="cellIs" dxfId="33" priority="19" operator="equal">
       <formula>"null"</formula>
     </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F24:F28">
+    <cfRule type="duplicateValues" dxfId="2" priority="1"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F24:F28">
+    <cfRule type="duplicateValues" dxfId="1" priority="2"/>
   </conditionalFormatting>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
   <ignoredErrors>
@@ -9031,7 +9094,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:U2">
-    <cfRule type="cellIs" dxfId="25" priority="1" operator="equal">
+    <cfRule type="cellIs" dxfId="32" priority="1" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -9076,7 +9139,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:A2">
-    <cfRule type="cellIs" dxfId="24" priority="1" operator="equal">
+    <cfRule type="cellIs" dxfId="31" priority="1" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -9496,34 +9559,34 @@
         <v>181</v>
       </c>
       <c r="X4" s="55" t="s">
-        <v>607</v>
+        <v>603</v>
       </c>
       <c r="Y4" s="56" t="s">
+        <v>587</v>
+      </c>
+      <c r="Z4" s="55" t="s">
+        <v>603</v>
+      </c>
+      <c r="AA4" s="56" t="s">
         <v>591</v>
       </c>
-      <c r="Z4" s="55" t="s">
-        <v>607</v>
-      </c>
-      <c r="AA4" s="56" t="s">
-        <v>595</v>
-      </c>
       <c r="AB4" s="55" t="s">
-        <v>607</v>
+        <v>603</v>
       </c>
       <c r="AC4" s="56" t="s">
-        <v>598</v>
+        <v>594</v>
       </c>
       <c r="AD4" s="55" t="s">
-        <v>607</v>
+        <v>603</v>
       </c>
       <c r="AE4" s="56" t="s">
-        <v>601</v>
+        <v>597</v>
       </c>
       <c r="AF4" s="55" t="s">
-        <v>607</v>
+        <v>603</v>
       </c>
       <c r="AG4" s="56" t="s">
-        <v>604</v>
+        <v>600</v>
       </c>
     </row>
     <row r="5" spans="1:33" ht="6" customHeight="1" x14ac:dyDescent="0.2">
@@ -9597,34 +9660,34 @@
         <v>181</v>
       </c>
       <c r="X5" s="55" t="s">
-        <v>607</v>
+        <v>603</v>
       </c>
       <c r="Y5" s="56" t="s">
+        <v>587</v>
+      </c>
+      <c r="Z5" s="55" t="s">
+        <v>603</v>
+      </c>
+      <c r="AA5" s="56" t="s">
         <v>591</v>
       </c>
-      <c r="Z5" s="55" t="s">
-        <v>607</v>
-      </c>
-      <c r="AA5" s="56" t="s">
-        <v>595</v>
-      </c>
       <c r="AB5" s="55" t="s">
-        <v>607</v>
+        <v>603</v>
       </c>
       <c r="AC5" s="56" t="s">
-        <v>598</v>
+        <v>594</v>
       </c>
       <c r="AD5" s="55" t="s">
-        <v>607</v>
+        <v>603</v>
       </c>
       <c r="AE5" s="56" t="s">
-        <v>601</v>
+        <v>597</v>
       </c>
       <c r="AF5" s="55" t="s">
-        <v>607</v>
+        <v>603</v>
       </c>
       <c r="AG5" s="56" t="s">
-        <v>604</v>
+        <v>600</v>
       </c>
     </row>
     <row r="6" spans="1:33" ht="6" customHeight="1" x14ac:dyDescent="0.2">
@@ -9698,34 +9761,34 @@
         <v>181</v>
       </c>
       <c r="X6" s="55" t="s">
-        <v>607</v>
+        <v>603</v>
       </c>
       <c r="Y6" s="56" t="s">
+        <v>587</v>
+      </c>
+      <c r="Z6" s="55" t="s">
+        <v>603</v>
+      </c>
+      <c r="AA6" s="56" t="s">
         <v>591</v>
       </c>
-      <c r="Z6" s="55" t="s">
-        <v>607</v>
-      </c>
-      <c r="AA6" s="56" t="s">
-        <v>595</v>
-      </c>
       <c r="AB6" s="55" t="s">
-        <v>607</v>
+        <v>603</v>
       </c>
       <c r="AC6" s="56" t="s">
-        <v>598</v>
+        <v>594</v>
       </c>
       <c r="AD6" s="55" t="s">
-        <v>607</v>
+        <v>603</v>
       </c>
       <c r="AE6" s="56" t="s">
-        <v>601</v>
+        <v>597</v>
       </c>
       <c r="AF6" s="55" t="s">
-        <v>607</v>
+        <v>603</v>
       </c>
       <c r="AG6" s="56" t="s">
-        <v>604</v>
+        <v>600</v>
       </c>
     </row>
     <row r="7" spans="1:33" ht="6" customHeight="1" x14ac:dyDescent="0.2">
@@ -9799,34 +9862,34 @@
         <v>181</v>
       </c>
       <c r="X7" s="55" t="s">
-        <v>607</v>
+        <v>603</v>
       </c>
       <c r="Y7" s="56" t="s">
+        <v>587</v>
+      </c>
+      <c r="Z7" s="55" t="s">
+        <v>603</v>
+      </c>
+      <c r="AA7" s="56" t="s">
         <v>591</v>
       </c>
-      <c r="Z7" s="55" t="s">
-        <v>607</v>
-      </c>
-      <c r="AA7" s="56" t="s">
-        <v>595</v>
-      </c>
       <c r="AB7" s="55" t="s">
-        <v>607</v>
+        <v>603</v>
       </c>
       <c r="AC7" s="56" t="s">
-        <v>598</v>
+        <v>594</v>
       </c>
       <c r="AD7" s="55" t="s">
-        <v>607</v>
+        <v>603</v>
       </c>
       <c r="AE7" s="56" t="s">
-        <v>601</v>
+        <v>597</v>
       </c>
       <c r="AF7" s="55" t="s">
-        <v>607</v>
+        <v>603</v>
       </c>
       <c r="AG7" s="56" t="s">
-        <v>604</v>
+        <v>600</v>
       </c>
     </row>
     <row r="8" spans="1:33" ht="6" customHeight="1" x14ac:dyDescent="0.2">
@@ -9900,34 +9963,34 @@
         <v>181</v>
       </c>
       <c r="X8" s="55" t="s">
-        <v>607</v>
+        <v>603</v>
       </c>
       <c r="Y8" s="56" t="s">
+        <v>587</v>
+      </c>
+      <c r="Z8" s="55" t="s">
+        <v>603</v>
+      </c>
+      <c r="AA8" s="56" t="s">
         <v>591</v>
       </c>
-      <c r="Z8" s="55" t="s">
-        <v>607</v>
-      </c>
-      <c r="AA8" s="56" t="s">
-        <v>595</v>
-      </c>
       <c r="AB8" s="55" t="s">
-        <v>607</v>
+        <v>603</v>
       </c>
       <c r="AC8" s="56" t="s">
-        <v>598</v>
+        <v>594</v>
       </c>
       <c r="AD8" s="55" t="s">
-        <v>607</v>
+        <v>603</v>
       </c>
       <c r="AE8" s="56" t="s">
-        <v>601</v>
+        <v>597</v>
       </c>
       <c r="AF8" s="55" t="s">
-        <v>607</v>
+        <v>603</v>
       </c>
       <c r="AG8" s="56" t="s">
-        <v>604</v>
+        <v>600</v>
       </c>
     </row>
     <row r="9" spans="1:33" ht="6" customHeight="1" x14ac:dyDescent="0.2">
@@ -10001,34 +10064,34 @@
         <v>181</v>
       </c>
       <c r="X9" s="55" t="s">
-        <v>607</v>
+        <v>603</v>
       </c>
       <c r="Y9" s="56" t="s">
+        <v>587</v>
+      </c>
+      <c r="Z9" s="55" t="s">
+        <v>603</v>
+      </c>
+      <c r="AA9" s="56" t="s">
         <v>591</v>
       </c>
-      <c r="Z9" s="55" t="s">
-        <v>607</v>
-      </c>
-      <c r="AA9" s="56" t="s">
-        <v>595</v>
-      </c>
       <c r="AB9" s="55" t="s">
-        <v>607</v>
+        <v>603</v>
       </c>
       <c r="AC9" s="56" t="s">
-        <v>598</v>
+        <v>594</v>
       </c>
       <c r="AD9" s="55" t="s">
-        <v>607</v>
+        <v>603</v>
       </c>
       <c r="AE9" s="56" t="s">
-        <v>601</v>
+        <v>597</v>
       </c>
       <c r="AF9" s="55" t="s">
-        <v>607</v>
+        <v>603</v>
       </c>
       <c r="AG9" s="56" t="s">
-        <v>604</v>
+        <v>600</v>
       </c>
     </row>
     <row r="10" spans="1:33" ht="6" customHeight="1" x14ac:dyDescent="0.2">
@@ -10102,34 +10165,34 @@
         <v>181</v>
       </c>
       <c r="X10" s="55" t="s">
-        <v>607</v>
+        <v>603</v>
       </c>
       <c r="Y10" s="56" t="s">
+        <v>587</v>
+      </c>
+      <c r="Z10" s="55" t="s">
+        <v>603</v>
+      </c>
+      <c r="AA10" s="56" t="s">
         <v>591</v>
       </c>
-      <c r="Z10" s="55" t="s">
-        <v>607</v>
-      </c>
-      <c r="AA10" s="56" t="s">
-        <v>595</v>
-      </c>
       <c r="AB10" s="55" t="s">
-        <v>607</v>
+        <v>603</v>
       </c>
       <c r="AC10" s="56" t="s">
-        <v>598</v>
+        <v>594</v>
       </c>
       <c r="AD10" s="55" t="s">
-        <v>607</v>
+        <v>603</v>
       </c>
       <c r="AE10" s="56" t="s">
-        <v>601</v>
+        <v>597</v>
       </c>
       <c r="AF10" s="55" t="s">
-        <v>607</v>
+        <v>603</v>
       </c>
       <c r="AG10" s="56" t="s">
-        <v>604</v>
+        <v>600</v>
       </c>
     </row>
     <row r="11" spans="1:33" ht="6" customHeight="1" x14ac:dyDescent="0.2">
@@ -10203,34 +10266,34 @@
         <v>181</v>
       </c>
       <c r="X11" s="55" t="s">
-        <v>607</v>
+        <v>603</v>
       </c>
       <c r="Y11" s="56" t="s">
+        <v>587</v>
+      </c>
+      <c r="Z11" s="55" t="s">
+        <v>603</v>
+      </c>
+      <c r="AA11" s="56" t="s">
         <v>591</v>
       </c>
-      <c r="Z11" s="55" t="s">
-        <v>607</v>
-      </c>
-      <c r="AA11" s="56" t="s">
-        <v>595</v>
-      </c>
       <c r="AB11" s="55" t="s">
-        <v>607</v>
+        <v>603</v>
       </c>
       <c r="AC11" s="56" t="s">
-        <v>598</v>
+        <v>594</v>
       </c>
       <c r="AD11" s="55" t="s">
-        <v>607</v>
+        <v>603</v>
       </c>
       <c r="AE11" s="56" t="s">
-        <v>601</v>
+        <v>597</v>
       </c>
       <c r="AF11" s="55" t="s">
-        <v>607</v>
+        <v>603</v>
       </c>
       <c r="AG11" s="56" t="s">
-        <v>604</v>
+        <v>600</v>
       </c>
     </row>
     <row r="12" spans="1:33" ht="6" customHeight="1" x14ac:dyDescent="0.2">
@@ -10304,34 +10367,34 @@
         <v>181</v>
       </c>
       <c r="X12" s="55" t="s">
-        <v>607</v>
+        <v>603</v>
       </c>
       <c r="Y12" s="56" t="s">
+        <v>587</v>
+      </c>
+      <c r="Z12" s="55" t="s">
+        <v>603</v>
+      </c>
+      <c r="AA12" s="56" t="s">
         <v>591</v>
       </c>
-      <c r="Z12" s="55" t="s">
-        <v>607</v>
-      </c>
-      <c r="AA12" s="56" t="s">
-        <v>595</v>
-      </c>
       <c r="AB12" s="55" t="s">
-        <v>607</v>
+        <v>603</v>
       </c>
       <c r="AC12" s="56" t="s">
-        <v>598</v>
+        <v>594</v>
       </c>
       <c r="AD12" s="55" t="s">
-        <v>607</v>
+        <v>603</v>
       </c>
       <c r="AE12" s="56" t="s">
-        <v>601</v>
+        <v>597</v>
       </c>
       <c r="AF12" s="55" t="s">
-        <v>607</v>
+        <v>603</v>
       </c>
       <c r="AG12" s="56" t="s">
-        <v>604</v>
+        <v>600</v>
       </c>
     </row>
     <row r="13" spans="1:33" ht="6" customHeight="1" x14ac:dyDescent="0.2">
@@ -10405,34 +10468,34 @@
         <v>181</v>
       </c>
       <c r="X13" s="55" t="s">
-        <v>607</v>
+        <v>603</v>
       </c>
       <c r="Y13" s="56" t="s">
+        <v>587</v>
+      </c>
+      <c r="Z13" s="55" t="s">
+        <v>603</v>
+      </c>
+      <c r="AA13" s="56" t="s">
         <v>591</v>
       </c>
-      <c r="Z13" s="55" t="s">
-        <v>607</v>
-      </c>
-      <c r="AA13" s="56" t="s">
-        <v>595</v>
-      </c>
       <c r="AB13" s="55" t="s">
-        <v>607</v>
+        <v>603</v>
       </c>
       <c r="AC13" s="56" t="s">
-        <v>598</v>
+        <v>594</v>
       </c>
       <c r="AD13" s="55" t="s">
-        <v>607</v>
+        <v>603</v>
       </c>
       <c r="AE13" s="56" t="s">
-        <v>601</v>
+        <v>597</v>
       </c>
       <c r="AF13" s="55" t="s">
-        <v>607</v>
+        <v>603</v>
       </c>
       <c r="AG13" s="56" t="s">
-        <v>604</v>
+        <v>600</v>
       </c>
     </row>
     <row r="14" spans="1:33" ht="6" customHeight="1" x14ac:dyDescent="0.2">
@@ -10506,34 +10569,34 @@
         <v>181</v>
       </c>
       <c r="X14" s="55" t="s">
-        <v>607</v>
+        <v>603</v>
       </c>
       <c r="Y14" s="56" t="s">
+        <v>587</v>
+      </c>
+      <c r="Z14" s="55" t="s">
+        <v>603</v>
+      </c>
+      <c r="AA14" s="56" t="s">
         <v>591</v>
       </c>
-      <c r="Z14" s="55" t="s">
-        <v>607</v>
-      </c>
-      <c r="AA14" s="56" t="s">
-        <v>595</v>
-      </c>
       <c r="AB14" s="55" t="s">
-        <v>607</v>
+        <v>603</v>
       </c>
       <c r="AC14" s="56" t="s">
-        <v>598</v>
+        <v>594</v>
       </c>
       <c r="AD14" s="55" t="s">
-        <v>607</v>
+        <v>603</v>
       </c>
       <c r="AE14" s="56" t="s">
-        <v>601</v>
+        <v>597</v>
       </c>
       <c r="AF14" s="55" t="s">
-        <v>607</v>
+        <v>603</v>
       </c>
       <c r="AG14" s="56" t="s">
-        <v>604</v>
+        <v>600</v>
       </c>
     </row>
     <row r="15" spans="1:33" ht="6" customHeight="1" x14ac:dyDescent="0.2">
@@ -10607,34 +10670,34 @@
         <v>181</v>
       </c>
       <c r="X15" s="55" t="s">
-        <v>607</v>
+        <v>603</v>
       </c>
       <c r="Y15" s="56" t="s">
+        <v>587</v>
+      </c>
+      <c r="Z15" s="55" t="s">
+        <v>603</v>
+      </c>
+      <c r="AA15" s="56" t="s">
         <v>591</v>
       </c>
-      <c r="Z15" s="55" t="s">
-        <v>607</v>
-      </c>
-      <c r="AA15" s="56" t="s">
-        <v>595</v>
-      </c>
       <c r="AB15" s="55" t="s">
-        <v>607</v>
+        <v>603</v>
       </c>
       <c r="AC15" s="56" t="s">
-        <v>598</v>
+        <v>594</v>
       </c>
       <c r="AD15" s="55" t="s">
-        <v>607</v>
+        <v>603</v>
       </c>
       <c r="AE15" s="56" t="s">
-        <v>601</v>
+        <v>597</v>
       </c>
       <c r="AF15" s="55" t="s">
-        <v>607</v>
+        <v>603</v>
       </c>
       <c r="AG15" s="56" t="s">
-        <v>604</v>
+        <v>600</v>
       </c>
     </row>
     <row r="16" spans="1:33" ht="6" customHeight="1" x14ac:dyDescent="0.2">
@@ -10708,34 +10771,34 @@
         <v>181</v>
       </c>
       <c r="X16" s="55" t="s">
-        <v>607</v>
+        <v>603</v>
       </c>
       <c r="Y16" s="56" t="s">
+        <v>587</v>
+      </c>
+      <c r="Z16" s="55" t="s">
+        <v>603</v>
+      </c>
+      <c r="AA16" s="56" t="s">
         <v>591</v>
       </c>
-      <c r="Z16" s="55" t="s">
-        <v>607</v>
-      </c>
-      <c r="AA16" s="56" t="s">
-        <v>595</v>
-      </c>
       <c r="AB16" s="55" t="s">
-        <v>607</v>
+        <v>603</v>
       </c>
       <c r="AC16" s="56" t="s">
-        <v>598</v>
+        <v>594</v>
       </c>
       <c r="AD16" s="55" t="s">
-        <v>607</v>
+        <v>603</v>
       </c>
       <c r="AE16" s="56" t="s">
-        <v>601</v>
+        <v>597</v>
       </c>
       <c r="AF16" s="55" t="s">
-        <v>607</v>
+        <v>603</v>
       </c>
       <c r="AG16" s="56" t="s">
-        <v>604</v>
+        <v>600</v>
       </c>
     </row>
     <row r="17" spans="1:33" ht="6" customHeight="1" x14ac:dyDescent="0.2">
@@ -10809,34 +10872,34 @@
         <v>181</v>
       </c>
       <c r="X17" s="55" t="s">
-        <v>607</v>
+        <v>603</v>
       </c>
       <c r="Y17" s="56" t="s">
+        <v>587</v>
+      </c>
+      <c r="Z17" s="55" t="s">
+        <v>603</v>
+      </c>
+      <c r="AA17" s="56" t="s">
         <v>591</v>
       </c>
-      <c r="Z17" s="55" t="s">
-        <v>607</v>
-      </c>
-      <c r="AA17" s="56" t="s">
-        <v>595</v>
-      </c>
       <c r="AB17" s="55" t="s">
-        <v>607</v>
+        <v>603</v>
       </c>
       <c r="AC17" s="56" t="s">
-        <v>598</v>
+        <v>594</v>
       </c>
       <c r="AD17" s="55" t="s">
-        <v>607</v>
+        <v>603</v>
       </c>
       <c r="AE17" s="56" t="s">
-        <v>601</v>
+        <v>597</v>
       </c>
       <c r="AF17" s="55" t="s">
-        <v>607</v>
+        <v>603</v>
       </c>
       <c r="AG17" s="56" t="s">
-        <v>604</v>
+        <v>600</v>
       </c>
     </row>
     <row r="18" spans="1:33" ht="6" customHeight="1" x14ac:dyDescent="0.2">
@@ -10910,34 +10973,34 @@
         <v>181</v>
       </c>
       <c r="X18" s="55" t="s">
-        <v>607</v>
+        <v>603</v>
       </c>
       <c r="Y18" s="56" t="s">
+        <v>587</v>
+      </c>
+      <c r="Z18" s="55" t="s">
+        <v>603</v>
+      </c>
+      <c r="AA18" s="56" t="s">
         <v>591</v>
       </c>
-      <c r="Z18" s="55" t="s">
-        <v>607</v>
-      </c>
-      <c r="AA18" s="56" t="s">
-        <v>595</v>
-      </c>
       <c r="AB18" s="55" t="s">
-        <v>607</v>
+        <v>603</v>
       </c>
       <c r="AC18" s="56" t="s">
-        <v>598</v>
+        <v>594</v>
       </c>
       <c r="AD18" s="55" t="s">
-        <v>607</v>
+        <v>603</v>
       </c>
       <c r="AE18" s="56" t="s">
-        <v>601</v>
+        <v>597</v>
       </c>
       <c r="AF18" s="55" t="s">
-        <v>607</v>
+        <v>603</v>
       </c>
       <c r="AG18" s="56" t="s">
-        <v>604</v>
+        <v>600</v>
       </c>
     </row>
     <row r="19" spans="1:33" ht="6" customHeight="1" x14ac:dyDescent="0.2">
@@ -11011,34 +11074,34 @@
         <v>181</v>
       </c>
       <c r="X19" s="55" t="s">
-        <v>607</v>
+        <v>603</v>
       </c>
       <c r="Y19" s="56" t="s">
+        <v>587</v>
+      </c>
+      <c r="Z19" s="55" t="s">
+        <v>603</v>
+      </c>
+      <c r="AA19" s="56" t="s">
         <v>591</v>
       </c>
-      <c r="Z19" s="55" t="s">
-        <v>607</v>
-      </c>
-      <c r="AA19" s="56" t="s">
-        <v>595</v>
-      </c>
       <c r="AB19" s="55" t="s">
-        <v>607</v>
+        <v>603</v>
       </c>
       <c r="AC19" s="56" t="s">
-        <v>598</v>
+        <v>594</v>
       </c>
       <c r="AD19" s="55" t="s">
-        <v>607</v>
+        <v>603</v>
       </c>
       <c r="AE19" s="56" t="s">
-        <v>601</v>
+        <v>597</v>
       </c>
       <c r="AF19" s="55" t="s">
-        <v>607</v>
+        <v>603</v>
       </c>
       <c r="AG19" s="56" t="s">
-        <v>604</v>
+        <v>600</v>
       </c>
     </row>
     <row r="20" spans="1:33" ht="6" customHeight="1" x14ac:dyDescent="0.2">
@@ -11112,34 +11175,34 @@
         <v>181</v>
       </c>
       <c r="X20" s="55" t="s">
-        <v>607</v>
+        <v>603</v>
       </c>
       <c r="Y20" s="56" t="s">
+        <v>587</v>
+      </c>
+      <c r="Z20" s="55" t="s">
+        <v>603</v>
+      </c>
+      <c r="AA20" s="56" t="s">
         <v>591</v>
       </c>
-      <c r="Z20" s="55" t="s">
-        <v>607</v>
-      </c>
-      <c r="AA20" s="56" t="s">
-        <v>595</v>
-      </c>
       <c r="AB20" s="55" t="s">
-        <v>607</v>
+        <v>603</v>
       </c>
       <c r="AC20" s="56" t="s">
-        <v>598</v>
+        <v>594</v>
       </c>
       <c r="AD20" s="55" t="s">
-        <v>607</v>
+        <v>603</v>
       </c>
       <c r="AE20" s="56" t="s">
-        <v>601</v>
+        <v>597</v>
       </c>
       <c r="AF20" s="55" t="s">
-        <v>607</v>
+        <v>603</v>
       </c>
       <c r="AG20" s="56" t="s">
-        <v>604</v>
+        <v>600</v>
       </c>
     </row>
     <row r="21" spans="1:33" ht="6" customHeight="1" x14ac:dyDescent="0.2">
@@ -11213,34 +11276,34 @@
         <v>181</v>
       </c>
       <c r="X21" s="55" t="s">
-        <v>607</v>
+        <v>603</v>
       </c>
       <c r="Y21" s="56" t="s">
+        <v>587</v>
+      </c>
+      <c r="Z21" s="55" t="s">
+        <v>603</v>
+      </c>
+      <c r="AA21" s="56" t="s">
         <v>591</v>
       </c>
-      <c r="Z21" s="55" t="s">
-        <v>607</v>
-      </c>
-      <c r="AA21" s="56" t="s">
-        <v>595</v>
-      </c>
       <c r="AB21" s="55" t="s">
-        <v>607</v>
+        <v>603</v>
       </c>
       <c r="AC21" s="56" t="s">
-        <v>598</v>
+        <v>594</v>
       </c>
       <c r="AD21" s="55" t="s">
-        <v>607</v>
+        <v>603</v>
       </c>
       <c r="AE21" s="56" t="s">
-        <v>601</v>
+        <v>597</v>
       </c>
       <c r="AF21" s="55" t="s">
-        <v>607</v>
+        <v>603</v>
       </c>
       <c r="AG21" s="56" t="s">
-        <v>604</v>
+        <v>600</v>
       </c>
     </row>
     <row r="22" spans="1:33" ht="6" customHeight="1" x14ac:dyDescent="0.2">
@@ -11314,34 +11377,34 @@
         <v>181</v>
       </c>
       <c r="X22" s="55" t="s">
-        <v>607</v>
+        <v>603</v>
       </c>
       <c r="Y22" s="56" t="s">
+        <v>587</v>
+      </c>
+      <c r="Z22" s="55" t="s">
+        <v>603</v>
+      </c>
+      <c r="AA22" s="56" t="s">
         <v>591</v>
       </c>
-      <c r="Z22" s="55" t="s">
-        <v>607</v>
-      </c>
-      <c r="AA22" s="56" t="s">
-        <v>595</v>
-      </c>
       <c r="AB22" s="55" t="s">
-        <v>607</v>
+        <v>603</v>
       </c>
       <c r="AC22" s="56" t="s">
-        <v>598</v>
+        <v>594</v>
       </c>
       <c r="AD22" s="55" t="s">
-        <v>607</v>
+        <v>603</v>
       </c>
       <c r="AE22" s="56" t="s">
-        <v>601</v>
+        <v>597</v>
       </c>
       <c r="AF22" s="55" t="s">
-        <v>607</v>
+        <v>603</v>
       </c>
       <c r="AG22" s="56" t="s">
-        <v>604</v>
+        <v>600</v>
       </c>
     </row>
     <row r="23" spans="1:33" ht="6" customHeight="1" x14ac:dyDescent="0.2">
@@ -11415,34 +11478,34 @@
         <v>181</v>
       </c>
       <c r="X23" s="55" t="s">
-        <v>607</v>
+        <v>603</v>
       </c>
       <c r="Y23" s="56" t="s">
+        <v>587</v>
+      </c>
+      <c r="Z23" s="55" t="s">
+        <v>603</v>
+      </c>
+      <c r="AA23" s="56" t="s">
         <v>591</v>
       </c>
-      <c r="Z23" s="55" t="s">
-        <v>607</v>
-      </c>
-      <c r="AA23" s="56" t="s">
-        <v>595</v>
-      </c>
       <c r="AB23" s="55" t="s">
-        <v>607</v>
+        <v>603</v>
       </c>
       <c r="AC23" s="56" t="s">
-        <v>598</v>
+        <v>594</v>
       </c>
       <c r="AD23" s="55" t="s">
-        <v>607</v>
+        <v>603</v>
       </c>
       <c r="AE23" s="56" t="s">
-        <v>601</v>
+        <v>597</v>
       </c>
       <c r="AF23" s="55" t="s">
-        <v>607</v>
+        <v>603</v>
       </c>
       <c r="AG23" s="56" t="s">
-        <v>604</v>
+        <v>600</v>
       </c>
     </row>
     <row r="24" spans="1:33" ht="6" customHeight="1" x14ac:dyDescent="0.2">
@@ -11516,34 +11579,34 @@
         <v>181</v>
       </c>
       <c r="X24" s="55" t="s">
-        <v>607</v>
+        <v>603</v>
       </c>
       <c r="Y24" s="56" t="s">
+        <v>587</v>
+      </c>
+      <c r="Z24" s="55" t="s">
+        <v>603</v>
+      </c>
+      <c r="AA24" s="56" t="s">
         <v>591</v>
       </c>
-      <c r="Z24" s="55" t="s">
-        <v>607</v>
-      </c>
-      <c r="AA24" s="56" t="s">
-        <v>595</v>
-      </c>
       <c r="AB24" s="55" t="s">
-        <v>607</v>
+        <v>603</v>
       </c>
       <c r="AC24" s="56" t="s">
-        <v>598</v>
+        <v>594</v>
       </c>
       <c r="AD24" s="55" t="s">
-        <v>607</v>
+        <v>603</v>
       </c>
       <c r="AE24" s="56" t="s">
-        <v>601</v>
+        <v>597</v>
       </c>
       <c r="AF24" s="55" t="s">
-        <v>607</v>
+        <v>603</v>
       </c>
       <c r="AG24" s="56" t="s">
-        <v>604</v>
+        <v>600</v>
       </c>
     </row>
     <row r="25" spans="1:33" ht="6" customHeight="1" x14ac:dyDescent="0.2">
@@ -11617,34 +11680,34 @@
         <v>181</v>
       </c>
       <c r="X25" s="55" t="s">
-        <v>607</v>
+        <v>603</v>
       </c>
       <c r="Y25" s="56" t="s">
+        <v>587</v>
+      </c>
+      <c r="Z25" s="55" t="s">
+        <v>603</v>
+      </c>
+      <c r="AA25" s="56" t="s">
         <v>591</v>
       </c>
-      <c r="Z25" s="55" t="s">
-        <v>607</v>
-      </c>
-      <c r="AA25" s="56" t="s">
-        <v>595</v>
-      </c>
       <c r="AB25" s="55" t="s">
-        <v>607</v>
+        <v>603</v>
       </c>
       <c r="AC25" s="56" t="s">
-        <v>598</v>
+        <v>594</v>
       </c>
       <c r="AD25" s="55" t="s">
-        <v>607</v>
+        <v>603</v>
       </c>
       <c r="AE25" s="56" t="s">
-        <v>601</v>
+        <v>597</v>
       </c>
       <c r="AF25" s="55" t="s">
-        <v>607</v>
+        <v>603</v>
       </c>
       <c r="AG25" s="56" t="s">
-        <v>604</v>
+        <v>600</v>
       </c>
     </row>
     <row r="26" spans="1:33" ht="6" customHeight="1" x14ac:dyDescent="0.2">
@@ -11718,34 +11781,34 @@
         <v>181</v>
       </c>
       <c r="X26" s="55" t="s">
-        <v>607</v>
+        <v>603</v>
       </c>
       <c r="Y26" s="56" t="s">
+        <v>587</v>
+      </c>
+      <c r="Z26" s="55" t="s">
+        <v>603</v>
+      </c>
+      <c r="AA26" s="56" t="s">
         <v>591</v>
       </c>
-      <c r="Z26" s="55" t="s">
-        <v>607</v>
-      </c>
-      <c r="AA26" s="56" t="s">
-        <v>595</v>
-      </c>
       <c r="AB26" s="55" t="s">
-        <v>607</v>
+        <v>603</v>
       </c>
       <c r="AC26" s="56" t="s">
-        <v>598</v>
+        <v>594</v>
       </c>
       <c r="AD26" s="55" t="s">
-        <v>607</v>
+        <v>603</v>
       </c>
       <c r="AE26" s="56" t="s">
-        <v>601</v>
+        <v>597</v>
       </c>
       <c r="AF26" s="55" t="s">
-        <v>607</v>
+        <v>603</v>
       </c>
       <c r="AG26" s="56" t="s">
-        <v>604</v>
+        <v>600</v>
       </c>
     </row>
     <row r="27" spans="1:33" ht="6" customHeight="1" x14ac:dyDescent="0.2">
@@ -11819,34 +11882,34 @@
         <v>181</v>
       </c>
       <c r="X27" s="55" t="s">
-        <v>607</v>
+        <v>603</v>
       </c>
       <c r="Y27" s="56" t="s">
+        <v>587</v>
+      </c>
+      <c r="Z27" s="55" t="s">
+        <v>603</v>
+      </c>
+      <c r="AA27" s="56" t="s">
         <v>591</v>
       </c>
-      <c r="Z27" s="55" t="s">
-        <v>607</v>
-      </c>
-      <c r="AA27" s="56" t="s">
-        <v>595</v>
-      </c>
       <c r="AB27" s="55" t="s">
-        <v>607</v>
+        <v>603</v>
       </c>
       <c r="AC27" s="56" t="s">
-        <v>598</v>
+        <v>594</v>
       </c>
       <c r="AD27" s="55" t="s">
-        <v>607</v>
+        <v>603</v>
       </c>
       <c r="AE27" s="56" t="s">
-        <v>601</v>
+        <v>597</v>
       </c>
       <c r="AF27" s="55" t="s">
-        <v>607</v>
+        <v>603</v>
       </c>
       <c r="AG27" s="56" t="s">
-        <v>604</v>
+        <v>600</v>
       </c>
     </row>
     <row r="28" spans="1:33" ht="6" customHeight="1" x14ac:dyDescent="0.2">
@@ -11920,34 +11983,34 @@
         <v>181</v>
       </c>
       <c r="X28" s="55" t="s">
-        <v>607</v>
+        <v>603</v>
       </c>
       <c r="Y28" s="56" t="s">
+        <v>587</v>
+      </c>
+      <c r="Z28" s="55" t="s">
+        <v>603</v>
+      </c>
+      <c r="AA28" s="56" t="s">
         <v>591</v>
       </c>
-      <c r="Z28" s="55" t="s">
-        <v>607</v>
-      </c>
-      <c r="AA28" s="56" t="s">
-        <v>595</v>
-      </c>
       <c r="AB28" s="55" t="s">
-        <v>607</v>
+        <v>603</v>
       </c>
       <c r="AC28" s="56" t="s">
-        <v>598</v>
+        <v>594</v>
       </c>
       <c r="AD28" s="55" t="s">
-        <v>607</v>
+        <v>603</v>
       </c>
       <c r="AE28" s="56" t="s">
-        <v>601</v>
+        <v>597</v>
       </c>
       <c r="AF28" s="55" t="s">
-        <v>607</v>
+        <v>603</v>
       </c>
       <c r="AG28" s="56" t="s">
-        <v>604</v>
+        <v>600</v>
       </c>
     </row>
     <row r="29" spans="1:33" ht="6" customHeight="1" x14ac:dyDescent="0.2">
@@ -12021,34 +12084,34 @@
         <v>181</v>
       </c>
       <c r="X29" s="55" t="s">
-        <v>607</v>
+        <v>603</v>
       </c>
       <c r="Y29" s="56" t="s">
+        <v>587</v>
+      </c>
+      <c r="Z29" s="55" t="s">
+        <v>603</v>
+      </c>
+      <c r="AA29" s="56" t="s">
         <v>591</v>
       </c>
-      <c r="Z29" s="55" t="s">
-        <v>607</v>
-      </c>
-      <c r="AA29" s="56" t="s">
-        <v>595</v>
-      </c>
       <c r="AB29" s="55" t="s">
-        <v>607</v>
+        <v>603</v>
       </c>
       <c r="AC29" s="56" t="s">
-        <v>598</v>
+        <v>594</v>
       </c>
       <c r="AD29" s="55" t="s">
-        <v>607</v>
+        <v>603</v>
       </c>
       <c r="AE29" s="56" t="s">
-        <v>601</v>
+        <v>597</v>
       </c>
       <c r="AF29" s="55" t="s">
-        <v>607</v>
+        <v>603</v>
       </c>
       <c r="AG29" s="56" t="s">
-        <v>604</v>
+        <v>600</v>
       </c>
     </row>
     <row r="30" spans="1:33" ht="6" customHeight="1" x14ac:dyDescent="0.2">
@@ -12122,34 +12185,34 @@
         <v>181</v>
       </c>
       <c r="X30" s="55" t="s">
-        <v>607</v>
+        <v>603</v>
       </c>
       <c r="Y30" s="56" t="s">
+        <v>587</v>
+      </c>
+      <c r="Z30" s="55" t="s">
+        <v>603</v>
+      </c>
+      <c r="AA30" s="56" t="s">
         <v>591</v>
       </c>
-      <c r="Z30" s="55" t="s">
-        <v>607</v>
-      </c>
-      <c r="AA30" s="56" t="s">
-        <v>595</v>
-      </c>
       <c r="AB30" s="55" t="s">
-        <v>607</v>
+        <v>603</v>
       </c>
       <c r="AC30" s="56" t="s">
-        <v>598</v>
+        <v>594</v>
       </c>
       <c r="AD30" s="55" t="s">
-        <v>607</v>
+        <v>603</v>
       </c>
       <c r="AE30" s="56" t="s">
-        <v>601</v>
+        <v>597</v>
       </c>
       <c r="AF30" s="55" t="s">
-        <v>607</v>
+        <v>603</v>
       </c>
       <c r="AG30" s="56" t="s">
-        <v>604</v>
+        <v>600</v>
       </c>
     </row>
     <row r="31" spans="1:33" ht="6" customHeight="1" x14ac:dyDescent="0.2">
@@ -12223,34 +12286,34 @@
         <v>181</v>
       </c>
       <c r="X31" s="55" t="s">
-        <v>607</v>
+        <v>603</v>
       </c>
       <c r="Y31" s="56" t="s">
+        <v>587</v>
+      </c>
+      <c r="Z31" s="55" t="s">
+        <v>603</v>
+      </c>
+      <c r="AA31" s="56" t="s">
         <v>591</v>
       </c>
-      <c r="Z31" s="55" t="s">
-        <v>607</v>
-      </c>
-      <c r="AA31" s="56" t="s">
-        <v>595</v>
-      </c>
       <c r="AB31" s="55" t="s">
-        <v>607</v>
+        <v>603</v>
       </c>
       <c r="AC31" s="56" t="s">
-        <v>598</v>
+        <v>594</v>
       </c>
       <c r="AD31" s="55" t="s">
-        <v>607</v>
+        <v>603</v>
       </c>
       <c r="AE31" s="56" t="s">
-        <v>601</v>
+        <v>597</v>
       </c>
       <c r="AF31" s="55" t="s">
-        <v>607</v>
+        <v>603</v>
       </c>
       <c r="AG31" s="56" t="s">
-        <v>604</v>
+        <v>600</v>
       </c>
     </row>
     <row r="32" spans="1:33" ht="6" customHeight="1" x14ac:dyDescent="0.2">
@@ -12324,34 +12387,34 @@
         <v>181</v>
       </c>
       <c r="X32" s="55" t="s">
-        <v>607</v>
+        <v>603</v>
       </c>
       <c r="Y32" s="56" t="s">
+        <v>587</v>
+      </c>
+      <c r="Z32" s="55" t="s">
+        <v>603</v>
+      </c>
+      <c r="AA32" s="56" t="s">
         <v>591</v>
       </c>
-      <c r="Z32" s="55" t="s">
-        <v>607</v>
-      </c>
-      <c r="AA32" s="56" t="s">
-        <v>595</v>
-      </c>
       <c r="AB32" s="55" t="s">
-        <v>607</v>
+        <v>603</v>
       </c>
       <c r="AC32" s="56" t="s">
-        <v>598</v>
+        <v>594</v>
       </c>
       <c r="AD32" s="55" t="s">
-        <v>607</v>
+        <v>603</v>
       </c>
       <c r="AE32" s="56" t="s">
-        <v>601</v>
+        <v>597</v>
       </c>
       <c r="AF32" s="55" t="s">
-        <v>607</v>
+        <v>603</v>
       </c>
       <c r="AG32" s="56" t="s">
-        <v>604</v>
+        <v>600</v>
       </c>
     </row>
     <row r="33" spans="1:33" ht="6" customHeight="1" x14ac:dyDescent="0.2">
@@ -12425,34 +12488,34 @@
         <v>181</v>
       </c>
       <c r="X33" s="55" t="s">
-        <v>607</v>
+        <v>603</v>
       </c>
       <c r="Y33" s="56" t="s">
+        <v>587</v>
+      </c>
+      <c r="Z33" s="55" t="s">
+        <v>603</v>
+      </c>
+      <c r="AA33" s="56" t="s">
         <v>591</v>
       </c>
-      <c r="Z33" s="55" t="s">
-        <v>607</v>
-      </c>
-      <c r="AA33" s="56" t="s">
-        <v>595</v>
-      </c>
       <c r="AB33" s="55" t="s">
-        <v>607</v>
+        <v>603</v>
       </c>
       <c r="AC33" s="56" t="s">
-        <v>598</v>
+        <v>594</v>
       </c>
       <c r="AD33" s="55" t="s">
-        <v>607</v>
+        <v>603</v>
       </c>
       <c r="AE33" s="56" t="s">
-        <v>601</v>
+        <v>597</v>
       </c>
       <c r="AF33" s="55" t="s">
-        <v>607</v>
+        <v>603</v>
       </c>
       <c r="AG33" s="56" t="s">
-        <v>604</v>
+        <v>600</v>
       </c>
     </row>
     <row r="34" spans="1:33" ht="6" customHeight="1" x14ac:dyDescent="0.2">
@@ -12526,34 +12589,34 @@
         <v>181</v>
       </c>
       <c r="X34" s="55" t="s">
-        <v>607</v>
+        <v>603</v>
       </c>
       <c r="Y34" s="56" t="s">
+        <v>587</v>
+      </c>
+      <c r="Z34" s="55" t="s">
+        <v>603</v>
+      </c>
+      <c r="AA34" s="56" t="s">
         <v>591</v>
       </c>
-      <c r="Z34" s="55" t="s">
-        <v>607</v>
-      </c>
-      <c r="AA34" s="56" t="s">
-        <v>595</v>
-      </c>
       <c r="AB34" s="55" t="s">
-        <v>607</v>
+        <v>603</v>
       </c>
       <c r="AC34" s="56" t="s">
-        <v>598</v>
+        <v>594</v>
       </c>
       <c r="AD34" s="55" t="s">
-        <v>607</v>
+        <v>603</v>
       </c>
       <c r="AE34" s="56" t="s">
-        <v>601</v>
+        <v>597</v>
       </c>
       <c r="AF34" s="55" t="s">
-        <v>607</v>
+        <v>603</v>
       </c>
       <c r="AG34" s="56" t="s">
-        <v>604</v>
+        <v>600</v>
       </c>
     </row>
     <row r="35" spans="1:33" ht="6" customHeight="1" x14ac:dyDescent="0.2">
@@ -12627,34 +12690,34 @@
         <v>181</v>
       </c>
       <c r="X35" s="55" t="s">
-        <v>607</v>
+        <v>603</v>
       </c>
       <c r="Y35" s="56" t="s">
+        <v>587</v>
+      </c>
+      <c r="Z35" s="55" t="s">
+        <v>603</v>
+      </c>
+      <c r="AA35" s="56" t="s">
         <v>591</v>
       </c>
-      <c r="Z35" s="55" t="s">
-        <v>607</v>
-      </c>
-      <c r="AA35" s="56" t="s">
-        <v>595</v>
-      </c>
       <c r="AB35" s="55" t="s">
-        <v>607</v>
+        <v>603</v>
       </c>
       <c r="AC35" s="56" t="s">
-        <v>598</v>
+        <v>594</v>
       </c>
       <c r="AD35" s="55" t="s">
-        <v>607</v>
+        <v>603</v>
       </c>
       <c r="AE35" s="56" t="s">
-        <v>601</v>
+        <v>597</v>
       </c>
       <c r="AF35" s="55" t="s">
-        <v>607</v>
+        <v>603</v>
       </c>
       <c r="AG35" s="56" t="s">
-        <v>604</v>
+        <v>600</v>
       </c>
     </row>
     <row r="36" spans="1:33" ht="6" customHeight="1" x14ac:dyDescent="0.2">
@@ -12728,34 +12791,34 @@
         <v>181</v>
       </c>
       <c r="X36" s="55" t="s">
-        <v>607</v>
+        <v>603</v>
       </c>
       <c r="Y36" s="56" t="s">
+        <v>587</v>
+      </c>
+      <c r="Z36" s="55" t="s">
+        <v>603</v>
+      </c>
+      <c r="AA36" s="56" t="s">
         <v>591</v>
       </c>
-      <c r="Z36" s="55" t="s">
-        <v>607</v>
-      </c>
-      <c r="AA36" s="56" t="s">
-        <v>595</v>
-      </c>
       <c r="AB36" s="55" t="s">
-        <v>607</v>
+        <v>603</v>
       </c>
       <c r="AC36" s="56" t="s">
-        <v>598</v>
+        <v>594</v>
       </c>
       <c r="AD36" s="55" t="s">
-        <v>607</v>
+        <v>603</v>
       </c>
       <c r="AE36" s="56" t="s">
-        <v>601</v>
+        <v>597</v>
       </c>
       <c r="AF36" s="55" t="s">
-        <v>607</v>
+        <v>603</v>
       </c>
       <c r="AG36" s="56" t="s">
-        <v>604</v>
+        <v>600</v>
       </c>
     </row>
     <row r="37" spans="1:33" ht="6" customHeight="1" x14ac:dyDescent="0.2">
@@ -12829,34 +12892,34 @@
         <v>181</v>
       </c>
       <c r="X37" s="55" t="s">
-        <v>607</v>
+        <v>603</v>
       </c>
       <c r="Y37" s="56" t="s">
+        <v>587</v>
+      </c>
+      <c r="Z37" s="55" t="s">
+        <v>603</v>
+      </c>
+      <c r="AA37" s="56" t="s">
         <v>591</v>
       </c>
-      <c r="Z37" s="55" t="s">
-        <v>607</v>
-      </c>
-      <c r="AA37" s="56" t="s">
-        <v>595</v>
-      </c>
       <c r="AB37" s="55" t="s">
-        <v>607</v>
+        <v>603</v>
       </c>
       <c r="AC37" s="56" t="s">
-        <v>598</v>
+        <v>594</v>
       </c>
       <c r="AD37" s="55" t="s">
-        <v>607</v>
+        <v>603</v>
       </c>
       <c r="AE37" s="56" t="s">
-        <v>601</v>
+        <v>597</v>
       </c>
       <c r="AF37" s="55" t="s">
-        <v>607</v>
+        <v>603</v>
       </c>
       <c r="AG37" s="56" t="s">
-        <v>604</v>
+        <v>600</v>
       </c>
     </row>
     <row r="38" spans="1:33" ht="6" customHeight="1" x14ac:dyDescent="0.2">
@@ -12930,34 +12993,34 @@
         <v>181</v>
       </c>
       <c r="X38" s="55" t="s">
-        <v>607</v>
+        <v>603</v>
       </c>
       <c r="Y38" s="56" t="s">
+        <v>587</v>
+      </c>
+      <c r="Z38" s="55" t="s">
+        <v>603</v>
+      </c>
+      <c r="AA38" s="56" t="s">
         <v>591</v>
       </c>
-      <c r="Z38" s="55" t="s">
-        <v>607</v>
-      </c>
-      <c r="AA38" s="56" t="s">
-        <v>595</v>
-      </c>
       <c r="AB38" s="55" t="s">
-        <v>607</v>
+        <v>603</v>
       </c>
       <c r="AC38" s="56" t="s">
-        <v>598</v>
+        <v>594</v>
       </c>
       <c r="AD38" s="55" t="s">
-        <v>607</v>
+        <v>603</v>
       </c>
       <c r="AE38" s="56" t="s">
-        <v>601</v>
+        <v>597</v>
       </c>
       <c r="AF38" s="55" t="s">
-        <v>607</v>
+        <v>603</v>
       </c>
       <c r="AG38" s="56" t="s">
-        <v>604</v>
+        <v>600</v>
       </c>
     </row>
     <row r="39" spans="1:33" ht="6" customHeight="1" x14ac:dyDescent="0.2">
@@ -13031,34 +13094,34 @@
         <v>181</v>
       </c>
       <c r="X39" s="55" t="s">
-        <v>607</v>
+        <v>603</v>
       </c>
       <c r="Y39" s="56" t="s">
+        <v>587</v>
+      </c>
+      <c r="Z39" s="55" t="s">
+        <v>603</v>
+      </c>
+      <c r="AA39" s="56" t="s">
         <v>591</v>
       </c>
-      <c r="Z39" s="55" t="s">
-        <v>607</v>
-      </c>
-      <c r="AA39" s="56" t="s">
-        <v>595</v>
-      </c>
       <c r="AB39" s="55" t="s">
-        <v>607</v>
+        <v>603</v>
       </c>
       <c r="AC39" s="56" t="s">
-        <v>598</v>
+        <v>594</v>
       </c>
       <c r="AD39" s="55" t="s">
-        <v>607</v>
+        <v>603</v>
       </c>
       <c r="AE39" s="56" t="s">
-        <v>601</v>
+        <v>597</v>
       </c>
       <c r="AF39" s="55" t="s">
-        <v>607</v>
+        <v>603</v>
       </c>
       <c r="AG39" s="56" t="s">
-        <v>604</v>
+        <v>600</v>
       </c>
     </row>
     <row r="40" spans="1:33" ht="6" customHeight="1" x14ac:dyDescent="0.2">
@@ -13132,34 +13195,34 @@
         <v>181</v>
       </c>
       <c r="X40" s="55" t="s">
-        <v>607</v>
+        <v>603</v>
       </c>
       <c r="Y40" s="56" t="s">
+        <v>587</v>
+      </c>
+      <c r="Z40" s="55" t="s">
+        <v>603</v>
+      </c>
+      <c r="AA40" s="56" t="s">
         <v>591</v>
       </c>
-      <c r="Z40" s="55" t="s">
-        <v>607</v>
-      </c>
-      <c r="AA40" s="56" t="s">
-        <v>595</v>
-      </c>
       <c r="AB40" s="55" t="s">
-        <v>607</v>
+        <v>603</v>
       </c>
       <c r="AC40" s="56" t="s">
-        <v>598</v>
+        <v>594</v>
       </c>
       <c r="AD40" s="55" t="s">
-        <v>607</v>
+        <v>603</v>
       </c>
       <c r="AE40" s="56" t="s">
-        <v>601</v>
+        <v>597</v>
       </c>
       <c r="AF40" s="55" t="s">
-        <v>607</v>
+        <v>603</v>
       </c>
       <c r="AG40" s="56" t="s">
-        <v>604</v>
+        <v>600</v>
       </c>
     </row>
     <row r="41" spans="1:33" ht="6" customHeight="1" x14ac:dyDescent="0.2">
@@ -13233,34 +13296,34 @@
         <v>181</v>
       </c>
       <c r="X41" s="55" t="s">
-        <v>607</v>
+        <v>603</v>
       </c>
       <c r="Y41" s="56" t="s">
+        <v>587</v>
+      </c>
+      <c r="Z41" s="55" t="s">
+        <v>603</v>
+      </c>
+      <c r="AA41" s="56" t="s">
         <v>591</v>
       </c>
-      <c r="Z41" s="55" t="s">
-        <v>607</v>
-      </c>
-      <c r="AA41" s="56" t="s">
-        <v>595</v>
-      </c>
       <c r="AB41" s="55" t="s">
-        <v>607</v>
+        <v>603</v>
       </c>
       <c r="AC41" s="56" t="s">
-        <v>598</v>
+        <v>594</v>
       </c>
       <c r="AD41" s="55" t="s">
-        <v>607</v>
+        <v>603</v>
       </c>
       <c r="AE41" s="56" t="s">
-        <v>601</v>
+        <v>597</v>
       </c>
       <c r="AF41" s="55" t="s">
-        <v>607</v>
+        <v>603</v>
       </c>
       <c r="AG41" s="56" t="s">
-        <v>604</v>
+        <v>600</v>
       </c>
     </row>
     <row r="42" spans="1:33" ht="6" customHeight="1" x14ac:dyDescent="0.2">
@@ -13334,34 +13397,34 @@
         <v>181</v>
       </c>
       <c r="X42" s="55" t="s">
-        <v>607</v>
+        <v>603</v>
       </c>
       <c r="Y42" s="56" t="s">
+        <v>587</v>
+      </c>
+      <c r="Z42" s="55" t="s">
+        <v>603</v>
+      </c>
+      <c r="AA42" s="56" t="s">
         <v>591</v>
       </c>
-      <c r="Z42" s="55" t="s">
-        <v>607</v>
-      </c>
-      <c r="AA42" s="56" t="s">
-        <v>595</v>
-      </c>
       <c r="AB42" s="55" t="s">
-        <v>607</v>
+        <v>603</v>
       </c>
       <c r="AC42" s="56" t="s">
-        <v>598</v>
+        <v>594</v>
       </c>
       <c r="AD42" s="55" t="s">
-        <v>607</v>
+        <v>603</v>
       </c>
       <c r="AE42" s="56" t="s">
-        <v>601</v>
+        <v>597</v>
       </c>
       <c r="AF42" s="55" t="s">
-        <v>607</v>
+        <v>603</v>
       </c>
       <c r="AG42" s="56" t="s">
-        <v>604</v>
+        <v>600</v>
       </c>
     </row>
     <row r="43" spans="1:33" ht="6" customHeight="1" x14ac:dyDescent="0.2">
@@ -13435,34 +13498,34 @@
         <v>181</v>
       </c>
       <c r="X43" s="55" t="s">
-        <v>607</v>
+        <v>603</v>
       </c>
       <c r="Y43" s="56" t="s">
+        <v>587</v>
+      </c>
+      <c r="Z43" s="55" t="s">
+        <v>603</v>
+      </c>
+      <c r="AA43" s="56" t="s">
         <v>591</v>
       </c>
-      <c r="Z43" s="55" t="s">
-        <v>607</v>
-      </c>
-      <c r="AA43" s="56" t="s">
-        <v>595</v>
-      </c>
       <c r="AB43" s="55" t="s">
-        <v>607</v>
+        <v>603</v>
       </c>
       <c r="AC43" s="56" t="s">
-        <v>598</v>
+        <v>594</v>
       </c>
       <c r="AD43" s="55" t="s">
-        <v>607</v>
+        <v>603</v>
       </c>
       <c r="AE43" s="56" t="s">
-        <v>601</v>
+        <v>597</v>
       </c>
       <c r="AF43" s="55" t="s">
-        <v>607</v>
+        <v>603</v>
       </c>
       <c r="AG43" s="56" t="s">
-        <v>604</v>
+        <v>600</v>
       </c>
     </row>
     <row r="44" spans="1:33" ht="6" customHeight="1" x14ac:dyDescent="0.2">
@@ -13536,34 +13599,34 @@
         <v>181</v>
       </c>
       <c r="X44" s="55" t="s">
-        <v>607</v>
+        <v>603</v>
       </c>
       <c r="Y44" s="56" t="s">
+        <v>587</v>
+      </c>
+      <c r="Z44" s="55" t="s">
+        <v>603</v>
+      </c>
+      <c r="AA44" s="56" t="s">
         <v>591</v>
       </c>
-      <c r="Z44" s="55" t="s">
-        <v>607</v>
-      </c>
-      <c r="AA44" s="56" t="s">
-        <v>595</v>
-      </c>
       <c r="AB44" s="55" t="s">
-        <v>607</v>
+        <v>603</v>
       </c>
       <c r="AC44" s="56" t="s">
-        <v>598</v>
+        <v>594</v>
       </c>
       <c r="AD44" s="55" t="s">
-        <v>607</v>
+        <v>603</v>
       </c>
       <c r="AE44" s="56" t="s">
-        <v>601</v>
+        <v>597</v>
       </c>
       <c r="AF44" s="55" t="s">
-        <v>607</v>
+        <v>603</v>
       </c>
       <c r="AG44" s="56" t="s">
-        <v>604</v>
+        <v>600</v>
       </c>
     </row>
     <row r="45" spans="1:33" ht="6" customHeight="1" x14ac:dyDescent="0.2">
@@ -13637,34 +13700,34 @@
         <v>181</v>
       </c>
       <c r="X45" s="55" t="s">
-        <v>607</v>
+        <v>603</v>
       </c>
       <c r="Y45" s="56" t="s">
+        <v>587</v>
+      </c>
+      <c r="Z45" s="55" t="s">
+        <v>603</v>
+      </c>
+      <c r="AA45" s="56" t="s">
         <v>591</v>
       </c>
-      <c r="Z45" s="55" t="s">
-        <v>607</v>
-      </c>
-      <c r="AA45" s="56" t="s">
-        <v>595</v>
-      </c>
       <c r="AB45" s="55" t="s">
-        <v>607</v>
+        <v>603</v>
       </c>
       <c r="AC45" s="56" t="s">
-        <v>598</v>
+        <v>594</v>
       </c>
       <c r="AD45" s="55" t="s">
-        <v>607</v>
+        <v>603</v>
       </c>
       <c r="AE45" s="56" t="s">
-        <v>601</v>
+        <v>597</v>
       </c>
       <c r="AF45" s="55" t="s">
-        <v>607</v>
+        <v>603</v>
       </c>
       <c r="AG45" s="56" t="s">
-        <v>604</v>
+        <v>600</v>
       </c>
     </row>
     <row r="46" spans="1:33" ht="6" customHeight="1" x14ac:dyDescent="0.2">
@@ -13738,34 +13801,34 @@
         <v>181</v>
       </c>
       <c r="X46" s="55" t="s">
-        <v>607</v>
+        <v>603</v>
       </c>
       <c r="Y46" s="56" t="s">
+        <v>587</v>
+      </c>
+      <c r="Z46" s="55" t="s">
+        <v>603</v>
+      </c>
+      <c r="AA46" s="56" t="s">
         <v>591</v>
       </c>
-      <c r="Z46" s="55" t="s">
-        <v>607</v>
-      </c>
-      <c r="AA46" s="56" t="s">
-        <v>595</v>
-      </c>
       <c r="AB46" s="55" t="s">
-        <v>607</v>
+        <v>603</v>
       </c>
       <c r="AC46" s="56" t="s">
-        <v>598</v>
+        <v>594</v>
       </c>
       <c r="AD46" s="55" t="s">
-        <v>607</v>
+        <v>603</v>
       </c>
       <c r="AE46" s="56" t="s">
-        <v>601</v>
+        <v>597</v>
       </c>
       <c r="AF46" s="55" t="s">
-        <v>607</v>
+        <v>603</v>
       </c>
       <c r="AG46" s="56" t="s">
-        <v>604</v>
+        <v>600</v>
       </c>
     </row>
     <row r="47" spans="1:33" ht="6" customHeight="1" x14ac:dyDescent="0.2">
@@ -13839,34 +13902,34 @@
         <v>181</v>
       </c>
       <c r="X47" s="55" t="s">
-        <v>607</v>
+        <v>603</v>
       </c>
       <c r="Y47" s="56" t="s">
+        <v>587</v>
+      </c>
+      <c r="Z47" s="55" t="s">
+        <v>603</v>
+      </c>
+      <c r="AA47" s="56" t="s">
         <v>591</v>
       </c>
-      <c r="Z47" s="55" t="s">
-        <v>607</v>
-      </c>
-      <c r="AA47" s="56" t="s">
-        <v>595</v>
-      </c>
       <c r="AB47" s="55" t="s">
-        <v>607</v>
+        <v>603</v>
       </c>
       <c r="AC47" s="56" t="s">
-        <v>598</v>
+        <v>594</v>
       </c>
       <c r="AD47" s="55" t="s">
-        <v>607</v>
+        <v>603</v>
       </c>
       <c r="AE47" s="56" t="s">
-        <v>601</v>
+        <v>597</v>
       </c>
       <c r="AF47" s="55" t="s">
-        <v>607</v>
+        <v>603</v>
       </c>
       <c r="AG47" s="56" t="s">
-        <v>604</v>
+        <v>600</v>
       </c>
     </row>
     <row r="48" spans="1:33" ht="6" customHeight="1" x14ac:dyDescent="0.2">
@@ -13940,34 +14003,34 @@
         <v>181</v>
       </c>
       <c r="X48" s="55" t="s">
-        <v>607</v>
+        <v>603</v>
       </c>
       <c r="Y48" s="56" t="s">
+        <v>587</v>
+      </c>
+      <c r="Z48" s="55" t="s">
+        <v>603</v>
+      </c>
+      <c r="AA48" s="56" t="s">
         <v>591</v>
       </c>
-      <c r="Z48" s="55" t="s">
-        <v>607</v>
-      </c>
-      <c r="AA48" s="56" t="s">
-        <v>595</v>
-      </c>
       <c r="AB48" s="55" t="s">
-        <v>607</v>
+        <v>603</v>
       </c>
       <c r="AC48" s="56" t="s">
-        <v>598</v>
+        <v>594</v>
       </c>
       <c r="AD48" s="55" t="s">
-        <v>607</v>
+        <v>603</v>
       </c>
       <c r="AE48" s="56" t="s">
-        <v>601</v>
+        <v>597</v>
       </c>
       <c r="AF48" s="55" t="s">
-        <v>607</v>
+        <v>603</v>
       </c>
       <c r="AG48" s="56" t="s">
-        <v>604</v>
+        <v>600</v>
       </c>
     </row>
     <row r="49" spans="1:33" ht="6" customHeight="1" x14ac:dyDescent="0.2">
@@ -14041,34 +14104,34 @@
         <v>181</v>
       </c>
       <c r="X49" s="55" t="s">
-        <v>607</v>
+        <v>603</v>
       </c>
       <c r="Y49" s="56" t="s">
+        <v>587</v>
+      </c>
+      <c r="Z49" s="55" t="s">
+        <v>603</v>
+      </c>
+      <c r="AA49" s="56" t="s">
         <v>591</v>
       </c>
-      <c r="Z49" s="55" t="s">
-        <v>607</v>
-      </c>
-      <c r="AA49" s="56" t="s">
-        <v>595</v>
-      </c>
       <c r="AB49" s="55" t="s">
-        <v>607</v>
+        <v>603</v>
       </c>
       <c r="AC49" s="56" t="s">
-        <v>598</v>
+        <v>594</v>
       </c>
       <c r="AD49" s="55" t="s">
-        <v>607</v>
+        <v>603</v>
       </c>
       <c r="AE49" s="56" t="s">
-        <v>601</v>
+        <v>597</v>
       </c>
       <c r="AF49" s="55" t="s">
-        <v>607</v>
+        <v>603</v>
       </c>
       <c r="AG49" s="56" t="s">
-        <v>604</v>
+        <v>600</v>
       </c>
     </row>
     <row r="50" spans="1:33" ht="6" customHeight="1" x14ac:dyDescent="0.2">
@@ -14142,34 +14205,34 @@
         <v>181</v>
       </c>
       <c r="X50" s="55" t="s">
-        <v>607</v>
+        <v>603</v>
       </c>
       <c r="Y50" s="56" t="s">
+        <v>587</v>
+      </c>
+      <c r="Z50" s="55" t="s">
+        <v>603</v>
+      </c>
+      <c r="AA50" s="56" t="s">
         <v>591</v>
       </c>
-      <c r="Z50" s="55" t="s">
-        <v>607</v>
-      </c>
-      <c r="AA50" s="56" t="s">
-        <v>595</v>
-      </c>
       <c r="AB50" s="55" t="s">
-        <v>607</v>
+        <v>603</v>
       </c>
       <c r="AC50" s="56" t="s">
-        <v>598</v>
+        <v>594</v>
       </c>
       <c r="AD50" s="55" t="s">
-        <v>607</v>
+        <v>603</v>
       </c>
       <c r="AE50" s="56" t="s">
-        <v>601</v>
+        <v>597</v>
       </c>
       <c r="AF50" s="55" t="s">
-        <v>607</v>
+        <v>603</v>
       </c>
       <c r="AG50" s="56" t="s">
-        <v>604</v>
+        <v>600</v>
       </c>
     </row>
     <row r="51" spans="1:33" ht="6" customHeight="1" x14ac:dyDescent="0.2">
@@ -14243,34 +14306,34 @@
         <v>181</v>
       </c>
       <c r="X51" s="55" t="s">
-        <v>607</v>
+        <v>603</v>
       </c>
       <c r="Y51" s="56" t="s">
+        <v>587</v>
+      </c>
+      <c r="Z51" s="55" t="s">
+        <v>603</v>
+      </c>
+      <c r="AA51" s="56" t="s">
         <v>591</v>
       </c>
-      <c r="Z51" s="55" t="s">
-        <v>607</v>
-      </c>
-      <c r="AA51" s="56" t="s">
-        <v>595</v>
-      </c>
       <c r="AB51" s="55" t="s">
-        <v>607</v>
+        <v>603</v>
       </c>
       <c r="AC51" s="56" t="s">
-        <v>598</v>
+        <v>594</v>
       </c>
       <c r="AD51" s="55" t="s">
-        <v>607</v>
+        <v>603</v>
       </c>
       <c r="AE51" s="56" t="s">
-        <v>601</v>
+        <v>597</v>
       </c>
       <c r="AF51" s="55" t="s">
-        <v>607</v>
+        <v>603</v>
       </c>
       <c r="AG51" s="56" t="s">
-        <v>604</v>
+        <v>600</v>
       </c>
     </row>
     <row r="52" spans="1:33" ht="6" customHeight="1" x14ac:dyDescent="0.2">
@@ -14344,34 +14407,34 @@
         <v>181</v>
       </c>
       <c r="X52" s="55" t="s">
-        <v>607</v>
+        <v>603</v>
       </c>
       <c r="Y52" s="56" t="s">
+        <v>587</v>
+      </c>
+      <c r="Z52" s="55" t="s">
+        <v>603</v>
+      </c>
+      <c r="AA52" s="56" t="s">
         <v>591</v>
       </c>
-      <c r="Z52" s="55" t="s">
-        <v>607</v>
-      </c>
-      <c r="AA52" s="56" t="s">
-        <v>595</v>
-      </c>
       <c r="AB52" s="55" t="s">
-        <v>607</v>
+        <v>603</v>
       </c>
       <c r="AC52" s="56" t="s">
-        <v>598</v>
+        <v>594</v>
       </c>
       <c r="AD52" s="55" t="s">
-        <v>607</v>
+        <v>603</v>
       </c>
       <c r="AE52" s="56" t="s">
-        <v>601</v>
+        <v>597</v>
       </c>
       <c r="AF52" s="55" t="s">
-        <v>607</v>
+        <v>603</v>
       </c>
       <c r="AG52" s="56" t="s">
-        <v>604</v>
+        <v>600</v>
       </c>
     </row>
     <row r="53" spans="1:33" ht="6" customHeight="1" x14ac:dyDescent="0.2">
@@ -14445,34 +14508,34 @@
         <v>181</v>
       </c>
       <c r="X53" s="55" t="s">
-        <v>607</v>
+        <v>603</v>
       </c>
       <c r="Y53" s="56" t="s">
+        <v>587</v>
+      </c>
+      <c r="Z53" s="55" t="s">
+        <v>603</v>
+      </c>
+      <c r="AA53" s="56" t="s">
         <v>591</v>
       </c>
-      <c r="Z53" s="55" t="s">
-        <v>607</v>
-      </c>
-      <c r="AA53" s="56" t="s">
-        <v>595</v>
-      </c>
       <c r="AB53" s="55" t="s">
-        <v>607</v>
+        <v>603</v>
       </c>
       <c r="AC53" s="56" t="s">
-        <v>598</v>
+        <v>594</v>
       </c>
       <c r="AD53" s="55" t="s">
-        <v>607</v>
+        <v>603</v>
       </c>
       <c r="AE53" s="56" t="s">
-        <v>601</v>
+        <v>597</v>
       </c>
       <c r="AF53" s="55" t="s">
-        <v>607</v>
+        <v>603</v>
       </c>
       <c r="AG53" s="56" t="s">
-        <v>604</v>
+        <v>600</v>
       </c>
     </row>
     <row r="54" spans="1:33" ht="6" customHeight="1" x14ac:dyDescent="0.2">
@@ -14546,34 +14609,34 @@
         <v>181</v>
       </c>
       <c r="X54" s="55" t="s">
-        <v>607</v>
+        <v>603</v>
       </c>
       <c r="Y54" s="56" t="s">
+        <v>587</v>
+      </c>
+      <c r="Z54" s="55" t="s">
+        <v>603</v>
+      </c>
+      <c r="AA54" s="56" t="s">
         <v>591</v>
       </c>
-      <c r="Z54" s="55" t="s">
-        <v>607</v>
-      </c>
-      <c r="AA54" s="56" t="s">
-        <v>595</v>
-      </c>
       <c r="AB54" s="55" t="s">
-        <v>607</v>
+        <v>603</v>
       </c>
       <c r="AC54" s="56" t="s">
-        <v>598</v>
+        <v>594</v>
       </c>
       <c r="AD54" s="55" t="s">
-        <v>607</v>
+        <v>603</v>
       </c>
       <c r="AE54" s="56" t="s">
-        <v>601</v>
+        <v>597</v>
       </c>
       <c r="AF54" s="55" t="s">
-        <v>607</v>
+        <v>603</v>
       </c>
       <c r="AG54" s="56" t="s">
-        <v>604</v>
+        <v>600</v>
       </c>
     </row>
     <row r="55" spans="1:33" ht="6" customHeight="1" x14ac:dyDescent="0.2">
@@ -14647,34 +14710,34 @@
         <v>181</v>
       </c>
       <c r="X55" s="55" t="s">
-        <v>607</v>
+        <v>603</v>
       </c>
       <c r="Y55" s="56" t="s">
+        <v>587</v>
+      </c>
+      <c r="Z55" s="55" t="s">
+        <v>603</v>
+      </c>
+      <c r="AA55" s="56" t="s">
         <v>591</v>
       </c>
-      <c r="Z55" s="55" t="s">
-        <v>607</v>
-      </c>
-      <c r="AA55" s="56" t="s">
-        <v>595</v>
-      </c>
       <c r="AB55" s="55" t="s">
-        <v>607</v>
+        <v>603</v>
       </c>
       <c r="AC55" s="56" t="s">
-        <v>598</v>
+        <v>594</v>
       </c>
       <c r="AD55" s="55" t="s">
-        <v>607</v>
+        <v>603</v>
       </c>
       <c r="AE55" s="56" t="s">
-        <v>601</v>
+        <v>597</v>
       </c>
       <c r="AF55" s="55" t="s">
-        <v>607</v>
+        <v>603</v>
       </c>
       <c r="AG55" s="56" t="s">
-        <v>604</v>
+        <v>600</v>
       </c>
     </row>
     <row r="56" spans="1:33" ht="6" customHeight="1" x14ac:dyDescent="0.2">
@@ -14748,34 +14811,34 @@
         <v>181</v>
       </c>
       <c r="X56" s="55" t="s">
-        <v>607</v>
+        <v>603</v>
       </c>
       <c r="Y56" s="56" t="s">
+        <v>587</v>
+      </c>
+      <c r="Z56" s="55" t="s">
+        <v>603</v>
+      </c>
+      <c r="AA56" s="56" t="s">
         <v>591</v>
       </c>
-      <c r="Z56" s="55" t="s">
-        <v>607</v>
-      </c>
-      <c r="AA56" s="56" t="s">
-        <v>595</v>
-      </c>
       <c r="AB56" s="55" t="s">
-        <v>607</v>
+        <v>603</v>
       </c>
       <c r="AC56" s="56" t="s">
-        <v>598</v>
+        <v>594</v>
       </c>
       <c r="AD56" s="55" t="s">
-        <v>607</v>
+        <v>603</v>
       </c>
       <c r="AE56" s="56" t="s">
-        <v>601</v>
+        <v>597</v>
       </c>
       <c r="AF56" s="55" t="s">
-        <v>607</v>
+        <v>603</v>
       </c>
       <c r="AG56" s="56" t="s">
-        <v>604</v>
+        <v>600</v>
       </c>
     </row>
     <row r="57" spans="1:33" ht="6" customHeight="1" x14ac:dyDescent="0.2">
@@ -14849,34 +14912,34 @@
         <v>181</v>
       </c>
       <c r="X57" s="55" t="s">
-        <v>607</v>
+        <v>603</v>
       </c>
       <c r="Y57" s="56" t="s">
+        <v>587</v>
+      </c>
+      <c r="Z57" s="55" t="s">
+        <v>603</v>
+      </c>
+      <c r="AA57" s="56" t="s">
         <v>591</v>
       </c>
-      <c r="Z57" s="55" t="s">
-        <v>607</v>
-      </c>
-      <c r="AA57" s="56" t="s">
-        <v>595</v>
-      </c>
       <c r="AB57" s="55" t="s">
-        <v>607</v>
+        <v>603</v>
       </c>
       <c r="AC57" s="56" t="s">
-        <v>598</v>
+        <v>594</v>
       </c>
       <c r="AD57" s="55" t="s">
-        <v>607</v>
+        <v>603</v>
       </c>
       <c r="AE57" s="56" t="s">
-        <v>601</v>
+        <v>597</v>
       </c>
       <c r="AF57" s="55" t="s">
-        <v>607</v>
+        <v>603</v>
       </c>
       <c r="AG57" s="56" t="s">
-        <v>604</v>
+        <v>600</v>
       </c>
     </row>
     <row r="58" spans="1:33" ht="6" customHeight="1" x14ac:dyDescent="0.2">
@@ -14950,34 +15013,34 @@
         <v>181</v>
       </c>
       <c r="X58" s="55" t="s">
-        <v>607</v>
+        <v>603</v>
       </c>
       <c r="Y58" s="56" t="s">
+        <v>587</v>
+      </c>
+      <c r="Z58" s="55" t="s">
+        <v>603</v>
+      </c>
+      <c r="AA58" s="56" t="s">
         <v>591</v>
       </c>
-      <c r="Z58" s="55" t="s">
-        <v>607</v>
-      </c>
-      <c r="AA58" s="56" t="s">
-        <v>595</v>
-      </c>
       <c r="AB58" s="55" t="s">
-        <v>607</v>
+        <v>603</v>
       </c>
       <c r="AC58" s="56" t="s">
-        <v>598</v>
+        <v>594</v>
       </c>
       <c r="AD58" s="55" t="s">
-        <v>607</v>
+        <v>603</v>
       </c>
       <c r="AE58" s="56" t="s">
-        <v>601</v>
+        <v>597</v>
       </c>
       <c r="AF58" s="55" t="s">
-        <v>607</v>
+        <v>603</v>
       </c>
       <c r="AG58" s="56" t="s">
-        <v>604</v>
+        <v>600</v>
       </c>
     </row>
     <row r="59" spans="1:33" ht="6" customHeight="1" x14ac:dyDescent="0.2">
@@ -15051,34 +15114,34 @@
         <v>181</v>
       </c>
       <c r="X59" s="55" t="s">
-        <v>607</v>
+        <v>603</v>
       </c>
       <c r="Y59" s="56" t="s">
+        <v>587</v>
+      </c>
+      <c r="Z59" s="55" t="s">
+        <v>603</v>
+      </c>
+      <c r="AA59" s="56" t="s">
         <v>591</v>
       </c>
-      <c r="Z59" s="55" t="s">
-        <v>607</v>
-      </c>
-      <c r="AA59" s="56" t="s">
-        <v>595</v>
-      </c>
       <c r="AB59" s="55" t="s">
-        <v>607</v>
+        <v>603</v>
       </c>
       <c r="AC59" s="56" t="s">
-        <v>598</v>
+        <v>594</v>
       </c>
       <c r="AD59" s="55" t="s">
-        <v>607</v>
+        <v>603</v>
       </c>
       <c r="AE59" s="56" t="s">
-        <v>601</v>
+        <v>597</v>
       </c>
       <c r="AF59" s="55" t="s">
-        <v>607</v>
+        <v>603</v>
       </c>
       <c r="AG59" s="56" t="s">
-        <v>604</v>
+        <v>600</v>
       </c>
     </row>
     <row r="60" spans="1:33" ht="6" customHeight="1" x14ac:dyDescent="0.2">
@@ -15152,34 +15215,34 @@
         <v>181</v>
       </c>
       <c r="X60" s="55" t="s">
-        <v>607</v>
+        <v>603</v>
       </c>
       <c r="Y60" s="56" t="s">
+        <v>587</v>
+      </c>
+      <c r="Z60" s="55" t="s">
+        <v>603</v>
+      </c>
+      <c r="AA60" s="56" t="s">
         <v>591</v>
       </c>
-      <c r="Z60" s="55" t="s">
-        <v>607</v>
-      </c>
-      <c r="AA60" s="56" t="s">
-        <v>595</v>
-      </c>
       <c r="AB60" s="55" t="s">
-        <v>607</v>
+        <v>603</v>
       </c>
       <c r="AC60" s="56" t="s">
-        <v>598</v>
+        <v>594</v>
       </c>
       <c r="AD60" s="55" t="s">
-        <v>607</v>
+        <v>603</v>
       </c>
       <c r="AE60" s="56" t="s">
-        <v>601</v>
+        <v>597</v>
       </c>
       <c r="AF60" s="55" t="s">
-        <v>607</v>
+        <v>603</v>
       </c>
       <c r="AG60" s="56" t="s">
-        <v>604</v>
+        <v>600</v>
       </c>
     </row>
     <row r="61" spans="1:33" ht="6" customHeight="1" x14ac:dyDescent="0.2">
@@ -15253,34 +15316,34 @@
         <v>181</v>
       </c>
       <c r="X61" s="55" t="s">
-        <v>607</v>
+        <v>603</v>
       </c>
       <c r="Y61" s="56" t="s">
+        <v>587</v>
+      </c>
+      <c r="Z61" s="55" t="s">
+        <v>603</v>
+      </c>
+      <c r="AA61" s="56" t="s">
         <v>591</v>
       </c>
-      <c r="Z61" s="55" t="s">
-        <v>607</v>
-      </c>
-      <c r="AA61" s="56" t="s">
-        <v>595</v>
-      </c>
       <c r="AB61" s="55" t="s">
-        <v>607</v>
+        <v>603</v>
       </c>
       <c r="AC61" s="56" t="s">
-        <v>598</v>
+        <v>594</v>
       </c>
       <c r="AD61" s="55" t="s">
-        <v>607</v>
+        <v>603</v>
       </c>
       <c r="AE61" s="56" t="s">
-        <v>601</v>
+        <v>597</v>
       </c>
       <c r="AF61" s="55" t="s">
-        <v>607</v>
+        <v>603</v>
       </c>
       <c r="AG61" s="56" t="s">
-        <v>604</v>
+        <v>600</v>
       </c>
     </row>
     <row r="62" spans="1:33" ht="6" customHeight="1" x14ac:dyDescent="0.2">
@@ -15354,34 +15417,34 @@
         <v>181</v>
       </c>
       <c r="X62" s="55" t="s">
-        <v>607</v>
+        <v>603</v>
       </c>
       <c r="Y62" s="56" t="s">
+        <v>587</v>
+      </c>
+      <c r="Z62" s="55" t="s">
+        <v>603</v>
+      </c>
+      <c r="AA62" s="56" t="s">
         <v>591</v>
       </c>
-      <c r="Z62" s="55" t="s">
-        <v>607</v>
-      </c>
-      <c r="AA62" s="56" t="s">
-        <v>595</v>
-      </c>
       <c r="AB62" s="55" t="s">
-        <v>607</v>
+        <v>603</v>
       </c>
       <c r="AC62" s="56" t="s">
-        <v>598</v>
+        <v>594</v>
       </c>
       <c r="AD62" s="55" t="s">
-        <v>607</v>
+        <v>603</v>
       </c>
       <c r="AE62" s="56" t="s">
-        <v>601</v>
+        <v>597</v>
       </c>
       <c r="AF62" s="55" t="s">
-        <v>607</v>
+        <v>603</v>
       </c>
       <c r="AG62" s="56" t="s">
-        <v>604</v>
+        <v>600</v>
       </c>
     </row>
     <row r="63" spans="1:33" ht="6" customHeight="1" x14ac:dyDescent="0.2">
@@ -15455,34 +15518,34 @@
         <v>181</v>
       </c>
       <c r="X63" s="55" t="s">
-        <v>607</v>
+        <v>603</v>
       </c>
       <c r="Y63" s="56" t="s">
+        <v>587</v>
+      </c>
+      <c r="Z63" s="55" t="s">
+        <v>603</v>
+      </c>
+      <c r="AA63" s="56" t="s">
         <v>591</v>
       </c>
-      <c r="Z63" s="55" t="s">
-        <v>607</v>
-      </c>
-      <c r="AA63" s="56" t="s">
-        <v>595</v>
-      </c>
       <c r="AB63" s="55" t="s">
-        <v>607</v>
+        <v>603</v>
       </c>
       <c r="AC63" s="56" t="s">
-        <v>598</v>
+        <v>594</v>
       </c>
       <c r="AD63" s="55" t="s">
-        <v>607</v>
+        <v>603</v>
       </c>
       <c r="AE63" s="56" t="s">
-        <v>601</v>
+        <v>597</v>
       </c>
       <c r="AF63" s="55" t="s">
-        <v>607</v>
+        <v>603</v>
       </c>
       <c r="AG63" s="56" t="s">
-        <v>604</v>
+        <v>600</v>
       </c>
     </row>
     <row r="64" spans="1:33" ht="6" customHeight="1" x14ac:dyDescent="0.2">
@@ -15556,34 +15619,34 @@
         <v>181</v>
       </c>
       <c r="X64" s="55" t="s">
-        <v>607</v>
+        <v>603</v>
       </c>
       <c r="Y64" s="56" t="s">
+        <v>587</v>
+      </c>
+      <c r="Z64" s="55" t="s">
+        <v>603</v>
+      </c>
+      <c r="AA64" s="56" t="s">
         <v>591</v>
       </c>
-      <c r="Z64" s="55" t="s">
-        <v>607</v>
-      </c>
-      <c r="AA64" s="56" t="s">
-        <v>595</v>
-      </c>
       <c r="AB64" s="55" t="s">
-        <v>607</v>
+        <v>603</v>
       </c>
       <c r="AC64" s="56" t="s">
-        <v>598</v>
+        <v>594</v>
       </c>
       <c r="AD64" s="55" t="s">
-        <v>607</v>
+        <v>603</v>
       </c>
       <c r="AE64" s="56" t="s">
-        <v>601</v>
+        <v>597</v>
       </c>
       <c r="AF64" s="55" t="s">
-        <v>607</v>
+        <v>603</v>
       </c>
       <c r="AG64" s="56" t="s">
-        <v>604</v>
+        <v>600</v>
       </c>
     </row>
     <row r="65" spans="1:33" ht="6" customHeight="1" x14ac:dyDescent="0.2">
@@ -15657,34 +15720,34 @@
         <v>181</v>
       </c>
       <c r="X65" s="55" t="s">
-        <v>607</v>
+        <v>603</v>
       </c>
       <c r="Y65" s="56" t="s">
+        <v>587</v>
+      </c>
+      <c r="Z65" s="55" t="s">
+        <v>603</v>
+      </c>
+      <c r="AA65" s="56" t="s">
         <v>591</v>
       </c>
-      <c r="Z65" s="55" t="s">
-        <v>607</v>
-      </c>
-      <c r="AA65" s="56" t="s">
-        <v>595</v>
-      </c>
       <c r="AB65" s="55" t="s">
-        <v>607</v>
+        <v>603</v>
       </c>
       <c r="AC65" s="56" t="s">
-        <v>598</v>
+        <v>594</v>
       </c>
       <c r="AD65" s="55" t="s">
-        <v>607</v>
+        <v>603</v>
       </c>
       <c r="AE65" s="56" t="s">
-        <v>601</v>
+        <v>597</v>
       </c>
       <c r="AF65" s="55" t="s">
-        <v>607</v>
+        <v>603</v>
       </c>
       <c r="AG65" s="56" t="s">
-        <v>604</v>
+        <v>600</v>
       </c>
     </row>
     <row r="66" spans="1:33" ht="6" customHeight="1" x14ac:dyDescent="0.2">
@@ -15758,34 +15821,34 @@
         <v>181</v>
       </c>
       <c r="X66" s="55" t="s">
-        <v>607</v>
+        <v>603</v>
       </c>
       <c r="Y66" s="56" t="s">
+        <v>587</v>
+      </c>
+      <c r="Z66" s="55" t="s">
+        <v>603</v>
+      </c>
+      <c r="AA66" s="56" t="s">
         <v>591</v>
       </c>
-      <c r="Z66" s="55" t="s">
-        <v>607</v>
-      </c>
-      <c r="AA66" s="56" t="s">
-        <v>595</v>
-      </c>
       <c r="AB66" s="55" t="s">
-        <v>607</v>
+        <v>603</v>
       </c>
       <c r="AC66" s="56" t="s">
-        <v>598</v>
+        <v>594</v>
       </c>
       <c r="AD66" s="55" t="s">
-        <v>607</v>
+        <v>603</v>
       </c>
       <c r="AE66" s="56" t="s">
-        <v>601</v>
+        <v>597</v>
       </c>
       <c r="AF66" s="55" t="s">
-        <v>607</v>
+        <v>603</v>
       </c>
       <c r="AG66" s="56" t="s">
-        <v>604</v>
+        <v>600</v>
       </c>
     </row>
     <row r="67" spans="1:33" ht="6" customHeight="1" x14ac:dyDescent="0.2">
@@ -15859,34 +15922,34 @@
         <v>181</v>
       </c>
       <c r="X67" s="55" t="s">
-        <v>607</v>
+        <v>603</v>
       </c>
       <c r="Y67" s="56" t="s">
+        <v>587</v>
+      </c>
+      <c r="Z67" s="55" t="s">
+        <v>603</v>
+      </c>
+      <c r="AA67" s="56" t="s">
         <v>591</v>
       </c>
-      <c r="Z67" s="55" t="s">
-        <v>607</v>
-      </c>
-      <c r="AA67" s="56" t="s">
-        <v>595</v>
-      </c>
       <c r="AB67" s="55" t="s">
-        <v>607</v>
+        <v>603</v>
       </c>
       <c r="AC67" s="56" t="s">
-        <v>598</v>
+        <v>594</v>
       </c>
       <c r="AD67" s="55" t="s">
-        <v>607</v>
+        <v>603</v>
       </c>
       <c r="AE67" s="56" t="s">
-        <v>601</v>
+        <v>597</v>
       </c>
       <c r="AF67" s="55" t="s">
-        <v>607</v>
+        <v>603</v>
       </c>
       <c r="AG67" s="56" t="s">
-        <v>604</v>
+        <v>600</v>
       </c>
     </row>
     <row r="68" spans="1:33" ht="6" customHeight="1" x14ac:dyDescent="0.2">
@@ -15960,34 +16023,34 @@
         <v>181</v>
       </c>
       <c r="X68" s="55" t="s">
-        <v>607</v>
+        <v>603</v>
       </c>
       <c r="Y68" s="56" t="s">
+        <v>587</v>
+      </c>
+      <c r="Z68" s="55" t="s">
+        <v>603</v>
+      </c>
+      <c r="AA68" s="56" t="s">
         <v>591</v>
       </c>
-      <c r="Z68" s="55" t="s">
-        <v>607</v>
-      </c>
-      <c r="AA68" s="56" t="s">
-        <v>595</v>
-      </c>
       <c r="AB68" s="55" t="s">
-        <v>607</v>
+        <v>603</v>
       </c>
       <c r="AC68" s="56" t="s">
-        <v>598</v>
+        <v>594</v>
       </c>
       <c r="AD68" s="55" t="s">
-        <v>607</v>
+        <v>603</v>
       </c>
       <c r="AE68" s="56" t="s">
-        <v>601</v>
+        <v>597</v>
       </c>
       <c r="AF68" s="55" t="s">
-        <v>607</v>
+        <v>603</v>
       </c>
       <c r="AG68" s="56" t="s">
-        <v>604</v>
+        <v>600</v>
       </c>
     </row>
     <row r="69" spans="1:33" ht="6" customHeight="1" x14ac:dyDescent="0.2">
@@ -16061,34 +16124,34 @@
         <v>181</v>
       </c>
       <c r="X69" s="55" t="s">
-        <v>607</v>
+        <v>603</v>
       </c>
       <c r="Y69" s="56" t="s">
+        <v>587</v>
+      </c>
+      <c r="Z69" s="55" t="s">
+        <v>603</v>
+      </c>
+      <c r="AA69" s="56" t="s">
         <v>591</v>
       </c>
-      <c r="Z69" s="55" t="s">
-        <v>607</v>
-      </c>
-      <c r="AA69" s="56" t="s">
-        <v>595</v>
-      </c>
       <c r="AB69" s="55" t="s">
-        <v>607</v>
+        <v>603</v>
       </c>
       <c r="AC69" s="56" t="s">
-        <v>598</v>
+        <v>594</v>
       </c>
       <c r="AD69" s="55" t="s">
-        <v>607</v>
+        <v>603</v>
       </c>
       <c r="AE69" s="56" t="s">
-        <v>601</v>
+        <v>597</v>
       </c>
       <c r="AF69" s="55" t="s">
-        <v>607</v>
+        <v>603</v>
       </c>
       <c r="AG69" s="56" t="s">
-        <v>604</v>
+        <v>600</v>
       </c>
     </row>
     <row r="70" spans="1:33" ht="6" customHeight="1" x14ac:dyDescent="0.2">
@@ -16162,34 +16225,34 @@
         <v>181</v>
       </c>
       <c r="X70" s="55" t="s">
-        <v>607</v>
+        <v>603</v>
       </c>
       <c r="Y70" s="56" t="s">
+        <v>587</v>
+      </c>
+      <c r="Z70" s="55" t="s">
+        <v>603</v>
+      </c>
+      <c r="AA70" s="56" t="s">
         <v>591</v>
       </c>
-      <c r="Z70" s="55" t="s">
-        <v>607</v>
-      </c>
-      <c r="AA70" s="56" t="s">
-        <v>595</v>
-      </c>
       <c r="AB70" s="55" t="s">
-        <v>607</v>
+        <v>603</v>
       </c>
       <c r="AC70" s="56" t="s">
-        <v>598</v>
+        <v>594</v>
       </c>
       <c r="AD70" s="55" t="s">
-        <v>607</v>
+        <v>603</v>
       </c>
       <c r="AE70" s="56" t="s">
-        <v>601</v>
+        <v>597</v>
       </c>
       <c r="AF70" s="55" t="s">
-        <v>607</v>
+        <v>603</v>
       </c>
       <c r="AG70" s="56" t="s">
-        <v>604</v>
+        <v>600</v>
       </c>
     </row>
     <row r="71" spans="1:33" ht="6" customHeight="1" x14ac:dyDescent="0.2">
@@ -16263,34 +16326,34 @@
         <v>181</v>
       </c>
       <c r="X71" s="55" t="s">
-        <v>607</v>
+        <v>603</v>
       </c>
       <c r="Y71" s="56" t="s">
+        <v>587</v>
+      </c>
+      <c r="Z71" s="55" t="s">
+        <v>603</v>
+      </c>
+      <c r="AA71" s="56" t="s">
         <v>591</v>
       </c>
-      <c r="Z71" s="55" t="s">
-        <v>607</v>
-      </c>
-      <c r="AA71" s="56" t="s">
-        <v>595</v>
-      </c>
       <c r="AB71" s="55" t="s">
-        <v>607</v>
+        <v>603</v>
       </c>
       <c r="AC71" s="56" t="s">
-        <v>598</v>
+        <v>594</v>
       </c>
       <c r="AD71" s="55" t="s">
-        <v>607</v>
+        <v>603</v>
       </c>
       <c r="AE71" s="56" t="s">
-        <v>601</v>
+        <v>597</v>
       </c>
       <c r="AF71" s="55" t="s">
-        <v>607</v>
+        <v>603</v>
       </c>
       <c r="AG71" s="56" t="s">
-        <v>604</v>
+        <v>600</v>
       </c>
     </row>
     <row r="72" spans="1:33" ht="6" customHeight="1" x14ac:dyDescent="0.2">
@@ -16364,34 +16427,34 @@
         <v>181</v>
       </c>
       <c r="X72" s="55" t="s">
-        <v>607</v>
+        <v>603</v>
       </c>
       <c r="Y72" s="56" t="s">
+        <v>587</v>
+      </c>
+      <c r="Z72" s="55" t="s">
+        <v>603</v>
+      </c>
+      <c r="AA72" s="56" t="s">
         <v>591</v>
       </c>
-      <c r="Z72" s="55" t="s">
-        <v>607</v>
-      </c>
-      <c r="AA72" s="56" t="s">
-        <v>595</v>
-      </c>
       <c r="AB72" s="55" t="s">
-        <v>607</v>
+        <v>603</v>
       </c>
       <c r="AC72" s="56" t="s">
-        <v>598</v>
+        <v>594</v>
       </c>
       <c r="AD72" s="55" t="s">
-        <v>607</v>
+        <v>603</v>
       </c>
       <c r="AE72" s="56" t="s">
-        <v>601</v>
+        <v>597</v>
       </c>
       <c r="AF72" s="55" t="s">
-        <v>607</v>
+        <v>603</v>
       </c>
       <c r="AG72" s="56" t="s">
-        <v>604</v>
+        <v>600</v>
       </c>
     </row>
     <row r="73" spans="1:33" ht="6" customHeight="1" x14ac:dyDescent="0.2">
@@ -16465,34 +16528,34 @@
         <v>181</v>
       </c>
       <c r="X73" s="55" t="s">
-        <v>607</v>
+        <v>603</v>
       </c>
       <c r="Y73" s="56" t="s">
+        <v>587</v>
+      </c>
+      <c r="Z73" s="55" t="s">
+        <v>603</v>
+      </c>
+      <c r="AA73" s="56" t="s">
         <v>591</v>
       </c>
-      <c r="Z73" s="55" t="s">
-        <v>607</v>
-      </c>
-      <c r="AA73" s="56" t="s">
-        <v>595</v>
-      </c>
       <c r="AB73" s="55" t="s">
-        <v>607</v>
+        <v>603</v>
       </c>
       <c r="AC73" s="56" t="s">
-        <v>598</v>
+        <v>594</v>
       </c>
       <c r="AD73" s="55" t="s">
-        <v>607</v>
+        <v>603</v>
       </c>
       <c r="AE73" s="56" t="s">
-        <v>601</v>
+        <v>597</v>
       </c>
       <c r="AF73" s="55" t="s">
-        <v>607</v>
+        <v>603</v>
       </c>
       <c r="AG73" s="56" t="s">
-        <v>604</v>
+        <v>600</v>
       </c>
     </row>
     <row r="74" spans="1:33" ht="6" customHeight="1" x14ac:dyDescent="0.2">
@@ -16566,34 +16629,34 @@
         <v>181</v>
       </c>
       <c r="X74" s="55" t="s">
-        <v>607</v>
+        <v>603</v>
       </c>
       <c r="Y74" s="56" t="s">
+        <v>587</v>
+      </c>
+      <c r="Z74" s="55" t="s">
+        <v>603</v>
+      </c>
+      <c r="AA74" s="56" t="s">
         <v>591</v>
       </c>
-      <c r="Z74" s="55" t="s">
-        <v>607</v>
-      </c>
-      <c r="AA74" s="56" t="s">
-        <v>595</v>
-      </c>
       <c r="AB74" s="55" t="s">
-        <v>607</v>
+        <v>603</v>
       </c>
       <c r="AC74" s="56" t="s">
-        <v>598</v>
+        <v>594</v>
       </c>
       <c r="AD74" s="55" t="s">
-        <v>607</v>
+        <v>603</v>
       </c>
       <c r="AE74" s="56" t="s">
-        <v>601</v>
+        <v>597</v>
       </c>
       <c r="AF74" s="55" t="s">
-        <v>607</v>
+        <v>603</v>
       </c>
       <c r="AG74" s="56" t="s">
-        <v>604</v>
+        <v>600</v>
       </c>
     </row>
     <row r="75" spans="1:33" ht="6" customHeight="1" x14ac:dyDescent="0.2">
@@ -16667,34 +16730,34 @@
         <v>181</v>
       </c>
       <c r="X75" s="55" t="s">
-        <v>607</v>
+        <v>603</v>
       </c>
       <c r="Y75" s="56" t="s">
+        <v>587</v>
+      </c>
+      <c r="Z75" s="55" t="s">
+        <v>603</v>
+      </c>
+      <c r="AA75" s="56" t="s">
         <v>591</v>
       </c>
-      <c r="Z75" s="55" t="s">
-        <v>607</v>
-      </c>
-      <c r="AA75" s="56" t="s">
-        <v>595</v>
-      </c>
       <c r="AB75" s="55" t="s">
-        <v>607</v>
+        <v>603</v>
       </c>
       <c r="AC75" s="56" t="s">
-        <v>598</v>
+        <v>594</v>
       </c>
       <c r="AD75" s="55" t="s">
-        <v>607</v>
+        <v>603</v>
       </c>
       <c r="AE75" s="56" t="s">
-        <v>601</v>
+        <v>597</v>
       </c>
       <c r="AF75" s="55" t="s">
-        <v>607</v>
+        <v>603</v>
       </c>
       <c r="AG75" s="56" t="s">
-        <v>604</v>
+        <v>600</v>
       </c>
     </row>
     <row r="76" spans="1:33" ht="6" customHeight="1" x14ac:dyDescent="0.2">
@@ -16768,34 +16831,34 @@
         <v>181</v>
       </c>
       <c r="X76" s="55" t="s">
-        <v>607</v>
+        <v>603</v>
       </c>
       <c r="Y76" s="56" t="s">
+        <v>587</v>
+      </c>
+      <c r="Z76" s="55" t="s">
+        <v>603</v>
+      </c>
+      <c r="AA76" s="56" t="s">
         <v>591</v>
       </c>
-      <c r="Z76" s="55" t="s">
-        <v>607</v>
-      </c>
-      <c r="AA76" s="56" t="s">
-        <v>595</v>
-      </c>
       <c r="AB76" s="55" t="s">
-        <v>607</v>
+        <v>603</v>
       </c>
       <c r="AC76" s="56" t="s">
-        <v>598</v>
+        <v>594</v>
       </c>
       <c r="AD76" s="55" t="s">
-        <v>607</v>
+        <v>603</v>
       </c>
       <c r="AE76" s="56" t="s">
-        <v>601</v>
+        <v>597</v>
       </c>
       <c r="AF76" s="55" t="s">
-        <v>607</v>
+        <v>603</v>
       </c>
       <c r="AG76" s="56" t="s">
-        <v>604</v>
+        <v>600</v>
       </c>
     </row>
     <row r="77" spans="1:33" ht="6" customHeight="1" x14ac:dyDescent="0.2">
@@ -16869,34 +16932,34 @@
         <v>181</v>
       </c>
       <c r="X77" s="55" t="s">
-        <v>607</v>
+        <v>603</v>
       </c>
       <c r="Y77" s="56" t="s">
+        <v>587</v>
+      </c>
+      <c r="Z77" s="55" t="s">
+        <v>603</v>
+      </c>
+      <c r="AA77" s="56" t="s">
         <v>591</v>
       </c>
-      <c r="Z77" s="55" t="s">
-        <v>607</v>
-      </c>
-      <c r="AA77" s="56" t="s">
-        <v>595</v>
-      </c>
       <c r="AB77" s="55" t="s">
-        <v>607</v>
+        <v>603</v>
       </c>
       <c r="AC77" s="56" t="s">
-        <v>598</v>
+        <v>594</v>
       </c>
       <c r="AD77" s="55" t="s">
-        <v>607</v>
+        <v>603</v>
       </c>
       <c r="AE77" s="56" t="s">
-        <v>601</v>
+        <v>597</v>
       </c>
       <c r="AF77" s="55" t="s">
-        <v>607</v>
+        <v>603</v>
       </c>
       <c r="AG77" s="56" t="s">
-        <v>604</v>
+        <v>600</v>
       </c>
     </row>
     <row r="78" spans="1:33" ht="6" customHeight="1" x14ac:dyDescent="0.2">
@@ -16970,34 +17033,34 @@
         <v>181</v>
       </c>
       <c r="X78" s="55" t="s">
-        <v>607</v>
+        <v>603</v>
       </c>
       <c r="Y78" s="56" t="s">
+        <v>587</v>
+      </c>
+      <c r="Z78" s="55" t="s">
+        <v>603</v>
+      </c>
+      <c r="AA78" s="56" t="s">
         <v>591</v>
       </c>
-      <c r="Z78" s="55" t="s">
-        <v>607</v>
-      </c>
-      <c r="AA78" s="56" t="s">
-        <v>595</v>
-      </c>
       <c r="AB78" s="55" t="s">
-        <v>607</v>
+        <v>603</v>
       </c>
       <c r="AC78" s="56" t="s">
-        <v>598</v>
+        <v>594</v>
       </c>
       <c r="AD78" s="55" t="s">
-        <v>607</v>
+        <v>603</v>
       </c>
       <c r="AE78" s="56" t="s">
-        <v>601</v>
+        <v>597</v>
       </c>
       <c r="AF78" s="55" t="s">
-        <v>607</v>
+        <v>603</v>
       </c>
       <c r="AG78" s="56" t="s">
-        <v>604</v>
+        <v>600</v>
       </c>
     </row>
     <row r="79" spans="1:33" ht="6" customHeight="1" x14ac:dyDescent="0.2">
@@ -17071,34 +17134,34 @@
         <v>181</v>
       </c>
       <c r="X79" s="55" t="s">
-        <v>607</v>
+        <v>603</v>
       </c>
       <c r="Y79" s="56" t="s">
+        <v>587</v>
+      </c>
+      <c r="Z79" s="55" t="s">
+        <v>603</v>
+      </c>
+      <c r="AA79" s="56" t="s">
         <v>591</v>
       </c>
-      <c r="Z79" s="55" t="s">
-        <v>607</v>
-      </c>
-      <c r="AA79" s="56" t="s">
-        <v>595</v>
-      </c>
       <c r="AB79" s="55" t="s">
-        <v>607</v>
+        <v>603</v>
       </c>
       <c r="AC79" s="56" t="s">
-        <v>598</v>
+        <v>594</v>
       </c>
       <c r="AD79" s="55" t="s">
-        <v>607</v>
+        <v>603</v>
       </c>
       <c r="AE79" s="56" t="s">
-        <v>601</v>
+        <v>597</v>
       </c>
       <c r="AF79" s="55" t="s">
-        <v>607</v>
+        <v>603</v>
       </c>
       <c r="AG79" s="56" t="s">
-        <v>604</v>
+        <v>600</v>
       </c>
     </row>
     <row r="80" spans="1:33" ht="6" customHeight="1" x14ac:dyDescent="0.2">
@@ -17172,34 +17235,34 @@
         <v>181</v>
       </c>
       <c r="X80" s="55" t="s">
-        <v>607</v>
+        <v>603</v>
       </c>
       <c r="Y80" s="56" t="s">
+        <v>587</v>
+      </c>
+      <c r="Z80" s="55" t="s">
+        <v>603</v>
+      </c>
+      <c r="AA80" s="56" t="s">
         <v>591</v>
       </c>
-      <c r="Z80" s="55" t="s">
-        <v>607</v>
-      </c>
-      <c r="AA80" s="56" t="s">
-        <v>595</v>
-      </c>
       <c r="AB80" s="55" t="s">
-        <v>607</v>
+        <v>603</v>
       </c>
       <c r="AC80" s="56" t="s">
-        <v>598</v>
+        <v>594</v>
       </c>
       <c r="AD80" s="55" t="s">
-        <v>607</v>
+        <v>603</v>
       </c>
       <c r="AE80" s="56" t="s">
-        <v>601</v>
+        <v>597</v>
       </c>
       <c r="AF80" s="55" t="s">
-        <v>607</v>
+        <v>603</v>
       </c>
       <c r="AG80" s="56" t="s">
-        <v>604</v>
+        <v>600</v>
       </c>
     </row>
     <row r="81" spans="1:33" ht="6" customHeight="1" x14ac:dyDescent="0.2">
@@ -17273,34 +17336,34 @@
         <v>181</v>
       </c>
       <c r="X81" s="55" t="s">
-        <v>607</v>
+        <v>603</v>
       </c>
       <c r="Y81" s="56" t="s">
+        <v>587</v>
+      </c>
+      <c r="Z81" s="55" t="s">
+        <v>603</v>
+      </c>
+      <c r="AA81" s="56" t="s">
         <v>591</v>
       </c>
-      <c r="Z81" s="55" t="s">
-        <v>607</v>
-      </c>
-      <c r="AA81" s="56" t="s">
-        <v>595</v>
-      </c>
       <c r="AB81" s="55" t="s">
-        <v>607</v>
+        <v>603</v>
       </c>
       <c r="AC81" s="56" t="s">
-        <v>598</v>
+        <v>594</v>
       </c>
       <c r="AD81" s="55" t="s">
-        <v>607</v>
+        <v>603</v>
       </c>
       <c r="AE81" s="56" t="s">
-        <v>601</v>
+        <v>597</v>
       </c>
       <c r="AF81" s="55" t="s">
-        <v>607</v>
+        <v>603</v>
       </c>
       <c r="AG81" s="56" t="s">
-        <v>604</v>
+        <v>600</v>
       </c>
     </row>
     <row r="82" spans="1:33" ht="6" customHeight="1" x14ac:dyDescent="0.2">
@@ -17374,34 +17437,34 @@
         <v>181</v>
       </c>
       <c r="X82" s="55" t="s">
-        <v>607</v>
+        <v>603</v>
       </c>
       <c r="Y82" s="56" t="s">
+        <v>587</v>
+      </c>
+      <c r="Z82" s="55" t="s">
+        <v>603</v>
+      </c>
+      <c r="AA82" s="56" t="s">
         <v>591</v>
       </c>
-      <c r="Z82" s="55" t="s">
-        <v>607</v>
-      </c>
-      <c r="AA82" s="56" t="s">
-        <v>595</v>
-      </c>
       <c r="AB82" s="55" t="s">
-        <v>607</v>
+        <v>603</v>
       </c>
       <c r="AC82" s="56" t="s">
-        <v>598</v>
+        <v>594</v>
       </c>
       <c r="AD82" s="55" t="s">
-        <v>607</v>
+        <v>603</v>
       </c>
       <c r="AE82" s="56" t="s">
-        <v>601</v>
+        <v>597</v>
       </c>
       <c r="AF82" s="55" t="s">
-        <v>607</v>
+        <v>603</v>
       </c>
       <c r="AG82" s="56" t="s">
-        <v>604</v>
+        <v>600</v>
       </c>
     </row>
     <row r="83" spans="1:33" ht="6" customHeight="1" x14ac:dyDescent="0.2">
@@ -17475,34 +17538,34 @@
         <v>181</v>
       </c>
       <c r="X83" s="55" t="s">
-        <v>607</v>
+        <v>603</v>
       </c>
       <c r="Y83" s="56" t="s">
+        <v>587</v>
+      </c>
+      <c r="Z83" s="55" t="s">
+        <v>603</v>
+      </c>
+      <c r="AA83" s="56" t="s">
         <v>591</v>
       </c>
-      <c r="Z83" s="55" t="s">
-        <v>607</v>
-      </c>
-      <c r="AA83" s="56" t="s">
-        <v>595</v>
-      </c>
       <c r="AB83" s="55" t="s">
-        <v>607</v>
+        <v>603</v>
       </c>
       <c r="AC83" s="56" t="s">
-        <v>598</v>
+        <v>594</v>
       </c>
       <c r="AD83" s="55" t="s">
-        <v>607</v>
+        <v>603</v>
       </c>
       <c r="AE83" s="56" t="s">
-        <v>601</v>
+        <v>597</v>
       </c>
       <c r="AF83" s="55" t="s">
-        <v>607</v>
+        <v>603</v>
       </c>
       <c r="AG83" s="56" t="s">
-        <v>604</v>
+        <v>600</v>
       </c>
     </row>
     <row r="84" spans="1:33" ht="6" customHeight="1" x14ac:dyDescent="0.2">
@@ -17576,34 +17639,34 @@
         <v>181</v>
       </c>
       <c r="X84" s="55" t="s">
-        <v>607</v>
+        <v>603</v>
       </c>
       <c r="Y84" s="56" t="s">
+        <v>587</v>
+      </c>
+      <c r="Z84" s="55" t="s">
+        <v>603</v>
+      </c>
+      <c r="AA84" s="56" t="s">
         <v>591</v>
       </c>
-      <c r="Z84" s="55" t="s">
-        <v>607</v>
-      </c>
-      <c r="AA84" s="56" t="s">
-        <v>595</v>
-      </c>
       <c r="AB84" s="55" t="s">
-        <v>607</v>
+        <v>603</v>
       </c>
       <c r="AC84" s="56" t="s">
-        <v>598</v>
+        <v>594</v>
       </c>
       <c r="AD84" s="55" t="s">
-        <v>607</v>
+        <v>603</v>
       </c>
       <c r="AE84" s="56" t="s">
-        <v>601</v>
+        <v>597</v>
       </c>
       <c r="AF84" s="55" t="s">
-        <v>607</v>
+        <v>603</v>
       </c>
       <c r="AG84" s="56" t="s">
-        <v>604</v>
+        <v>600</v>
       </c>
     </row>
     <row r="85" spans="1:33" ht="6" customHeight="1" x14ac:dyDescent="0.2">
@@ -17677,34 +17740,34 @@
         <v>181</v>
       </c>
       <c r="X85" s="55" t="s">
-        <v>607</v>
+        <v>603</v>
       </c>
       <c r="Y85" s="56" t="s">
+        <v>587</v>
+      </c>
+      <c r="Z85" s="55" t="s">
+        <v>603</v>
+      </c>
+      <c r="AA85" s="56" t="s">
         <v>591</v>
       </c>
-      <c r="Z85" s="55" t="s">
-        <v>607</v>
-      </c>
-      <c r="AA85" s="56" t="s">
-        <v>595</v>
-      </c>
       <c r="AB85" s="55" t="s">
-        <v>607</v>
+        <v>603</v>
       </c>
       <c r="AC85" s="56" t="s">
-        <v>598</v>
+        <v>594</v>
       </c>
       <c r="AD85" s="55" t="s">
-        <v>607</v>
+        <v>603</v>
       </c>
       <c r="AE85" s="56" t="s">
-        <v>601</v>
+        <v>597</v>
       </c>
       <c r="AF85" s="55" t="s">
-        <v>607</v>
+        <v>603</v>
       </c>
       <c r="AG85" s="56" t="s">
-        <v>604</v>
+        <v>600</v>
       </c>
     </row>
     <row r="86" spans="1:33" ht="6" customHeight="1" x14ac:dyDescent="0.2">
@@ -17778,34 +17841,34 @@
         <v>181</v>
       </c>
       <c r="X86" s="55" t="s">
-        <v>607</v>
+        <v>603</v>
       </c>
       <c r="Y86" s="56" t="s">
+        <v>587</v>
+      </c>
+      <c r="Z86" s="55" t="s">
+        <v>603</v>
+      </c>
+      <c r="AA86" s="56" t="s">
         <v>591</v>
       </c>
-      <c r="Z86" s="55" t="s">
-        <v>607</v>
-      </c>
-      <c r="AA86" s="56" t="s">
-        <v>595</v>
-      </c>
       <c r="AB86" s="55" t="s">
-        <v>607</v>
+        <v>603</v>
       </c>
       <c r="AC86" s="56" t="s">
-        <v>598</v>
+        <v>594</v>
       </c>
       <c r="AD86" s="55" t="s">
-        <v>607</v>
+        <v>603</v>
       </c>
       <c r="AE86" s="56" t="s">
-        <v>601</v>
+        <v>597</v>
       </c>
       <c r="AF86" s="55" t="s">
-        <v>607</v>
+        <v>603</v>
       </c>
       <c r="AG86" s="56" t="s">
-        <v>604</v>
+        <v>600</v>
       </c>
     </row>
     <row r="87" spans="1:33" ht="6" customHeight="1" x14ac:dyDescent="0.2">
@@ -17879,34 +17942,34 @@
         <v>181</v>
       </c>
       <c r="X87" s="55" t="s">
-        <v>607</v>
+        <v>603</v>
       </c>
       <c r="Y87" s="56" t="s">
+        <v>587</v>
+      </c>
+      <c r="Z87" s="55" t="s">
+        <v>603</v>
+      </c>
+      <c r="AA87" s="56" t="s">
         <v>591</v>
       </c>
-      <c r="Z87" s="55" t="s">
-        <v>607</v>
-      </c>
-      <c r="AA87" s="56" t="s">
-        <v>595</v>
-      </c>
       <c r="AB87" s="55" t="s">
-        <v>607</v>
+        <v>603</v>
       </c>
       <c r="AC87" s="56" t="s">
-        <v>598</v>
+        <v>594</v>
       </c>
       <c r="AD87" s="55" t="s">
-        <v>607</v>
+        <v>603</v>
       </c>
       <c r="AE87" s="56" t="s">
-        <v>601</v>
+        <v>597</v>
       </c>
       <c r="AF87" s="55" t="s">
-        <v>607</v>
+        <v>603</v>
       </c>
       <c r="AG87" s="56" t="s">
-        <v>604</v>
+        <v>600</v>
       </c>
     </row>
     <row r="88" spans="1:33" ht="6" customHeight="1" x14ac:dyDescent="0.2">
@@ -17980,34 +18043,34 @@
         <v>181</v>
       </c>
       <c r="X88" s="55" t="s">
-        <v>607</v>
+        <v>603</v>
       </c>
       <c r="Y88" s="56" t="s">
+        <v>587</v>
+      </c>
+      <c r="Z88" s="55" t="s">
+        <v>603</v>
+      </c>
+      <c r="AA88" s="56" t="s">
         <v>591</v>
       </c>
-      <c r="Z88" s="55" t="s">
-        <v>607</v>
-      </c>
-      <c r="AA88" s="56" t="s">
-        <v>595</v>
-      </c>
       <c r="AB88" s="55" t="s">
-        <v>607</v>
+        <v>603</v>
       </c>
       <c r="AC88" s="56" t="s">
-        <v>598</v>
+        <v>594</v>
       </c>
       <c r="AD88" s="55" t="s">
-        <v>607</v>
+        <v>603</v>
       </c>
       <c r="AE88" s="56" t="s">
-        <v>601</v>
+        <v>597</v>
       </c>
       <c r="AF88" s="55" t="s">
-        <v>607</v>
+        <v>603</v>
       </c>
       <c r="AG88" s="56" t="s">
-        <v>604</v>
+        <v>600</v>
       </c>
     </row>
     <row r="89" spans="1:33" ht="6" customHeight="1" x14ac:dyDescent="0.2">
@@ -18081,34 +18144,34 @@
         <v>181</v>
       </c>
       <c r="X89" s="55" t="s">
-        <v>607</v>
+        <v>603</v>
       </c>
       <c r="Y89" s="56" t="s">
+        <v>587</v>
+      </c>
+      <c r="Z89" s="55" t="s">
+        <v>603</v>
+      </c>
+      <c r="AA89" s="56" t="s">
         <v>591</v>
       </c>
-      <c r="Z89" s="55" t="s">
-        <v>607</v>
-      </c>
-      <c r="AA89" s="56" t="s">
-        <v>595</v>
-      </c>
       <c r="AB89" s="55" t="s">
-        <v>607</v>
+        <v>603</v>
       </c>
       <c r="AC89" s="56" t="s">
-        <v>598</v>
+        <v>594</v>
       </c>
       <c r="AD89" s="55" t="s">
-        <v>607</v>
+        <v>603</v>
       </c>
       <c r="AE89" s="56" t="s">
-        <v>601</v>
+        <v>597</v>
       </c>
       <c r="AF89" s="55" t="s">
-        <v>607</v>
+        <v>603</v>
       </c>
       <c r="AG89" s="56" t="s">
-        <v>604</v>
+        <v>600</v>
       </c>
     </row>
     <row r="90" spans="1:33" ht="6" customHeight="1" x14ac:dyDescent="0.2">
@@ -18182,34 +18245,34 @@
         <v>181</v>
       </c>
       <c r="X90" s="55" t="s">
-        <v>607</v>
+        <v>603</v>
       </c>
       <c r="Y90" s="56" t="s">
+        <v>587</v>
+      </c>
+      <c r="Z90" s="55" t="s">
+        <v>603</v>
+      </c>
+      <c r="AA90" s="56" t="s">
         <v>591</v>
       </c>
-      <c r="Z90" s="55" t="s">
-        <v>607</v>
-      </c>
-      <c r="AA90" s="56" t="s">
-        <v>595</v>
-      </c>
       <c r="AB90" s="55" t="s">
-        <v>607</v>
+        <v>603</v>
       </c>
       <c r="AC90" s="56" t="s">
-        <v>598</v>
+        <v>594</v>
       </c>
       <c r="AD90" s="55" t="s">
-        <v>607</v>
+        <v>603</v>
       </c>
       <c r="AE90" s="56" t="s">
-        <v>601</v>
+        <v>597</v>
       </c>
       <c r="AF90" s="55" t="s">
-        <v>607</v>
+        <v>603</v>
       </c>
       <c r="AG90" s="56" t="s">
-        <v>604</v>
+        <v>600</v>
       </c>
     </row>
     <row r="91" spans="1:33" ht="6" customHeight="1" x14ac:dyDescent="0.2">
@@ -18283,34 +18346,34 @@
         <v>181</v>
       </c>
       <c r="X91" s="55" t="s">
-        <v>607</v>
+        <v>603</v>
       </c>
       <c r="Y91" s="56" t="s">
+        <v>587</v>
+      </c>
+      <c r="Z91" s="55" t="s">
+        <v>603</v>
+      </c>
+      <c r="AA91" s="56" t="s">
         <v>591</v>
       </c>
-      <c r="Z91" s="55" t="s">
-        <v>607</v>
-      </c>
-      <c r="AA91" s="56" t="s">
-        <v>595</v>
-      </c>
       <c r="AB91" s="55" t="s">
-        <v>607</v>
+        <v>603</v>
       </c>
       <c r="AC91" s="56" t="s">
-        <v>598</v>
+        <v>594</v>
       </c>
       <c r="AD91" s="55" t="s">
-        <v>607</v>
+        <v>603</v>
       </c>
       <c r="AE91" s="56" t="s">
-        <v>601</v>
+        <v>597</v>
       </c>
       <c r="AF91" s="55" t="s">
-        <v>607</v>
+        <v>603</v>
       </c>
       <c r="AG91" s="56" t="s">
-        <v>604</v>
+        <v>600</v>
       </c>
     </row>
     <row r="92" spans="1:33" ht="6" customHeight="1" x14ac:dyDescent="0.2">
@@ -18384,34 +18447,34 @@
         <v>181</v>
       </c>
       <c r="X92" s="55" t="s">
-        <v>607</v>
+        <v>603</v>
       </c>
       <c r="Y92" s="56" t="s">
+        <v>587</v>
+      </c>
+      <c r="Z92" s="55" t="s">
+        <v>603</v>
+      </c>
+      <c r="AA92" s="56" t="s">
         <v>591</v>
       </c>
-      <c r="Z92" s="55" t="s">
-        <v>607</v>
-      </c>
-      <c r="AA92" s="56" t="s">
-        <v>595</v>
-      </c>
       <c r="AB92" s="55" t="s">
-        <v>607</v>
+        <v>603</v>
       </c>
       <c r="AC92" s="56" t="s">
-        <v>598</v>
+        <v>594</v>
       </c>
       <c r="AD92" s="55" t="s">
-        <v>607</v>
+        <v>603</v>
       </c>
       <c r="AE92" s="56" t="s">
-        <v>601</v>
+        <v>597</v>
       </c>
       <c r="AF92" s="55" t="s">
-        <v>607</v>
+        <v>603</v>
       </c>
       <c r="AG92" s="56" t="s">
-        <v>604</v>
+        <v>600</v>
       </c>
     </row>
     <row r="93" spans="1:33" ht="6" customHeight="1" x14ac:dyDescent="0.2">
@@ -18485,34 +18548,34 @@
         <v>181</v>
       </c>
       <c r="X93" s="55" t="s">
-        <v>607</v>
+        <v>603</v>
       </c>
       <c r="Y93" s="56" t="s">
+        <v>587</v>
+      </c>
+      <c r="Z93" s="55" t="s">
+        <v>603</v>
+      </c>
+      <c r="AA93" s="56" t="s">
         <v>591</v>
       </c>
-      <c r="Z93" s="55" t="s">
-        <v>607</v>
-      </c>
-      <c r="AA93" s="56" t="s">
-        <v>595</v>
-      </c>
       <c r="AB93" s="55" t="s">
-        <v>607</v>
+        <v>603</v>
       </c>
       <c r="AC93" s="56" t="s">
-        <v>598</v>
+        <v>594</v>
       </c>
       <c r="AD93" s="55" t="s">
-        <v>607</v>
+        <v>603</v>
       </c>
       <c r="AE93" s="56" t="s">
-        <v>601</v>
+        <v>597</v>
       </c>
       <c r="AF93" s="55" t="s">
-        <v>607</v>
+        <v>603</v>
       </c>
       <c r="AG93" s="56" t="s">
-        <v>604</v>
+        <v>600</v>
       </c>
     </row>
     <row r="94" spans="1:33" ht="6" customHeight="1" x14ac:dyDescent="0.2">
@@ -18586,34 +18649,34 @@
         <v>181</v>
       </c>
       <c r="X94" s="55" t="s">
-        <v>607</v>
+        <v>603</v>
       </c>
       <c r="Y94" s="56" t="s">
+        <v>587</v>
+      </c>
+      <c r="Z94" s="55" t="s">
+        <v>603</v>
+      </c>
+      <c r="AA94" s="56" t="s">
         <v>591</v>
       </c>
-      <c r="Z94" s="55" t="s">
-        <v>607</v>
-      </c>
-      <c r="AA94" s="56" t="s">
-        <v>595</v>
-      </c>
       <c r="AB94" s="55" t="s">
-        <v>607</v>
+        <v>603</v>
       </c>
       <c r="AC94" s="56" t="s">
-        <v>598</v>
+        <v>594</v>
       </c>
       <c r="AD94" s="55" t="s">
-        <v>607</v>
+        <v>603</v>
       </c>
       <c r="AE94" s="56" t="s">
-        <v>601</v>
+        <v>597</v>
       </c>
       <c r="AF94" s="55" t="s">
-        <v>607</v>
+        <v>603</v>
       </c>
       <c r="AG94" s="56" t="s">
-        <v>604</v>
+        <v>600</v>
       </c>
     </row>
     <row r="95" spans="1:33" ht="6" customHeight="1" x14ac:dyDescent="0.2">
@@ -18687,34 +18750,34 @@
         <v>181</v>
       </c>
       <c r="X95" s="55" t="s">
-        <v>607</v>
+        <v>603</v>
       </c>
       <c r="Y95" s="56" t="s">
+        <v>587</v>
+      </c>
+      <c r="Z95" s="55" t="s">
+        <v>603</v>
+      </c>
+      <c r="AA95" s="56" t="s">
         <v>591</v>
       </c>
-      <c r="Z95" s="55" t="s">
-        <v>607</v>
-      </c>
-      <c r="AA95" s="56" t="s">
-        <v>595</v>
-      </c>
       <c r="AB95" s="55" t="s">
-        <v>607</v>
+        <v>603</v>
       </c>
       <c r="AC95" s="56" t="s">
-        <v>598</v>
+        <v>594</v>
       </c>
       <c r="AD95" s="55" t="s">
-        <v>607</v>
+        <v>603</v>
       </c>
       <c r="AE95" s="56" t="s">
-        <v>601</v>
+        <v>597</v>
       </c>
       <c r="AF95" s="55" t="s">
-        <v>607</v>
+        <v>603</v>
       </c>
       <c r="AG95" s="56" t="s">
-        <v>604</v>
+        <v>600</v>
       </c>
     </row>
     <row r="96" spans="1:33" ht="6" customHeight="1" x14ac:dyDescent="0.2">
@@ -18788,34 +18851,34 @@
         <v>181</v>
       </c>
       <c r="X96" s="55" t="s">
-        <v>607</v>
+        <v>603</v>
       </c>
       <c r="Y96" s="56" t="s">
+        <v>587</v>
+      </c>
+      <c r="Z96" s="55" t="s">
+        <v>603</v>
+      </c>
+      <c r="AA96" s="56" t="s">
         <v>591</v>
       </c>
-      <c r="Z96" s="55" t="s">
-        <v>607</v>
-      </c>
-      <c r="AA96" s="56" t="s">
-        <v>595</v>
-      </c>
       <c r="AB96" s="55" t="s">
-        <v>607</v>
+        <v>603</v>
       </c>
       <c r="AC96" s="56" t="s">
-        <v>598</v>
+        <v>594</v>
       </c>
       <c r="AD96" s="55" t="s">
-        <v>607</v>
+        <v>603</v>
       </c>
       <c r="AE96" s="56" t="s">
-        <v>601</v>
+        <v>597</v>
       </c>
       <c r="AF96" s="55" t="s">
-        <v>607</v>
+        <v>603</v>
       </c>
       <c r="AG96" s="56" t="s">
-        <v>604</v>
+        <v>600</v>
       </c>
     </row>
     <row r="97" spans="1:33" ht="6" customHeight="1" x14ac:dyDescent="0.2">
@@ -18889,34 +18952,34 @@
         <v>181</v>
       </c>
       <c r="X97" s="55" t="s">
-        <v>607</v>
+        <v>603</v>
       </c>
       <c r="Y97" s="56" t="s">
+        <v>587</v>
+      </c>
+      <c r="Z97" s="55" t="s">
+        <v>603</v>
+      </c>
+      <c r="AA97" s="56" t="s">
         <v>591</v>
       </c>
-      <c r="Z97" s="55" t="s">
-        <v>607</v>
-      </c>
-      <c r="AA97" s="56" t="s">
-        <v>595</v>
-      </c>
       <c r="AB97" s="55" t="s">
-        <v>607</v>
+        <v>603</v>
       </c>
       <c r="AC97" s="56" t="s">
-        <v>598</v>
+        <v>594</v>
       </c>
       <c r="AD97" s="55" t="s">
-        <v>607</v>
+        <v>603</v>
       </c>
       <c r="AE97" s="56" t="s">
-        <v>601</v>
+        <v>597</v>
       </c>
       <c r="AF97" s="55" t="s">
-        <v>607</v>
+        <v>603</v>
       </c>
       <c r="AG97" s="56" t="s">
-        <v>604</v>
+        <v>600</v>
       </c>
     </row>
     <row r="98" spans="1:33" ht="6" customHeight="1" x14ac:dyDescent="0.2">
@@ -18990,34 +19053,34 @@
         <v>181</v>
       </c>
       <c r="X98" s="55" t="s">
-        <v>607</v>
+        <v>603</v>
       </c>
       <c r="Y98" s="56" t="s">
+        <v>587</v>
+      </c>
+      <c r="Z98" s="55" t="s">
+        <v>603</v>
+      </c>
+      <c r="AA98" s="56" t="s">
         <v>591</v>
       </c>
-      <c r="Z98" s="55" t="s">
-        <v>607</v>
-      </c>
-      <c r="AA98" s="56" t="s">
-        <v>595</v>
-      </c>
       <c r="AB98" s="55" t="s">
-        <v>607</v>
+        <v>603</v>
       </c>
       <c r="AC98" s="56" t="s">
-        <v>598</v>
+        <v>594</v>
       </c>
       <c r="AD98" s="55" t="s">
-        <v>607</v>
+        <v>603</v>
       </c>
       <c r="AE98" s="56" t="s">
-        <v>601</v>
+        <v>597</v>
       </c>
       <c r="AF98" s="55" t="s">
-        <v>607</v>
+        <v>603</v>
       </c>
       <c r="AG98" s="56" t="s">
-        <v>604</v>
+        <v>600</v>
       </c>
     </row>
     <row r="99" spans="1:33" ht="6" customHeight="1" x14ac:dyDescent="0.2">
@@ -19091,34 +19154,34 @@
         <v>181</v>
       </c>
       <c r="X99" s="55" t="s">
-        <v>607</v>
+        <v>603</v>
       </c>
       <c r="Y99" s="56" t="s">
+        <v>587</v>
+      </c>
+      <c r="Z99" s="55" t="s">
+        <v>603</v>
+      </c>
+      <c r="AA99" s="56" t="s">
         <v>591</v>
       </c>
-      <c r="Z99" s="55" t="s">
-        <v>607</v>
-      </c>
-      <c r="AA99" s="56" t="s">
-        <v>595</v>
-      </c>
       <c r="AB99" s="55" t="s">
-        <v>607</v>
+        <v>603</v>
       </c>
       <c r="AC99" s="56" t="s">
-        <v>598</v>
+        <v>594</v>
       </c>
       <c r="AD99" s="55" t="s">
-        <v>607</v>
+        <v>603</v>
       </c>
       <c r="AE99" s="56" t="s">
-        <v>601</v>
+        <v>597</v>
       </c>
       <c r="AF99" s="55" t="s">
-        <v>607</v>
+        <v>603</v>
       </c>
       <c r="AG99" s="56" t="s">
-        <v>604</v>
+        <v>600</v>
       </c>
     </row>
     <row r="100" spans="1:33" ht="6" customHeight="1" x14ac:dyDescent="0.2">
@@ -19192,34 +19255,34 @@
         <v>181</v>
       </c>
       <c r="X100" s="55" t="s">
-        <v>607</v>
+        <v>603</v>
       </c>
       <c r="Y100" s="56" t="s">
+        <v>587</v>
+      </c>
+      <c r="Z100" s="55" t="s">
+        <v>603</v>
+      </c>
+      <c r="AA100" s="56" t="s">
         <v>591</v>
       </c>
-      <c r="Z100" s="55" t="s">
-        <v>607</v>
-      </c>
-      <c r="AA100" s="56" t="s">
-        <v>595</v>
-      </c>
       <c r="AB100" s="55" t="s">
-        <v>607</v>
+        <v>603</v>
       </c>
       <c r="AC100" s="56" t="s">
-        <v>598</v>
+        <v>594</v>
       </c>
       <c r="AD100" s="55" t="s">
-        <v>607</v>
+        <v>603</v>
       </c>
       <c r="AE100" s="56" t="s">
-        <v>601</v>
+        <v>597</v>
       </c>
       <c r="AF100" s="55" t="s">
-        <v>607</v>
+        <v>603</v>
       </c>
       <c r="AG100" s="56" t="s">
-        <v>604</v>
+        <v>600</v>
       </c>
     </row>
     <row r="101" spans="1:33" ht="6" customHeight="1" x14ac:dyDescent="0.2">
@@ -19293,34 +19356,34 @@
         <v>181</v>
       </c>
       <c r="X101" s="55" t="s">
-        <v>607</v>
+        <v>603</v>
       </c>
       <c r="Y101" s="56" t="s">
+        <v>587</v>
+      </c>
+      <c r="Z101" s="55" t="s">
+        <v>603</v>
+      </c>
+      <c r="AA101" s="56" t="s">
         <v>591</v>
       </c>
-      <c r="Z101" s="55" t="s">
-        <v>607</v>
-      </c>
-      <c r="AA101" s="56" t="s">
-        <v>595</v>
-      </c>
       <c r="AB101" s="55" t="s">
-        <v>607</v>
+        <v>603</v>
       </c>
       <c r="AC101" s="56" t="s">
-        <v>598</v>
+        <v>594</v>
       </c>
       <c r="AD101" s="55" t="s">
-        <v>607</v>
+        <v>603</v>
       </c>
       <c r="AE101" s="56" t="s">
-        <v>601</v>
+        <v>597</v>
       </c>
       <c r="AF101" s="55" t="s">
-        <v>607</v>
+        <v>603</v>
       </c>
       <c r="AG101" s="56" t="s">
-        <v>604</v>
+        <v>600</v>
       </c>
     </row>
     <row r="102" spans="1:33" ht="6" customHeight="1" x14ac:dyDescent="0.2">
@@ -19394,34 +19457,34 @@
         <v>181</v>
       </c>
       <c r="X102" s="55" t="s">
-        <v>607</v>
+        <v>603</v>
       </c>
       <c r="Y102" s="56" t="s">
+        <v>587</v>
+      </c>
+      <c r="Z102" s="55" t="s">
+        <v>603</v>
+      </c>
+      <c r="AA102" s="56" t="s">
         <v>591</v>
       </c>
-      <c r="Z102" s="55" t="s">
-        <v>607</v>
-      </c>
-      <c r="AA102" s="56" t="s">
-        <v>595</v>
-      </c>
       <c r="AB102" s="55" t="s">
-        <v>607</v>
+        <v>603</v>
       </c>
       <c r="AC102" s="56" t="s">
-        <v>598</v>
+        <v>594</v>
       </c>
       <c r="AD102" s="55" t="s">
-        <v>607</v>
+        <v>603</v>
       </c>
       <c r="AE102" s="56" t="s">
-        <v>601</v>
+        <v>597</v>
       </c>
       <c r="AF102" s="55" t="s">
-        <v>607</v>
+        <v>603</v>
       </c>
       <c r="AG102" s="56" t="s">
-        <v>604</v>
+        <v>600</v>
       </c>
     </row>
     <row r="103" spans="1:33" ht="6" customHeight="1" x14ac:dyDescent="0.2">
@@ -19495,34 +19558,34 @@
         <v>181</v>
       </c>
       <c r="X103" s="55" t="s">
-        <v>607</v>
+        <v>603</v>
       </c>
       <c r="Y103" s="56" t="s">
+        <v>587</v>
+      </c>
+      <c r="Z103" s="55" t="s">
+        <v>603</v>
+      </c>
+      <c r="AA103" s="56" t="s">
         <v>591</v>
       </c>
-      <c r="Z103" s="55" t="s">
-        <v>607</v>
-      </c>
-      <c r="AA103" s="56" t="s">
-        <v>595</v>
-      </c>
       <c r="AB103" s="55" t="s">
-        <v>607</v>
+        <v>603</v>
       </c>
       <c r="AC103" s="56" t="s">
-        <v>598</v>
+        <v>594</v>
       </c>
       <c r="AD103" s="55" t="s">
-        <v>607</v>
+        <v>603</v>
       </c>
       <c r="AE103" s="56" t="s">
-        <v>601</v>
+        <v>597</v>
       </c>
       <c r="AF103" s="55" t="s">
-        <v>607</v>
+        <v>603</v>
       </c>
       <c r="AG103" s="56" t="s">
-        <v>604</v>
+        <v>600</v>
       </c>
     </row>
     <row r="104" spans="1:33" ht="6" customHeight="1" x14ac:dyDescent="0.2">
@@ -19596,34 +19659,34 @@
         <v>181</v>
       </c>
       <c r="X104" s="55" t="s">
-        <v>607</v>
+        <v>603</v>
       </c>
       <c r="Y104" s="56" t="s">
+        <v>587</v>
+      </c>
+      <c r="Z104" s="55" t="s">
+        <v>603</v>
+      </c>
+      <c r="AA104" s="56" t="s">
         <v>591</v>
       </c>
-      <c r="Z104" s="55" t="s">
-        <v>607</v>
-      </c>
-      <c r="AA104" s="56" t="s">
-        <v>595</v>
-      </c>
       <c r="AB104" s="55" t="s">
-        <v>607</v>
+        <v>603</v>
       </c>
       <c r="AC104" s="56" t="s">
-        <v>598</v>
+        <v>594</v>
       </c>
       <c r="AD104" s="55" t="s">
-        <v>607</v>
+        <v>603</v>
       </c>
       <c r="AE104" s="56" t="s">
-        <v>601</v>
+        <v>597</v>
       </c>
       <c r="AF104" s="55" t="s">
-        <v>607</v>
+        <v>603</v>
       </c>
       <c r="AG104" s="56" t="s">
-        <v>604</v>
+        <v>600</v>
       </c>
     </row>
     <row r="105" spans="1:33" ht="6" customHeight="1" x14ac:dyDescent="0.2">
@@ -19697,34 +19760,34 @@
         <v>181</v>
       </c>
       <c r="X105" s="55" t="s">
-        <v>607</v>
+        <v>603</v>
       </c>
       <c r="Y105" s="56" t="s">
+        <v>587</v>
+      </c>
+      <c r="Z105" s="55" t="s">
+        <v>603</v>
+      </c>
+      <c r="AA105" s="56" t="s">
         <v>591</v>
       </c>
-      <c r="Z105" s="55" t="s">
-        <v>607</v>
-      </c>
-      <c r="AA105" s="56" t="s">
-        <v>595</v>
-      </c>
       <c r="AB105" s="55" t="s">
-        <v>607</v>
+        <v>603</v>
       </c>
       <c r="AC105" s="56" t="s">
-        <v>598</v>
+        <v>594</v>
       </c>
       <c r="AD105" s="55" t="s">
-        <v>607</v>
+        <v>603</v>
       </c>
       <c r="AE105" s="56" t="s">
-        <v>601</v>
+        <v>597</v>
       </c>
       <c r="AF105" s="55" t="s">
-        <v>607</v>
+        <v>603</v>
       </c>
       <c r="AG105" s="56" t="s">
-        <v>604</v>
+        <v>600</v>
       </c>
     </row>
     <row r="106" spans="1:33" ht="6" customHeight="1" x14ac:dyDescent="0.2">
@@ -19798,34 +19861,34 @@
         <v>181</v>
       </c>
       <c r="X106" s="55" t="s">
-        <v>607</v>
+        <v>603</v>
       </c>
       <c r="Y106" s="56" t="s">
+        <v>587</v>
+      </c>
+      <c r="Z106" s="55" t="s">
+        <v>603</v>
+      </c>
+      <c r="AA106" s="56" t="s">
         <v>591</v>
       </c>
-      <c r="Z106" s="55" t="s">
-        <v>607</v>
-      </c>
-      <c r="AA106" s="56" t="s">
-        <v>595</v>
-      </c>
       <c r="AB106" s="55" t="s">
-        <v>607</v>
+        <v>603</v>
       </c>
       <c r="AC106" s="56" t="s">
-        <v>598</v>
+        <v>594</v>
       </c>
       <c r="AD106" s="55" t="s">
-        <v>607</v>
+        <v>603</v>
       </c>
       <c r="AE106" s="56" t="s">
-        <v>601</v>
+        <v>597</v>
       </c>
       <c r="AF106" s="55" t="s">
-        <v>607</v>
+        <v>603</v>
       </c>
       <c r="AG106" s="56" t="s">
-        <v>604</v>
+        <v>600</v>
       </c>
     </row>
     <row r="107" spans="1:33" ht="6" customHeight="1" x14ac:dyDescent="0.2">
@@ -19899,34 +19962,34 @@
         <v>181</v>
       </c>
       <c r="X107" s="55" t="s">
-        <v>607</v>
+        <v>603</v>
       </c>
       <c r="Y107" s="56" t="s">
+        <v>587</v>
+      </c>
+      <c r="Z107" s="55" t="s">
+        <v>603</v>
+      </c>
+      <c r="AA107" s="56" t="s">
         <v>591</v>
       </c>
-      <c r="Z107" s="55" t="s">
-        <v>607</v>
-      </c>
-      <c r="AA107" s="56" t="s">
-        <v>595</v>
-      </c>
       <c r="AB107" s="55" t="s">
-        <v>607</v>
+        <v>603</v>
       </c>
       <c r="AC107" s="56" t="s">
-        <v>598</v>
+        <v>594</v>
       </c>
       <c r="AD107" s="55" t="s">
-        <v>607</v>
+        <v>603</v>
       </c>
       <c r="AE107" s="56" t="s">
-        <v>601</v>
+        <v>597</v>
       </c>
       <c r="AF107" s="55" t="s">
-        <v>607</v>
+        <v>603</v>
       </c>
       <c r="AG107" s="56" t="s">
-        <v>604</v>
+        <v>600</v>
       </c>
     </row>
     <row r="108" spans="1:33" ht="6" customHeight="1" x14ac:dyDescent="0.2">
@@ -20000,34 +20063,34 @@
         <v>181</v>
       </c>
       <c r="X108" s="55" t="s">
-        <v>607</v>
+        <v>603</v>
       </c>
       <c r="Y108" s="56" t="s">
+        <v>587</v>
+      </c>
+      <c r="Z108" s="55" t="s">
+        <v>603</v>
+      </c>
+      <c r="AA108" s="56" t="s">
         <v>591</v>
       </c>
-      <c r="Z108" s="55" t="s">
-        <v>607</v>
-      </c>
-      <c r="AA108" s="56" t="s">
-        <v>595</v>
-      </c>
       <c r="AB108" s="55" t="s">
-        <v>607</v>
+        <v>603</v>
       </c>
       <c r="AC108" s="56" t="s">
-        <v>598</v>
+        <v>594</v>
       </c>
       <c r="AD108" s="55" t="s">
-        <v>607</v>
+        <v>603</v>
       </c>
       <c r="AE108" s="56" t="s">
-        <v>601</v>
+        <v>597</v>
       </c>
       <c r="AF108" s="55" t="s">
-        <v>607</v>
+        <v>603</v>
       </c>
       <c r="AG108" s="56" t="s">
-        <v>604</v>
+        <v>600</v>
       </c>
     </row>
     <row r="109" spans="1:33" ht="6" customHeight="1" x14ac:dyDescent="0.2">
@@ -20101,34 +20164,34 @@
         <v>181</v>
       </c>
       <c r="X109" s="55" t="s">
-        <v>607</v>
+        <v>603</v>
       </c>
       <c r="Y109" s="56" t="s">
+        <v>587</v>
+      </c>
+      <c r="Z109" s="55" t="s">
+        <v>603</v>
+      </c>
+      <c r="AA109" s="56" t="s">
         <v>591</v>
       </c>
-      <c r="Z109" s="55" t="s">
-        <v>607</v>
-      </c>
-      <c r="AA109" s="56" t="s">
-        <v>595</v>
-      </c>
       <c r="AB109" s="55" t="s">
-        <v>607</v>
+        <v>603</v>
       </c>
       <c r="AC109" s="56" t="s">
-        <v>598</v>
+        <v>594</v>
       </c>
       <c r="AD109" s="55" t="s">
-        <v>607</v>
+        <v>603</v>
       </c>
       <c r="AE109" s="56" t="s">
-        <v>601</v>
+        <v>597</v>
       </c>
       <c r="AF109" s="55" t="s">
-        <v>607</v>
+        <v>603</v>
       </c>
       <c r="AG109" s="56" t="s">
-        <v>604</v>
+        <v>600</v>
       </c>
     </row>
     <row r="110" spans="1:33" ht="6" customHeight="1" x14ac:dyDescent="0.2">
@@ -20202,34 +20265,34 @@
         <v>181</v>
       </c>
       <c r="X110" s="55" t="s">
-        <v>607</v>
+        <v>603</v>
       </c>
       <c r="Y110" s="56" t="s">
+        <v>587</v>
+      </c>
+      <c r="Z110" s="55" t="s">
+        <v>603</v>
+      </c>
+      <c r="AA110" s="56" t="s">
         <v>591</v>
       </c>
-      <c r="Z110" s="55" t="s">
-        <v>607</v>
-      </c>
-      <c r="AA110" s="56" t="s">
-        <v>595</v>
-      </c>
       <c r="AB110" s="55" t="s">
-        <v>607</v>
+        <v>603</v>
       </c>
       <c r="AC110" s="56" t="s">
-        <v>598</v>
+        <v>594</v>
       </c>
       <c r="AD110" s="55" t="s">
-        <v>607</v>
+        <v>603</v>
       </c>
       <c r="AE110" s="56" t="s">
-        <v>601</v>
+        <v>597</v>
       </c>
       <c r="AF110" s="55" t="s">
-        <v>607</v>
+        <v>603</v>
       </c>
       <c r="AG110" s="56" t="s">
-        <v>604</v>
+        <v>600</v>
       </c>
     </row>
     <row r="111" spans="1:33" ht="6" customHeight="1" x14ac:dyDescent="0.2">
@@ -20303,34 +20366,34 @@
         <v>181</v>
       </c>
       <c r="X111" s="55" t="s">
-        <v>607</v>
+        <v>603</v>
       </c>
       <c r="Y111" s="56" t="s">
+        <v>587</v>
+      </c>
+      <c r="Z111" s="55" t="s">
+        <v>603</v>
+      </c>
+      <c r="AA111" s="56" t="s">
         <v>591</v>
       </c>
-      <c r="Z111" s="55" t="s">
-        <v>607</v>
-      </c>
-      <c r="AA111" s="56" t="s">
-        <v>595</v>
-      </c>
       <c r="AB111" s="55" t="s">
-        <v>607</v>
+        <v>603</v>
       </c>
       <c r="AC111" s="56" t="s">
-        <v>598</v>
+        <v>594</v>
       </c>
       <c r="AD111" s="55" t="s">
-        <v>607</v>
+        <v>603</v>
       </c>
       <c r="AE111" s="56" t="s">
-        <v>601</v>
+        <v>597</v>
       </c>
       <c r="AF111" s="55" t="s">
-        <v>607</v>
+        <v>603</v>
       </c>
       <c r="AG111" s="56" t="s">
-        <v>604</v>
+        <v>600</v>
       </c>
     </row>
     <row r="112" spans="1:33" ht="6" customHeight="1" x14ac:dyDescent="0.2">
@@ -20404,34 +20467,34 @@
         <v>181</v>
       </c>
       <c r="X112" s="55" t="s">
-        <v>607</v>
+        <v>603</v>
       </c>
       <c r="Y112" s="56" t="s">
+        <v>587</v>
+      </c>
+      <c r="Z112" s="55" t="s">
+        <v>603</v>
+      </c>
+      <c r="AA112" s="56" t="s">
         <v>591</v>
       </c>
-      <c r="Z112" s="55" t="s">
-        <v>607</v>
-      </c>
-      <c r="AA112" s="56" t="s">
-        <v>595</v>
-      </c>
       <c r="AB112" s="55" t="s">
-        <v>607</v>
+        <v>603</v>
       </c>
       <c r="AC112" s="56" t="s">
-        <v>598</v>
+        <v>594</v>
       </c>
       <c r="AD112" s="55" t="s">
-        <v>607</v>
+        <v>603</v>
       </c>
       <c r="AE112" s="56" t="s">
-        <v>601</v>
+        <v>597</v>
       </c>
       <c r="AF112" s="55" t="s">
-        <v>607</v>
+        <v>603</v>
       </c>
       <c r="AG112" s="56" t="s">
-        <v>604</v>
+        <v>600</v>
       </c>
     </row>
     <row r="113" spans="1:33" ht="6" customHeight="1" x14ac:dyDescent="0.2">
@@ -20505,34 +20568,34 @@
         <v>181</v>
       </c>
       <c r="X113" s="55" t="s">
-        <v>607</v>
+        <v>603</v>
       </c>
       <c r="Y113" s="56" t="s">
+        <v>587</v>
+      </c>
+      <c r="Z113" s="55" t="s">
+        <v>603</v>
+      </c>
+      <c r="AA113" s="56" t="s">
         <v>591</v>
       </c>
-      <c r="Z113" s="55" t="s">
-        <v>607</v>
-      </c>
-      <c r="AA113" s="56" t="s">
-        <v>595</v>
-      </c>
       <c r="AB113" s="55" t="s">
-        <v>607</v>
+        <v>603</v>
       </c>
       <c r="AC113" s="56" t="s">
-        <v>598</v>
+        <v>594</v>
       </c>
       <c r="AD113" s="55" t="s">
-        <v>607</v>
+        <v>603</v>
       </c>
       <c r="AE113" s="56" t="s">
-        <v>601</v>
+        <v>597</v>
       </c>
       <c r="AF113" s="55" t="s">
-        <v>607</v>
+        <v>603</v>
       </c>
       <c r="AG113" s="56" t="s">
-        <v>604</v>
+        <v>600</v>
       </c>
     </row>
     <row r="114" spans="1:33" ht="6" customHeight="1" x14ac:dyDescent="0.2">
@@ -20606,34 +20669,34 @@
         <v>181</v>
       </c>
       <c r="X114" s="55" t="s">
-        <v>607</v>
+        <v>603</v>
       </c>
       <c r="Y114" s="56" t="s">
+        <v>587</v>
+      </c>
+      <c r="Z114" s="55" t="s">
+        <v>603</v>
+      </c>
+      <c r="AA114" s="56" t="s">
         <v>591</v>
       </c>
-      <c r="Z114" s="55" t="s">
-        <v>607</v>
-      </c>
-      <c r="AA114" s="56" t="s">
-        <v>595</v>
-      </c>
       <c r="AB114" s="55" t="s">
-        <v>607</v>
+        <v>603</v>
       </c>
       <c r="AC114" s="56" t="s">
-        <v>598</v>
+        <v>594</v>
       </c>
       <c r="AD114" s="55" t="s">
-        <v>607</v>
+        <v>603</v>
       </c>
       <c r="AE114" s="56" t="s">
-        <v>601</v>
+        <v>597</v>
       </c>
       <c r="AF114" s="55" t="s">
-        <v>607</v>
+        <v>603</v>
       </c>
       <c r="AG114" s="56" t="s">
-        <v>604</v>
+        <v>600</v>
       </c>
     </row>
     <row r="115" spans="1:33" ht="6" customHeight="1" x14ac:dyDescent="0.2">
@@ -20707,34 +20770,34 @@
         <v>181</v>
       </c>
       <c r="X115" s="55" t="s">
-        <v>607</v>
+        <v>603</v>
       </c>
       <c r="Y115" s="56" t="s">
+        <v>587</v>
+      </c>
+      <c r="Z115" s="55" t="s">
+        <v>603</v>
+      </c>
+      <c r="AA115" s="56" t="s">
         <v>591</v>
       </c>
-      <c r="Z115" s="55" t="s">
-        <v>607</v>
-      </c>
-      <c r="AA115" s="56" t="s">
-        <v>595</v>
-      </c>
       <c r="AB115" s="55" t="s">
-        <v>607</v>
+        <v>603</v>
       </c>
       <c r="AC115" s="56" t="s">
-        <v>598</v>
+        <v>594</v>
       </c>
       <c r="AD115" s="55" t="s">
-        <v>607</v>
+        <v>603</v>
       </c>
       <c r="AE115" s="56" t="s">
-        <v>601</v>
+        <v>597</v>
       </c>
       <c r="AF115" s="55" t="s">
-        <v>607</v>
+        <v>603</v>
       </c>
       <c r="AG115" s="56" t="s">
-        <v>604</v>
+        <v>600</v>
       </c>
     </row>
     <row r="116" spans="1:33" ht="6" customHeight="1" x14ac:dyDescent="0.2">
@@ -20808,34 +20871,34 @@
         <v>181</v>
       </c>
       <c r="X116" s="55" t="s">
-        <v>607</v>
+        <v>603</v>
       </c>
       <c r="Y116" s="56" t="s">
+        <v>587</v>
+      </c>
+      <c r="Z116" s="55" t="s">
+        <v>603</v>
+      </c>
+      <c r="AA116" s="56" t="s">
         <v>591</v>
       </c>
-      <c r="Z116" s="55" t="s">
-        <v>607</v>
-      </c>
-      <c r="AA116" s="56" t="s">
-        <v>595</v>
-      </c>
       <c r="AB116" s="55" t="s">
-        <v>607</v>
+        <v>603</v>
       </c>
       <c r="AC116" s="56" t="s">
-        <v>598</v>
+        <v>594</v>
       </c>
       <c r="AD116" s="55" t="s">
-        <v>607</v>
+        <v>603</v>
       </c>
       <c r="AE116" s="56" t="s">
-        <v>601</v>
+        <v>597</v>
       </c>
       <c r="AF116" s="55" t="s">
-        <v>607</v>
+        <v>603</v>
       </c>
       <c r="AG116" s="56" t="s">
-        <v>604</v>
+        <v>600</v>
       </c>
     </row>
     <row r="117" spans="1:33" ht="6" customHeight="1" x14ac:dyDescent="0.2">
@@ -20909,34 +20972,34 @@
         <v>181</v>
       </c>
       <c r="X117" s="55" t="s">
-        <v>607</v>
+        <v>603</v>
       </c>
       <c r="Y117" s="56" t="s">
+        <v>587</v>
+      </c>
+      <c r="Z117" s="55" t="s">
+        <v>603</v>
+      </c>
+      <c r="AA117" s="56" t="s">
         <v>591</v>
       </c>
-      <c r="Z117" s="55" t="s">
-        <v>607</v>
-      </c>
-      <c r="AA117" s="56" t="s">
-        <v>595</v>
-      </c>
       <c r="AB117" s="55" t="s">
-        <v>607</v>
+        <v>603</v>
       </c>
       <c r="AC117" s="56" t="s">
-        <v>598</v>
+        <v>594</v>
       </c>
       <c r="AD117" s="55" t="s">
-        <v>607</v>
+        <v>603</v>
       </c>
       <c r="AE117" s="56" t="s">
-        <v>601</v>
+        <v>597</v>
       </c>
       <c r="AF117" s="55" t="s">
-        <v>607</v>
+        <v>603</v>
       </c>
       <c r="AG117" s="56" t="s">
-        <v>604</v>
+        <v>600</v>
       </c>
     </row>
     <row r="118" spans="1:33" ht="6" customHeight="1" x14ac:dyDescent="0.2">
@@ -21010,34 +21073,34 @@
         <v>181</v>
       </c>
       <c r="X118" s="55" t="s">
-        <v>607</v>
+        <v>603</v>
       </c>
       <c r="Y118" s="56" t="s">
+        <v>587</v>
+      </c>
+      <c r="Z118" s="55" t="s">
+        <v>603</v>
+      </c>
+      <c r="AA118" s="56" t="s">
         <v>591</v>
       </c>
-      <c r="Z118" s="55" t="s">
-        <v>607</v>
-      </c>
-      <c r="AA118" s="56" t="s">
-        <v>595</v>
-      </c>
       <c r="AB118" s="55" t="s">
-        <v>607</v>
+        <v>603</v>
       </c>
       <c r="AC118" s="56" t="s">
-        <v>598</v>
+        <v>594</v>
       </c>
       <c r="AD118" s="55" t="s">
-        <v>607</v>
+        <v>603</v>
       </c>
       <c r="AE118" s="56" t="s">
-        <v>601</v>
+        <v>597</v>
       </c>
       <c r="AF118" s="55" t="s">
-        <v>607</v>
+        <v>603</v>
       </c>
       <c r="AG118" s="56" t="s">
-        <v>604</v>
+        <v>600</v>
       </c>
     </row>
     <row r="119" spans="1:33" ht="6" customHeight="1" x14ac:dyDescent="0.2">
@@ -21111,34 +21174,34 @@
         <v>181</v>
       </c>
       <c r="X119" s="55" t="s">
-        <v>607</v>
+        <v>603</v>
       </c>
       <c r="Y119" s="56" t="s">
+        <v>587</v>
+      </c>
+      <c r="Z119" s="55" t="s">
+        <v>603</v>
+      </c>
+      <c r="AA119" s="56" t="s">
         <v>591</v>
       </c>
-      <c r="Z119" s="55" t="s">
-        <v>607</v>
-      </c>
-      <c r="AA119" s="56" t="s">
-        <v>595</v>
-      </c>
       <c r="AB119" s="55" t="s">
-        <v>607</v>
+        <v>603</v>
       </c>
       <c r="AC119" s="56" t="s">
-        <v>598</v>
+        <v>594</v>
       </c>
       <c r="AD119" s="55" t="s">
-        <v>607</v>
+        <v>603</v>
       </c>
       <c r="AE119" s="56" t="s">
-        <v>601</v>
+        <v>597</v>
       </c>
       <c r="AF119" s="55" t="s">
-        <v>607</v>
+        <v>603</v>
       </c>
       <c r="AG119" s="56" t="s">
-        <v>604</v>
+        <v>600</v>
       </c>
     </row>
     <row r="120" spans="1:33" ht="6" customHeight="1" x14ac:dyDescent="0.2">
@@ -21212,34 +21275,34 @@
         <v>181</v>
       </c>
       <c r="X120" s="55" t="s">
-        <v>607</v>
+        <v>603</v>
       </c>
       <c r="Y120" s="56" t="s">
+        <v>587</v>
+      </c>
+      <c r="Z120" s="55" t="s">
+        <v>603</v>
+      </c>
+      <c r="AA120" s="56" t="s">
         <v>591</v>
       </c>
-      <c r="Z120" s="55" t="s">
-        <v>607</v>
-      </c>
-      <c r="AA120" s="56" t="s">
-        <v>595</v>
-      </c>
       <c r="AB120" s="55" t="s">
-        <v>607</v>
+        <v>603</v>
       </c>
       <c r="AC120" s="56" t="s">
-        <v>598</v>
+        <v>594</v>
       </c>
       <c r="AD120" s="55" t="s">
-        <v>607</v>
+        <v>603</v>
       </c>
       <c r="AE120" s="56" t="s">
-        <v>601</v>
+        <v>597</v>
       </c>
       <c r="AF120" s="55" t="s">
-        <v>607</v>
+        <v>603</v>
       </c>
       <c r="AG120" s="56" t="s">
-        <v>604</v>
+        <v>600</v>
       </c>
     </row>
     <row r="121" spans="1:33" ht="6" customHeight="1" x14ac:dyDescent="0.2">
@@ -21313,34 +21376,34 @@
         <v>181</v>
       </c>
       <c r="X121" s="55" t="s">
-        <v>607</v>
+        <v>603</v>
       </c>
       <c r="Y121" s="56" t="s">
+        <v>587</v>
+      </c>
+      <c r="Z121" s="55" t="s">
+        <v>603</v>
+      </c>
+      <c r="AA121" s="56" t="s">
         <v>591</v>
       </c>
-      <c r="Z121" s="55" t="s">
-        <v>607</v>
-      </c>
-      <c r="AA121" s="56" t="s">
-        <v>595</v>
-      </c>
       <c r="AB121" s="55" t="s">
-        <v>607</v>
+        <v>603</v>
       </c>
       <c r="AC121" s="56" t="s">
-        <v>598</v>
+        <v>594</v>
       </c>
       <c r="AD121" s="55" t="s">
-        <v>607</v>
+        <v>603</v>
       </c>
       <c r="AE121" s="56" t="s">
-        <v>601</v>
+        <v>597</v>
       </c>
       <c r="AF121" s="55" t="s">
-        <v>607</v>
+        <v>603</v>
       </c>
       <c r="AG121" s="56" t="s">
-        <v>604</v>
+        <v>600</v>
       </c>
     </row>
     <row r="122" spans="1:33" ht="6" customHeight="1" x14ac:dyDescent="0.2">
@@ -21414,34 +21477,34 @@
         <v>181</v>
       </c>
       <c r="X122" s="55" t="s">
-        <v>607</v>
+        <v>603</v>
       </c>
       <c r="Y122" s="56" t="s">
+        <v>587</v>
+      </c>
+      <c r="Z122" s="55" t="s">
+        <v>603</v>
+      </c>
+      <c r="AA122" s="56" t="s">
         <v>591</v>
       </c>
-      <c r="Z122" s="55" t="s">
-        <v>607</v>
-      </c>
-      <c r="AA122" s="56" t="s">
-        <v>595</v>
-      </c>
       <c r="AB122" s="55" t="s">
-        <v>607</v>
+        <v>603</v>
       </c>
       <c r="AC122" s="56" t="s">
-        <v>598</v>
+        <v>594</v>
       </c>
       <c r="AD122" s="55" t="s">
-        <v>607</v>
+        <v>603</v>
       </c>
       <c r="AE122" s="56" t="s">
-        <v>601</v>
+        <v>597</v>
       </c>
       <c r="AF122" s="55" t="s">
-        <v>607</v>
+        <v>603</v>
       </c>
       <c r="AG122" s="56" t="s">
-        <v>604</v>
+        <v>600</v>
       </c>
     </row>
     <row r="123" spans="1:33" ht="6" customHeight="1" x14ac:dyDescent="0.2">
@@ -21515,34 +21578,34 @@
         <v>181</v>
       </c>
       <c r="X123" s="55" t="s">
-        <v>607</v>
+        <v>603</v>
       </c>
       <c r="Y123" s="56" t="s">
+        <v>587</v>
+      </c>
+      <c r="Z123" s="55" t="s">
+        <v>603</v>
+      </c>
+      <c r="AA123" s="56" t="s">
         <v>591</v>
       </c>
-      <c r="Z123" s="55" t="s">
-        <v>607</v>
-      </c>
-      <c r="AA123" s="56" t="s">
-        <v>595</v>
-      </c>
       <c r="AB123" s="55" t="s">
-        <v>607</v>
+        <v>603</v>
       </c>
       <c r="AC123" s="56" t="s">
-        <v>598</v>
+        <v>594</v>
       </c>
       <c r="AD123" s="55" t="s">
-        <v>607</v>
+        <v>603</v>
       </c>
       <c r="AE123" s="56" t="s">
-        <v>601</v>
+        <v>597</v>
       </c>
       <c r="AF123" s="55" t="s">
-        <v>607</v>
+        <v>603</v>
       </c>
       <c r="AG123" s="56" t="s">
-        <v>604</v>
+        <v>600</v>
       </c>
     </row>
     <row r="124" spans="1:33" ht="6" customHeight="1" x14ac:dyDescent="0.2">
@@ -21616,34 +21679,34 @@
         <v>181</v>
       </c>
       <c r="X124" s="55" t="s">
-        <v>607</v>
+        <v>603</v>
       </c>
       <c r="Y124" s="56" t="s">
+        <v>587</v>
+      </c>
+      <c r="Z124" s="55" t="s">
+        <v>603</v>
+      </c>
+      <c r="AA124" s="56" t="s">
         <v>591</v>
       </c>
-      <c r="Z124" s="55" t="s">
-        <v>607</v>
-      </c>
-      <c r="AA124" s="56" t="s">
-        <v>595</v>
-      </c>
       <c r="AB124" s="55" t="s">
-        <v>607</v>
+        <v>603</v>
       </c>
       <c r="AC124" s="56" t="s">
-        <v>598</v>
+        <v>594</v>
       </c>
       <c r="AD124" s="55" t="s">
-        <v>607</v>
+        <v>603</v>
       </c>
       <c r="AE124" s="56" t="s">
-        <v>601</v>
+        <v>597</v>
       </c>
       <c r="AF124" s="55" t="s">
-        <v>607</v>
+        <v>603</v>
       </c>
       <c r="AG124" s="56" t="s">
-        <v>604</v>
+        <v>600</v>
       </c>
     </row>
     <row r="125" spans="1:33" ht="6" customHeight="1" x14ac:dyDescent="0.2">
@@ -21717,34 +21780,34 @@
         <v>181</v>
       </c>
       <c r="X125" s="55" t="s">
-        <v>607</v>
+        <v>603</v>
       </c>
       <c r="Y125" s="56" t="s">
+        <v>587</v>
+      </c>
+      <c r="Z125" s="55" t="s">
+        <v>603</v>
+      </c>
+      <c r="AA125" s="56" t="s">
         <v>591</v>
       </c>
-      <c r="Z125" s="55" t="s">
-        <v>607</v>
-      </c>
-      <c r="AA125" s="56" t="s">
-        <v>595</v>
-      </c>
       <c r="AB125" s="55" t="s">
-        <v>607</v>
+        <v>603</v>
       </c>
       <c r="AC125" s="56" t="s">
-        <v>598</v>
+        <v>594</v>
       </c>
       <c r="AD125" s="55" t="s">
-        <v>607</v>
+        <v>603</v>
       </c>
       <c r="AE125" s="56" t="s">
-        <v>601</v>
+        <v>597</v>
       </c>
       <c r="AF125" s="55" t="s">
-        <v>607</v>
+        <v>603</v>
       </c>
       <c r="AG125" s="56" t="s">
-        <v>604</v>
+        <v>600</v>
       </c>
     </row>
     <row r="126" spans="1:33" ht="6" customHeight="1" x14ac:dyDescent="0.2">
@@ -21818,34 +21881,34 @@
         <v>181</v>
       </c>
       <c r="X126" s="55" t="s">
-        <v>607</v>
+        <v>603</v>
       </c>
       <c r="Y126" s="56" t="s">
+        <v>587</v>
+      </c>
+      <c r="Z126" s="55" t="s">
+        <v>603</v>
+      </c>
+      <c r="AA126" s="56" t="s">
         <v>591</v>
       </c>
-      <c r="Z126" s="55" t="s">
-        <v>607</v>
-      </c>
-      <c r="AA126" s="56" t="s">
-        <v>595</v>
-      </c>
       <c r="AB126" s="55" t="s">
-        <v>607</v>
+        <v>603</v>
       </c>
       <c r="AC126" s="56" t="s">
-        <v>598</v>
+        <v>594</v>
       </c>
       <c r="AD126" s="55" t="s">
-        <v>607</v>
+        <v>603</v>
       </c>
       <c r="AE126" s="56" t="s">
-        <v>601</v>
+        <v>597</v>
       </c>
       <c r="AF126" s="55" t="s">
-        <v>607</v>
+        <v>603</v>
       </c>
       <c r="AG126" s="56" t="s">
-        <v>604</v>
+        <v>600</v>
       </c>
     </row>
     <row r="127" spans="1:33" ht="6" customHeight="1" x14ac:dyDescent="0.2">
@@ -21919,34 +21982,34 @@
         <v>181</v>
       </c>
       <c r="X127" s="55" t="s">
-        <v>607</v>
+        <v>603</v>
       </c>
       <c r="Y127" s="56" t="s">
+        <v>587</v>
+      </c>
+      <c r="Z127" s="55" t="s">
+        <v>603</v>
+      </c>
+      <c r="AA127" s="56" t="s">
         <v>591</v>
       </c>
-      <c r="Z127" s="55" t="s">
-        <v>607</v>
-      </c>
-      <c r="AA127" s="56" t="s">
-        <v>595</v>
-      </c>
       <c r="AB127" s="55" t="s">
-        <v>607</v>
+        <v>603</v>
       </c>
       <c r="AC127" s="56" t="s">
-        <v>598</v>
+        <v>594</v>
       </c>
       <c r="AD127" s="55" t="s">
-        <v>607</v>
+        <v>603</v>
       </c>
       <c r="AE127" s="56" t="s">
-        <v>601</v>
+        <v>597</v>
       </c>
       <c r="AF127" s="55" t="s">
-        <v>607</v>
+        <v>603</v>
       </c>
       <c r="AG127" s="56" t="s">
-        <v>604</v>
+        <v>600</v>
       </c>
     </row>
     <row r="128" spans="1:33" ht="6" customHeight="1" x14ac:dyDescent="0.2">
@@ -22020,34 +22083,34 @@
         <v>181</v>
       </c>
       <c r="X128" s="55" t="s">
-        <v>607</v>
+        <v>603</v>
       </c>
       <c r="Y128" s="56" t="s">
+        <v>587</v>
+      </c>
+      <c r="Z128" s="55" t="s">
+        <v>603</v>
+      </c>
+      <c r="AA128" s="56" t="s">
         <v>591</v>
       </c>
-      <c r="Z128" s="55" t="s">
-        <v>607</v>
-      </c>
-      <c r="AA128" s="56" t="s">
-        <v>595</v>
-      </c>
       <c r="AB128" s="55" t="s">
-        <v>607</v>
+        <v>603</v>
       </c>
       <c r="AC128" s="56" t="s">
-        <v>598</v>
+        <v>594</v>
       </c>
       <c r="AD128" s="55" t="s">
-        <v>607</v>
+        <v>603</v>
       </c>
       <c r="AE128" s="56" t="s">
-        <v>601</v>
+        <v>597</v>
       </c>
       <c r="AF128" s="55" t="s">
-        <v>607</v>
+        <v>603</v>
       </c>
       <c r="AG128" s="56" t="s">
-        <v>604</v>
+        <v>600</v>
       </c>
     </row>
     <row r="129" spans="1:33" ht="6" customHeight="1" x14ac:dyDescent="0.2">
@@ -22121,34 +22184,34 @@
         <v>181</v>
       </c>
       <c r="X129" s="55" t="s">
-        <v>607</v>
+        <v>603</v>
       </c>
       <c r="Y129" s="56" t="s">
+        <v>587</v>
+      </c>
+      <c r="Z129" s="55" t="s">
+        <v>603</v>
+      </c>
+      <c r="AA129" s="56" t="s">
         <v>591</v>
       </c>
-      <c r="Z129" s="55" t="s">
-        <v>607</v>
-      </c>
-      <c r="AA129" s="56" t="s">
-        <v>595</v>
-      </c>
       <c r="AB129" s="55" t="s">
-        <v>607</v>
+        <v>603</v>
       </c>
       <c r="AC129" s="56" t="s">
-        <v>598</v>
+        <v>594</v>
       </c>
       <c r="AD129" s="55" t="s">
-        <v>607</v>
+        <v>603</v>
       </c>
       <c r="AE129" s="56" t="s">
-        <v>601</v>
+        <v>597</v>
       </c>
       <c r="AF129" s="55" t="s">
-        <v>607</v>
+        <v>603</v>
       </c>
       <c r="AG129" s="56" t="s">
-        <v>604</v>
+        <v>600</v>
       </c>
     </row>
     <row r="130" spans="1:33" ht="6" customHeight="1" x14ac:dyDescent="0.2">
@@ -22222,34 +22285,34 @@
         <v>181</v>
       </c>
       <c r="X130" s="55" t="s">
-        <v>607</v>
+        <v>603</v>
       </c>
       <c r="Y130" s="56" t="s">
+        <v>587</v>
+      </c>
+      <c r="Z130" s="55" t="s">
+        <v>603</v>
+      </c>
+      <c r="AA130" s="56" t="s">
         <v>591</v>
       </c>
-      <c r="Z130" s="55" t="s">
-        <v>607</v>
-      </c>
-      <c r="AA130" s="56" t="s">
-        <v>595</v>
-      </c>
       <c r="AB130" s="55" t="s">
-        <v>607</v>
+        <v>603</v>
       </c>
       <c r="AC130" s="56" t="s">
-        <v>598</v>
+        <v>594</v>
       </c>
       <c r="AD130" s="55" t="s">
-        <v>607</v>
+        <v>603</v>
       </c>
       <c r="AE130" s="56" t="s">
-        <v>601</v>
+        <v>597</v>
       </c>
       <c r="AF130" s="55" t="s">
-        <v>607</v>
+        <v>603</v>
       </c>
       <c r="AG130" s="56" t="s">
-        <v>604</v>
+        <v>600</v>
       </c>
     </row>
     <row r="131" spans="1:33" ht="6" customHeight="1" x14ac:dyDescent="0.2">
@@ -22323,34 +22386,34 @@
         <v>181</v>
       </c>
       <c r="X131" s="55" t="s">
-        <v>607</v>
+        <v>603</v>
       </c>
       <c r="Y131" s="56" t="s">
+        <v>587</v>
+      </c>
+      <c r="Z131" s="55" t="s">
+        <v>603</v>
+      </c>
+      <c r="AA131" s="56" t="s">
         <v>591</v>
       </c>
-      <c r="Z131" s="55" t="s">
-        <v>607</v>
-      </c>
-      <c r="AA131" s="56" t="s">
-        <v>595</v>
-      </c>
       <c r="AB131" s="55" t="s">
-        <v>607</v>
+        <v>603</v>
       </c>
       <c r="AC131" s="56" t="s">
-        <v>598</v>
+        <v>594</v>
       </c>
       <c r="AD131" s="55" t="s">
-        <v>607</v>
+        <v>603</v>
       </c>
       <c r="AE131" s="56" t="s">
-        <v>601</v>
+        <v>597</v>
       </c>
       <c r="AF131" s="55" t="s">
-        <v>607</v>
+        <v>603</v>
       </c>
       <c r="AG131" s="56" t="s">
-        <v>604</v>
+        <v>600</v>
       </c>
     </row>
     <row r="132" spans="1:33" ht="6" customHeight="1" x14ac:dyDescent="0.2">
@@ -22424,34 +22487,34 @@
         <v>181</v>
       </c>
       <c r="X132" s="55" t="s">
-        <v>607</v>
+        <v>603</v>
       </c>
       <c r="Y132" s="56" t="s">
+        <v>587</v>
+      </c>
+      <c r="Z132" s="55" t="s">
+        <v>603</v>
+      </c>
+      <c r="AA132" s="56" t="s">
         <v>591</v>
       </c>
-      <c r="Z132" s="55" t="s">
-        <v>607</v>
-      </c>
-      <c r="AA132" s="56" t="s">
-        <v>595</v>
-      </c>
       <c r="AB132" s="55" t="s">
-        <v>607</v>
+        <v>603</v>
       </c>
       <c r="AC132" s="56" t="s">
-        <v>598</v>
+        <v>594</v>
       </c>
       <c r="AD132" s="55" t="s">
-        <v>607</v>
+        <v>603</v>
       </c>
       <c r="AE132" s="56" t="s">
-        <v>601</v>
+        <v>597</v>
       </c>
       <c r="AF132" s="55" t="s">
-        <v>607</v>
+        <v>603</v>
       </c>
       <c r="AG132" s="56" t="s">
-        <v>604</v>
+        <v>600</v>
       </c>
     </row>
     <row r="133" spans="1:33" ht="6" customHeight="1" x14ac:dyDescent="0.2">
@@ -22525,34 +22588,34 @@
         <v>181</v>
       </c>
       <c r="X133" s="55" t="s">
-        <v>607</v>
+        <v>603</v>
       </c>
       <c r="Y133" s="56" t="s">
+        <v>587</v>
+      </c>
+      <c r="Z133" s="55" t="s">
+        <v>603</v>
+      </c>
+      <c r="AA133" s="56" t="s">
         <v>591</v>
       </c>
-      <c r="Z133" s="55" t="s">
-        <v>607</v>
-      </c>
-      <c r="AA133" s="56" t="s">
-        <v>595</v>
-      </c>
       <c r="AB133" s="55" t="s">
-        <v>607</v>
+        <v>603</v>
       </c>
       <c r="AC133" s="56" t="s">
-        <v>598</v>
+        <v>594</v>
       </c>
       <c r="AD133" s="55" t="s">
-        <v>607</v>
+        <v>603</v>
       </c>
       <c r="AE133" s="56" t="s">
-        <v>601</v>
+        <v>597</v>
       </c>
       <c r="AF133" s="55" t="s">
-        <v>607</v>
+        <v>603</v>
       </c>
       <c r="AG133" s="56" t="s">
-        <v>604</v>
+        <v>600</v>
       </c>
     </row>
     <row r="134" spans="1:33" ht="6" customHeight="1" x14ac:dyDescent="0.2">
@@ -22626,34 +22689,34 @@
         <v>181</v>
       </c>
       <c r="X134" s="55" t="s">
-        <v>607</v>
+        <v>603</v>
       </c>
       <c r="Y134" s="56" t="s">
+        <v>587</v>
+      </c>
+      <c r="Z134" s="55" t="s">
+        <v>603</v>
+      </c>
+      <c r="AA134" s="56" t="s">
         <v>591</v>
       </c>
-      <c r="Z134" s="55" t="s">
-        <v>607</v>
-      </c>
-      <c r="AA134" s="56" t="s">
-        <v>595</v>
-      </c>
       <c r="AB134" s="55" t="s">
-        <v>607</v>
+        <v>603</v>
       </c>
       <c r="AC134" s="56" t="s">
-        <v>598</v>
+        <v>594</v>
       </c>
       <c r="AD134" s="55" t="s">
-        <v>607</v>
+        <v>603</v>
       </c>
       <c r="AE134" s="56" t="s">
-        <v>601</v>
+        <v>597</v>
       </c>
       <c r="AF134" s="55" t="s">
-        <v>607</v>
+        <v>603</v>
       </c>
       <c r="AG134" s="56" t="s">
-        <v>604</v>
+        <v>600</v>
       </c>
     </row>
     <row r="135" spans="1:33" ht="6" customHeight="1" x14ac:dyDescent="0.2">
@@ -22727,34 +22790,34 @@
         <v>181</v>
       </c>
       <c r="X135" s="55" t="s">
-        <v>607</v>
+        <v>603</v>
       </c>
       <c r="Y135" s="56" t="s">
+        <v>587</v>
+      </c>
+      <c r="Z135" s="55" t="s">
+        <v>603</v>
+      </c>
+      <c r="AA135" s="56" t="s">
         <v>591</v>
       </c>
-      <c r="Z135" s="55" t="s">
-        <v>607</v>
-      </c>
-      <c r="AA135" s="56" t="s">
-        <v>595</v>
-      </c>
       <c r="AB135" s="55" t="s">
-        <v>607</v>
+        <v>603</v>
       </c>
       <c r="AC135" s="56" t="s">
-        <v>598</v>
+        <v>594</v>
       </c>
       <c r="AD135" s="55" t="s">
-        <v>607</v>
+        <v>603</v>
       </c>
       <c r="AE135" s="56" t="s">
-        <v>601</v>
+        <v>597</v>
       </c>
       <c r="AF135" s="55" t="s">
-        <v>607</v>
+        <v>603</v>
       </c>
       <c r="AG135" s="56" t="s">
-        <v>604</v>
+        <v>600</v>
       </c>
     </row>
     <row r="136" spans="1:33" ht="6" customHeight="1" x14ac:dyDescent="0.2">
@@ -22828,34 +22891,34 @@
         <v>181</v>
       </c>
       <c r="X136" s="55" t="s">
-        <v>607</v>
+        <v>603</v>
       </c>
       <c r="Y136" s="56" t="s">
+        <v>587</v>
+      </c>
+      <c r="Z136" s="55" t="s">
+        <v>603</v>
+      </c>
+      <c r="AA136" s="56" t="s">
         <v>591</v>
       </c>
-      <c r="Z136" s="55" t="s">
-        <v>607</v>
-      </c>
-      <c r="AA136" s="56" t="s">
-        <v>595</v>
-      </c>
       <c r="AB136" s="55" t="s">
-        <v>607</v>
+        <v>603</v>
       </c>
       <c r="AC136" s="56" t="s">
-        <v>598</v>
+        <v>594</v>
       </c>
       <c r="AD136" s="55" t="s">
-        <v>607</v>
+        <v>603</v>
       </c>
       <c r="AE136" s="56" t="s">
-        <v>601</v>
+        <v>597</v>
       </c>
       <c r="AF136" s="55" t="s">
-        <v>607</v>
+        <v>603</v>
       </c>
       <c r="AG136" s="56" t="s">
-        <v>604</v>
+        <v>600</v>
       </c>
     </row>
     <row r="137" spans="1:33" ht="6" customHeight="1" x14ac:dyDescent="0.2">
@@ -22929,34 +22992,34 @@
         <v>181</v>
       </c>
       <c r="X137" s="55" t="s">
-        <v>607</v>
+        <v>603</v>
       </c>
       <c r="Y137" s="56" t="s">
+        <v>587</v>
+      </c>
+      <c r="Z137" s="55" t="s">
+        <v>603</v>
+      </c>
+      <c r="AA137" s="56" t="s">
         <v>591</v>
       </c>
-      <c r="Z137" s="55" t="s">
-        <v>607</v>
-      </c>
-      <c r="AA137" s="56" t="s">
-        <v>595</v>
-      </c>
       <c r="AB137" s="55" t="s">
-        <v>607</v>
+        <v>603</v>
       </c>
       <c r="AC137" s="56" t="s">
-        <v>598</v>
+        <v>594</v>
       </c>
       <c r="AD137" s="55" t="s">
-        <v>607</v>
+        <v>603</v>
       </c>
       <c r="AE137" s="56" t="s">
-        <v>601</v>
+        <v>597</v>
       </c>
       <c r="AF137" s="55" t="s">
-        <v>607</v>
+        <v>603</v>
       </c>
       <c r="AG137" s="56" t="s">
-        <v>604</v>
+        <v>600</v>
       </c>
     </row>
     <row r="138" spans="1:33" ht="6" customHeight="1" x14ac:dyDescent="0.2">
@@ -23030,34 +23093,34 @@
         <v>181</v>
       </c>
       <c r="X138" s="55" t="s">
-        <v>607</v>
+        <v>603</v>
       </c>
       <c r="Y138" s="56" t="s">
+        <v>587</v>
+      </c>
+      <c r="Z138" s="55" t="s">
+        <v>603</v>
+      </c>
+      <c r="AA138" s="56" t="s">
         <v>591</v>
       </c>
-      <c r="Z138" s="55" t="s">
-        <v>607</v>
-      </c>
-      <c r="AA138" s="56" t="s">
-        <v>595</v>
-      </c>
       <c r="AB138" s="55" t="s">
-        <v>607</v>
+        <v>603</v>
       </c>
       <c r="AC138" s="56" t="s">
-        <v>598</v>
+        <v>594</v>
       </c>
       <c r="AD138" s="55" t="s">
-        <v>607</v>
+        <v>603</v>
       </c>
       <c r="AE138" s="56" t="s">
-        <v>601</v>
+        <v>597</v>
       </c>
       <c r="AF138" s="55" t="s">
-        <v>607</v>
+        <v>603</v>
       </c>
       <c r="AG138" s="56" t="s">
-        <v>604</v>
+        <v>600</v>
       </c>
     </row>
     <row r="139" spans="1:33" ht="6" customHeight="1" x14ac:dyDescent="0.2">
@@ -23131,34 +23194,34 @@
         <v>181</v>
       </c>
       <c r="X139" s="55" t="s">
-        <v>607</v>
+        <v>603</v>
       </c>
       <c r="Y139" s="56" t="s">
+        <v>587</v>
+      </c>
+      <c r="Z139" s="55" t="s">
+        <v>603</v>
+      </c>
+      <c r="AA139" s="56" t="s">
         <v>591</v>
       </c>
-      <c r="Z139" s="55" t="s">
-        <v>607</v>
-      </c>
-      <c r="AA139" s="56" t="s">
-        <v>595</v>
-      </c>
       <c r="AB139" s="55" t="s">
-        <v>607</v>
+        <v>603</v>
       </c>
       <c r="AC139" s="56" t="s">
-        <v>598</v>
+        <v>594</v>
       </c>
       <c r="AD139" s="55" t="s">
-        <v>607</v>
+        <v>603</v>
       </c>
       <c r="AE139" s="56" t="s">
-        <v>601</v>
+        <v>597</v>
       </c>
       <c r="AF139" s="55" t="s">
-        <v>607</v>
+        <v>603</v>
       </c>
       <c r="AG139" s="56" t="s">
-        <v>604</v>
+        <v>600</v>
       </c>
     </row>
     <row r="140" spans="1:33" ht="6" customHeight="1" x14ac:dyDescent="0.2">
@@ -23232,34 +23295,34 @@
         <v>181</v>
       </c>
       <c r="X140" s="55" t="s">
-        <v>607</v>
+        <v>603</v>
       </c>
       <c r="Y140" s="56" t="s">
+        <v>587</v>
+      </c>
+      <c r="Z140" s="55" t="s">
+        <v>603</v>
+      </c>
+      <c r="AA140" s="56" t="s">
         <v>591</v>
       </c>
-      <c r="Z140" s="55" t="s">
-        <v>607</v>
-      </c>
-      <c r="AA140" s="56" t="s">
-        <v>595</v>
-      </c>
       <c r="AB140" s="55" t="s">
-        <v>607</v>
+        <v>603</v>
       </c>
       <c r="AC140" s="56" t="s">
-        <v>598</v>
+        <v>594</v>
       </c>
       <c r="AD140" s="55" t="s">
-        <v>607</v>
+        <v>603</v>
       </c>
       <c r="AE140" s="56" t="s">
-        <v>601</v>
+        <v>597</v>
       </c>
       <c r="AF140" s="55" t="s">
-        <v>607</v>
+        <v>603</v>
       </c>
       <c r="AG140" s="56" t="s">
-        <v>604</v>
+        <v>600</v>
       </c>
     </row>
     <row r="141" spans="1:33" ht="6" customHeight="1" x14ac:dyDescent="0.2">
@@ -23333,34 +23396,34 @@
         <v>181</v>
       </c>
       <c r="X141" s="55" t="s">
-        <v>607</v>
+        <v>603</v>
       </c>
       <c r="Y141" s="56" t="s">
+        <v>587</v>
+      </c>
+      <c r="Z141" s="55" t="s">
+        <v>603</v>
+      </c>
+      <c r="AA141" s="56" t="s">
         <v>591</v>
       </c>
-      <c r="Z141" s="55" t="s">
-        <v>607</v>
-      </c>
-      <c r="AA141" s="56" t="s">
-        <v>595</v>
-      </c>
       <c r="AB141" s="55" t="s">
-        <v>607</v>
+        <v>603</v>
       </c>
       <c r="AC141" s="56" t="s">
-        <v>598</v>
+        <v>594</v>
       </c>
       <c r="AD141" s="55" t="s">
-        <v>607</v>
+        <v>603</v>
       </c>
       <c r="AE141" s="56" t="s">
-        <v>601</v>
+        <v>597</v>
       </c>
       <c r="AF141" s="55" t="s">
-        <v>607</v>
+        <v>603</v>
       </c>
       <c r="AG141" s="56" t="s">
-        <v>604</v>
+        <v>600</v>
       </c>
     </row>
     <row r="142" spans="1:33" ht="6" customHeight="1" x14ac:dyDescent="0.2">
@@ -23434,34 +23497,34 @@
         <v>181</v>
       </c>
       <c r="X142" s="55" t="s">
-        <v>607</v>
+        <v>603</v>
       </c>
       <c r="Y142" s="56" t="s">
+        <v>587</v>
+      </c>
+      <c r="Z142" s="55" t="s">
+        <v>603</v>
+      </c>
+      <c r="AA142" s="56" t="s">
         <v>591</v>
       </c>
-      <c r="Z142" s="55" t="s">
-        <v>607</v>
-      </c>
-      <c r="AA142" s="56" t="s">
-        <v>595</v>
-      </c>
       <c r="AB142" s="55" t="s">
-        <v>607</v>
+        <v>603</v>
       </c>
       <c r="AC142" s="56" t="s">
-        <v>598</v>
+        <v>594</v>
       </c>
       <c r="AD142" s="55" t="s">
-        <v>607</v>
+        <v>603</v>
       </c>
       <c r="AE142" s="56" t="s">
-        <v>601</v>
+        <v>597</v>
       </c>
       <c r="AF142" s="55" t="s">
-        <v>607</v>
+        <v>603</v>
       </c>
       <c r="AG142" s="56" t="s">
-        <v>604</v>
+        <v>600</v>
       </c>
     </row>
     <row r="143" spans="1:33" ht="6" customHeight="1" x14ac:dyDescent="0.2">
@@ -23535,34 +23598,34 @@
         <v>181</v>
       </c>
       <c r="X143" s="55" t="s">
-        <v>607</v>
+        <v>603</v>
       </c>
       <c r="Y143" s="56" t="s">
+        <v>587</v>
+      </c>
+      <c r="Z143" s="55" t="s">
+        <v>603</v>
+      </c>
+      <c r="AA143" s="56" t="s">
         <v>591</v>
       </c>
-      <c r="Z143" s="55" t="s">
-        <v>607</v>
-      </c>
-      <c r="AA143" s="56" t="s">
-        <v>595</v>
-      </c>
       <c r="AB143" s="55" t="s">
-        <v>607</v>
+        <v>603</v>
       </c>
       <c r="AC143" s="56" t="s">
-        <v>598</v>
+        <v>594</v>
       </c>
       <c r="AD143" s="55" t="s">
-        <v>607</v>
+        <v>603</v>
       </c>
       <c r="AE143" s="56" t="s">
-        <v>601</v>
+        <v>597</v>
       </c>
       <c r="AF143" s="55" t="s">
-        <v>607</v>
+        <v>603</v>
       </c>
       <c r="AG143" s="56" t="s">
-        <v>604</v>
+        <v>600</v>
       </c>
     </row>
     <row r="144" spans="1:33" ht="6" customHeight="1" x14ac:dyDescent="0.2">
@@ -23636,34 +23699,34 @@
         <v>181</v>
       </c>
       <c r="X144" s="55" t="s">
-        <v>607</v>
+        <v>603</v>
       </c>
       <c r="Y144" s="56" t="s">
+        <v>587</v>
+      </c>
+      <c r="Z144" s="55" t="s">
+        <v>603</v>
+      </c>
+      <c r="AA144" s="56" t="s">
         <v>591</v>
       </c>
-      <c r="Z144" s="55" t="s">
-        <v>607</v>
-      </c>
-      <c r="AA144" s="56" t="s">
-        <v>595</v>
-      </c>
       <c r="AB144" s="55" t="s">
-        <v>607</v>
+        <v>603</v>
       </c>
       <c r="AC144" s="56" t="s">
-        <v>598</v>
+        <v>594</v>
       </c>
       <c r="AD144" s="55" t="s">
-        <v>607</v>
+        <v>603</v>
       </c>
       <c r="AE144" s="56" t="s">
-        <v>601</v>
+        <v>597</v>
       </c>
       <c r="AF144" s="55" t="s">
-        <v>607</v>
+        <v>603</v>
       </c>
       <c r="AG144" s="56" t="s">
-        <v>604</v>
+        <v>600</v>
       </c>
     </row>
     <row r="145" spans="1:33" ht="6" customHeight="1" x14ac:dyDescent="0.2">
@@ -23737,34 +23800,34 @@
         <v>181</v>
       </c>
       <c r="X145" s="55" t="s">
-        <v>607</v>
+        <v>603</v>
       </c>
       <c r="Y145" s="56" t="s">
+        <v>587</v>
+      </c>
+      <c r="Z145" s="55" t="s">
+        <v>603</v>
+      </c>
+      <c r="AA145" s="56" t="s">
         <v>591</v>
       </c>
-      <c r="Z145" s="55" t="s">
-        <v>607</v>
-      </c>
-      <c r="AA145" s="56" t="s">
-        <v>595</v>
-      </c>
       <c r="AB145" s="55" t="s">
-        <v>607</v>
+        <v>603</v>
       </c>
       <c r="AC145" s="56" t="s">
-        <v>598</v>
+        <v>594</v>
       </c>
       <c r="AD145" s="55" t="s">
-        <v>607</v>
+        <v>603</v>
       </c>
       <c r="AE145" s="56" t="s">
-        <v>601</v>
+        <v>597</v>
       </c>
       <c r="AF145" s="55" t="s">
-        <v>607</v>
+        <v>603</v>
       </c>
       <c r="AG145" s="56" t="s">
-        <v>604</v>
+        <v>600</v>
       </c>
     </row>
     <row r="146" spans="1:33" ht="6" customHeight="1" x14ac:dyDescent="0.2">
@@ -23838,34 +23901,34 @@
         <v>181</v>
       </c>
       <c r="X146" s="55" t="s">
-        <v>607</v>
+        <v>603</v>
       </c>
       <c r="Y146" s="56" t="s">
+        <v>587</v>
+      </c>
+      <c r="Z146" s="55" t="s">
+        <v>603</v>
+      </c>
+      <c r="AA146" s="56" t="s">
         <v>591</v>
       </c>
-      <c r="Z146" s="55" t="s">
-        <v>607</v>
-      </c>
-      <c r="AA146" s="56" t="s">
-        <v>595</v>
-      </c>
       <c r="AB146" s="55" t="s">
-        <v>607</v>
+        <v>603</v>
       </c>
       <c r="AC146" s="56" t="s">
-        <v>598</v>
+        <v>594</v>
       </c>
       <c r="AD146" s="55" t="s">
-        <v>607</v>
+        <v>603</v>
       </c>
       <c r="AE146" s="56" t="s">
-        <v>601</v>
+        <v>597</v>
       </c>
       <c r="AF146" s="55" t="s">
-        <v>607</v>
+        <v>603</v>
       </c>
       <c r="AG146" s="56" t="s">
-        <v>604</v>
+        <v>600</v>
       </c>
     </row>
     <row r="147" spans="1:33" ht="6" customHeight="1" x14ac:dyDescent="0.2">
@@ -23939,34 +24002,34 @@
         <v>181</v>
       </c>
       <c r="X147" s="55" t="s">
-        <v>607</v>
+        <v>603</v>
       </c>
       <c r="Y147" s="56" t="s">
+        <v>587</v>
+      </c>
+      <c r="Z147" s="55" t="s">
+        <v>603</v>
+      </c>
+      <c r="AA147" s="56" t="s">
         <v>591</v>
       </c>
-      <c r="Z147" s="55" t="s">
-        <v>607</v>
-      </c>
-      <c r="AA147" s="56" t="s">
-        <v>595</v>
-      </c>
       <c r="AB147" s="55" t="s">
-        <v>607</v>
+        <v>603</v>
       </c>
       <c r="AC147" s="56" t="s">
-        <v>598</v>
+        <v>594</v>
       </c>
       <c r="AD147" s="55" t="s">
-        <v>607</v>
+        <v>603</v>
       </c>
       <c r="AE147" s="56" t="s">
-        <v>601</v>
+        <v>597</v>
       </c>
       <c r="AF147" s="55" t="s">
-        <v>607</v>
+        <v>603</v>
       </c>
       <c r="AG147" s="56" t="s">
-        <v>604</v>
+        <v>600</v>
       </c>
     </row>
     <row r="148" spans="1:33" ht="6" customHeight="1" x14ac:dyDescent="0.2">
@@ -24040,34 +24103,34 @@
         <v>181</v>
       </c>
       <c r="X148" s="55" t="s">
-        <v>607</v>
+        <v>603</v>
       </c>
       <c r="Y148" s="56" t="s">
+        <v>587</v>
+      </c>
+      <c r="Z148" s="55" t="s">
+        <v>603</v>
+      </c>
+      <c r="AA148" s="56" t="s">
         <v>591</v>
       </c>
-      <c r="Z148" s="55" t="s">
-        <v>607</v>
-      </c>
-      <c r="AA148" s="56" t="s">
-        <v>595</v>
-      </c>
       <c r="AB148" s="55" t="s">
-        <v>607</v>
+        <v>603</v>
       </c>
       <c r="AC148" s="56" t="s">
-        <v>598</v>
+        <v>594</v>
       </c>
       <c r="AD148" s="55" t="s">
-        <v>607</v>
+        <v>603</v>
       </c>
       <c r="AE148" s="56" t="s">
-        <v>601</v>
+        <v>597</v>
       </c>
       <c r="AF148" s="55" t="s">
-        <v>607</v>
+        <v>603</v>
       </c>
       <c r="AG148" s="56" t="s">
-        <v>604</v>
+        <v>600</v>
       </c>
     </row>
     <row r="149" spans="1:33" ht="6" customHeight="1" x14ac:dyDescent="0.2">
@@ -24141,34 +24204,34 @@
         <v>181</v>
       </c>
       <c r="X149" s="55" t="s">
-        <v>607</v>
+        <v>603</v>
       </c>
       <c r="Y149" s="56" t="s">
+        <v>587</v>
+      </c>
+      <c r="Z149" s="55" t="s">
+        <v>603</v>
+      </c>
+      <c r="AA149" s="56" t="s">
         <v>591</v>
       </c>
-      <c r="Z149" s="55" t="s">
-        <v>607</v>
-      </c>
-      <c r="AA149" s="56" t="s">
-        <v>595</v>
-      </c>
       <c r="AB149" s="55" t="s">
-        <v>607</v>
+        <v>603</v>
       </c>
       <c r="AC149" s="56" t="s">
-        <v>598</v>
+        <v>594</v>
       </c>
       <c r="AD149" s="55" t="s">
-        <v>607</v>
+        <v>603</v>
       </c>
       <c r="AE149" s="56" t="s">
-        <v>601</v>
+        <v>597</v>
       </c>
       <c r="AF149" s="55" t="s">
-        <v>607</v>
+        <v>603</v>
       </c>
       <c r="AG149" s="56" t="s">
-        <v>604</v>
+        <v>600</v>
       </c>
     </row>
     <row r="150" spans="1:33" ht="6" customHeight="1" x14ac:dyDescent="0.2">
@@ -24242,34 +24305,34 @@
         <v>181</v>
       </c>
       <c r="X150" s="55" t="s">
-        <v>607</v>
+        <v>603</v>
       </c>
       <c r="Y150" s="56" t="s">
+        <v>587</v>
+      </c>
+      <c r="Z150" s="55" t="s">
+        <v>603</v>
+      </c>
+      <c r="AA150" s="56" t="s">
         <v>591</v>
       </c>
-      <c r="Z150" s="55" t="s">
-        <v>607</v>
-      </c>
-      <c r="AA150" s="56" t="s">
-        <v>595</v>
-      </c>
       <c r="AB150" s="55" t="s">
-        <v>607</v>
+        <v>603</v>
       </c>
       <c r="AC150" s="56" t="s">
-        <v>598</v>
+        <v>594</v>
       </c>
       <c r="AD150" s="55" t="s">
-        <v>607</v>
+        <v>603</v>
       </c>
       <c r="AE150" s="56" t="s">
-        <v>601</v>
+        <v>597</v>
       </c>
       <c r="AF150" s="55" t="s">
-        <v>607</v>
+        <v>603</v>
       </c>
       <c r="AG150" s="56" t="s">
-        <v>604</v>
+        <v>600</v>
       </c>
     </row>
     <row r="151" spans="1:33" ht="6" customHeight="1" x14ac:dyDescent="0.2">
@@ -24343,34 +24406,34 @@
         <v>181</v>
       </c>
       <c r="X151" s="55" t="s">
-        <v>607</v>
+        <v>603</v>
       </c>
       <c r="Y151" s="56" t="s">
+        <v>587</v>
+      </c>
+      <c r="Z151" s="55" t="s">
+        <v>603</v>
+      </c>
+      <c r="AA151" s="56" t="s">
         <v>591</v>
       </c>
-      <c r="Z151" s="55" t="s">
-        <v>607</v>
-      </c>
-      <c r="AA151" s="56" t="s">
-        <v>595</v>
-      </c>
       <c r="AB151" s="55" t="s">
-        <v>607</v>
+        <v>603</v>
       </c>
       <c r="AC151" s="56" t="s">
-        <v>598</v>
+        <v>594</v>
       </c>
       <c r="AD151" s="55" t="s">
-        <v>607</v>
+        <v>603</v>
       </c>
       <c r="AE151" s="56" t="s">
-        <v>601</v>
+        <v>597</v>
       </c>
       <c r="AF151" s="55" t="s">
-        <v>607</v>
+        <v>603</v>
       </c>
       <c r="AG151" s="56" t="s">
-        <v>604</v>
+        <v>600</v>
       </c>
     </row>
     <row r="152" spans="1:33" ht="6" customHeight="1" x14ac:dyDescent="0.2">
@@ -24444,34 +24507,34 @@
         <v>181</v>
       </c>
       <c r="X152" s="55" t="s">
-        <v>607</v>
+        <v>603</v>
       </c>
       <c r="Y152" s="56" t="s">
+        <v>587</v>
+      </c>
+      <c r="Z152" s="55" t="s">
+        <v>603</v>
+      </c>
+      <c r="AA152" s="56" t="s">
         <v>591</v>
       </c>
-      <c r="Z152" s="55" t="s">
-        <v>607</v>
-      </c>
-      <c r="AA152" s="56" t="s">
-        <v>595</v>
-      </c>
       <c r="AB152" s="55" t="s">
-        <v>607</v>
+        <v>603</v>
       </c>
       <c r="AC152" s="56" t="s">
-        <v>598</v>
+        <v>594</v>
       </c>
       <c r="AD152" s="55" t="s">
-        <v>607</v>
+        <v>603</v>
       </c>
       <c r="AE152" s="56" t="s">
-        <v>601</v>
+        <v>597</v>
       </c>
       <c r="AF152" s="55" t="s">
-        <v>607</v>
+        <v>603</v>
       </c>
       <c r="AG152" s="56" t="s">
-        <v>604</v>
+        <v>600</v>
       </c>
     </row>
     <row r="153" spans="1:33" ht="6" customHeight="1" x14ac:dyDescent="0.2">
@@ -24545,34 +24608,34 @@
         <v>181</v>
       </c>
       <c r="X153" s="55" t="s">
-        <v>607</v>
+        <v>603</v>
       </c>
       <c r="Y153" s="56" t="s">
+        <v>587</v>
+      </c>
+      <c r="Z153" s="55" t="s">
+        <v>603</v>
+      </c>
+      <c r="AA153" s="56" t="s">
         <v>591</v>
       </c>
-      <c r="Z153" s="55" t="s">
-        <v>607</v>
-      </c>
-      <c r="AA153" s="56" t="s">
-        <v>595</v>
-      </c>
       <c r="AB153" s="55" t="s">
-        <v>607</v>
+        <v>603</v>
       </c>
       <c r="AC153" s="56" t="s">
-        <v>598</v>
+        <v>594</v>
       </c>
       <c r="AD153" s="55" t="s">
-        <v>607</v>
+        <v>603</v>
       </c>
       <c r="AE153" s="56" t="s">
-        <v>601</v>
+        <v>597</v>
       </c>
       <c r="AF153" s="55" t="s">
-        <v>607</v>
+        <v>603</v>
       </c>
       <c r="AG153" s="56" t="s">
-        <v>604</v>
+        <v>600</v>
       </c>
     </row>
     <row r="154" spans="1:33" ht="6" customHeight="1" x14ac:dyDescent="0.2">
@@ -24646,34 +24709,34 @@
         <v>181</v>
       </c>
       <c r="X154" s="55" t="s">
-        <v>607</v>
+        <v>603</v>
       </c>
       <c r="Y154" s="56" t="s">
+        <v>587</v>
+      </c>
+      <c r="Z154" s="55" t="s">
+        <v>603</v>
+      </c>
+      <c r="AA154" s="56" t="s">
         <v>591</v>
       </c>
-      <c r="Z154" s="55" t="s">
-        <v>607</v>
-      </c>
-      <c r="AA154" s="56" t="s">
-        <v>595</v>
-      </c>
       <c r="AB154" s="55" t="s">
-        <v>607</v>
+        <v>603</v>
       </c>
       <c r="AC154" s="56" t="s">
-        <v>598</v>
+        <v>594</v>
       </c>
       <c r="AD154" s="55" t="s">
-        <v>607</v>
+        <v>603</v>
       </c>
       <c r="AE154" s="56" t="s">
-        <v>601</v>
+        <v>597</v>
       </c>
       <c r="AF154" s="55" t="s">
-        <v>607</v>
+        <v>603</v>
       </c>
       <c r="AG154" s="56" t="s">
-        <v>604</v>
+        <v>600</v>
       </c>
     </row>
     <row r="155" spans="1:33" ht="6" customHeight="1" x14ac:dyDescent="0.2">
@@ -24747,34 +24810,34 @@
         <v>181</v>
       </c>
       <c r="X155" s="55" t="s">
-        <v>607</v>
+        <v>603</v>
       </c>
       <c r="Y155" s="56" t="s">
+        <v>587</v>
+      </c>
+      <c r="Z155" s="55" t="s">
+        <v>603</v>
+      </c>
+      <c r="AA155" s="56" t="s">
         <v>591</v>
       </c>
-      <c r="Z155" s="55" t="s">
-        <v>607</v>
-      </c>
-      <c r="AA155" s="56" t="s">
-        <v>595</v>
-      </c>
       <c r="AB155" s="55" t="s">
-        <v>607</v>
+        <v>603</v>
       </c>
       <c r="AC155" s="56" t="s">
-        <v>598</v>
+        <v>594</v>
       </c>
       <c r="AD155" s="55" t="s">
-        <v>607</v>
+        <v>603</v>
       </c>
       <c r="AE155" s="56" t="s">
-        <v>601</v>
+        <v>597</v>
       </c>
       <c r="AF155" s="55" t="s">
-        <v>607</v>
+        <v>603</v>
       </c>
       <c r="AG155" s="56" t="s">
-        <v>604</v>
+        <v>600</v>
       </c>
     </row>
     <row r="156" spans="1:33" ht="6" customHeight="1" x14ac:dyDescent="0.2">
@@ -24848,34 +24911,34 @@
         <v>181</v>
       </c>
       <c r="X156" s="55" t="s">
-        <v>607</v>
+        <v>603</v>
       </c>
       <c r="Y156" s="56" t="s">
+        <v>587</v>
+      </c>
+      <c r="Z156" s="55" t="s">
+        <v>603</v>
+      </c>
+      <c r="AA156" s="56" t="s">
         <v>591</v>
       </c>
-      <c r="Z156" s="55" t="s">
-        <v>607</v>
-      </c>
-      <c r="AA156" s="56" t="s">
-        <v>595</v>
-      </c>
       <c r="AB156" s="55" t="s">
-        <v>607</v>
+        <v>603</v>
       </c>
       <c r="AC156" s="56" t="s">
-        <v>598</v>
+        <v>594</v>
       </c>
       <c r="AD156" s="55" t="s">
-        <v>607</v>
+        <v>603</v>
       </c>
       <c r="AE156" s="56" t="s">
-        <v>601</v>
+        <v>597</v>
       </c>
       <c r="AF156" s="55" t="s">
-        <v>607</v>
+        <v>603</v>
       </c>
       <c r="AG156" s="56" t="s">
-        <v>604</v>
+        <v>600</v>
       </c>
     </row>
     <row r="157" spans="1:33" ht="6" customHeight="1" x14ac:dyDescent="0.2">
@@ -24949,34 +25012,34 @@
         <v>181</v>
       </c>
       <c r="X157" s="55" t="s">
-        <v>607</v>
+        <v>603</v>
       </c>
       <c r="Y157" s="56" t="s">
+        <v>587</v>
+      </c>
+      <c r="Z157" s="55" t="s">
+        <v>603</v>
+      </c>
+      <c r="AA157" s="56" t="s">
         <v>591</v>
       </c>
-      <c r="Z157" s="55" t="s">
-        <v>607</v>
-      </c>
-      <c r="AA157" s="56" t="s">
-        <v>595</v>
-      </c>
       <c r="AB157" s="55" t="s">
-        <v>607</v>
+        <v>603</v>
       </c>
       <c r="AC157" s="56" t="s">
-        <v>598</v>
+        <v>594</v>
       </c>
       <c r="AD157" s="55" t="s">
-        <v>607</v>
+        <v>603</v>
       </c>
       <c r="AE157" s="56" t="s">
-        <v>601</v>
+        <v>597</v>
       </c>
       <c r="AF157" s="55" t="s">
-        <v>607</v>
+        <v>603</v>
       </c>
       <c r="AG157" s="56" t="s">
-        <v>604</v>
+        <v>600</v>
       </c>
     </row>
     <row r="158" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -24984,10 +25047,10 @@
         <v>158</v>
       </c>
       <c r="B158" s="15" t="s">
-        <v>591</v>
+        <v>587</v>
       </c>
       <c r="C158" s="33" t="s">
-        <v>625</v>
+        <v>621</v>
       </c>
       <c r="D158" s="80" t="s">
         <v>181</v>
@@ -25011,26 +25074,26 @@
         <v>340</v>
       </c>
       <c r="K158" s="78" t="s">
-        <v>592</v>
+        <v>588</v>
       </c>
       <c r="L158" s="71" t="s">
         <v>412</v>
       </c>
       <c r="M158" s="46" t="s">
-        <v>593</v>
+        <v>589</v>
       </c>
       <c r="N158" s="47" t="s">
         <v>1</v>
       </c>
       <c r="O158" s="72" t="s">
-        <v>594</v>
+        <v>590</v>
       </c>
       <c r="P158" s="85" t="str">
         <f t="shared" ref="P158:P162" si="0">IF(Q158="null", "null", "método.revit")</f>
         <v>método.revit</v>
       </c>
       <c r="Q158" s="86" t="s">
-        <v>608</v>
+        <v>604</v>
       </c>
       <c r="R158" s="45" t="s">
         <v>181</v>
@@ -25051,34 +25114,34 @@
         <v>181</v>
       </c>
       <c r="X158" s="55" t="s">
-        <v>607</v>
+        <v>603</v>
       </c>
       <c r="Y158" s="56" t="s">
+        <v>587</v>
+      </c>
+      <c r="Z158" s="55" t="s">
+        <v>603</v>
+      </c>
+      <c r="AA158" s="56" t="s">
         <v>591</v>
       </c>
-      <c r="Z158" s="55" t="s">
-        <v>607</v>
-      </c>
-      <c r="AA158" s="56" t="s">
-        <v>595</v>
-      </c>
       <c r="AB158" s="55" t="s">
-        <v>607</v>
+        <v>603</v>
       </c>
       <c r="AC158" s="56" t="s">
-        <v>598</v>
+        <v>594</v>
       </c>
       <c r="AD158" s="55" t="s">
-        <v>607</v>
+        <v>603</v>
       </c>
       <c r="AE158" s="56" t="s">
-        <v>601</v>
+        <v>597</v>
       </c>
       <c r="AF158" s="55" t="s">
-        <v>607</v>
+        <v>603</v>
       </c>
       <c r="AG158" s="56" t="s">
-        <v>604</v>
+        <v>600</v>
       </c>
     </row>
     <row r="159" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -25086,10 +25149,10 @@
         <v>159</v>
       </c>
       <c r="B159" s="15" t="s">
-        <v>595</v>
+        <v>591</v>
       </c>
       <c r="C159" s="33" t="s">
-        <v>625</v>
+        <v>621</v>
       </c>
       <c r="D159" s="80" t="s">
         <v>181</v>
@@ -25113,26 +25176,26 @@
         <v>340</v>
       </c>
       <c r="K159" s="78" t="s">
-        <v>592</v>
+        <v>588</v>
       </c>
       <c r="L159" s="71" t="s">
         <v>412</v>
       </c>
       <c r="M159" s="46" t="s">
-        <v>596</v>
+        <v>592</v>
       </c>
       <c r="N159" s="47" t="s">
         <v>1</v>
       </c>
       <c r="O159" s="72" t="s">
-        <v>597</v>
+        <v>593</v>
       </c>
       <c r="P159" s="85" t="str">
         <f t="shared" si="0"/>
         <v>método.revit</v>
       </c>
       <c r="Q159" s="86" t="s">
-        <v>609</v>
+        <v>605</v>
       </c>
       <c r="R159" s="45" t="s">
         <v>181</v>
@@ -25153,34 +25216,34 @@
         <v>181</v>
       </c>
       <c r="X159" s="55" t="s">
-        <v>607</v>
+        <v>603</v>
       </c>
       <c r="Y159" s="56" t="s">
+        <v>587</v>
+      </c>
+      <c r="Z159" s="55" t="s">
+        <v>603</v>
+      </c>
+      <c r="AA159" s="56" t="s">
         <v>591</v>
       </c>
-      <c r="Z159" s="55" t="s">
-        <v>607</v>
-      </c>
-      <c r="AA159" s="56" t="s">
-        <v>595</v>
-      </c>
       <c r="AB159" s="55" t="s">
-        <v>607</v>
+        <v>603</v>
       </c>
       <c r="AC159" s="56" t="s">
-        <v>598</v>
+        <v>594</v>
       </c>
       <c r="AD159" s="55" t="s">
-        <v>607</v>
+        <v>603</v>
       </c>
       <c r="AE159" s="56" t="s">
-        <v>601</v>
+        <v>597</v>
       </c>
       <c r="AF159" s="55" t="s">
-        <v>607</v>
+        <v>603</v>
       </c>
       <c r="AG159" s="56" t="s">
-        <v>604</v>
+        <v>600</v>
       </c>
     </row>
     <row r="160" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -25188,10 +25251,10 @@
         <v>160</v>
       </c>
       <c r="B160" s="15" t="s">
-        <v>598</v>
+        <v>594</v>
       </c>
       <c r="C160" s="33" t="s">
-        <v>625</v>
+        <v>621</v>
       </c>
       <c r="D160" s="80" t="s">
         <v>181</v>
@@ -25215,26 +25278,26 @@
         <v>340</v>
       </c>
       <c r="K160" s="78" t="s">
-        <v>592</v>
+        <v>588</v>
       </c>
       <c r="L160" s="71" t="s">
         <v>412</v>
       </c>
       <c r="M160" s="46" t="s">
-        <v>599</v>
+        <v>595</v>
       </c>
       <c r="N160" s="47" t="s">
         <v>1</v>
       </c>
       <c r="O160" s="72" t="s">
-        <v>600</v>
+        <v>596</v>
       </c>
       <c r="P160" s="85" t="str">
         <f t="shared" si="0"/>
         <v>método.revit</v>
       </c>
       <c r="Q160" s="86" t="s">
-        <v>610</v>
+        <v>606</v>
       </c>
       <c r="R160" s="45" t="s">
         <v>181</v>
@@ -25255,34 +25318,34 @@
         <v>181</v>
       </c>
       <c r="X160" s="55" t="s">
-        <v>607</v>
+        <v>603</v>
       </c>
       <c r="Y160" s="56" t="s">
+        <v>587</v>
+      </c>
+      <c r="Z160" s="55" t="s">
+        <v>603</v>
+      </c>
+      <c r="AA160" s="56" t="s">
         <v>591</v>
       </c>
-      <c r="Z160" s="55" t="s">
-        <v>607</v>
-      </c>
-      <c r="AA160" s="56" t="s">
-        <v>595</v>
-      </c>
       <c r="AB160" s="55" t="s">
-        <v>607</v>
+        <v>603</v>
       </c>
       <c r="AC160" s="56" t="s">
-        <v>598</v>
+        <v>594</v>
       </c>
       <c r="AD160" s="55" t="s">
-        <v>607</v>
+        <v>603</v>
       </c>
       <c r="AE160" s="56" t="s">
-        <v>601</v>
+        <v>597</v>
       </c>
       <c r="AF160" s="55" t="s">
-        <v>607</v>
+        <v>603</v>
       </c>
       <c r="AG160" s="56" t="s">
-        <v>604</v>
+        <v>600</v>
       </c>
     </row>
     <row r="161" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -25290,10 +25353,10 @@
         <v>161</v>
       </c>
       <c r="B161" s="15" t="s">
-        <v>601</v>
+        <v>597</v>
       </c>
       <c r="C161" s="33" t="s">
-        <v>625</v>
+        <v>621</v>
       </c>
       <c r="D161" s="80" t="s">
         <v>181</v>
@@ -25317,26 +25380,26 @@
         <v>340</v>
       </c>
       <c r="K161" s="78" t="s">
-        <v>592</v>
+        <v>588</v>
       </c>
       <c r="L161" s="71" t="s">
         <v>412</v>
       </c>
       <c r="M161" s="46" t="s">
-        <v>602</v>
+        <v>598</v>
       </c>
       <c r="N161" s="47" t="s">
         <v>1</v>
       </c>
       <c r="O161" s="72" t="s">
-        <v>603</v>
+        <v>599</v>
       </c>
       <c r="P161" s="85" t="str">
         <f t="shared" si="0"/>
         <v>método.revit</v>
       </c>
       <c r="Q161" s="86" t="s">
-        <v>611</v>
+        <v>607</v>
       </c>
       <c r="R161" s="45" t="s">
         <v>181</v>
@@ -25357,34 +25420,34 @@
         <v>181</v>
       </c>
       <c r="X161" s="55" t="s">
-        <v>607</v>
+        <v>603</v>
       </c>
       <c r="Y161" s="56" t="s">
+        <v>587</v>
+      </c>
+      <c r="Z161" s="55" t="s">
+        <v>603</v>
+      </c>
+      <c r="AA161" s="56" t="s">
         <v>591</v>
       </c>
-      <c r="Z161" s="55" t="s">
-        <v>607</v>
-      </c>
-      <c r="AA161" s="56" t="s">
-        <v>595</v>
-      </c>
       <c r="AB161" s="55" t="s">
-        <v>607</v>
+        <v>603</v>
       </c>
       <c r="AC161" s="56" t="s">
-        <v>598</v>
+        <v>594</v>
       </c>
       <c r="AD161" s="55" t="s">
-        <v>607</v>
+        <v>603</v>
       </c>
       <c r="AE161" s="56" t="s">
-        <v>601</v>
+        <v>597</v>
       </c>
       <c r="AF161" s="55" t="s">
-        <v>607</v>
+        <v>603</v>
       </c>
       <c r="AG161" s="56" t="s">
-        <v>604</v>
+        <v>600</v>
       </c>
     </row>
     <row r="162" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -25392,10 +25455,10 @@
         <v>162</v>
       </c>
       <c r="B162" s="19" t="s">
-        <v>604</v>
+        <v>600</v>
       </c>
       <c r="C162" s="33" t="s">
-        <v>625</v>
+        <v>621</v>
       </c>
       <c r="D162" s="81" t="s">
         <v>181</v>
@@ -25419,26 +25482,26 @@
         <v>340</v>
       </c>
       <c r="K162" s="79" t="s">
-        <v>592</v>
+        <v>588</v>
       </c>
       <c r="L162" s="74" t="s">
         <v>412</v>
       </c>
       <c r="M162" s="73" t="s">
-        <v>605</v>
+        <v>601</v>
       </c>
       <c r="N162" s="75" t="s">
         <v>1</v>
       </c>
       <c r="O162" s="76" t="s">
-        <v>606</v>
+        <v>602</v>
       </c>
       <c r="P162" s="85" t="str">
         <f t="shared" si="0"/>
         <v>método.revit</v>
       </c>
       <c r="Q162" s="86" t="s">
-        <v>612</v>
+        <v>608</v>
       </c>
       <c r="R162" s="77" t="s">
         <v>181</v>
@@ -25459,147 +25522,147 @@
         <v>181</v>
       </c>
       <c r="X162" s="55" t="s">
-        <v>607</v>
+        <v>603</v>
       </c>
       <c r="Y162" s="56" t="s">
+        <v>587</v>
+      </c>
+      <c r="Z162" s="55" t="s">
+        <v>603</v>
+      </c>
+      <c r="AA162" s="56" t="s">
         <v>591</v>
       </c>
-      <c r="Z162" s="55" t="s">
-        <v>607</v>
-      </c>
-      <c r="AA162" s="56" t="s">
-        <v>595</v>
-      </c>
       <c r="AB162" s="55" t="s">
-        <v>607</v>
+        <v>603</v>
       </c>
       <c r="AC162" s="56" t="s">
-        <v>598</v>
+        <v>594</v>
       </c>
       <c r="AD162" s="55" t="s">
-        <v>607</v>
+        <v>603</v>
       </c>
       <c r="AE162" s="56" t="s">
-        <v>601</v>
+        <v>597</v>
       </c>
       <c r="AF162" s="55" t="s">
-        <v>607</v>
+        <v>603</v>
       </c>
       <c r="AG162" s="56" t="s">
-        <v>604</v>
+        <v>600</v>
       </c>
     </row>
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>
   <conditionalFormatting sqref="B1:B157 B163:B1048576">
-    <cfRule type="duplicateValues" dxfId="23" priority="29"/>
+    <cfRule type="duplicateValues" dxfId="30" priority="29"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B158:B162">
-    <cfRule type="duplicateValues" dxfId="22" priority="27"/>
-    <cfRule type="duplicateValues" dxfId="21" priority="28"/>
+    <cfRule type="duplicateValues" dxfId="29" priority="27"/>
+    <cfRule type="duplicateValues" dxfId="28" priority="28"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="R158:W162">
-    <cfRule type="cellIs" dxfId="20" priority="26" operator="equal">
+    <cfRule type="cellIs" dxfId="27" priority="26" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="T1:W157">
-    <cfRule type="cellIs" dxfId="19" priority="30" operator="equal">
+    <cfRule type="cellIs" dxfId="26" priority="30" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="T163:Z1048576">
-    <cfRule type="cellIs" dxfId="18" priority="13" operator="equal">
+    <cfRule type="cellIs" dxfId="25" priority="13" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="X1">
-    <cfRule type="cellIs" dxfId="17" priority="25" operator="equal">
+    <cfRule type="cellIs" dxfId="24" priority="25" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="X2:Y162">
-    <cfRule type="cellIs" dxfId="16" priority="18" operator="equal">
+    <cfRule type="cellIs" dxfId="23" priority="18" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="X1:AG1">
-    <cfRule type="cellIs" dxfId="15" priority="20" operator="equal">
+    <cfRule type="cellIs" dxfId="22" priority="20" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="Z1">
-    <cfRule type="cellIs" dxfId="14" priority="12" operator="equal">
+    <cfRule type="cellIs" dxfId="21" priority="12" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="Z2:Z162">
-    <cfRule type="cellIs" dxfId="13" priority="11" operator="equal">
+    <cfRule type="cellIs" dxfId="20" priority="11" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AA2:AA162">
-    <cfRule type="cellIs" dxfId="12" priority="17" operator="equal">
+    <cfRule type="cellIs" dxfId="19" priority="17" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AB1">
-    <cfRule type="cellIs" dxfId="11" priority="9" operator="equal">
+    <cfRule type="cellIs" dxfId="18" priority="9" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AB2:AB162">
-    <cfRule type="cellIs" dxfId="10" priority="8" operator="equal">
+    <cfRule type="cellIs" dxfId="17" priority="8" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AB163:AB1048576">
-    <cfRule type="cellIs" dxfId="9" priority="10" operator="equal">
+    <cfRule type="cellIs" dxfId="16" priority="10" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AC2:AC162">
-    <cfRule type="cellIs" dxfId="8" priority="16" operator="equal">
+    <cfRule type="cellIs" dxfId="15" priority="16" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AD1">
-    <cfRule type="cellIs" dxfId="7" priority="6" operator="equal">
+    <cfRule type="cellIs" dxfId="14" priority="6" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AD2:AD162">
-    <cfRule type="cellIs" dxfId="6" priority="5" operator="equal">
+    <cfRule type="cellIs" dxfId="13" priority="5" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AD163:AD1048576">
-    <cfRule type="cellIs" dxfId="5" priority="7" operator="equal">
+    <cfRule type="cellIs" dxfId="12" priority="7" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AE2:AE162">
-    <cfRule type="cellIs" dxfId="4" priority="15" operator="equal">
+    <cfRule type="cellIs" dxfId="11" priority="15" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AF1">
-    <cfRule type="cellIs" dxfId="3" priority="3" operator="equal">
+    <cfRule type="cellIs" dxfId="10" priority="3" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AF2:AF162">
-    <cfRule type="cellIs" dxfId="2" priority="2" operator="equal">
+    <cfRule type="cellIs" dxfId="9" priority="2" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AF163:AF1048576">
-    <cfRule type="cellIs" dxfId="1" priority="4" operator="equal">
+    <cfRule type="cellIs" dxfId="8" priority="4" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AG2:AG162">
-    <cfRule type="cellIs" dxfId="0" priority="14" operator="equal">
+    <cfRule type="cellIs" dxfId="7" priority="14" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
